--- a/TAZA/_документы/Штатка Фонда и проектного офиса.xlsx
+++ b/TAZA/_документы/Штатка Фонда и проектного офиса.xlsx
@@ -772,7 +772,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="461">
   <si>
     <t>№ п/п</t>
   </si>
@@ -1679,86 +1679,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>Жандилдаев</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Главный специалист / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
       <t>Омиртай</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Главный специалист / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Куандык</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Ведущий специалист / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Шербаева</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Ведущий специалист / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Абенов</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Руководитель/</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Тастан</t>
     </r>
   </si>
   <si>
@@ -1815,20 +1736,6 @@
     <t>Департамент цифрового развития</t>
   </si>
   <si>
-    <r>
-      <t>Главный специалист /PR - пресс-секретарь/</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Талгат</t>
-    </r>
-  </si>
-  <si>
     <t>II</t>
   </si>
   <si>
@@ -1947,21 +1854,6 @@
         <family val="1"/>
       </rPr>
       <t>Бекжанова</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Национальный Координатор Проектного офиса / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Серикжанова</t>
     </r>
   </si>
   <si>
@@ -2172,18 +2064,12 @@
     <t>Съёмка и монтаж роликов и документальных фильмов, YouTube-проект «Құндылық елшісі»</t>
   </si>
   <si>
-    <t>Работа со СМИ, пресс-релизы и пресс-мероприятия, официальные комментарии</t>
-  </si>
-  <si>
     <t>Коммуникационная стратегия, медиаплан, единый образ Tazabek, работа с амбассадорами</t>
   </si>
   <si>
     <t>Разработка и сопровождение платформы TAZA.KZ, AI- и GIS-инструменты</t>
   </si>
   <si>
-    <t>Цифровая платформа TAZA.KZ, интеграция TazaQazBot и госсистем, AI/GIS-мониторинг</t>
-  </si>
-  <si>
     <t>02.2027</t>
   </si>
   <si>
@@ -2481,9 +2367,6 @@
     <t>poiskraboty.kz – индекс зарплат в вакансиях, Астана 370 000 ₸: https://poiskraboty.kz/zarplaty</t>
   </si>
   <si>
-    <t>Проектный офис для Центральной Азии по изменению климата и зеленой энергетике</t>
-  </si>
-  <si>
     <t>Менеджер проектов</t>
   </si>
   <si>
@@ -2497,6 +2380,48 @@
   </si>
   <si>
     <t>Заместитель директора ПУ, менеджер проектов</t>
+  </si>
+  <si>
+    <t>Проектный офис для Центральной Азии по изменению климата и зеленой энергетике (Эксперттный совет)</t>
+  </si>
+  <si>
+    <t>Руководитель Проектного офиса / Серикжанова А.Т.</t>
+  </si>
+  <si>
+    <t>Главный специалист (проектный менеджер) / Қуандық Ж.Б.</t>
+  </si>
+  <si>
+    <t>Ведение проектов и закреплённых регионов, молодёжные проекты, мониторинг мероприятий</t>
+  </si>
+  <si>
+    <t>Главный специалист (проектный менеджер) / Жандилдаев Б.Б.</t>
+  </si>
+  <si>
+    <t>Координация регионов, взаимодействие с госорганами и общественными организациями</t>
+  </si>
+  <si>
+    <t>Ведущий специалист (проектный менеджер) / Шербаева Б.Б.</t>
+  </si>
+  <si>
+    <t>Ведение проектов календаря, планы и отчёты, взаимодействие с акиматами</t>
+  </si>
+  <si>
+    <t>Ведущий специалист (аналитик) / Абенов А.Д.</t>
+  </si>
+  <si>
+    <t>Аналитическое сопровождение проектов, методические материалы, отчётность</t>
+  </si>
+  <si>
+    <t>Руководитель (IT-специалист) / Тастан Н.Е.</t>
+  </si>
+  <si>
+    <t>Цифровая платформа TAZA.KZ, информационная безопасность, интеграция TazaQazBot и госсистем, AI/GIS-мониторинг</t>
+  </si>
+  <si>
+    <t>Главный специалист / PR-менеджер, пресс-секретарь / Талғат А.Т.</t>
+  </si>
+  <si>
+    <t>Работа со СМИ, пресс-релизы и пресс-мероприятия, тексты для соцсетей</t>
   </si>
 </sst>
 </file>
@@ -21177,7 +21102,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="H1" s="447" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="I1" s="447"/>
     </row>
@@ -21195,7 +21120,7 @@
     </row>
     <row r="3" spans="1:12" ht="15.75">
       <c r="A3" s="257" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B3" s="250"/>
       <c r="C3" s="250"/>
@@ -21229,28 +21154,28 @@
         <v>265</v>
       </c>
       <c r="E5" s="237" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="F5" s="238" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="G5" s="219" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="H5" s="221" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="I5" s="220" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="J5" s="220" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="K5" s="220" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="L5" s="220" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -21258,7 +21183,7 @@
         <v>262</v>
       </c>
       <c r="B6" s="202" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C6" s="201"/>
       <c r="D6" s="181">
@@ -21294,7 +21219,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="207" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C7" s="208" t="s">
         <v>269</v>
@@ -21321,13 +21246,13 @@
         <v>19200</v>
       </c>
       <c r="J7" s="177" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K7" s="283" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="L7" s="289" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="30">
@@ -21335,7 +21260,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="207" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C8" s="208" t="s">
         <v>274</v>
@@ -21362,13 +21287,13 @@
         <v>16800</v>
       </c>
       <c r="J8" s="177" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K8" s="283" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="L8" s="289" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="45">
@@ -21376,7 +21301,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="207" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="C9" s="208" t="s">
         <v>274</v>
@@ -21403,21 +21328,21 @@
         <v>16800</v>
       </c>
       <c r="J9" s="177" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K9" s="283" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="L9" s="289" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="201" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B10" s="202" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C10" s="201"/>
       <c r="D10" s="181">
@@ -21453,7 +21378,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="207" t="s">
-        <v>303</v>
+        <v>448</v>
       </c>
       <c r="C11" s="208" t="s">
         <v>274</v>
@@ -21480,21 +21405,21 @@
         <v>16800</v>
       </c>
       <c r="J11" s="177" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K11" s="283" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="L11" s="289" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="28.5">
       <c r="A12" s="203" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B12" s="204" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C12" s="205"/>
       <c r="D12" s="181">
@@ -21557,13 +21482,13 @@
         <v>15600</v>
       </c>
       <c r="J13" s="260" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K13" s="285" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="L13" s="290" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -21571,7 +21496,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="211" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C14" s="195" t="s">
         <v>272</v>
@@ -21598,13 +21523,13 @@
         <v>12000</v>
       </c>
       <c r="J14" s="177" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K14" s="283" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="L14" s="289" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="215" customFormat="1">
@@ -21612,7 +21537,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="259" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C15" s="258" t="s">
         <v>272</v>
@@ -21639,13 +21564,13 @@
         <v>12000</v>
       </c>
       <c r="J15" s="260" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K15" s="285" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="L15" s="290" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="215" customFormat="1">
@@ -21680,13 +21605,13 @@
         <v>8400</v>
       </c>
       <c r="J16" s="260" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K16" s="285" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="L16" s="290" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="215" customFormat="1" ht="30">
@@ -21694,7 +21619,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="259" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C17" s="258" t="s">
         <v>271</v>
@@ -21721,43 +21646,43 @@
         <v>8400</v>
       </c>
       <c r="J17" s="260" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K17" s="285" t="s">
+        <v>343</v>
+      </c>
+      <c r="L17" s="290" t="s">
         <v>352</v>
-      </c>
-      <c r="L17" s="290" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="42.75">
       <c r="A18" s="203"/>
       <c r="B18" s="204" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C18" s="205"/>
       <c r="D18" s="181">
-        <f>SUM(D19:D22)</f>
+        <f t="shared" ref="D18:I18" si="3">SUM(D19:D22)</f>
         <v>4</v>
       </c>
       <c r="E18" s="239">
-        <f>SUM(E19:E22)</f>
+        <f t="shared" si="3"/>
         <v>1500000</v>
       </c>
       <c r="F18" s="240">
-        <f>SUM(F19:F22)</f>
+        <f t="shared" si="3"/>
         <v>18000</v>
       </c>
       <c r="G18" s="222">
-        <f>SUM(G19:G22)</f>
+        <f t="shared" si="3"/>
         <v>4100000</v>
       </c>
       <c r="H18" s="223">
-        <f>SUM(H19:H22)</f>
+        <f t="shared" si="3"/>
         <v>3299100</v>
       </c>
       <c r="I18" s="181">
-        <f>SUM(I19:I22)</f>
+        <f t="shared" si="3"/>
         <v>49200</v>
       </c>
       <c r="J18" s="181"/>
@@ -21769,7 +21694,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="259" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C19" s="258" t="s">
         <v>270</v>
@@ -21796,13 +21721,13 @@
         <v>15600</v>
       </c>
       <c r="J19" s="260" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K19" s="285" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="L19" s="290" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="45">
@@ -21810,7 +21735,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="212" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C20" s="195" t="s">
         <v>272</v>
@@ -21835,13 +21760,13 @@
         <v>14400</v>
       </c>
       <c r="J20" s="177" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K20" s="283" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="L20" s="289" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="215" customFormat="1" ht="30">
@@ -21849,7 +21774,7 @@
         <v>3</v>
       </c>
       <c r="B21" s="259" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="C21" s="258" t="s">
         <v>272</v>
@@ -21874,13 +21799,13 @@
         <v>9600</v>
       </c>
       <c r="J21" s="260" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K21" s="285" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="L21" s="290" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="215" customFormat="1" ht="30">
@@ -21888,7 +21813,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="259" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C22" s="258" t="s">
         <v>272</v>
@@ -21913,21 +21838,21 @@
         <v>9600</v>
       </c>
       <c r="J22" s="260" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K22" s="285" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="L22" s="290" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="28.5">
       <c r="A23" s="171" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B23" s="180" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C23" s="179"/>
       <c r="D23" s="181">
@@ -21935,15 +21860,15 @@
         <v>10</v>
       </c>
       <c r="E23" s="239">
-        <f t="shared" ref="E23:I23" si="3">SUM(E24:E33)</f>
+        <f t="shared" ref="E23:I23" si="4">SUM(E24:E33)</f>
         <v>11100000</v>
       </c>
       <c r="F23" s="240">
-        <f t="shared" ref="F23" si="4">SUM(F24:F33)</f>
+        <f t="shared" ref="F23" si="5">SUM(F24:F33)</f>
         <v>133200</v>
       </c>
       <c r="G23" s="222">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9300000</v>
       </c>
       <c r="H23" s="223">
@@ -21951,7 +21876,7 @@
         <v>7495350</v>
       </c>
       <c r="I23" s="181">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>111600</v>
       </c>
       <c r="J23" s="181"/>
@@ -21975,28 +21900,28 @@
         <v>1500000</v>
       </c>
       <c r="F24" s="262">
-        <f t="shared" ref="F24:F33" si="5">D24*E24*12/1000</f>
+        <f t="shared" ref="F24:F33" si="6">D24*E24*12/1000</f>
         <v>18000</v>
       </c>
       <c r="G24" s="263">
         <v>1300000</v>
       </c>
       <c r="H24" s="264">
-        <f t="shared" ref="H24:H33" si="6">IF(G24&gt;0,G24-MIN(G24,4250000)*10%-MIN(G24,1700000)*2%-MAX(0,G24-MIN(G24,4250000)*10%-MIN(G24,1700000)*2%-129750)*10%,0)</f>
+        <f t="shared" ref="H24:H33" si="7">IF(G24&gt;0,G24-MIN(G24,4250000)*10%-MIN(G24,1700000)*2%-MAX(0,G24-MIN(G24,4250000)*10%-MIN(G24,1700000)*2%-129750)*10%,0)</f>
         <v>1042575</v>
       </c>
       <c r="I24" s="260">
-        <f t="shared" ref="I24:I33" si="7">D24*G24*12/1000</f>
+        <f t="shared" ref="I24:I33" si="8">D24*G24*12/1000</f>
         <v>15600</v>
       </c>
       <c r="J24" s="260" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K24" s="285" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="L24" s="290" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="30">
@@ -22004,7 +21929,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="183" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="C25" s="195" t="s">
         <v>272</v>
@@ -22016,28 +21941,28 @@
         <v>1200000</v>
       </c>
       <c r="F25" s="242">
-        <f t="shared" ref="F25" si="8">D25*E25*12/1000</f>
+        <f t="shared" ref="F25" si="9">D25*E25*12/1000</f>
         <v>14400</v>
       </c>
       <c r="G25" s="224">
         <v>1100000</v>
       </c>
       <c r="H25" s="225">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>884175</v>
       </c>
       <c r="I25" s="177">
-        <f t="shared" ref="I25" si="9">D25*G25*12/1000</f>
+        <f t="shared" ref="I25" si="10">D25*G25*12/1000</f>
         <v>13200</v>
       </c>
       <c r="J25" s="177" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K25" s="283" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="L25" s="289" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="30">
@@ -22045,7 +21970,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="183" t="s">
-        <v>281</v>
+        <v>449</v>
       </c>
       <c r="C26" s="195" t="s">
         <v>272</v>
@@ -22057,28 +21982,28 @@
         <v>1200000</v>
       </c>
       <c r="F26" s="242">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14400</v>
       </c>
       <c r="G26" s="224">
         <v>1000000</v>
       </c>
       <c r="H26" s="225">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>804975</v>
       </c>
       <c r="I26" s="177">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>12000</v>
       </c>
       <c r="J26" s="177" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K26" s="283" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="L26" s="289" t="s">
-        <v>355</v>
+        <v>450</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="215" customFormat="1" ht="30">
@@ -22086,7 +22011,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="265" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C27" s="258" t="s">
         <v>272</v>
@@ -22098,28 +22023,28 @@
         <v>1200000</v>
       </c>
       <c r="F27" s="262">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14400</v>
       </c>
       <c r="G27" s="263">
         <v>1000000</v>
       </c>
       <c r="H27" s="264">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>804975</v>
       </c>
       <c r="I27" s="260">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>12000</v>
       </c>
       <c r="J27" s="260" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K27" s="285" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="L27" s="290" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="30">
@@ -22127,7 +22052,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="183" t="s">
-        <v>279</v>
+        <v>451</v>
       </c>
       <c r="C28" s="195" t="s">
         <v>272</v>
@@ -22139,28 +22064,28 @@
         <v>1200000</v>
       </c>
       <c r="F28" s="242">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14400</v>
       </c>
       <c r="G28" s="224">
         <v>1000000</v>
       </c>
       <c r="H28" s="225">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>804975</v>
       </c>
       <c r="I28" s="177">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>12000</v>
       </c>
       <c r="J28" s="177" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K28" s="283" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="L28" s="289" t="s">
-        <v>355</v>
+        <v>452</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="30">
@@ -22168,7 +22093,7 @@
         <v>6</v>
       </c>
       <c r="B29" s="183" t="s">
-        <v>282</v>
+        <v>453</v>
       </c>
       <c r="C29" s="195" t="s">
         <v>272</v>
@@ -22180,28 +22105,28 @@
         <v>1200000</v>
       </c>
       <c r="F29" s="242">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14400</v>
       </c>
       <c r="G29" s="224">
         <v>1000000</v>
       </c>
       <c r="H29" s="225">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>804975</v>
       </c>
       <c r="I29" s="177">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>12000</v>
       </c>
       <c r="J29" s="177" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K29" s="283" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="L29" s="289" t="s">
-        <v>354</v>
+        <v>454</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="30">
@@ -22209,7 +22134,7 @@
         <v>7</v>
       </c>
       <c r="B30" s="183" t="s">
-        <v>283</v>
+        <v>455</v>
       </c>
       <c r="C30" s="196" t="s">
         <v>271</v>
@@ -22221,28 +22146,28 @@
         <v>900000</v>
       </c>
       <c r="F30" s="242">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10800</v>
       </c>
       <c r="G30" s="224">
         <v>700000</v>
       </c>
       <c r="H30" s="225">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>567375</v>
       </c>
       <c r="I30" s="177">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8400</v>
       </c>
       <c r="J30" s="177" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K30" s="283" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="L30" s="289" t="s">
-        <v>354</v>
+        <v>456</v>
       </c>
     </row>
     <row r="31" spans="1:12" s="215" customFormat="1" ht="30">
@@ -22250,7 +22175,7 @@
         <v>8</v>
       </c>
       <c r="B31" s="259" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C31" s="258" t="s">
         <v>271</v>
@@ -22262,28 +22187,28 @@
         <v>900000</v>
       </c>
       <c r="F31" s="262">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10800</v>
       </c>
       <c r="G31" s="263">
         <v>700000</v>
       </c>
       <c r="H31" s="264">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>567375</v>
       </c>
       <c r="I31" s="260">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8400</v>
       </c>
       <c r="J31" s="260" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K31" s="285" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="L31" s="290" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
     </row>
     <row r="32" spans="1:12" s="215" customFormat="1" ht="30">
@@ -22291,7 +22216,7 @@
         <v>9</v>
       </c>
       <c r="B32" s="259" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C32" s="258" t="s">
         <v>271</v>
@@ -22303,28 +22228,28 @@
         <v>900000</v>
       </c>
       <c r="F32" s="262">
-        <f t="shared" ref="F32" si="10">D32*E32*12/1000</f>
+        <f t="shared" ref="F32" si="11">D32*E32*12/1000</f>
         <v>10800</v>
       </c>
       <c r="G32" s="263">
         <v>700000</v>
       </c>
       <c r="H32" s="264">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>567375</v>
       </c>
       <c r="I32" s="260">
-        <f t="shared" ref="I32" si="11">D32*G32*12/1000</f>
+        <f t="shared" ref="I32" si="12">D32*G32*12/1000</f>
         <v>8400</v>
       </c>
       <c r="J32" s="260" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K32" s="285" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="L32" s="290" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
     </row>
     <row r="33" spans="1:12" s="215" customFormat="1" ht="30">
@@ -22332,7 +22257,7 @@
         <v>10</v>
       </c>
       <c r="B33" s="259" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C33" s="258" t="s">
         <v>271</v>
@@ -22344,60 +22269,60 @@
         <v>900000</v>
       </c>
       <c r="F33" s="262">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10800</v>
       </c>
       <c r="G33" s="263">
         <v>800000</v>
       </c>
       <c r="H33" s="264">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>646575</v>
       </c>
       <c r="I33" s="260">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9600</v>
       </c>
       <c r="J33" s="260" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K33" s="285" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="L33" s="290" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
     </row>
     <row r="34" spans="1:12" s="166" customFormat="1">
       <c r="A34" s="171" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B34" s="185" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C34" s="188"/>
       <c r="D34" s="186">
-        <f t="shared" ref="D34:I34" si="12">SUM(D35:D36)</f>
+        <f t="shared" ref="D34:I34" si="13">SUM(D35:D36)</f>
         <v>1</v>
       </c>
       <c r="E34" s="244">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1500000</v>
       </c>
       <c r="F34" s="245">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>18000</v>
       </c>
       <c r="G34" s="226">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1300000</v>
       </c>
       <c r="H34" s="227">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1042575</v>
       </c>
       <c r="I34" s="186">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15600</v>
       </c>
       <c r="J34" s="186"/>
@@ -22409,7 +22334,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="183" t="s">
-        <v>284</v>
+        <v>457</v>
       </c>
       <c r="C35" s="193" t="s">
         <v>270</v>
@@ -22436,13 +22361,13 @@
         <v>15600</v>
       </c>
       <c r="J35" s="177" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K35" s="283" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="L35" s="289" t="s">
-        <v>351</v>
+        <v>458</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="30">
@@ -22450,7 +22375,7 @@
         <v>2</v>
       </c>
       <c r="B36" s="267" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C36" s="266"/>
       <c r="D36" s="268"/>
@@ -22460,13 +22385,13 @@
       <c r="H36" s="272"/>
       <c r="I36" s="268"/>
       <c r="J36" s="268" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="K36" s="282" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="L36" s="291" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -22478,19 +22403,19 @@
       </c>
       <c r="C37" s="189"/>
       <c r="D37" s="173">
-        <f t="shared" ref="D37:I37" si="13">SUM(D38:D45)</f>
+        <f t="shared" ref="D37:I37" si="14">SUM(D38:D45)</f>
         <v>4</v>
       </c>
       <c r="E37" s="246">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4800000</v>
       </c>
       <c r="F37" s="247">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>57600</v>
       </c>
       <c r="G37" s="228">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4000000</v>
       </c>
       <c r="H37" s="229">
@@ -22498,7 +22423,7 @@
         <v>3219900</v>
       </c>
       <c r="I37" s="173">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>48000</v>
       </c>
       <c r="J37" s="173"/>
@@ -22510,7 +22435,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="176" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C38" s="194" t="s">
         <v>270</v>
@@ -22522,7 +22447,7 @@
         <v>1500000</v>
       </c>
       <c r="F38" s="242">
-        <f t="shared" ref="F38:F44" si="14">D38*E38*12/1000</f>
+        <f t="shared" ref="F38:F44" si="15">D38*E38*12/1000</f>
         <v>18000</v>
       </c>
       <c r="G38" s="230">
@@ -22533,17 +22458,17 @@
         <v>1042575</v>
       </c>
       <c r="I38" s="170">
-        <f t="shared" ref="I38:I44" si="15">D38*G38*12/1000</f>
+        <f t="shared" ref="I38:I44" si="16">D38*G38*12/1000</f>
         <v>15600</v>
       </c>
       <c r="J38" s="170" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K38" s="284" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="L38" s="292" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="30">
@@ -22551,7 +22476,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="211" t="s">
-        <v>291</v>
+        <v>459</v>
       </c>
       <c r="C39" s="195" t="s">
         <v>272</v>
@@ -22563,7 +22488,7 @@
         <v>1200000</v>
       </c>
       <c r="F39" s="242">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>14400</v>
       </c>
       <c r="G39" s="230">
@@ -22574,17 +22499,17 @@
         <v>804975</v>
       </c>
       <c r="I39" s="170">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>12000</v>
       </c>
       <c r="J39" s="170" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K39" s="284" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="L39" s="292" t="s">
-        <v>348</v>
+        <v>460</v>
       </c>
     </row>
     <row r="40" spans="1:12" s="213" customFormat="1" ht="30">
@@ -22592,7 +22517,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="274" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="C40" s="266" t="s">
         <v>272</v>
@@ -22604,13 +22529,13 @@
       <c r="H40" s="277"/>
       <c r="I40" s="275"/>
       <c r="J40" s="275" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="K40" s="281" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="L40" s="293" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="41" spans="1:12" s="213" customFormat="1" ht="30">
@@ -22618,7 +22543,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="274" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C41" s="266" t="s">
         <v>271</v>
@@ -22630,13 +22555,13 @@
       <c r="H41" s="277"/>
       <c r="I41" s="275"/>
       <c r="J41" s="275" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="K41" s="281" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="L41" s="293" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="42" spans="1:12" s="213" customFormat="1">
@@ -22644,7 +22569,7 @@
         <v>5</v>
       </c>
       <c r="B42" s="274" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C42" s="266" t="s">
         <v>271</v>
@@ -22656,13 +22581,13 @@
       <c r="H42" s="277"/>
       <c r="I42" s="275"/>
       <c r="J42" s="275" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="K42" s="281" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="L42" s="293" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="30">
@@ -22670,7 +22595,7 @@
         <v>6</v>
       </c>
       <c r="B43" s="176" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C43" s="195" t="s">
         <v>272</v>
@@ -22682,7 +22607,7 @@
         <v>1200000</v>
       </c>
       <c r="F43" s="242">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>14400</v>
       </c>
       <c r="G43" s="230">
@@ -22693,17 +22618,17 @@
         <v>804975</v>
       </c>
       <c r="I43" s="170">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>12000</v>
       </c>
       <c r="J43" s="170" t="s">
+        <v>330</v>
+      </c>
+      <c r="K43" s="284" t="s">
+        <v>327</v>
+      </c>
+      <c r="L43" s="292" t="s">
         <v>337</v>
-      </c>
-      <c r="K43" s="284" t="s">
-        <v>334</v>
-      </c>
-      <c r="L43" s="292" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="30">
@@ -22711,7 +22636,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="176" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C44" s="196" t="s">
         <v>271</v>
@@ -22723,7 +22648,7 @@
         <v>900000</v>
       </c>
       <c r="F44" s="242">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10800</v>
       </c>
       <c r="G44" s="224">
@@ -22734,17 +22659,17 @@
         <v>567375</v>
       </c>
       <c r="I44" s="177">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8400</v>
       </c>
       <c r="J44" s="177" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K44" s="283" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="L44" s="289" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
     </row>
     <row r="45" spans="1:12" s="213" customFormat="1" ht="30">
@@ -22752,7 +22677,7 @@
         <v>8</v>
       </c>
       <c r="B45" s="274" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C45" s="266" t="s">
         <v>271</v>
@@ -22766,13 +22691,13 @@
       <c r="H45" s="277"/>
       <c r="I45" s="275"/>
       <c r="J45" s="275" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="K45" s="281" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="L45" s="293" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -22780,31 +22705,31 @@
         <v>267</v>
       </c>
       <c r="B46" s="167" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C46" s="167"/>
       <c r="D46" s="167">
-        <f t="shared" ref="D46:I46" si="16">SUM(D47:D50)</f>
+        <f t="shared" ref="D46:I46" si="17">SUM(D47:D50)</f>
         <v>2</v>
       </c>
       <c r="E46" s="239">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2200000</v>
       </c>
       <c r="F46" s="240">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>26400</v>
       </c>
       <c r="G46" s="232">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2100000</v>
       </c>
       <c r="H46" s="233">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1689150</v>
       </c>
       <c r="I46" s="167">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>25200</v>
       </c>
       <c r="J46" s="167"/>
@@ -22816,7 +22741,7 @@
         <v>1</v>
       </c>
       <c r="B47" s="169" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="C47" s="194" t="s">
         <v>270</v>
@@ -22843,13 +22768,13 @@
         <v>16800</v>
       </c>
       <c r="J47" s="170" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K47" s="284" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="L47" s="292" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -22857,7 +22782,7 @@
         <v>2</v>
       </c>
       <c r="B48" s="216" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C48" s="195" t="s">
         <v>272</v>
@@ -22884,13 +22809,13 @@
         <v>8400</v>
       </c>
       <c r="J48" s="177" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K48" s="283" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="L48" s="289" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -22898,7 +22823,7 @@
         <v>3</v>
       </c>
       <c r="B49" s="279" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C49" s="266"/>
       <c r="D49" s="275"/>
@@ -22908,13 +22833,13 @@
       <c r="H49" s="272"/>
       <c r="I49" s="268"/>
       <c r="J49" s="268" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="K49" s="282" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="L49" s="291" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="30">
@@ -22922,7 +22847,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="279" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C50" s="266"/>
       <c r="D50" s="268"/>
@@ -22932,43 +22857,43 @@
       <c r="H50" s="277"/>
       <c r="I50" s="275"/>
       <c r="J50" s="275" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="K50" s="281" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="L50" s="293" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="15.75" thickBot="1">
       <c r="A51" s="198"/>
       <c r="B51" s="199" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C51" s="190"/>
       <c r="D51" s="174">
-        <f>D6+D10+D12+D18+D23+D34+D37+D46</f>
+        <f t="shared" ref="D51:I51" si="18">D6+D10+D12+D18+D23+D34+D37+D46</f>
         <v>30</v>
       </c>
       <c r="E51" s="248">
-        <f>E6+E10+E12+E18+E23+E34+E37+E46</f>
+        <f t="shared" si="18"/>
         <v>33700000</v>
       </c>
       <c r="F51" s="249">
-        <f>F6+F10+F12+F18+F23+F34+F37+F46</f>
+        <f t="shared" si="18"/>
         <v>404400</v>
       </c>
       <c r="G51" s="234">
-        <f>G6+G10+G12+G18+G23+G34+G37+G46</f>
+        <f t="shared" si="18"/>
         <v>31300000</v>
       </c>
       <c r="H51" s="236">
-        <f>H6+H10+H12+H18+H23+H34+H37+H46</f>
+        <f t="shared" si="18"/>
         <v>25178850</v>
       </c>
       <c r="I51" s="235">
-        <f>I6+I10+I12+I18+I23+I34+I37+I46</f>
+        <f t="shared" si="18"/>
         <v>375600</v>
       </c>
       <c r="J51" s="235"/>
@@ -22978,7 +22903,7 @@
     <row r="52" spans="1:12" ht="45">
       <c r="A52" s="256"/>
       <c r="B52" s="218" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="C52" s="187"/>
       <c r="D52" s="1"/>
@@ -22990,7 +22915,7 @@
     <row r="53" spans="1:12">
       <c r="A53" s="256"/>
       <c r="B53" s="280" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C53" s="191"/>
       <c r="D53" s="129"/>
@@ -31851,12 +31776,12 @@
   <sheetData>
     <row r="1" spans="1:6" ht="16.5">
       <c r="A1" s="296" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
       <c r="A3" s="449" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B3" s="449"/>
       <c r="C3" s="449"/>
@@ -31866,7 +31791,7 @@
     </row>
     <row r="4" spans="1:6" ht="44.1" customHeight="1">
       <c r="A4" s="449" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="B4" s="449"/>
       <c r="C4" s="449"/>
@@ -31876,7 +31801,7 @@
     </row>
     <row r="5" spans="1:6" ht="44.1" customHeight="1">
       <c r="A5" s="449" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B5" s="449"/>
       <c r="C5" s="449"/>
@@ -31886,7 +31811,7 @@
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1">
       <c r="A6" s="449" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B6" s="449"/>
       <c r="C6" s="449"/>
@@ -31896,7 +31821,7 @@
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
       <c r="A7" s="449" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="B7" s="449"/>
       <c r="C7" s="449"/>
@@ -31906,272 +31831,272 @@
     </row>
     <row r="9" spans="1:6" ht="25.5">
       <c r="A9" s="298" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B9" s="298" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="C9" s="298" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="D9" s="298" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="E9" s="298" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="F9" s="298" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="51">
       <c r="A10" s="297" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B10" s="299" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="C10" s="299" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="D10" s="297" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="E10" s="297" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="F10" s="297" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="76.5">
       <c r="A11" s="297" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="B11" s="299" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="C11" s="299" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="D11" s="297" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="E11" s="297" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="F11" s="297" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="51">
       <c r="A12" s="297" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="B12" s="299" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="C12" s="299" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D12" s="297" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="E12" s="297" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="F12" s="297" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="63.75">
       <c r="A13" s="297" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="B13" s="299" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="C13" s="299" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="D13" s="297" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="E13" s="297" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="F13" s="297" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="51">
       <c r="A14" s="297" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="B14" s="299" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="C14" s="299" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="D14" s="297" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="E14" s="297" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="F14" s="297" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="51">
       <c r="A15" s="297" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="B15" s="299" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="C15" s="299" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="D15" s="297" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="E15" s="297" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="F15" s="297" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="51">
       <c r="A16" s="297" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="B16" s="299" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="C16" s="299" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="D16" s="297" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="E16" s="297" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="F16" s="297" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="25.5">
       <c r="A17" s="297" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="B17" s="299" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="C17" s="299" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="D17" s="297" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="E17" s="297" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="F17" s="297" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="38.25">
       <c r="A18" s="297" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="B18" s="299" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="C18" s="299" t="s">
+        <v>410</v>
+      </c>
+      <c r="D18" s="297" t="s">
+        <v>418</v>
+      </c>
+      <c r="E18" s="297" t="s">
         <v>419</v>
       </c>
-      <c r="D18" s="297" t="s">
-        <v>427</v>
-      </c>
-      <c r="E18" s="297" t="s">
-        <v>428</v>
-      </c>
       <c r="F18" s="297" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="38.25">
       <c r="A19" s="297" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="B19" s="299" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="C19" s="299" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="D19" s="297" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="E19" s="297" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="F19" s="297" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="51">
       <c r="A20" s="297" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="B20" s="299" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="C20" s="299" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="D20" s="297" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="E20" s="297" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="F20" s="297" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="25.5">
       <c r="A21" s="297" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="B21" s="299" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="C21" s="299" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="D21" s="297" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="E21" s="297" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="F21" s="297" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="295" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="27" customHeight="1">
       <c r="A24" s="448" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="B24" s="448"/>
       <c r="C24" s="448"/>
@@ -32181,7 +32106,7 @@
     </row>
     <row r="25" spans="1:6" ht="27" customHeight="1">
       <c r="A25" s="448" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="B25" s="448"/>
       <c r="C25" s="448"/>
@@ -32191,7 +32116,7 @@
     </row>
     <row r="26" spans="1:6" ht="27" customHeight="1">
       <c r="A26" s="448" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="B26" s="448"/>
       <c r="C26" s="448"/>
@@ -32201,7 +32126,7 @@
     </row>
     <row r="27" spans="1:6" ht="27" customHeight="1">
       <c r="A27" s="448" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B27" s="448"/>
       <c r="C27" s="448"/>
@@ -32211,7 +32136,7 @@
     </row>
     <row r="28" spans="1:6" ht="27" customHeight="1">
       <c r="A28" s="448" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="B28" s="448"/>
       <c r="C28" s="448"/>
@@ -32221,7 +32146,7 @@
     </row>
     <row r="29" spans="1:6" ht="27" customHeight="1">
       <c r="A29" s="448" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="B29" s="448"/>
       <c r="C29" s="448"/>
@@ -32231,7 +32156,7 @@
     </row>
     <row r="30" spans="1:6" ht="27" customHeight="1">
       <c r="A30" s="448" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="B30" s="448"/>
       <c r="C30" s="448"/>
@@ -32241,7 +32166,7 @@
     </row>
     <row r="31" spans="1:6" ht="27" customHeight="1">
       <c r="A31" s="448" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="B31" s="448"/>
       <c r="C31" s="448"/>

--- a/TAZA/_документы/Штатка Фонда и проектного офиса.xlsx
+++ b/TAZA/_документы/Штатка Фонда и проектного офиса.xlsx
@@ -2385,43 +2385,43 @@
     <t>Проектный офис для Центральной Азии по изменению климата и зеленой энергетике (Эксперттный совет)</t>
   </si>
   <si>
-    <t>Руководитель Проектного офиса / Серикжанова А.Т.</t>
-  </si>
-  <si>
-    <t>Главный специалист (проектный менеджер) / Қуандық Ж.Б.</t>
-  </si>
-  <si>
     <t>Ведение проектов и закреплённых регионов, молодёжные проекты, мониторинг мероприятий</t>
   </si>
   <si>
-    <t>Главный специалист (проектный менеджер) / Жандилдаев Б.Б.</t>
-  </si>
-  <si>
     <t>Координация регионов, взаимодействие с госорганами и общественными организациями</t>
   </si>
   <si>
-    <t>Ведущий специалист (проектный менеджер) / Шербаева Б.Б.</t>
-  </si>
-  <si>
     <t>Ведение проектов календаря, планы и отчёты, взаимодействие с акиматами</t>
   </si>
   <si>
-    <t>Ведущий специалист (аналитик) / Абенов А.Д.</t>
-  </si>
-  <si>
     <t>Аналитическое сопровождение проектов, методические материалы, отчётность</t>
   </si>
   <si>
-    <t>Руководитель (IT-специалист) / Тастан Н.Е.</t>
-  </si>
-  <si>
     <t>Цифровая платформа TAZA.KZ, информационная безопасность, интеграция TazaQazBot и госсистем, AI/GIS-мониторинг</t>
   </si>
   <si>
-    <t>Главный специалист / PR-менеджер, пресс-секретарь / Талғат А.Т.</t>
-  </si>
-  <si>
     <t>Работа со СМИ, пресс-релизы и пресс-мероприятия, тексты для соцсетей</t>
+  </si>
+  <si>
+    <t>Руководитель Проектного офиса / Серикжанова Айгерим</t>
+  </si>
+  <si>
+    <t>Главный специалист (проектный менеджер) / Қуандық Жасұлан</t>
+  </si>
+  <si>
+    <t>Главный специалист (проектный менеджер) / Жандилдаев Бакдаулет</t>
+  </si>
+  <si>
+    <t>Ведущий специалист (проектный менеджер) / Шербаева Бибинур</t>
+  </si>
+  <si>
+    <t>Ведущий специалист (аналитик) / Абенов Алибек</t>
+  </si>
+  <si>
+    <t>Руководитель (IT-специалист) / Тастан Нұрбол</t>
+  </si>
+  <si>
+    <t>Главный специалист / PR-менеджер, пресс-секретарь / Талғат Айман</t>
   </si>
 </sst>
 </file>
@@ -5606,60 +5606,174 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="32" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="34" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="32" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="10" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="2" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="17" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="39" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="3" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="33" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="34" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="35" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5711,119 +5825,29 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="33" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="34" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="35" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="32" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="39" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="3" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="10" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="2" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="17" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="32" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="34" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5834,47 +5858,98 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="46" fillId="2" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="46" fillId="2" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="46" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5885,15 +5960,6 @@
     <xf numFmtId="49" fontId="46" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -5906,13 +5972,67 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5923,126 +6043,6 @@
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6384,7 +6384,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6442,7 +6442,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6497,7 +6497,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000004000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10274,26 +10274,26 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="301" t="s">
+      <c r="A2" s="309" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="301"/>
+      <c r="B2" s="309"/>
       <c r="C2" s="132" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="302" t="s">
+      <c r="A3" s="314" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="303"/>
+      <c r="B3" s="315"/>
       <c r="C3" s="133"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="302" t="s">
+      <c r="A4" s="314" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="303" t="s">
+      <c r="B4" s="315" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="133"/>
@@ -10306,24 +10306,24 @@
       <c r="C5" s="133"/>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
-      <c r="A6" s="302" t="s">
+      <c r="A6" s="314" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="303"/>
+      <c r="B6" s="315"/>
       <c r="C6" s="134"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
-      <c r="A7" s="302" t="s">
+      <c r="A7" s="314" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="303"/>
+      <c r="B7" s="315"/>
       <c r="C7" s="135"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="304" t="s">
+      <c r="A8" s="305" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="305"/>
+      <c r="B8" s="306"/>
       <c r="C8" s="131">
         <f>SUM(C3:C7)</f>
         <v>0</v>
@@ -10333,17 +10333,17 @@
       <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="306" t="s">
+      <c r="A10" s="316" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="306"/>
-      <c r="C10" s="306"/>
+      <c r="B10" s="316"/>
+      <c r="C10" s="316"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="301" t="s">
+      <c r="A11" s="309" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="301"/>
+      <c r="B11" s="309"/>
       <c r="C11" s="132" t="s">
         <v>1</v>
       </c>
@@ -10370,10 +10370,10 @@
       <c r="C14" s="136"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="304" t="s">
+      <c r="A15" s="305" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="305"/>
+      <c r="B15" s="306"/>
       <c r="C15" s="130">
         <f>SUM(C12:C14)</f>
         <v>0</v>
@@ -10403,10 +10403,10 @@
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="301" t="s">
+      <c r="A20" s="309" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="301"/>
+      <c r="B20" s="309"/>
       <c r="C20" s="132" t="s">
         <v>1</v>
       </c>
@@ -10451,17 +10451,17 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="309" t="s">
+      <c r="A26" s="310" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="310"/>
-      <c r="C26" s="311"/>
+      <c r="B26" s="311"/>
+      <c r="C26" s="312"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="301" t="s">
+      <c r="A27" s="309" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="301"/>
+      <c r="B27" s="309"/>
       <c r="C27" s="138"/>
     </row>
     <row r="28" spans="1:4">
@@ -10478,17 +10478,17 @@
       <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="312" t="s">
+      <c r="A30" s="313" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="312"/>
+      <c r="B30" s="313"/>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="301" t="s">
+      <c r="A31" s="309" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="301"/>
+      <c r="B31" s="309"/>
       <c r="C31" s="132" t="s">
         <v>1</v>
       </c>
@@ -10525,8 +10525,8 @@
       <c r="D35" s="3"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="313"/>
-      <c r="B36" s="314"/>
+      <c r="A36" s="301"/>
+      <c r="B36" s="302"/>
       <c r="C36" s="144">
         <f>SUM(C32:C35)</f>
         <v>0</v>
@@ -10538,10 +10538,10 @@
       <c r="C37" s="8"/>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="315" t="s">
+      <c r="A38" s="303" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="316"/>
+      <c r="B38" s="304"/>
       <c r="C38" s="145">
         <f>C28-C36</f>
         <v>0</v>
@@ -10564,11 +10564,18 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A17:B17"/>
@@ -10581,18 +10588,11 @@
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A38:B38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10860,11 +10860,11 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1"/>
-      <c r="B19" s="301" t="s">
+      <c r="B19" s="309" t="s">
         <v>259</v>
       </c>
-      <c r="C19" s="301"/>
-      <c r="D19" s="301"/>
+      <c r="C19" s="309"/>
+      <c r="D19" s="309"/>
       <c r="E19" s="162" t="e">
         <f>E15/E18</f>
         <v>#REF!</v>
@@ -10941,17 +10941,17 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="319" t="s">
+      <c r="B1" s="357" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="319"/>
-      <c r="D1" s="319"/>
-      <c r="E1" s="319"/>
-      <c r="F1" s="319"/>
-      <c r="G1" s="319"/>
-      <c r="H1" s="319"/>
-      <c r="I1" s="319"/>
-      <c r="J1" s="319"/>
+      <c r="C1" s="357"/>
+      <c r="D1" s="357"/>
+      <c r="E1" s="357"/>
+      <c r="F1" s="357"/>
+      <c r="G1" s="357"/>
+      <c r="H1" s="357"/>
+      <c r="I1" s="357"/>
+      <c r="J1" s="357"/>
       <c r="K1" s="85"/>
       <c r="O1" s="51"/>
     </row>
@@ -10989,17 +10989,17 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="320" t="s">
+      <c r="B3" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="320"/>
-      <c r="D3" s="320"/>
-      <c r="E3" s="320"/>
-      <c r="F3" s="320"/>
-      <c r="G3" s="320"/>
-      <c r="H3" s="320"/>
-      <c r="I3" s="320"/>
-      <c r="J3" s="320"/>
+      <c r="C3" s="358"/>
+      <c r="D3" s="358"/>
+      <c r="E3" s="358"/>
+      <c r="F3" s="358"/>
+      <c r="G3" s="358"/>
+      <c r="H3" s="358"/>
+      <c r="I3" s="358"/>
+      <c r="J3" s="358"/>
       <c r="K3" s="88"/>
       <c r="O3" s="51"/>
     </row>
@@ -11007,17 +11007,17 @@
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="321" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="321"/>
-      <c r="D4" s="321"/>
-      <c r="E4" s="321"/>
-      <c r="F4" s="321"/>
-      <c r="G4" s="321"/>
-      <c r="H4" s="321"/>
-      <c r="I4" s="321"/>
-      <c r="J4" s="321"/>
+      <c r="B4" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="359"/>
+      <c r="D4" s="359"/>
+      <c r="E4" s="359"/>
+      <c r="F4" s="359"/>
+      <c r="G4" s="359"/>
+      <c r="H4" s="359"/>
+      <c r="I4" s="359"/>
+      <c r="J4" s="359"/>
       <c r="K4" s="89"/>
       <c r="O4" s="51"/>
     </row>
@@ -11025,17 +11025,17 @@
       <c r="A5" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="322" t="s">
+      <c r="B5" s="360" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="322"/>
-      <c r="D5" s="322"/>
-      <c r="E5" s="322"/>
-      <c r="F5" s="322"/>
-      <c r="G5" s="322"/>
-      <c r="H5" s="322"/>
-      <c r="I5" s="322"/>
-      <c r="J5" s="322"/>
+      <c r="C5" s="360"/>
+      <c r="D5" s="360"/>
+      <c r="E5" s="360"/>
+      <c r="F5" s="360"/>
+      <c r="G5" s="360"/>
+      <c r="H5" s="360"/>
+      <c r="I5" s="360"/>
+      <c r="J5" s="360"/>
       <c r="K5" s="90"/>
       <c r="O5" s="51"/>
     </row>
@@ -11043,17 +11043,17 @@
       <c r="A6" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="322" t="s">
+      <c r="B6" s="360" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="322"/>
-      <c r="D6" s="322"/>
-      <c r="E6" s="322"/>
-      <c r="F6" s="322"/>
-      <c r="G6" s="322"/>
-      <c r="H6" s="322"/>
-      <c r="I6" s="322"/>
-      <c r="J6" s="322"/>
+      <c r="C6" s="360"/>
+      <c r="D6" s="360"/>
+      <c r="E6" s="360"/>
+      <c r="F6" s="360"/>
+      <c r="G6" s="360"/>
+      <c r="H6" s="360"/>
+      <c r="I6" s="360"/>
+      <c r="J6" s="360"/>
       <c r="K6" s="90"/>
       <c r="O6" s="51"/>
     </row>
@@ -11061,15 +11061,15 @@
       <c r="A7" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="323" t="s">
+      <c r="B7" s="361" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="323"/>
-      <c r="D7" s="323"/>
-      <c r="E7" s="323"/>
-      <c r="F7" s="323"/>
-      <c r="G7" s="323"/>
-      <c r="H7" s="323"/>
+      <c r="C7" s="361"/>
+      <c r="D7" s="361"/>
+      <c r="E7" s="361"/>
+      <c r="F7" s="361"/>
+      <c r="G7" s="361"/>
+      <c r="H7" s="361"/>
       <c r="I7" s="91"/>
       <c r="J7" s="71" t="s">
         <v>50</v>
@@ -11095,51 +11095,51 @@
       <c r="A22" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="324" t="s">
+      <c r="B22" s="362" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="327" t="s">
+      <c r="C22" s="365" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="328"/>
-      <c r="E22" s="328"/>
-      <c r="F22" s="328"/>
-      <c r="G22" s="329"/>
+      <c r="D22" s="366"/>
+      <c r="E22" s="366"/>
+      <c r="F22" s="366"/>
+      <c r="G22" s="367"/>
       <c r="H22" s="93"/>
-      <c r="I22" s="328" t="s">
+      <c r="I22" s="366" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="329"/>
+      <c r="J22" s="367"/>
       <c r="K22" s="94"/>
     </row>
     <row r="23" spans="1:16" ht="12" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="325"/>
-      <c r="C23" s="330"/>
-      <c r="D23" s="331"/>
-      <c r="E23" s="331"/>
-      <c r="F23" s="331"/>
-      <c r="G23" s="332"/>
+      <c r="B23" s="363"/>
+      <c r="C23" s="368"/>
+      <c r="D23" s="369"/>
+      <c r="E23" s="369"/>
+      <c r="F23" s="369"/>
+      <c r="G23" s="370"/>
       <c r="H23" s="95"/>
-      <c r="I23" s="331"/>
-      <c r="J23" s="332"/>
+      <c r="I23" s="369"/>
+      <c r="J23" s="370"/>
       <c r="K23" s="94"/>
     </row>
     <row r="24" spans="1:16" ht="24" customHeight="1">
       <c r="A24" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="326"/>
-      <c r="C24" s="333"/>
-      <c r="D24" s="334"/>
-      <c r="E24" s="334"/>
-      <c r="F24" s="334"/>
-      <c r="G24" s="335"/>
+      <c r="B24" s="364"/>
+      <c r="C24" s="371"/>
+      <c r="D24" s="372"/>
+      <c r="E24" s="372"/>
+      <c r="F24" s="372"/>
+      <c r="G24" s="373"/>
       <c r="H24" s="96"/>
-      <c r="I24" s="334"/>
-      <c r="J24" s="335"/>
+      <c r="I24" s="372"/>
+      <c r="J24" s="373"/>
       <c r="K24" s="94"/>
     </row>
     <row r="25" spans="1:16" ht="15.75" hidden="1" customHeight="1"/>
@@ -11181,13 +11181,13 @@
       <c r="B29" s="58">
         <v>1</v>
       </c>
-      <c r="C29" s="336" t="s">
+      <c r="C29" s="323" t="s">
         <v>202</v>
       </c>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
-      <c r="G29" s="338"/>
+      <c r="D29" s="324"/>
+      <c r="E29" s="324"/>
+      <c r="F29" s="324"/>
+      <c r="G29" s="325"/>
       <c r="H29" s="97"/>
       <c r="I29" s="97" t="e">
         <f>I35+I44+I46+I47+I50+#REF!+I68+I71+I72+I73+I77+I89+I97+I101+I106+I108+I116+I131+I142+I146+I147+I154+I32+I34+#REF!+#REF!+I151+#REF!+I98+I113+I155</f>
@@ -11204,15 +11204,15 @@
       <c r="B30" s="58">
         <v>2</v>
       </c>
-      <c r="C30" s="339" t="s">
+      <c r="C30" s="332" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="336" t="s">
+      <c r="D30" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="337"/>
-      <c r="F30" s="337"/>
-      <c r="G30" s="338"/>
+      <c r="E30" s="324"/>
+      <c r="F30" s="324"/>
+      <c r="G30" s="325"/>
       <c r="H30" s="97"/>
       <c r="I30" s="97"/>
       <c r="J30" s="99" t="e">
@@ -11232,15 +11232,15 @@
       <c r="B31" s="58">
         <v>3</v>
       </c>
-      <c r="C31" s="340"/>
+      <c r="C31" s="333"/>
       <c r="D31" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="345" t="s">
+      <c r="E31" s="319" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="346"/>
-      <c r="G31" s="347"/>
+      <c r="F31" s="320"/>
+      <c r="G31" s="321"/>
       <c r="H31" s="72"/>
       <c r="I31" s="72"/>
       <c r="J31" s="100"/>
@@ -11257,13 +11257,13 @@
       <c r="B32" s="58">
         <v>4</v>
       </c>
-      <c r="C32" s="340"/>
+      <c r="C32" s="333"/>
       <c r="D32" s="343"/>
-      <c r="E32" s="345" t="s">
+      <c r="E32" s="319" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="346"/>
-      <c r="G32" s="347"/>
+      <c r="F32" s="320"/>
+      <c r="G32" s="321"/>
       <c r="H32" s="72"/>
       <c r="I32" s="72"/>
       <c r="J32" s="81" t="e">
@@ -11283,13 +11283,13 @@
       <c r="B33" s="58">
         <v>5</v>
       </c>
-      <c r="C33" s="340"/>
+      <c r="C33" s="333"/>
       <c r="D33" s="343"/>
-      <c r="E33" s="348" t="s">
+      <c r="E33" s="352" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="349"/>
-      <c r="G33" s="350"/>
+      <c r="F33" s="353"/>
+      <c r="G33" s="354"/>
       <c r="H33" s="72"/>
       <c r="I33" s="72"/>
       <c r="J33" s="81"/>
@@ -11302,13 +11302,13 @@
       <c r="B34" s="58">
         <v>6</v>
       </c>
-      <c r="C34" s="341"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="352" t="s">
+      <c r="C34" s="349"/>
+      <c r="D34" s="351"/>
+      <c r="E34" s="329" t="s">
         <v>170</v>
       </c>
-      <c r="F34" s="352"/>
-      <c r="G34" s="352"/>
+      <c r="F34" s="329"/>
+      <c r="G34" s="329"/>
       <c r="H34" s="72"/>
       <c r="I34" s="72"/>
       <c r="J34" s="81" t="e">
@@ -11324,15 +11324,15 @@
       <c r="B35" s="58">
         <v>7</v>
       </c>
-      <c r="C35" s="339" t="s">
+      <c r="C35" s="332" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="336" t="s">
+      <c r="D35" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E35" s="353"/>
-      <c r="F35" s="353"/>
-      <c r="G35" s="354"/>
+      <c r="E35" s="355"/>
+      <c r="F35" s="355"/>
+      <c r="G35" s="356"/>
       <c r="H35" s="97"/>
       <c r="I35" s="101">
         <f>I36+I37</f>
@@ -11348,15 +11348,15 @@
       <c r="B36" s="58">
         <v>8</v>
       </c>
-      <c r="C36" s="340"/>
+      <c r="C36" s="333"/>
       <c r="D36" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="355" t="s">
+      <c r="E36" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="356"/>
-      <c r="G36" s="357"/>
+      <c r="F36" s="337"/>
+      <c r="G36" s="338"/>
       <c r="H36" s="72"/>
       <c r="I36" s="72"/>
       <c r="J36" s="81" t="e">
@@ -11373,13 +11373,13 @@
       <c r="B37" s="58">
         <v>9</v>
       </c>
-      <c r="C37" s="341"/>
-      <c r="D37" s="351"/>
-      <c r="E37" s="355" t="s">
+      <c r="C37" s="349"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="F37" s="356"/>
-      <c r="G37" s="357"/>
+      <c r="F37" s="337"/>
+      <c r="G37" s="338"/>
       <c r="H37" s="72"/>
       <c r="I37" s="72"/>
       <c r="J37" s="81" t="e">
@@ -11396,13 +11396,13 @@
       <c r="B38" s="58">
         <v>10</v>
       </c>
-      <c r="C38" s="336" t="s">
+      <c r="C38" s="323" t="s">
         <v>203</v>
       </c>
-      <c r="D38" s="337"/>
-      <c r="E38" s="337"/>
-      <c r="F38" s="337"/>
-      <c r="G38" s="338"/>
+      <c r="D38" s="324"/>
+      <c r="E38" s="324"/>
+      <c r="F38" s="324"/>
+      <c r="G38" s="325"/>
       <c r="H38" s="97"/>
       <c r="I38" s="97"/>
       <c r="J38" s="102"/>
@@ -11415,15 +11415,15 @@
       <c r="B39" s="58">
         <v>11</v>
       </c>
-      <c r="C39" s="339" t="s">
+      <c r="C39" s="332" t="s">
         <v>186</v>
       </c>
-      <c r="D39" s="336" t="s">
+      <c r="D39" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
-      <c r="G39" s="338"/>
+      <c r="E39" s="324"/>
+      <c r="F39" s="324"/>
+      <c r="G39" s="325"/>
       <c r="H39" s="97"/>
       <c r="I39" s="97"/>
       <c r="J39" s="102"/>
@@ -11436,15 +11436,15 @@
       <c r="B40" s="58">
         <v>12</v>
       </c>
-      <c r="C40" s="340"/>
+      <c r="C40" s="333"/>
       <c r="D40" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E40" s="345" t="s">
+      <c r="E40" s="319" t="s">
         <v>128</v>
       </c>
-      <c r="F40" s="346"/>
-      <c r="G40" s="347"/>
+      <c r="F40" s="320"/>
+      <c r="G40" s="321"/>
       <c r="H40" s="72"/>
       <c r="I40" s="72"/>
       <c r="J40" s="81" t="e">
@@ -11460,13 +11460,13 @@
       <c r="B41" s="58">
         <v>13</v>
       </c>
-      <c r="C41" s="341"/>
-      <c r="D41" s="351"/>
-      <c r="E41" s="345" t="s">
+      <c r="C41" s="349"/>
+      <c r="D41" s="350"/>
+      <c r="E41" s="319" t="s">
         <v>129</v>
       </c>
-      <c r="F41" s="346"/>
-      <c r="G41" s="347"/>
+      <c r="F41" s="320"/>
+      <c r="G41" s="321"/>
       <c r="H41" s="72"/>
       <c r="I41" s="72"/>
       <c r="J41" s="81" t="e">
@@ -11482,15 +11482,15 @@
       <c r="B42" s="58">
         <v>14</v>
       </c>
-      <c r="C42" s="339" t="s">
+      <c r="C42" s="332" t="s">
         <v>204</v>
       </c>
-      <c r="D42" s="336" t="s">
+      <c r="D42" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E42" s="337"/>
-      <c r="F42" s="337"/>
-      <c r="G42" s="338"/>
+      <c r="E42" s="324"/>
+      <c r="F42" s="324"/>
+      <c r="G42" s="325"/>
       <c r="H42" s="97"/>
       <c r="I42" s="97"/>
       <c r="J42" s="102"/>
@@ -11503,15 +11503,15 @@
       <c r="B43" s="58">
         <v>15</v>
       </c>
-      <c r="C43" s="340"/>
+      <c r="C43" s="333"/>
       <c r="D43" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="345" t="s">
+      <c r="E43" s="319" t="s">
         <v>128</v>
       </c>
-      <c r="F43" s="346"/>
-      <c r="G43" s="347"/>
+      <c r="F43" s="320"/>
+      <c r="G43" s="321"/>
       <c r="H43" s="72"/>
       <c r="I43" s="72"/>
       <c r="J43" s="81" t="e">
@@ -11527,13 +11527,13 @@
       <c r="B44" s="58">
         <v>16</v>
       </c>
-      <c r="C44" s="341"/>
-      <c r="D44" s="351"/>
-      <c r="E44" s="345" t="s">
+      <c r="C44" s="349"/>
+      <c r="D44" s="350"/>
+      <c r="E44" s="319" t="s">
         <v>129</v>
       </c>
-      <c r="F44" s="346"/>
-      <c r="G44" s="347"/>
+      <c r="F44" s="320"/>
+      <c r="G44" s="321"/>
       <c r="H44" s="72"/>
       <c r="I44" s="72"/>
       <c r="J44" s="81" t="e">
@@ -11549,15 +11549,15 @@
       <c r="B45" s="58">
         <v>17</v>
       </c>
-      <c r="C45" s="339" t="s">
+      <c r="C45" s="332" t="s">
         <v>62</v>
       </c>
-      <c r="D45" s="336" t="s">
+      <c r="D45" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="337"/>
-      <c r="F45" s="337"/>
-      <c r="G45" s="338"/>
+      <c r="E45" s="324"/>
+      <c r="F45" s="324"/>
+      <c r="G45" s="325"/>
       <c r="H45" s="97"/>
       <c r="I45" s="97"/>
       <c r="J45" s="102"/>
@@ -11570,15 +11570,15 @@
       <c r="B46" s="58">
         <v>18</v>
       </c>
-      <c r="C46" s="340"/>
+      <c r="C46" s="333"/>
       <c r="D46" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E46" s="345" t="s">
+      <c r="E46" s="319" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="346"/>
-      <c r="G46" s="347"/>
+      <c r="F46" s="320"/>
+      <c r="G46" s="321"/>
       <c r="H46" s="72"/>
       <c r="I46" s="72"/>
       <c r="J46" s="81" t="e">
@@ -11594,13 +11594,13 @@
       <c r="B47" s="58">
         <v>19</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="345" t="s">
+      <c r="C47" s="349"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="319" t="s">
         <v>64</v>
       </c>
-      <c r="F47" s="346"/>
-      <c r="G47" s="347"/>
+      <c r="F47" s="320"/>
+      <c r="G47" s="321"/>
       <c r="H47" s="72"/>
       <c r="I47" s="72"/>
       <c r="J47" s="81" t="e">
@@ -11616,15 +11616,15 @@
       <c r="B48" s="58">
         <v>20</v>
       </c>
-      <c r="C48" s="339" t="s">
+      <c r="C48" s="332" t="s">
         <v>205</v>
       </c>
-      <c r="D48" s="336" t="s">
+      <c r="D48" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="337"/>
-      <c r="F48" s="337"/>
-      <c r="G48" s="338"/>
+      <c r="E48" s="324"/>
+      <c r="F48" s="324"/>
+      <c r="G48" s="325"/>
       <c r="H48" s="97"/>
       <c r="I48" s="97"/>
       <c r="J48" s="102"/>
@@ -11637,15 +11637,15 @@
       <c r="B49" s="58">
         <v>21</v>
       </c>
-      <c r="C49" s="340"/>
+      <c r="C49" s="333"/>
       <c r="D49" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="358" t="s">
-        <v>44</v>
-      </c>
-      <c r="F49" s="359"/>
-      <c r="G49" s="359"/>
+      <c r="E49" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" s="335"/>
+      <c r="G49" s="335"/>
       <c r="H49" s="104"/>
       <c r="I49" s="104"/>
       <c r="J49" s="81"/>
@@ -11664,11 +11664,11 @@
       <c r="D50" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E50" s="345" t="s">
+      <c r="E50" s="319" t="s">
         <v>206</v>
       </c>
-      <c r="F50" s="346"/>
-      <c r="G50" s="347"/>
+      <c r="F50" s="320"/>
+      <c r="G50" s="321"/>
       <c r="H50" s="72"/>
       <c r="I50" s="72"/>
       <c r="J50" s="81" t="e">
@@ -11691,11 +11691,11 @@
       <c r="D51" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E51" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="346"/>
-      <c r="G51" s="347"/>
+      <c r="E51" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="320"/>
+      <c r="G51" s="321"/>
       <c r="H51" s="72"/>
       <c r="I51" s="72"/>
       <c r="J51" s="81"/>
@@ -11709,15 +11709,15 @@
       <c r="B52" s="58">
         <v>24</v>
       </c>
-      <c r="C52" s="339" t="s">
+      <c r="C52" s="332" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="336" t="s">
+      <c r="D52" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E52" s="337"/>
-      <c r="F52" s="337"/>
-      <c r="G52" s="338"/>
+      <c r="E52" s="324"/>
+      <c r="F52" s="324"/>
+      <c r="G52" s="325"/>
       <c r="H52" s="97"/>
       <c r="I52" s="97"/>
       <c r="J52" s="102"/>
@@ -11730,15 +11730,15 @@
       <c r="B53" s="58">
         <v>25</v>
       </c>
-      <c r="C53" s="340"/>
+      <c r="C53" s="333"/>
       <c r="D53" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E53" s="345" t="s">
+      <c r="E53" s="319" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="346"/>
-      <c r="G53" s="347"/>
+      <c r="F53" s="320"/>
+      <c r="G53" s="321"/>
       <c r="H53" s="72"/>
       <c r="I53" s="72"/>
       <c r="J53" s="81"/>
@@ -11757,11 +11757,11 @@
       <c r="D54" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E54" s="345" t="s">
+      <c r="E54" s="319" t="s">
         <v>207</v>
       </c>
-      <c r="F54" s="346"/>
-      <c r="G54" s="347"/>
+      <c r="F54" s="320"/>
+      <c r="G54" s="321"/>
       <c r="H54" s="72"/>
       <c r="I54" s="72"/>
       <c r="J54" s="81" t="e">
@@ -11778,15 +11778,15 @@
       <c r="B55" s="58">
         <v>30</v>
       </c>
-      <c r="C55" s="339" t="s">
+      <c r="C55" s="332" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="336" t="s">
+      <c r="D55" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="337"/>
-      <c r="F55" s="337"/>
-      <c r="G55" s="338"/>
+      <c r="E55" s="324"/>
+      <c r="F55" s="324"/>
+      <c r="G55" s="325"/>
       <c r="H55" s="97"/>
       <c r="I55" s="97"/>
       <c r="J55" s="102"/>
@@ -11799,15 +11799,15 @@
       <c r="B56" s="58">
         <v>31</v>
       </c>
-      <c r="C56" s="340"/>
+      <c r="C56" s="333"/>
       <c r="D56" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="345" t="s">
+      <c r="E56" s="319" t="s">
         <v>146</v>
       </c>
-      <c r="F56" s="346"/>
-      <c r="G56" s="347"/>
+      <c r="F56" s="320"/>
+      <c r="G56" s="321"/>
       <c r="H56" s="72"/>
       <c r="I56" s="72"/>
       <c r="J56" s="81"/>
@@ -11820,15 +11820,15 @@
       <c r="B57" s="58">
         <v>32</v>
       </c>
-      <c r="C57" s="340"/>
+      <c r="C57" s="333"/>
       <c r="D57" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="345" t="s">
+      <c r="E57" s="319" t="s">
         <v>147</v>
       </c>
-      <c r="F57" s="346"/>
-      <c r="G57" s="347"/>
+      <c r="F57" s="320"/>
+      <c r="G57" s="321"/>
       <c r="H57" s="72"/>
       <c r="I57" s="72"/>
       <c r="J57" s="81"/>
@@ -11847,11 +11847,11 @@
       <c r="D58" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="345" t="s">
+      <c r="E58" s="319" t="s">
         <v>148</v>
       </c>
-      <c r="F58" s="346"/>
-      <c r="G58" s="347"/>
+      <c r="F58" s="320"/>
+      <c r="G58" s="321"/>
       <c r="H58" s="72"/>
       <c r="I58" s="72"/>
       <c r="J58" s="81"/>
@@ -11870,11 +11870,11 @@
       <c r="D59" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E59" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F59" s="346"/>
-      <c r="G59" s="347"/>
+      <c r="E59" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F59" s="320"/>
+      <c r="G59" s="321"/>
       <c r="H59" s="72"/>
       <c r="I59" s="72"/>
       <c r="J59" s="81"/>
@@ -11888,15 +11888,15 @@
       <c r="B60" s="58">
         <v>35</v>
       </c>
-      <c r="C60" s="339" t="s">
+      <c r="C60" s="332" t="s">
         <v>190</v>
       </c>
-      <c r="D60" s="336" t="s">
+      <c r="D60" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E60" s="337"/>
-      <c r="F60" s="337"/>
-      <c r="G60" s="338"/>
+      <c r="E60" s="324"/>
+      <c r="F60" s="324"/>
+      <c r="G60" s="325"/>
       <c r="H60" s="97"/>
       <c r="I60" s="97"/>
       <c r="J60" s="102"/>
@@ -11909,15 +11909,15 @@
       <c r="B61" s="58">
         <v>36</v>
       </c>
-      <c r="C61" s="340"/>
+      <c r="C61" s="333"/>
       <c r="D61" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E61" s="345" t="s">
+      <c r="E61" s="319" t="s">
         <v>128</v>
       </c>
-      <c r="F61" s="346"/>
-      <c r="G61" s="347"/>
+      <c r="F61" s="320"/>
+      <c r="G61" s="321"/>
       <c r="H61" s="72"/>
       <c r="I61" s="72"/>
       <c r="J61" s="81"/>
@@ -11930,15 +11930,15 @@
       <c r="B62" s="58">
         <v>37</v>
       </c>
-      <c r="C62" s="340"/>
+      <c r="C62" s="333"/>
       <c r="D62" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E62" s="345" t="s">
+      <c r="E62" s="319" t="s">
         <v>154</v>
       </c>
-      <c r="F62" s="346"/>
-      <c r="G62" s="347"/>
+      <c r="F62" s="320"/>
+      <c r="G62" s="321"/>
       <c r="H62" s="72"/>
       <c r="I62" s="72"/>
       <c r="J62" s="81"/>
@@ -11957,11 +11957,11 @@
       <c r="D63" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E63" s="345" t="s">
+      <c r="E63" s="319" t="s">
         <v>208</v>
       </c>
-      <c r="F63" s="346"/>
-      <c r="G63" s="347"/>
+      <c r="F63" s="320"/>
+      <c r="G63" s="321"/>
       <c r="H63" s="72"/>
       <c r="I63" s="72"/>
       <c r="J63" s="81"/>
@@ -11980,11 +11980,11 @@
       <c r="D64" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E64" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F64" s="346"/>
-      <c r="G64" s="347"/>
+      <c r="E64" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F64" s="320"/>
+      <c r="G64" s="321"/>
       <c r="H64" s="72"/>
       <c r="I64" s="72"/>
       <c r="J64" s="81"/>
@@ -11998,15 +11998,15 @@
       <c r="B65" s="58">
         <v>40</v>
       </c>
-      <c r="C65" s="339" t="s">
+      <c r="C65" s="332" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="336" t="s">
+      <c r="D65" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E65" s="337"/>
-      <c r="F65" s="337"/>
-      <c r="G65" s="338"/>
+      <c r="E65" s="324"/>
+      <c r="F65" s="324"/>
+      <c r="G65" s="325"/>
       <c r="H65" s="97"/>
       <c r="I65" s="97"/>
       <c r="J65" s="102"/>
@@ -12019,17 +12019,17 @@
       <c r="B66" s="58">
         <v>41</v>
       </c>
-      <c r="C66" s="340"/>
+      <c r="C66" s="333"/>
       <c r="D66" s="66" t="s">
         <v>55</v>
       </c>
       <c r="E66" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="F66" s="336" t="s">
+      <c r="F66" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G66" s="338"/>
+      <c r="G66" s="325"/>
       <c r="H66" s="97"/>
       <c r="I66" s="97"/>
       <c r="J66" s="102"/>
@@ -12042,7 +12042,7 @@
       <c r="B67" s="58">
         <v>42</v>
       </c>
-      <c r="C67" s="340"/>
+      <c r="C67" s="333"/>
       <c r="D67" s="67" t="s">
         <v>44</v>
       </c>
@@ -12135,10 +12135,10 @@
       <c r="E70" s="103" t="s">
         <v>210</v>
       </c>
-      <c r="F70" s="336" t="s">
+      <c r="F70" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G70" s="338"/>
+      <c r="G70" s="325"/>
       <c r="H70" s="97"/>
       <c r="I70" s="97"/>
       <c r="J70" s="102"/>
@@ -12307,10 +12307,10 @@
       <c r="E76" s="103" t="s">
         <v>214</v>
       </c>
-      <c r="F76" s="336" t="s">
+      <c r="F76" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G76" s="338"/>
+      <c r="G76" s="325"/>
       <c r="H76" s="97"/>
       <c r="I76" s="97"/>
       <c r="J76" s="102"/>
@@ -12412,13 +12412,13 @@
       <c r="D80" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E80" s="360" t="s">
+      <c r="E80" s="344" t="s">
         <v>216</v>
       </c>
-      <c r="F80" s="336" t="s">
+      <c r="F80" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G80" s="338"/>
+      <c r="G80" s="325"/>
       <c r="H80" s="97"/>
       <c r="I80" s="97"/>
       <c r="J80" s="102"/>
@@ -12438,15 +12438,15 @@
       <c r="D81" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E81" s="361"/>
+      <c r="E81" s="345"/>
       <c r="F81" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="G81" s="362" t="s">
+      <c r="G81" s="346" t="s">
         <v>136</v>
       </c>
-      <c r="H81" s="363"/>
-      <c r="I81" s="364"/>
+      <c r="H81" s="347"/>
+      <c r="I81" s="348"/>
       <c r="J81" s="81" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -12525,13 +12525,13 @@
       <c r="D84" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E84" s="360" t="s">
-        <v>44</v>
-      </c>
-      <c r="F84" s="336" t="s">
+      <c r="E84" s="344" t="s">
+        <v>44</v>
+      </c>
+      <c r="F84" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G84" s="338"/>
+      <c r="G84" s="325"/>
       <c r="H84" s="97"/>
       <c r="I84" s="97"/>
       <c r="J84" s="102"/>
@@ -12551,7 +12551,7 @@
       <c r="D85" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E85" s="361"/>
+      <c r="E85" s="345"/>
       <c r="F85" s="66" t="s">
         <v>55</v>
       </c>
@@ -12600,15 +12600,15 @@
       <c r="B87" s="58">
         <v>62</v>
       </c>
-      <c r="C87" s="339" t="s">
+      <c r="C87" s="332" t="s">
         <v>144</v>
       </c>
-      <c r="D87" s="336" t="s">
+      <c r="D87" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E87" s="337"/>
-      <c r="F87" s="337"/>
-      <c r="G87" s="338"/>
+      <c r="E87" s="324"/>
+      <c r="F87" s="324"/>
+      <c r="G87" s="325"/>
       <c r="H87" s="97"/>
       <c r="I87" s="110"/>
       <c r="J87" s="102"/>
@@ -12621,15 +12621,15 @@
       <c r="B88" s="58">
         <v>63</v>
       </c>
-      <c r="C88" s="340"/>
+      <c r="C88" s="333"/>
       <c r="D88" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E88" s="358" t="s">
-        <v>44</v>
-      </c>
-      <c r="F88" s="359"/>
-      <c r="G88" s="359"/>
+      <c r="E88" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F88" s="335"/>
+      <c r="G88" s="335"/>
       <c r="H88" s="104"/>
       <c r="I88" s="104"/>
       <c r="J88" s="81" t="e">
@@ -12651,11 +12651,11 @@
       <c r="D89" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F89" s="346"/>
-      <c r="G89" s="347"/>
+      <c r="E89" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F89" s="320"/>
+      <c r="G89" s="321"/>
       <c r="H89" s="72"/>
       <c r="I89" s="109"/>
       <c r="J89" s="81"/>
@@ -12675,11 +12675,11 @@
       <c r="D90" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E90" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F90" s="346"/>
-      <c r="G90" s="347"/>
+      <c r="E90" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F90" s="320"/>
+      <c r="G90" s="321"/>
       <c r="H90" s="72"/>
       <c r="I90" s="109"/>
       <c r="J90" s="81"/>
@@ -12693,15 +12693,15 @@
       <c r="B91" s="58">
         <v>66</v>
       </c>
-      <c r="C91" s="339" t="s">
+      <c r="C91" s="332" t="s">
         <v>189</v>
       </c>
-      <c r="D91" s="336" t="s">
+      <c r="D91" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="337"/>
-      <c r="F91" s="337"/>
-      <c r="G91" s="338"/>
+      <c r="E91" s="324"/>
+      <c r="F91" s="324"/>
+      <c r="G91" s="325"/>
       <c r="H91" s="97"/>
       <c r="I91" s="110"/>
       <c r="J91" s="102"/>
@@ -12714,15 +12714,15 @@
       <c r="B92" s="58">
         <v>67</v>
       </c>
-      <c r="C92" s="340"/>
+      <c r="C92" s="333"/>
       <c r="D92" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E92" s="358" t="s">
-        <v>44</v>
-      </c>
-      <c r="F92" s="359"/>
-      <c r="G92" s="359"/>
+      <c r="E92" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F92" s="335"/>
+      <c r="G92" s="335"/>
       <c r="H92" s="104"/>
       <c r="I92" s="104"/>
       <c r="J92" s="81"/>
@@ -12741,11 +12741,11 @@
       <c r="D93" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F93" s="346"/>
-      <c r="G93" s="347"/>
+      <c r="E93" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F93" s="320"/>
+      <c r="G93" s="321"/>
       <c r="H93" s="72"/>
       <c r="I93" s="109"/>
       <c r="J93" s="81"/>
@@ -12765,11 +12765,11 @@
       <c r="D94" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E94" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F94" s="346"/>
-      <c r="G94" s="347"/>
+      <c r="E94" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F94" s="320"/>
+      <c r="G94" s="321"/>
       <c r="H94" s="72"/>
       <c r="I94" s="109"/>
       <c r="J94" s="81"/>
@@ -12783,15 +12783,15 @@
       <c r="B95" s="58">
         <v>70</v>
       </c>
-      <c r="C95" s="339" t="s">
+      <c r="C95" s="332" t="s">
         <v>137</v>
       </c>
-      <c r="D95" s="336" t="s">
+      <c r="D95" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E95" s="337"/>
-      <c r="F95" s="337"/>
-      <c r="G95" s="338"/>
+      <c r="E95" s="324"/>
+      <c r="F95" s="324"/>
+      <c r="G95" s="325"/>
       <c r="H95" s="97"/>
       <c r="I95" s="110"/>
       <c r="J95" s="102"/>
@@ -12804,15 +12804,15 @@
       <c r="B96" s="58">
         <v>71</v>
       </c>
-      <c r="C96" s="340"/>
+      <c r="C96" s="333"/>
       <c r="D96" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E96" s="358" t="s">
-        <v>44</v>
-      </c>
-      <c r="F96" s="359"/>
-      <c r="G96" s="359"/>
+      <c r="E96" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F96" s="335"/>
+      <c r="G96" s="335"/>
       <c r="H96" s="104"/>
       <c r="I96" s="104"/>
       <c r="J96" s="81"/>
@@ -12831,11 +12831,11 @@
       <c r="D97" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E97" s="345" t="s">
+      <c r="E97" s="319" t="s">
         <v>217</v>
       </c>
-      <c r="F97" s="346"/>
-      <c r="G97" s="347"/>
+      <c r="F97" s="320"/>
+      <c r="G97" s="321"/>
       <c r="H97" s="72"/>
       <c r="I97" s="109"/>
       <c r="J97" s="81" t="e">
@@ -12850,11 +12850,11 @@
       <c r="B98" s="58"/>
       <c r="C98" s="77"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="345" t="s">
+      <c r="E98" s="319" t="s">
         <v>218</v>
       </c>
-      <c r="F98" s="346"/>
-      <c r="G98" s="347"/>
+      <c r="F98" s="320"/>
+      <c r="G98" s="321"/>
       <c r="H98" s="72"/>
       <c r="I98" s="109"/>
       <c r="J98" s="81"/>
@@ -12866,9 +12866,9 @@
       <c r="B99" s="58"/>
       <c r="C99" s="77"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="345"/>
-      <c r="F99" s="346"/>
-      <c r="G99" s="347"/>
+      <c r="E99" s="319"/>
+      <c r="F99" s="320"/>
+      <c r="G99" s="321"/>
       <c r="H99" s="72"/>
       <c r="I99" s="109"/>
       <c r="J99" s="81"/>
@@ -12888,11 +12888,11 @@
       <c r="D100" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E100" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F100" s="346"/>
-      <c r="G100" s="347"/>
+      <c r="E100" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F100" s="320"/>
+      <c r="G100" s="321"/>
       <c r="H100" s="72"/>
       <c r="I100" s="109"/>
       <c r="J100" s="81"/>
@@ -12906,15 +12906,15 @@
       <c r="B101" s="58">
         <v>75</v>
       </c>
-      <c r="C101" s="339" t="s">
+      <c r="C101" s="332" t="s">
         <v>17</v>
       </c>
-      <c r="D101" s="336" t="s">
+      <c r="D101" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E101" s="337"/>
-      <c r="F101" s="337"/>
-      <c r="G101" s="338"/>
+      <c r="E101" s="324"/>
+      <c r="F101" s="324"/>
+      <c r="G101" s="325"/>
       <c r="H101" s="97"/>
       <c r="I101" s="111">
         <f>I102+I103+I104</f>
@@ -12930,15 +12930,15 @@
       <c r="B102" s="58">
         <v>76</v>
       </c>
-      <c r="C102" s="340"/>
+      <c r="C102" s="333"/>
       <c r="D102" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E102" s="355" t="s">
+      <c r="E102" s="336" t="s">
         <v>219</v>
       </c>
-      <c r="F102" s="356"/>
-      <c r="G102" s="357"/>
+      <c r="F102" s="337"/>
+      <c r="G102" s="338"/>
       <c r="H102" s="72"/>
       <c r="I102" s="109"/>
       <c r="J102" s="81">
@@ -12954,15 +12954,15 @@
       <c r="B103" s="58">
         <v>77</v>
       </c>
-      <c r="C103" s="340"/>
+      <c r="C103" s="333"/>
       <c r="D103" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E103" s="355" t="s">
+      <c r="E103" s="336" t="s">
         <v>220</v>
       </c>
-      <c r="F103" s="356"/>
-      <c r="G103" s="357"/>
+      <c r="F103" s="337"/>
+      <c r="G103" s="338"/>
       <c r="H103" s="72"/>
       <c r="I103" s="72"/>
       <c r="J103" s="81">
@@ -12984,11 +12984,11 @@
       <c r="D104" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E104" s="355" t="s">
+      <c r="E104" s="336" t="s">
         <v>221</v>
       </c>
-      <c r="F104" s="356"/>
-      <c r="G104" s="357"/>
+      <c r="F104" s="337"/>
+      <c r="G104" s="338"/>
       <c r="H104" s="72"/>
       <c r="I104" s="72"/>
       <c r="J104" s="81">
@@ -13004,13 +13004,13 @@
       <c r="B105" s="58">
         <v>83</v>
       </c>
-      <c r="C105" s="336" t="s">
+      <c r="C105" s="323" t="s">
         <v>7</v>
       </c>
-      <c r="D105" s="337"/>
-      <c r="E105" s="337"/>
-      <c r="F105" s="337"/>
-      <c r="G105" s="338"/>
+      <c r="D105" s="324"/>
+      <c r="E105" s="324"/>
+      <c r="F105" s="324"/>
+      <c r="G105" s="325"/>
       <c r="H105" s="97"/>
       <c r="I105" s="97"/>
       <c r="J105" s="102" t="e">
@@ -13026,13 +13026,13 @@
       <c r="B106" s="58">
         <v>84</v>
       </c>
-      <c r="C106" s="336" t="s">
+      <c r="C106" s="323" t="s">
         <v>222</v>
       </c>
-      <c r="D106" s="337"/>
-      <c r="E106" s="337"/>
-      <c r="F106" s="337"/>
-      <c r="G106" s="338"/>
+      <c r="D106" s="324"/>
+      <c r="E106" s="324"/>
+      <c r="F106" s="324"/>
+      <c r="G106" s="325"/>
       <c r="H106" s="97"/>
       <c r="I106" s="101"/>
       <c r="J106" s="102" t="e">
@@ -13048,15 +13048,15 @@
       <c r="B107" s="58">
         <v>85</v>
       </c>
-      <c r="C107" s="339" t="s">
+      <c r="C107" s="332" t="s">
         <v>223</v>
       </c>
-      <c r="D107" s="336" t="s">
+      <c r="D107" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E107" s="337"/>
-      <c r="F107" s="337"/>
-      <c r="G107" s="338"/>
+      <c r="E107" s="324"/>
+      <c r="F107" s="324"/>
+      <c r="G107" s="325"/>
       <c r="H107" s="97"/>
       <c r="I107" s="97"/>
       <c r="J107" s="102"/>
@@ -13069,15 +13069,15 @@
       <c r="B108" s="58">
         <v>86</v>
       </c>
-      <c r="C108" s="340"/>
+      <c r="C108" s="333"/>
       <c r="D108" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E108" s="355" t="s">
+      <c r="E108" s="336" t="s">
         <v>224</v>
       </c>
-      <c r="F108" s="356"/>
-      <c r="G108" s="357"/>
+      <c r="F108" s="337"/>
+      <c r="G108" s="338"/>
       <c r="H108" s="72"/>
       <c r="I108" s="63"/>
       <c r="J108" s="81" t="e">
@@ -13099,11 +13099,11 @@
       <c r="D109" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E109" s="345" t="s">
+      <c r="E109" s="319" t="s">
         <v>225</v>
       </c>
-      <c r="F109" s="346"/>
-      <c r="G109" s="347"/>
+      <c r="F109" s="320"/>
+      <c r="G109" s="321"/>
       <c r="H109" s="72"/>
       <c r="I109" s="63"/>
       <c r="J109" s="81"/>
@@ -13123,11 +13123,11 @@
       <c r="D110" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E110" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F110" s="346"/>
-      <c r="G110" s="347"/>
+      <c r="E110" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F110" s="320"/>
+      <c r="G110" s="321"/>
       <c r="H110" s="72"/>
       <c r="I110" s="72"/>
       <c r="J110" s="81"/>
@@ -13141,15 +13141,15 @@
       <c r="B111" s="58">
         <v>89</v>
       </c>
-      <c r="C111" s="339" t="s">
+      <c r="C111" s="332" t="s">
         <v>192</v>
       </c>
-      <c r="D111" s="336" t="s">
+      <c r="D111" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E111" s="337"/>
-      <c r="F111" s="337"/>
-      <c r="G111" s="338"/>
+      <c r="E111" s="324"/>
+      <c r="F111" s="324"/>
+      <c r="G111" s="325"/>
       <c r="H111" s="97"/>
       <c r="I111" s="97"/>
       <c r="J111" s="102"/>
@@ -13162,15 +13162,15 @@
       <c r="B112" s="58">
         <v>90</v>
       </c>
-      <c r="C112" s="340"/>
+      <c r="C112" s="333"/>
       <c r="D112" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E112" s="355" t="s">
+      <c r="E112" s="336" t="s">
         <v>226</v>
       </c>
-      <c r="F112" s="356"/>
-      <c r="G112" s="357"/>
+      <c r="F112" s="337"/>
+      <c r="G112" s="338"/>
       <c r="H112" s="72"/>
       <c r="I112" s="72"/>
       <c r="J112" s="81"/>
@@ -13189,11 +13189,11 @@
       <c r="D113" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E113" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F113" s="346"/>
-      <c r="G113" s="347"/>
+      <c r="E113" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F113" s="320"/>
+      <c r="G113" s="321"/>
       <c r="H113" s="72"/>
       <c r="I113" s="72"/>
       <c r="J113" s="81"/>
@@ -13206,15 +13206,15 @@
       <c r="B114" s="58">
         <v>92</v>
       </c>
-      <c r="C114" s="339" t="s">
+      <c r="C114" s="332" t="s">
         <v>191</v>
       </c>
-      <c r="D114" s="336" t="s">
+      <c r="D114" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E114" s="337"/>
-      <c r="F114" s="337"/>
-      <c r="G114" s="338"/>
+      <c r="E114" s="324"/>
+      <c r="F114" s="324"/>
+      <c r="G114" s="325"/>
       <c r="H114" s="97"/>
       <c r="I114" s="97"/>
       <c r="J114" s="102"/>
@@ -13227,15 +13227,15 @@
       <c r="B115" s="58">
         <v>93</v>
       </c>
-      <c r="C115" s="340"/>
+      <c r="C115" s="333"/>
       <c r="D115" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E115" s="358" t="s">
-        <v>44</v>
-      </c>
-      <c r="F115" s="359"/>
-      <c r="G115" s="359"/>
+      <c r="E115" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F115" s="335"/>
+      <c r="G115" s="335"/>
       <c r="H115" s="104"/>
       <c r="I115" s="104"/>
       <c r="J115" s="112"/>
@@ -13254,11 +13254,11 @@
       <c r="D116" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E116" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F116" s="346"/>
-      <c r="G116" s="347"/>
+      <c r="E116" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F116" s="320"/>
+      <c r="G116" s="321"/>
       <c r="H116" s="72"/>
       <c r="I116" s="63"/>
       <c r="J116" s="81"/>
@@ -13278,11 +13278,11 @@
       <c r="D117" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E117" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F117" s="346"/>
-      <c r="G117" s="347"/>
+      <c r="E117" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F117" s="320"/>
+      <c r="G117" s="321"/>
       <c r="H117" s="72"/>
       <c r="I117" s="72"/>
       <c r="J117" s="81"/>
@@ -13296,15 +13296,15 @@
       <c r="B118" s="58">
         <v>96</v>
       </c>
-      <c r="C118" s="339" t="s">
+      <c r="C118" s="332" t="s">
         <v>149</v>
       </c>
-      <c r="D118" s="336" t="s">
+      <c r="D118" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E118" s="337"/>
-      <c r="F118" s="337"/>
-      <c r="G118" s="338"/>
+      <c r="E118" s="324"/>
+      <c r="F118" s="324"/>
+      <c r="G118" s="325"/>
       <c r="H118" s="97"/>
       <c r="I118" s="97"/>
       <c r="J118" s="102"/>
@@ -13317,15 +13317,15 @@
       <c r="B119" s="58">
         <v>97</v>
       </c>
-      <c r="C119" s="340"/>
+      <c r="C119" s="333"/>
       <c r="D119" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E119" s="355" t="s">
+      <c r="E119" s="336" t="s">
         <v>227</v>
       </c>
-      <c r="F119" s="356"/>
-      <c r="G119" s="357"/>
+      <c r="F119" s="337"/>
+      <c r="G119" s="338"/>
       <c r="H119" s="72"/>
       <c r="I119" s="72"/>
       <c r="J119" s="81"/>
@@ -13344,11 +13344,11 @@
       <c r="D120" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E120" s="355" t="s">
+      <c r="E120" s="336" t="s">
         <v>228</v>
       </c>
-      <c r="F120" s="356"/>
-      <c r="G120" s="357"/>
+      <c r="F120" s="337"/>
+      <c r="G120" s="338"/>
       <c r="H120" s="72"/>
       <c r="I120" s="72"/>
       <c r="J120" s="81"/>
@@ -13367,11 +13367,11 @@
       <c r="D121" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E121" s="355" t="s">
+      <c r="E121" s="336" t="s">
         <v>229</v>
       </c>
-      <c r="F121" s="356"/>
-      <c r="G121" s="357"/>
+      <c r="F121" s="337"/>
+      <c r="G121" s="338"/>
       <c r="H121" s="72"/>
       <c r="I121" s="72"/>
       <c r="J121" s="81"/>
@@ -13390,11 +13390,11 @@
       <c r="D122" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E122" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F122" s="346"/>
-      <c r="G122" s="347"/>
+      <c r="E122" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F122" s="320"/>
+      <c r="G122" s="321"/>
       <c r="H122" s="72"/>
       <c r="I122" s="72"/>
       <c r="J122" s="81"/>
@@ -13408,15 +13408,15 @@
       <c r="B123" s="58">
         <v>101</v>
       </c>
-      <c r="C123" s="339" t="s">
+      <c r="C123" s="332" t="s">
         <v>230</v>
       </c>
-      <c r="D123" s="336" t="s">
+      <c r="D123" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E123" s="337"/>
-      <c r="F123" s="337"/>
-      <c r="G123" s="338"/>
+      <c r="E123" s="324"/>
+      <c r="F123" s="324"/>
+      <c r="G123" s="325"/>
       <c r="H123" s="97"/>
       <c r="I123" s="97"/>
       <c r="J123" s="102"/>
@@ -13429,17 +13429,17 @@
       <c r="B124" s="58">
         <v>102</v>
       </c>
-      <c r="C124" s="340"/>
+      <c r="C124" s="333"/>
       <c r="D124" s="66" t="s">
         <v>55</v>
       </c>
       <c r="E124" s="342" t="s">
         <v>231</v>
       </c>
-      <c r="F124" s="336" t="s">
+      <c r="F124" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G124" s="338"/>
+      <c r="G124" s="325"/>
       <c r="H124" s="97"/>
       <c r="I124" s="97"/>
       <c r="J124" s="102"/>
@@ -13452,7 +13452,7 @@
       <c r="B125" s="58">
         <v>103</v>
       </c>
-      <c r="C125" s="340"/>
+      <c r="C125" s="333"/>
       <c r="D125" s="67" t="s">
         <v>44</v>
       </c>
@@ -13475,7 +13475,7 @@
       <c r="B126" s="58">
         <v>104</v>
       </c>
-      <c r="C126" s="340"/>
+      <c r="C126" s="333"/>
       <c r="D126" s="67" t="s">
         <v>44</v>
       </c>
@@ -13561,11 +13561,11 @@
       <c r="D129" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E129" s="355" t="s">
+      <c r="E129" s="336" t="s">
         <v>234</v>
       </c>
-      <c r="F129" s="356"/>
-      <c r="G129" s="357"/>
+      <c r="F129" s="337"/>
+      <c r="G129" s="338"/>
       <c r="H129" s="72"/>
       <c r="I129" s="72"/>
       <c r="J129" s="81"/>
@@ -13584,11 +13584,11 @@
       <c r="D130" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E130" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F130" s="346"/>
-      <c r="G130" s="347"/>
+      <c r="E130" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F130" s="320"/>
+      <c r="G130" s="321"/>
       <c r="H130" s="72"/>
       <c r="I130" s="72"/>
       <c r="J130" s="81"/>
@@ -13602,15 +13602,15 @@
       <c r="B131" s="58">
         <v>109</v>
       </c>
-      <c r="C131" s="339" t="s">
+      <c r="C131" s="332" t="s">
         <v>175</v>
       </c>
-      <c r="D131" s="336" t="s">
+      <c r="D131" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E131" s="337"/>
-      <c r="F131" s="337"/>
-      <c r="G131" s="338"/>
+      <c r="E131" s="324"/>
+      <c r="F131" s="324"/>
+      <c r="G131" s="325"/>
       <c r="H131" s="97"/>
       <c r="I131" s="101">
         <f>SUM(I132:I136)</f>
@@ -13626,15 +13626,15 @@
       <c r="B132" s="58">
         <v>110</v>
       </c>
-      <c r="C132" s="340"/>
+      <c r="C132" s="333"/>
       <c r="D132" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E132" s="355" t="s">
+      <c r="E132" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="F132" s="356"/>
-      <c r="G132" s="357"/>
+      <c r="F132" s="337"/>
+      <c r="G132" s="338"/>
       <c r="H132" s="72"/>
       <c r="I132" s="72"/>
       <c r="J132" s="81" t="e">
@@ -13650,15 +13650,15 @@
       <c r="B133" s="58">
         <v>111</v>
       </c>
-      <c r="C133" s="340"/>
+      <c r="C133" s="333"/>
       <c r="D133" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E133" s="355" t="s">
+      <c r="E133" s="336" t="s">
         <v>235</v>
       </c>
-      <c r="F133" s="356"/>
-      <c r="G133" s="357"/>
+      <c r="F133" s="337"/>
+      <c r="G133" s="338"/>
       <c r="H133" s="72"/>
       <c r="I133" s="72"/>
       <c r="J133" s="81" t="e">
@@ -13680,11 +13680,11 @@
       <c r="D134" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E134" s="355" t="s">
+      <c r="E134" s="336" t="s">
         <v>11</v>
       </c>
-      <c r="F134" s="356"/>
-      <c r="G134" s="357"/>
+      <c r="F134" s="337"/>
+      <c r="G134" s="338"/>
       <c r="H134" s="72"/>
       <c r="I134" s="72"/>
       <c r="J134" s="81" t="e">
@@ -13706,11 +13706,11 @@
       <c r="D135" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E135" s="355" t="s">
+      <c r="E135" s="336" t="s">
         <v>9</v>
       </c>
-      <c r="F135" s="356"/>
-      <c r="G135" s="357"/>
+      <c r="F135" s="337"/>
+      <c r="G135" s="338"/>
       <c r="H135" s="72"/>
       <c r="I135" s="72"/>
       <c r="J135" s="81" t="e">
@@ -13732,11 +13732,11 @@
       <c r="D136" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E136" s="352" t="s">
+      <c r="E136" s="329" t="s">
         <v>236</v>
       </c>
-      <c r="F136" s="352"/>
-      <c r="G136" s="352"/>
+      <c r="F136" s="329"/>
+      <c r="G136" s="329"/>
       <c r="H136" s="72"/>
       <c r="I136" s="72"/>
       <c r="J136" s="81" t="e">
@@ -13759,11 +13759,11 @@
       <c r="D137" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E137" s="365" t="s">
-        <v>44</v>
-      </c>
-      <c r="F137" s="366"/>
-      <c r="G137" s="367"/>
+      <c r="E137" s="339" t="s">
+        <v>44</v>
+      </c>
+      <c r="F137" s="340"/>
+      <c r="G137" s="341"/>
       <c r="H137" s="115"/>
       <c r="I137" s="115"/>
       <c r="J137" s="116"/>
@@ -13777,15 +13777,15 @@
       <c r="B138" s="58">
         <v>118</v>
       </c>
-      <c r="C138" s="339" t="s">
+      <c r="C138" s="332" t="s">
         <v>237</v>
       </c>
-      <c r="D138" s="336" t="s">
+      <c r="D138" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E138" s="337"/>
-      <c r="F138" s="337"/>
-      <c r="G138" s="338"/>
+      <c r="E138" s="324"/>
+      <c r="F138" s="324"/>
+      <c r="G138" s="325"/>
       <c r="H138" s="97"/>
       <c r="I138" s="117"/>
       <c r="J138" s="118"/>
@@ -13798,15 +13798,15 @@
       <c r="B139" s="58">
         <v>119</v>
       </c>
-      <c r="C139" s="340"/>
+      <c r="C139" s="333"/>
       <c r="D139" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E139" s="355" t="s">
+      <c r="E139" s="336" t="s">
         <v>19</v>
       </c>
-      <c r="F139" s="356"/>
-      <c r="G139" s="357"/>
+      <c r="F139" s="337"/>
+      <c r="G139" s="338"/>
       <c r="H139" s="109"/>
       <c r="I139" s="113"/>
       <c r="J139" s="81" t="e">
@@ -13831,10 +13831,10 @@
       <c r="E140" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="F140" s="336" t="s">
+      <c r="F140" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G140" s="338"/>
+      <c r="G140" s="325"/>
       <c r="H140" s="110"/>
       <c r="I140" s="97"/>
       <c r="J140" s="102"/>
@@ -13856,7 +13856,7 @@
       <c r="E141" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F141" s="372" t="s">
+      <c r="F141" s="330" t="s">
         <v>55</v>
       </c>
       <c r="G141" s="108" t="s">
@@ -13883,7 +13883,7 @@
       <c r="E142" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F142" s="373"/>
+      <c r="F142" s="331"/>
       <c r="G142" s="60" t="s">
         <v>238</v>
       </c>
@@ -13934,10 +13934,10 @@
       <c r="E144" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="F144" s="336" t="s">
+      <c r="F144" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G144" s="338"/>
+      <c r="G144" s="325"/>
       <c r="H144" s="97"/>
       <c r="I144" s="110"/>
       <c r="J144" s="102"/>
@@ -13959,7 +13959,7 @@
       <c r="E145" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F145" s="372" t="s">
+      <c r="F145" s="330" t="s">
         <v>55</v>
       </c>
       <c r="G145" s="108" t="s">
@@ -13986,7 +13986,7 @@
       <c r="E146" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F146" s="373"/>
+      <c r="F146" s="331"/>
       <c r="G146" s="60" t="s">
         <v>18</v>
       </c>
@@ -14056,15 +14056,15 @@
       <c r="B149" s="58">
         <v>129</v>
       </c>
-      <c r="C149" s="339" t="s">
+      <c r="C149" s="332" t="s">
         <v>239</v>
       </c>
-      <c r="D149" s="336" t="s">
+      <c r="D149" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E149" s="337"/>
-      <c r="F149" s="337"/>
-      <c r="G149" s="338"/>
+      <c r="E149" s="324"/>
+      <c r="F149" s="324"/>
+      <c r="G149" s="325"/>
       <c r="H149" s="97"/>
       <c r="I149" s="110"/>
       <c r="J149" s="102"/>
@@ -14077,15 +14077,15 @@
       <c r="B150" s="121">
         <v>130</v>
       </c>
-      <c r="C150" s="340"/>
+      <c r="C150" s="333"/>
       <c r="D150" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E150" s="358" t="s">
-        <v>44</v>
-      </c>
-      <c r="F150" s="359"/>
-      <c r="G150" s="359"/>
+      <c r="E150" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F150" s="335"/>
+      <c r="G150" s="335"/>
       <c r="H150" s="104"/>
       <c r="I150" s="104"/>
       <c r="J150" s="81"/>
@@ -14104,11 +14104,11 @@
       <c r="D151" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E151" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F151" s="346"/>
-      <c r="G151" s="347"/>
+      <c r="E151" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F151" s="320"/>
+      <c r="G151" s="321"/>
       <c r="H151" s="72"/>
       <c r="I151" s="109"/>
       <c r="J151" s="81"/>
@@ -14122,15 +14122,15 @@
       <c r="B152" s="58">
         <v>132</v>
       </c>
-      <c r="C152" s="368" t="s">
+      <c r="C152" s="322" t="s">
         <v>240</v>
       </c>
-      <c r="D152" s="336" t="s">
+      <c r="D152" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E152" s="337"/>
-      <c r="F152" s="337"/>
-      <c r="G152" s="338"/>
+      <c r="E152" s="324"/>
+      <c r="F152" s="324"/>
+      <c r="G152" s="325"/>
       <c r="H152" s="97"/>
       <c r="I152" s="110"/>
       <c r="J152" s="102"/>
@@ -14143,15 +14143,15 @@
       <c r="B153" s="58">
         <v>133</v>
       </c>
-      <c r="C153" s="368"/>
+      <c r="C153" s="322"/>
       <c r="D153" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E153" s="369" t="s">
+      <c r="E153" s="326" t="s">
         <v>241</v>
       </c>
-      <c r="F153" s="370"/>
-      <c r="G153" s="371"/>
+      <c r="F153" s="327"/>
+      <c r="G153" s="328"/>
       <c r="H153" s="122"/>
       <c r="I153" s="123"/>
       <c r="J153" s="81"/>
@@ -14170,11 +14170,11 @@
       <c r="D154" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E154" s="352" t="s">
+      <c r="E154" s="329" t="s">
         <v>198</v>
       </c>
-      <c r="F154" s="352"/>
-      <c r="G154" s="352"/>
+      <c r="F154" s="329"/>
+      <c r="G154" s="329"/>
       <c r="H154" s="72"/>
       <c r="I154" s="120" t="e">
         <f>SUM(#REF!)</f>
@@ -14200,120 +14200,15 @@
     </row>
   </sheetData>
   <mergeCells count="142">
-    <mergeCell ref="E151:G151"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D152:G152"/>
-    <mergeCell ref="E153:G153"/>
-    <mergeCell ref="E154:G154"/>
-    <mergeCell ref="F140:G140"/>
-    <mergeCell ref="F141:F142"/>
-    <mergeCell ref="F144:G144"/>
-    <mergeCell ref="F145:F146"/>
-    <mergeCell ref="C149:C150"/>
-    <mergeCell ref="D149:G149"/>
-    <mergeCell ref="E150:G150"/>
-    <mergeCell ref="E134:G134"/>
-    <mergeCell ref="E135:G135"/>
-    <mergeCell ref="E136:G136"/>
-    <mergeCell ref="E137:G137"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:G138"/>
-    <mergeCell ref="E139:G139"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="E130:G130"/>
-    <mergeCell ref="C131:C133"/>
-    <mergeCell ref="D131:G131"/>
-    <mergeCell ref="E132:G132"/>
-    <mergeCell ref="E133:G133"/>
-    <mergeCell ref="E121:G121"/>
-    <mergeCell ref="E122:G122"/>
-    <mergeCell ref="C123:C126"/>
-    <mergeCell ref="D123:G123"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="E116:G116"/>
-    <mergeCell ref="E117:G117"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:G118"/>
-    <mergeCell ref="E119:G119"/>
-    <mergeCell ref="E120:G120"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="D111:G111"/>
-    <mergeCell ref="E112:G112"/>
-    <mergeCell ref="E113:G113"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="D114:G114"/>
-    <mergeCell ref="E115:G115"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="D107:G107"/>
-    <mergeCell ref="E108:G108"/>
-    <mergeCell ref="E109:G109"/>
-    <mergeCell ref="E110:G110"/>
-    <mergeCell ref="E104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="E98:G98"/>
-    <mergeCell ref="E99:G99"/>
-    <mergeCell ref="E100:G100"/>
-    <mergeCell ref="C101:C103"/>
-    <mergeCell ref="D101:G101"/>
-    <mergeCell ref="E102:G102"/>
-    <mergeCell ref="E103:G103"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="E94:G94"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="D95:G95"/>
-    <mergeCell ref="E96:G96"/>
-    <mergeCell ref="E97:G97"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:G87"/>
-    <mergeCell ref="E88:G88"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="E90:G90"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="D91:G91"/>
-    <mergeCell ref="E92:G92"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="G81:I81"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="E64:G64"/>
-    <mergeCell ref="C65:C67"/>
-    <mergeCell ref="D65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="D60:G60"/>
-    <mergeCell ref="E61:G61"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D55:G55"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:G48"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:G46"/>
-    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:G24"/>
+    <mergeCell ref="I22:J24"/>
     <mergeCell ref="C29:G29"/>
     <mergeCell ref="C30:C34"/>
     <mergeCell ref="D30:G30"/>
@@ -14333,15 +14228,120 @@
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="E36:G36"/>
     <mergeCell ref="E37:G37"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:G24"/>
-    <mergeCell ref="I22:J24"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D55:G55"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="G81:I81"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="C65:C67"/>
+    <mergeCell ref="D65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="E94:G94"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:G95"/>
+    <mergeCell ref="E96:G96"/>
+    <mergeCell ref="E97:G97"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:G87"/>
+    <mergeCell ref="E88:G88"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="E90:G90"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="D91:G91"/>
+    <mergeCell ref="E92:G92"/>
+    <mergeCell ref="E104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="E98:G98"/>
+    <mergeCell ref="E99:G99"/>
+    <mergeCell ref="E100:G100"/>
+    <mergeCell ref="C101:C103"/>
+    <mergeCell ref="D101:G101"/>
+    <mergeCell ref="E102:G102"/>
+    <mergeCell ref="E103:G103"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="D111:G111"/>
+    <mergeCell ref="E112:G112"/>
+    <mergeCell ref="E113:G113"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:G114"/>
+    <mergeCell ref="E115:G115"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="D107:G107"/>
+    <mergeCell ref="E108:G108"/>
+    <mergeCell ref="E109:G109"/>
+    <mergeCell ref="E110:G110"/>
+    <mergeCell ref="E121:G121"/>
+    <mergeCell ref="E122:G122"/>
+    <mergeCell ref="C123:C126"/>
+    <mergeCell ref="D123:G123"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="E116:G116"/>
+    <mergeCell ref="E117:G117"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:G118"/>
+    <mergeCell ref="E119:G119"/>
+    <mergeCell ref="E120:G120"/>
+    <mergeCell ref="E134:G134"/>
+    <mergeCell ref="E135:G135"/>
+    <mergeCell ref="E136:G136"/>
+    <mergeCell ref="E137:G137"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:G138"/>
+    <mergeCell ref="E139:G139"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="E130:G130"/>
+    <mergeCell ref="C131:C133"/>
+    <mergeCell ref="D131:G131"/>
+    <mergeCell ref="E132:G132"/>
+    <mergeCell ref="E133:G133"/>
+    <mergeCell ref="E151:G151"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:G152"/>
+    <mergeCell ref="E153:G153"/>
+    <mergeCell ref="E154:G154"/>
+    <mergeCell ref="F140:G140"/>
+    <mergeCell ref="F141:F142"/>
+    <mergeCell ref="F144:G144"/>
+    <mergeCell ref="F145:F146"/>
+    <mergeCell ref="C149:C150"/>
+    <mergeCell ref="D149:G149"/>
+    <mergeCell ref="E150:G150"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="64" orientation="portrait" r:id="rId1"/>
@@ -14371,15 +14371,15 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="319" t="s">
+      <c r="B1" s="357" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="319"/>
-      <c r="D1" s="319"/>
-      <c r="E1" s="319"/>
-      <c r="F1" s="319"/>
-      <c r="G1" s="319"/>
-      <c r="H1" s="319"/>
+      <c r="C1" s="357"/>
+      <c r="D1" s="357"/>
+      <c r="E1" s="357"/>
+      <c r="F1" s="357"/>
+      <c r="G1" s="357"/>
+      <c r="H1" s="357"/>
       <c r="L1" s="51"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1">
@@ -14413,30 +14413,30 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="320" t="s">
+      <c r="B3" s="358" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="320"/>
-      <c r="D3" s="320"/>
-      <c r="E3" s="320"/>
-      <c r="F3" s="320"/>
-      <c r="G3" s="320"/>
-      <c r="H3" s="320"/>
+      <c r="C3" s="358"/>
+      <c r="D3" s="358"/>
+      <c r="E3" s="358"/>
+      <c r="F3" s="358"/>
+      <c r="G3" s="358"/>
+      <c r="H3" s="358"/>
       <c r="L3" s="51"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="321" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="321"/>
-      <c r="D4" s="321"/>
-      <c r="E4" s="321"/>
-      <c r="F4" s="321"/>
-      <c r="G4" s="321"/>
-      <c r="H4" s="321"/>
+      <c r="B4" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="359"/>
+      <c r="D4" s="359"/>
+      <c r="E4" s="359"/>
+      <c r="F4" s="359"/>
+      <c r="G4" s="359"/>
+      <c r="H4" s="359"/>
       <c r="L4" s="51"/>
       <c r="M4" s="53"/>
     </row>
@@ -14458,40 +14458,40 @@
       <c r="A19" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="374" t="s">
+      <c r="B19" s="382" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="327" t="s">
+      <c r="C19" s="365" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="328"/>
-      <c r="E19" s="328"/>
-      <c r="F19" s="328"/>
-      <c r="G19" s="329"/>
+      <c r="D19" s="366"/>
+      <c r="E19" s="366"/>
+      <c r="F19" s="366"/>
+      <c r="G19" s="367"/>
       <c r="H19" s="55"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1">
       <c r="A20" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="325"/>
-      <c r="C20" s="330"/>
-      <c r="D20" s="331"/>
-      <c r="E20" s="331"/>
-      <c r="F20" s="331"/>
-      <c r="G20" s="332"/>
+      <c r="B20" s="363"/>
+      <c r="C20" s="368"/>
+      <c r="D20" s="369"/>
+      <c r="E20" s="369"/>
+      <c r="F20" s="369"/>
+      <c r="G20" s="370"/>
       <c r="H20" s="55"/>
     </row>
     <row r="21" spans="1:13" ht="24" customHeight="1">
       <c r="A21" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="326"/>
-      <c r="C21" s="333"/>
-      <c r="D21" s="334"/>
-      <c r="E21" s="334"/>
-      <c r="F21" s="334"/>
-      <c r="G21" s="335"/>
+      <c r="B21" s="364"/>
+      <c r="C21" s="371"/>
+      <c r="D21" s="372"/>
+      <c r="E21" s="372"/>
+      <c r="F21" s="372"/>
+      <c r="G21" s="373"/>
       <c r="H21" s="57" t="s">
         <v>52</v>
       </c>
@@ -14507,17 +14507,17 @@
       <c r="B25" s="57">
         <v>1</v>
       </c>
-      <c r="C25" s="375">
+      <c r="C25" s="383">
         <v>2</v>
       </c>
-      <c r="D25" s="376"/>
+      <c r="D25" s="384"/>
       <c r="E25" s="57">
         <v>3</v>
       </c>
-      <c r="F25" s="375">
+      <c r="F25" s="383">
         <v>4</v>
       </c>
-      <c r="G25" s="376"/>
+      <c r="G25" s="384"/>
       <c r="H25" s="57">
         <v>8</v>
       </c>
@@ -14573,15 +14573,15 @@
       <c r="B29" s="58">
         <v>2</v>
       </c>
-      <c r="C29" s="377" t="s">
+      <c r="C29" s="374" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="378"/>
-      <c r="E29" s="336" t="s">
+      <c r="D29" s="375"/>
+      <c r="E29" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F29" s="337"/>
-      <c r="G29" s="338"/>
+      <c r="F29" s="324"/>
+      <c r="G29" s="325"/>
       <c r="H29" s="64"/>
       <c r="I29" s="49"/>
       <c r="M29" s="65"/>
@@ -14593,15 +14593,15 @@
       <c r="B30" s="58">
         <v>3</v>
       </c>
-      <c r="C30" s="379"/>
-      <c r="D30" s="380"/>
+      <c r="C30" s="376"/>
+      <c r="D30" s="377"/>
       <c r="E30" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="355" t="s">
+      <c r="F30" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="G30" s="357"/>
+      <c r="G30" s="338"/>
       <c r="H30" s="72" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14616,15 +14616,15 @@
       <c r="B31" s="58">
         <v>4</v>
       </c>
-      <c r="C31" s="379"/>
-      <c r="D31" s="380"/>
+      <c r="C31" s="376"/>
+      <c r="D31" s="377"/>
       <c r="E31" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="355" t="s">
+      <c r="F31" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="G31" s="357"/>
+      <c r="G31" s="338"/>
       <c r="H31" s="64"/>
       <c r="I31" s="49"/>
       <c r="M31" s="53"/>
@@ -14636,15 +14636,15 @@
       <c r="B32" s="58">
         <v>5</v>
       </c>
-      <c r="C32" s="379"/>
-      <c r="D32" s="380"/>
+      <c r="C32" s="376"/>
+      <c r="D32" s="377"/>
       <c r="E32" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="355" t="s">
+      <c r="F32" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="G32" s="357"/>
+      <c r="G32" s="338"/>
       <c r="H32" s="64"/>
       <c r="I32" s="49"/>
     </row>
@@ -14664,10 +14664,10 @@
       <c r="E33" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F33" s="345" t="s">
+      <c r="F33" s="319" t="s">
         <v>170</v>
       </c>
-      <c r="G33" s="347"/>
+      <c r="G33" s="321"/>
       <c r="H33" s="64"/>
       <c r="I33" s="49"/>
       <c r="J33" s="49"/>
@@ -14688,10 +14688,10 @@
       <c r="E34" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G34" s="347"/>
+      <c r="F34" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="321"/>
       <c r="H34" s="64"/>
       <c r="I34" s="49"/>
       <c r="J34" s="49"/>
@@ -14704,15 +14704,15 @@
       <c r="B35" s="58">
         <v>8</v>
       </c>
-      <c r="C35" s="377" t="s">
+      <c r="C35" s="374" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="378"/>
-      <c r="E35" s="336" t="s">
+      <c r="D35" s="375"/>
+      <c r="E35" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F35" s="337"/>
-      <c r="G35" s="338"/>
+      <c r="F35" s="324"/>
+      <c r="G35" s="325"/>
       <c r="H35" s="64"/>
       <c r="I35" s="49"/>
     </row>
@@ -14723,15 +14723,15 @@
       <c r="B36" s="58">
         <v>9</v>
       </c>
-      <c r="C36" s="379"/>
-      <c r="D36" s="380"/>
-      <c r="E36" s="372" t="s">
+      <c r="C36" s="376"/>
+      <c r="D36" s="377"/>
+      <c r="E36" s="330" t="s">
         <v>55</v>
       </c>
-      <c r="F36" s="355" t="s">
+      <c r="F36" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="G36" s="357"/>
+      <c r="G36" s="338"/>
       <c r="H36" s="72" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -14746,13 +14746,13 @@
       <c r="B37" s="58">
         <v>10</v>
       </c>
-      <c r="C37" s="381"/>
-      <c r="D37" s="382"/>
-      <c r="E37" s="373"/>
-      <c r="F37" s="355" t="s">
+      <c r="C37" s="380"/>
+      <c r="D37" s="381"/>
+      <c r="E37" s="331"/>
+      <c r="F37" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="G37" s="357"/>
+      <c r="G37" s="338"/>
       <c r="H37" s="64"/>
       <c r="I37" s="49"/>
     </row>
@@ -14763,15 +14763,15 @@
       <c r="B38" s="58">
         <v>11</v>
       </c>
-      <c r="C38" s="377" t="s">
+      <c r="C38" s="374" t="s">
         <v>174</v>
       </c>
-      <c r="D38" s="378"/>
-      <c r="E38" s="336" t="s">
+      <c r="D38" s="375"/>
+      <c r="E38" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F38" s="337"/>
-      <c r="G38" s="338"/>
+      <c r="F38" s="324"/>
+      <c r="G38" s="325"/>
       <c r="H38" s="64"/>
       <c r="I38" s="49"/>
     </row>
@@ -14782,15 +14782,15 @@
       <c r="B39" s="58">
         <v>12</v>
       </c>
-      <c r="C39" s="379"/>
-      <c r="D39" s="380"/>
+      <c r="C39" s="376"/>
+      <c r="D39" s="377"/>
       <c r="E39" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="G39" s="384"/>
+      <c r="F39" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G39" s="379"/>
       <c r="H39" s="64"/>
       <c r="I39" s="49"/>
     </row>
@@ -14810,10 +14810,10 @@
       <c r="E40" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G40" s="347"/>
+      <c r="F40" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G40" s="321"/>
       <c r="H40" s="64"/>
       <c r="I40" s="49"/>
       <c r="J40" s="49"/>
@@ -14825,15 +14825,15 @@
       <c r="B41" s="58">
         <v>14</v>
       </c>
-      <c r="C41" s="377" t="s">
+      <c r="C41" s="374" t="s">
         <v>175</v>
       </c>
-      <c r="D41" s="378"/>
-      <c r="E41" s="336" t="s">
+      <c r="D41" s="375"/>
+      <c r="E41" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F41" s="337"/>
-      <c r="G41" s="338"/>
+      <c r="F41" s="324"/>
+      <c r="G41" s="325"/>
       <c r="H41" s="64"/>
       <c r="I41" s="49"/>
     </row>
@@ -14844,15 +14844,15 @@
       <c r="B42" s="58">
         <v>15</v>
       </c>
-      <c r="C42" s="379"/>
-      <c r="D42" s="380"/>
+      <c r="C42" s="376"/>
+      <c r="D42" s="377"/>
       <c r="E42" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="355" t="s">
+      <c r="F42" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="G42" s="357"/>
+      <c r="G42" s="338"/>
       <c r="H42" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14875,10 +14875,10 @@
       <c r="E43" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F43" s="345" t="s">
+      <c r="F43" s="319" t="s">
         <v>176</v>
       </c>
-      <c r="G43" s="347"/>
+      <c r="G43" s="321"/>
       <c r="H43" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14902,10 +14902,10 @@
       <c r="E44" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F44" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G44" s="347"/>
+      <c r="F44" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" s="321"/>
       <c r="H44" s="64"/>
       <c r="I44" s="49"/>
       <c r="J44" s="49"/>
@@ -14917,15 +14917,15 @@
       <c r="B45" s="58">
         <v>18</v>
       </c>
-      <c r="C45" s="377" t="s">
+      <c r="C45" s="374" t="s">
         <v>177</v>
       </c>
-      <c r="D45" s="378"/>
-      <c r="E45" s="336" t="s">
+      <c r="D45" s="375"/>
+      <c r="E45" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="337"/>
-      <c r="G45" s="338"/>
+      <c r="F45" s="324"/>
+      <c r="G45" s="325"/>
       <c r="H45" s="64"/>
       <c r="I45" s="49"/>
     </row>
@@ -14936,15 +14936,15 @@
       <c r="B46" s="58">
         <v>19</v>
       </c>
-      <c r="C46" s="379"/>
-      <c r="D46" s="380"/>
+      <c r="C46" s="376"/>
+      <c r="D46" s="377"/>
       <c r="E46" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="G46" s="384"/>
+      <c r="F46" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" s="379"/>
       <c r="H46" s="64"/>
       <c r="I46" s="49"/>
     </row>
@@ -14964,8 +14964,8 @@
       <c r="E47" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F47" s="345"/>
-      <c r="G47" s="347"/>
+      <c r="F47" s="319"/>
+      <c r="G47" s="321"/>
       <c r="H47" s="64"/>
       <c r="I47" s="49"/>
       <c r="J47" s="49"/>
@@ -14986,10 +14986,10 @@
       <c r="E48" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F48" s="345" t="s">
+      <c r="F48" s="319" t="s">
         <v>178</v>
       </c>
-      <c r="G48" s="347"/>
+      <c r="G48" s="321"/>
       <c r="H48" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15013,10 +15013,10 @@
       <c r="E49" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F49" s="345" t="s">
+      <c r="F49" s="319" t="s">
         <v>8</v>
       </c>
-      <c r="G49" s="347"/>
+      <c r="G49" s="321"/>
       <c r="H49" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15031,13 +15031,13 @@
       <c r="B50" s="58">
         <v>24</v>
       </c>
-      <c r="C50" s="336" t="s">
+      <c r="C50" s="323" t="s">
         <v>179</v>
       </c>
-      <c r="D50" s="337"/>
-      <c r="E50" s="337"/>
-      <c r="F50" s="337"/>
-      <c r="G50" s="338"/>
+      <c r="D50" s="324"/>
+      <c r="E50" s="324"/>
+      <c r="F50" s="324"/>
+      <c r="G50" s="325"/>
       <c r="H50" s="64"/>
       <c r="I50" s="49"/>
     </row>
@@ -15048,13 +15048,13 @@
       <c r="B51" s="58">
         <v>25</v>
       </c>
-      <c r="C51" s="336" t="s">
+      <c r="C51" s="323" t="s">
         <v>180</v>
       </c>
-      <c r="D51" s="337"/>
-      <c r="E51" s="337"/>
-      <c r="F51" s="337"/>
-      <c r="G51" s="338"/>
+      <c r="D51" s="324"/>
+      <c r="E51" s="324"/>
+      <c r="F51" s="324"/>
+      <c r="G51" s="325"/>
       <c r="H51" s="64" t="e">
         <f>нак.расх.!G29-зат.осн.про.!H75-зат.осн.про.!H99</f>
         <v>#REF!</v>
@@ -15100,15 +15100,15 @@
       <c r="B53" s="58">
         <v>2</v>
       </c>
-      <c r="C53" s="377" t="s">
+      <c r="C53" s="374" t="s">
         <v>54</v>
       </c>
-      <c r="D53" s="378"/>
-      <c r="E53" s="336" t="s">
+      <c r="D53" s="375"/>
+      <c r="E53" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F53" s="337"/>
-      <c r="G53" s="338"/>
+      <c r="F53" s="324"/>
+      <c r="G53" s="325"/>
       <c r="H53" s="64"/>
       <c r="I53" s="49"/>
       <c r="M53" s="53" t="e">
@@ -15123,15 +15123,15 @@
       <c r="B54" s="58">
         <v>3</v>
       </c>
-      <c r="C54" s="379"/>
-      <c r="D54" s="380"/>
+      <c r="C54" s="376"/>
+      <c r="D54" s="377"/>
       <c r="E54" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F54" s="355" t="s">
+      <c r="F54" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="G54" s="357"/>
+      <c r="G54" s="338"/>
       <c r="H54" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15145,15 +15145,15 @@
       <c r="B55" s="58">
         <v>4</v>
       </c>
-      <c r="C55" s="379"/>
-      <c r="D55" s="380"/>
+      <c r="C55" s="376"/>
+      <c r="D55" s="377"/>
       <c r="E55" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F55" s="355" t="s">
+      <c r="F55" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="G55" s="357"/>
+      <c r="G55" s="338"/>
       <c r="H55" s="64"/>
       <c r="I55" s="49"/>
     </row>
@@ -15164,15 +15164,15 @@
       <c r="B56" s="58">
         <v>5</v>
       </c>
-      <c r="C56" s="379"/>
-      <c r="D56" s="380"/>
+      <c r="C56" s="376"/>
+      <c r="D56" s="377"/>
       <c r="E56" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="355" t="s">
+      <c r="F56" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="G56" s="357"/>
+      <c r="G56" s="338"/>
       <c r="H56" s="64"/>
       <c r="I56" s="49"/>
     </row>
@@ -15192,10 +15192,10 @@
       <c r="E57" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="345" t="s">
+      <c r="F57" s="319" t="s">
         <v>170</v>
       </c>
-      <c r="G57" s="347"/>
+      <c r="G57" s="321"/>
       <c r="H57" s="64"/>
       <c r="I57" s="49"/>
       <c r="J57" s="49"/>
@@ -15216,10 +15216,10 @@
       <c r="E58" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F58" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G58" s="347"/>
+      <c r="F58" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G58" s="321"/>
       <c r="H58" s="64"/>
       <c r="I58" s="49"/>
     </row>
@@ -15230,15 +15230,15 @@
       <c r="B59" s="58">
         <v>8</v>
       </c>
-      <c r="C59" s="377" t="s">
+      <c r="C59" s="374" t="s">
         <v>171</v>
       </c>
-      <c r="D59" s="378"/>
-      <c r="E59" s="336" t="s">
+      <c r="D59" s="375"/>
+      <c r="E59" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F59" s="337"/>
-      <c r="G59" s="338"/>
+      <c r="F59" s="324"/>
+      <c r="G59" s="325"/>
       <c r="H59" s="64"/>
       <c r="I59" s="49"/>
     </row>
@@ -15249,15 +15249,15 @@
       <c r="B60" s="58">
         <v>9</v>
       </c>
-      <c r="C60" s="379"/>
-      <c r="D60" s="380"/>
-      <c r="E60" s="372" t="s">
+      <c r="C60" s="376"/>
+      <c r="D60" s="377"/>
+      <c r="E60" s="330" t="s">
         <v>55</v>
       </c>
-      <c r="F60" s="355" t="s">
+      <c r="F60" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="G60" s="357"/>
+      <c r="G60" s="338"/>
       <c r="H60" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15271,13 +15271,13 @@
       <c r="B61" s="58">
         <v>10</v>
       </c>
-      <c r="C61" s="381"/>
-      <c r="D61" s="382"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="355" t="s">
+      <c r="C61" s="380"/>
+      <c r="D61" s="381"/>
+      <c r="E61" s="331"/>
+      <c r="F61" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="G61" s="357"/>
+      <c r="G61" s="338"/>
       <c r="H61" s="64"/>
       <c r="I61" s="49"/>
     </row>
@@ -15288,15 +15288,15 @@
       <c r="B62" s="58">
         <v>11</v>
       </c>
-      <c r="C62" s="377" t="s">
+      <c r="C62" s="374" t="s">
         <v>174</v>
       </c>
-      <c r="D62" s="378"/>
-      <c r="E62" s="336" t="s">
+      <c r="D62" s="375"/>
+      <c r="E62" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F62" s="337"/>
-      <c r="G62" s="338"/>
+      <c r="F62" s="324"/>
+      <c r="G62" s="325"/>
       <c r="H62" s="64"/>
       <c r="I62" s="49"/>
     </row>
@@ -15307,15 +15307,15 @@
       <c r="B63" s="58">
         <v>12</v>
       </c>
-      <c r="C63" s="379"/>
-      <c r="D63" s="380"/>
+      <c r="C63" s="376"/>
+      <c r="D63" s="377"/>
       <c r="E63" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F63" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="G63" s="384"/>
+      <c r="F63" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G63" s="379"/>
       <c r="H63" s="64"/>
       <c r="I63" s="49"/>
       <c r="J63" s="49"/>
@@ -15336,10 +15336,10 @@
       <c r="E64" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F64" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G64" s="347"/>
+      <c r="F64" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G64" s="321"/>
       <c r="H64" s="64"/>
       <c r="I64" s="49"/>
     </row>
@@ -15350,15 +15350,15 @@
       <c r="B65" s="58">
         <v>14</v>
       </c>
-      <c r="C65" s="377" t="s">
+      <c r="C65" s="374" t="s">
         <v>175</v>
       </c>
-      <c r="D65" s="378"/>
-      <c r="E65" s="336" t="s">
+      <c r="D65" s="375"/>
+      <c r="E65" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="337"/>
-      <c r="G65" s="338"/>
+      <c r="F65" s="324"/>
+      <c r="G65" s="325"/>
       <c r="H65" s="64"/>
       <c r="I65" s="49"/>
     </row>
@@ -15369,15 +15369,15 @@
       <c r="B66" s="58">
         <v>15</v>
       </c>
-      <c r="C66" s="379"/>
-      <c r="D66" s="380"/>
+      <c r="C66" s="376"/>
+      <c r="D66" s="377"/>
       <c r="E66" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F66" s="355" t="s">
+      <c r="F66" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="G66" s="357"/>
+      <c r="G66" s="338"/>
       <c r="H66" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15401,10 +15401,10 @@
       <c r="E67" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="345" t="s">
+      <c r="F67" s="319" t="s">
         <v>176</v>
       </c>
-      <c r="G67" s="347"/>
+      <c r="G67" s="321"/>
       <c r="H67" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15427,10 +15427,10 @@
       <c r="E68" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F68" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G68" s="347"/>
+      <c r="F68" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G68" s="321"/>
       <c r="H68" s="64"/>
       <c r="I68" s="49"/>
     </row>
@@ -15441,15 +15441,15 @@
       <c r="B69" s="58">
         <v>18</v>
       </c>
-      <c r="C69" s="377" t="s">
+      <c r="C69" s="374" t="s">
         <v>177</v>
       </c>
-      <c r="D69" s="378"/>
-      <c r="E69" s="336" t="s">
+      <c r="D69" s="375"/>
+      <c r="E69" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="337"/>
-      <c r="G69" s="338"/>
+      <c r="F69" s="324"/>
+      <c r="G69" s="325"/>
       <c r="H69" s="64"/>
       <c r="I69" s="49"/>
       <c r="J69" s="49"/>
@@ -15461,15 +15461,15 @@
       <c r="B70" s="58">
         <v>19</v>
       </c>
-      <c r="C70" s="379"/>
-      <c r="D70" s="380"/>
+      <c r="C70" s="376"/>
+      <c r="D70" s="377"/>
       <c r="E70" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F70" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="G70" s="384"/>
+      <c r="F70" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G70" s="379"/>
       <c r="H70" s="64"/>
       <c r="I70" s="49"/>
     </row>
@@ -15489,8 +15489,8 @@
       <c r="E71" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F71" s="345"/>
-      <c r="G71" s="347"/>
+      <c r="F71" s="319"/>
+      <c r="G71" s="321"/>
       <c r="H71" s="64"/>
       <c r="I71" s="49"/>
     </row>
@@ -15507,10 +15507,10 @@
       <c r="E72" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F72" s="345" t="s">
+      <c r="F72" s="319" t="s">
         <v>178</v>
       </c>
-      <c r="G72" s="347"/>
+      <c r="G72" s="321"/>
       <c r="H72" s="64"/>
       <c r="I72" s="49"/>
       <c r="J72" s="49"/>
@@ -15533,10 +15533,10 @@
       <c r="E73" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F73" s="345" t="s">
+      <c r="F73" s="319" t="s">
         <v>8</v>
       </c>
-      <c r="G73" s="347"/>
+      <c r="G73" s="321"/>
       <c r="H73" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15550,13 +15550,13 @@
       <c r="B74" s="58">
         <v>24</v>
       </c>
-      <c r="C74" s="336" t="s">
+      <c r="C74" s="323" t="s">
         <v>179</v>
       </c>
-      <c r="D74" s="337"/>
-      <c r="E74" s="337"/>
-      <c r="F74" s="337"/>
-      <c r="G74" s="338"/>
+      <c r="D74" s="324"/>
+      <c r="E74" s="324"/>
+      <c r="F74" s="324"/>
+      <c r="G74" s="325"/>
       <c r="H74" s="64"/>
       <c r="I74" s="49"/>
       <c r="J74" s="49"/>
@@ -15567,13 +15567,13 @@
       <c r="B75" s="58">
         <v>25</v>
       </c>
-      <c r="C75" s="336" t="s">
+      <c r="C75" s="323" t="s">
         <v>180</v>
       </c>
-      <c r="D75" s="337"/>
-      <c r="E75" s="337"/>
-      <c r="F75" s="337"/>
-      <c r="G75" s="338"/>
+      <c r="D75" s="324"/>
+      <c r="E75" s="324"/>
+      <c r="F75" s="324"/>
+      <c r="G75" s="325"/>
       <c r="H75" s="64" t="e">
         <f>нак.расх.!G29*4%</f>
         <v>#REF!</v>
@@ -15619,15 +15619,15 @@
       <c r="B77" s="58">
         <v>2</v>
       </c>
-      <c r="C77" s="377" t="s">
+      <c r="C77" s="374" t="s">
         <v>54</v>
       </c>
-      <c r="D77" s="378"/>
-      <c r="E77" s="336" t="s">
+      <c r="D77" s="375"/>
+      <c r="E77" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F77" s="337"/>
-      <c r="G77" s="338"/>
+      <c r="F77" s="324"/>
+      <c r="G77" s="325"/>
       <c r="H77" s="64"/>
       <c r="M77" s="53" t="e">
         <f>H76-M76</f>
@@ -15638,15 +15638,15 @@
       <c r="B78" s="58">
         <v>3</v>
       </c>
-      <c r="C78" s="379"/>
-      <c r="D78" s="380"/>
+      <c r="C78" s="376"/>
+      <c r="D78" s="377"/>
       <c r="E78" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F78" s="355" t="s">
+      <c r="F78" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="G78" s="357"/>
+      <c r="G78" s="338"/>
       <c r="H78" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15656,30 +15656,30 @@
       <c r="B79" s="58">
         <v>4</v>
       </c>
-      <c r="C79" s="379"/>
-      <c r="D79" s="380"/>
+      <c r="C79" s="376"/>
+      <c r="D79" s="377"/>
       <c r="E79" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F79" s="355" t="s">
+      <c r="F79" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="G79" s="357"/>
+      <c r="G79" s="338"/>
       <c r="H79" s="64"/>
     </row>
     <row r="80" spans="1:13" ht="15.75" customHeight="1">
       <c r="B80" s="58">
         <v>5</v>
       </c>
-      <c r="C80" s="379"/>
-      <c r="D80" s="380"/>
+      <c r="C80" s="376"/>
+      <c r="D80" s="377"/>
       <c r="E80" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F80" s="355" t="s">
+      <c r="F80" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="G80" s="357"/>
+      <c r="G80" s="338"/>
       <c r="H80" s="64"/>
     </row>
     <row r="81" spans="2:8" ht="15.75" customHeight="1">
@@ -15695,10 +15695,10 @@
       <c r="E81" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="345" t="s">
+      <c r="F81" s="319" t="s">
         <v>170</v>
       </c>
-      <c r="G81" s="347"/>
+      <c r="G81" s="321"/>
       <c r="H81" s="64"/>
     </row>
     <row r="82" spans="2:8" ht="15.75" customHeight="1">
@@ -15714,40 +15714,40 @@
       <c r="E82" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G82" s="347"/>
+      <c r="F82" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G82" s="321"/>
       <c r="H82" s="64"/>
     </row>
     <row r="83" spans="2:8" ht="15.75" customHeight="1">
       <c r="B83" s="58">
         <v>8</v>
       </c>
-      <c r="C83" s="377" t="s">
+      <c r="C83" s="374" t="s">
         <v>171</v>
       </c>
-      <c r="D83" s="378"/>
-      <c r="E83" s="336" t="s">
+      <c r="D83" s="375"/>
+      <c r="E83" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F83" s="337"/>
-      <c r="G83" s="338"/>
+      <c r="F83" s="324"/>
+      <c r="G83" s="325"/>
       <c r="H83" s="64"/>
     </row>
     <row r="84" spans="2:8" ht="15.75" customHeight="1">
       <c r="B84" s="58">
         <v>9</v>
       </c>
-      <c r="C84" s="379"/>
-      <c r="D84" s="380"/>
-      <c r="E84" s="372" t="s">
+      <c r="C84" s="376"/>
+      <c r="D84" s="377"/>
+      <c r="E84" s="330" t="s">
         <v>55</v>
       </c>
-      <c r="F84" s="355" t="s">
+      <c r="F84" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="G84" s="357"/>
+      <c r="G84" s="338"/>
       <c r="H84" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15757,43 +15757,43 @@
       <c r="B85" s="58">
         <v>10</v>
       </c>
-      <c r="C85" s="381"/>
-      <c r="D85" s="382"/>
-      <c r="E85" s="373"/>
-      <c r="F85" s="355" t="s">
+      <c r="C85" s="380"/>
+      <c r="D85" s="381"/>
+      <c r="E85" s="331"/>
+      <c r="F85" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="G85" s="357"/>
+      <c r="G85" s="338"/>
       <c r="H85" s="64"/>
     </row>
     <row r="86" spans="2:8" ht="15.75" customHeight="1">
       <c r="B86" s="58">
         <v>11</v>
       </c>
-      <c r="C86" s="377" t="s">
+      <c r="C86" s="374" t="s">
         <v>174</v>
       </c>
-      <c r="D86" s="378"/>
-      <c r="E86" s="336" t="s">
+      <c r="D86" s="375"/>
+      <c r="E86" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F86" s="337"/>
-      <c r="G86" s="338"/>
+      <c r="F86" s="324"/>
+      <c r="G86" s="325"/>
       <c r="H86" s="64"/>
     </row>
     <row r="87" spans="2:8" ht="15.75" customHeight="1">
       <c r="B87" s="58">
         <v>12</v>
       </c>
-      <c r="C87" s="379"/>
-      <c r="D87" s="380"/>
+      <c r="C87" s="376"/>
+      <c r="D87" s="377"/>
       <c r="E87" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F87" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="G87" s="384"/>
+      <c r="F87" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G87" s="379"/>
       <c r="H87" s="64"/>
     </row>
     <row r="88" spans="2:8" ht="15.75" customHeight="1">
@@ -15809,40 +15809,40 @@
       <c r="E88" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G88" s="347"/>
+      <c r="F88" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G88" s="321"/>
       <c r="H88" s="64"/>
     </row>
     <row r="89" spans="2:8" ht="15.75" customHeight="1">
       <c r="B89" s="58">
         <v>14</v>
       </c>
-      <c r="C89" s="377" t="s">
+      <c r="C89" s="374" t="s">
         <v>175</v>
       </c>
-      <c r="D89" s="378"/>
-      <c r="E89" s="336" t="s">
+      <c r="D89" s="375"/>
+      <c r="E89" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F89" s="337"/>
-      <c r="G89" s="338"/>
+      <c r="F89" s="324"/>
+      <c r="G89" s="325"/>
       <c r="H89" s="64"/>
     </row>
     <row r="90" spans="2:8" ht="15.75" customHeight="1">
       <c r="B90" s="58">
         <v>15</v>
       </c>
-      <c r="C90" s="379"/>
-      <c r="D90" s="380"/>
+      <c r="C90" s="376"/>
+      <c r="D90" s="377"/>
       <c r="E90" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F90" s="355" t="s">
+      <c r="F90" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="G90" s="357"/>
+      <c r="G90" s="338"/>
       <c r="H90" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15861,10 +15861,10 @@
       <c r="E91" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F91" s="345" t="s">
+      <c r="F91" s="319" t="s">
         <v>176</v>
       </c>
-      <c r="G91" s="347"/>
+      <c r="G91" s="321"/>
       <c r="H91" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15883,40 +15883,40 @@
       <c r="E92" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F92" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G92" s="347"/>
+      <c r="F92" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G92" s="321"/>
       <c r="H92" s="64"/>
     </row>
     <row r="93" spans="2:8" ht="15.75" customHeight="1">
       <c r="B93" s="58">
         <v>18</v>
       </c>
-      <c r="C93" s="377" t="s">
+      <c r="C93" s="374" t="s">
         <v>177</v>
       </c>
-      <c r="D93" s="378"/>
-      <c r="E93" s="336" t="s">
+      <c r="D93" s="375"/>
+      <c r="E93" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F93" s="337"/>
-      <c r="G93" s="338"/>
+      <c r="F93" s="324"/>
+      <c r="G93" s="325"/>
       <c r="H93" s="64"/>
     </row>
     <row r="94" spans="2:8" ht="15.75" customHeight="1">
       <c r="B94" s="58">
         <v>19</v>
       </c>
-      <c r="C94" s="379"/>
-      <c r="D94" s="380"/>
+      <c r="C94" s="376"/>
+      <c r="D94" s="377"/>
       <c r="E94" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F94" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="G94" s="384"/>
+      <c r="F94" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G94" s="379"/>
       <c r="H94" s="64"/>
     </row>
     <row r="95" spans="2:8" ht="15.75" customHeight="1">
@@ -15932,8 +15932,8 @@
       <c r="E95" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F95" s="345"/>
-      <c r="G95" s="347"/>
+      <c r="F95" s="319"/>
+      <c r="G95" s="321"/>
       <c r="H95" s="64"/>
     </row>
     <row r="96" spans="2:8" ht="32.25" customHeight="1">
@@ -15949,10 +15949,10 @@
       <c r="E96" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F96" s="345" t="s">
+      <c r="F96" s="319" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="347"/>
+      <c r="G96" s="321"/>
       <c r="H96" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15971,34 +15971,34 @@
       <c r="E97" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F97" s="345"/>
-      <c r="G97" s="347"/>
+      <c r="F97" s="319"/>
+      <c r="G97" s="321"/>
       <c r="H97" s="64"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1">
       <c r="B98" s="58">
         <v>24</v>
       </c>
-      <c r="C98" s="336" t="s">
+      <c r="C98" s="323" t="s">
         <v>179</v>
       </c>
-      <c r="D98" s="337"/>
-      <c r="E98" s="337"/>
-      <c r="F98" s="337"/>
-      <c r="G98" s="338"/>
+      <c r="D98" s="324"/>
+      <c r="E98" s="324"/>
+      <c r="F98" s="324"/>
+      <c r="G98" s="325"/>
       <c r="H98" s="64"/>
     </row>
     <row r="99" spans="2:8" ht="15.75" customHeight="1">
       <c r="B99" s="58">
         <v>25</v>
       </c>
-      <c r="C99" s="336" t="s">
+      <c r="C99" s="323" t="s">
         <v>180</v>
       </c>
-      <c r="D99" s="337"/>
-      <c r="E99" s="337"/>
-      <c r="F99" s="337"/>
-      <c r="G99" s="338"/>
+      <c r="D99" s="324"/>
+      <c r="E99" s="324"/>
+      <c r="F99" s="324"/>
+      <c r="G99" s="325"/>
       <c r="H99" s="64" t="e">
         <f>нак.расх.!G29*16%</f>
         <v>#REF!</v>
@@ -16006,39 +16006,54 @@
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="C93:D94"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="C86:D87"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="C89:D90"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="C83:D85"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C77:D80"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:G21"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C29:D32"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="C35:D37"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="C45:D46"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C53:D56"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="C59:D61"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F61:G61"/>
     <mergeCell ref="F71:G71"/>
     <mergeCell ref="C62:D63"/>
     <mergeCell ref="E62:G62"/>
@@ -16052,54 +16067,39 @@
     <mergeCell ref="C69:D70"/>
     <mergeCell ref="E69:G69"/>
     <mergeCell ref="F70:G70"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="C59:D61"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C53:D56"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="C41:D42"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="C45:D46"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="C35:D37"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C29:D32"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C77:D80"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="C83:D85"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="C86:D87"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="C89:D90"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="C93:D94"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="F95:G95"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="76" orientation="portrait" r:id="rId1"/>
@@ -16128,14 +16128,14 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="319" t="s">
+      <c r="B1" s="357" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="319"/>
-      <c r="D1" s="319"/>
-      <c r="E1" s="319"/>
-      <c r="F1" s="319"/>
-      <c r="G1" s="319"/>
+      <c r="C1" s="357"/>
+      <c r="D1" s="357"/>
+      <c r="E1" s="357"/>
+      <c r="F1" s="357"/>
+      <c r="G1" s="357"/>
       <c r="K1" s="51"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1">
@@ -16166,69 +16166,69 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="319" t="s">
+      <c r="B3" s="357" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="319"/>
-      <c r="D3" s="319"/>
-      <c r="E3" s="319"/>
-      <c r="F3" s="319"/>
-      <c r="G3" s="319"/>
+      <c r="C3" s="357"/>
+      <c r="D3" s="357"/>
+      <c r="E3" s="357"/>
+      <c r="F3" s="357"/>
+      <c r="G3" s="357"/>
       <c r="K3" s="51"/>
     </row>
     <row r="4" spans="1:11" ht="14.25" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="321" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="321"/>
-      <c r="D4" s="321"/>
-      <c r="E4" s="321"/>
-      <c r="F4" s="321"/>
-      <c r="G4" s="321"/>
+      <c r="B4" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="359"/>
+      <c r="D4" s="359"/>
+      <c r="E4" s="359"/>
+      <c r="F4" s="359"/>
+      <c r="G4" s="359"/>
       <c r="K4" s="51"/>
     </row>
     <row r="5" spans="1:11" ht="24.75" customHeight="1">
       <c r="A5" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="322" t="s">
+      <c r="B5" s="360" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="322"/>
-      <c r="D5" s="322"/>
-      <c r="E5" s="322"/>
-      <c r="F5" s="322"/>
-      <c r="G5" s="322"/>
+      <c r="C5" s="360"/>
+      <c r="D5" s="360"/>
+      <c r="E5" s="360"/>
+      <c r="F5" s="360"/>
+      <c r="G5" s="360"/>
       <c r="K5" s="51"/>
     </row>
     <row r="6" spans="1:11" ht="12" customHeight="1">
       <c r="A6" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="322" t="s">
+      <c r="B6" s="360" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="322"/>
-      <c r="D6" s="322"/>
-      <c r="E6" s="322"/>
-      <c r="F6" s="322"/>
-      <c r="G6" s="322"/>
+      <c r="C6" s="360"/>
+      <c r="D6" s="360"/>
+      <c r="E6" s="360"/>
+      <c r="F6" s="360"/>
+      <c r="G6" s="360"/>
       <c r="K6" s="51"/>
     </row>
     <row r="7" spans="1:11" ht="12" customHeight="1">
       <c r="A7" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="323" t="s">
+      <c r="B7" s="361" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="323"/>
-      <c r="D7" s="323"/>
-      <c r="E7" s="323"/>
-      <c r="F7" s="323"/>
+      <c r="C7" s="361"/>
+      <c r="D7" s="361"/>
+      <c r="E7" s="361"/>
+      <c r="F7" s="361"/>
       <c r="G7" s="71" t="s">
         <v>50</v>
       </c>
@@ -16252,37 +16252,37 @@
       <c r="A22" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="324" t="s">
+      <c r="B22" s="362" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="327" t="s">
+      <c r="C22" s="365" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="328"/>
-      <c r="E22" s="328"/>
-      <c r="F22" s="329"/>
+      <c r="D22" s="366"/>
+      <c r="E22" s="366"/>
+      <c r="F22" s="367"/>
       <c r="G22" s="55"/>
     </row>
     <row r="23" spans="1:12" ht="12" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="325"/>
-      <c r="C23" s="330"/>
-      <c r="D23" s="331"/>
-      <c r="E23" s="331"/>
-      <c r="F23" s="332"/>
+      <c r="B23" s="363"/>
+      <c r="C23" s="368"/>
+      <c r="D23" s="369"/>
+      <c r="E23" s="369"/>
+      <c r="F23" s="370"/>
       <c r="G23" s="55"/>
     </row>
     <row r="24" spans="1:12" ht="24" customHeight="1">
       <c r="A24" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="326"/>
-      <c r="C24" s="333"/>
-      <c r="D24" s="334"/>
-      <c r="E24" s="334"/>
-      <c r="F24" s="335"/>
+      <c r="B24" s="364"/>
+      <c r="C24" s="371"/>
+      <c r="D24" s="372"/>
+      <c r="E24" s="372"/>
+      <c r="F24" s="373"/>
       <c r="G24" s="57" t="s">
         <v>52</v>
       </c>
@@ -16303,10 +16303,10 @@
       <c r="D28" s="57">
         <v>3</v>
       </c>
-      <c r="E28" s="375">
+      <c r="E28" s="383">
         <v>4</v>
       </c>
-      <c r="F28" s="376"/>
+      <c r="F28" s="384"/>
       <c r="G28" s="57">
         <v>8</v>
       </c>
@@ -16318,12 +16318,12 @@
       <c r="B29" s="58">
         <v>1</v>
       </c>
-      <c r="C29" s="336" t="s">
+      <c r="C29" s="323" t="s">
         <v>184</v>
       </c>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="D29" s="324"/>
+      <c r="E29" s="324"/>
+      <c r="F29" s="324"/>
       <c r="G29" s="72" t="e">
         <f>SUM(G30:G77)</f>
         <v>#REF!</v>
@@ -16343,11 +16343,11 @@
       <c r="C30" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="336" t="s">
+      <c r="D30" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="337"/>
-      <c r="F30" s="337"/>
+      <c r="E30" s="324"/>
+      <c r="F30" s="324"/>
       <c r="G30" s="74"/>
       <c r="L30" s="53" t="e">
         <f>G29-L29</f>
@@ -16367,10 +16367,10 @@
       <c r="D31" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="355" t="s">
+      <c r="E31" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="356"/>
+      <c r="F31" s="337"/>
       <c r="G31" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16390,10 +16390,10 @@
       <c r="D32" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="355" t="s">
+      <c r="E32" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="356"/>
+      <c r="F32" s="337"/>
       <c r="G32" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16413,10 +16413,10 @@
       <c r="D33" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E33" s="355" t="s">
+      <c r="E33" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="356"/>
+      <c r="F33" s="337"/>
       <c r="G33" s="74"/>
     </row>
     <row r="34" spans="1:13" ht="12" customHeight="1">
@@ -16473,10 +16473,10 @@
       <c r="D36" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E36" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="346"/>
+      <c r="E36" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="320"/>
       <c r="G36" s="74"/>
       <c r="H36" s="49"/>
     </row>
@@ -16490,11 +16490,11 @@
       <c r="C37" s="73" t="s">
         <v>171</v>
       </c>
-      <c r="D37" s="336" t="s">
+      <c r="D37" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E37" s="337"/>
-      <c r="F37" s="337"/>
+      <c r="E37" s="324"/>
+      <c r="F37" s="324"/>
       <c r="G37" s="74"/>
     </row>
     <row r="38" spans="1:13" ht="12" customHeight="1">
@@ -16510,10 +16510,10 @@
       <c r="D38" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E38" s="355" t="s">
+      <c r="E38" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="F38" s="356"/>
+      <c r="F38" s="337"/>
       <c r="G38" s="74" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -16533,10 +16533,10 @@
       <c r="D39" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="355" t="s">
+      <c r="E39" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="F39" s="356"/>
+      <c r="F39" s="337"/>
       <c r="G39" s="74"/>
     </row>
     <row r="40" spans="1:13" ht="12" customHeight="1">
@@ -16546,14 +16546,14 @@
       <c r="B40" s="58">
         <v>26</v>
       </c>
-      <c r="C40" s="339" t="s">
+      <c r="C40" s="332" t="s">
         <v>174</v>
       </c>
-      <c r="D40" s="336" t="s">
+      <c r="D40" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E40" s="337"/>
-      <c r="F40" s="337"/>
+      <c r="E40" s="324"/>
+      <c r="F40" s="324"/>
       <c r="G40" s="74"/>
     </row>
     <row r="41" spans="1:13" ht="12" customHeight="1">
@@ -16563,14 +16563,14 @@
       <c r="B41" s="58">
         <v>27</v>
       </c>
-      <c r="C41" s="340"/>
+      <c r="C41" s="333"/>
       <c r="D41" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="F41" s="385"/>
+      <c r="E41" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="386"/>
       <c r="G41" s="74"/>
     </row>
     <row r="42" spans="1:13" ht="12" customHeight="1">
@@ -16586,10 +16586,10 @@
       <c r="D42" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E42" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="346"/>
+      <c r="E42" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" s="320"/>
       <c r="G42" s="74"/>
       <c r="H42" s="49"/>
     </row>
@@ -16600,14 +16600,14 @@
       <c r="B43" s="58">
         <v>29</v>
       </c>
-      <c r="C43" s="339" t="s">
+      <c r="C43" s="332" t="s">
         <v>186</v>
       </c>
-      <c r="D43" s="336" t="s">
+      <c r="D43" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="337"/>
-      <c r="F43" s="337"/>
+      <c r="E43" s="324"/>
+      <c r="F43" s="324"/>
       <c r="G43" s="74"/>
     </row>
     <row r="44" spans="1:13" ht="12" customHeight="1">
@@ -16617,14 +16617,14 @@
       <c r="B44" s="58">
         <v>30</v>
       </c>
-      <c r="C44" s="340"/>
+      <c r="C44" s="333"/>
       <c r="D44" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E44" s="345" t="s">
+      <c r="E44" s="319" t="s">
         <v>128</v>
       </c>
-      <c r="F44" s="346"/>
+      <c r="F44" s="320"/>
       <c r="G44" s="74"/>
     </row>
     <row r="45" spans="1:13" ht="18.75" customHeight="1">
@@ -16634,14 +16634,14 @@
       <c r="B45" s="58">
         <v>31</v>
       </c>
-      <c r="C45" s="341"/>
+      <c r="C45" s="349"/>
       <c r="D45" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E45" s="386" t="s">
+      <c r="E45" s="389" t="s">
         <v>129</v>
       </c>
-      <c r="F45" s="387"/>
+      <c r="F45" s="390"/>
       <c r="G45" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16656,12 +16656,12 @@
       <c r="B46" s="58">
         <v>32</v>
       </c>
-      <c r="C46" s="336" t="s">
+      <c r="C46" s="323" t="s">
         <v>20</v>
       </c>
-      <c r="D46" s="337"/>
-      <c r="E46" s="337"/>
-      <c r="F46" s="337"/>
+      <c r="D46" s="324"/>
+      <c r="E46" s="324"/>
+      <c r="F46" s="324"/>
       <c r="G46" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16678,11 +16678,11 @@
       <c r="C47" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="D47" s="336" t="s">
+      <c r="D47" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="E47" s="324"/>
+      <c r="F47" s="324"/>
       <c r="G47" s="74"/>
       <c r="L47" s="53"/>
     </row>
@@ -16699,10 +16699,10 @@
       <c r="D48" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E48" s="355" t="s">
+      <c r="E48" s="336" t="s">
         <v>63</v>
       </c>
-      <c r="F48" s="356"/>
+      <c r="F48" s="337"/>
       <c r="G48" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16721,10 +16721,10 @@
       <c r="D49" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E49" s="355" t="s">
+      <c r="E49" s="336" t="s">
         <v>64</v>
       </c>
-      <c r="F49" s="356"/>
+      <c r="F49" s="337"/>
       <c r="G49" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16737,14 +16737,14 @@
       <c r="B50" s="58">
         <v>36</v>
       </c>
-      <c r="C50" s="339" t="s">
+      <c r="C50" s="332" t="s">
         <v>187</v>
       </c>
-      <c r="D50" s="336" t="s">
+      <c r="D50" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E50" s="337"/>
-      <c r="F50" s="337"/>
+      <c r="E50" s="324"/>
+      <c r="F50" s="324"/>
       <c r="G50" s="74"/>
     </row>
     <row r="51" spans="1:8" ht="12" customHeight="1">
@@ -16754,14 +16754,14 @@
       <c r="B51" s="58">
         <v>37</v>
       </c>
-      <c r="C51" s="340"/>
+      <c r="C51" s="333"/>
       <c r="D51" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E51" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="385"/>
+      <c r="E51" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="386"/>
       <c r="G51" s="74"/>
     </row>
     <row r="52" spans="1:8" ht="24.75" customHeight="1">
@@ -16777,10 +16777,10 @@
       <c r="D52" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E52" s="345" t="s">
+      <c r="E52" s="319" t="s">
         <v>188</v>
       </c>
-      <c r="F52" s="346"/>
+      <c r="F52" s="320"/>
       <c r="G52" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16794,12 +16794,12 @@
       <c r="B53" s="58">
         <v>43</v>
       </c>
-      <c r="C53" s="336" t="s">
+      <c r="C53" s="323" t="s">
         <v>16</v>
       </c>
-      <c r="D53" s="337"/>
-      <c r="E53" s="337"/>
-      <c r="F53" s="337"/>
+      <c r="D53" s="324"/>
+      <c r="E53" s="324"/>
+      <c r="F53" s="324"/>
       <c r="G53" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16812,12 +16812,12 @@
       <c r="B54" s="58">
         <v>44</v>
       </c>
-      <c r="C54" s="336" t="s">
+      <c r="C54" s="323" t="s">
         <v>14</v>
       </c>
-      <c r="D54" s="337"/>
-      <c r="E54" s="337"/>
-      <c r="F54" s="337"/>
+      <c r="D54" s="324"/>
+      <c r="E54" s="324"/>
+      <c r="F54" s="324"/>
       <c r="G54" s="74"/>
     </row>
     <row r="55" spans="1:8" ht="12" customHeight="1">
@@ -16830,11 +16830,11 @@
       <c r="C55" s="73" t="s">
         <v>137</v>
       </c>
-      <c r="D55" s="336" t="s">
+      <c r="D55" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="337"/>
-      <c r="F55" s="337"/>
+      <c r="E55" s="324"/>
+      <c r="F55" s="324"/>
       <c r="G55" s="74"/>
     </row>
     <row r="56" spans="1:8" ht="12" customHeight="1">
@@ -16850,10 +16850,10 @@
       <c r="D56" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="F56" s="385"/>
+      <c r="E56" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" s="386"/>
       <c r="G56" s="74"/>
     </row>
     <row r="57" spans="1:8" ht="24.75" customHeight="1">
@@ -16869,10 +16869,10 @@
       <c r="D57" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="345" t="s">
+      <c r="E57" s="319" t="s">
         <v>4</v>
       </c>
-      <c r="F57" s="346"/>
+      <c r="F57" s="320"/>
       <c r="G57" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16892,10 +16892,10 @@
       <c r="D58" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F58" s="346"/>
+      <c r="E58" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F58" s="320"/>
       <c r="G58" s="74"/>
       <c r="H58" s="49"/>
     </row>
@@ -16906,12 +16906,12 @@
       <c r="B59" s="58">
         <v>51</v>
       </c>
-      <c r="C59" s="336" t="s">
+      <c r="C59" s="323" t="s">
         <v>189</v>
       </c>
-      <c r="D59" s="337"/>
-      <c r="E59" s="337"/>
-      <c r="F59" s="337"/>
+      <c r="D59" s="324"/>
+      <c r="E59" s="324"/>
+      <c r="F59" s="324"/>
       <c r="G59" s="74"/>
     </row>
     <row r="60" spans="1:8" ht="12" customHeight="1">
@@ -16921,12 +16921,12 @@
       <c r="B60" s="58">
         <v>52</v>
       </c>
-      <c r="C60" s="336" t="s">
+      <c r="C60" s="323" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="337"/>
-      <c r="E60" s="337"/>
-      <c r="F60" s="337"/>
+      <c r="D60" s="324"/>
+      <c r="E60" s="324"/>
+      <c r="F60" s="324"/>
       <c r="G60" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16939,12 +16939,12 @@
       <c r="B61" s="58">
         <v>53</v>
       </c>
-      <c r="C61" s="336" t="s">
+      <c r="C61" s="323" t="s">
         <v>190</v>
       </c>
-      <c r="D61" s="337"/>
-      <c r="E61" s="337"/>
-      <c r="F61" s="337"/>
+      <c r="D61" s="324"/>
+      <c r="E61" s="324"/>
+      <c r="F61" s="324"/>
       <c r="G61" s="74"/>
     </row>
     <row r="62" spans="1:8" ht="12" customHeight="1">
@@ -16954,12 +16954,12 @@
       <c r="B62" s="58">
         <v>54</v>
       </c>
-      <c r="C62" s="336" t="s">
+      <c r="C62" s="323" t="s">
         <v>191</v>
       </c>
-      <c r="D62" s="337"/>
-      <c r="E62" s="337"/>
-      <c r="F62" s="337"/>
+      <c r="D62" s="324"/>
+      <c r="E62" s="324"/>
+      <c r="F62" s="324"/>
       <c r="G62" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16972,12 +16972,12 @@
       <c r="B63" s="58">
         <v>55</v>
       </c>
-      <c r="C63" s="336" t="s">
+      <c r="C63" s="323" t="s">
         <v>192</v>
       </c>
-      <c r="D63" s="337"/>
-      <c r="E63" s="337"/>
-      <c r="F63" s="337"/>
+      <c r="D63" s="324"/>
+      <c r="E63" s="324"/>
+      <c r="F63" s="324"/>
       <c r="G63" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16990,14 +16990,14 @@
       <c r="B64" s="58">
         <v>56</v>
       </c>
-      <c r="C64" s="339" t="s">
+      <c r="C64" s="332" t="s">
         <v>175</v>
       </c>
-      <c r="D64" s="336" t="s">
+      <c r="D64" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E64" s="337"/>
-      <c r="F64" s="337"/>
+      <c r="E64" s="324"/>
+      <c r="F64" s="324"/>
       <c r="G64" s="74"/>
     </row>
     <row r="65" spans="1:11" ht="12" customHeight="1">
@@ -17007,14 +17007,14 @@
       <c r="B65" s="58">
         <v>57</v>
       </c>
-      <c r="C65" s="340"/>
+      <c r="C65" s="333"/>
       <c r="D65" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E65" s="355" t="s">
+      <c r="E65" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="F65" s="356"/>
+      <c r="F65" s="337"/>
       <c r="G65" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17033,10 +17033,10 @@
       <c r="D66" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E66" s="345" t="s">
+      <c r="E66" s="319" t="s">
         <v>193</v>
       </c>
-      <c r="F66" s="346"/>
+      <c r="F66" s="320"/>
       <c r="G66" s="74"/>
       <c r="H66" s="49"/>
     </row>
@@ -17047,14 +17047,14 @@
       <c r="B67" s="58">
         <v>59</v>
       </c>
-      <c r="C67" s="339" t="s">
+      <c r="C67" s="332" t="s">
         <v>102</v>
       </c>
-      <c r="D67" s="336" t="s">
+      <c r="D67" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E67" s="337"/>
-      <c r="F67" s="337"/>
+      <c r="E67" s="324"/>
+      <c r="F67" s="324"/>
       <c r="G67" s="74"/>
     </row>
     <row r="68" spans="1:11" ht="12" customHeight="1">
@@ -17064,14 +17064,14 @@
       <c r="B68" s="58">
         <v>60</v>
       </c>
-      <c r="C68" s="340"/>
+      <c r="C68" s="333"/>
       <c r="D68" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E68" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="F68" s="385"/>
+      <c r="E68" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="F68" s="386"/>
       <c r="G68" s="74"/>
     </row>
     <row r="69" spans="1:11" ht="12" customHeight="1">
@@ -17087,10 +17087,10 @@
       <c r="D69" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E69" s="345" t="s">
+      <c r="E69" s="319" t="s">
         <v>194</v>
       </c>
-      <c r="F69" s="346"/>
+      <c r="F69" s="320"/>
       <c r="G69" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17110,10 +17110,10 @@
       <c r="D70" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E70" s="345" t="s">
+      <c r="E70" s="319" t="s">
         <v>195</v>
       </c>
-      <c r="F70" s="346"/>
+      <c r="F70" s="320"/>
       <c r="G70" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17133,10 +17133,10 @@
       <c r="D71" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E71" s="388" t="s">
+      <c r="E71" s="387" t="s">
         <v>196</v>
       </c>
-      <c r="F71" s="389"/>
+      <c r="F71" s="388"/>
       <c r="G71" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17148,10 +17148,10 @@
       <c r="B72" s="58"/>
       <c r="C72" s="77"/>
       <c r="D72" s="70"/>
-      <c r="E72" s="388" t="s">
+      <c r="E72" s="387" t="s">
         <v>13</v>
       </c>
-      <c r="F72" s="389"/>
+      <c r="F72" s="388"/>
       <c r="G72" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17163,10 +17163,10 @@
       <c r="B73" s="58"/>
       <c r="C73" s="77"/>
       <c r="D73" s="70"/>
-      <c r="E73" s="388" t="s">
+      <c r="E73" s="387" t="s">
         <v>8</v>
       </c>
-      <c r="F73" s="389"/>
+      <c r="F73" s="388"/>
       <c r="G73" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17186,10 +17186,10 @@
       <c r="D74" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E74" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F74" s="346"/>
+      <c r="E74" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F74" s="320"/>
       <c r="G74" s="74"/>
       <c r="H74" s="49"/>
     </row>
@@ -17200,14 +17200,14 @@
       <c r="B75" s="58">
         <v>65</v>
       </c>
-      <c r="C75" s="339" t="s">
+      <c r="C75" s="332" t="s">
         <v>197</v>
       </c>
-      <c r="D75" s="336" t="s">
+      <c r="D75" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E75" s="337"/>
-      <c r="F75" s="337"/>
+      <c r="E75" s="324"/>
+      <c r="F75" s="324"/>
       <c r="G75" s="74"/>
     </row>
     <row r="76" spans="1:11" ht="12" customHeight="1">
@@ -17217,14 +17217,14 @@
       <c r="B76" s="58">
         <v>66</v>
       </c>
-      <c r="C76" s="340"/>
+      <c r="C76" s="333"/>
       <c r="D76" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E76" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="F76" s="385"/>
+      <c r="E76" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="F76" s="386"/>
       <c r="G76" s="74"/>
     </row>
     <row r="77" spans="1:11" ht="12" customHeight="1">
@@ -17240,10 +17240,10 @@
       <c r="D77" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E77" s="345" t="s">
+      <c r="E77" s="319" t="s">
         <v>198</v>
       </c>
-      <c r="F77" s="346"/>
+      <c r="F77" s="320"/>
       <c r="G77" s="81" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -17302,13 +17302,13 @@
       <c r="K79" s="51"/>
     </row>
     <row r="80" spans="1:11" ht="15" customHeight="1">
-      <c r="B80" s="390" t="s">
+      <c r="B80" s="385" t="s">
         <v>199</v>
       </c>
-      <c r="C80" s="390"/>
-      <c r="D80" s="390"/>
-      <c r="E80" s="390"/>
-      <c r="F80" s="390"/>
+      <c r="C80" s="385"/>
+      <c r="D80" s="385"/>
+      <c r="E80" s="385"/>
+      <c r="F80" s="385"/>
       <c r="G80" s="83"/>
       <c r="H80" s="83"/>
       <c r="I80" s="82"/>
@@ -17316,13 +17316,13 @@
       <c r="K80" s="51"/>
     </row>
     <row r="81" spans="2:11" ht="15" customHeight="1">
-      <c r="B81" s="390" t="s">
-        <v>44</v>
-      </c>
-      <c r="C81" s="390"/>
-      <c r="D81" s="390"/>
-      <c r="E81" s="390"/>
-      <c r="F81" s="390"/>
+      <c r="B81" s="385" t="s">
+        <v>44</v>
+      </c>
+      <c r="C81" s="385"/>
+      <c r="D81" s="385"/>
+      <c r="E81" s="385"/>
+      <c r="F81" s="385"/>
       <c r="G81" s="84"/>
       <c r="H81" s="84"/>
       <c r="I81" s="83"/>
@@ -17332,14 +17332,14 @@
     <row r="82" spans="2:11" ht="15.75" hidden="1" customHeight="1"/>
     <row r="83" spans="2:11" ht="15.75" hidden="1" customHeight="1"/>
     <row r="84" spans="2:11" ht="15" customHeight="1">
-      <c r="B84" s="390" t="s">
+      <c r="B84" s="385" t="s">
         <v>200</v>
       </c>
-      <c r="C84" s="390"/>
-      <c r="D84" s="390"/>
-      <c r="E84" s="390"/>
-      <c r="F84" s="390"/>
-      <c r="G84" s="390"/>
+      <c r="C84" s="385"/>
+      <c r="D84" s="385"/>
+      <c r="E84" s="385"/>
+      <c r="F84" s="385"/>
+      <c r="G84" s="385"/>
       <c r="H84" s="83"/>
       <c r="I84" s="83"/>
       <c r="J84" s="83"/>
@@ -17368,13 +17368,51 @@
     <row r="105" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B84:G84"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:F24"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C59:F59"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="C62:F62"/>
     <mergeCell ref="E74:F74"/>
     <mergeCell ref="C64:C65"/>
     <mergeCell ref="D64:F64"/>
@@ -17388,51 +17426,13 @@
     <mergeCell ref="E71:F71"/>
     <mergeCell ref="E72:F72"/>
     <mergeCell ref="E73:F73"/>
-    <mergeCell ref="C63:F63"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="C53:F53"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C59:F59"/>
-    <mergeCell ref="C60:F60"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="C62:F62"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:F24"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B84:G84"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Наименование на государственном языке заполняется автоматически в соответствии с КТРУ" sqref="B76 B49:B50 B95:B96"/>
@@ -17468,79 +17468,79 @@
       <c r="A1" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="430" t="s">
+      <c r="B1" s="399" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="430"/>
-      <c r="D1" s="430"/>
-      <c r="E1" s="430"/>
-      <c r="F1" s="430"/>
-      <c r="G1" s="430"/>
-      <c r="H1" s="430"/>
-      <c r="I1" s="430"/>
+      <c r="C1" s="399"/>
+      <c r="D1" s="399"/>
+      <c r="E1" s="399"/>
+      <c r="F1" s="399"/>
+      <c r="G1" s="399"/>
+      <c r="H1" s="399"/>
+      <c r="I1" s="399"/>
       <c r="M1" s="12"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1">
       <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="431" t="s">
+      <c r="B2" s="400" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="431"/>
-      <c r="D2" s="431"/>
-      <c r="E2" s="431"/>
-      <c r="F2" s="431"/>
-      <c r="G2" s="431"/>
-      <c r="H2" s="431"/>
-      <c r="I2" s="431"/>
+      <c r="C2" s="400"/>
+      <c r="D2" s="400"/>
+      <c r="E2" s="400"/>
+      <c r="F2" s="400"/>
+      <c r="G2" s="400"/>
+      <c r="H2" s="400"/>
+      <c r="I2" s="400"/>
       <c r="M2" s="12"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="432" t="s">
+      <c r="B3" s="401" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="432"/>
-      <c r="D3" s="432"/>
-      <c r="E3" s="432"/>
-      <c r="F3" s="432"/>
-      <c r="G3" s="432"/>
-      <c r="H3" s="432"/>
-      <c r="I3" s="432"/>
+      <c r="C3" s="401"/>
+      <c r="D3" s="401"/>
+      <c r="E3" s="401"/>
+      <c r="F3" s="401"/>
+      <c r="G3" s="401"/>
+      <c r="H3" s="401"/>
+      <c r="I3" s="401"/>
       <c r="M3" s="12"/>
     </row>
     <row r="4" spans="1:13" ht="30" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="432" t="s">
+      <c r="B4" s="401" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="432"/>
-      <c r="D4" s="432"/>
-      <c r="E4" s="432"/>
-      <c r="F4" s="432"/>
-      <c r="G4" s="432"/>
-      <c r="H4" s="432"/>
-      <c r="I4" s="432"/>
+      <c r="C4" s="401"/>
+      <c r="D4" s="401"/>
+      <c r="E4" s="401"/>
+      <c r="F4" s="401"/>
+      <c r="G4" s="401"/>
+      <c r="H4" s="401"/>
+      <c r="I4" s="401"/>
       <c r="M4" s="12"/>
     </row>
     <row r="5" spans="1:13" ht="12" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="433" t="s">
+      <c r="B5" s="402" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="433"/>
-      <c r="D5" s="433"/>
-      <c r="E5" s="433"/>
-      <c r="F5" s="433"/>
-      <c r="G5" s="433"/>
-      <c r="H5" s="433"/>
+      <c r="C5" s="402"/>
+      <c r="D5" s="402"/>
+      <c r="E5" s="402"/>
+      <c r="F5" s="402"/>
+      <c r="G5" s="402"/>
+      <c r="H5" s="402"/>
       <c r="I5" s="13" t="s">
         <v>50</v>
       </c>
@@ -17564,18 +17564,18 @@
       <c r="A20" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="434" t="s">
+      <c r="B20" s="403" t="s">
         <v>0</v>
       </c>
-      <c r="C20" s="437" t="s">
+      <c r="C20" s="406" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="438"/>
-      <c r="E20" s="438"/>
-      <c r="F20" s="438"/>
-      <c r="G20" s="438"/>
-      <c r="H20" s="439"/>
-      <c r="I20" s="446" t="s">
+      <c r="D20" s="407"/>
+      <c r="E20" s="407"/>
+      <c r="F20" s="407"/>
+      <c r="G20" s="407"/>
+      <c r="H20" s="408"/>
+      <c r="I20" s="415" t="s">
         <v>52</v>
       </c>
       <c r="J20" s="10"/>
@@ -17588,14 +17588,14 @@
       <c r="A21" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="435"/>
-      <c r="C21" s="440"/>
-      <c r="D21" s="441"/>
-      <c r="E21" s="441"/>
-      <c r="F21" s="441"/>
-      <c r="G21" s="441"/>
-      <c r="H21" s="442"/>
-      <c r="I21" s="435"/>
+      <c r="B21" s="404"/>
+      <c r="C21" s="409"/>
+      <c r="D21" s="410"/>
+      <c r="E21" s="410"/>
+      <c r="F21" s="410"/>
+      <c r="G21" s="410"/>
+      <c r="H21" s="411"/>
+      <c r="I21" s="404"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
@@ -17605,14 +17605,14 @@
       <c r="A22" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="436"/>
-      <c r="C22" s="443"/>
-      <c r="D22" s="444"/>
-      <c r="E22" s="444"/>
-      <c r="F22" s="444"/>
-      <c r="G22" s="444"/>
-      <c r="H22" s="445"/>
-      <c r="I22" s="436"/>
+      <c r="B22" s="405"/>
+      <c r="C22" s="412"/>
+      <c r="D22" s="413"/>
+      <c r="E22" s="413"/>
+      <c r="F22" s="413"/>
+      <c r="G22" s="413"/>
+      <c r="H22" s="414"/>
+      <c r="I22" s="405"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
@@ -17628,10 +17628,10 @@
       <c r="B26" s="18">
         <v>1</v>
       </c>
-      <c r="C26" s="428">
+      <c r="C26" s="391">
         <v>2</v>
       </c>
-      <c r="D26" s="429"/>
+      <c r="D26" s="392"/>
       <c r="E26" s="18">
         <v>3</v>
       </c>
@@ -17655,14 +17655,14 @@
       <c r="B27" s="19">
         <v>1</v>
       </c>
-      <c r="C27" s="394" t="s">
+      <c r="C27" s="393" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="395"/>
-      <c r="E27" s="395"/>
-      <c r="F27" s="395"/>
-      <c r="G27" s="395"/>
-      <c r="H27" s="396"/>
+      <c r="D27" s="394"/>
+      <c r="E27" s="394"/>
+      <c r="F27" s="394"/>
+      <c r="G27" s="394"/>
+      <c r="H27" s="395"/>
       <c r="I27" s="20"/>
       <c r="N27" s="16"/>
     </row>
@@ -17679,12 +17679,12 @@
       <c r="D28" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="394" t="s">
+      <c r="E28" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F28" s="395"/>
-      <c r="G28" s="395"/>
-      <c r="H28" s="396"/>
+      <c r="F28" s="394"/>
+      <c r="G28" s="394"/>
+      <c r="H28" s="395"/>
       <c r="I28" s="20" t="e">
         <f>SUM(I29:I190)</f>
         <v>#REF!</v>
@@ -17710,11 +17710,11 @@
       <c r="E29" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="401" t="s">
+      <c r="F29" s="396" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="402"/>
-      <c r="H29" s="403"/>
+      <c r="G29" s="397"/>
+      <c r="H29" s="398"/>
       <c r="I29" s="20" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17740,11 +17740,11 @@
       <c r="E30" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="401" t="s">
+      <c r="F30" s="396" t="s">
         <v>57</v>
       </c>
-      <c r="G30" s="402"/>
-      <c r="H30" s="403"/>
+      <c r="G30" s="397"/>
+      <c r="H30" s="398"/>
       <c r="I30" s="20" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17767,11 +17767,11 @@
       <c r="E31" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="401" t="s">
+      <c r="F31" s="396" t="s">
         <v>58</v>
       </c>
-      <c r="G31" s="402"/>
-      <c r="H31" s="403"/>
+      <c r="G31" s="397"/>
+      <c r="H31" s="398"/>
       <c r="I31" s="20"/>
     </row>
     <row r="32" spans="1:14" ht="12" customHeight="1">
@@ -17790,11 +17790,11 @@
       <c r="E32" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="391" t="s">
+      <c r="F32" s="416" t="s">
         <v>59</v>
       </c>
-      <c r="G32" s="392"/>
-      <c r="H32" s="393"/>
+      <c r="G32" s="417"/>
+      <c r="H32" s="418"/>
       <c r="I32" s="20" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -17820,16 +17820,16 @@
       <c r="B34" s="21">
         <v>7</v>
       </c>
-      <c r="C34" s="397" t="s">
+      <c r="C34" s="419" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="398"/>
-      <c r="E34" s="394" t="s">
+      <c r="D34" s="420"/>
+      <c r="E34" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="395"/>
-      <c r="G34" s="395"/>
-      <c r="H34" s="396"/>
+      <c r="F34" s="394"/>
+      <c r="G34" s="394"/>
+      <c r="H34" s="395"/>
       <c r="I34" s="32"/>
     </row>
     <row r="35" spans="1:15" ht="12" customHeight="1">
@@ -17839,16 +17839,16 @@
       <c r="B35" s="21">
         <v>8</v>
       </c>
-      <c r="C35" s="399"/>
-      <c r="D35" s="400"/>
+      <c r="C35" s="421"/>
+      <c r="D35" s="422"/>
       <c r="E35" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F35" s="401" t="s">
-        <v>44</v>
-      </c>
-      <c r="G35" s="402"/>
-      <c r="H35" s="403"/>
+      <c r="F35" s="396" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" s="397"/>
+      <c r="H35" s="398"/>
       <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:15" hidden="1">
@@ -17861,16 +17861,16 @@
       <c r="B37" s="21">
         <v>10</v>
       </c>
-      <c r="C37" s="407" t="s">
+      <c r="C37" s="423" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="408"/>
-      <c r="E37" s="394" t="s">
+      <c r="D37" s="424"/>
+      <c r="E37" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F37" s="395"/>
-      <c r="G37" s="395"/>
-      <c r="H37" s="396"/>
+      <c r="F37" s="394"/>
+      <c r="G37" s="394"/>
+      <c r="H37" s="395"/>
       <c r="I37" s="32"/>
     </row>
     <row r="38" spans="1:15" ht="12" customHeight="1">
@@ -17880,16 +17880,16 @@
       <c r="B38" s="21">
         <v>11</v>
       </c>
-      <c r="C38" s="409"/>
-      <c r="D38" s="410"/>
-      <c r="E38" s="413" t="s">
+      <c r="C38" s="425"/>
+      <c r="D38" s="426"/>
+      <c r="E38" s="429" t="s">
         <v>55</v>
       </c>
-      <c r="F38" s="401" t="s">
+      <c r="F38" s="396" t="s">
         <v>63</v>
       </c>
-      <c r="G38" s="402"/>
-      <c r="H38" s="403"/>
+      <c r="G38" s="397"/>
+      <c r="H38" s="398"/>
       <c r="I38" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17902,14 +17902,14 @@
       <c r="B39" s="21">
         <v>12</v>
       </c>
-      <c r="C39" s="411"/>
-      <c r="D39" s="412"/>
-      <c r="E39" s="414"/>
-      <c r="F39" s="401" t="s">
+      <c r="C39" s="427"/>
+      <c r="D39" s="428"/>
+      <c r="E39" s="430"/>
+      <c r="F39" s="396" t="s">
         <v>64</v>
       </c>
-      <c r="G39" s="402"/>
-      <c r="H39" s="403"/>
+      <c r="G39" s="397"/>
+      <c r="H39" s="398"/>
       <c r="I39" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17922,16 +17922,16 @@
       <c r="B40" s="21">
         <v>13</v>
       </c>
-      <c r="C40" s="397" t="s">
+      <c r="C40" s="419" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="398"/>
-      <c r="E40" s="394" t="s">
+      <c r="D40" s="420"/>
+      <c r="E40" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F40" s="395"/>
-      <c r="G40" s="395"/>
-      <c r="H40" s="396"/>
+      <c r="F40" s="394"/>
+      <c r="G40" s="394"/>
+      <c r="H40" s="395"/>
       <c r="I40" s="32"/>
     </row>
     <row r="41" spans="1:15" ht="17.25" customHeight="1">
@@ -17941,16 +17941,16 @@
       <c r="B41" s="21">
         <v>14</v>
       </c>
-      <c r="C41" s="399"/>
-      <c r="D41" s="400"/>
+      <c r="C41" s="421"/>
+      <c r="D41" s="422"/>
       <c r="E41" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F41" s="401" t="s">
-        <v>44</v>
-      </c>
-      <c r="G41" s="402"/>
-      <c r="H41" s="403"/>
+      <c r="F41" s="396" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" s="397"/>
+      <c r="H41" s="398"/>
       <c r="I41" s="32"/>
     </row>
     <row r="42" spans="1:15" ht="12" customHeight="1">
@@ -17969,11 +17969,11 @@
       <c r="E42" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F42" s="391" t="s">
+      <c r="F42" s="416" t="s">
         <v>66</v>
       </c>
-      <c r="G42" s="392"/>
-      <c r="H42" s="393"/>
+      <c r="G42" s="417"/>
+      <c r="H42" s="418"/>
       <c r="I42" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17990,14 +17990,14 @@
       <c r="B44" s="21">
         <v>17</v>
       </c>
-      <c r="C44" s="394" t="s">
+      <c r="C44" s="393" t="s">
         <v>67</v>
       </c>
-      <c r="D44" s="395"/>
-      <c r="E44" s="395"/>
-      <c r="F44" s="395"/>
-      <c r="G44" s="395"/>
-      <c r="H44" s="396"/>
+      <c r="D44" s="394"/>
+      <c r="E44" s="394"/>
+      <c r="F44" s="394"/>
+      <c r="G44" s="394"/>
+      <c r="H44" s="395"/>
       <c r="I44" s="32"/>
     </row>
     <row r="45" spans="1:15" ht="12" customHeight="1">
@@ -18007,16 +18007,16 @@
       <c r="B45" s="21">
         <v>18</v>
       </c>
-      <c r="C45" s="422" t="s">
+      <c r="C45" s="431" t="s">
         <v>68</v>
       </c>
-      <c r="D45" s="423"/>
-      <c r="E45" s="394" t="s">
+      <c r="D45" s="432"/>
+      <c r="E45" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="395"/>
-      <c r="G45" s="395"/>
-      <c r="H45" s="396"/>
+      <c r="F45" s="394"/>
+      <c r="G45" s="394"/>
+      <c r="H45" s="395"/>
       <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:15" ht="30" customHeight="1">
@@ -18026,16 +18026,16 @@
       <c r="B46" s="21">
         <v>19</v>
       </c>
-      <c r="C46" s="424"/>
-      <c r="D46" s="425"/>
-      <c r="E46" s="413" t="s">
+      <c r="C46" s="433"/>
+      <c r="D46" s="434"/>
+      <c r="E46" s="429" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="401" t="s">
+      <c r="F46" s="396" t="s">
         <v>69</v>
       </c>
-      <c r="G46" s="402"/>
-      <c r="H46" s="403"/>
+      <c r="G46" s="397"/>
+      <c r="H46" s="398"/>
       <c r="I46" s="127" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18050,14 +18050,14 @@
       <c r="B47" s="21">
         <v>20</v>
       </c>
-      <c r="C47" s="424"/>
-      <c r="D47" s="425"/>
-      <c r="E47" s="415"/>
-      <c r="F47" s="401" t="s">
+      <c r="C47" s="433"/>
+      <c r="D47" s="434"/>
+      <c r="E47" s="437"/>
+      <c r="F47" s="396" t="s">
         <v>70</v>
       </c>
-      <c r="G47" s="402"/>
-      <c r="H47" s="403"/>
+      <c r="G47" s="397"/>
+      <c r="H47" s="398"/>
       <c r="I47" s="127" t="e">
         <f>#REF!+#REF!-#REF!</f>
         <v>#REF!</v>
@@ -18072,14 +18072,14 @@
       <c r="B48" s="21">
         <v>21</v>
       </c>
-      <c r="C48" s="424"/>
-      <c r="D48" s="425"/>
-      <c r="E48" s="415"/>
-      <c r="F48" s="401" t="s">
+      <c r="C48" s="433"/>
+      <c r="D48" s="434"/>
+      <c r="E48" s="437"/>
+      <c r="F48" s="396" t="s">
         <v>71</v>
       </c>
-      <c r="G48" s="402"/>
-      <c r="H48" s="403"/>
+      <c r="G48" s="397"/>
+      <c r="H48" s="398"/>
       <c r="I48" s="127" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18093,14 +18093,14 @@
       <c r="B49" s="21">
         <v>22</v>
       </c>
-      <c r="C49" s="426"/>
-      <c r="D49" s="427"/>
-      <c r="E49" s="414"/>
-      <c r="F49" s="401" t="s">
+      <c r="C49" s="435"/>
+      <c r="D49" s="436"/>
+      <c r="E49" s="430"/>
+      <c r="F49" s="396" t="s">
         <v>72</v>
       </c>
-      <c r="G49" s="402"/>
-      <c r="H49" s="403"/>
+      <c r="G49" s="397"/>
+      <c r="H49" s="398"/>
       <c r="I49" s="34" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18114,16 +18114,16 @@
       <c r="B50" s="21">
         <v>23</v>
       </c>
-      <c r="C50" s="418" t="s">
+      <c r="C50" s="438" t="s">
         <v>73</v>
       </c>
-      <c r="D50" s="419"/>
-      <c r="E50" s="394" t="s">
+      <c r="D50" s="439"/>
+      <c r="E50" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F50" s="395"/>
-      <c r="G50" s="395"/>
-      <c r="H50" s="396"/>
+      <c r="F50" s="394"/>
+      <c r="G50" s="394"/>
+      <c r="H50" s="395"/>
       <c r="I50" s="32"/>
     </row>
     <row r="51" spans="1:14" ht="12" customHeight="1">
@@ -18133,16 +18133,16 @@
       <c r="B51" s="21">
         <v>24</v>
       </c>
-      <c r="C51" s="420"/>
-      <c r="D51" s="421"/>
+      <c r="C51" s="440"/>
+      <c r="D51" s="441"/>
       <c r="E51" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="401" t="s">
+      <c r="F51" s="396" t="s">
         <v>23</v>
       </c>
-      <c r="G51" s="402"/>
-      <c r="H51" s="403"/>
+      <c r="G51" s="397"/>
+      <c r="H51" s="398"/>
       <c r="I51" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18165,11 +18165,11 @@
       <c r="E52" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="401" t="s">
+      <c r="F52" s="396" t="s">
         <v>74</v>
       </c>
-      <c r="G52" s="402"/>
-      <c r="H52" s="403"/>
+      <c r="G52" s="397"/>
+      <c r="H52" s="398"/>
       <c r="I52" s="32"/>
       <c r="N52" s="35"/>
     </row>
@@ -18183,16 +18183,16 @@
       <c r="B54" s="21">
         <v>27</v>
       </c>
-      <c r="C54" s="397" t="s">
+      <c r="C54" s="419" t="s">
         <v>75</v>
       </c>
-      <c r="D54" s="398"/>
-      <c r="E54" s="394" t="s">
+      <c r="D54" s="420"/>
+      <c r="E54" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F54" s="395"/>
-      <c r="G54" s="395"/>
-      <c r="H54" s="396"/>
+      <c r="F54" s="394"/>
+      <c r="G54" s="394"/>
+      <c r="H54" s="395"/>
       <c r="I54" s="32"/>
     </row>
     <row r="55" spans="1:14" ht="12" customHeight="1">
@@ -18202,16 +18202,16 @@
       <c r="B55" s="21">
         <v>28</v>
       </c>
-      <c r="C55" s="399"/>
-      <c r="D55" s="400"/>
+      <c r="C55" s="421"/>
+      <c r="D55" s="422"/>
       <c r="E55" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F55" s="401" t="s">
+      <c r="F55" s="396" t="s">
         <v>76</v>
       </c>
-      <c r="G55" s="402"/>
-      <c r="H55" s="403"/>
+      <c r="G55" s="397"/>
+      <c r="H55" s="398"/>
       <c r="I55" s="32"/>
     </row>
     <row r="56" spans="1:14" ht="12" customHeight="1">
@@ -18221,16 +18221,16 @@
       <c r="B56" s="21">
         <v>29</v>
       </c>
-      <c r="C56" s="399"/>
-      <c r="D56" s="400"/>
+      <c r="C56" s="421"/>
+      <c r="D56" s="422"/>
       <c r="E56" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="401" t="s">
+      <c r="F56" s="396" t="s">
         <v>77</v>
       </c>
-      <c r="G56" s="402"/>
-      <c r="H56" s="403"/>
+      <c r="G56" s="397"/>
+      <c r="H56" s="398"/>
       <c r="I56" s="32"/>
     </row>
     <row r="57" spans="1:14" ht="12" customHeight="1">
@@ -18240,16 +18240,16 @@
       <c r="B57" s="21">
         <v>30</v>
       </c>
-      <c r="C57" s="399"/>
-      <c r="D57" s="400"/>
+      <c r="C57" s="421"/>
+      <c r="D57" s="422"/>
       <c r="E57" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="401" t="s">
+      <c r="F57" s="396" t="s">
         <v>78</v>
       </c>
-      <c r="G57" s="402"/>
-      <c r="H57" s="403"/>
+      <c r="G57" s="397"/>
+      <c r="H57" s="398"/>
       <c r="I57" s="32"/>
     </row>
     <row r="58" spans="1:14" ht="12" customHeight="1">
@@ -18268,11 +18268,11 @@
       <c r="E58" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F58" s="401" t="s">
+      <c r="F58" s="396" t="s">
         <v>79</v>
       </c>
-      <c r="G58" s="402"/>
-      <c r="H58" s="403"/>
+      <c r="G58" s="397"/>
+      <c r="H58" s="398"/>
       <c r="I58" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18288,14 +18288,14 @@
       <c r="B60" s="21">
         <v>33</v>
       </c>
-      <c r="C60" s="394" t="s">
+      <c r="C60" s="393" t="s">
         <v>80</v>
       </c>
-      <c r="D60" s="395"/>
-      <c r="E60" s="395"/>
-      <c r="F60" s="395"/>
-      <c r="G60" s="395"/>
-      <c r="H60" s="396"/>
+      <c r="D60" s="394"/>
+      <c r="E60" s="394"/>
+      <c r="F60" s="394"/>
+      <c r="G60" s="394"/>
+      <c r="H60" s="395"/>
       <c r="I60" s="32"/>
     </row>
     <row r="61" spans="1:14" ht="12" customHeight="1">
@@ -18305,16 +18305,16 @@
       <c r="B61" s="21">
         <v>34</v>
       </c>
-      <c r="C61" s="397" t="s">
+      <c r="C61" s="419" t="s">
         <v>81</v>
       </c>
-      <c r="D61" s="398"/>
-      <c r="E61" s="394" t="s">
+      <c r="D61" s="420"/>
+      <c r="E61" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F61" s="395"/>
-      <c r="G61" s="395"/>
-      <c r="H61" s="396"/>
+      <c r="F61" s="394"/>
+      <c r="G61" s="394"/>
+      <c r="H61" s="395"/>
       <c r="I61" s="32"/>
     </row>
     <row r="62" spans="1:14" ht="12" customHeight="1">
@@ -18324,18 +18324,18 @@
       <c r="B62" s="21">
         <v>35</v>
       </c>
-      <c r="C62" s="399"/>
-      <c r="D62" s="400"/>
+      <c r="C62" s="421"/>
+      <c r="D62" s="422"/>
       <c r="E62" s="26" t="s">
         <v>55</v>
       </c>
       <c r="F62" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G62" s="416" t="s">
+      <c r="G62" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H62" s="417"/>
+      <c r="H62" s="443"/>
       <c r="I62" s="32"/>
     </row>
     <row r="63" spans="1:14" ht="12" customHeight="1">
@@ -18345,8 +18345,8 @@
       <c r="B63" s="21">
         <v>36</v>
       </c>
-      <c r="C63" s="399"/>
-      <c r="D63" s="400"/>
+      <c r="C63" s="421"/>
+      <c r="D63" s="422"/>
       <c r="E63" s="27" t="s">
         <v>44</v>
       </c>
@@ -18410,10 +18410,10 @@
       <c r="F66" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="G66" s="416" t="s">
+      <c r="G66" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H66" s="417"/>
+      <c r="H66" s="443"/>
       <c r="I66" s="32"/>
     </row>
     <row r="67" spans="1:14" ht="12" customHeight="1">
@@ -18492,10 +18492,10 @@
       <c r="F70" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G70" s="416" t="s">
+      <c r="G70" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H70" s="417"/>
+      <c r="H70" s="443"/>
       <c r="I70" s="32"/>
     </row>
     <row r="71" spans="1:14" ht="12" customHeight="1">
@@ -18574,10 +18574,10 @@
       <c r="F74" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="G74" s="416" t="s">
+      <c r="G74" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H74" s="417"/>
+      <c r="H74" s="443"/>
       <c r="I74" s="32"/>
     </row>
     <row r="75" spans="1:14" ht="12" customHeight="1">
@@ -18644,16 +18644,16 @@
       <c r="B78" s="21">
         <v>51</v>
       </c>
-      <c r="C78" s="397" t="s">
+      <c r="C78" s="419" t="s">
         <v>88</v>
       </c>
-      <c r="D78" s="398"/>
-      <c r="E78" s="394" t="s">
+      <c r="D78" s="420"/>
+      <c r="E78" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F78" s="395"/>
-      <c r="G78" s="395"/>
-      <c r="H78" s="396"/>
+      <c r="F78" s="394"/>
+      <c r="G78" s="394"/>
+      <c r="H78" s="395"/>
       <c r="I78" s="32"/>
     </row>
     <row r="79" spans="1:14" ht="12" customHeight="1">
@@ -18663,16 +18663,16 @@
       <c r="B79" s="21">
         <v>52</v>
       </c>
-      <c r="C79" s="399"/>
-      <c r="D79" s="400"/>
+      <c r="C79" s="421"/>
+      <c r="D79" s="422"/>
       <c r="E79" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F79" s="401" t="s">
+      <c r="F79" s="396" t="s">
         <v>89</v>
       </c>
-      <c r="G79" s="402"/>
-      <c r="H79" s="403"/>
+      <c r="G79" s="397"/>
+      <c r="H79" s="398"/>
       <c r="I79" s="32"/>
     </row>
     <row r="80" spans="1:14" ht="12" customHeight="1">
@@ -18691,11 +18691,11 @@
       <c r="E80" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F80" s="401" t="s">
+      <c r="F80" s="396" t="s">
         <v>24</v>
       </c>
-      <c r="G80" s="402"/>
-      <c r="H80" s="403"/>
+      <c r="G80" s="397"/>
+      <c r="H80" s="398"/>
       <c r="I80" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18718,11 +18718,11 @@
       <c r="E81" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="401" t="s">
+      <c r="F81" s="396" t="s">
         <v>90</v>
       </c>
-      <c r="G81" s="402"/>
-      <c r="H81" s="403"/>
+      <c r="G81" s="397"/>
+      <c r="H81" s="398"/>
       <c r="I81" s="32"/>
       <c r="N81" s="35"/>
     </row>
@@ -18742,13 +18742,13 @@
       <c r="E82" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="413" t="s">
+      <c r="F82" s="429" t="s">
         <v>91</v>
       </c>
-      <c r="G82" s="416" t="s">
+      <c r="G82" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H82" s="417"/>
+      <c r="H82" s="443"/>
       <c r="I82" s="32"/>
     </row>
     <row r="83" spans="1:14" ht="24" customHeight="1">
@@ -18767,8 +18767,8 @@
       <c r="E83" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F83" s="415"/>
-      <c r="G83" s="413" t="s">
+      <c r="F83" s="437"/>
+      <c r="G83" s="429" t="s">
         <v>55</v>
       </c>
       <c r="H83" s="15" t="s">
@@ -18795,8 +18795,8 @@
       <c r="E84" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F84" s="414"/>
-      <c r="G84" s="414"/>
+      <c r="F84" s="430"/>
+      <c r="G84" s="430"/>
       <c r="H84" s="15" t="s">
         <v>92</v>
       </c>
@@ -18821,11 +18821,11 @@
       <c r="E85" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F85" s="401" t="s">
+      <c r="F85" s="396" t="s">
         <v>9</v>
       </c>
-      <c r="G85" s="402"/>
-      <c r="H85" s="403"/>
+      <c r="G85" s="397"/>
+      <c r="H85" s="398"/>
       <c r="I85" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18847,11 +18847,11 @@
       <c r="E86" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F86" s="401" t="s">
+      <c r="F86" s="396" t="s">
         <v>10</v>
       </c>
-      <c r="G86" s="402"/>
-      <c r="H86" s="403"/>
+      <c r="G86" s="397"/>
+      <c r="H86" s="398"/>
       <c r="I86" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18873,11 +18873,11 @@
       <c r="E87" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F87" s="401" t="s">
+      <c r="F87" s="396" t="s">
         <v>11</v>
       </c>
-      <c r="G87" s="402"/>
-      <c r="H87" s="403"/>
+      <c r="G87" s="397"/>
+      <c r="H87" s="398"/>
       <c r="I87" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18899,11 +18899,11 @@
       <c r="E88" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="401" t="s">
+      <c r="F88" s="396" t="s">
         <v>93</v>
       </c>
-      <c r="G88" s="402"/>
-      <c r="H88" s="403"/>
+      <c r="G88" s="397"/>
+      <c r="H88" s="398"/>
       <c r="I88" s="32"/>
     </row>
     <row r="89" spans="1:14" ht="12" customHeight="1">
@@ -18922,11 +18922,11 @@
       <c r="E89" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F89" s="391" t="s">
+      <c r="F89" s="416" t="s">
         <v>94</v>
       </c>
-      <c r="G89" s="392"/>
-      <c r="H89" s="393"/>
+      <c r="G89" s="417"/>
+      <c r="H89" s="418"/>
       <c r="I89" s="32"/>
       <c r="J89" s="10"/>
     </row>
@@ -18946,9 +18946,9 @@
       <c r="E90" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F90" s="391"/>
-      <c r="G90" s="392"/>
-      <c r="H90" s="393"/>
+      <c r="F90" s="416"/>
+      <c r="G90" s="417"/>
+      <c r="H90" s="418"/>
       <c r="I90" s="39"/>
       <c r="J90" s="10"/>
     </row>
@@ -18962,16 +18962,16 @@
       <c r="B92" s="21">
         <v>63</v>
       </c>
-      <c r="C92" s="397" t="s">
+      <c r="C92" s="419" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="398"/>
-      <c r="E92" s="394" t="s">
+      <c r="D92" s="420"/>
+      <c r="E92" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F92" s="395"/>
-      <c r="G92" s="395"/>
-      <c r="H92" s="396"/>
+      <c r="F92" s="394"/>
+      <c r="G92" s="394"/>
+      <c r="H92" s="395"/>
       <c r="I92" s="32"/>
     </row>
     <row r="93" spans="1:14" ht="12" customHeight="1">
@@ -18987,14 +18987,14 @@
       <c r="D93" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="413" t="s">
+      <c r="E93" s="429" t="s">
         <v>55</v>
       </c>
-      <c r="F93" s="401" t="s">
-        <v>44</v>
-      </c>
-      <c r="G93" s="402"/>
-      <c r="H93" s="403"/>
+      <c r="F93" s="396" t="s">
+        <v>44</v>
+      </c>
+      <c r="G93" s="397"/>
+      <c r="H93" s="398"/>
       <c r="I93" s="32"/>
     </row>
     <row r="94" spans="1:14" ht="12" customHeight="1">
@@ -19010,12 +19010,12 @@
       <c r="D94" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="E94" s="414"/>
-      <c r="F94" s="391" t="s">
+      <c r="E94" s="430"/>
+      <c r="F94" s="416" t="s">
         <v>96</v>
       </c>
-      <c r="G94" s="392"/>
-      <c r="H94" s="393"/>
+      <c r="G94" s="417"/>
+      <c r="H94" s="418"/>
       <c r="I94" s="32"/>
       <c r="J94" s="10"/>
     </row>
@@ -19029,16 +19029,16 @@
       <c r="B96" s="21">
         <v>66</v>
       </c>
-      <c r="C96" s="397" t="s">
+      <c r="C96" s="419" t="s">
         <v>97</v>
       </c>
-      <c r="D96" s="398"/>
-      <c r="E96" s="394" t="s">
+      <c r="D96" s="420"/>
+      <c r="E96" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F96" s="395"/>
-      <c r="G96" s="395"/>
-      <c r="H96" s="396"/>
+      <c r="F96" s="394"/>
+      <c r="G96" s="394"/>
+      <c r="H96" s="395"/>
       <c r="I96" s="32"/>
     </row>
     <row r="97" spans="1:10" ht="12" customHeight="1">
@@ -19057,11 +19057,11 @@
       <c r="E97" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F97" s="401" t="s">
+      <c r="F97" s="396" t="s">
         <v>98</v>
       </c>
-      <c r="G97" s="402"/>
-      <c r="H97" s="403"/>
+      <c r="G97" s="397"/>
+      <c r="H97" s="398"/>
       <c r="I97" s="32"/>
     </row>
     <row r="98" spans="1:10" ht="12" customHeight="1">
@@ -19080,11 +19080,11 @@
       <c r="E98" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F98" s="401" t="s">
+      <c r="F98" s="396" t="s">
         <v>99</v>
       </c>
-      <c r="G98" s="402"/>
-      <c r="H98" s="403"/>
+      <c r="G98" s="397"/>
+      <c r="H98" s="398"/>
       <c r="I98" s="32"/>
     </row>
     <row r="99" spans="1:10" ht="12" customHeight="1">
@@ -19103,11 +19103,11 @@
       <c r="E99" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F99" s="401" t="s">
+      <c r="F99" s="396" t="s">
         <v>12</v>
       </c>
-      <c r="G99" s="402"/>
-      <c r="H99" s="403"/>
+      <c r="G99" s="397"/>
+      <c r="H99" s="398"/>
       <c r="I99" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19129,11 +19129,11 @@
       <c r="E100" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F100" s="401" t="s">
+      <c r="F100" s="396" t="s">
         <v>100</v>
       </c>
-      <c r="G100" s="402"/>
-      <c r="H100" s="403"/>
+      <c r="G100" s="397"/>
+      <c r="H100" s="398"/>
       <c r="I100" s="32"/>
     </row>
     <row r="101" spans="1:10" ht="12" customHeight="1">
@@ -19152,11 +19152,11 @@
       <c r="E101" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F101" s="391" t="s">
-        <v>44</v>
-      </c>
-      <c r="G101" s="392"/>
-      <c r="H101" s="393"/>
+      <c r="F101" s="416" t="s">
+        <v>44</v>
+      </c>
+      <c r="G101" s="417"/>
+      <c r="H101" s="418"/>
       <c r="I101" s="32"/>
       <c r="J101" s="10"/>
     </row>
@@ -19176,11 +19176,11 @@
       <c r="E102" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F102" s="391" t="s">
-        <v>44</v>
-      </c>
-      <c r="G102" s="392"/>
-      <c r="H102" s="393"/>
+      <c r="F102" s="416" t="s">
+        <v>44</v>
+      </c>
+      <c r="G102" s="417"/>
+      <c r="H102" s="418"/>
       <c r="I102" s="32"/>
       <c r="J102" s="10"/>
     </row>
@@ -19194,14 +19194,14 @@
       <c r="B104" s="21">
         <v>72</v>
       </c>
-      <c r="C104" s="394" t="s">
+      <c r="C104" s="393" t="s">
         <v>19</v>
       </c>
-      <c r="D104" s="395"/>
-      <c r="E104" s="395"/>
-      <c r="F104" s="395"/>
-      <c r="G104" s="395"/>
-      <c r="H104" s="396"/>
+      <c r="D104" s="394"/>
+      <c r="E104" s="394"/>
+      <c r="F104" s="394"/>
+      <c r="G104" s="394"/>
+      <c r="H104" s="395"/>
       <c r="I104" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19214,14 +19214,14 @@
       <c r="B105" s="21">
         <v>73</v>
       </c>
-      <c r="C105" s="394" t="s">
+      <c r="C105" s="393" t="s">
         <v>101</v>
       </c>
-      <c r="D105" s="395"/>
-      <c r="E105" s="395"/>
-      <c r="F105" s="395"/>
-      <c r="G105" s="395"/>
-      <c r="H105" s="396"/>
+      <c r="D105" s="394"/>
+      <c r="E105" s="394"/>
+      <c r="F105" s="394"/>
+      <c r="G105" s="394"/>
+      <c r="H105" s="395"/>
       <c r="I105" s="32"/>
     </row>
     <row r="106" spans="1:10" ht="12" customHeight="1">
@@ -19231,16 +19231,16 @@
       <c r="B106" s="21">
         <v>74</v>
       </c>
-      <c r="C106" s="397" t="s">
+      <c r="C106" s="419" t="s">
         <v>102</v>
       </c>
-      <c r="D106" s="398"/>
-      <c r="E106" s="394" t="s">
+      <c r="D106" s="420"/>
+      <c r="E106" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F106" s="395"/>
-      <c r="G106" s="395"/>
-      <c r="H106" s="396"/>
+      <c r="F106" s="394"/>
+      <c r="G106" s="394"/>
+      <c r="H106" s="395"/>
       <c r="I106" s="32"/>
     </row>
     <row r="107" spans="1:10" ht="18.75" customHeight="1">
@@ -19250,16 +19250,16 @@
       <c r="B107" s="21">
         <v>75</v>
       </c>
-      <c r="C107" s="399"/>
-      <c r="D107" s="400"/>
+      <c r="C107" s="421"/>
+      <c r="D107" s="422"/>
       <c r="E107" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F107" s="401" t="s">
+      <c r="F107" s="396" t="s">
         <v>13</v>
       </c>
-      <c r="G107" s="402"/>
-      <c r="H107" s="403"/>
+      <c r="G107" s="397"/>
+      <c r="H107" s="398"/>
       <c r="I107" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19281,11 +19281,11 @@
       <c r="E108" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F108" s="391" t="s">
+      <c r="F108" s="416" t="s">
         <v>103</v>
       </c>
-      <c r="G108" s="392"/>
-      <c r="H108" s="393"/>
+      <c r="G108" s="417"/>
+      <c r="H108" s="418"/>
       <c r="I108" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19308,11 +19308,11 @@
       <c r="E109" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F109" s="391" t="s">
+      <c r="F109" s="416" t="s">
         <v>104</v>
       </c>
-      <c r="G109" s="392"/>
-      <c r="H109" s="393"/>
+      <c r="G109" s="417"/>
+      <c r="H109" s="418"/>
       <c r="I109" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19335,11 +19335,11 @@
       <c r="E110" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F110" s="391" t="s">
+      <c r="F110" s="416" t="s">
         <v>8</v>
       </c>
-      <c r="G110" s="392"/>
-      <c r="H110" s="393"/>
+      <c r="G110" s="417"/>
+      <c r="H110" s="418"/>
       <c r="I110" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19356,16 +19356,16 @@
       <c r="B112" s="21">
         <v>77</v>
       </c>
-      <c r="C112" s="397" t="s">
+      <c r="C112" s="419" t="s">
         <v>105</v>
       </c>
-      <c r="D112" s="398"/>
-      <c r="E112" s="394" t="s">
+      <c r="D112" s="420"/>
+      <c r="E112" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F112" s="395"/>
-      <c r="G112" s="395"/>
-      <c r="H112" s="396"/>
+      <c r="F112" s="394"/>
+      <c r="G112" s="394"/>
+      <c r="H112" s="395"/>
       <c r="I112" s="32"/>
     </row>
     <row r="113" spans="1:9" ht="12" customHeight="1">
@@ -19384,11 +19384,11 @@
       <c r="E113" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F113" s="401" t="s">
+      <c r="F113" s="396" t="s">
         <v>106</v>
       </c>
-      <c r="G113" s="402"/>
-      <c r="H113" s="403"/>
+      <c r="G113" s="397"/>
+      <c r="H113" s="398"/>
       <c r="I113" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19410,11 +19410,11 @@
       <c r="E114" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F114" s="401" t="s">
+      <c r="F114" s="396" t="s">
         <v>107</v>
       </c>
-      <c r="G114" s="402"/>
-      <c r="H114" s="403"/>
+      <c r="G114" s="397"/>
+      <c r="H114" s="398"/>
       <c r="I114" s="32"/>
     </row>
     <row r="115" spans="1:9" ht="12" customHeight="1">
@@ -19424,14 +19424,14 @@
       <c r="B115" s="21">
         <v>80</v>
       </c>
-      <c r="C115" s="394" t="s">
+      <c r="C115" s="393" t="s">
         <v>108</v>
       </c>
-      <c r="D115" s="395"/>
-      <c r="E115" s="395"/>
-      <c r="F115" s="395"/>
-      <c r="G115" s="395"/>
-      <c r="H115" s="396"/>
+      <c r="D115" s="394"/>
+      <c r="E115" s="394"/>
+      <c r="F115" s="394"/>
+      <c r="G115" s="394"/>
+      <c r="H115" s="395"/>
       <c r="I115" s="32"/>
     </row>
     <row r="116" spans="1:9" ht="12" customHeight="1">
@@ -19441,16 +19441,16 @@
       <c r="B116" s="21">
         <v>81</v>
       </c>
-      <c r="C116" s="397" t="s">
+      <c r="C116" s="419" t="s">
         <v>109</v>
       </c>
-      <c r="D116" s="398"/>
-      <c r="E116" s="394" t="s">
+      <c r="D116" s="420"/>
+      <c r="E116" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F116" s="395"/>
-      <c r="G116" s="395"/>
-      <c r="H116" s="396"/>
+      <c r="F116" s="394"/>
+      <c r="G116" s="394"/>
+      <c r="H116" s="395"/>
       <c r="I116" s="32"/>
     </row>
     <row r="117" spans="1:9" ht="12" customHeight="1">
@@ -19460,16 +19460,16 @@
       <c r="B117" s="21">
         <v>82</v>
       </c>
-      <c r="C117" s="399"/>
-      <c r="D117" s="400"/>
+      <c r="C117" s="421"/>
+      <c r="D117" s="422"/>
       <c r="E117" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F117" s="401" t="s">
+      <c r="F117" s="396" t="s">
         <v>110</v>
       </c>
-      <c r="G117" s="402"/>
-      <c r="H117" s="403"/>
+      <c r="G117" s="397"/>
+      <c r="H117" s="398"/>
       <c r="I117" s="32"/>
     </row>
     <row r="118" spans="1:9" ht="12" customHeight="1">
@@ -19488,11 +19488,11 @@
       <c r="E118" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F118" s="401" t="s">
+      <c r="F118" s="396" t="s">
         <v>111</v>
       </c>
-      <c r="G118" s="402"/>
-      <c r="H118" s="403"/>
+      <c r="G118" s="397"/>
+      <c r="H118" s="398"/>
       <c r="I118" s="32"/>
     </row>
     <row r="119" spans="1:9" hidden="1">
@@ -19505,16 +19505,16 @@
       <c r="B120" s="21">
         <v>85</v>
       </c>
-      <c r="C120" s="397" t="s">
+      <c r="C120" s="419" t="s">
         <v>112</v>
       </c>
-      <c r="D120" s="398"/>
-      <c r="E120" s="394" t="s">
+      <c r="D120" s="420"/>
+      <c r="E120" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F120" s="395"/>
-      <c r="G120" s="395"/>
-      <c r="H120" s="396"/>
+      <c r="F120" s="394"/>
+      <c r="G120" s="394"/>
+      <c r="H120" s="395"/>
       <c r="I120" s="32"/>
     </row>
     <row r="121" spans="1:9" ht="12" customHeight="1">
@@ -19524,16 +19524,16 @@
       <c r="B121" s="21">
         <v>86</v>
       </c>
-      <c r="C121" s="399"/>
-      <c r="D121" s="400"/>
+      <c r="C121" s="421"/>
+      <c r="D121" s="422"/>
       <c r="E121" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F121" s="401" t="s">
+      <c r="F121" s="396" t="s">
         <v>113</v>
       </c>
-      <c r="G121" s="402"/>
-      <c r="H121" s="403"/>
+      <c r="G121" s="397"/>
+      <c r="H121" s="398"/>
       <c r="I121" s="32"/>
     </row>
     <row r="122" spans="1:9" ht="12" customHeight="1">
@@ -19552,11 +19552,11 @@
       <c r="E122" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F122" s="401" t="s">
+      <c r="F122" s="396" t="s">
         <v>111</v>
       </c>
-      <c r="G122" s="402"/>
-      <c r="H122" s="403"/>
+      <c r="G122" s="397"/>
+      <c r="H122" s="398"/>
       <c r="I122" s="32"/>
     </row>
     <row r="123" spans="1:9" ht="12" customHeight="1">
@@ -19575,11 +19575,11 @@
       <c r="E123" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F123" s="401" t="s">
+      <c r="F123" s="396" t="s">
         <v>114</v>
       </c>
-      <c r="G123" s="402"/>
-      <c r="H123" s="403"/>
+      <c r="G123" s="397"/>
+      <c r="H123" s="398"/>
       <c r="I123" s="32"/>
     </row>
     <row r="124" spans="1:9" ht="12" customHeight="1">
@@ -19598,11 +19598,11 @@
       <c r="E124" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F124" s="401" t="s">
+      <c r="F124" s="396" t="s">
         <v>115</v>
       </c>
-      <c r="G124" s="402"/>
-      <c r="H124" s="403"/>
+      <c r="G124" s="397"/>
+      <c r="H124" s="398"/>
       <c r="I124" s="32"/>
     </row>
     <row r="125" spans="1:9" hidden="1">
@@ -19615,14 +19615,14 @@
       <c r="B126" s="21">
         <v>91</v>
       </c>
-      <c r="C126" s="394" t="s">
+      <c r="C126" s="393" t="s">
         <v>116</v>
       </c>
-      <c r="D126" s="395"/>
-      <c r="E126" s="395"/>
-      <c r="F126" s="395"/>
-      <c r="G126" s="395"/>
-      <c r="H126" s="396"/>
+      <c r="D126" s="394"/>
+      <c r="E126" s="394"/>
+      <c r="F126" s="394"/>
+      <c r="G126" s="394"/>
+      <c r="H126" s="395"/>
       <c r="I126" s="32"/>
     </row>
     <row r="127" spans="1:9" ht="12" customHeight="1">
@@ -19632,16 +19632,16 @@
       <c r="B127" s="21">
         <v>92</v>
       </c>
-      <c r="C127" s="397" t="s">
+      <c r="C127" s="419" t="s">
         <v>117</v>
       </c>
-      <c r="D127" s="398"/>
-      <c r="E127" s="394" t="s">
+      <c r="D127" s="420"/>
+      <c r="E127" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F127" s="395"/>
-      <c r="G127" s="395"/>
-      <c r="H127" s="396"/>
+      <c r="F127" s="394"/>
+      <c r="G127" s="394"/>
+      <c r="H127" s="395"/>
       <c r="I127" s="32"/>
     </row>
     <row r="128" spans="1:9" ht="12" customHeight="1">
@@ -19651,16 +19651,16 @@
       <c r="B128" s="21">
         <v>93</v>
       </c>
-      <c r="C128" s="399"/>
-      <c r="D128" s="400"/>
+      <c r="C128" s="421"/>
+      <c r="D128" s="422"/>
       <c r="E128" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F128" s="404" t="s">
-        <v>44</v>
-      </c>
-      <c r="G128" s="405"/>
-      <c r="H128" s="406"/>
+      <c r="F128" s="444" t="s">
+        <v>44</v>
+      </c>
+      <c r="G128" s="445"/>
+      <c r="H128" s="446"/>
       <c r="I128" s="40"/>
     </row>
     <row r="129" spans="1:14" hidden="1">
@@ -19673,14 +19673,14 @@
       <c r="B130" s="21">
         <v>95</v>
       </c>
-      <c r="C130" s="394" t="s">
+      <c r="C130" s="393" t="s">
         <v>118</v>
       </c>
-      <c r="D130" s="395"/>
-      <c r="E130" s="395"/>
-      <c r="F130" s="395"/>
-      <c r="G130" s="395"/>
-      <c r="H130" s="396"/>
+      <c r="D130" s="394"/>
+      <c r="E130" s="394"/>
+      <c r="F130" s="394"/>
+      <c r="G130" s="394"/>
+      <c r="H130" s="395"/>
       <c r="I130" s="32"/>
     </row>
     <row r="131" spans="1:14" ht="12" customHeight="1">
@@ -19690,14 +19690,14 @@
       <c r="B131" s="21">
         <v>96</v>
       </c>
-      <c r="C131" s="394" t="s">
+      <c r="C131" s="393" t="s">
         <v>119</v>
       </c>
-      <c r="D131" s="395"/>
-      <c r="E131" s="395"/>
-      <c r="F131" s="395"/>
-      <c r="G131" s="395"/>
-      <c r="H131" s="396"/>
+      <c r="D131" s="394"/>
+      <c r="E131" s="394"/>
+      <c r="F131" s="394"/>
+      <c r="G131" s="394"/>
+      <c r="H131" s="395"/>
       <c r="I131" s="32"/>
     </row>
     <row r="132" spans="1:14" ht="12" customHeight="1">
@@ -19707,16 +19707,16 @@
       <c r="B132" s="21">
         <v>97</v>
       </c>
-      <c r="C132" s="397" t="s">
+      <c r="C132" s="419" t="s">
         <v>120</v>
       </c>
-      <c r="D132" s="398"/>
-      <c r="E132" s="394" t="s">
+      <c r="D132" s="420"/>
+      <c r="E132" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F132" s="395"/>
-      <c r="G132" s="395"/>
-      <c r="H132" s="396"/>
+      <c r="F132" s="394"/>
+      <c r="G132" s="394"/>
+      <c r="H132" s="395"/>
       <c r="I132" s="32"/>
     </row>
     <row r="133" spans="1:14" ht="12" customHeight="1">
@@ -19726,16 +19726,16 @@
       <c r="B133" s="21">
         <v>98</v>
       </c>
-      <c r="C133" s="399"/>
-      <c r="D133" s="400"/>
+      <c r="C133" s="421"/>
+      <c r="D133" s="422"/>
       <c r="E133" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F133" s="401" t="s">
+      <c r="F133" s="396" t="s">
         <v>121</v>
       </c>
-      <c r="G133" s="402"/>
-      <c r="H133" s="403"/>
+      <c r="G133" s="397"/>
+      <c r="H133" s="398"/>
       <c r="I133" s="32"/>
     </row>
     <row r="134" spans="1:14" ht="12" customHeight="1">
@@ -19745,16 +19745,16 @@
       <c r="B134" s="21">
         <v>99</v>
       </c>
-      <c r="C134" s="399"/>
-      <c r="D134" s="400"/>
+      <c r="C134" s="421"/>
+      <c r="D134" s="422"/>
       <c r="E134" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F134" s="401" t="s">
+      <c r="F134" s="396" t="s">
         <v>122</v>
       </c>
-      <c r="G134" s="402"/>
-      <c r="H134" s="403"/>
+      <c r="G134" s="397"/>
+      <c r="H134" s="398"/>
       <c r="I134" s="32"/>
     </row>
     <row r="135" spans="1:14" ht="12" customHeight="1">
@@ -19764,16 +19764,16 @@
       <c r="B135" s="21">
         <v>100</v>
       </c>
-      <c r="C135" s="399"/>
-      <c r="D135" s="400"/>
+      <c r="C135" s="421"/>
+      <c r="D135" s="422"/>
       <c r="E135" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F135" s="401" t="s">
+      <c r="F135" s="396" t="s">
         <v>123</v>
       </c>
-      <c r="G135" s="402"/>
-      <c r="H135" s="403"/>
+      <c r="G135" s="397"/>
+      <c r="H135" s="398"/>
       <c r="I135" s="32"/>
     </row>
     <row r="136" spans="1:14" ht="12" customHeight="1">
@@ -19792,11 +19792,11 @@
       <c r="E136" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F136" s="401" t="s">
+      <c r="F136" s="396" t="s">
         <v>124</v>
       </c>
-      <c r="G136" s="402"/>
-      <c r="H136" s="403"/>
+      <c r="G136" s="397"/>
+      <c r="H136" s="398"/>
       <c r="I136" s="32"/>
     </row>
     <row r="137" spans="1:14" ht="12" customHeight="1">
@@ -19815,11 +19815,11 @@
       <c r="E137" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F137" s="401" t="s">
+      <c r="F137" s="396" t="s">
         <v>125</v>
       </c>
-      <c r="G137" s="402"/>
-      <c r="H137" s="403"/>
+      <c r="G137" s="397"/>
+      <c r="H137" s="398"/>
       <c r="I137" s="32"/>
     </row>
     <row r="138" spans="1:14" ht="12" customHeight="1">
@@ -19838,11 +19838,11 @@
       <c r="E138" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F138" s="401" t="s">
+      <c r="F138" s="396" t="s">
         <v>126</v>
       </c>
-      <c r="G138" s="402"/>
-      <c r="H138" s="403"/>
+      <c r="G138" s="397"/>
+      <c r="H138" s="398"/>
       <c r="I138" s="32"/>
     </row>
     <row r="139" spans="1:14" hidden="1">
@@ -19855,16 +19855,16 @@
       <c r="B140" s="21">
         <v>105</v>
       </c>
-      <c r="C140" s="407" t="s">
+      <c r="C140" s="423" t="s">
         <v>127</v>
       </c>
-      <c r="D140" s="408"/>
-      <c r="E140" s="394" t="s">
+      <c r="D140" s="424"/>
+      <c r="E140" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F140" s="395"/>
-      <c r="G140" s="395"/>
-      <c r="H140" s="396"/>
+      <c r="F140" s="394"/>
+      <c r="G140" s="394"/>
+      <c r="H140" s="395"/>
       <c r="I140" s="32"/>
     </row>
     <row r="141" spans="1:14" ht="12" customHeight="1">
@@ -19874,16 +19874,16 @@
       <c r="B141" s="21">
         <v>106</v>
       </c>
-      <c r="C141" s="409"/>
-      <c r="D141" s="410"/>
-      <c r="E141" s="413" t="s">
+      <c r="C141" s="425"/>
+      <c r="D141" s="426"/>
+      <c r="E141" s="429" t="s">
         <v>55</v>
       </c>
-      <c r="F141" s="401" t="s">
+      <c r="F141" s="396" t="s">
         <v>128</v>
       </c>
-      <c r="G141" s="402"/>
-      <c r="H141" s="403"/>
+      <c r="G141" s="397"/>
+      <c r="H141" s="398"/>
       <c r="I141" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -19896,14 +19896,14 @@
       <c r="B142" s="21">
         <v>107</v>
       </c>
-      <c r="C142" s="411"/>
-      <c r="D142" s="412"/>
-      <c r="E142" s="414"/>
-      <c r="F142" s="401" t="s">
+      <c r="C142" s="427"/>
+      <c r="D142" s="428"/>
+      <c r="E142" s="430"/>
+      <c r="F142" s="396" t="s">
         <v>129</v>
       </c>
-      <c r="G142" s="402"/>
-      <c r="H142" s="403"/>
+      <c r="G142" s="397"/>
+      <c r="H142" s="398"/>
       <c r="I142" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19917,14 +19917,14 @@
       <c r="B143" s="21">
         <v>108</v>
       </c>
-      <c r="C143" s="394" t="s">
+      <c r="C143" s="393" t="s">
         <v>22</v>
       </c>
-      <c r="D143" s="395"/>
-      <c r="E143" s="395"/>
-      <c r="F143" s="395"/>
-      <c r="G143" s="395"/>
-      <c r="H143" s="396"/>
+      <c r="D143" s="394"/>
+      <c r="E143" s="394"/>
+      <c r="F143" s="394"/>
+      <c r="G143" s="394"/>
+      <c r="H143" s="395"/>
       <c r="I143" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19944,12 +19944,12 @@
       <c r="D144" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E144" s="394" t="s">
+      <c r="E144" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F144" s="395"/>
-      <c r="G144" s="395"/>
-      <c r="H144" s="396"/>
+      <c r="F144" s="394"/>
+      <c r="G144" s="394"/>
+      <c r="H144" s="395"/>
       <c r="I144" s="32"/>
     </row>
     <row r="145" spans="1:10" ht="12" customHeight="1">
@@ -19968,11 +19968,11 @@
       <c r="E145" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F145" s="401" t="s">
+      <c r="F145" s="396" t="s">
         <v>131</v>
       </c>
-      <c r="G145" s="402"/>
-      <c r="H145" s="403"/>
+      <c r="G145" s="397"/>
+      <c r="H145" s="398"/>
       <c r="I145" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19994,11 +19994,11 @@
       <c r="E146" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F146" s="401" t="s">
+      <c r="F146" s="396" t="s">
         <v>132</v>
       </c>
-      <c r="G146" s="402"/>
-      <c r="H146" s="403"/>
+      <c r="G146" s="397"/>
+      <c r="H146" s="398"/>
       <c r="I146" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20020,11 +20020,11 @@
       <c r="E147" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F147" s="401" t="s">
+      <c r="F147" s="396" t="s">
         <v>64</v>
       </c>
-      <c r="G147" s="402"/>
-      <c r="H147" s="403"/>
+      <c r="G147" s="397"/>
+      <c r="H147" s="398"/>
       <c r="I147" s="32"/>
     </row>
     <row r="148" spans="1:10" ht="12" customHeight="1">
@@ -20043,11 +20043,11 @@
       <c r="E148" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F148" s="391" t="s">
+      <c r="F148" s="416" t="s">
         <v>133</v>
       </c>
-      <c r="G148" s="392"/>
-      <c r="H148" s="393"/>
+      <c r="G148" s="417"/>
+      <c r="H148" s="418"/>
       <c r="I148" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20070,11 +20070,11 @@
       <c r="E149" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F149" s="391" t="s">
+      <c r="F149" s="416" t="s">
         <v>134</v>
       </c>
-      <c r="G149" s="392"/>
-      <c r="H149" s="393"/>
+      <c r="G149" s="417"/>
+      <c r="H149" s="418"/>
       <c r="I149" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20097,11 +20097,11 @@
       <c r="E150" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F150" s="391" t="s">
+      <c r="F150" s="416" t="s">
         <v>135</v>
       </c>
-      <c r="G150" s="392"/>
-      <c r="H150" s="393"/>
+      <c r="G150" s="417"/>
+      <c r="H150" s="418"/>
       <c r="I150" s="32"/>
       <c r="J150" s="10"/>
     </row>
@@ -20121,11 +20121,11 @@
       <c r="E151" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F151" s="391" t="s">
+      <c r="F151" s="416" t="s">
         <v>136</v>
       </c>
-      <c r="G151" s="392"/>
-      <c r="H151" s="393"/>
+      <c r="G151" s="417"/>
+      <c r="H151" s="418"/>
       <c r="I151" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20142,16 +20142,16 @@
       <c r="B153" s="21">
         <v>114</v>
       </c>
-      <c r="C153" s="397" t="s">
+      <c r="C153" s="419" t="s">
         <v>137</v>
       </c>
-      <c r="D153" s="398"/>
-      <c r="E153" s="394" t="s">
+      <c r="D153" s="420"/>
+      <c r="E153" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F153" s="395"/>
-      <c r="G153" s="395"/>
-      <c r="H153" s="396"/>
+      <c r="F153" s="394"/>
+      <c r="G153" s="394"/>
+      <c r="H153" s="395"/>
       <c r="I153" s="32"/>
     </row>
     <row r="154" spans="1:10" ht="12" customHeight="1">
@@ -20161,16 +20161,16 @@
       <c r="B154" s="21">
         <v>115</v>
       </c>
-      <c r="C154" s="399"/>
-      <c r="D154" s="400"/>
+      <c r="C154" s="421"/>
+      <c r="D154" s="422"/>
       <c r="E154" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F154" s="404" t="s">
-        <v>44</v>
-      </c>
-      <c r="G154" s="405"/>
-      <c r="H154" s="406"/>
+      <c r="F154" s="444" t="s">
+        <v>44</v>
+      </c>
+      <c r="G154" s="445"/>
+      <c r="H154" s="446"/>
       <c r="I154" s="40"/>
     </row>
     <row r="155" spans="1:10" ht="12" customHeight="1">
@@ -20189,11 +20189,11 @@
       <c r="E155" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F155" s="391" t="s">
+      <c r="F155" s="416" t="s">
         <v>4</v>
       </c>
-      <c r="G155" s="392"/>
-      <c r="H155" s="393"/>
+      <c r="G155" s="417"/>
+      <c r="H155" s="418"/>
       <c r="I155" s="32"/>
       <c r="J155" s="10"/>
     </row>
@@ -20213,11 +20213,11 @@
       <c r="E156" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F156" s="391" t="s">
+      <c r="F156" s="416" t="s">
         <v>138</v>
       </c>
-      <c r="G156" s="392"/>
-      <c r="H156" s="393"/>
+      <c r="G156" s="417"/>
+      <c r="H156" s="418"/>
       <c r="I156" s="32"/>
       <c r="J156" s="10"/>
     </row>
@@ -20237,11 +20237,11 @@
       <c r="E157" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F157" s="391" t="s">
+      <c r="F157" s="416" t="s">
         <v>139</v>
       </c>
-      <c r="G157" s="392"/>
-      <c r="H157" s="393"/>
+      <c r="G157" s="417"/>
+      <c r="H157" s="418"/>
       <c r="I157" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20264,9 +20264,9 @@
       <c r="E158" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F158" s="391"/>
-      <c r="G158" s="392"/>
-      <c r="H158" s="393"/>
+      <c r="F158" s="416"/>
+      <c r="G158" s="417"/>
+      <c r="H158" s="418"/>
       <c r="I158" s="32"/>
       <c r="J158" s="10"/>
     </row>
@@ -20280,14 +20280,14 @@
       <c r="B160" s="21">
         <v>117</v>
       </c>
-      <c r="C160" s="394" t="s">
+      <c r="C160" s="393" t="s">
         <v>140</v>
       </c>
-      <c r="D160" s="395"/>
-      <c r="E160" s="395"/>
-      <c r="F160" s="395"/>
-      <c r="G160" s="395"/>
-      <c r="H160" s="396"/>
+      <c r="D160" s="394"/>
+      <c r="E160" s="394"/>
+      <c r="F160" s="394"/>
+      <c r="G160" s="394"/>
+      <c r="H160" s="395"/>
       <c r="I160" s="32"/>
     </row>
     <row r="161" spans="1:9" ht="12" customHeight="1">
@@ -20297,14 +20297,14 @@
       <c r="B161" s="21">
         <v>118</v>
       </c>
-      <c r="C161" s="394" t="s">
+      <c r="C161" s="393" t="s">
         <v>141</v>
       </c>
-      <c r="D161" s="395"/>
-      <c r="E161" s="395"/>
-      <c r="F161" s="395"/>
-      <c r="G161" s="395"/>
-      <c r="H161" s="396"/>
+      <c r="D161" s="394"/>
+      <c r="E161" s="394"/>
+      <c r="F161" s="394"/>
+      <c r="G161" s="394"/>
+      <c r="H161" s="395"/>
       <c r="I161" s="42" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -20317,14 +20317,14 @@
       <c r="B162" s="21">
         <v>119</v>
       </c>
-      <c r="C162" s="394" t="s">
+      <c r="C162" s="393" t="s">
         <v>142</v>
       </c>
-      <c r="D162" s="395"/>
-      <c r="E162" s="395"/>
-      <c r="F162" s="395"/>
-      <c r="G162" s="395"/>
-      <c r="H162" s="396"/>
+      <c r="D162" s="394"/>
+      <c r="E162" s="394"/>
+      <c r="F162" s="394"/>
+      <c r="G162" s="394"/>
+      <c r="H162" s="395"/>
       <c r="I162" s="32"/>
     </row>
     <row r="163" spans="1:9" ht="12" customHeight="1">
@@ -20334,14 +20334,14 @@
       <c r="B163" s="21">
         <v>120</v>
       </c>
-      <c r="C163" s="394" t="s">
+      <c r="C163" s="393" t="s">
         <v>143</v>
       </c>
-      <c r="D163" s="395"/>
-      <c r="E163" s="395"/>
-      <c r="F163" s="395"/>
-      <c r="G163" s="395"/>
-      <c r="H163" s="396"/>
+      <c r="D163" s="394"/>
+      <c r="E163" s="394"/>
+      <c r="F163" s="394"/>
+      <c r="G163" s="394"/>
+      <c r="H163" s="395"/>
       <c r="I163" s="32"/>
     </row>
     <row r="164" spans="1:9" ht="12" customHeight="1">
@@ -20351,14 +20351,14 @@
       <c r="B164" s="21">
         <v>121</v>
       </c>
-      <c r="C164" s="394" t="s">
+      <c r="C164" s="393" t="s">
         <v>144</v>
       </c>
-      <c r="D164" s="395"/>
-      <c r="E164" s="395"/>
-      <c r="F164" s="395"/>
-      <c r="G164" s="395"/>
-      <c r="H164" s="396"/>
+      <c r="D164" s="394"/>
+      <c r="E164" s="394"/>
+      <c r="F164" s="394"/>
+      <c r="G164" s="394"/>
+      <c r="H164" s="395"/>
       <c r="I164" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20371,16 +20371,16 @@
       <c r="B165" s="21">
         <v>122</v>
       </c>
-      <c r="C165" s="397" t="s">
+      <c r="C165" s="419" t="s">
         <v>145</v>
       </c>
-      <c r="D165" s="398"/>
-      <c r="E165" s="394" t="s">
+      <c r="D165" s="420"/>
+      <c r="E165" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F165" s="395"/>
-      <c r="G165" s="395"/>
-      <c r="H165" s="396"/>
+      <c r="F165" s="394"/>
+      <c r="G165" s="394"/>
+      <c r="H165" s="395"/>
       <c r="I165" s="32"/>
     </row>
     <row r="166" spans="1:9" ht="12" customHeight="1">
@@ -20390,16 +20390,16 @@
       <c r="B166" s="21">
         <v>123</v>
       </c>
-      <c r="C166" s="399"/>
-      <c r="D166" s="400"/>
+      <c r="C166" s="421"/>
+      <c r="D166" s="422"/>
       <c r="E166" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F166" s="401" t="s">
+      <c r="F166" s="396" t="s">
         <v>146</v>
       </c>
-      <c r="G166" s="402"/>
-      <c r="H166" s="403"/>
+      <c r="G166" s="397"/>
+      <c r="H166" s="398"/>
       <c r="I166" s="32"/>
     </row>
     <row r="167" spans="1:9" ht="12" customHeight="1">
@@ -20418,11 +20418,11 @@
       <c r="E167" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F167" s="401" t="s">
+      <c r="F167" s="396" t="s">
         <v>147</v>
       </c>
-      <c r="G167" s="402"/>
-      <c r="H167" s="403"/>
+      <c r="G167" s="397"/>
+      <c r="H167" s="398"/>
       <c r="I167" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20444,11 +20444,11 @@
       <c r="E168" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F168" s="401" t="s">
+      <c r="F168" s="396" t="s">
         <v>148</v>
       </c>
-      <c r="G168" s="402"/>
-      <c r="H168" s="403"/>
+      <c r="G168" s="397"/>
+      <c r="H168" s="398"/>
       <c r="I168" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20464,14 +20464,14 @@
       <c r="B170" s="21">
         <v>127</v>
       </c>
-      <c r="C170" s="394" t="s">
+      <c r="C170" s="393" t="s">
         <v>17</v>
       </c>
-      <c r="D170" s="395"/>
-      <c r="E170" s="395"/>
-      <c r="F170" s="395"/>
-      <c r="G170" s="395"/>
-      <c r="H170" s="396"/>
+      <c r="D170" s="394"/>
+      <c r="E170" s="394"/>
+      <c r="F170" s="394"/>
+      <c r="G170" s="394"/>
+      <c r="H170" s="395"/>
       <c r="I170" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20484,14 +20484,14 @@
       <c r="B171" s="21">
         <v>128</v>
       </c>
-      <c r="C171" s="394" t="s">
+      <c r="C171" s="393" t="s">
         <v>149</v>
       </c>
-      <c r="D171" s="395"/>
-      <c r="E171" s="395"/>
-      <c r="F171" s="395"/>
-      <c r="G171" s="395"/>
-      <c r="H171" s="396"/>
+      <c r="D171" s="394"/>
+      <c r="E171" s="394"/>
+      <c r="F171" s="394"/>
+      <c r="G171" s="394"/>
+      <c r="H171" s="395"/>
       <c r="I171" s="32"/>
     </row>
     <row r="172" spans="1:9" ht="12" customHeight="1">
@@ -20501,14 +20501,14 @@
       <c r="B172" s="21">
         <v>129</v>
       </c>
-      <c r="C172" s="394" t="s">
+      <c r="C172" s="393" t="s">
         <v>150</v>
       </c>
-      <c r="D172" s="395"/>
-      <c r="E172" s="395"/>
-      <c r="F172" s="395"/>
-      <c r="G172" s="395"/>
-      <c r="H172" s="396"/>
+      <c r="D172" s="394"/>
+      <c r="E172" s="394"/>
+      <c r="F172" s="394"/>
+      <c r="G172" s="394"/>
+      <c r="H172" s="395"/>
       <c r="I172" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20521,14 +20521,14 @@
       <c r="B173" s="21">
         <v>130</v>
       </c>
-      <c r="C173" s="394" t="s">
+      <c r="C173" s="393" t="s">
         <v>151</v>
       </c>
-      <c r="D173" s="395"/>
-      <c r="E173" s="395"/>
-      <c r="F173" s="395"/>
-      <c r="G173" s="395"/>
-      <c r="H173" s="396"/>
+      <c r="D173" s="394"/>
+      <c r="E173" s="394"/>
+      <c r="F173" s="394"/>
+      <c r="G173" s="394"/>
+      <c r="H173" s="395"/>
       <c r="I173" s="32"/>
     </row>
     <row r="174" spans="1:9" ht="12" customHeight="1">
@@ -20538,14 +20538,14 @@
       <c r="B174" s="21">
         <v>131</v>
       </c>
-      <c r="C174" s="394" t="s">
+      <c r="C174" s="393" t="s">
         <v>152</v>
       </c>
-      <c r="D174" s="395"/>
-      <c r="E174" s="395"/>
-      <c r="F174" s="395"/>
-      <c r="G174" s="395"/>
-      <c r="H174" s="396"/>
+      <c r="D174" s="394"/>
+      <c r="E174" s="394"/>
+      <c r="F174" s="394"/>
+      <c r="G174" s="394"/>
+      <c r="H174" s="395"/>
       <c r="I174" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20558,16 +20558,16 @@
       <c r="B175" s="21">
         <v>132</v>
       </c>
-      <c r="C175" s="397" t="s">
+      <c r="C175" s="419" t="s">
         <v>153</v>
       </c>
-      <c r="D175" s="398"/>
-      <c r="E175" s="394" t="s">
+      <c r="D175" s="420"/>
+      <c r="E175" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F175" s="395"/>
-      <c r="G175" s="395"/>
-      <c r="H175" s="396"/>
+      <c r="F175" s="394"/>
+      <c r="G175" s="394"/>
+      <c r="H175" s="395"/>
       <c r="I175" s="32"/>
     </row>
     <row r="176" spans="1:9" ht="12" customHeight="1">
@@ -20577,16 +20577,16 @@
       <c r="B176" s="21">
         <v>133</v>
       </c>
-      <c r="C176" s="399"/>
-      <c r="D176" s="400"/>
+      <c r="C176" s="421"/>
+      <c r="D176" s="422"/>
       <c r="E176" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F176" s="401" t="s">
+      <c r="F176" s="396" t="s">
         <v>128</v>
       </c>
-      <c r="G176" s="402"/>
-      <c r="H176" s="403"/>
+      <c r="G176" s="397"/>
+      <c r="H176" s="398"/>
       <c r="I176" s="32"/>
     </row>
     <row r="177" spans="1:14" ht="12" customHeight="1">
@@ -20596,16 +20596,16 @@
       <c r="B177" s="21">
         <v>134</v>
       </c>
-      <c r="C177" s="399"/>
-      <c r="D177" s="400"/>
+      <c r="C177" s="421"/>
+      <c r="D177" s="422"/>
       <c r="E177" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F177" s="401" t="s">
+      <c r="F177" s="396" t="s">
         <v>154</v>
       </c>
-      <c r="G177" s="402"/>
-      <c r="H177" s="403"/>
+      <c r="G177" s="397"/>
+      <c r="H177" s="398"/>
       <c r="I177" s="32"/>
     </row>
     <row r="178" spans="1:14" ht="12" customHeight="1">
@@ -20624,11 +20624,11 @@
       <c r="E178" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F178" s="401" t="s">
+      <c r="F178" s="396" t="s">
         <v>155</v>
       </c>
-      <c r="G178" s="402"/>
-      <c r="H178" s="403"/>
+      <c r="G178" s="397"/>
+      <c r="H178" s="398"/>
       <c r="I178" s="32"/>
     </row>
     <row r="179" spans="1:14" hidden="1">
@@ -20641,14 +20641,14 @@
       <c r="B180" s="21">
         <v>137</v>
       </c>
-      <c r="C180" s="394" t="s">
+      <c r="C180" s="393" t="s">
         <v>156</v>
       </c>
-      <c r="D180" s="395"/>
-      <c r="E180" s="395"/>
-      <c r="F180" s="395"/>
-      <c r="G180" s="395"/>
-      <c r="H180" s="396"/>
+      <c r="D180" s="394"/>
+      <c r="E180" s="394"/>
+      <c r="F180" s="394"/>
+      <c r="G180" s="394"/>
+      <c r="H180" s="395"/>
       <c r="I180" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20661,14 +20661,14 @@
       <c r="B181" s="21">
         <v>138</v>
       </c>
-      <c r="C181" s="394" t="s">
+      <c r="C181" s="393" t="s">
         <v>21</v>
       </c>
-      <c r="D181" s="395"/>
-      <c r="E181" s="395"/>
-      <c r="F181" s="395"/>
-      <c r="G181" s="395"/>
-      <c r="H181" s="396"/>
+      <c r="D181" s="394"/>
+      <c r="E181" s="394"/>
+      <c r="F181" s="394"/>
+      <c r="G181" s="394"/>
+      <c r="H181" s="395"/>
       <c r="I181" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20681,16 +20681,16 @@
       <c r="B182" s="21">
         <v>139</v>
       </c>
-      <c r="C182" s="397" t="s">
+      <c r="C182" s="419" t="s">
         <v>157</v>
       </c>
-      <c r="D182" s="398"/>
-      <c r="E182" s="394" t="s">
+      <c r="D182" s="420"/>
+      <c r="E182" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F182" s="395"/>
-      <c r="G182" s="395"/>
-      <c r="H182" s="396"/>
+      <c r="F182" s="394"/>
+      <c r="G182" s="394"/>
+      <c r="H182" s="395"/>
       <c r="I182" s="32"/>
     </row>
     <row r="183" spans="1:14" ht="12" customHeight="1">
@@ -20700,16 +20700,16 @@
       <c r="B183" s="21">
         <v>140</v>
       </c>
-      <c r="C183" s="399"/>
-      <c r="D183" s="400"/>
+      <c r="C183" s="421"/>
+      <c r="D183" s="422"/>
       <c r="E183" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F183" s="401" t="s">
-        <v>44</v>
-      </c>
-      <c r="G183" s="402"/>
-      <c r="H183" s="403"/>
+      <c r="F183" s="396" t="s">
+        <v>44</v>
+      </c>
+      <c r="G183" s="397"/>
+      <c r="H183" s="398"/>
       <c r="I183" s="32"/>
     </row>
     <row r="184" spans="1:14" hidden="1">
@@ -20722,16 +20722,16 @@
       <c r="B185" s="21">
         <v>142</v>
       </c>
-      <c r="C185" s="397" t="s">
+      <c r="C185" s="419" t="s">
         <v>158</v>
       </c>
-      <c r="D185" s="398"/>
-      <c r="E185" s="394" t="s">
+      <c r="D185" s="420"/>
+      <c r="E185" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F185" s="395"/>
-      <c r="G185" s="395"/>
-      <c r="H185" s="396"/>
+      <c r="F185" s="394"/>
+      <c r="G185" s="394"/>
+      <c r="H185" s="395"/>
       <c r="I185" s="32"/>
     </row>
     <row r="186" spans="1:14" ht="12" customHeight="1">
@@ -20741,16 +20741,16 @@
       <c r="B186" s="21">
         <v>143</v>
       </c>
-      <c r="C186" s="399"/>
-      <c r="D186" s="400"/>
+      <c r="C186" s="421"/>
+      <c r="D186" s="422"/>
       <c r="E186" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F186" s="401" t="s">
+      <c r="F186" s="396" t="s">
         <v>159</v>
       </c>
-      <c r="G186" s="402"/>
-      <c r="H186" s="403"/>
+      <c r="G186" s="397"/>
+      <c r="H186" s="398"/>
       <c r="I186" s="32"/>
     </row>
     <row r="187" spans="1:14" ht="12" customHeight="1">
@@ -20760,16 +20760,16 @@
       <c r="B187" s="21">
         <v>144</v>
       </c>
-      <c r="C187" s="399"/>
-      <c r="D187" s="400"/>
+      <c r="C187" s="421"/>
+      <c r="D187" s="422"/>
       <c r="E187" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F187" s="401" t="s">
+      <c r="F187" s="396" t="s">
         <v>160</v>
       </c>
-      <c r="G187" s="402"/>
-      <c r="H187" s="403"/>
+      <c r="G187" s="397"/>
+      <c r="H187" s="398"/>
       <c r="I187" s="32"/>
     </row>
     <row r="188" spans="1:14" ht="12" customHeight="1">
@@ -20788,11 +20788,11 @@
       <c r="E188" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F188" s="391" t="s">
+      <c r="F188" s="416" t="s">
         <v>161</v>
       </c>
-      <c r="G188" s="392"/>
-      <c r="H188" s="393"/>
+      <c r="G188" s="417"/>
+      <c r="H188" s="418"/>
       <c r="I188" s="32"/>
       <c r="J188" s="10"/>
     </row>
@@ -20812,11 +20812,11 @@
       <c r="E189" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F189" s="391" t="s">
+      <c r="F189" s="416" t="s">
         <v>162</v>
       </c>
-      <c r="G189" s="392"/>
-      <c r="H189" s="393"/>
+      <c r="G189" s="417"/>
+      <c r="H189" s="418"/>
       <c r="I189" s="32"/>
       <c r="J189" s="10"/>
     </row>
@@ -20836,11 +20836,11 @@
       <c r="E190" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="F190" s="391" t="s">
+      <c r="F190" s="416" t="s">
         <v>163</v>
       </c>
-      <c r="G190" s="392"/>
-      <c r="H190" s="393"/>
+      <c r="G190" s="417"/>
+      <c r="H190" s="418"/>
       <c r="I190" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -20903,6 +20903,161 @@
     </row>
   </sheetData>
   <mergeCells count="169">
+    <mergeCell ref="F188:H188"/>
+    <mergeCell ref="F189:H189"/>
+    <mergeCell ref="F190:H190"/>
+    <mergeCell ref="C180:H180"/>
+    <mergeCell ref="C181:H181"/>
+    <mergeCell ref="C182:D183"/>
+    <mergeCell ref="E182:H182"/>
+    <mergeCell ref="F183:H183"/>
+    <mergeCell ref="C185:D187"/>
+    <mergeCell ref="E185:H185"/>
+    <mergeCell ref="F186:H186"/>
+    <mergeCell ref="F187:H187"/>
+    <mergeCell ref="C174:H174"/>
+    <mergeCell ref="C175:D177"/>
+    <mergeCell ref="E175:H175"/>
+    <mergeCell ref="F176:H176"/>
+    <mergeCell ref="F177:H177"/>
+    <mergeCell ref="F178:H178"/>
+    <mergeCell ref="F167:H167"/>
+    <mergeCell ref="F168:H168"/>
+    <mergeCell ref="C170:H170"/>
+    <mergeCell ref="C171:H171"/>
+    <mergeCell ref="C172:H172"/>
+    <mergeCell ref="C173:H173"/>
+    <mergeCell ref="C162:H162"/>
+    <mergeCell ref="C163:H163"/>
+    <mergeCell ref="C164:H164"/>
+    <mergeCell ref="C165:D166"/>
+    <mergeCell ref="E165:H165"/>
+    <mergeCell ref="F166:H166"/>
+    <mergeCell ref="F155:H155"/>
+    <mergeCell ref="F156:H156"/>
+    <mergeCell ref="F157:H157"/>
+    <mergeCell ref="F158:H158"/>
+    <mergeCell ref="C160:H160"/>
+    <mergeCell ref="C161:H161"/>
+    <mergeCell ref="F149:H149"/>
+    <mergeCell ref="F150:H150"/>
+    <mergeCell ref="F151:H151"/>
+    <mergeCell ref="C153:D154"/>
+    <mergeCell ref="E153:H153"/>
+    <mergeCell ref="F154:H154"/>
+    <mergeCell ref="C143:H143"/>
+    <mergeCell ref="E144:H144"/>
+    <mergeCell ref="F145:H145"/>
+    <mergeCell ref="F146:H146"/>
+    <mergeCell ref="F147:H147"/>
+    <mergeCell ref="F148:H148"/>
+    <mergeCell ref="F137:H137"/>
+    <mergeCell ref="F138:H138"/>
+    <mergeCell ref="C140:D142"/>
+    <mergeCell ref="E140:H140"/>
+    <mergeCell ref="E141:E142"/>
+    <mergeCell ref="F141:H141"/>
+    <mergeCell ref="F142:H142"/>
+    <mergeCell ref="C132:D135"/>
+    <mergeCell ref="E132:H132"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="F134:H134"/>
+    <mergeCell ref="F135:H135"/>
+    <mergeCell ref="F136:H136"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="C127:D128"/>
+    <mergeCell ref="E127:H127"/>
+    <mergeCell ref="F128:H128"/>
+    <mergeCell ref="C130:H130"/>
+    <mergeCell ref="C131:H131"/>
+    <mergeCell ref="C120:D121"/>
+    <mergeCell ref="E120:H120"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="F122:H122"/>
+    <mergeCell ref="F123:H123"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="C115:H115"/>
+    <mergeCell ref="C116:D117"/>
+    <mergeCell ref="E116:H116"/>
+    <mergeCell ref="F117:H117"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="F110:H110"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="E112:H112"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="C104:H104"/>
+    <mergeCell ref="C105:H105"/>
+    <mergeCell ref="C106:D107"/>
+    <mergeCell ref="E106:H106"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="F97:H97"/>
+    <mergeCell ref="F98:H98"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="F88:H88"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="F90:H90"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:E94"/>
+    <mergeCell ref="F93:H93"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="F82:F84"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="G83:G84"/>
+    <mergeCell ref="F85:H85"/>
+    <mergeCell ref="F86:H86"/>
+    <mergeCell ref="F87:H87"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="C78:D79"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="F80:H80"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="C60:H60"/>
+    <mergeCell ref="C61:D63"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="C54:D57"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="F58:H58"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="C50:D51"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="C44:H44"/>
+    <mergeCell ref="C45:D49"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:D35"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:D39"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:H27"/>
     <mergeCell ref="E28:H28"/>
@@ -20917,161 +21072,6 @@
     <mergeCell ref="B20:B22"/>
     <mergeCell ref="C20:H22"/>
     <mergeCell ref="I20:I22"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:D35"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C37:D39"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="C44:H44"/>
-    <mergeCell ref="C45:D49"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="C54:D57"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="F58:H58"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="C50:D51"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="G74:H74"/>
-    <mergeCell ref="C78:D79"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="F80:H80"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="C60:H60"/>
-    <mergeCell ref="C61:D63"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="F88:H88"/>
-    <mergeCell ref="F89:H89"/>
-    <mergeCell ref="F90:H90"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:E94"/>
-    <mergeCell ref="F93:H93"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="F82:F84"/>
-    <mergeCell ref="G82:H82"/>
-    <mergeCell ref="G83:G84"/>
-    <mergeCell ref="F85:H85"/>
-    <mergeCell ref="F86:H86"/>
-    <mergeCell ref="F87:H87"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="C104:H104"/>
-    <mergeCell ref="C105:H105"/>
-    <mergeCell ref="C106:D107"/>
-    <mergeCell ref="E106:H106"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="F97:H97"/>
-    <mergeCell ref="F98:H98"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="F100:H100"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="C115:H115"/>
-    <mergeCell ref="C116:D117"/>
-    <mergeCell ref="E116:H116"/>
-    <mergeCell ref="F117:H117"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="F110:H110"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="E112:H112"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="C126:H126"/>
-    <mergeCell ref="C127:D128"/>
-    <mergeCell ref="E127:H127"/>
-    <mergeCell ref="F128:H128"/>
-    <mergeCell ref="C130:H130"/>
-    <mergeCell ref="C131:H131"/>
-    <mergeCell ref="C120:D121"/>
-    <mergeCell ref="E120:H120"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="F122:H122"/>
-    <mergeCell ref="F123:H123"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="F137:H137"/>
-    <mergeCell ref="F138:H138"/>
-    <mergeCell ref="C140:D142"/>
-    <mergeCell ref="E140:H140"/>
-    <mergeCell ref="E141:E142"/>
-    <mergeCell ref="F141:H141"/>
-    <mergeCell ref="F142:H142"/>
-    <mergeCell ref="C132:D135"/>
-    <mergeCell ref="E132:H132"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="F134:H134"/>
-    <mergeCell ref="F135:H135"/>
-    <mergeCell ref="F136:H136"/>
-    <mergeCell ref="F149:H149"/>
-    <mergeCell ref="F150:H150"/>
-    <mergeCell ref="F151:H151"/>
-    <mergeCell ref="C153:D154"/>
-    <mergeCell ref="E153:H153"/>
-    <mergeCell ref="F154:H154"/>
-    <mergeCell ref="C143:H143"/>
-    <mergeCell ref="E144:H144"/>
-    <mergeCell ref="F145:H145"/>
-    <mergeCell ref="F146:H146"/>
-    <mergeCell ref="F147:H147"/>
-    <mergeCell ref="F148:H148"/>
-    <mergeCell ref="C162:H162"/>
-    <mergeCell ref="C163:H163"/>
-    <mergeCell ref="C164:H164"/>
-    <mergeCell ref="C165:D166"/>
-    <mergeCell ref="E165:H165"/>
-    <mergeCell ref="F166:H166"/>
-    <mergeCell ref="F155:H155"/>
-    <mergeCell ref="F156:H156"/>
-    <mergeCell ref="F157:H157"/>
-    <mergeCell ref="F158:H158"/>
-    <mergeCell ref="C160:H160"/>
-    <mergeCell ref="C161:H161"/>
-    <mergeCell ref="C174:H174"/>
-    <mergeCell ref="C175:D177"/>
-    <mergeCell ref="E175:H175"/>
-    <mergeCell ref="F176:H176"/>
-    <mergeCell ref="F177:H177"/>
-    <mergeCell ref="F178:H178"/>
-    <mergeCell ref="F167:H167"/>
-    <mergeCell ref="F168:H168"/>
-    <mergeCell ref="C170:H170"/>
-    <mergeCell ref="C171:H171"/>
-    <mergeCell ref="C172:H172"/>
-    <mergeCell ref="C173:H173"/>
-    <mergeCell ref="F188:H188"/>
-    <mergeCell ref="F189:H189"/>
-    <mergeCell ref="F190:H190"/>
-    <mergeCell ref="C180:H180"/>
-    <mergeCell ref="C181:H181"/>
-    <mergeCell ref="C182:D183"/>
-    <mergeCell ref="E182:H182"/>
-    <mergeCell ref="F183:H183"/>
-    <mergeCell ref="C185:D187"/>
-    <mergeCell ref="E185:H185"/>
-    <mergeCell ref="F186:H186"/>
-    <mergeCell ref="F187:H187"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
@@ -21378,7 +21378,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="207" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="C11" s="208" t="s">
         <v>274</v>
@@ -21970,7 +21970,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="183" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="C26" s="195" t="s">
         <v>272</v>
@@ -22003,7 +22003,7 @@
         <v>327</v>
       </c>
       <c r="L26" s="289" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="215" customFormat="1" ht="30">
@@ -22052,7 +22052,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="183" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C28" s="195" t="s">
         <v>272</v>
@@ -22085,7 +22085,7 @@
         <v>327</v>
       </c>
       <c r="L28" s="289" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="30">
@@ -22093,7 +22093,7 @@
         <v>6</v>
       </c>
       <c r="B29" s="183" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C29" s="195" t="s">
         <v>272</v>
@@ -22126,7 +22126,7 @@
         <v>327</v>
       </c>
       <c r="L29" s="289" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="30">
@@ -22134,7 +22134,7 @@
         <v>7</v>
       </c>
       <c r="B30" s="183" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C30" s="196" t="s">
         <v>271</v>
@@ -22167,7 +22167,7 @@
         <v>327</v>
       </c>
       <c r="L30" s="289" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="31" spans="1:12" s="215" customFormat="1" ht="30">
@@ -22334,7 +22334,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="183" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C35" s="193" t="s">
         <v>270</v>
@@ -22367,7 +22367,7 @@
         <v>327</v>
       </c>
       <c r="L35" s="289" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="30">
@@ -22476,7 +22476,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="211" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C39" s="195" t="s">
         <v>272</v>
@@ -22509,7 +22509,7 @@
         <v>327</v>
       </c>
       <c r="L39" s="292" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
     </row>
     <row r="40" spans="1:12" s="213" customFormat="1" ht="30">
@@ -32176,6 +32176,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="A26:F26"/>
@@ -32183,12 +32189,6 @@
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>

--- a/TAZA/_документы/Штатка Фонда и проектного офиса.xlsx
+++ b/TAZA/_документы/Штатка Фонда и проектного офиса.xlsx
@@ -551,7 +551,6 @@
     <definedName name="нотя" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"Лист15"}</definedName>
     <definedName name="нотя" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"Лист15"}</definedName>
     <definedName name="нотя" hidden="1">{#N/A,#N/A,FALSE,"Лист15"}</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">ФОТ!$A$1:$J$55</definedName>
     <definedName name="Область_печати_ИМ" localSheetId="2">#REF!</definedName>
     <definedName name="Область_печати_ИМ" localSheetId="5">#REF!</definedName>
     <definedName name="Область_печати_ИМ" localSheetId="3">#REF!</definedName>
@@ -2063,9 +2062,6 @@
     <t>Проекты и международные партнёры Проектного офиса для Центральной Азии, гранты, заявки и переписка на английском языке</t>
   </si>
   <si>
-    <t>Стратегия и портфель проектов, международные партнёры, Проектный офис для Центральной Азии; курирует проектное управление</t>
-  </si>
-  <si>
     <t>Руководители департаментов и групп, руководитель Проектного офиса для Центральной Азии, директор ПУ</t>
   </si>
   <si>
@@ -2104,22 +2100,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Заместитель Главного исполнительного директора Фонда по стратегии и проектам / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Кононец</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Главный специалист / PR-менеджер, пресс-секретарь / </t>
     </r>
     <r>
@@ -2314,21 +2294,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Руководитель / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Юнусов</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Эксперт-эколог / </t>
     </r>
     <r>
@@ -2494,6 +2459,15 @@
   </si>
   <si>
     <t>Зам.дир. / МЭПР (ЦГО, регионы)</t>
+  </si>
+  <si>
+    <t>Советник Главного исполнительного директора по стратегии и науке / Кононец</t>
+  </si>
+  <si>
+    <t>Стратегия и научное направление Фонда, аналитические и экспертные материалы, международные партнёры; поручения ГИД</t>
+  </si>
+  <si>
+    <t>Руководитель / вакансия</t>
   </si>
 </sst>
 </file>
@@ -5645,6 +5619,42 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5657,48 +5667,90 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="34" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5708,18 +5760,69 @@
     <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="33" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="34" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="35" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="32" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="39" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="3" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="10" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="2" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="17" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="32" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5729,139 +5832,19 @@
     <xf numFmtId="0" fontId="46" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="32" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="10" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="2" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="17" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="39" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="3" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="33" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="34" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="35" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="34" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5876,43 +5859,145 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="2" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="2" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="2" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="2" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5921,24 +6006,6 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5989,99 +6056,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6423,7 +6397,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6481,7 +6455,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6536,7 +6510,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10313,26 +10287,26 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="310" t="s">
+      <c r="A2" s="302" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="310"/>
+      <c r="B2" s="302"/>
       <c r="C2" s="132" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="315" t="s">
+      <c r="A3" s="303" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="316"/>
+      <c r="B3" s="304"/>
       <c r="C3" s="133"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="315" t="s">
+      <c r="A4" s="303" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="316" t="s">
+      <c r="B4" s="304" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="133"/>
@@ -10345,24 +10319,24 @@
       <c r="C5" s="133"/>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
-      <c r="A6" s="315" t="s">
+      <c r="A6" s="303" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="316"/>
+      <c r="B6" s="304"/>
       <c r="C6" s="134"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
-      <c r="A7" s="315" t="s">
+      <c r="A7" s="303" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="316"/>
+      <c r="B7" s="304"/>
       <c r="C7" s="135"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="306" t="s">
+      <c r="A8" s="305" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="307"/>
+      <c r="B8" s="306"/>
       <c r="C8" s="131">
         <f>SUM(C3:C7)</f>
         <v>0</v>
@@ -10372,17 +10346,17 @@
       <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="317" t="s">
+      <c r="A10" s="307" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="317"/>
-      <c r="C10" s="317"/>
+      <c r="B10" s="307"/>
+      <c r="C10" s="307"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="310" t="s">
+      <c r="A11" s="302" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="310"/>
+      <c r="B11" s="302"/>
       <c r="C11" s="132" t="s">
         <v>1</v>
       </c>
@@ -10409,10 +10383,10 @@
       <c r="C14" s="136"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="306" t="s">
+      <c r="A15" s="305" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="307"/>
+      <c r="B15" s="306"/>
       <c r="C15" s="130">
         <f>SUM(C12:C14)</f>
         <v>0</v>
@@ -10442,10 +10416,10 @@
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="310" t="s">
+      <c r="A20" s="302" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="310"/>
+      <c r="B20" s="302"/>
       <c r="C20" s="132" t="s">
         <v>1</v>
       </c>
@@ -10490,17 +10464,17 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="311" t="s">
+      <c r="A26" s="310" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="312"/>
-      <c r="C26" s="313"/>
+      <c r="B26" s="311"/>
+      <c r="C26" s="312"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="310" t="s">
+      <c r="A27" s="302" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="310"/>
+      <c r="B27" s="302"/>
       <c r="C27" s="138"/>
     </row>
     <row r="28" spans="1:4">
@@ -10517,17 +10491,17 @@
       <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="314" t="s">
+      <c r="A30" s="313" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="314"/>
+      <c r="B30" s="313"/>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="310" t="s">
+      <c r="A31" s="302" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="310"/>
+      <c r="B31" s="302"/>
       <c r="C31" s="132" t="s">
         <v>1</v>
       </c>
@@ -10564,8 +10538,8 @@
       <c r="D35" s="3"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="302"/>
-      <c r="B36" s="303"/>
+      <c r="A36" s="314"/>
+      <c r="B36" s="315"/>
       <c r="C36" s="144">
         <f>SUM(C32:C35)</f>
         <v>0</v>
@@ -10577,10 +10551,10 @@
       <c r="C37" s="8"/>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="304" t="s">
+      <c r="A38" s="316" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="305"/>
+      <c r="B38" s="317"/>
       <c r="C38" s="145">
         <f>C28-C36</f>
         <v>0</v>
@@ -10603,6 +10577,23 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
@@ -10615,23 +10606,6 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10899,11 +10873,11 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1"/>
-      <c r="B19" s="310" t="s">
+      <c r="B19" s="302" t="s">
         <v>259</v>
       </c>
-      <c r="C19" s="310"/>
-      <c r="D19" s="310"/>
+      <c r="C19" s="302"/>
+      <c r="D19" s="302"/>
       <c r="E19" s="162" t="e">
         <f>E15/E18</f>
         <v>#REF!</v>
@@ -10980,17 +10954,17 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="358" t="s">
+      <c r="B1" s="320" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="358"/>
-      <c r="D1" s="358"/>
-      <c r="E1" s="358"/>
-      <c r="F1" s="358"/>
-      <c r="G1" s="358"/>
-      <c r="H1" s="358"/>
-      <c r="I1" s="358"/>
-      <c r="J1" s="358"/>
+      <c r="C1" s="320"/>
+      <c r="D1" s="320"/>
+      <c r="E1" s="320"/>
+      <c r="F1" s="320"/>
+      <c r="G1" s="320"/>
+      <c r="H1" s="320"/>
+      <c r="I1" s="320"/>
+      <c r="J1" s="320"/>
       <c r="K1" s="85"/>
       <c r="O1" s="51"/>
     </row>
@@ -11028,17 +11002,17 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="359" t="s">
+      <c r="B3" s="321" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
+      <c r="C3" s="321"/>
+      <c r="D3" s="321"/>
+      <c r="E3" s="321"/>
+      <c r="F3" s="321"/>
+      <c r="G3" s="321"/>
+      <c r="H3" s="321"/>
+      <c r="I3" s="321"/>
+      <c r="J3" s="321"/>
       <c r="K3" s="88"/>
       <c r="O3" s="51"/>
     </row>
@@ -11046,17 +11020,17 @@
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="360" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="360"/>
-      <c r="D4" s="360"/>
-      <c r="E4" s="360"/>
-      <c r="F4" s="360"/>
-      <c r="G4" s="360"/>
-      <c r="H4" s="360"/>
-      <c r="I4" s="360"/>
-      <c r="J4" s="360"/>
+      <c r="B4" s="322" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="322"/>
+      <c r="D4" s="322"/>
+      <c r="E4" s="322"/>
+      <c r="F4" s="322"/>
+      <c r="G4" s="322"/>
+      <c r="H4" s="322"/>
+      <c r="I4" s="322"/>
+      <c r="J4" s="322"/>
       <c r="K4" s="89"/>
       <c r="O4" s="51"/>
     </row>
@@ -11064,17 +11038,17 @@
       <c r="A5" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="361" t="s">
+      <c r="B5" s="323" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="361"/>
-      <c r="D5" s="361"/>
-      <c r="E5" s="361"/>
-      <c r="F5" s="361"/>
-      <c r="G5" s="361"/>
-      <c r="H5" s="361"/>
-      <c r="I5" s="361"/>
-      <c r="J5" s="361"/>
+      <c r="C5" s="323"/>
+      <c r="D5" s="323"/>
+      <c r="E5" s="323"/>
+      <c r="F5" s="323"/>
+      <c r="G5" s="323"/>
+      <c r="H5" s="323"/>
+      <c r="I5" s="323"/>
+      <c r="J5" s="323"/>
       <c r="K5" s="90"/>
       <c r="O5" s="51"/>
     </row>
@@ -11082,17 +11056,17 @@
       <c r="A6" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="361" t="s">
+      <c r="B6" s="323" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="361"/>
-      <c r="D6" s="361"/>
-      <c r="E6" s="361"/>
-      <c r="F6" s="361"/>
-      <c r="G6" s="361"/>
-      <c r="H6" s="361"/>
-      <c r="I6" s="361"/>
-      <c r="J6" s="361"/>
+      <c r="C6" s="323"/>
+      <c r="D6" s="323"/>
+      <c r="E6" s="323"/>
+      <c r="F6" s="323"/>
+      <c r="G6" s="323"/>
+      <c r="H6" s="323"/>
+      <c r="I6" s="323"/>
+      <c r="J6" s="323"/>
       <c r="K6" s="90"/>
       <c r="O6" s="51"/>
     </row>
@@ -11100,15 +11074,15 @@
       <c r="A7" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="362" t="s">
+      <c r="B7" s="324" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="362"/>
-      <c r="D7" s="362"/>
-      <c r="E7" s="362"/>
-      <c r="F7" s="362"/>
-      <c r="G7" s="362"/>
-      <c r="H7" s="362"/>
+      <c r="C7" s="324"/>
+      <c r="D7" s="324"/>
+      <c r="E7" s="324"/>
+      <c r="F7" s="324"/>
+      <c r="G7" s="324"/>
+      <c r="H7" s="324"/>
       <c r="I7" s="91"/>
       <c r="J7" s="71" t="s">
         <v>50</v>
@@ -11134,51 +11108,51 @@
       <c r="A22" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="363" t="s">
+      <c r="B22" s="325" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="366" t="s">
+      <c r="C22" s="328" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="367"/>
-      <c r="E22" s="367"/>
-      <c r="F22" s="367"/>
-      <c r="G22" s="368"/>
+      <c r="D22" s="329"/>
+      <c r="E22" s="329"/>
+      <c r="F22" s="329"/>
+      <c r="G22" s="330"/>
       <c r="H22" s="93"/>
-      <c r="I22" s="367" t="s">
+      <c r="I22" s="329" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="368"/>
+      <c r="J22" s="330"/>
       <c r="K22" s="94"/>
     </row>
     <row r="23" spans="1:16" ht="12" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="364"/>
-      <c r="C23" s="369"/>
-      <c r="D23" s="370"/>
-      <c r="E23" s="370"/>
-      <c r="F23" s="370"/>
-      <c r="G23" s="371"/>
+      <c r="B23" s="326"/>
+      <c r="C23" s="331"/>
+      <c r="D23" s="332"/>
+      <c r="E23" s="332"/>
+      <c r="F23" s="332"/>
+      <c r="G23" s="333"/>
       <c r="H23" s="95"/>
-      <c r="I23" s="370"/>
-      <c r="J23" s="371"/>
+      <c r="I23" s="332"/>
+      <c r="J23" s="333"/>
       <c r="K23" s="94"/>
     </row>
     <row r="24" spans="1:16" ht="24" customHeight="1">
       <c r="A24" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="365"/>
-      <c r="C24" s="372"/>
-      <c r="D24" s="373"/>
-      <c r="E24" s="373"/>
-      <c r="F24" s="373"/>
-      <c r="G24" s="374"/>
+      <c r="B24" s="327"/>
+      <c r="C24" s="334"/>
+      <c r="D24" s="335"/>
+      <c r="E24" s="335"/>
+      <c r="F24" s="335"/>
+      <c r="G24" s="336"/>
       <c r="H24" s="96"/>
-      <c r="I24" s="373"/>
-      <c r="J24" s="374"/>
+      <c r="I24" s="335"/>
+      <c r="J24" s="336"/>
       <c r="K24" s="94"/>
     </row>
     <row r="25" spans="1:16" ht="15.75" hidden="1" customHeight="1"/>
@@ -11220,13 +11194,13 @@
       <c r="B29" s="58">
         <v>1</v>
       </c>
-      <c r="C29" s="324" t="s">
+      <c r="C29" s="337" t="s">
         <v>202</v>
       </c>
-      <c r="D29" s="325"/>
-      <c r="E29" s="325"/>
-      <c r="F29" s="325"/>
-      <c r="G29" s="326"/>
+      <c r="D29" s="338"/>
+      <c r="E29" s="338"/>
+      <c r="F29" s="338"/>
+      <c r="G29" s="339"/>
       <c r="H29" s="97"/>
       <c r="I29" s="97" t="e">
         <f>I35+I44+I46+I47+I50+#REF!+I68+I71+I72+I73+I77+I89+I97+I101+I106+I108+I116+I131+I142+I146+I147+I154+I32+I34+#REF!+#REF!+I151+#REF!+I98+I113+I155</f>
@@ -11243,15 +11217,15 @@
       <c r="B30" s="58">
         <v>2</v>
       </c>
-      <c r="C30" s="333" t="s">
+      <c r="C30" s="340" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="324" t="s">
+      <c r="D30" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="325"/>
-      <c r="F30" s="325"/>
-      <c r="G30" s="326"/>
+      <c r="E30" s="338"/>
+      <c r="F30" s="338"/>
+      <c r="G30" s="339"/>
       <c r="H30" s="97"/>
       <c r="I30" s="97"/>
       <c r="J30" s="99" t="e">
@@ -11271,15 +11245,15 @@
       <c r="B31" s="58">
         <v>3</v>
       </c>
-      <c r="C31" s="334"/>
+      <c r="C31" s="341"/>
       <c r="D31" s="343" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="320" t="s">
+      <c r="E31" s="346" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="321"/>
-      <c r="G31" s="322"/>
+      <c r="F31" s="347"/>
+      <c r="G31" s="348"/>
       <c r="H31" s="72"/>
       <c r="I31" s="72"/>
       <c r="J31" s="100"/>
@@ -11296,13 +11270,13 @@
       <c r="B32" s="58">
         <v>4</v>
       </c>
-      <c r="C32" s="334"/>
+      <c r="C32" s="341"/>
       <c r="D32" s="344"/>
-      <c r="E32" s="320" t="s">
+      <c r="E32" s="346" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="321"/>
-      <c r="G32" s="322"/>
+      <c r="F32" s="347"/>
+      <c r="G32" s="348"/>
       <c r="H32" s="72"/>
       <c r="I32" s="72"/>
       <c r="J32" s="81" t="e">
@@ -11322,13 +11296,13 @@
       <c r="B33" s="58">
         <v>5</v>
       </c>
-      <c r="C33" s="334"/>
+      <c r="C33" s="341"/>
       <c r="D33" s="344"/>
-      <c r="E33" s="353" t="s">
+      <c r="E33" s="349" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="354"/>
-      <c r="G33" s="355"/>
+      <c r="F33" s="350"/>
+      <c r="G33" s="351"/>
       <c r="H33" s="72"/>
       <c r="I33" s="72"/>
       <c r="J33" s="81"/>
@@ -11341,13 +11315,13 @@
       <c r="B34" s="58">
         <v>6</v>
       </c>
-      <c r="C34" s="350"/>
-      <c r="D34" s="352"/>
-      <c r="E34" s="330" t="s">
+      <c r="C34" s="342"/>
+      <c r="D34" s="345"/>
+      <c r="E34" s="353" t="s">
         <v>170</v>
       </c>
-      <c r="F34" s="330"/>
-      <c r="G34" s="330"/>
+      <c r="F34" s="353"/>
+      <c r="G34" s="353"/>
       <c r="H34" s="72"/>
       <c r="I34" s="72"/>
       <c r="J34" s="81" t="e">
@@ -11363,15 +11337,15 @@
       <c r="B35" s="58">
         <v>7</v>
       </c>
-      <c r="C35" s="333" t="s">
+      <c r="C35" s="340" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="324" t="s">
+      <c r="D35" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E35" s="356"/>
-      <c r="F35" s="356"/>
-      <c r="G35" s="357"/>
+      <c r="E35" s="354"/>
+      <c r="F35" s="354"/>
+      <c r="G35" s="355"/>
       <c r="H35" s="97"/>
       <c r="I35" s="101">
         <f>I36+I37</f>
@@ -11387,15 +11361,15 @@
       <c r="B36" s="58">
         <v>8</v>
       </c>
-      <c r="C36" s="334"/>
+      <c r="C36" s="341"/>
       <c r="D36" s="343" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="337" t="s">
+      <c r="E36" s="356" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="338"/>
-      <c r="G36" s="339"/>
+      <c r="F36" s="357"/>
+      <c r="G36" s="358"/>
       <c r="H36" s="72"/>
       <c r="I36" s="72"/>
       <c r="J36" s="81" t="e">
@@ -11412,13 +11386,13 @@
       <c r="B37" s="58">
         <v>9</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="351"/>
-      <c r="E37" s="337" t="s">
+      <c r="C37" s="342"/>
+      <c r="D37" s="352"/>
+      <c r="E37" s="356" t="s">
         <v>173</v>
       </c>
-      <c r="F37" s="338"/>
-      <c r="G37" s="339"/>
+      <c r="F37" s="357"/>
+      <c r="G37" s="358"/>
       <c r="H37" s="72"/>
       <c r="I37" s="72"/>
       <c r="J37" s="81" t="e">
@@ -11435,13 +11409,13 @@
       <c r="B38" s="58">
         <v>10</v>
       </c>
-      <c r="C38" s="324" t="s">
+      <c r="C38" s="337" t="s">
         <v>203</v>
       </c>
-      <c r="D38" s="325"/>
-      <c r="E38" s="325"/>
-      <c r="F38" s="325"/>
-      <c r="G38" s="326"/>
+      <c r="D38" s="338"/>
+      <c r="E38" s="338"/>
+      <c r="F38" s="338"/>
+      <c r="G38" s="339"/>
       <c r="H38" s="97"/>
       <c r="I38" s="97"/>
       <c r="J38" s="102"/>
@@ -11454,15 +11428,15 @@
       <c r="B39" s="58">
         <v>11</v>
       </c>
-      <c r="C39" s="333" t="s">
+      <c r="C39" s="340" t="s">
         <v>186</v>
       </c>
-      <c r="D39" s="324" t="s">
+      <c r="D39" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E39" s="325"/>
-      <c r="F39" s="325"/>
-      <c r="G39" s="326"/>
+      <c r="E39" s="338"/>
+      <c r="F39" s="338"/>
+      <c r="G39" s="339"/>
       <c r="H39" s="97"/>
       <c r="I39" s="97"/>
       <c r="J39" s="102"/>
@@ -11475,15 +11449,15 @@
       <c r="B40" s="58">
         <v>12</v>
       </c>
-      <c r="C40" s="334"/>
+      <c r="C40" s="341"/>
       <c r="D40" s="343" t="s">
         <v>55</v>
       </c>
-      <c r="E40" s="320" t="s">
+      <c r="E40" s="346" t="s">
         <v>128</v>
       </c>
-      <c r="F40" s="321"/>
-      <c r="G40" s="322"/>
+      <c r="F40" s="347"/>
+      <c r="G40" s="348"/>
       <c r="H40" s="72"/>
       <c r="I40" s="72"/>
       <c r="J40" s="81" t="e">
@@ -11499,13 +11473,13 @@
       <c r="B41" s="58">
         <v>13</v>
       </c>
-      <c r="C41" s="350"/>
-      <c r="D41" s="351"/>
-      <c r="E41" s="320" t="s">
+      <c r="C41" s="342"/>
+      <c r="D41" s="352"/>
+      <c r="E41" s="346" t="s">
         <v>129</v>
       </c>
-      <c r="F41" s="321"/>
-      <c r="G41" s="322"/>
+      <c r="F41" s="347"/>
+      <c r="G41" s="348"/>
       <c r="H41" s="72"/>
       <c r="I41" s="72"/>
       <c r="J41" s="81" t="e">
@@ -11521,15 +11495,15 @@
       <c r="B42" s="58">
         <v>14</v>
       </c>
-      <c r="C42" s="333" t="s">
+      <c r="C42" s="340" t="s">
         <v>204</v>
       </c>
-      <c r="D42" s="324" t="s">
+      <c r="D42" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E42" s="325"/>
-      <c r="F42" s="325"/>
-      <c r="G42" s="326"/>
+      <c r="E42" s="338"/>
+      <c r="F42" s="338"/>
+      <c r="G42" s="339"/>
       <c r="H42" s="97"/>
       <c r="I42" s="97"/>
       <c r="J42" s="102"/>
@@ -11542,15 +11516,15 @@
       <c r="B43" s="58">
         <v>15</v>
       </c>
-      <c r="C43" s="334"/>
+      <c r="C43" s="341"/>
       <c r="D43" s="343" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="320" t="s">
+      <c r="E43" s="346" t="s">
         <v>128</v>
       </c>
-      <c r="F43" s="321"/>
-      <c r="G43" s="322"/>
+      <c r="F43" s="347"/>
+      <c r="G43" s="348"/>
       <c r="H43" s="72"/>
       <c r="I43" s="72"/>
       <c r="J43" s="81" t="e">
@@ -11566,13 +11540,13 @@
       <c r="B44" s="58">
         <v>16</v>
       </c>
-      <c r="C44" s="350"/>
-      <c r="D44" s="351"/>
-      <c r="E44" s="320" t="s">
+      <c r="C44" s="342"/>
+      <c r="D44" s="352"/>
+      <c r="E44" s="346" t="s">
         <v>129</v>
       </c>
-      <c r="F44" s="321"/>
-      <c r="G44" s="322"/>
+      <c r="F44" s="347"/>
+      <c r="G44" s="348"/>
       <c r="H44" s="72"/>
       <c r="I44" s="72"/>
       <c r="J44" s="81" t="e">
@@ -11588,15 +11562,15 @@
       <c r="B45" s="58">
         <v>17</v>
       </c>
-      <c r="C45" s="333" t="s">
+      <c r="C45" s="340" t="s">
         <v>62</v>
       </c>
-      <c r="D45" s="324" t="s">
+      <c r="D45" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="325"/>
-      <c r="F45" s="325"/>
-      <c r="G45" s="326"/>
+      <c r="E45" s="338"/>
+      <c r="F45" s="338"/>
+      <c r="G45" s="339"/>
       <c r="H45" s="97"/>
       <c r="I45" s="97"/>
       <c r="J45" s="102"/>
@@ -11609,15 +11583,15 @@
       <c r="B46" s="58">
         <v>18</v>
       </c>
-      <c r="C46" s="334"/>
+      <c r="C46" s="341"/>
       <c r="D46" s="343" t="s">
         <v>55</v>
       </c>
-      <c r="E46" s="320" t="s">
+      <c r="E46" s="346" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="321"/>
-      <c r="G46" s="322"/>
+      <c r="F46" s="347"/>
+      <c r="G46" s="348"/>
       <c r="H46" s="72"/>
       <c r="I46" s="72"/>
       <c r="J46" s="81" t="e">
@@ -11633,13 +11607,13 @@
       <c r="B47" s="58">
         <v>19</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="320" t="s">
+      <c r="C47" s="342"/>
+      <c r="D47" s="352"/>
+      <c r="E47" s="346" t="s">
         <v>64</v>
       </c>
-      <c r="F47" s="321"/>
-      <c r="G47" s="322"/>
+      <c r="F47" s="347"/>
+      <c r="G47" s="348"/>
       <c r="H47" s="72"/>
       <c r="I47" s="72"/>
       <c r="J47" s="81" t="e">
@@ -11655,15 +11629,15 @@
       <c r="B48" s="58">
         <v>20</v>
       </c>
-      <c r="C48" s="333" t="s">
+      <c r="C48" s="340" t="s">
         <v>205</v>
       </c>
-      <c r="D48" s="324" t="s">
+      <c r="D48" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="325"/>
-      <c r="F48" s="325"/>
-      <c r="G48" s="326"/>
+      <c r="E48" s="338"/>
+      <c r="F48" s="338"/>
+      <c r="G48" s="339"/>
       <c r="H48" s="97"/>
       <c r="I48" s="97"/>
       <c r="J48" s="102"/>
@@ -11676,15 +11650,15 @@
       <c r="B49" s="58">
         <v>21</v>
       </c>
-      <c r="C49" s="334"/>
+      <c r="C49" s="341"/>
       <c r="D49" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="335" t="s">
-        <v>44</v>
-      </c>
-      <c r="F49" s="336"/>
-      <c r="G49" s="336"/>
+      <c r="E49" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" s="360"/>
+      <c r="G49" s="360"/>
       <c r="H49" s="104"/>
       <c r="I49" s="104"/>
       <c r="J49" s="81"/>
@@ -11703,11 +11677,11 @@
       <c r="D50" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E50" s="320" t="s">
+      <c r="E50" s="346" t="s">
         <v>206</v>
       </c>
-      <c r="F50" s="321"/>
-      <c r="G50" s="322"/>
+      <c r="F50" s="347"/>
+      <c r="G50" s="348"/>
       <c r="H50" s="72"/>
       <c r="I50" s="72"/>
       <c r="J50" s="81" t="e">
@@ -11730,11 +11704,11 @@
       <c r="D51" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E51" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="321"/>
-      <c r="G51" s="322"/>
+      <c r="E51" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="347"/>
+      <c r="G51" s="348"/>
       <c r="H51" s="72"/>
       <c r="I51" s="72"/>
       <c r="J51" s="81"/>
@@ -11748,15 +11722,15 @@
       <c r="B52" s="58">
         <v>24</v>
       </c>
-      <c r="C52" s="333" t="s">
+      <c r="C52" s="340" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="324" t="s">
+      <c r="D52" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E52" s="325"/>
-      <c r="F52" s="325"/>
-      <c r="G52" s="326"/>
+      <c r="E52" s="338"/>
+      <c r="F52" s="338"/>
+      <c r="G52" s="339"/>
       <c r="H52" s="97"/>
       <c r="I52" s="97"/>
       <c r="J52" s="102"/>
@@ -11769,15 +11743,15 @@
       <c r="B53" s="58">
         <v>25</v>
       </c>
-      <c r="C53" s="334"/>
+      <c r="C53" s="341"/>
       <c r="D53" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E53" s="320" t="s">
+      <c r="E53" s="346" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="321"/>
-      <c r="G53" s="322"/>
+      <c r="F53" s="347"/>
+      <c r="G53" s="348"/>
       <c r="H53" s="72"/>
       <c r="I53" s="72"/>
       <c r="J53" s="81"/>
@@ -11796,11 +11770,11 @@
       <c r="D54" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E54" s="320" t="s">
+      <c r="E54" s="346" t="s">
         <v>207</v>
       </c>
-      <c r="F54" s="321"/>
-      <c r="G54" s="322"/>
+      <c r="F54" s="347"/>
+      <c r="G54" s="348"/>
       <c r="H54" s="72"/>
       <c r="I54" s="72"/>
       <c r="J54" s="81" t="e">
@@ -11817,15 +11791,15 @@
       <c r="B55" s="58">
         <v>30</v>
       </c>
-      <c r="C55" s="333" t="s">
+      <c r="C55" s="340" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="324" t="s">
+      <c r="D55" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="325"/>
-      <c r="F55" s="325"/>
-      <c r="G55" s="326"/>
+      <c r="E55" s="338"/>
+      <c r="F55" s="338"/>
+      <c r="G55" s="339"/>
       <c r="H55" s="97"/>
       <c r="I55" s="97"/>
       <c r="J55" s="102"/>
@@ -11838,15 +11812,15 @@
       <c r="B56" s="58">
         <v>31</v>
       </c>
-      <c r="C56" s="334"/>
+      <c r="C56" s="341"/>
       <c r="D56" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="320" t="s">
+      <c r="E56" s="346" t="s">
         <v>146</v>
       </c>
-      <c r="F56" s="321"/>
-      <c r="G56" s="322"/>
+      <c r="F56" s="347"/>
+      <c r="G56" s="348"/>
       <c r="H56" s="72"/>
       <c r="I56" s="72"/>
       <c r="J56" s="81"/>
@@ -11859,15 +11833,15 @@
       <c r="B57" s="58">
         <v>32</v>
       </c>
-      <c r="C57" s="334"/>
+      <c r="C57" s="341"/>
       <c r="D57" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="320" t="s">
+      <c r="E57" s="346" t="s">
         <v>147</v>
       </c>
-      <c r="F57" s="321"/>
-      <c r="G57" s="322"/>
+      <c r="F57" s="347"/>
+      <c r="G57" s="348"/>
       <c r="H57" s="72"/>
       <c r="I57" s="72"/>
       <c r="J57" s="81"/>
@@ -11886,11 +11860,11 @@
       <c r="D58" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="320" t="s">
+      <c r="E58" s="346" t="s">
         <v>148</v>
       </c>
-      <c r="F58" s="321"/>
-      <c r="G58" s="322"/>
+      <c r="F58" s="347"/>
+      <c r="G58" s="348"/>
       <c r="H58" s="72"/>
       <c r="I58" s="72"/>
       <c r="J58" s="81"/>
@@ -11909,11 +11883,11 @@
       <c r="D59" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E59" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F59" s="321"/>
-      <c r="G59" s="322"/>
+      <c r="E59" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F59" s="347"/>
+      <c r="G59" s="348"/>
       <c r="H59" s="72"/>
       <c r="I59" s="72"/>
       <c r="J59" s="81"/>
@@ -11927,15 +11901,15 @@
       <c r="B60" s="58">
         <v>35</v>
       </c>
-      <c r="C60" s="333" t="s">
+      <c r="C60" s="340" t="s">
         <v>190</v>
       </c>
-      <c r="D60" s="324" t="s">
+      <c r="D60" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E60" s="325"/>
-      <c r="F60" s="325"/>
-      <c r="G60" s="326"/>
+      <c r="E60" s="338"/>
+      <c r="F60" s="338"/>
+      <c r="G60" s="339"/>
       <c r="H60" s="97"/>
       <c r="I60" s="97"/>
       <c r="J60" s="102"/>
@@ -11948,15 +11922,15 @@
       <c r="B61" s="58">
         <v>36</v>
       </c>
-      <c r="C61" s="334"/>
+      <c r="C61" s="341"/>
       <c r="D61" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E61" s="320" t="s">
+      <c r="E61" s="346" t="s">
         <v>128</v>
       </c>
-      <c r="F61" s="321"/>
-      <c r="G61" s="322"/>
+      <c r="F61" s="347"/>
+      <c r="G61" s="348"/>
       <c r="H61" s="72"/>
       <c r="I61" s="72"/>
       <c r="J61" s="81"/>
@@ -11969,15 +11943,15 @@
       <c r="B62" s="58">
         <v>37</v>
       </c>
-      <c r="C62" s="334"/>
+      <c r="C62" s="341"/>
       <c r="D62" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E62" s="320" t="s">
+      <c r="E62" s="346" t="s">
         <v>154</v>
       </c>
-      <c r="F62" s="321"/>
-      <c r="G62" s="322"/>
+      <c r="F62" s="347"/>
+      <c r="G62" s="348"/>
       <c r="H62" s="72"/>
       <c r="I62" s="72"/>
       <c r="J62" s="81"/>
@@ -11996,11 +11970,11 @@
       <c r="D63" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E63" s="320" t="s">
+      <c r="E63" s="346" t="s">
         <v>208</v>
       </c>
-      <c r="F63" s="321"/>
-      <c r="G63" s="322"/>
+      <c r="F63" s="347"/>
+      <c r="G63" s="348"/>
       <c r="H63" s="72"/>
       <c r="I63" s="72"/>
       <c r="J63" s="81"/>
@@ -12019,11 +11993,11 @@
       <c r="D64" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E64" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F64" s="321"/>
-      <c r="G64" s="322"/>
+      <c r="E64" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F64" s="347"/>
+      <c r="G64" s="348"/>
       <c r="H64" s="72"/>
       <c r="I64" s="72"/>
       <c r="J64" s="81"/>
@@ -12037,15 +12011,15 @@
       <c r="B65" s="58">
         <v>40</v>
       </c>
-      <c r="C65" s="333" t="s">
+      <c r="C65" s="340" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="324" t="s">
+      <c r="D65" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E65" s="325"/>
-      <c r="F65" s="325"/>
-      <c r="G65" s="326"/>
+      <c r="E65" s="338"/>
+      <c r="F65" s="338"/>
+      <c r="G65" s="339"/>
       <c r="H65" s="97"/>
       <c r="I65" s="97"/>
       <c r="J65" s="102"/>
@@ -12058,17 +12032,17 @@
       <c r="B66" s="58">
         <v>41</v>
       </c>
-      <c r="C66" s="334"/>
+      <c r="C66" s="341"/>
       <c r="D66" s="66" t="s">
         <v>55</v>
       </c>
       <c r="E66" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="F66" s="324" t="s">
+      <c r="F66" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="G66" s="326"/>
+      <c r="G66" s="339"/>
       <c r="H66" s="97"/>
       <c r="I66" s="97"/>
       <c r="J66" s="102"/>
@@ -12081,7 +12055,7 @@
       <c r="B67" s="58">
         <v>42</v>
       </c>
-      <c r="C67" s="334"/>
+      <c r="C67" s="341"/>
       <c r="D67" s="67" t="s">
         <v>44</v>
       </c>
@@ -12174,10 +12148,10 @@
       <c r="E70" s="103" t="s">
         <v>210</v>
       </c>
-      <c r="F70" s="324" t="s">
+      <c r="F70" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="G70" s="326"/>
+      <c r="G70" s="339"/>
       <c r="H70" s="97"/>
       <c r="I70" s="97"/>
       <c r="J70" s="102"/>
@@ -12346,10 +12320,10 @@
       <c r="E76" s="103" t="s">
         <v>214</v>
       </c>
-      <c r="F76" s="324" t="s">
+      <c r="F76" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="G76" s="326"/>
+      <c r="G76" s="339"/>
       <c r="H76" s="97"/>
       <c r="I76" s="97"/>
       <c r="J76" s="102"/>
@@ -12451,13 +12425,13 @@
       <c r="D80" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E80" s="345" t="s">
+      <c r="E80" s="361" t="s">
         <v>216</v>
       </c>
-      <c r="F80" s="324" t="s">
+      <c r="F80" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="G80" s="326"/>
+      <c r="G80" s="339"/>
       <c r="H80" s="97"/>
       <c r="I80" s="97"/>
       <c r="J80" s="102"/>
@@ -12477,15 +12451,15 @@
       <c r="D81" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E81" s="346"/>
+      <c r="E81" s="362"/>
       <c r="F81" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="G81" s="347" t="s">
+      <c r="G81" s="363" t="s">
         <v>136</v>
       </c>
-      <c r="H81" s="348"/>
-      <c r="I81" s="349"/>
+      <c r="H81" s="364"/>
+      <c r="I81" s="365"/>
       <c r="J81" s="81" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -12564,13 +12538,13 @@
       <c r="D84" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E84" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F84" s="324" t="s">
+      <c r="E84" s="361" t="s">
+        <v>44</v>
+      </c>
+      <c r="F84" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="G84" s="326"/>
+      <c r="G84" s="339"/>
       <c r="H84" s="97"/>
       <c r="I84" s="97"/>
       <c r="J84" s="102"/>
@@ -12590,7 +12564,7 @@
       <c r="D85" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E85" s="346"/>
+      <c r="E85" s="362"/>
       <c r="F85" s="66" t="s">
         <v>55</v>
       </c>
@@ -12639,15 +12613,15 @@
       <c r="B87" s="58">
         <v>62</v>
       </c>
-      <c r="C87" s="333" t="s">
+      <c r="C87" s="340" t="s">
         <v>144</v>
       </c>
-      <c r="D87" s="324" t="s">
+      <c r="D87" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E87" s="325"/>
-      <c r="F87" s="325"/>
-      <c r="G87" s="326"/>
+      <c r="E87" s="338"/>
+      <c r="F87" s="338"/>
+      <c r="G87" s="339"/>
       <c r="H87" s="97"/>
       <c r="I87" s="110"/>
       <c r="J87" s="102"/>
@@ -12660,15 +12634,15 @@
       <c r="B88" s="58">
         <v>63</v>
       </c>
-      <c r="C88" s="334"/>
+      <c r="C88" s="341"/>
       <c r="D88" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E88" s="335" t="s">
-        <v>44</v>
-      </c>
-      <c r="F88" s="336"/>
-      <c r="G88" s="336"/>
+      <c r="E88" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="F88" s="360"/>
+      <c r="G88" s="360"/>
       <c r="H88" s="104"/>
       <c r="I88" s="104"/>
       <c r="J88" s="81" t="e">
@@ -12690,11 +12664,11 @@
       <c r="D89" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F89" s="321"/>
-      <c r="G89" s="322"/>
+      <c r="E89" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F89" s="347"/>
+      <c r="G89" s="348"/>
       <c r="H89" s="72"/>
       <c r="I89" s="109"/>
       <c r="J89" s="81"/>
@@ -12714,11 +12688,11 @@
       <c r="D90" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E90" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F90" s="321"/>
-      <c r="G90" s="322"/>
+      <c r="E90" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F90" s="347"/>
+      <c r="G90" s="348"/>
       <c r="H90" s="72"/>
       <c r="I90" s="109"/>
       <c r="J90" s="81"/>
@@ -12732,15 +12706,15 @@
       <c r="B91" s="58">
         <v>66</v>
       </c>
-      <c r="C91" s="333" t="s">
+      <c r="C91" s="340" t="s">
         <v>189</v>
       </c>
-      <c r="D91" s="324" t="s">
+      <c r="D91" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="325"/>
-      <c r="F91" s="325"/>
-      <c r="G91" s="326"/>
+      <c r="E91" s="338"/>
+      <c r="F91" s="338"/>
+      <c r="G91" s="339"/>
       <c r="H91" s="97"/>
       <c r="I91" s="110"/>
       <c r="J91" s="102"/>
@@ -12753,15 +12727,15 @@
       <c r="B92" s="58">
         <v>67</v>
       </c>
-      <c r="C92" s="334"/>
+      <c r="C92" s="341"/>
       <c r="D92" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E92" s="335" t="s">
-        <v>44</v>
-      </c>
-      <c r="F92" s="336"/>
-      <c r="G92" s="336"/>
+      <c r="E92" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="F92" s="360"/>
+      <c r="G92" s="360"/>
       <c r="H92" s="104"/>
       <c r="I92" s="104"/>
       <c r="J92" s="81"/>
@@ -12780,11 +12754,11 @@
       <c r="D93" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F93" s="321"/>
-      <c r="G93" s="322"/>
+      <c r="E93" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F93" s="347"/>
+      <c r="G93" s="348"/>
       <c r="H93" s="72"/>
       <c r="I93" s="109"/>
       <c r="J93" s="81"/>
@@ -12804,11 +12778,11 @@
       <c r="D94" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E94" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F94" s="321"/>
-      <c r="G94" s="322"/>
+      <c r="E94" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F94" s="347"/>
+      <c r="G94" s="348"/>
       <c r="H94" s="72"/>
       <c r="I94" s="109"/>
       <c r="J94" s="81"/>
@@ -12822,15 +12796,15 @@
       <c r="B95" s="58">
         <v>70</v>
       </c>
-      <c r="C95" s="333" t="s">
+      <c r="C95" s="340" t="s">
         <v>137</v>
       </c>
-      <c r="D95" s="324" t="s">
+      <c r="D95" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E95" s="325"/>
-      <c r="F95" s="325"/>
-      <c r="G95" s="326"/>
+      <c r="E95" s="338"/>
+      <c r="F95" s="338"/>
+      <c r="G95" s="339"/>
       <c r="H95" s="97"/>
       <c r="I95" s="110"/>
       <c r="J95" s="102"/>
@@ -12843,15 +12817,15 @@
       <c r="B96" s="58">
         <v>71</v>
       </c>
-      <c r="C96" s="334"/>
+      <c r="C96" s="341"/>
       <c r="D96" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E96" s="335" t="s">
-        <v>44</v>
-      </c>
-      <c r="F96" s="336"/>
-      <c r="G96" s="336"/>
+      <c r="E96" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="F96" s="360"/>
+      <c r="G96" s="360"/>
       <c r="H96" s="104"/>
       <c r="I96" s="104"/>
       <c r="J96" s="81"/>
@@ -12870,11 +12844,11 @@
       <c r="D97" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E97" s="320" t="s">
+      <c r="E97" s="346" t="s">
         <v>217</v>
       </c>
-      <c r="F97" s="321"/>
-      <c r="G97" s="322"/>
+      <c r="F97" s="347"/>
+      <c r="G97" s="348"/>
       <c r="H97" s="72"/>
       <c r="I97" s="109"/>
       <c r="J97" s="81" t="e">
@@ -12889,11 +12863,11 @@
       <c r="B98" s="58"/>
       <c r="C98" s="77"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="320" t="s">
+      <c r="E98" s="346" t="s">
         <v>218</v>
       </c>
-      <c r="F98" s="321"/>
-      <c r="G98" s="322"/>
+      <c r="F98" s="347"/>
+      <c r="G98" s="348"/>
       <c r="H98" s="72"/>
       <c r="I98" s="109"/>
       <c r="J98" s="81"/>
@@ -12905,9 +12879,9 @@
       <c r="B99" s="58"/>
       <c r="C99" s="77"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="320"/>
-      <c r="F99" s="321"/>
-      <c r="G99" s="322"/>
+      <c r="E99" s="346"/>
+      <c r="F99" s="347"/>
+      <c r="G99" s="348"/>
       <c r="H99" s="72"/>
       <c r="I99" s="109"/>
       <c r="J99" s="81"/>
@@ -12927,11 +12901,11 @@
       <c r="D100" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E100" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F100" s="321"/>
-      <c r="G100" s="322"/>
+      <c r="E100" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F100" s="347"/>
+      <c r="G100" s="348"/>
       <c r="H100" s="72"/>
       <c r="I100" s="109"/>
       <c r="J100" s="81"/>
@@ -12945,15 +12919,15 @@
       <c r="B101" s="58">
         <v>75</v>
       </c>
-      <c r="C101" s="333" t="s">
+      <c r="C101" s="340" t="s">
         <v>17</v>
       </c>
-      <c r="D101" s="324" t="s">
+      <c r="D101" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E101" s="325"/>
-      <c r="F101" s="325"/>
-      <c r="G101" s="326"/>
+      <c r="E101" s="338"/>
+      <c r="F101" s="338"/>
+      <c r="G101" s="339"/>
       <c r="H101" s="97"/>
       <c r="I101" s="111">
         <f>I102+I103+I104</f>
@@ -12969,15 +12943,15 @@
       <c r="B102" s="58">
         <v>76</v>
       </c>
-      <c r="C102" s="334"/>
+      <c r="C102" s="341"/>
       <c r="D102" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E102" s="337" t="s">
+      <c r="E102" s="356" t="s">
         <v>219</v>
       </c>
-      <c r="F102" s="338"/>
-      <c r="G102" s="339"/>
+      <c r="F102" s="357"/>
+      <c r="G102" s="358"/>
       <c r="H102" s="72"/>
       <c r="I102" s="109"/>
       <c r="J102" s="81">
@@ -12993,15 +12967,15 @@
       <c r="B103" s="58">
         <v>77</v>
       </c>
-      <c r="C103" s="334"/>
+      <c r="C103" s="341"/>
       <c r="D103" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E103" s="337" t="s">
+      <c r="E103" s="356" t="s">
         <v>220</v>
       </c>
-      <c r="F103" s="338"/>
-      <c r="G103" s="339"/>
+      <c r="F103" s="357"/>
+      <c r="G103" s="358"/>
       <c r="H103" s="72"/>
       <c r="I103" s="72"/>
       <c r="J103" s="81">
@@ -13023,11 +12997,11 @@
       <c r="D104" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E104" s="337" t="s">
+      <c r="E104" s="356" t="s">
         <v>221</v>
       </c>
-      <c r="F104" s="338"/>
-      <c r="G104" s="339"/>
+      <c r="F104" s="357"/>
+      <c r="G104" s="358"/>
       <c r="H104" s="72"/>
       <c r="I104" s="72"/>
       <c r="J104" s="81">
@@ -13043,13 +13017,13 @@
       <c r="B105" s="58">
         <v>83</v>
       </c>
-      <c r="C105" s="324" t="s">
+      <c r="C105" s="337" t="s">
         <v>7</v>
       </c>
-      <c r="D105" s="325"/>
-      <c r="E105" s="325"/>
-      <c r="F105" s="325"/>
-      <c r="G105" s="326"/>
+      <c r="D105" s="338"/>
+      <c r="E105" s="338"/>
+      <c r="F105" s="338"/>
+      <c r="G105" s="339"/>
       <c r="H105" s="97"/>
       <c r="I105" s="97"/>
       <c r="J105" s="102" t="e">
@@ -13065,13 +13039,13 @@
       <c r="B106" s="58">
         <v>84</v>
       </c>
-      <c r="C106" s="324" t="s">
+      <c r="C106" s="337" t="s">
         <v>222</v>
       </c>
-      <c r="D106" s="325"/>
-      <c r="E106" s="325"/>
-      <c r="F106" s="325"/>
-      <c r="G106" s="326"/>
+      <c r="D106" s="338"/>
+      <c r="E106" s="338"/>
+      <c r="F106" s="338"/>
+      <c r="G106" s="339"/>
       <c r="H106" s="97"/>
       <c r="I106" s="101"/>
       <c r="J106" s="102" t="e">
@@ -13087,15 +13061,15 @@
       <c r="B107" s="58">
         <v>85</v>
       </c>
-      <c r="C107" s="333" t="s">
+      <c r="C107" s="340" t="s">
         <v>223</v>
       </c>
-      <c r="D107" s="324" t="s">
+      <c r="D107" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E107" s="325"/>
-      <c r="F107" s="325"/>
-      <c r="G107" s="326"/>
+      <c r="E107" s="338"/>
+      <c r="F107" s="338"/>
+      <c r="G107" s="339"/>
       <c r="H107" s="97"/>
       <c r="I107" s="97"/>
       <c r="J107" s="102"/>
@@ -13108,15 +13082,15 @@
       <c r="B108" s="58">
         <v>86</v>
       </c>
-      <c r="C108" s="334"/>
+      <c r="C108" s="341"/>
       <c r="D108" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E108" s="337" t="s">
+      <c r="E108" s="356" t="s">
         <v>224</v>
       </c>
-      <c r="F108" s="338"/>
-      <c r="G108" s="339"/>
+      <c r="F108" s="357"/>
+      <c r="G108" s="358"/>
       <c r="H108" s="72"/>
       <c r="I108" s="63"/>
       <c r="J108" s="81" t="e">
@@ -13138,11 +13112,11 @@
       <c r="D109" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E109" s="320" t="s">
+      <c r="E109" s="346" t="s">
         <v>225</v>
       </c>
-      <c r="F109" s="321"/>
-      <c r="G109" s="322"/>
+      <c r="F109" s="347"/>
+      <c r="G109" s="348"/>
       <c r="H109" s="72"/>
       <c r="I109" s="63"/>
       <c r="J109" s="81"/>
@@ -13162,11 +13136,11 @@
       <c r="D110" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E110" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F110" s="321"/>
-      <c r="G110" s="322"/>
+      <c r="E110" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F110" s="347"/>
+      <c r="G110" s="348"/>
       <c r="H110" s="72"/>
       <c r="I110" s="72"/>
       <c r="J110" s="81"/>
@@ -13180,15 +13154,15 @@
       <c r="B111" s="58">
         <v>89</v>
       </c>
-      <c r="C111" s="333" t="s">
+      <c r="C111" s="340" t="s">
         <v>192</v>
       </c>
-      <c r="D111" s="324" t="s">
+      <c r="D111" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E111" s="325"/>
-      <c r="F111" s="325"/>
-      <c r="G111" s="326"/>
+      <c r="E111" s="338"/>
+      <c r="F111" s="338"/>
+      <c r="G111" s="339"/>
       <c r="H111" s="97"/>
       <c r="I111" s="97"/>
       <c r="J111" s="102"/>
@@ -13201,15 +13175,15 @@
       <c r="B112" s="58">
         <v>90</v>
       </c>
-      <c r="C112" s="334"/>
+      <c r="C112" s="341"/>
       <c r="D112" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E112" s="337" t="s">
+      <c r="E112" s="356" t="s">
         <v>226</v>
       </c>
-      <c r="F112" s="338"/>
-      <c r="G112" s="339"/>
+      <c r="F112" s="357"/>
+      <c r="G112" s="358"/>
       <c r="H112" s="72"/>
       <c r="I112" s="72"/>
       <c r="J112" s="81"/>
@@ -13228,11 +13202,11 @@
       <c r="D113" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E113" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F113" s="321"/>
-      <c r="G113" s="322"/>
+      <c r="E113" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F113" s="347"/>
+      <c r="G113" s="348"/>
       <c r="H113" s="72"/>
       <c r="I113" s="72"/>
       <c r="J113" s="81"/>
@@ -13245,15 +13219,15 @@
       <c r="B114" s="58">
         <v>92</v>
       </c>
-      <c r="C114" s="333" t="s">
+      <c r="C114" s="340" t="s">
         <v>191</v>
       </c>
-      <c r="D114" s="324" t="s">
+      <c r="D114" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E114" s="325"/>
-      <c r="F114" s="325"/>
-      <c r="G114" s="326"/>
+      <c r="E114" s="338"/>
+      <c r="F114" s="338"/>
+      <c r="G114" s="339"/>
       <c r="H114" s="97"/>
       <c r="I114" s="97"/>
       <c r="J114" s="102"/>
@@ -13266,15 +13240,15 @@
       <c r="B115" s="58">
         <v>93</v>
       </c>
-      <c r="C115" s="334"/>
+      <c r="C115" s="341"/>
       <c r="D115" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E115" s="335" t="s">
-        <v>44</v>
-      </c>
-      <c r="F115" s="336"/>
-      <c r="G115" s="336"/>
+      <c r="E115" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="F115" s="360"/>
+      <c r="G115" s="360"/>
       <c r="H115" s="104"/>
       <c r="I115" s="104"/>
       <c r="J115" s="112"/>
@@ -13293,11 +13267,11 @@
       <c r="D116" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E116" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F116" s="321"/>
-      <c r="G116" s="322"/>
+      <c r="E116" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F116" s="347"/>
+      <c r="G116" s="348"/>
       <c r="H116" s="72"/>
       <c r="I116" s="63"/>
       <c r="J116" s="81"/>
@@ -13317,11 +13291,11 @@
       <c r="D117" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E117" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F117" s="321"/>
-      <c r="G117" s="322"/>
+      <c r="E117" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F117" s="347"/>
+      <c r="G117" s="348"/>
       <c r="H117" s="72"/>
       <c r="I117" s="72"/>
       <c r="J117" s="81"/>
@@ -13335,15 +13309,15 @@
       <c r="B118" s="58">
         <v>96</v>
       </c>
-      <c r="C118" s="333" t="s">
+      <c r="C118" s="340" t="s">
         <v>149</v>
       </c>
-      <c r="D118" s="324" t="s">
+      <c r="D118" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E118" s="325"/>
-      <c r="F118" s="325"/>
-      <c r="G118" s="326"/>
+      <c r="E118" s="338"/>
+      <c r="F118" s="338"/>
+      <c r="G118" s="339"/>
       <c r="H118" s="97"/>
       <c r="I118" s="97"/>
       <c r="J118" s="102"/>
@@ -13356,15 +13330,15 @@
       <c r="B119" s="58">
         <v>97</v>
       </c>
-      <c r="C119" s="334"/>
+      <c r="C119" s="341"/>
       <c r="D119" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E119" s="337" t="s">
+      <c r="E119" s="356" t="s">
         <v>227</v>
       </c>
-      <c r="F119" s="338"/>
-      <c r="G119" s="339"/>
+      <c r="F119" s="357"/>
+      <c r="G119" s="358"/>
       <c r="H119" s="72"/>
       <c r="I119" s="72"/>
       <c r="J119" s="81"/>
@@ -13383,11 +13357,11 @@
       <c r="D120" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E120" s="337" t="s">
+      <c r="E120" s="356" t="s">
         <v>228</v>
       </c>
-      <c r="F120" s="338"/>
-      <c r="G120" s="339"/>
+      <c r="F120" s="357"/>
+      <c r="G120" s="358"/>
       <c r="H120" s="72"/>
       <c r="I120" s="72"/>
       <c r="J120" s="81"/>
@@ -13406,11 +13380,11 @@
       <c r="D121" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E121" s="337" t="s">
+      <c r="E121" s="356" t="s">
         <v>229</v>
       </c>
-      <c r="F121" s="338"/>
-      <c r="G121" s="339"/>
+      <c r="F121" s="357"/>
+      <c r="G121" s="358"/>
       <c r="H121" s="72"/>
       <c r="I121" s="72"/>
       <c r="J121" s="81"/>
@@ -13429,11 +13403,11 @@
       <c r="D122" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E122" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F122" s="321"/>
-      <c r="G122" s="322"/>
+      <c r="E122" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F122" s="347"/>
+      <c r="G122" s="348"/>
       <c r="H122" s="72"/>
       <c r="I122" s="72"/>
       <c r="J122" s="81"/>
@@ -13447,15 +13421,15 @@
       <c r="B123" s="58">
         <v>101</v>
       </c>
-      <c r="C123" s="333" t="s">
+      <c r="C123" s="340" t="s">
         <v>230</v>
       </c>
-      <c r="D123" s="324" t="s">
+      <c r="D123" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E123" s="325"/>
-      <c r="F123" s="325"/>
-      <c r="G123" s="326"/>
+      <c r="E123" s="338"/>
+      <c r="F123" s="338"/>
+      <c r="G123" s="339"/>
       <c r="H123" s="97"/>
       <c r="I123" s="97"/>
       <c r="J123" s="102"/>
@@ -13468,17 +13442,17 @@
       <c r="B124" s="58">
         <v>102</v>
       </c>
-      <c r="C124" s="334"/>
+      <c r="C124" s="341"/>
       <c r="D124" s="66" t="s">
         <v>55</v>
       </c>
       <c r="E124" s="343" t="s">
         <v>231</v>
       </c>
-      <c r="F124" s="324" t="s">
+      <c r="F124" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="G124" s="326"/>
+      <c r="G124" s="339"/>
       <c r="H124" s="97"/>
       <c r="I124" s="97"/>
       <c r="J124" s="102"/>
@@ -13491,7 +13465,7 @@
       <c r="B125" s="58">
         <v>103</v>
       </c>
-      <c r="C125" s="334"/>
+      <c r="C125" s="341"/>
       <c r="D125" s="67" t="s">
         <v>44</v>
       </c>
@@ -13514,7 +13488,7 @@
       <c r="B126" s="58">
         <v>104</v>
       </c>
-      <c r="C126" s="334"/>
+      <c r="C126" s="341"/>
       <c r="D126" s="67" t="s">
         <v>44</v>
       </c>
@@ -13600,11 +13574,11 @@
       <c r="D129" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E129" s="337" t="s">
+      <c r="E129" s="356" t="s">
         <v>234</v>
       </c>
-      <c r="F129" s="338"/>
-      <c r="G129" s="339"/>
+      <c r="F129" s="357"/>
+      <c r="G129" s="358"/>
       <c r="H129" s="72"/>
       <c r="I129" s="72"/>
       <c r="J129" s="81"/>
@@ -13623,11 +13597,11 @@
       <c r="D130" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E130" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F130" s="321"/>
-      <c r="G130" s="322"/>
+      <c r="E130" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F130" s="347"/>
+      <c r="G130" s="348"/>
       <c r="H130" s="72"/>
       <c r="I130" s="72"/>
       <c r="J130" s="81"/>
@@ -13641,15 +13615,15 @@
       <c r="B131" s="58">
         <v>109</v>
       </c>
-      <c r="C131" s="333" t="s">
+      <c r="C131" s="340" t="s">
         <v>175</v>
       </c>
-      <c r="D131" s="324" t="s">
+      <c r="D131" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E131" s="325"/>
-      <c r="F131" s="325"/>
-      <c r="G131" s="326"/>
+      <c r="E131" s="338"/>
+      <c r="F131" s="338"/>
+      <c r="G131" s="339"/>
       <c r="H131" s="97"/>
       <c r="I131" s="101">
         <f>SUM(I132:I136)</f>
@@ -13665,15 +13639,15 @@
       <c r="B132" s="58">
         <v>110</v>
       </c>
-      <c r="C132" s="334"/>
+      <c r="C132" s="341"/>
       <c r="D132" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E132" s="337" t="s">
+      <c r="E132" s="356" t="s">
         <v>91</v>
       </c>
-      <c r="F132" s="338"/>
-      <c r="G132" s="339"/>
+      <c r="F132" s="357"/>
+      <c r="G132" s="358"/>
       <c r="H132" s="72"/>
       <c r="I132" s="72"/>
       <c r="J132" s="81" t="e">
@@ -13689,15 +13663,15 @@
       <c r="B133" s="58">
         <v>111</v>
       </c>
-      <c r="C133" s="334"/>
+      <c r="C133" s="341"/>
       <c r="D133" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E133" s="337" t="s">
+      <c r="E133" s="356" t="s">
         <v>235</v>
       </c>
-      <c r="F133" s="338"/>
-      <c r="G133" s="339"/>
+      <c r="F133" s="357"/>
+      <c r="G133" s="358"/>
       <c r="H133" s="72"/>
       <c r="I133" s="72"/>
       <c r="J133" s="81" t="e">
@@ -13719,11 +13693,11 @@
       <c r="D134" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E134" s="337" t="s">
+      <c r="E134" s="356" t="s">
         <v>11</v>
       </c>
-      <c r="F134" s="338"/>
-      <c r="G134" s="339"/>
+      <c r="F134" s="357"/>
+      <c r="G134" s="358"/>
       <c r="H134" s="72"/>
       <c r="I134" s="72"/>
       <c r="J134" s="81" t="e">
@@ -13745,11 +13719,11 @@
       <c r="D135" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E135" s="337" t="s">
+      <c r="E135" s="356" t="s">
         <v>9</v>
       </c>
-      <c r="F135" s="338"/>
-      <c r="G135" s="339"/>
+      <c r="F135" s="357"/>
+      <c r="G135" s="358"/>
       <c r="H135" s="72"/>
       <c r="I135" s="72"/>
       <c r="J135" s="81" t="e">
@@ -13771,11 +13745,11 @@
       <c r="D136" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E136" s="330" t="s">
+      <c r="E136" s="353" t="s">
         <v>236</v>
       </c>
-      <c r="F136" s="330"/>
-      <c r="G136" s="330"/>
+      <c r="F136" s="353"/>
+      <c r="G136" s="353"/>
       <c r="H136" s="72"/>
       <c r="I136" s="72"/>
       <c r="J136" s="81" t="e">
@@ -13798,11 +13772,11 @@
       <c r="D137" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E137" s="340" t="s">
-        <v>44</v>
-      </c>
-      <c r="F137" s="341"/>
-      <c r="G137" s="342"/>
+      <c r="E137" s="366" t="s">
+        <v>44</v>
+      </c>
+      <c r="F137" s="367"/>
+      <c r="G137" s="368"/>
       <c r="H137" s="115"/>
       <c r="I137" s="115"/>
       <c r="J137" s="116"/>
@@ -13816,15 +13790,15 @@
       <c r="B138" s="58">
         <v>118</v>
       </c>
-      <c r="C138" s="333" t="s">
+      <c r="C138" s="340" t="s">
         <v>237</v>
       </c>
-      <c r="D138" s="324" t="s">
+      <c r="D138" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E138" s="325"/>
-      <c r="F138" s="325"/>
-      <c r="G138" s="326"/>
+      <c r="E138" s="338"/>
+      <c r="F138" s="338"/>
+      <c r="G138" s="339"/>
       <c r="H138" s="97"/>
       <c r="I138" s="117"/>
       <c r="J138" s="118"/>
@@ -13837,15 +13811,15 @@
       <c r="B139" s="58">
         <v>119</v>
       </c>
-      <c r="C139" s="334"/>
+      <c r="C139" s="341"/>
       <c r="D139" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E139" s="337" t="s">
+      <c r="E139" s="356" t="s">
         <v>19</v>
       </c>
-      <c r="F139" s="338"/>
-      <c r="G139" s="339"/>
+      <c r="F139" s="357"/>
+      <c r="G139" s="358"/>
       <c r="H139" s="109"/>
       <c r="I139" s="113"/>
       <c r="J139" s="81" t="e">
@@ -13870,10 +13844,10 @@
       <c r="E140" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="F140" s="324" t="s">
+      <c r="F140" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="G140" s="326"/>
+      <c r="G140" s="339"/>
       <c r="H140" s="110"/>
       <c r="I140" s="97"/>
       <c r="J140" s="102"/>
@@ -13895,7 +13869,7 @@
       <c r="E141" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F141" s="331" t="s">
+      <c r="F141" s="373" t="s">
         <v>55</v>
       </c>
       <c r="G141" s="108" t="s">
@@ -13922,7 +13896,7 @@
       <c r="E142" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F142" s="332"/>
+      <c r="F142" s="374"/>
       <c r="G142" s="60" t="s">
         <v>238</v>
       </c>
@@ -13973,10 +13947,10 @@
       <c r="E144" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="F144" s="324" t="s">
+      <c r="F144" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="G144" s="326"/>
+      <c r="G144" s="339"/>
       <c r="H144" s="97"/>
       <c r="I144" s="110"/>
       <c r="J144" s="102"/>
@@ -13998,7 +13972,7 @@
       <c r="E145" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F145" s="331" t="s">
+      <c r="F145" s="373" t="s">
         <v>55</v>
       </c>
       <c r="G145" s="108" t="s">
@@ -14025,7 +13999,7 @@
       <c r="E146" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F146" s="332"/>
+      <c r="F146" s="374"/>
       <c r="G146" s="60" t="s">
         <v>18</v>
       </c>
@@ -14095,15 +14069,15 @@
       <c r="B149" s="58">
         <v>129</v>
       </c>
-      <c r="C149" s="333" t="s">
+      <c r="C149" s="340" t="s">
         <v>239</v>
       </c>
-      <c r="D149" s="324" t="s">
+      <c r="D149" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E149" s="325"/>
-      <c r="F149" s="325"/>
-      <c r="G149" s="326"/>
+      <c r="E149" s="338"/>
+      <c r="F149" s="338"/>
+      <c r="G149" s="339"/>
       <c r="H149" s="97"/>
       <c r="I149" s="110"/>
       <c r="J149" s="102"/>
@@ -14116,15 +14090,15 @@
       <c r="B150" s="121">
         <v>130</v>
       </c>
-      <c r="C150" s="334"/>
+      <c r="C150" s="341"/>
       <c r="D150" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E150" s="335" t="s">
-        <v>44</v>
-      </c>
-      <c r="F150" s="336"/>
-      <c r="G150" s="336"/>
+      <c r="E150" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="F150" s="360"/>
+      <c r="G150" s="360"/>
       <c r="H150" s="104"/>
       <c r="I150" s="104"/>
       <c r="J150" s="81"/>
@@ -14143,11 +14117,11 @@
       <c r="D151" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E151" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F151" s="321"/>
-      <c r="G151" s="322"/>
+      <c r="E151" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F151" s="347"/>
+      <c r="G151" s="348"/>
       <c r="H151" s="72"/>
       <c r="I151" s="109"/>
       <c r="J151" s="81"/>
@@ -14161,15 +14135,15 @@
       <c r="B152" s="58">
         <v>132</v>
       </c>
-      <c r="C152" s="323" t="s">
+      <c r="C152" s="369" t="s">
         <v>240</v>
       </c>
-      <c r="D152" s="324" t="s">
+      <c r="D152" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E152" s="325"/>
-      <c r="F152" s="325"/>
-      <c r="G152" s="326"/>
+      <c r="E152" s="338"/>
+      <c r="F152" s="338"/>
+      <c r="G152" s="339"/>
       <c r="H152" s="97"/>
       <c r="I152" s="110"/>
       <c r="J152" s="102"/>
@@ -14182,15 +14156,15 @@
       <c r="B153" s="58">
         <v>133</v>
       </c>
-      <c r="C153" s="323"/>
+      <c r="C153" s="369"/>
       <c r="D153" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E153" s="327" t="s">
+      <c r="E153" s="370" t="s">
         <v>241</v>
       </c>
-      <c r="F153" s="328"/>
-      <c r="G153" s="329"/>
+      <c r="F153" s="371"/>
+      <c r="G153" s="372"/>
       <c r="H153" s="122"/>
       <c r="I153" s="123"/>
       <c r="J153" s="81"/>
@@ -14209,11 +14183,11 @@
       <c r="D154" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E154" s="330" t="s">
+      <c r="E154" s="353" t="s">
         <v>198</v>
       </c>
-      <c r="F154" s="330"/>
-      <c r="G154" s="330"/>
+      <c r="F154" s="353"/>
+      <c r="G154" s="353"/>
       <c r="H154" s="72"/>
       <c r="I154" s="120" t="e">
         <f>SUM(#REF!)</f>
@@ -14239,15 +14213,120 @@
     </row>
   </sheetData>
   <mergeCells count="142">
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:G24"/>
-    <mergeCell ref="I22:J24"/>
+    <mergeCell ref="E151:G151"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:G152"/>
+    <mergeCell ref="E153:G153"/>
+    <mergeCell ref="E154:G154"/>
+    <mergeCell ref="F140:G140"/>
+    <mergeCell ref="F141:F142"/>
+    <mergeCell ref="F144:G144"/>
+    <mergeCell ref="F145:F146"/>
+    <mergeCell ref="C149:C150"/>
+    <mergeCell ref="D149:G149"/>
+    <mergeCell ref="E150:G150"/>
+    <mergeCell ref="E134:G134"/>
+    <mergeCell ref="E135:G135"/>
+    <mergeCell ref="E136:G136"/>
+    <mergeCell ref="E137:G137"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:G138"/>
+    <mergeCell ref="E139:G139"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="E130:G130"/>
+    <mergeCell ref="C131:C133"/>
+    <mergeCell ref="D131:G131"/>
+    <mergeCell ref="E132:G132"/>
+    <mergeCell ref="E133:G133"/>
+    <mergeCell ref="E121:G121"/>
+    <mergeCell ref="E122:G122"/>
+    <mergeCell ref="C123:C126"/>
+    <mergeCell ref="D123:G123"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="E116:G116"/>
+    <mergeCell ref="E117:G117"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:G118"/>
+    <mergeCell ref="E119:G119"/>
+    <mergeCell ref="E120:G120"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="D111:G111"/>
+    <mergeCell ref="E112:G112"/>
+    <mergeCell ref="E113:G113"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:G114"/>
+    <mergeCell ref="E115:G115"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="D107:G107"/>
+    <mergeCell ref="E108:G108"/>
+    <mergeCell ref="E109:G109"/>
+    <mergeCell ref="E110:G110"/>
+    <mergeCell ref="E104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="E98:G98"/>
+    <mergeCell ref="E99:G99"/>
+    <mergeCell ref="E100:G100"/>
+    <mergeCell ref="C101:C103"/>
+    <mergeCell ref="D101:G101"/>
+    <mergeCell ref="E102:G102"/>
+    <mergeCell ref="E103:G103"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="E94:G94"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:G95"/>
+    <mergeCell ref="E96:G96"/>
+    <mergeCell ref="E97:G97"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:G87"/>
+    <mergeCell ref="E88:G88"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="E90:G90"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="D91:G91"/>
+    <mergeCell ref="E92:G92"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="G81:I81"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="C65:C67"/>
+    <mergeCell ref="D65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D55:G55"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="E47:G47"/>
     <mergeCell ref="C29:G29"/>
     <mergeCell ref="C30:C34"/>
     <mergeCell ref="D30:G30"/>
@@ -14267,120 +14346,15 @@
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="E36:G36"/>
     <mergeCell ref="E37:G37"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:G48"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:G46"/>
-    <mergeCell ref="E47:G47"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="D60:G60"/>
-    <mergeCell ref="E61:G61"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D55:G55"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="G81:I81"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="E64:G64"/>
-    <mergeCell ref="C65:C67"/>
-    <mergeCell ref="D65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="E94:G94"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="D95:G95"/>
-    <mergeCell ref="E96:G96"/>
-    <mergeCell ref="E97:G97"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:G87"/>
-    <mergeCell ref="E88:G88"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="E90:G90"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="D91:G91"/>
-    <mergeCell ref="E92:G92"/>
-    <mergeCell ref="E104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="E98:G98"/>
-    <mergeCell ref="E99:G99"/>
-    <mergeCell ref="E100:G100"/>
-    <mergeCell ref="C101:C103"/>
-    <mergeCell ref="D101:G101"/>
-    <mergeCell ref="E102:G102"/>
-    <mergeCell ref="E103:G103"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="D111:G111"/>
-    <mergeCell ref="E112:G112"/>
-    <mergeCell ref="E113:G113"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="D114:G114"/>
-    <mergeCell ref="E115:G115"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="D107:G107"/>
-    <mergeCell ref="E108:G108"/>
-    <mergeCell ref="E109:G109"/>
-    <mergeCell ref="E110:G110"/>
-    <mergeCell ref="E121:G121"/>
-    <mergeCell ref="E122:G122"/>
-    <mergeCell ref="C123:C126"/>
-    <mergeCell ref="D123:G123"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="E116:G116"/>
-    <mergeCell ref="E117:G117"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:G118"/>
-    <mergeCell ref="E119:G119"/>
-    <mergeCell ref="E120:G120"/>
-    <mergeCell ref="E134:G134"/>
-    <mergeCell ref="E135:G135"/>
-    <mergeCell ref="E136:G136"/>
-    <mergeCell ref="E137:G137"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:G138"/>
-    <mergeCell ref="E139:G139"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="E130:G130"/>
-    <mergeCell ref="C131:C133"/>
-    <mergeCell ref="D131:G131"/>
-    <mergeCell ref="E132:G132"/>
-    <mergeCell ref="E133:G133"/>
-    <mergeCell ref="E151:G151"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D152:G152"/>
-    <mergeCell ref="E153:G153"/>
-    <mergeCell ref="E154:G154"/>
-    <mergeCell ref="F140:G140"/>
-    <mergeCell ref="F141:F142"/>
-    <mergeCell ref="F144:G144"/>
-    <mergeCell ref="F145:F146"/>
-    <mergeCell ref="C149:C150"/>
-    <mergeCell ref="D149:G149"/>
-    <mergeCell ref="E150:G150"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:G24"/>
+    <mergeCell ref="I22:J24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="64" orientation="portrait" r:id="rId1"/>
@@ -14410,15 +14384,15 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="358" t="s">
+      <c r="B1" s="320" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="358"/>
-      <c r="D1" s="358"/>
-      <c r="E1" s="358"/>
-      <c r="F1" s="358"/>
-      <c r="G1" s="358"/>
-      <c r="H1" s="358"/>
+      <c r="C1" s="320"/>
+      <c r="D1" s="320"/>
+      <c r="E1" s="320"/>
+      <c r="F1" s="320"/>
+      <c r="G1" s="320"/>
+      <c r="H1" s="320"/>
       <c r="L1" s="51"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1">
@@ -14452,30 +14426,30 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="359" t="s">
+      <c r="B3" s="321" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
+      <c r="C3" s="321"/>
+      <c r="D3" s="321"/>
+      <c r="E3" s="321"/>
+      <c r="F3" s="321"/>
+      <c r="G3" s="321"/>
+      <c r="H3" s="321"/>
       <c r="L3" s="51"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="360" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="360"/>
-      <c r="D4" s="360"/>
-      <c r="E4" s="360"/>
-      <c r="F4" s="360"/>
-      <c r="G4" s="360"/>
-      <c r="H4" s="360"/>
+      <c r="B4" s="322" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="322"/>
+      <c r="D4" s="322"/>
+      <c r="E4" s="322"/>
+      <c r="F4" s="322"/>
+      <c r="G4" s="322"/>
+      <c r="H4" s="322"/>
       <c r="L4" s="51"/>
       <c r="M4" s="53"/>
     </row>
@@ -14497,40 +14471,40 @@
       <c r="A19" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="383" t="s">
+      <c r="B19" s="375" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="366" t="s">
+      <c r="C19" s="328" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="367"/>
-      <c r="E19" s="367"/>
-      <c r="F19" s="367"/>
-      <c r="G19" s="368"/>
+      <c r="D19" s="329"/>
+      <c r="E19" s="329"/>
+      <c r="F19" s="329"/>
+      <c r="G19" s="330"/>
       <c r="H19" s="55"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1">
       <c r="A20" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="364"/>
-      <c r="C20" s="369"/>
-      <c r="D20" s="370"/>
-      <c r="E20" s="370"/>
-      <c r="F20" s="370"/>
-      <c r="G20" s="371"/>
+      <c r="B20" s="326"/>
+      <c r="C20" s="331"/>
+      <c r="D20" s="332"/>
+      <c r="E20" s="332"/>
+      <c r="F20" s="332"/>
+      <c r="G20" s="333"/>
       <c r="H20" s="55"/>
     </row>
     <row r="21" spans="1:13" ht="24" customHeight="1">
       <c r="A21" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="365"/>
-      <c r="C21" s="372"/>
-      <c r="D21" s="373"/>
-      <c r="E21" s="373"/>
-      <c r="F21" s="373"/>
-      <c r="G21" s="374"/>
+      <c r="B21" s="327"/>
+      <c r="C21" s="334"/>
+      <c r="D21" s="335"/>
+      <c r="E21" s="335"/>
+      <c r="F21" s="335"/>
+      <c r="G21" s="336"/>
       <c r="H21" s="57" t="s">
         <v>52</v>
       </c>
@@ -14546,17 +14520,17 @@
       <c r="B25" s="57">
         <v>1</v>
       </c>
-      <c r="C25" s="384">
+      <c r="C25" s="376">
         <v>2</v>
       </c>
-      <c r="D25" s="385"/>
+      <c r="D25" s="377"/>
       <c r="E25" s="57">
         <v>3</v>
       </c>
-      <c r="F25" s="384">
+      <c r="F25" s="376">
         <v>4</v>
       </c>
-      <c r="G25" s="385"/>
+      <c r="G25" s="377"/>
       <c r="H25" s="57">
         <v>8</v>
       </c>
@@ -14612,15 +14586,15 @@
       <c r="B29" s="58">
         <v>2</v>
       </c>
-      <c r="C29" s="375" t="s">
+      <c r="C29" s="378" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="376"/>
-      <c r="E29" s="324" t="s">
+      <c r="D29" s="379"/>
+      <c r="E29" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F29" s="325"/>
-      <c r="G29" s="326"/>
+      <c r="F29" s="338"/>
+      <c r="G29" s="339"/>
       <c r="H29" s="64"/>
       <c r="I29" s="49"/>
       <c r="M29" s="65"/>
@@ -14632,15 +14606,15 @@
       <c r="B30" s="58">
         <v>3</v>
       </c>
-      <c r="C30" s="377"/>
-      <c r="D30" s="378"/>
+      <c r="C30" s="380"/>
+      <c r="D30" s="381"/>
       <c r="E30" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="337" t="s">
+      <c r="F30" s="356" t="s">
         <v>56</v>
       </c>
-      <c r="G30" s="339"/>
+      <c r="G30" s="358"/>
       <c r="H30" s="72" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14655,15 +14629,15 @@
       <c r="B31" s="58">
         <v>4</v>
       </c>
-      <c r="C31" s="377"/>
-      <c r="D31" s="378"/>
+      <c r="C31" s="380"/>
+      <c r="D31" s="381"/>
       <c r="E31" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="337" t="s">
+      <c r="F31" s="356" t="s">
         <v>57</v>
       </c>
-      <c r="G31" s="339"/>
+      <c r="G31" s="358"/>
       <c r="H31" s="64"/>
       <c r="I31" s="49"/>
       <c r="M31" s="53"/>
@@ -14675,15 +14649,15 @@
       <c r="B32" s="58">
         <v>5</v>
       </c>
-      <c r="C32" s="377"/>
-      <c r="D32" s="378"/>
+      <c r="C32" s="380"/>
+      <c r="D32" s="381"/>
       <c r="E32" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="337" t="s">
+      <c r="F32" s="356" t="s">
         <v>58</v>
       </c>
-      <c r="G32" s="339"/>
+      <c r="G32" s="358"/>
       <c r="H32" s="64"/>
       <c r="I32" s="49"/>
     </row>
@@ -14703,10 +14677,10 @@
       <c r="E33" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F33" s="320" t="s">
+      <c r="F33" s="346" t="s">
         <v>170</v>
       </c>
-      <c r="G33" s="322"/>
+      <c r="G33" s="348"/>
       <c r="H33" s="64"/>
       <c r="I33" s="49"/>
       <c r="J33" s="49"/>
@@ -14727,10 +14701,10 @@
       <c r="E34" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G34" s="322"/>
+      <c r="F34" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="348"/>
       <c r="H34" s="64"/>
       <c r="I34" s="49"/>
       <c r="J34" s="49"/>
@@ -14743,15 +14717,15 @@
       <c r="B35" s="58">
         <v>8</v>
       </c>
-      <c r="C35" s="375" t="s">
+      <c r="C35" s="378" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="376"/>
-      <c r="E35" s="324" t="s">
+      <c r="D35" s="379"/>
+      <c r="E35" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F35" s="325"/>
-      <c r="G35" s="326"/>
+      <c r="F35" s="338"/>
+      <c r="G35" s="339"/>
       <c r="H35" s="64"/>
       <c r="I35" s="49"/>
     </row>
@@ -14762,15 +14736,15 @@
       <c r="B36" s="58">
         <v>9</v>
       </c>
-      <c r="C36" s="377"/>
-      <c r="D36" s="378"/>
-      <c r="E36" s="331" t="s">
+      <c r="C36" s="380"/>
+      <c r="D36" s="381"/>
+      <c r="E36" s="373" t="s">
         <v>55</v>
       </c>
-      <c r="F36" s="337" t="s">
+      <c r="F36" s="356" t="s">
         <v>172</v>
       </c>
-      <c r="G36" s="339"/>
+      <c r="G36" s="358"/>
       <c r="H36" s="72" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -14785,13 +14759,13 @@
       <c r="B37" s="58">
         <v>10</v>
       </c>
-      <c r="C37" s="381"/>
-      <c r="D37" s="382"/>
-      <c r="E37" s="332"/>
-      <c r="F37" s="337" t="s">
+      <c r="C37" s="382"/>
+      <c r="D37" s="383"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="356" t="s">
         <v>173</v>
       </c>
-      <c r="G37" s="339"/>
+      <c r="G37" s="358"/>
       <c r="H37" s="64"/>
       <c r="I37" s="49"/>
     </row>
@@ -14802,15 +14776,15 @@
       <c r="B38" s="58">
         <v>11</v>
       </c>
-      <c r="C38" s="375" t="s">
+      <c r="C38" s="378" t="s">
         <v>174</v>
       </c>
-      <c r="D38" s="376"/>
-      <c r="E38" s="324" t="s">
+      <c r="D38" s="379"/>
+      <c r="E38" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F38" s="325"/>
-      <c r="G38" s="326"/>
+      <c r="F38" s="338"/>
+      <c r="G38" s="339"/>
       <c r="H38" s="64"/>
       <c r="I38" s="49"/>
     </row>
@@ -14821,15 +14795,15 @@
       <c r="B39" s="58">
         <v>12</v>
       </c>
-      <c r="C39" s="377"/>
-      <c r="D39" s="378"/>
+      <c r="C39" s="380"/>
+      <c r="D39" s="381"/>
       <c r="E39" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="G39" s="380"/>
+      <c r="F39" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="G39" s="385"/>
       <c r="H39" s="64"/>
       <c r="I39" s="49"/>
     </row>
@@ -14849,10 +14823,10 @@
       <c r="E40" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G40" s="322"/>
+      <c r="F40" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="G40" s="348"/>
       <c r="H40" s="64"/>
       <c r="I40" s="49"/>
       <c r="J40" s="49"/>
@@ -14864,15 +14838,15 @@
       <c r="B41" s="58">
         <v>14</v>
       </c>
-      <c r="C41" s="375" t="s">
+      <c r="C41" s="378" t="s">
         <v>175</v>
       </c>
-      <c r="D41" s="376"/>
-      <c r="E41" s="324" t="s">
+      <c r="D41" s="379"/>
+      <c r="E41" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F41" s="325"/>
-      <c r="G41" s="326"/>
+      <c r="F41" s="338"/>
+      <c r="G41" s="339"/>
       <c r="H41" s="64"/>
       <c r="I41" s="49"/>
     </row>
@@ -14883,15 +14857,15 @@
       <c r="B42" s="58">
         <v>15</v>
       </c>
-      <c r="C42" s="377"/>
-      <c r="D42" s="378"/>
+      <c r="C42" s="380"/>
+      <c r="D42" s="381"/>
       <c r="E42" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="337" t="s">
+      <c r="F42" s="356" t="s">
         <v>91</v>
       </c>
-      <c r="G42" s="339"/>
+      <c r="G42" s="358"/>
       <c r="H42" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14914,10 +14888,10 @@
       <c r="E43" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F43" s="320" t="s">
+      <c r="F43" s="346" t="s">
         <v>176</v>
       </c>
-      <c r="G43" s="322"/>
+      <c r="G43" s="348"/>
       <c r="H43" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14941,10 +14915,10 @@
       <c r="E44" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F44" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G44" s="322"/>
+      <c r="F44" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" s="348"/>
       <c r="H44" s="64"/>
       <c r="I44" s="49"/>
       <c r="J44" s="49"/>
@@ -14956,15 +14930,15 @@
       <c r="B45" s="58">
         <v>18</v>
       </c>
-      <c r="C45" s="375" t="s">
+      <c r="C45" s="378" t="s">
         <v>177</v>
       </c>
-      <c r="D45" s="376"/>
-      <c r="E45" s="324" t="s">
+      <c r="D45" s="379"/>
+      <c r="E45" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="325"/>
-      <c r="G45" s="326"/>
+      <c r="F45" s="338"/>
+      <c r="G45" s="339"/>
       <c r="H45" s="64"/>
       <c r="I45" s="49"/>
     </row>
@@ -14975,15 +14949,15 @@
       <c r="B46" s="58">
         <v>19</v>
       </c>
-      <c r="C46" s="377"/>
-      <c r="D46" s="378"/>
+      <c r="C46" s="380"/>
+      <c r="D46" s="381"/>
       <c r="E46" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="G46" s="380"/>
+      <c r="F46" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" s="385"/>
       <c r="H46" s="64"/>
       <c r="I46" s="49"/>
     </row>
@@ -15003,8 +14977,8 @@
       <c r="E47" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F47" s="320"/>
-      <c r="G47" s="322"/>
+      <c r="F47" s="346"/>
+      <c r="G47" s="348"/>
       <c r="H47" s="64"/>
       <c r="I47" s="49"/>
       <c r="J47" s="49"/>
@@ -15025,10 +14999,10 @@
       <c r="E48" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F48" s="320" t="s">
+      <c r="F48" s="346" t="s">
         <v>178</v>
       </c>
-      <c r="G48" s="322"/>
+      <c r="G48" s="348"/>
       <c r="H48" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15052,10 +15026,10 @@
       <c r="E49" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F49" s="320" t="s">
+      <c r="F49" s="346" t="s">
         <v>8</v>
       </c>
-      <c r="G49" s="322"/>
+      <c r="G49" s="348"/>
       <c r="H49" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15070,13 +15044,13 @@
       <c r="B50" s="58">
         <v>24</v>
       </c>
-      <c r="C50" s="324" t="s">
+      <c r="C50" s="337" t="s">
         <v>179</v>
       </c>
-      <c r="D50" s="325"/>
-      <c r="E50" s="325"/>
-      <c r="F50" s="325"/>
-      <c r="G50" s="326"/>
+      <c r="D50" s="338"/>
+      <c r="E50" s="338"/>
+      <c r="F50" s="338"/>
+      <c r="G50" s="339"/>
       <c r="H50" s="64"/>
       <c r="I50" s="49"/>
     </row>
@@ -15087,13 +15061,13 @@
       <c r="B51" s="58">
         <v>25</v>
       </c>
-      <c r="C51" s="324" t="s">
+      <c r="C51" s="337" t="s">
         <v>180</v>
       </c>
-      <c r="D51" s="325"/>
-      <c r="E51" s="325"/>
-      <c r="F51" s="325"/>
-      <c r="G51" s="326"/>
+      <c r="D51" s="338"/>
+      <c r="E51" s="338"/>
+      <c r="F51" s="338"/>
+      <c r="G51" s="339"/>
       <c r="H51" s="64" t="e">
         <f>нак.расх.!G29-зат.осн.про.!H75-зат.осн.про.!H99</f>
         <v>#REF!</v>
@@ -15139,15 +15113,15 @@
       <c r="B53" s="58">
         <v>2</v>
       </c>
-      <c r="C53" s="375" t="s">
+      <c r="C53" s="378" t="s">
         <v>54</v>
       </c>
-      <c r="D53" s="376"/>
-      <c r="E53" s="324" t="s">
+      <c r="D53" s="379"/>
+      <c r="E53" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F53" s="325"/>
-      <c r="G53" s="326"/>
+      <c r="F53" s="338"/>
+      <c r="G53" s="339"/>
       <c r="H53" s="64"/>
       <c r="I53" s="49"/>
       <c r="M53" s="53" t="e">
@@ -15162,15 +15136,15 @@
       <c r="B54" s="58">
         <v>3</v>
       </c>
-      <c r="C54" s="377"/>
-      <c r="D54" s="378"/>
+      <c r="C54" s="380"/>
+      <c r="D54" s="381"/>
       <c r="E54" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F54" s="337" t="s">
+      <c r="F54" s="356" t="s">
         <v>56</v>
       </c>
-      <c r="G54" s="339"/>
+      <c r="G54" s="358"/>
       <c r="H54" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15184,15 +15158,15 @@
       <c r="B55" s="58">
         <v>4</v>
       </c>
-      <c r="C55" s="377"/>
-      <c r="D55" s="378"/>
+      <c r="C55" s="380"/>
+      <c r="D55" s="381"/>
       <c r="E55" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F55" s="337" t="s">
+      <c r="F55" s="356" t="s">
         <v>57</v>
       </c>
-      <c r="G55" s="339"/>
+      <c r="G55" s="358"/>
       <c r="H55" s="64"/>
       <c r="I55" s="49"/>
     </row>
@@ -15203,15 +15177,15 @@
       <c r="B56" s="58">
         <v>5</v>
       </c>
-      <c r="C56" s="377"/>
-      <c r="D56" s="378"/>
+      <c r="C56" s="380"/>
+      <c r="D56" s="381"/>
       <c r="E56" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="337" t="s">
+      <c r="F56" s="356" t="s">
         <v>58</v>
       </c>
-      <c r="G56" s="339"/>
+      <c r="G56" s="358"/>
       <c r="H56" s="64"/>
       <c r="I56" s="49"/>
     </row>
@@ -15231,10 +15205,10 @@
       <c r="E57" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="320" t="s">
+      <c r="F57" s="346" t="s">
         <v>170</v>
       </c>
-      <c r="G57" s="322"/>
+      <c r="G57" s="348"/>
       <c r="H57" s="64"/>
       <c r="I57" s="49"/>
       <c r="J57" s="49"/>
@@ -15255,10 +15229,10 @@
       <c r="E58" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F58" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G58" s="322"/>
+      <c r="F58" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="G58" s="348"/>
       <c r="H58" s="64"/>
       <c r="I58" s="49"/>
     </row>
@@ -15269,15 +15243,15 @@
       <c r="B59" s="58">
         <v>8</v>
       </c>
-      <c r="C59" s="375" t="s">
+      <c r="C59" s="378" t="s">
         <v>171</v>
       </c>
-      <c r="D59" s="376"/>
-      <c r="E59" s="324" t="s">
+      <c r="D59" s="379"/>
+      <c r="E59" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F59" s="325"/>
-      <c r="G59" s="326"/>
+      <c r="F59" s="338"/>
+      <c r="G59" s="339"/>
       <c r="H59" s="64"/>
       <c r="I59" s="49"/>
     </row>
@@ -15288,15 +15262,15 @@
       <c r="B60" s="58">
         <v>9</v>
       </c>
-      <c r="C60" s="377"/>
-      <c r="D60" s="378"/>
-      <c r="E60" s="331" t="s">
+      <c r="C60" s="380"/>
+      <c r="D60" s="381"/>
+      <c r="E60" s="373" t="s">
         <v>55</v>
       </c>
-      <c r="F60" s="337" t="s">
+      <c r="F60" s="356" t="s">
         <v>172</v>
       </c>
-      <c r="G60" s="339"/>
+      <c r="G60" s="358"/>
       <c r="H60" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15310,13 +15284,13 @@
       <c r="B61" s="58">
         <v>10</v>
       </c>
-      <c r="C61" s="381"/>
-      <c r="D61" s="382"/>
-      <c r="E61" s="332"/>
-      <c r="F61" s="337" t="s">
+      <c r="C61" s="382"/>
+      <c r="D61" s="383"/>
+      <c r="E61" s="374"/>
+      <c r="F61" s="356" t="s">
         <v>173</v>
       </c>
-      <c r="G61" s="339"/>
+      <c r="G61" s="358"/>
       <c r="H61" s="64"/>
       <c r="I61" s="49"/>
     </row>
@@ -15327,15 +15301,15 @@
       <c r="B62" s="58">
         <v>11</v>
       </c>
-      <c r="C62" s="375" t="s">
+      <c r="C62" s="378" t="s">
         <v>174</v>
       </c>
-      <c r="D62" s="376"/>
-      <c r="E62" s="324" t="s">
+      <c r="D62" s="379"/>
+      <c r="E62" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F62" s="325"/>
-      <c r="G62" s="326"/>
+      <c r="F62" s="338"/>
+      <c r="G62" s="339"/>
       <c r="H62" s="64"/>
       <c r="I62" s="49"/>
     </row>
@@ -15346,15 +15320,15 @@
       <c r="B63" s="58">
         <v>12</v>
       </c>
-      <c r="C63" s="377"/>
-      <c r="D63" s="378"/>
+      <c r="C63" s="380"/>
+      <c r="D63" s="381"/>
       <c r="E63" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F63" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="G63" s="380"/>
+      <c r="F63" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="G63" s="385"/>
       <c r="H63" s="64"/>
       <c r="I63" s="49"/>
       <c r="J63" s="49"/>
@@ -15375,10 +15349,10 @@
       <c r="E64" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F64" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G64" s="322"/>
+      <c r="F64" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="G64" s="348"/>
       <c r="H64" s="64"/>
       <c r="I64" s="49"/>
     </row>
@@ -15389,15 +15363,15 @@
       <c r="B65" s="58">
         <v>14</v>
       </c>
-      <c r="C65" s="375" t="s">
+      <c r="C65" s="378" t="s">
         <v>175</v>
       </c>
-      <c r="D65" s="376"/>
-      <c r="E65" s="324" t="s">
+      <c r="D65" s="379"/>
+      <c r="E65" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="325"/>
-      <c r="G65" s="326"/>
+      <c r="F65" s="338"/>
+      <c r="G65" s="339"/>
       <c r="H65" s="64"/>
       <c r="I65" s="49"/>
     </row>
@@ -15408,15 +15382,15 @@
       <c r="B66" s="58">
         <v>15</v>
       </c>
-      <c r="C66" s="377"/>
-      <c r="D66" s="378"/>
+      <c r="C66" s="380"/>
+      <c r="D66" s="381"/>
       <c r="E66" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F66" s="337" t="s">
+      <c r="F66" s="356" t="s">
         <v>91</v>
       </c>
-      <c r="G66" s="339"/>
+      <c r="G66" s="358"/>
       <c r="H66" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15440,10 +15414,10 @@
       <c r="E67" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="320" t="s">
+      <c r="F67" s="346" t="s">
         <v>176</v>
       </c>
-      <c r="G67" s="322"/>
+      <c r="G67" s="348"/>
       <c r="H67" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15466,10 +15440,10 @@
       <c r="E68" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F68" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G68" s="322"/>
+      <c r="F68" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="G68" s="348"/>
       <c r="H68" s="64"/>
       <c r="I68" s="49"/>
     </row>
@@ -15480,15 +15454,15 @@
       <c r="B69" s="58">
         <v>18</v>
       </c>
-      <c r="C69" s="375" t="s">
+      <c r="C69" s="378" t="s">
         <v>177</v>
       </c>
-      <c r="D69" s="376"/>
-      <c r="E69" s="324" t="s">
+      <c r="D69" s="379"/>
+      <c r="E69" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="325"/>
-      <c r="G69" s="326"/>
+      <c r="F69" s="338"/>
+      <c r="G69" s="339"/>
       <c r="H69" s="64"/>
       <c r="I69" s="49"/>
       <c r="J69" s="49"/>
@@ -15500,15 +15474,15 @@
       <c r="B70" s="58">
         <v>19</v>
       </c>
-      <c r="C70" s="377"/>
-      <c r="D70" s="378"/>
+      <c r="C70" s="380"/>
+      <c r="D70" s="381"/>
       <c r="E70" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F70" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="G70" s="380"/>
+      <c r="F70" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="G70" s="385"/>
       <c r="H70" s="64"/>
       <c r="I70" s="49"/>
     </row>
@@ -15528,8 +15502,8 @@
       <c r="E71" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F71" s="320"/>
-      <c r="G71" s="322"/>
+      <c r="F71" s="346"/>
+      <c r="G71" s="348"/>
       <c r="H71" s="64"/>
       <c r="I71" s="49"/>
     </row>
@@ -15546,10 +15520,10 @@
       <c r="E72" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F72" s="320" t="s">
+      <c r="F72" s="346" t="s">
         <v>178</v>
       </c>
-      <c r="G72" s="322"/>
+      <c r="G72" s="348"/>
       <c r="H72" s="64"/>
       <c r="I72" s="49"/>
       <c r="J72" s="49"/>
@@ -15572,10 +15546,10 @@
       <c r="E73" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F73" s="320" t="s">
+      <c r="F73" s="346" t="s">
         <v>8</v>
       </c>
-      <c r="G73" s="322"/>
+      <c r="G73" s="348"/>
       <c r="H73" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15589,13 +15563,13 @@
       <c r="B74" s="58">
         <v>24</v>
       </c>
-      <c r="C74" s="324" t="s">
+      <c r="C74" s="337" t="s">
         <v>179</v>
       </c>
-      <c r="D74" s="325"/>
-      <c r="E74" s="325"/>
-      <c r="F74" s="325"/>
-      <c r="G74" s="326"/>
+      <c r="D74" s="338"/>
+      <c r="E74" s="338"/>
+      <c r="F74" s="338"/>
+      <c r="G74" s="339"/>
       <c r="H74" s="64"/>
       <c r="I74" s="49"/>
       <c r="J74" s="49"/>
@@ -15606,13 +15580,13 @@
       <c r="B75" s="58">
         <v>25</v>
       </c>
-      <c r="C75" s="324" t="s">
+      <c r="C75" s="337" t="s">
         <v>180</v>
       </c>
-      <c r="D75" s="325"/>
-      <c r="E75" s="325"/>
-      <c r="F75" s="325"/>
-      <c r="G75" s="326"/>
+      <c r="D75" s="338"/>
+      <c r="E75" s="338"/>
+      <c r="F75" s="338"/>
+      <c r="G75" s="339"/>
       <c r="H75" s="64" t="e">
         <f>нак.расх.!G29*4%</f>
         <v>#REF!</v>
@@ -15658,15 +15632,15 @@
       <c r="B77" s="58">
         <v>2</v>
       </c>
-      <c r="C77" s="375" t="s">
+      <c r="C77" s="378" t="s">
         <v>54</v>
       </c>
-      <c r="D77" s="376"/>
-      <c r="E77" s="324" t="s">
+      <c r="D77" s="379"/>
+      <c r="E77" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F77" s="325"/>
-      <c r="G77" s="326"/>
+      <c r="F77" s="338"/>
+      <c r="G77" s="339"/>
       <c r="H77" s="64"/>
       <c r="M77" s="53" t="e">
         <f>H76-M76</f>
@@ -15677,15 +15651,15 @@
       <c r="B78" s="58">
         <v>3</v>
       </c>
-      <c r="C78" s="377"/>
-      <c r="D78" s="378"/>
+      <c r="C78" s="380"/>
+      <c r="D78" s="381"/>
       <c r="E78" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F78" s="337" t="s">
+      <c r="F78" s="356" t="s">
         <v>56</v>
       </c>
-      <c r="G78" s="339"/>
+      <c r="G78" s="358"/>
       <c r="H78" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15695,30 +15669,30 @@
       <c r="B79" s="58">
         <v>4</v>
       </c>
-      <c r="C79" s="377"/>
-      <c r="D79" s="378"/>
+      <c r="C79" s="380"/>
+      <c r="D79" s="381"/>
       <c r="E79" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F79" s="337" t="s">
+      <c r="F79" s="356" t="s">
         <v>57</v>
       </c>
-      <c r="G79" s="339"/>
+      <c r="G79" s="358"/>
       <c r="H79" s="64"/>
     </row>
     <row r="80" spans="1:13" ht="15.75" customHeight="1">
       <c r="B80" s="58">
         <v>5</v>
       </c>
-      <c r="C80" s="377"/>
-      <c r="D80" s="378"/>
+      <c r="C80" s="380"/>
+      <c r="D80" s="381"/>
       <c r="E80" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F80" s="337" t="s">
+      <c r="F80" s="356" t="s">
         <v>58</v>
       </c>
-      <c r="G80" s="339"/>
+      <c r="G80" s="358"/>
       <c r="H80" s="64"/>
     </row>
     <row r="81" spans="2:8" ht="15.75" customHeight="1">
@@ -15734,10 +15708,10 @@
       <c r="E81" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="320" t="s">
+      <c r="F81" s="346" t="s">
         <v>170</v>
       </c>
-      <c r="G81" s="322"/>
+      <c r="G81" s="348"/>
       <c r="H81" s="64"/>
     </row>
     <row r="82" spans="2:8" ht="15.75" customHeight="1">
@@ -15753,40 +15727,40 @@
       <c r="E82" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G82" s="322"/>
+      <c r="F82" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="G82" s="348"/>
       <c r="H82" s="64"/>
     </row>
     <row r="83" spans="2:8" ht="15.75" customHeight="1">
       <c r="B83" s="58">
         <v>8</v>
       </c>
-      <c r="C83" s="375" t="s">
+      <c r="C83" s="378" t="s">
         <v>171</v>
       </c>
-      <c r="D83" s="376"/>
-      <c r="E83" s="324" t="s">
+      <c r="D83" s="379"/>
+      <c r="E83" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F83" s="325"/>
-      <c r="G83" s="326"/>
+      <c r="F83" s="338"/>
+      <c r="G83" s="339"/>
       <c r="H83" s="64"/>
     </row>
     <row r="84" spans="2:8" ht="15.75" customHeight="1">
       <c r="B84" s="58">
         <v>9</v>
       </c>
-      <c r="C84" s="377"/>
-      <c r="D84" s="378"/>
-      <c r="E84" s="331" t="s">
+      <c r="C84" s="380"/>
+      <c r="D84" s="381"/>
+      <c r="E84" s="373" t="s">
         <v>55</v>
       </c>
-      <c r="F84" s="337" t="s">
+      <c r="F84" s="356" t="s">
         <v>172</v>
       </c>
-      <c r="G84" s="339"/>
+      <c r="G84" s="358"/>
       <c r="H84" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15796,43 +15770,43 @@
       <c r="B85" s="58">
         <v>10</v>
       </c>
-      <c r="C85" s="381"/>
-      <c r="D85" s="382"/>
-      <c r="E85" s="332"/>
-      <c r="F85" s="337" t="s">
+      <c r="C85" s="382"/>
+      <c r="D85" s="383"/>
+      <c r="E85" s="374"/>
+      <c r="F85" s="356" t="s">
         <v>173</v>
       </c>
-      <c r="G85" s="339"/>
+      <c r="G85" s="358"/>
       <c r="H85" s="64"/>
     </row>
     <row r="86" spans="2:8" ht="15.75" customHeight="1">
       <c r="B86" s="58">
         <v>11</v>
       </c>
-      <c r="C86" s="375" t="s">
+      <c r="C86" s="378" t="s">
         <v>174</v>
       </c>
-      <c r="D86" s="376"/>
-      <c r="E86" s="324" t="s">
+      <c r="D86" s="379"/>
+      <c r="E86" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F86" s="325"/>
-      <c r="G86" s="326"/>
+      <c r="F86" s="338"/>
+      <c r="G86" s="339"/>
       <c r="H86" s="64"/>
     </row>
     <row r="87" spans="2:8" ht="15.75" customHeight="1">
       <c r="B87" s="58">
         <v>12</v>
       </c>
-      <c r="C87" s="377"/>
-      <c r="D87" s="378"/>
+      <c r="C87" s="380"/>
+      <c r="D87" s="381"/>
       <c r="E87" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F87" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="G87" s="380"/>
+      <c r="F87" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="G87" s="385"/>
       <c r="H87" s="64"/>
     </row>
     <row r="88" spans="2:8" ht="15.75" customHeight="1">
@@ -15848,40 +15822,40 @@
       <c r="E88" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G88" s="322"/>
+      <c r="F88" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="G88" s="348"/>
       <c r="H88" s="64"/>
     </row>
     <row r="89" spans="2:8" ht="15.75" customHeight="1">
       <c r="B89" s="58">
         <v>14</v>
       </c>
-      <c r="C89" s="375" t="s">
+      <c r="C89" s="378" t="s">
         <v>175</v>
       </c>
-      <c r="D89" s="376"/>
-      <c r="E89" s="324" t="s">
+      <c r="D89" s="379"/>
+      <c r="E89" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F89" s="325"/>
-      <c r="G89" s="326"/>
+      <c r="F89" s="338"/>
+      <c r="G89" s="339"/>
       <c r="H89" s="64"/>
     </row>
     <row r="90" spans="2:8" ht="15.75" customHeight="1">
       <c r="B90" s="58">
         <v>15</v>
       </c>
-      <c r="C90" s="377"/>
-      <c r="D90" s="378"/>
+      <c r="C90" s="380"/>
+      <c r="D90" s="381"/>
       <c r="E90" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F90" s="337" t="s">
+      <c r="F90" s="356" t="s">
         <v>91</v>
       </c>
-      <c r="G90" s="339"/>
+      <c r="G90" s="358"/>
       <c r="H90" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15900,10 +15874,10 @@
       <c r="E91" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F91" s="320" t="s">
+      <c r="F91" s="346" t="s">
         <v>176</v>
       </c>
-      <c r="G91" s="322"/>
+      <c r="G91" s="348"/>
       <c r="H91" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15922,40 +15896,40 @@
       <c r="E92" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F92" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G92" s="322"/>
+      <c r="F92" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="G92" s="348"/>
       <c r="H92" s="64"/>
     </row>
     <row r="93" spans="2:8" ht="15.75" customHeight="1">
       <c r="B93" s="58">
         <v>18</v>
       </c>
-      <c r="C93" s="375" t="s">
+      <c r="C93" s="378" t="s">
         <v>177</v>
       </c>
-      <c r="D93" s="376"/>
-      <c r="E93" s="324" t="s">
+      <c r="D93" s="379"/>
+      <c r="E93" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F93" s="325"/>
-      <c r="G93" s="326"/>
+      <c r="F93" s="338"/>
+      <c r="G93" s="339"/>
       <c r="H93" s="64"/>
     </row>
     <row r="94" spans="2:8" ht="15.75" customHeight="1">
       <c r="B94" s="58">
         <v>19</v>
       </c>
-      <c r="C94" s="377"/>
-      <c r="D94" s="378"/>
+      <c r="C94" s="380"/>
+      <c r="D94" s="381"/>
       <c r="E94" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F94" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="G94" s="380"/>
+      <c r="F94" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="G94" s="385"/>
       <c r="H94" s="64"/>
     </row>
     <row r="95" spans="2:8" ht="15.75" customHeight="1">
@@ -15971,8 +15945,8 @@
       <c r="E95" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F95" s="320"/>
-      <c r="G95" s="322"/>
+      <c r="F95" s="346"/>
+      <c r="G95" s="348"/>
       <c r="H95" s="64"/>
     </row>
     <row r="96" spans="2:8" ht="32.25" customHeight="1">
@@ -15988,10 +15962,10 @@
       <c r="E96" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F96" s="320" t="s">
+      <c r="F96" s="346" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="322"/>
+      <c r="G96" s="348"/>
       <c r="H96" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16010,34 +15984,34 @@
       <c r="E97" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F97" s="320"/>
-      <c r="G97" s="322"/>
+      <c r="F97" s="346"/>
+      <c r="G97" s="348"/>
       <c r="H97" s="64"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1">
       <c r="B98" s="58">
         <v>24</v>
       </c>
-      <c r="C98" s="324" t="s">
+      <c r="C98" s="337" t="s">
         <v>179</v>
       </c>
-      <c r="D98" s="325"/>
-      <c r="E98" s="325"/>
-      <c r="F98" s="325"/>
-      <c r="G98" s="326"/>
+      <c r="D98" s="338"/>
+      <c r="E98" s="338"/>
+      <c r="F98" s="338"/>
+      <c r="G98" s="339"/>
       <c r="H98" s="64"/>
     </row>
     <row r="99" spans="2:8" ht="15.75" customHeight="1">
       <c r="B99" s="58">
         <v>25</v>
       </c>
-      <c r="C99" s="324" t="s">
+      <c r="C99" s="337" t="s">
         <v>180</v>
       </c>
-      <c r="D99" s="325"/>
-      <c r="E99" s="325"/>
-      <c r="F99" s="325"/>
-      <c r="G99" s="326"/>
+      <c r="D99" s="338"/>
+      <c r="E99" s="338"/>
+      <c r="F99" s="338"/>
+      <c r="G99" s="339"/>
       <c r="H99" s="64" t="e">
         <f>нак.расх.!G29*16%</f>
         <v>#REF!</v>
@@ -16045,6 +16019,87 @@
     </row>
   </sheetData>
   <mergeCells count="94">
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="C93:D94"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="C86:D87"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="C89:D90"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="C83:D85"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C77:D80"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="C62:D63"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="C65:D66"/>
+    <mergeCell ref="E65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="C69:D70"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="C59:D61"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C53:D56"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="C45:D46"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="C35:D37"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B3:H3"/>
@@ -16058,87 +16113,6 @@
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="C35:D37"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="C41:D42"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="C45:D46"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C53:D56"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="C59:D61"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="C62:D63"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="C65:D66"/>
-    <mergeCell ref="E65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="C69:D70"/>
-    <mergeCell ref="E69:G69"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C77:D80"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="C83:D85"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="C86:D87"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="C89:D90"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="C93:D94"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="F95:G95"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="76" orientation="portrait" r:id="rId1"/>
@@ -16167,14 +16141,14 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="358" t="s">
+      <c r="B1" s="320" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="358"/>
-      <c r="D1" s="358"/>
-      <c r="E1" s="358"/>
-      <c r="F1" s="358"/>
-      <c r="G1" s="358"/>
+      <c r="C1" s="320"/>
+      <c r="D1" s="320"/>
+      <c r="E1" s="320"/>
+      <c r="F1" s="320"/>
+      <c r="G1" s="320"/>
       <c r="K1" s="51"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1">
@@ -16205,69 +16179,69 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="358" t="s">
+      <c r="B3" s="320" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="358"/>
-      <c r="D3" s="358"/>
-      <c r="E3" s="358"/>
-      <c r="F3" s="358"/>
-      <c r="G3" s="358"/>
+      <c r="C3" s="320"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="320"/>
+      <c r="G3" s="320"/>
       <c r="K3" s="51"/>
     </row>
     <row r="4" spans="1:11" ht="14.25" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="360" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="360"/>
-      <c r="D4" s="360"/>
-      <c r="E4" s="360"/>
-      <c r="F4" s="360"/>
-      <c r="G4" s="360"/>
+      <c r="B4" s="322" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="322"/>
+      <c r="D4" s="322"/>
+      <c r="E4" s="322"/>
+      <c r="F4" s="322"/>
+      <c r="G4" s="322"/>
       <c r="K4" s="51"/>
     </row>
     <row r="5" spans="1:11" ht="24.75" customHeight="1">
       <c r="A5" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="361" t="s">
+      <c r="B5" s="323" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="361"/>
-      <c r="D5" s="361"/>
-      <c r="E5" s="361"/>
-      <c r="F5" s="361"/>
-      <c r="G5" s="361"/>
+      <c r="C5" s="323"/>
+      <c r="D5" s="323"/>
+      <c r="E5" s="323"/>
+      <c r="F5" s="323"/>
+      <c r="G5" s="323"/>
       <c r="K5" s="51"/>
     </row>
     <row r="6" spans="1:11" ht="12" customHeight="1">
       <c r="A6" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="361" t="s">
+      <c r="B6" s="323" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="361"/>
-      <c r="D6" s="361"/>
-      <c r="E6" s="361"/>
-      <c r="F6" s="361"/>
-      <c r="G6" s="361"/>
+      <c r="C6" s="323"/>
+      <c r="D6" s="323"/>
+      <c r="E6" s="323"/>
+      <c r="F6" s="323"/>
+      <c r="G6" s="323"/>
       <c r="K6" s="51"/>
     </row>
     <row r="7" spans="1:11" ht="12" customHeight="1">
       <c r="A7" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="362" t="s">
+      <c r="B7" s="324" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="362"/>
-      <c r="D7" s="362"/>
-      <c r="E7" s="362"/>
-      <c r="F7" s="362"/>
+      <c r="C7" s="324"/>
+      <c r="D7" s="324"/>
+      <c r="E7" s="324"/>
+      <c r="F7" s="324"/>
       <c r="G7" s="71" t="s">
         <v>50</v>
       </c>
@@ -16291,37 +16265,37 @@
       <c r="A22" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="363" t="s">
+      <c r="B22" s="325" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="366" t="s">
+      <c r="C22" s="328" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="367"/>
-      <c r="E22" s="367"/>
-      <c r="F22" s="368"/>
+      <c r="D22" s="329"/>
+      <c r="E22" s="329"/>
+      <c r="F22" s="330"/>
       <c r="G22" s="55"/>
     </row>
     <row r="23" spans="1:12" ht="12" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="364"/>
-      <c r="C23" s="369"/>
-      <c r="D23" s="370"/>
-      <c r="E23" s="370"/>
-      <c r="F23" s="371"/>
+      <c r="B23" s="326"/>
+      <c r="C23" s="331"/>
+      <c r="D23" s="332"/>
+      <c r="E23" s="332"/>
+      <c r="F23" s="333"/>
       <c r="G23" s="55"/>
     </row>
     <row r="24" spans="1:12" ht="24" customHeight="1">
       <c r="A24" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="365"/>
-      <c r="C24" s="372"/>
-      <c r="D24" s="373"/>
-      <c r="E24" s="373"/>
-      <c r="F24" s="374"/>
+      <c r="B24" s="327"/>
+      <c r="C24" s="334"/>
+      <c r="D24" s="335"/>
+      <c r="E24" s="335"/>
+      <c r="F24" s="336"/>
       <c r="G24" s="57" t="s">
         <v>52</v>
       </c>
@@ -16342,10 +16316,10 @@
       <c r="D28" s="57">
         <v>3</v>
       </c>
-      <c r="E28" s="384">
+      <c r="E28" s="376">
         <v>4</v>
       </c>
-      <c r="F28" s="385"/>
+      <c r="F28" s="377"/>
       <c r="G28" s="57">
         <v>8</v>
       </c>
@@ -16357,12 +16331,12 @@
       <c r="B29" s="58">
         <v>1</v>
       </c>
-      <c r="C29" s="324" t="s">
+      <c r="C29" s="337" t="s">
         <v>184</v>
       </c>
-      <c r="D29" s="325"/>
-      <c r="E29" s="325"/>
-      <c r="F29" s="325"/>
+      <c r="D29" s="338"/>
+      <c r="E29" s="338"/>
+      <c r="F29" s="338"/>
       <c r="G29" s="72" t="e">
         <f>SUM(G30:G77)</f>
         <v>#REF!</v>
@@ -16382,11 +16356,11 @@
       <c r="C30" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="324" t="s">
+      <c r="D30" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="325"/>
-      <c r="F30" s="325"/>
+      <c r="E30" s="338"/>
+      <c r="F30" s="338"/>
       <c r="G30" s="74"/>
       <c r="L30" s="53" t="e">
         <f>G29-L29</f>
@@ -16406,10 +16380,10 @@
       <c r="D31" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="337" t="s">
+      <c r="E31" s="356" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="338"/>
+      <c r="F31" s="357"/>
       <c r="G31" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16429,10 +16403,10 @@
       <c r="D32" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="337" t="s">
+      <c r="E32" s="356" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="338"/>
+      <c r="F32" s="357"/>
       <c r="G32" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16452,10 +16426,10 @@
       <c r="D33" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E33" s="337" t="s">
+      <c r="E33" s="356" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="338"/>
+      <c r="F33" s="357"/>
       <c r="G33" s="74"/>
     </row>
     <row r="34" spans="1:13" ht="12" customHeight="1">
@@ -16512,10 +16486,10 @@
       <c r="D36" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E36" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="321"/>
+      <c r="E36" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="347"/>
       <c r="G36" s="74"/>
       <c r="H36" s="49"/>
     </row>
@@ -16529,11 +16503,11 @@
       <c r="C37" s="73" t="s">
         <v>171</v>
       </c>
-      <c r="D37" s="324" t="s">
+      <c r="D37" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E37" s="325"/>
-      <c r="F37" s="325"/>
+      <c r="E37" s="338"/>
+      <c r="F37" s="338"/>
       <c r="G37" s="74"/>
     </row>
     <row r="38" spans="1:13" ht="12" customHeight="1">
@@ -16549,10 +16523,10 @@
       <c r="D38" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E38" s="337" t="s">
+      <c r="E38" s="356" t="s">
         <v>172</v>
       </c>
-      <c r="F38" s="338"/>
+      <c r="F38" s="357"/>
       <c r="G38" s="74" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -16572,10 +16546,10 @@
       <c r="D39" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="337" t="s">
+      <c r="E39" s="356" t="s">
         <v>173</v>
       </c>
-      <c r="F39" s="338"/>
+      <c r="F39" s="357"/>
       <c r="G39" s="74"/>
     </row>
     <row r="40" spans="1:13" ht="12" customHeight="1">
@@ -16585,14 +16559,14 @@
       <c r="B40" s="58">
         <v>26</v>
       </c>
-      <c r="C40" s="333" t="s">
+      <c r="C40" s="340" t="s">
         <v>174</v>
       </c>
-      <c r="D40" s="324" t="s">
+      <c r="D40" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E40" s="325"/>
-      <c r="F40" s="325"/>
+      <c r="E40" s="338"/>
+      <c r="F40" s="338"/>
       <c r="G40" s="74"/>
     </row>
     <row r="41" spans="1:13" ht="12" customHeight="1">
@@ -16602,14 +16576,14 @@
       <c r="B41" s="58">
         <v>27</v>
       </c>
-      <c r="C41" s="334"/>
+      <c r="C41" s="341"/>
       <c r="D41" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="F41" s="387"/>
+      <c r="E41" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="386"/>
       <c r="G41" s="74"/>
     </row>
     <row r="42" spans="1:13" ht="12" customHeight="1">
@@ -16625,10 +16599,10 @@
       <c r="D42" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E42" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="321"/>
+      <c r="E42" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" s="347"/>
       <c r="G42" s="74"/>
       <c r="H42" s="49"/>
     </row>
@@ -16639,14 +16613,14 @@
       <c r="B43" s="58">
         <v>29</v>
       </c>
-      <c r="C43" s="333" t="s">
+      <c r="C43" s="340" t="s">
         <v>186</v>
       </c>
-      <c r="D43" s="324" t="s">
+      <c r="D43" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="325"/>
-      <c r="F43" s="325"/>
+      <c r="E43" s="338"/>
+      <c r="F43" s="338"/>
       <c r="G43" s="74"/>
     </row>
     <row r="44" spans="1:13" ht="12" customHeight="1">
@@ -16656,14 +16630,14 @@
       <c r="B44" s="58">
         <v>30</v>
       </c>
-      <c r="C44" s="334"/>
+      <c r="C44" s="341"/>
       <c r="D44" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E44" s="320" t="s">
+      <c r="E44" s="346" t="s">
         <v>128</v>
       </c>
-      <c r="F44" s="321"/>
+      <c r="F44" s="347"/>
       <c r="G44" s="74"/>
     </row>
     <row r="45" spans="1:13" ht="18.75" customHeight="1">
@@ -16673,14 +16647,14 @@
       <c r="B45" s="58">
         <v>31</v>
       </c>
-      <c r="C45" s="350"/>
+      <c r="C45" s="342"/>
       <c r="D45" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E45" s="390" t="s">
+      <c r="E45" s="387" t="s">
         <v>129</v>
       </c>
-      <c r="F45" s="391"/>
+      <c r="F45" s="388"/>
       <c r="G45" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16695,12 +16669,12 @@
       <c r="B46" s="58">
         <v>32</v>
       </c>
-      <c r="C46" s="324" t="s">
+      <c r="C46" s="337" t="s">
         <v>20</v>
       </c>
-      <c r="D46" s="325"/>
-      <c r="E46" s="325"/>
-      <c r="F46" s="325"/>
+      <c r="D46" s="338"/>
+      <c r="E46" s="338"/>
+      <c r="F46" s="338"/>
       <c r="G46" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16717,11 +16691,11 @@
       <c r="C47" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="D47" s="324" t="s">
+      <c r="D47" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E47" s="325"/>
-      <c r="F47" s="325"/>
+      <c r="E47" s="338"/>
+      <c r="F47" s="338"/>
       <c r="G47" s="74"/>
       <c r="L47" s="53"/>
     </row>
@@ -16738,10 +16712,10 @@
       <c r="D48" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E48" s="337" t="s">
+      <c r="E48" s="356" t="s">
         <v>63</v>
       </c>
-      <c r="F48" s="338"/>
+      <c r="F48" s="357"/>
       <c r="G48" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16760,10 +16734,10 @@
       <c r="D49" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E49" s="337" t="s">
+      <c r="E49" s="356" t="s">
         <v>64</v>
       </c>
-      <c r="F49" s="338"/>
+      <c r="F49" s="357"/>
       <c r="G49" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16776,14 +16750,14 @@
       <c r="B50" s="58">
         <v>36</v>
       </c>
-      <c r="C50" s="333" t="s">
+      <c r="C50" s="340" t="s">
         <v>187</v>
       </c>
-      <c r="D50" s="324" t="s">
+      <c r="D50" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E50" s="325"/>
-      <c r="F50" s="325"/>
+      <c r="E50" s="338"/>
+      <c r="F50" s="338"/>
       <c r="G50" s="74"/>
     </row>
     <row r="51" spans="1:8" ht="12" customHeight="1">
@@ -16793,14 +16767,14 @@
       <c r="B51" s="58">
         <v>37</v>
       </c>
-      <c r="C51" s="334"/>
+      <c r="C51" s="341"/>
       <c r="D51" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E51" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="387"/>
+      <c r="E51" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="386"/>
       <c r="G51" s="74"/>
     </row>
     <row r="52" spans="1:8" ht="24.75" customHeight="1">
@@ -16816,10 +16790,10 @@
       <c r="D52" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E52" s="320" t="s">
+      <c r="E52" s="346" t="s">
         <v>188</v>
       </c>
-      <c r="F52" s="321"/>
+      <c r="F52" s="347"/>
       <c r="G52" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16833,12 +16807,12 @@
       <c r="B53" s="58">
         <v>43</v>
       </c>
-      <c r="C53" s="324" t="s">
+      <c r="C53" s="337" t="s">
         <v>16</v>
       </c>
-      <c r="D53" s="325"/>
-      <c r="E53" s="325"/>
-      <c r="F53" s="325"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
       <c r="G53" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16851,12 +16825,12 @@
       <c r="B54" s="58">
         <v>44</v>
       </c>
-      <c r="C54" s="324" t="s">
+      <c r="C54" s="337" t="s">
         <v>14</v>
       </c>
-      <c r="D54" s="325"/>
-      <c r="E54" s="325"/>
-      <c r="F54" s="325"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
       <c r="G54" s="74"/>
     </row>
     <row r="55" spans="1:8" ht="12" customHeight="1">
@@ -16869,11 +16843,11 @@
       <c r="C55" s="73" t="s">
         <v>137</v>
       </c>
-      <c r="D55" s="324" t="s">
+      <c r="D55" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="325"/>
-      <c r="F55" s="325"/>
+      <c r="E55" s="338"/>
+      <c r="F55" s="338"/>
       <c r="G55" s="74"/>
     </row>
     <row r="56" spans="1:8" ht="12" customHeight="1">
@@ -16889,10 +16863,10 @@
       <c r="D56" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="F56" s="387"/>
+      <c r="E56" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" s="386"/>
       <c r="G56" s="74"/>
     </row>
     <row r="57" spans="1:8" ht="24.75" customHeight="1">
@@ -16908,10 +16882,10 @@
       <c r="D57" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="320" t="s">
+      <c r="E57" s="346" t="s">
         <v>4</v>
       </c>
-      <c r="F57" s="321"/>
+      <c r="F57" s="347"/>
       <c r="G57" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16931,10 +16905,10 @@
       <c r="D58" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F58" s="321"/>
+      <c r="E58" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F58" s="347"/>
       <c r="G58" s="74"/>
       <c r="H58" s="49"/>
     </row>
@@ -16945,12 +16919,12 @@
       <c r="B59" s="58">
         <v>51</v>
       </c>
-      <c r="C59" s="324" t="s">
+      <c r="C59" s="337" t="s">
         <v>189</v>
       </c>
-      <c r="D59" s="325"/>
-      <c r="E59" s="325"/>
-      <c r="F59" s="325"/>
+      <c r="D59" s="338"/>
+      <c r="E59" s="338"/>
+      <c r="F59" s="338"/>
       <c r="G59" s="74"/>
     </row>
     <row r="60" spans="1:8" ht="12" customHeight="1">
@@ -16960,12 +16934,12 @@
       <c r="B60" s="58">
         <v>52</v>
       </c>
-      <c r="C60" s="324" t="s">
+      <c r="C60" s="337" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="325"/>
-      <c r="E60" s="325"/>
-      <c r="F60" s="325"/>
+      <c r="D60" s="338"/>
+      <c r="E60" s="338"/>
+      <c r="F60" s="338"/>
       <c r="G60" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16978,12 +16952,12 @@
       <c r="B61" s="58">
         <v>53</v>
       </c>
-      <c r="C61" s="324" t="s">
+      <c r="C61" s="337" t="s">
         <v>190</v>
       </c>
-      <c r="D61" s="325"/>
-      <c r="E61" s="325"/>
-      <c r="F61" s="325"/>
+      <c r="D61" s="338"/>
+      <c r="E61" s="338"/>
+      <c r="F61" s="338"/>
       <c r="G61" s="74"/>
     </row>
     <row r="62" spans="1:8" ht="12" customHeight="1">
@@ -16993,12 +16967,12 @@
       <c r="B62" s="58">
         <v>54</v>
       </c>
-      <c r="C62" s="324" t="s">
+      <c r="C62" s="337" t="s">
         <v>191</v>
       </c>
-      <c r="D62" s="325"/>
-      <c r="E62" s="325"/>
-      <c r="F62" s="325"/>
+      <c r="D62" s="338"/>
+      <c r="E62" s="338"/>
+      <c r="F62" s="338"/>
       <c r="G62" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17011,12 +16985,12 @@
       <c r="B63" s="58">
         <v>55</v>
       </c>
-      <c r="C63" s="324" t="s">
+      <c r="C63" s="337" t="s">
         <v>192</v>
       </c>
-      <c r="D63" s="325"/>
-      <c r="E63" s="325"/>
-      <c r="F63" s="325"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
       <c r="G63" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17029,14 +17003,14 @@
       <c r="B64" s="58">
         <v>56</v>
       </c>
-      <c r="C64" s="333" t="s">
+      <c r="C64" s="340" t="s">
         <v>175</v>
       </c>
-      <c r="D64" s="324" t="s">
+      <c r="D64" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E64" s="325"/>
-      <c r="F64" s="325"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
       <c r="G64" s="74"/>
     </row>
     <row r="65" spans="1:11" ht="12" customHeight="1">
@@ -17046,14 +17020,14 @@
       <c r="B65" s="58">
         <v>57</v>
       </c>
-      <c r="C65" s="334"/>
+      <c r="C65" s="341"/>
       <c r="D65" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E65" s="337" t="s">
+      <c r="E65" s="356" t="s">
         <v>91</v>
       </c>
-      <c r="F65" s="338"/>
+      <c r="F65" s="357"/>
       <c r="G65" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17072,10 +17046,10 @@
       <c r="D66" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E66" s="320" t="s">
+      <c r="E66" s="346" t="s">
         <v>193</v>
       </c>
-      <c r="F66" s="321"/>
+      <c r="F66" s="347"/>
       <c r="G66" s="74"/>
       <c r="H66" s="49"/>
     </row>
@@ -17086,14 +17060,14 @@
       <c r="B67" s="58">
         <v>59</v>
       </c>
-      <c r="C67" s="333" t="s">
+      <c r="C67" s="340" t="s">
         <v>102</v>
       </c>
-      <c r="D67" s="324" t="s">
+      <c r="D67" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E67" s="325"/>
-      <c r="F67" s="325"/>
+      <c r="E67" s="338"/>
+      <c r="F67" s="338"/>
       <c r="G67" s="74"/>
     </row>
     <row r="68" spans="1:11" ht="12" customHeight="1">
@@ -17103,14 +17077,14 @@
       <c r="B68" s="58">
         <v>60</v>
       </c>
-      <c r="C68" s="334"/>
+      <c r="C68" s="341"/>
       <c r="D68" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E68" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="F68" s="387"/>
+      <c r="E68" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="F68" s="386"/>
       <c r="G68" s="74"/>
     </row>
     <row r="69" spans="1:11" ht="12" customHeight="1">
@@ -17126,10 +17100,10 @@
       <c r="D69" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E69" s="320" t="s">
+      <c r="E69" s="346" t="s">
         <v>194</v>
       </c>
-      <c r="F69" s="321"/>
+      <c r="F69" s="347"/>
       <c r="G69" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17149,10 +17123,10 @@
       <c r="D70" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E70" s="320" t="s">
+      <c r="E70" s="346" t="s">
         <v>195</v>
       </c>
-      <c r="F70" s="321"/>
+      <c r="F70" s="347"/>
       <c r="G70" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17172,10 +17146,10 @@
       <c r="D71" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E71" s="388" t="s">
+      <c r="E71" s="389" t="s">
         <v>196</v>
       </c>
-      <c r="F71" s="389"/>
+      <c r="F71" s="390"/>
       <c r="G71" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17187,10 +17161,10 @@
       <c r="B72" s="58"/>
       <c r="C72" s="77"/>
       <c r="D72" s="70"/>
-      <c r="E72" s="388" t="s">
+      <c r="E72" s="389" t="s">
         <v>13</v>
       </c>
-      <c r="F72" s="389"/>
+      <c r="F72" s="390"/>
       <c r="G72" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17202,10 +17176,10 @@
       <c r="B73" s="58"/>
       <c r="C73" s="77"/>
       <c r="D73" s="70"/>
-      <c r="E73" s="388" t="s">
+      <c r="E73" s="389" t="s">
         <v>8</v>
       </c>
-      <c r="F73" s="389"/>
+      <c r="F73" s="390"/>
       <c r="G73" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17225,10 +17199,10 @@
       <c r="D74" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E74" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F74" s="321"/>
+      <c r="E74" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F74" s="347"/>
       <c r="G74" s="74"/>
       <c r="H74" s="49"/>
     </row>
@@ -17239,14 +17213,14 @@
       <c r="B75" s="58">
         <v>65</v>
       </c>
-      <c r="C75" s="333" t="s">
+      <c r="C75" s="340" t="s">
         <v>197</v>
       </c>
-      <c r="D75" s="324" t="s">
+      <c r="D75" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E75" s="325"/>
-      <c r="F75" s="325"/>
+      <c r="E75" s="338"/>
+      <c r="F75" s="338"/>
       <c r="G75" s="74"/>
     </row>
     <row r="76" spans="1:11" ht="12" customHeight="1">
@@ -17256,14 +17230,14 @@
       <c r="B76" s="58">
         <v>66</v>
       </c>
-      <c r="C76" s="334"/>
+      <c r="C76" s="341"/>
       <c r="D76" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E76" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="F76" s="387"/>
+      <c r="E76" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="F76" s="386"/>
       <c r="G76" s="74"/>
     </row>
     <row r="77" spans="1:11" ht="12" customHeight="1">
@@ -17279,10 +17253,10 @@
       <c r="D77" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E77" s="320" t="s">
+      <c r="E77" s="346" t="s">
         <v>198</v>
       </c>
-      <c r="F77" s="321"/>
+      <c r="F77" s="347"/>
       <c r="G77" s="81" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -17341,13 +17315,13 @@
       <c r="K79" s="51"/>
     </row>
     <row r="80" spans="1:11" ht="15" customHeight="1">
-      <c r="B80" s="386" t="s">
+      <c r="B80" s="391" t="s">
         <v>199</v>
       </c>
-      <c r="C80" s="386"/>
-      <c r="D80" s="386"/>
-      <c r="E80" s="386"/>
-      <c r="F80" s="386"/>
+      <c r="C80" s="391"/>
+      <c r="D80" s="391"/>
+      <c r="E80" s="391"/>
+      <c r="F80" s="391"/>
       <c r="G80" s="83"/>
       <c r="H80" s="83"/>
       <c r="I80" s="82"/>
@@ -17355,13 +17329,13 @@
       <c r="K80" s="51"/>
     </row>
     <row r="81" spans="2:11" ht="15" customHeight="1">
-      <c r="B81" s="386" t="s">
-        <v>44</v>
-      </c>
-      <c r="C81" s="386"/>
-      <c r="D81" s="386"/>
-      <c r="E81" s="386"/>
-      <c r="F81" s="386"/>
+      <c r="B81" s="391" t="s">
+        <v>44</v>
+      </c>
+      <c r="C81" s="391"/>
+      <c r="D81" s="391"/>
+      <c r="E81" s="391"/>
+      <c r="F81" s="391"/>
       <c r="G81" s="84"/>
       <c r="H81" s="84"/>
       <c r="I81" s="83"/>
@@ -17371,14 +17345,14 @@
     <row r="82" spans="2:11" ht="15.75" hidden="1" customHeight="1"/>
     <row r="83" spans="2:11" ht="15.75" hidden="1" customHeight="1"/>
     <row r="84" spans="2:11" ht="15" customHeight="1">
-      <c r="B84" s="386" t="s">
+      <c r="B84" s="391" t="s">
         <v>200</v>
       </c>
-      <c r="C84" s="386"/>
-      <c r="D84" s="386"/>
-      <c r="E84" s="386"/>
-      <c r="F84" s="386"/>
-      <c r="G84" s="386"/>
+      <c r="C84" s="391"/>
+      <c r="D84" s="391"/>
+      <c r="E84" s="391"/>
+      <c r="F84" s="391"/>
+      <c r="G84" s="391"/>
       <c r="H84" s="83"/>
       <c r="I84" s="83"/>
       <c r="J84" s="83"/>
@@ -17407,51 +17381,13 @@
     <row r="105" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:F24"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="C63:F63"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="C53:F53"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C59:F59"/>
-    <mergeCell ref="C60:F60"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="B84:G84"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
     <mergeCell ref="E74:F74"/>
     <mergeCell ref="C64:C65"/>
     <mergeCell ref="D64:F64"/>
@@ -17465,13 +17401,51 @@
     <mergeCell ref="E71:F71"/>
     <mergeCell ref="E72:F72"/>
     <mergeCell ref="E73:F73"/>
-    <mergeCell ref="B84:G84"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C59:F59"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:F24"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Наименование на государственном языке заполняется автоматически в соответствии с КТРУ" sqref="B76 B49:B50 B95:B96"/>
@@ -17507,79 +17481,79 @@
       <c r="A1" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="400" t="s">
+      <c r="B1" s="431" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="400"/>
-      <c r="D1" s="400"/>
-      <c r="E1" s="400"/>
-      <c r="F1" s="400"/>
-      <c r="G1" s="400"/>
-      <c r="H1" s="400"/>
-      <c r="I1" s="400"/>
+      <c r="C1" s="431"/>
+      <c r="D1" s="431"/>
+      <c r="E1" s="431"/>
+      <c r="F1" s="431"/>
+      <c r="G1" s="431"/>
+      <c r="H1" s="431"/>
+      <c r="I1" s="431"/>
       <c r="M1" s="12"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1">
       <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="401" t="s">
+      <c r="B2" s="432" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="401"/>
-      <c r="D2" s="401"/>
-      <c r="E2" s="401"/>
-      <c r="F2" s="401"/>
-      <c r="G2" s="401"/>
-      <c r="H2" s="401"/>
-      <c r="I2" s="401"/>
+      <c r="C2" s="432"/>
+      <c r="D2" s="432"/>
+      <c r="E2" s="432"/>
+      <c r="F2" s="432"/>
+      <c r="G2" s="432"/>
+      <c r="H2" s="432"/>
+      <c r="I2" s="432"/>
       <c r="M2" s="12"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="402" t="s">
+      <c r="B3" s="433" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="402"/>
-      <c r="D3" s="402"/>
-      <c r="E3" s="402"/>
-      <c r="F3" s="402"/>
-      <c r="G3" s="402"/>
-      <c r="H3" s="402"/>
-      <c r="I3" s="402"/>
+      <c r="C3" s="433"/>
+      <c r="D3" s="433"/>
+      <c r="E3" s="433"/>
+      <c r="F3" s="433"/>
+      <c r="G3" s="433"/>
+      <c r="H3" s="433"/>
+      <c r="I3" s="433"/>
       <c r="M3" s="12"/>
     </row>
     <row r="4" spans="1:13" ht="30" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="402" t="s">
+      <c r="B4" s="433" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="402"/>
-      <c r="D4" s="402"/>
-      <c r="E4" s="402"/>
-      <c r="F4" s="402"/>
-      <c r="G4" s="402"/>
-      <c r="H4" s="402"/>
-      <c r="I4" s="402"/>
+      <c r="C4" s="433"/>
+      <c r="D4" s="433"/>
+      <c r="E4" s="433"/>
+      <c r="F4" s="433"/>
+      <c r="G4" s="433"/>
+      <c r="H4" s="433"/>
+      <c r="I4" s="433"/>
       <c r="M4" s="12"/>
     </row>
     <row r="5" spans="1:13" ht="12" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="403" t="s">
+      <c r="B5" s="434" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="403"/>
-      <c r="D5" s="403"/>
-      <c r="E5" s="403"/>
-      <c r="F5" s="403"/>
-      <c r="G5" s="403"/>
-      <c r="H5" s="403"/>
+      <c r="C5" s="434"/>
+      <c r="D5" s="434"/>
+      <c r="E5" s="434"/>
+      <c r="F5" s="434"/>
+      <c r="G5" s="434"/>
+      <c r="H5" s="434"/>
       <c r="I5" s="13" t="s">
         <v>50</v>
       </c>
@@ -17603,18 +17577,18 @@
       <c r="A20" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="404" t="s">
+      <c r="B20" s="435" t="s">
         <v>0</v>
       </c>
-      <c r="C20" s="407" t="s">
+      <c r="C20" s="438" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="408"/>
-      <c r="E20" s="408"/>
-      <c r="F20" s="408"/>
-      <c r="G20" s="408"/>
-      <c r="H20" s="409"/>
-      <c r="I20" s="416" t="s">
+      <c r="D20" s="439"/>
+      <c r="E20" s="439"/>
+      <c r="F20" s="439"/>
+      <c r="G20" s="439"/>
+      <c r="H20" s="440"/>
+      <c r="I20" s="447" t="s">
         <v>52</v>
       </c>
       <c r="J20" s="10"/>
@@ -17627,14 +17601,14 @@
       <c r="A21" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="405"/>
-      <c r="C21" s="410"/>
-      <c r="D21" s="411"/>
-      <c r="E21" s="411"/>
-      <c r="F21" s="411"/>
-      <c r="G21" s="411"/>
-      <c r="H21" s="412"/>
-      <c r="I21" s="405"/>
+      <c r="B21" s="436"/>
+      <c r="C21" s="441"/>
+      <c r="D21" s="442"/>
+      <c r="E21" s="442"/>
+      <c r="F21" s="442"/>
+      <c r="G21" s="442"/>
+      <c r="H21" s="443"/>
+      <c r="I21" s="436"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
@@ -17644,14 +17618,14 @@
       <c r="A22" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="406"/>
-      <c r="C22" s="413"/>
-      <c r="D22" s="414"/>
-      <c r="E22" s="414"/>
-      <c r="F22" s="414"/>
-      <c r="G22" s="414"/>
-      <c r="H22" s="415"/>
-      <c r="I22" s="406"/>
+      <c r="B22" s="437"/>
+      <c r="C22" s="444"/>
+      <c r="D22" s="445"/>
+      <c r="E22" s="445"/>
+      <c r="F22" s="445"/>
+      <c r="G22" s="445"/>
+      <c r="H22" s="446"/>
+      <c r="I22" s="437"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
@@ -17667,10 +17641,10 @@
       <c r="B26" s="18">
         <v>1</v>
       </c>
-      <c r="C26" s="392">
+      <c r="C26" s="429">
         <v>2</v>
       </c>
-      <c r="D26" s="393"/>
+      <c r="D26" s="430"/>
       <c r="E26" s="18">
         <v>3</v>
       </c>
@@ -17694,14 +17668,14 @@
       <c r="B27" s="19">
         <v>1</v>
       </c>
-      <c r="C27" s="394" t="s">
+      <c r="C27" s="395" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="395"/>
-      <c r="E27" s="395"/>
-      <c r="F27" s="395"/>
-      <c r="G27" s="395"/>
-      <c r="H27" s="396"/>
+      <c r="D27" s="396"/>
+      <c r="E27" s="396"/>
+      <c r="F27" s="396"/>
+      <c r="G27" s="396"/>
+      <c r="H27" s="397"/>
       <c r="I27" s="20"/>
       <c r="N27" s="16"/>
     </row>
@@ -17718,12 +17692,12 @@
       <c r="D28" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="394" t="s">
+      <c r="E28" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F28" s="395"/>
-      <c r="G28" s="395"/>
-      <c r="H28" s="396"/>
+      <c r="F28" s="396"/>
+      <c r="G28" s="396"/>
+      <c r="H28" s="397"/>
       <c r="I28" s="20" t="e">
         <f>SUM(I29:I190)</f>
         <v>#REF!</v>
@@ -17749,11 +17723,11 @@
       <c r="E29" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="397" t="s">
+      <c r="F29" s="402" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="398"/>
-      <c r="H29" s="399"/>
+      <c r="G29" s="403"/>
+      <c r="H29" s="404"/>
       <c r="I29" s="20" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17779,11 +17753,11 @@
       <c r="E30" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="397" t="s">
+      <c r="F30" s="402" t="s">
         <v>57</v>
       </c>
-      <c r="G30" s="398"/>
-      <c r="H30" s="399"/>
+      <c r="G30" s="403"/>
+      <c r="H30" s="404"/>
       <c r="I30" s="20" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17806,11 +17780,11 @@
       <c r="E31" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="397" t="s">
+      <c r="F31" s="402" t="s">
         <v>58</v>
       </c>
-      <c r="G31" s="398"/>
-      <c r="H31" s="399"/>
+      <c r="G31" s="403"/>
+      <c r="H31" s="404"/>
       <c r="I31" s="20"/>
     </row>
     <row r="32" spans="1:14" ht="12" customHeight="1">
@@ -17829,11 +17803,11 @@
       <c r="E32" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="417" t="s">
+      <c r="F32" s="392" t="s">
         <v>59</v>
       </c>
-      <c r="G32" s="418"/>
-      <c r="H32" s="419"/>
+      <c r="G32" s="393"/>
+      <c r="H32" s="394"/>
       <c r="I32" s="20" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -17859,16 +17833,16 @@
       <c r="B34" s="21">
         <v>7</v>
       </c>
-      <c r="C34" s="420" t="s">
+      <c r="C34" s="398" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="421"/>
-      <c r="E34" s="394" t="s">
+      <c r="D34" s="399"/>
+      <c r="E34" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="395"/>
-      <c r="G34" s="395"/>
-      <c r="H34" s="396"/>
+      <c r="F34" s="396"/>
+      <c r="G34" s="396"/>
+      <c r="H34" s="397"/>
       <c r="I34" s="32"/>
     </row>
     <row r="35" spans="1:15" ht="12" customHeight="1">
@@ -17878,16 +17852,16 @@
       <c r="B35" s="21">
         <v>8</v>
       </c>
-      <c r="C35" s="422"/>
-      <c r="D35" s="423"/>
+      <c r="C35" s="400"/>
+      <c r="D35" s="401"/>
       <c r="E35" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F35" s="397" t="s">
-        <v>44</v>
-      </c>
-      <c r="G35" s="398"/>
-      <c r="H35" s="399"/>
+      <c r="F35" s="402" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" s="403"/>
+      <c r="H35" s="404"/>
       <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:15" hidden="1">
@@ -17900,16 +17874,16 @@
       <c r="B37" s="21">
         <v>10</v>
       </c>
-      <c r="C37" s="424" t="s">
+      <c r="C37" s="408" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="425"/>
-      <c r="E37" s="394" t="s">
+      <c r="D37" s="409"/>
+      <c r="E37" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F37" s="395"/>
-      <c r="G37" s="395"/>
-      <c r="H37" s="396"/>
+      <c r="F37" s="396"/>
+      <c r="G37" s="396"/>
+      <c r="H37" s="397"/>
       <c r="I37" s="32"/>
     </row>
     <row r="38" spans="1:15" ht="12" customHeight="1">
@@ -17919,16 +17893,16 @@
       <c r="B38" s="21">
         <v>11</v>
       </c>
-      <c r="C38" s="426"/>
-      <c r="D38" s="427"/>
-      <c r="E38" s="430" t="s">
+      <c r="C38" s="410"/>
+      <c r="D38" s="411"/>
+      <c r="E38" s="414" t="s">
         <v>55</v>
       </c>
-      <c r="F38" s="397" t="s">
+      <c r="F38" s="402" t="s">
         <v>63</v>
       </c>
-      <c r="G38" s="398"/>
-      <c r="H38" s="399"/>
+      <c r="G38" s="403"/>
+      <c r="H38" s="404"/>
       <c r="I38" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17941,14 +17915,14 @@
       <c r="B39" s="21">
         <v>12</v>
       </c>
-      <c r="C39" s="428"/>
-      <c r="D39" s="429"/>
-      <c r="E39" s="431"/>
-      <c r="F39" s="397" t="s">
+      <c r="C39" s="412"/>
+      <c r="D39" s="413"/>
+      <c r="E39" s="415"/>
+      <c r="F39" s="402" t="s">
         <v>64</v>
       </c>
-      <c r="G39" s="398"/>
-      <c r="H39" s="399"/>
+      <c r="G39" s="403"/>
+      <c r="H39" s="404"/>
       <c r="I39" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17961,16 +17935,16 @@
       <c r="B40" s="21">
         <v>13</v>
       </c>
-      <c r="C40" s="420" t="s">
+      <c r="C40" s="398" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="421"/>
-      <c r="E40" s="394" t="s">
+      <c r="D40" s="399"/>
+      <c r="E40" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F40" s="395"/>
-      <c r="G40" s="395"/>
-      <c r="H40" s="396"/>
+      <c r="F40" s="396"/>
+      <c r="G40" s="396"/>
+      <c r="H40" s="397"/>
       <c r="I40" s="32"/>
     </row>
     <row r="41" spans="1:15" ht="17.25" customHeight="1">
@@ -17980,16 +17954,16 @@
       <c r="B41" s="21">
         <v>14</v>
       </c>
-      <c r="C41" s="422"/>
-      <c r="D41" s="423"/>
+      <c r="C41" s="400"/>
+      <c r="D41" s="401"/>
       <c r="E41" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F41" s="397" t="s">
-        <v>44</v>
-      </c>
-      <c r="G41" s="398"/>
-      <c r="H41" s="399"/>
+      <c r="F41" s="402" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" s="403"/>
+      <c r="H41" s="404"/>
       <c r="I41" s="32"/>
     </row>
     <row r="42" spans="1:15" ht="12" customHeight="1">
@@ -18008,11 +17982,11 @@
       <c r="E42" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F42" s="417" t="s">
+      <c r="F42" s="392" t="s">
         <v>66</v>
       </c>
-      <c r="G42" s="418"/>
-      <c r="H42" s="419"/>
+      <c r="G42" s="393"/>
+      <c r="H42" s="394"/>
       <c r="I42" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18029,14 +18003,14 @@
       <c r="B44" s="21">
         <v>17</v>
       </c>
-      <c r="C44" s="394" t="s">
+      <c r="C44" s="395" t="s">
         <v>67</v>
       </c>
-      <c r="D44" s="395"/>
-      <c r="E44" s="395"/>
-      <c r="F44" s="395"/>
-      <c r="G44" s="395"/>
-      <c r="H44" s="396"/>
+      <c r="D44" s="396"/>
+      <c r="E44" s="396"/>
+      <c r="F44" s="396"/>
+      <c r="G44" s="396"/>
+      <c r="H44" s="397"/>
       <c r="I44" s="32"/>
     </row>
     <row r="45" spans="1:15" ht="12" customHeight="1">
@@ -18046,16 +18020,16 @@
       <c r="B45" s="21">
         <v>18</v>
       </c>
-      <c r="C45" s="432" t="s">
+      <c r="C45" s="423" t="s">
         <v>68</v>
       </c>
-      <c r="D45" s="433"/>
-      <c r="E45" s="394" t="s">
+      <c r="D45" s="424"/>
+      <c r="E45" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="395"/>
-      <c r="G45" s="395"/>
-      <c r="H45" s="396"/>
+      <c r="F45" s="396"/>
+      <c r="G45" s="396"/>
+      <c r="H45" s="397"/>
       <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:15" ht="30" customHeight="1">
@@ -18065,16 +18039,16 @@
       <c r="B46" s="21">
         <v>19</v>
       </c>
-      <c r="C46" s="434"/>
-      <c r="D46" s="435"/>
-      <c r="E46" s="430" t="s">
+      <c r="C46" s="425"/>
+      <c r="D46" s="426"/>
+      <c r="E46" s="414" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="397" t="s">
+      <c r="F46" s="402" t="s">
         <v>69</v>
       </c>
-      <c r="G46" s="398"/>
-      <c r="H46" s="399"/>
+      <c r="G46" s="403"/>
+      <c r="H46" s="404"/>
       <c r="I46" s="127" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18089,14 +18063,14 @@
       <c r="B47" s="21">
         <v>20</v>
       </c>
-      <c r="C47" s="434"/>
-      <c r="D47" s="435"/>
-      <c r="E47" s="438"/>
-      <c r="F47" s="397" t="s">
+      <c r="C47" s="425"/>
+      <c r="D47" s="426"/>
+      <c r="E47" s="416"/>
+      <c r="F47" s="402" t="s">
         <v>70</v>
       </c>
-      <c r="G47" s="398"/>
-      <c r="H47" s="399"/>
+      <c r="G47" s="403"/>
+      <c r="H47" s="404"/>
       <c r="I47" s="127" t="e">
         <f>#REF!+#REF!-#REF!</f>
         <v>#REF!</v>
@@ -18111,14 +18085,14 @@
       <c r="B48" s="21">
         <v>21</v>
       </c>
-      <c r="C48" s="434"/>
-      <c r="D48" s="435"/>
-      <c r="E48" s="438"/>
-      <c r="F48" s="397" t="s">
+      <c r="C48" s="425"/>
+      <c r="D48" s="426"/>
+      <c r="E48" s="416"/>
+      <c r="F48" s="402" t="s">
         <v>71</v>
       </c>
-      <c r="G48" s="398"/>
-      <c r="H48" s="399"/>
+      <c r="G48" s="403"/>
+      <c r="H48" s="404"/>
       <c r="I48" s="127" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18132,14 +18106,14 @@
       <c r="B49" s="21">
         <v>22</v>
       </c>
-      <c r="C49" s="436"/>
-      <c r="D49" s="437"/>
-      <c r="E49" s="431"/>
-      <c r="F49" s="397" t="s">
+      <c r="C49" s="427"/>
+      <c r="D49" s="428"/>
+      <c r="E49" s="415"/>
+      <c r="F49" s="402" t="s">
         <v>72</v>
       </c>
-      <c r="G49" s="398"/>
-      <c r="H49" s="399"/>
+      <c r="G49" s="403"/>
+      <c r="H49" s="404"/>
       <c r="I49" s="34" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18153,16 +18127,16 @@
       <c r="B50" s="21">
         <v>23</v>
       </c>
-      <c r="C50" s="439" t="s">
+      <c r="C50" s="419" t="s">
         <v>73</v>
       </c>
-      <c r="D50" s="440"/>
-      <c r="E50" s="394" t="s">
+      <c r="D50" s="420"/>
+      <c r="E50" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F50" s="395"/>
-      <c r="G50" s="395"/>
-      <c r="H50" s="396"/>
+      <c r="F50" s="396"/>
+      <c r="G50" s="396"/>
+      <c r="H50" s="397"/>
       <c r="I50" s="32"/>
     </row>
     <row r="51" spans="1:14" ht="12" customHeight="1">
@@ -18172,16 +18146,16 @@
       <c r="B51" s="21">
         <v>24</v>
       </c>
-      <c r="C51" s="441"/>
-      <c r="D51" s="442"/>
+      <c r="C51" s="421"/>
+      <c r="D51" s="422"/>
       <c r="E51" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="397" t="s">
+      <c r="F51" s="402" t="s">
         <v>23</v>
       </c>
-      <c r="G51" s="398"/>
-      <c r="H51" s="399"/>
+      <c r="G51" s="403"/>
+      <c r="H51" s="404"/>
       <c r="I51" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18204,11 +18178,11 @@
       <c r="E52" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="397" t="s">
+      <c r="F52" s="402" t="s">
         <v>74</v>
       </c>
-      <c r="G52" s="398"/>
-      <c r="H52" s="399"/>
+      <c r="G52" s="403"/>
+      <c r="H52" s="404"/>
       <c r="I52" s="32"/>
       <c r="N52" s="35"/>
     </row>
@@ -18222,16 +18196,16 @@
       <c r="B54" s="21">
         <v>27</v>
       </c>
-      <c r="C54" s="420" t="s">
+      <c r="C54" s="398" t="s">
         <v>75</v>
       </c>
-      <c r="D54" s="421"/>
-      <c r="E54" s="394" t="s">
+      <c r="D54" s="399"/>
+      <c r="E54" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F54" s="395"/>
-      <c r="G54" s="395"/>
-      <c r="H54" s="396"/>
+      <c r="F54" s="396"/>
+      <c r="G54" s="396"/>
+      <c r="H54" s="397"/>
       <c r="I54" s="32"/>
     </row>
     <row r="55" spans="1:14" ht="12" customHeight="1">
@@ -18241,16 +18215,16 @@
       <c r="B55" s="21">
         <v>28</v>
       </c>
-      <c r="C55" s="422"/>
-      <c r="D55" s="423"/>
+      <c r="C55" s="400"/>
+      <c r="D55" s="401"/>
       <c r="E55" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F55" s="397" t="s">
+      <c r="F55" s="402" t="s">
         <v>76</v>
       </c>
-      <c r="G55" s="398"/>
-      <c r="H55" s="399"/>
+      <c r="G55" s="403"/>
+      <c r="H55" s="404"/>
       <c r="I55" s="32"/>
     </row>
     <row r="56" spans="1:14" ht="12" customHeight="1">
@@ -18260,16 +18234,16 @@
       <c r="B56" s="21">
         <v>29</v>
       </c>
-      <c r="C56" s="422"/>
-      <c r="D56" s="423"/>
+      <c r="C56" s="400"/>
+      <c r="D56" s="401"/>
       <c r="E56" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="397" t="s">
+      <c r="F56" s="402" t="s">
         <v>77</v>
       </c>
-      <c r="G56" s="398"/>
-      <c r="H56" s="399"/>
+      <c r="G56" s="403"/>
+      <c r="H56" s="404"/>
       <c r="I56" s="32"/>
     </row>
     <row r="57" spans="1:14" ht="12" customHeight="1">
@@ -18279,16 +18253,16 @@
       <c r="B57" s="21">
         <v>30</v>
       </c>
-      <c r="C57" s="422"/>
-      <c r="D57" s="423"/>
+      <c r="C57" s="400"/>
+      <c r="D57" s="401"/>
       <c r="E57" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="397" t="s">
+      <c r="F57" s="402" t="s">
         <v>78</v>
       </c>
-      <c r="G57" s="398"/>
-      <c r="H57" s="399"/>
+      <c r="G57" s="403"/>
+      <c r="H57" s="404"/>
       <c r="I57" s="32"/>
     </row>
     <row r="58" spans="1:14" ht="12" customHeight="1">
@@ -18307,11 +18281,11 @@
       <c r="E58" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F58" s="397" t="s">
+      <c r="F58" s="402" t="s">
         <v>79</v>
       </c>
-      <c r="G58" s="398"/>
-      <c r="H58" s="399"/>
+      <c r="G58" s="403"/>
+      <c r="H58" s="404"/>
       <c r="I58" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18327,14 +18301,14 @@
       <c r="B60" s="21">
         <v>33</v>
       </c>
-      <c r="C60" s="394" t="s">
+      <c r="C60" s="395" t="s">
         <v>80</v>
       </c>
-      <c r="D60" s="395"/>
-      <c r="E60" s="395"/>
-      <c r="F60" s="395"/>
-      <c r="G60" s="395"/>
-      <c r="H60" s="396"/>
+      <c r="D60" s="396"/>
+      <c r="E60" s="396"/>
+      <c r="F60" s="396"/>
+      <c r="G60" s="396"/>
+      <c r="H60" s="397"/>
       <c r="I60" s="32"/>
     </row>
     <row r="61" spans="1:14" ht="12" customHeight="1">
@@ -18344,16 +18318,16 @@
       <c r="B61" s="21">
         <v>34</v>
       </c>
-      <c r="C61" s="420" t="s">
+      <c r="C61" s="398" t="s">
         <v>81</v>
       </c>
-      <c r="D61" s="421"/>
-      <c r="E61" s="394" t="s">
+      <c r="D61" s="399"/>
+      <c r="E61" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F61" s="395"/>
-      <c r="G61" s="395"/>
-      <c r="H61" s="396"/>
+      <c r="F61" s="396"/>
+      <c r="G61" s="396"/>
+      <c r="H61" s="397"/>
       <c r="I61" s="32"/>
     </row>
     <row r="62" spans="1:14" ht="12" customHeight="1">
@@ -18363,18 +18337,18 @@
       <c r="B62" s="21">
         <v>35</v>
       </c>
-      <c r="C62" s="422"/>
-      <c r="D62" s="423"/>
+      <c r="C62" s="400"/>
+      <c r="D62" s="401"/>
       <c r="E62" s="26" t="s">
         <v>55</v>
       </c>
       <c r="F62" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G62" s="443" t="s">
+      <c r="G62" s="417" t="s">
         <v>5</v>
       </c>
-      <c r="H62" s="444"/>
+      <c r="H62" s="418"/>
       <c r="I62" s="32"/>
     </row>
     <row r="63" spans="1:14" ht="12" customHeight="1">
@@ -18384,8 +18358,8 @@
       <c r="B63" s="21">
         <v>36</v>
       </c>
-      <c r="C63" s="422"/>
-      <c r="D63" s="423"/>
+      <c r="C63" s="400"/>
+      <c r="D63" s="401"/>
       <c r="E63" s="27" t="s">
         <v>44</v>
       </c>
@@ -18449,10 +18423,10 @@
       <c r="F66" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="G66" s="443" t="s">
+      <c r="G66" s="417" t="s">
         <v>5</v>
       </c>
-      <c r="H66" s="444"/>
+      <c r="H66" s="418"/>
       <c r="I66" s="32"/>
     </row>
     <row r="67" spans="1:14" ht="12" customHeight="1">
@@ -18531,10 +18505,10 @@
       <c r="F70" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G70" s="443" t="s">
+      <c r="G70" s="417" t="s">
         <v>5</v>
       </c>
-      <c r="H70" s="444"/>
+      <c r="H70" s="418"/>
       <c r="I70" s="32"/>
     </row>
     <row r="71" spans="1:14" ht="12" customHeight="1">
@@ -18613,10 +18587,10 @@
       <c r="F74" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="G74" s="443" t="s">
+      <c r="G74" s="417" t="s">
         <v>5</v>
       </c>
-      <c r="H74" s="444"/>
+      <c r="H74" s="418"/>
       <c r="I74" s="32"/>
     </row>
     <row r="75" spans="1:14" ht="12" customHeight="1">
@@ -18683,16 +18657,16 @@
       <c r="B78" s="21">
         <v>51</v>
       </c>
-      <c r="C78" s="420" t="s">
+      <c r="C78" s="398" t="s">
         <v>88</v>
       </c>
-      <c r="D78" s="421"/>
-      <c r="E78" s="394" t="s">
+      <c r="D78" s="399"/>
+      <c r="E78" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F78" s="395"/>
-      <c r="G78" s="395"/>
-      <c r="H78" s="396"/>
+      <c r="F78" s="396"/>
+      <c r="G78" s="396"/>
+      <c r="H78" s="397"/>
       <c r="I78" s="32"/>
     </row>
     <row r="79" spans="1:14" ht="12" customHeight="1">
@@ -18702,16 +18676,16 @@
       <c r="B79" s="21">
         <v>52</v>
       </c>
-      <c r="C79" s="422"/>
-      <c r="D79" s="423"/>
+      <c r="C79" s="400"/>
+      <c r="D79" s="401"/>
       <c r="E79" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F79" s="397" t="s">
+      <c r="F79" s="402" t="s">
         <v>89</v>
       </c>
-      <c r="G79" s="398"/>
-      <c r="H79" s="399"/>
+      <c r="G79" s="403"/>
+      <c r="H79" s="404"/>
       <c r="I79" s="32"/>
     </row>
     <row r="80" spans="1:14" ht="12" customHeight="1">
@@ -18730,11 +18704,11 @@
       <c r="E80" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F80" s="397" t="s">
+      <c r="F80" s="402" t="s">
         <v>24</v>
       </c>
-      <c r="G80" s="398"/>
-      <c r="H80" s="399"/>
+      <c r="G80" s="403"/>
+      <c r="H80" s="404"/>
       <c r="I80" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18757,11 +18731,11 @@
       <c r="E81" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="397" t="s">
+      <c r="F81" s="402" t="s">
         <v>90</v>
       </c>
-      <c r="G81" s="398"/>
-      <c r="H81" s="399"/>
+      <c r="G81" s="403"/>
+      <c r="H81" s="404"/>
       <c r="I81" s="32"/>
       <c r="N81" s="35"/>
     </row>
@@ -18781,13 +18755,13 @@
       <c r="E82" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="430" t="s">
+      <c r="F82" s="414" t="s">
         <v>91</v>
       </c>
-      <c r="G82" s="443" t="s">
+      <c r="G82" s="417" t="s">
         <v>5</v>
       </c>
-      <c r="H82" s="444"/>
+      <c r="H82" s="418"/>
       <c r="I82" s="32"/>
     </row>
     <row r="83" spans="1:14" ht="24" customHeight="1">
@@ -18806,8 +18780,8 @@
       <c r="E83" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F83" s="438"/>
-      <c r="G83" s="430" t="s">
+      <c r="F83" s="416"/>
+      <c r="G83" s="414" t="s">
         <v>55</v>
       </c>
       <c r="H83" s="15" t="s">
@@ -18834,8 +18808,8 @@
       <c r="E84" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F84" s="431"/>
-      <c r="G84" s="431"/>
+      <c r="F84" s="415"/>
+      <c r="G84" s="415"/>
       <c r="H84" s="15" t="s">
         <v>92</v>
       </c>
@@ -18860,11 +18834,11 @@
       <c r="E85" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F85" s="397" t="s">
+      <c r="F85" s="402" t="s">
         <v>9</v>
       </c>
-      <c r="G85" s="398"/>
-      <c r="H85" s="399"/>
+      <c r="G85" s="403"/>
+      <c r="H85" s="404"/>
       <c r="I85" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18886,11 +18860,11 @@
       <c r="E86" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F86" s="397" t="s">
+      <c r="F86" s="402" t="s">
         <v>10</v>
       </c>
-      <c r="G86" s="398"/>
-      <c r="H86" s="399"/>
+      <c r="G86" s="403"/>
+      <c r="H86" s="404"/>
       <c r="I86" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18912,11 +18886,11 @@
       <c r="E87" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F87" s="397" t="s">
+      <c r="F87" s="402" t="s">
         <v>11</v>
       </c>
-      <c r="G87" s="398"/>
-      <c r="H87" s="399"/>
+      <c r="G87" s="403"/>
+      <c r="H87" s="404"/>
       <c r="I87" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18938,11 +18912,11 @@
       <c r="E88" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="397" t="s">
+      <c r="F88" s="402" t="s">
         <v>93</v>
       </c>
-      <c r="G88" s="398"/>
-      <c r="H88" s="399"/>
+      <c r="G88" s="403"/>
+      <c r="H88" s="404"/>
       <c r="I88" s="32"/>
     </row>
     <row r="89" spans="1:14" ht="12" customHeight="1">
@@ -18961,11 +18935,11 @@
       <c r="E89" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F89" s="417" t="s">
+      <c r="F89" s="392" t="s">
         <v>94</v>
       </c>
-      <c r="G89" s="418"/>
-      <c r="H89" s="419"/>
+      <c r="G89" s="393"/>
+      <c r="H89" s="394"/>
       <c r="I89" s="32"/>
       <c r="J89" s="10"/>
     </row>
@@ -18985,9 +18959,9 @@
       <c r="E90" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F90" s="417"/>
-      <c r="G90" s="418"/>
-      <c r="H90" s="419"/>
+      <c r="F90" s="392"/>
+      <c r="G90" s="393"/>
+      <c r="H90" s="394"/>
       <c r="I90" s="39"/>
       <c r="J90" s="10"/>
     </row>
@@ -19001,16 +18975,16 @@
       <c r="B92" s="21">
         <v>63</v>
       </c>
-      <c r="C92" s="420" t="s">
+      <c r="C92" s="398" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="421"/>
-      <c r="E92" s="394" t="s">
+      <c r="D92" s="399"/>
+      <c r="E92" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F92" s="395"/>
-      <c r="G92" s="395"/>
-      <c r="H92" s="396"/>
+      <c r="F92" s="396"/>
+      <c r="G92" s="396"/>
+      <c r="H92" s="397"/>
       <c r="I92" s="32"/>
     </row>
     <row r="93" spans="1:14" ht="12" customHeight="1">
@@ -19026,14 +19000,14 @@
       <c r="D93" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="430" t="s">
+      <c r="E93" s="414" t="s">
         <v>55</v>
       </c>
-      <c r="F93" s="397" t="s">
-        <v>44</v>
-      </c>
-      <c r="G93" s="398"/>
-      <c r="H93" s="399"/>
+      <c r="F93" s="402" t="s">
+        <v>44</v>
+      </c>
+      <c r="G93" s="403"/>
+      <c r="H93" s="404"/>
       <c r="I93" s="32"/>
     </row>
     <row r="94" spans="1:14" ht="12" customHeight="1">
@@ -19049,12 +19023,12 @@
       <c r="D94" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="E94" s="431"/>
-      <c r="F94" s="417" t="s">
+      <c r="E94" s="415"/>
+      <c r="F94" s="392" t="s">
         <v>96</v>
       </c>
-      <c r="G94" s="418"/>
-      <c r="H94" s="419"/>
+      <c r="G94" s="393"/>
+      <c r="H94" s="394"/>
       <c r="I94" s="32"/>
       <c r="J94" s="10"/>
     </row>
@@ -19068,16 +19042,16 @@
       <c r="B96" s="21">
         <v>66</v>
       </c>
-      <c r="C96" s="420" t="s">
+      <c r="C96" s="398" t="s">
         <v>97</v>
       </c>
-      <c r="D96" s="421"/>
-      <c r="E96" s="394" t="s">
+      <c r="D96" s="399"/>
+      <c r="E96" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F96" s="395"/>
-      <c r="G96" s="395"/>
-      <c r="H96" s="396"/>
+      <c r="F96" s="396"/>
+      <c r="G96" s="396"/>
+      <c r="H96" s="397"/>
       <c r="I96" s="32"/>
     </row>
     <row r="97" spans="1:10" ht="12" customHeight="1">
@@ -19096,11 +19070,11 @@
       <c r="E97" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F97" s="397" t="s">
+      <c r="F97" s="402" t="s">
         <v>98</v>
       </c>
-      <c r="G97" s="398"/>
-      <c r="H97" s="399"/>
+      <c r="G97" s="403"/>
+      <c r="H97" s="404"/>
       <c r="I97" s="32"/>
     </row>
     <row r="98" spans="1:10" ht="12" customHeight="1">
@@ -19119,11 +19093,11 @@
       <c r="E98" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F98" s="397" t="s">
+      <c r="F98" s="402" t="s">
         <v>99</v>
       </c>
-      <c r="G98" s="398"/>
-      <c r="H98" s="399"/>
+      <c r="G98" s="403"/>
+      <c r="H98" s="404"/>
       <c r="I98" s="32"/>
     </row>
     <row r="99" spans="1:10" ht="12" customHeight="1">
@@ -19142,11 +19116,11 @@
       <c r="E99" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F99" s="397" t="s">
+      <c r="F99" s="402" t="s">
         <v>12</v>
       </c>
-      <c r="G99" s="398"/>
-      <c r="H99" s="399"/>
+      <c r="G99" s="403"/>
+      <c r="H99" s="404"/>
       <c r="I99" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19168,11 +19142,11 @@
       <c r="E100" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F100" s="397" t="s">
+      <c r="F100" s="402" t="s">
         <v>100</v>
       </c>
-      <c r="G100" s="398"/>
-      <c r="H100" s="399"/>
+      <c r="G100" s="403"/>
+      <c r="H100" s="404"/>
       <c r="I100" s="32"/>
     </row>
     <row r="101" spans="1:10" ht="12" customHeight="1">
@@ -19191,11 +19165,11 @@
       <c r="E101" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F101" s="417" t="s">
-        <v>44</v>
-      </c>
-      <c r="G101" s="418"/>
-      <c r="H101" s="419"/>
+      <c r="F101" s="392" t="s">
+        <v>44</v>
+      </c>
+      <c r="G101" s="393"/>
+      <c r="H101" s="394"/>
       <c r="I101" s="32"/>
       <c r="J101" s="10"/>
     </row>
@@ -19215,11 +19189,11 @@
       <c r="E102" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F102" s="417" t="s">
-        <v>44</v>
-      </c>
-      <c r="G102" s="418"/>
-      <c r="H102" s="419"/>
+      <c r="F102" s="392" t="s">
+        <v>44</v>
+      </c>
+      <c r="G102" s="393"/>
+      <c r="H102" s="394"/>
       <c r="I102" s="32"/>
       <c r="J102" s="10"/>
     </row>
@@ -19233,14 +19207,14 @@
       <c r="B104" s="21">
         <v>72</v>
       </c>
-      <c r="C104" s="394" t="s">
+      <c r="C104" s="395" t="s">
         <v>19</v>
       </c>
-      <c r="D104" s="395"/>
-      <c r="E104" s="395"/>
-      <c r="F104" s="395"/>
-      <c r="G104" s="395"/>
-      <c r="H104" s="396"/>
+      <c r="D104" s="396"/>
+      <c r="E104" s="396"/>
+      <c r="F104" s="396"/>
+      <c r="G104" s="396"/>
+      <c r="H104" s="397"/>
       <c r="I104" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19253,14 +19227,14 @@
       <c r="B105" s="21">
         <v>73</v>
       </c>
-      <c r="C105" s="394" t="s">
+      <c r="C105" s="395" t="s">
         <v>101</v>
       </c>
-      <c r="D105" s="395"/>
-      <c r="E105" s="395"/>
-      <c r="F105" s="395"/>
-      <c r="G105" s="395"/>
-      <c r="H105" s="396"/>
+      <c r="D105" s="396"/>
+      <c r="E105" s="396"/>
+      <c r="F105" s="396"/>
+      <c r="G105" s="396"/>
+      <c r="H105" s="397"/>
       <c r="I105" s="32"/>
     </row>
     <row r="106" spans="1:10" ht="12" customHeight="1">
@@ -19270,16 +19244,16 @@
       <c r="B106" s="21">
         <v>74</v>
       </c>
-      <c r="C106" s="420" t="s">
+      <c r="C106" s="398" t="s">
         <v>102</v>
       </c>
-      <c r="D106" s="421"/>
-      <c r="E106" s="394" t="s">
+      <c r="D106" s="399"/>
+      <c r="E106" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F106" s="395"/>
-      <c r="G106" s="395"/>
-      <c r="H106" s="396"/>
+      <c r="F106" s="396"/>
+      <c r="G106" s="396"/>
+      <c r="H106" s="397"/>
       <c r="I106" s="32"/>
     </row>
     <row r="107" spans="1:10" ht="18.75" customHeight="1">
@@ -19289,16 +19263,16 @@
       <c r="B107" s="21">
         <v>75</v>
       </c>
-      <c r="C107" s="422"/>
-      <c r="D107" s="423"/>
+      <c r="C107" s="400"/>
+      <c r="D107" s="401"/>
       <c r="E107" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F107" s="397" t="s">
+      <c r="F107" s="402" t="s">
         <v>13</v>
       </c>
-      <c r="G107" s="398"/>
-      <c r="H107" s="399"/>
+      <c r="G107" s="403"/>
+      <c r="H107" s="404"/>
       <c r="I107" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19320,11 +19294,11 @@
       <c r="E108" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F108" s="417" t="s">
+      <c r="F108" s="392" t="s">
         <v>103</v>
       </c>
-      <c r="G108" s="418"/>
-      <c r="H108" s="419"/>
+      <c r="G108" s="393"/>
+      <c r="H108" s="394"/>
       <c r="I108" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19347,11 +19321,11 @@
       <c r="E109" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F109" s="417" t="s">
+      <c r="F109" s="392" t="s">
         <v>104</v>
       </c>
-      <c r="G109" s="418"/>
-      <c r="H109" s="419"/>
+      <c r="G109" s="393"/>
+      <c r="H109" s="394"/>
       <c r="I109" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19374,11 +19348,11 @@
       <c r="E110" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F110" s="417" t="s">
+      <c r="F110" s="392" t="s">
         <v>8</v>
       </c>
-      <c r="G110" s="418"/>
-      <c r="H110" s="419"/>
+      <c r="G110" s="393"/>
+      <c r="H110" s="394"/>
       <c r="I110" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19395,16 +19369,16 @@
       <c r="B112" s="21">
         <v>77</v>
       </c>
-      <c r="C112" s="420" t="s">
+      <c r="C112" s="398" t="s">
         <v>105</v>
       </c>
-      <c r="D112" s="421"/>
-      <c r="E112" s="394" t="s">
+      <c r="D112" s="399"/>
+      <c r="E112" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F112" s="395"/>
-      <c r="G112" s="395"/>
-      <c r="H112" s="396"/>
+      <c r="F112" s="396"/>
+      <c r="G112" s="396"/>
+      <c r="H112" s="397"/>
       <c r="I112" s="32"/>
     </row>
     <row r="113" spans="1:9" ht="12" customHeight="1">
@@ -19423,11 +19397,11 @@
       <c r="E113" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F113" s="397" t="s">
+      <c r="F113" s="402" t="s">
         <v>106</v>
       </c>
-      <c r="G113" s="398"/>
-      <c r="H113" s="399"/>
+      <c r="G113" s="403"/>
+      <c r="H113" s="404"/>
       <c r="I113" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19449,11 +19423,11 @@
       <c r="E114" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F114" s="397" t="s">
+      <c r="F114" s="402" t="s">
         <v>107</v>
       </c>
-      <c r="G114" s="398"/>
-      <c r="H114" s="399"/>
+      <c r="G114" s="403"/>
+      <c r="H114" s="404"/>
       <c r="I114" s="32"/>
     </row>
     <row r="115" spans="1:9" ht="12" customHeight="1">
@@ -19463,14 +19437,14 @@
       <c r="B115" s="21">
         <v>80</v>
       </c>
-      <c r="C115" s="394" t="s">
+      <c r="C115" s="395" t="s">
         <v>108</v>
       </c>
-      <c r="D115" s="395"/>
-      <c r="E115" s="395"/>
-      <c r="F115" s="395"/>
-      <c r="G115" s="395"/>
-      <c r="H115" s="396"/>
+      <c r="D115" s="396"/>
+      <c r="E115" s="396"/>
+      <c r="F115" s="396"/>
+      <c r="G115" s="396"/>
+      <c r="H115" s="397"/>
       <c r="I115" s="32"/>
     </row>
     <row r="116" spans="1:9" ht="12" customHeight="1">
@@ -19480,16 +19454,16 @@
       <c r="B116" s="21">
         <v>81</v>
       </c>
-      <c r="C116" s="420" t="s">
+      <c r="C116" s="398" t="s">
         <v>109</v>
       </c>
-      <c r="D116" s="421"/>
-      <c r="E116" s="394" t="s">
+      <c r="D116" s="399"/>
+      <c r="E116" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F116" s="395"/>
-      <c r="G116" s="395"/>
-      <c r="H116" s="396"/>
+      <c r="F116" s="396"/>
+      <c r="G116" s="396"/>
+      <c r="H116" s="397"/>
       <c r="I116" s="32"/>
     </row>
     <row r="117" spans="1:9" ht="12" customHeight="1">
@@ -19499,16 +19473,16 @@
       <c r="B117" s="21">
         <v>82</v>
       </c>
-      <c r="C117" s="422"/>
-      <c r="D117" s="423"/>
+      <c r="C117" s="400"/>
+      <c r="D117" s="401"/>
       <c r="E117" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F117" s="397" t="s">
+      <c r="F117" s="402" t="s">
         <v>110</v>
       </c>
-      <c r="G117" s="398"/>
-      <c r="H117" s="399"/>
+      <c r="G117" s="403"/>
+      <c r="H117" s="404"/>
       <c r="I117" s="32"/>
     </row>
     <row r="118" spans="1:9" ht="12" customHeight="1">
@@ -19527,11 +19501,11 @@
       <c r="E118" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F118" s="397" t="s">
+      <c r="F118" s="402" t="s">
         <v>111</v>
       </c>
-      <c r="G118" s="398"/>
-      <c r="H118" s="399"/>
+      <c r="G118" s="403"/>
+      <c r="H118" s="404"/>
       <c r="I118" s="32"/>
     </row>
     <row r="119" spans="1:9" hidden="1">
@@ -19544,16 +19518,16 @@
       <c r="B120" s="21">
         <v>85</v>
       </c>
-      <c r="C120" s="420" t="s">
+      <c r="C120" s="398" t="s">
         <v>112</v>
       </c>
-      <c r="D120" s="421"/>
-      <c r="E120" s="394" t="s">
+      <c r="D120" s="399"/>
+      <c r="E120" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F120" s="395"/>
-      <c r="G120" s="395"/>
-      <c r="H120" s="396"/>
+      <c r="F120" s="396"/>
+      <c r="G120" s="396"/>
+      <c r="H120" s="397"/>
       <c r="I120" s="32"/>
     </row>
     <row r="121" spans="1:9" ht="12" customHeight="1">
@@ -19563,16 +19537,16 @@
       <c r="B121" s="21">
         <v>86</v>
       </c>
-      <c r="C121" s="422"/>
-      <c r="D121" s="423"/>
+      <c r="C121" s="400"/>
+      <c r="D121" s="401"/>
       <c r="E121" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F121" s="397" t="s">
+      <c r="F121" s="402" t="s">
         <v>113</v>
       </c>
-      <c r="G121" s="398"/>
-      <c r="H121" s="399"/>
+      <c r="G121" s="403"/>
+      <c r="H121" s="404"/>
       <c r="I121" s="32"/>
     </row>
     <row r="122" spans="1:9" ht="12" customHeight="1">
@@ -19591,11 +19565,11 @@
       <c r="E122" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F122" s="397" t="s">
+      <c r="F122" s="402" t="s">
         <v>111</v>
       </c>
-      <c r="G122" s="398"/>
-      <c r="H122" s="399"/>
+      <c r="G122" s="403"/>
+      <c r="H122" s="404"/>
       <c r="I122" s="32"/>
     </row>
     <row r="123" spans="1:9" ht="12" customHeight="1">
@@ -19614,11 +19588,11 @@
       <c r="E123" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F123" s="397" t="s">
+      <c r="F123" s="402" t="s">
         <v>114</v>
       </c>
-      <c r="G123" s="398"/>
-      <c r="H123" s="399"/>
+      <c r="G123" s="403"/>
+      <c r="H123" s="404"/>
       <c r="I123" s="32"/>
     </row>
     <row r="124" spans="1:9" ht="12" customHeight="1">
@@ -19637,11 +19611,11 @@
       <c r="E124" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F124" s="397" t="s">
+      <c r="F124" s="402" t="s">
         <v>115</v>
       </c>
-      <c r="G124" s="398"/>
-      <c r="H124" s="399"/>
+      <c r="G124" s="403"/>
+      <c r="H124" s="404"/>
       <c r="I124" s="32"/>
     </row>
     <row r="125" spans="1:9" hidden="1">
@@ -19654,14 +19628,14 @@
       <c r="B126" s="21">
         <v>91</v>
       </c>
-      <c r="C126" s="394" t="s">
+      <c r="C126" s="395" t="s">
         <v>116</v>
       </c>
-      <c r="D126" s="395"/>
-      <c r="E126" s="395"/>
-      <c r="F126" s="395"/>
-      <c r="G126" s="395"/>
-      <c r="H126" s="396"/>
+      <c r="D126" s="396"/>
+      <c r="E126" s="396"/>
+      <c r="F126" s="396"/>
+      <c r="G126" s="396"/>
+      <c r="H126" s="397"/>
       <c r="I126" s="32"/>
     </row>
     <row r="127" spans="1:9" ht="12" customHeight="1">
@@ -19671,16 +19645,16 @@
       <c r="B127" s="21">
         <v>92</v>
       </c>
-      <c r="C127" s="420" t="s">
+      <c r="C127" s="398" t="s">
         <v>117</v>
       </c>
-      <c r="D127" s="421"/>
-      <c r="E127" s="394" t="s">
+      <c r="D127" s="399"/>
+      <c r="E127" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F127" s="395"/>
-      <c r="G127" s="395"/>
-      <c r="H127" s="396"/>
+      <c r="F127" s="396"/>
+      <c r="G127" s="396"/>
+      <c r="H127" s="397"/>
       <c r="I127" s="32"/>
     </row>
     <row r="128" spans="1:9" ht="12" customHeight="1">
@@ -19690,16 +19664,16 @@
       <c r="B128" s="21">
         <v>93</v>
       </c>
-      <c r="C128" s="422"/>
-      <c r="D128" s="423"/>
+      <c r="C128" s="400"/>
+      <c r="D128" s="401"/>
       <c r="E128" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F128" s="445" t="s">
-        <v>44</v>
-      </c>
-      <c r="G128" s="446"/>
-      <c r="H128" s="447"/>
+      <c r="F128" s="405" t="s">
+        <v>44</v>
+      </c>
+      <c r="G128" s="406"/>
+      <c r="H128" s="407"/>
       <c r="I128" s="40"/>
     </row>
     <row r="129" spans="1:14" hidden="1">
@@ -19712,14 +19686,14 @@
       <c r="B130" s="21">
         <v>95</v>
       </c>
-      <c r="C130" s="394" t="s">
+      <c r="C130" s="395" t="s">
         <v>118</v>
       </c>
-      <c r="D130" s="395"/>
-      <c r="E130" s="395"/>
-      <c r="F130" s="395"/>
-      <c r="G130" s="395"/>
-      <c r="H130" s="396"/>
+      <c r="D130" s="396"/>
+      <c r="E130" s="396"/>
+      <c r="F130" s="396"/>
+      <c r="G130" s="396"/>
+      <c r="H130" s="397"/>
       <c r="I130" s="32"/>
     </row>
     <row r="131" spans="1:14" ht="12" customHeight="1">
@@ -19729,14 +19703,14 @@
       <c r="B131" s="21">
         <v>96</v>
       </c>
-      <c r="C131" s="394" t="s">
+      <c r="C131" s="395" t="s">
         <v>119</v>
       </c>
-      <c r="D131" s="395"/>
-      <c r="E131" s="395"/>
-      <c r="F131" s="395"/>
-      <c r="G131" s="395"/>
-      <c r="H131" s="396"/>
+      <c r="D131" s="396"/>
+      <c r="E131" s="396"/>
+      <c r="F131" s="396"/>
+      <c r="G131" s="396"/>
+      <c r="H131" s="397"/>
       <c r="I131" s="32"/>
     </row>
     <row r="132" spans="1:14" ht="12" customHeight="1">
@@ -19746,16 +19720,16 @@
       <c r="B132" s="21">
         <v>97</v>
       </c>
-      <c r="C132" s="420" t="s">
+      <c r="C132" s="398" t="s">
         <v>120</v>
       </c>
-      <c r="D132" s="421"/>
-      <c r="E132" s="394" t="s">
+      <c r="D132" s="399"/>
+      <c r="E132" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F132" s="395"/>
-      <c r="G132" s="395"/>
-      <c r="H132" s="396"/>
+      <c r="F132" s="396"/>
+      <c r="G132" s="396"/>
+      <c r="H132" s="397"/>
       <c r="I132" s="32"/>
     </row>
     <row r="133" spans="1:14" ht="12" customHeight="1">
@@ -19765,16 +19739,16 @@
       <c r="B133" s="21">
         <v>98</v>
       </c>
-      <c r="C133" s="422"/>
-      <c r="D133" s="423"/>
+      <c r="C133" s="400"/>
+      <c r="D133" s="401"/>
       <c r="E133" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F133" s="397" t="s">
+      <c r="F133" s="402" t="s">
         <v>121</v>
       </c>
-      <c r="G133" s="398"/>
-      <c r="H133" s="399"/>
+      <c r="G133" s="403"/>
+      <c r="H133" s="404"/>
       <c r="I133" s="32"/>
     </row>
     <row r="134" spans="1:14" ht="12" customHeight="1">
@@ -19784,16 +19758,16 @@
       <c r="B134" s="21">
         <v>99</v>
       </c>
-      <c r="C134" s="422"/>
-      <c r="D134" s="423"/>
+      <c r="C134" s="400"/>
+      <c r="D134" s="401"/>
       <c r="E134" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F134" s="397" t="s">
+      <c r="F134" s="402" t="s">
         <v>122</v>
       </c>
-      <c r="G134" s="398"/>
-      <c r="H134" s="399"/>
+      <c r="G134" s="403"/>
+      <c r="H134" s="404"/>
       <c r="I134" s="32"/>
     </row>
     <row r="135" spans="1:14" ht="12" customHeight="1">
@@ -19803,16 +19777,16 @@
       <c r="B135" s="21">
         <v>100</v>
       </c>
-      <c r="C135" s="422"/>
-      <c r="D135" s="423"/>
+      <c r="C135" s="400"/>
+      <c r="D135" s="401"/>
       <c r="E135" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F135" s="397" t="s">
+      <c r="F135" s="402" t="s">
         <v>123</v>
       </c>
-      <c r="G135" s="398"/>
-      <c r="H135" s="399"/>
+      <c r="G135" s="403"/>
+      <c r="H135" s="404"/>
       <c r="I135" s="32"/>
     </row>
     <row r="136" spans="1:14" ht="12" customHeight="1">
@@ -19831,11 +19805,11 @@
       <c r="E136" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F136" s="397" t="s">
+      <c r="F136" s="402" t="s">
         <v>124</v>
       </c>
-      <c r="G136" s="398"/>
-      <c r="H136" s="399"/>
+      <c r="G136" s="403"/>
+      <c r="H136" s="404"/>
       <c r="I136" s="32"/>
     </row>
     <row r="137" spans="1:14" ht="12" customHeight="1">
@@ -19854,11 +19828,11 @@
       <c r="E137" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F137" s="397" t="s">
+      <c r="F137" s="402" t="s">
         <v>125</v>
       </c>
-      <c r="G137" s="398"/>
-      <c r="H137" s="399"/>
+      <c r="G137" s="403"/>
+      <c r="H137" s="404"/>
       <c r="I137" s="32"/>
     </row>
     <row r="138" spans="1:14" ht="12" customHeight="1">
@@ -19877,11 +19851,11 @@
       <c r="E138" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F138" s="397" t="s">
+      <c r="F138" s="402" t="s">
         <v>126</v>
       </c>
-      <c r="G138" s="398"/>
-      <c r="H138" s="399"/>
+      <c r="G138" s="403"/>
+      <c r="H138" s="404"/>
       <c r="I138" s="32"/>
     </row>
     <row r="139" spans="1:14" hidden="1">
@@ -19894,16 +19868,16 @@
       <c r="B140" s="21">
         <v>105</v>
       </c>
-      <c r="C140" s="424" t="s">
+      <c r="C140" s="408" t="s">
         <v>127</v>
       </c>
-      <c r="D140" s="425"/>
-      <c r="E140" s="394" t="s">
+      <c r="D140" s="409"/>
+      <c r="E140" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F140" s="395"/>
-      <c r="G140" s="395"/>
-      <c r="H140" s="396"/>
+      <c r="F140" s="396"/>
+      <c r="G140" s="396"/>
+      <c r="H140" s="397"/>
       <c r="I140" s="32"/>
     </row>
     <row r="141" spans="1:14" ht="12" customHeight="1">
@@ -19913,16 +19887,16 @@
       <c r="B141" s="21">
         <v>106</v>
       </c>
-      <c r="C141" s="426"/>
-      <c r="D141" s="427"/>
-      <c r="E141" s="430" t="s">
+      <c r="C141" s="410"/>
+      <c r="D141" s="411"/>
+      <c r="E141" s="414" t="s">
         <v>55</v>
       </c>
-      <c r="F141" s="397" t="s">
+      <c r="F141" s="402" t="s">
         <v>128</v>
       </c>
-      <c r="G141" s="398"/>
-      <c r="H141" s="399"/>
+      <c r="G141" s="403"/>
+      <c r="H141" s="404"/>
       <c r="I141" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -19935,14 +19909,14 @@
       <c r="B142" s="21">
         <v>107</v>
       </c>
-      <c r="C142" s="428"/>
-      <c r="D142" s="429"/>
-      <c r="E142" s="431"/>
-      <c r="F142" s="397" t="s">
+      <c r="C142" s="412"/>
+      <c r="D142" s="413"/>
+      <c r="E142" s="415"/>
+      <c r="F142" s="402" t="s">
         <v>129</v>
       </c>
-      <c r="G142" s="398"/>
-      <c r="H142" s="399"/>
+      <c r="G142" s="403"/>
+      <c r="H142" s="404"/>
       <c r="I142" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19956,14 +19930,14 @@
       <c r="B143" s="21">
         <v>108</v>
       </c>
-      <c r="C143" s="394" t="s">
+      <c r="C143" s="395" t="s">
         <v>22</v>
       </c>
-      <c r="D143" s="395"/>
-      <c r="E143" s="395"/>
-      <c r="F143" s="395"/>
-      <c r="G143" s="395"/>
-      <c r="H143" s="396"/>
+      <c r="D143" s="396"/>
+      <c r="E143" s="396"/>
+      <c r="F143" s="396"/>
+      <c r="G143" s="396"/>
+      <c r="H143" s="397"/>
       <c r="I143" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19983,12 +19957,12 @@
       <c r="D144" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E144" s="394" t="s">
+      <c r="E144" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F144" s="395"/>
-      <c r="G144" s="395"/>
-      <c r="H144" s="396"/>
+      <c r="F144" s="396"/>
+      <c r="G144" s="396"/>
+      <c r="H144" s="397"/>
       <c r="I144" s="32"/>
     </row>
     <row r="145" spans="1:10" ht="12" customHeight="1">
@@ -20007,11 +19981,11 @@
       <c r="E145" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F145" s="397" t="s">
+      <c r="F145" s="402" t="s">
         <v>131</v>
       </c>
-      <c r="G145" s="398"/>
-      <c r="H145" s="399"/>
+      <c r="G145" s="403"/>
+      <c r="H145" s="404"/>
       <c r="I145" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20033,11 +20007,11 @@
       <c r="E146" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F146" s="397" t="s">
+      <c r="F146" s="402" t="s">
         <v>132</v>
       </c>
-      <c r="G146" s="398"/>
-      <c r="H146" s="399"/>
+      <c r="G146" s="403"/>
+      <c r="H146" s="404"/>
       <c r="I146" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20059,11 +20033,11 @@
       <c r="E147" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F147" s="397" t="s">
+      <c r="F147" s="402" t="s">
         <v>64</v>
       </c>
-      <c r="G147" s="398"/>
-      <c r="H147" s="399"/>
+      <c r="G147" s="403"/>
+      <c r="H147" s="404"/>
       <c r="I147" s="32"/>
     </row>
     <row r="148" spans="1:10" ht="12" customHeight="1">
@@ -20082,11 +20056,11 @@
       <c r="E148" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F148" s="417" t="s">
+      <c r="F148" s="392" t="s">
         <v>133</v>
       </c>
-      <c r="G148" s="418"/>
-      <c r="H148" s="419"/>
+      <c r="G148" s="393"/>
+      <c r="H148" s="394"/>
       <c r="I148" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20109,11 +20083,11 @@
       <c r="E149" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F149" s="417" t="s">
+      <c r="F149" s="392" t="s">
         <v>134</v>
       </c>
-      <c r="G149" s="418"/>
-      <c r="H149" s="419"/>
+      <c r="G149" s="393"/>
+      <c r="H149" s="394"/>
       <c r="I149" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20136,11 +20110,11 @@
       <c r="E150" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F150" s="417" t="s">
+      <c r="F150" s="392" t="s">
         <v>135</v>
       </c>
-      <c r="G150" s="418"/>
-      <c r="H150" s="419"/>
+      <c r="G150" s="393"/>
+      <c r="H150" s="394"/>
       <c r="I150" s="32"/>
       <c r="J150" s="10"/>
     </row>
@@ -20160,11 +20134,11 @@
       <c r="E151" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F151" s="417" t="s">
+      <c r="F151" s="392" t="s">
         <v>136</v>
       </c>
-      <c r="G151" s="418"/>
-      <c r="H151" s="419"/>
+      <c r="G151" s="393"/>
+      <c r="H151" s="394"/>
       <c r="I151" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20181,16 +20155,16 @@
       <c r="B153" s="21">
         <v>114</v>
       </c>
-      <c r="C153" s="420" t="s">
+      <c r="C153" s="398" t="s">
         <v>137</v>
       </c>
-      <c r="D153" s="421"/>
-      <c r="E153" s="394" t="s">
+      <c r="D153" s="399"/>
+      <c r="E153" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F153" s="395"/>
-      <c r="G153" s="395"/>
-      <c r="H153" s="396"/>
+      <c r="F153" s="396"/>
+      <c r="G153" s="396"/>
+      <c r="H153" s="397"/>
       <c r="I153" s="32"/>
     </row>
     <row r="154" spans="1:10" ht="12" customHeight="1">
@@ -20200,16 +20174,16 @@
       <c r="B154" s="21">
         <v>115</v>
       </c>
-      <c r="C154" s="422"/>
-      <c r="D154" s="423"/>
+      <c r="C154" s="400"/>
+      <c r="D154" s="401"/>
       <c r="E154" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F154" s="445" t="s">
-        <v>44</v>
-      </c>
-      <c r="G154" s="446"/>
-      <c r="H154" s="447"/>
+      <c r="F154" s="405" t="s">
+        <v>44</v>
+      </c>
+      <c r="G154" s="406"/>
+      <c r="H154" s="407"/>
       <c r="I154" s="40"/>
     </row>
     <row r="155" spans="1:10" ht="12" customHeight="1">
@@ -20228,11 +20202,11 @@
       <c r="E155" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F155" s="417" t="s">
+      <c r="F155" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="G155" s="418"/>
-      <c r="H155" s="419"/>
+      <c r="G155" s="393"/>
+      <c r="H155" s="394"/>
       <c r="I155" s="32"/>
       <c r="J155" s="10"/>
     </row>
@@ -20252,11 +20226,11 @@
       <c r="E156" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F156" s="417" t="s">
+      <c r="F156" s="392" t="s">
         <v>138</v>
       </c>
-      <c r="G156" s="418"/>
-      <c r="H156" s="419"/>
+      <c r="G156" s="393"/>
+      <c r="H156" s="394"/>
       <c r="I156" s="32"/>
       <c r="J156" s="10"/>
     </row>
@@ -20276,11 +20250,11 @@
       <c r="E157" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F157" s="417" t="s">
+      <c r="F157" s="392" t="s">
         <v>139</v>
       </c>
-      <c r="G157" s="418"/>
-      <c r="H157" s="419"/>
+      <c r="G157" s="393"/>
+      <c r="H157" s="394"/>
       <c r="I157" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20303,9 +20277,9 @@
       <c r="E158" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F158" s="417"/>
-      <c r="G158" s="418"/>
-      <c r="H158" s="419"/>
+      <c r="F158" s="392"/>
+      <c r="G158" s="393"/>
+      <c r="H158" s="394"/>
       <c r="I158" s="32"/>
       <c r="J158" s="10"/>
     </row>
@@ -20319,14 +20293,14 @@
       <c r="B160" s="21">
         <v>117</v>
       </c>
-      <c r="C160" s="394" t="s">
+      <c r="C160" s="395" t="s">
         <v>140</v>
       </c>
-      <c r="D160" s="395"/>
-      <c r="E160" s="395"/>
-      <c r="F160" s="395"/>
-      <c r="G160" s="395"/>
-      <c r="H160" s="396"/>
+      <c r="D160" s="396"/>
+      <c r="E160" s="396"/>
+      <c r="F160" s="396"/>
+      <c r="G160" s="396"/>
+      <c r="H160" s="397"/>
       <c r="I160" s="32"/>
     </row>
     <row r="161" spans="1:9" ht="12" customHeight="1">
@@ -20336,14 +20310,14 @@
       <c r="B161" s="21">
         <v>118</v>
       </c>
-      <c r="C161" s="394" t="s">
+      <c r="C161" s="395" t="s">
         <v>141</v>
       </c>
-      <c r="D161" s="395"/>
-      <c r="E161" s="395"/>
-      <c r="F161" s="395"/>
-      <c r="G161" s="395"/>
-      <c r="H161" s="396"/>
+      <c r="D161" s="396"/>
+      <c r="E161" s="396"/>
+      <c r="F161" s="396"/>
+      <c r="G161" s="396"/>
+      <c r="H161" s="397"/>
       <c r="I161" s="42" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -20356,14 +20330,14 @@
       <c r="B162" s="21">
         <v>119</v>
       </c>
-      <c r="C162" s="394" t="s">
+      <c r="C162" s="395" t="s">
         <v>142</v>
       </c>
-      <c r="D162" s="395"/>
-      <c r="E162" s="395"/>
-      <c r="F162" s="395"/>
-      <c r="G162" s="395"/>
-      <c r="H162" s="396"/>
+      <c r="D162" s="396"/>
+      <c r="E162" s="396"/>
+      <c r="F162" s="396"/>
+      <c r="G162" s="396"/>
+      <c r="H162" s="397"/>
       <c r="I162" s="32"/>
     </row>
     <row r="163" spans="1:9" ht="12" customHeight="1">
@@ -20373,14 +20347,14 @@
       <c r="B163" s="21">
         <v>120</v>
       </c>
-      <c r="C163" s="394" t="s">
+      <c r="C163" s="395" t="s">
         <v>143</v>
       </c>
-      <c r="D163" s="395"/>
-      <c r="E163" s="395"/>
-      <c r="F163" s="395"/>
-      <c r="G163" s="395"/>
-      <c r="H163" s="396"/>
+      <c r="D163" s="396"/>
+      <c r="E163" s="396"/>
+      <c r="F163" s="396"/>
+      <c r="G163" s="396"/>
+      <c r="H163" s="397"/>
       <c r="I163" s="32"/>
     </row>
     <row r="164" spans="1:9" ht="12" customHeight="1">
@@ -20390,14 +20364,14 @@
       <c r="B164" s="21">
         <v>121</v>
       </c>
-      <c r="C164" s="394" t="s">
+      <c r="C164" s="395" t="s">
         <v>144</v>
       </c>
-      <c r="D164" s="395"/>
-      <c r="E164" s="395"/>
-      <c r="F164" s="395"/>
-      <c r="G164" s="395"/>
-      <c r="H164" s="396"/>
+      <c r="D164" s="396"/>
+      <c r="E164" s="396"/>
+      <c r="F164" s="396"/>
+      <c r="G164" s="396"/>
+      <c r="H164" s="397"/>
       <c r="I164" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20410,16 +20384,16 @@
       <c r="B165" s="21">
         <v>122</v>
       </c>
-      <c r="C165" s="420" t="s">
+      <c r="C165" s="398" t="s">
         <v>145</v>
       </c>
-      <c r="D165" s="421"/>
-      <c r="E165" s="394" t="s">
+      <c r="D165" s="399"/>
+      <c r="E165" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F165" s="395"/>
-      <c r="G165" s="395"/>
-      <c r="H165" s="396"/>
+      <c r="F165" s="396"/>
+      <c r="G165" s="396"/>
+      <c r="H165" s="397"/>
       <c r="I165" s="32"/>
     </row>
     <row r="166" spans="1:9" ht="12" customHeight="1">
@@ -20429,16 +20403,16 @@
       <c r="B166" s="21">
         <v>123</v>
       </c>
-      <c r="C166" s="422"/>
-      <c r="D166" s="423"/>
+      <c r="C166" s="400"/>
+      <c r="D166" s="401"/>
       <c r="E166" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F166" s="397" t="s">
+      <c r="F166" s="402" t="s">
         <v>146</v>
       </c>
-      <c r="G166" s="398"/>
-      <c r="H166" s="399"/>
+      <c r="G166" s="403"/>
+      <c r="H166" s="404"/>
       <c r="I166" s="32"/>
     </row>
     <row r="167" spans="1:9" ht="12" customHeight="1">
@@ -20457,11 +20431,11 @@
       <c r="E167" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F167" s="397" t="s">
+      <c r="F167" s="402" t="s">
         <v>147</v>
       </c>
-      <c r="G167" s="398"/>
-      <c r="H167" s="399"/>
+      <c r="G167" s="403"/>
+      <c r="H167" s="404"/>
       <c r="I167" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20483,11 +20457,11 @@
       <c r="E168" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F168" s="397" t="s">
+      <c r="F168" s="402" t="s">
         <v>148</v>
       </c>
-      <c r="G168" s="398"/>
-      <c r="H168" s="399"/>
+      <c r="G168" s="403"/>
+      <c r="H168" s="404"/>
       <c r="I168" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20503,14 +20477,14 @@
       <c r="B170" s="21">
         <v>127</v>
       </c>
-      <c r="C170" s="394" t="s">
+      <c r="C170" s="395" t="s">
         <v>17</v>
       </c>
-      <c r="D170" s="395"/>
-      <c r="E170" s="395"/>
-      <c r="F170" s="395"/>
-      <c r="G170" s="395"/>
-      <c r="H170" s="396"/>
+      <c r="D170" s="396"/>
+      <c r="E170" s="396"/>
+      <c r="F170" s="396"/>
+      <c r="G170" s="396"/>
+      <c r="H170" s="397"/>
       <c r="I170" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20523,14 +20497,14 @@
       <c r="B171" s="21">
         <v>128</v>
       </c>
-      <c r="C171" s="394" t="s">
+      <c r="C171" s="395" t="s">
         <v>149</v>
       </c>
-      <c r="D171" s="395"/>
-      <c r="E171" s="395"/>
-      <c r="F171" s="395"/>
-      <c r="G171" s="395"/>
-      <c r="H171" s="396"/>
+      <c r="D171" s="396"/>
+      <c r="E171" s="396"/>
+      <c r="F171" s="396"/>
+      <c r="G171" s="396"/>
+      <c r="H171" s="397"/>
       <c r="I171" s="32"/>
     </row>
     <row r="172" spans="1:9" ht="12" customHeight="1">
@@ -20540,14 +20514,14 @@
       <c r="B172" s="21">
         <v>129</v>
       </c>
-      <c r="C172" s="394" t="s">
+      <c r="C172" s="395" t="s">
         <v>150</v>
       </c>
-      <c r="D172" s="395"/>
-      <c r="E172" s="395"/>
-      <c r="F172" s="395"/>
-      <c r="G172" s="395"/>
-      <c r="H172" s="396"/>
+      <c r="D172" s="396"/>
+      <c r="E172" s="396"/>
+      <c r="F172" s="396"/>
+      <c r="G172" s="396"/>
+      <c r="H172" s="397"/>
       <c r="I172" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20560,14 +20534,14 @@
       <c r="B173" s="21">
         <v>130</v>
       </c>
-      <c r="C173" s="394" t="s">
+      <c r="C173" s="395" t="s">
         <v>151</v>
       </c>
-      <c r="D173" s="395"/>
-      <c r="E173" s="395"/>
-      <c r="F173" s="395"/>
-      <c r="G173" s="395"/>
-      <c r="H173" s="396"/>
+      <c r="D173" s="396"/>
+      <c r="E173" s="396"/>
+      <c r="F173" s="396"/>
+      <c r="G173" s="396"/>
+      <c r="H173" s="397"/>
       <c r="I173" s="32"/>
     </row>
     <row r="174" spans="1:9" ht="12" customHeight="1">
@@ -20577,14 +20551,14 @@
       <c r="B174" s="21">
         <v>131</v>
       </c>
-      <c r="C174" s="394" t="s">
+      <c r="C174" s="395" t="s">
         <v>152</v>
       </c>
-      <c r="D174" s="395"/>
-      <c r="E174" s="395"/>
-      <c r="F174" s="395"/>
-      <c r="G174" s="395"/>
-      <c r="H174" s="396"/>
+      <c r="D174" s="396"/>
+      <c r="E174" s="396"/>
+      <c r="F174" s="396"/>
+      <c r="G174" s="396"/>
+      <c r="H174" s="397"/>
       <c r="I174" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20597,16 +20571,16 @@
       <c r="B175" s="21">
         <v>132</v>
       </c>
-      <c r="C175" s="420" t="s">
+      <c r="C175" s="398" t="s">
         <v>153</v>
       </c>
-      <c r="D175" s="421"/>
-      <c r="E175" s="394" t="s">
+      <c r="D175" s="399"/>
+      <c r="E175" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F175" s="395"/>
-      <c r="G175" s="395"/>
-      <c r="H175" s="396"/>
+      <c r="F175" s="396"/>
+      <c r="G175" s="396"/>
+      <c r="H175" s="397"/>
       <c r="I175" s="32"/>
     </row>
     <row r="176" spans="1:9" ht="12" customHeight="1">
@@ -20616,16 +20590,16 @@
       <c r="B176" s="21">
         <v>133</v>
       </c>
-      <c r="C176" s="422"/>
-      <c r="D176" s="423"/>
+      <c r="C176" s="400"/>
+      <c r="D176" s="401"/>
       <c r="E176" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F176" s="397" t="s">
+      <c r="F176" s="402" t="s">
         <v>128</v>
       </c>
-      <c r="G176" s="398"/>
-      <c r="H176" s="399"/>
+      <c r="G176" s="403"/>
+      <c r="H176" s="404"/>
       <c r="I176" s="32"/>
     </row>
     <row r="177" spans="1:14" ht="12" customHeight="1">
@@ -20635,16 +20609,16 @@
       <c r="B177" s="21">
         <v>134</v>
       </c>
-      <c r="C177" s="422"/>
-      <c r="D177" s="423"/>
+      <c r="C177" s="400"/>
+      <c r="D177" s="401"/>
       <c r="E177" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F177" s="397" t="s">
+      <c r="F177" s="402" t="s">
         <v>154</v>
       </c>
-      <c r="G177" s="398"/>
-      <c r="H177" s="399"/>
+      <c r="G177" s="403"/>
+      <c r="H177" s="404"/>
       <c r="I177" s="32"/>
     </row>
     <row r="178" spans="1:14" ht="12" customHeight="1">
@@ -20663,11 +20637,11 @@
       <c r="E178" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F178" s="397" t="s">
+      <c r="F178" s="402" t="s">
         <v>155</v>
       </c>
-      <c r="G178" s="398"/>
-      <c r="H178" s="399"/>
+      <c r="G178" s="403"/>
+      <c r="H178" s="404"/>
       <c r="I178" s="32"/>
     </row>
     <row r="179" spans="1:14" hidden="1">
@@ -20680,14 +20654,14 @@
       <c r="B180" s="21">
         <v>137</v>
       </c>
-      <c r="C180" s="394" t="s">
+      <c r="C180" s="395" t="s">
         <v>156</v>
       </c>
-      <c r="D180" s="395"/>
-      <c r="E180" s="395"/>
-      <c r="F180" s="395"/>
-      <c r="G180" s="395"/>
-      <c r="H180" s="396"/>
+      <c r="D180" s="396"/>
+      <c r="E180" s="396"/>
+      <c r="F180" s="396"/>
+      <c r="G180" s="396"/>
+      <c r="H180" s="397"/>
       <c r="I180" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20700,14 +20674,14 @@
       <c r="B181" s="21">
         <v>138</v>
       </c>
-      <c r="C181" s="394" t="s">
+      <c r="C181" s="395" t="s">
         <v>21</v>
       </c>
-      <c r="D181" s="395"/>
-      <c r="E181" s="395"/>
-      <c r="F181" s="395"/>
-      <c r="G181" s="395"/>
-      <c r="H181" s="396"/>
+      <c r="D181" s="396"/>
+      <c r="E181" s="396"/>
+      <c r="F181" s="396"/>
+      <c r="G181" s="396"/>
+      <c r="H181" s="397"/>
       <c r="I181" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20720,16 +20694,16 @@
       <c r="B182" s="21">
         <v>139</v>
       </c>
-      <c r="C182" s="420" t="s">
+      <c r="C182" s="398" t="s">
         <v>157</v>
       </c>
-      <c r="D182" s="421"/>
-      <c r="E182" s="394" t="s">
+      <c r="D182" s="399"/>
+      <c r="E182" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F182" s="395"/>
-      <c r="G182" s="395"/>
-      <c r="H182" s="396"/>
+      <c r="F182" s="396"/>
+      <c r="G182" s="396"/>
+      <c r="H182" s="397"/>
       <c r="I182" s="32"/>
     </row>
     <row r="183" spans="1:14" ht="12" customHeight="1">
@@ -20739,16 +20713,16 @@
       <c r="B183" s="21">
         <v>140</v>
       </c>
-      <c r="C183" s="422"/>
-      <c r="D183" s="423"/>
+      <c r="C183" s="400"/>
+      <c r="D183" s="401"/>
       <c r="E183" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F183" s="397" t="s">
-        <v>44</v>
-      </c>
-      <c r="G183" s="398"/>
-      <c r="H183" s="399"/>
+      <c r="F183" s="402" t="s">
+        <v>44</v>
+      </c>
+      <c r="G183" s="403"/>
+      <c r="H183" s="404"/>
       <c r="I183" s="32"/>
     </row>
     <row r="184" spans="1:14" hidden="1">
@@ -20761,16 +20735,16 @@
       <c r="B185" s="21">
         <v>142</v>
       </c>
-      <c r="C185" s="420" t="s">
+      <c r="C185" s="398" t="s">
         <v>158</v>
       </c>
-      <c r="D185" s="421"/>
-      <c r="E185" s="394" t="s">
+      <c r="D185" s="399"/>
+      <c r="E185" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F185" s="395"/>
-      <c r="G185" s="395"/>
-      <c r="H185" s="396"/>
+      <c r="F185" s="396"/>
+      <c r="G185" s="396"/>
+      <c r="H185" s="397"/>
       <c r="I185" s="32"/>
     </row>
     <row r="186" spans="1:14" ht="12" customHeight="1">
@@ -20780,16 +20754,16 @@
       <c r="B186" s="21">
         <v>143</v>
       </c>
-      <c r="C186" s="422"/>
-      <c r="D186" s="423"/>
+      <c r="C186" s="400"/>
+      <c r="D186" s="401"/>
       <c r="E186" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F186" s="397" t="s">
+      <c r="F186" s="402" t="s">
         <v>159</v>
       </c>
-      <c r="G186" s="398"/>
-      <c r="H186" s="399"/>
+      <c r="G186" s="403"/>
+      <c r="H186" s="404"/>
       <c r="I186" s="32"/>
     </row>
     <row r="187" spans="1:14" ht="12" customHeight="1">
@@ -20799,16 +20773,16 @@
       <c r="B187" s="21">
         <v>144</v>
       </c>
-      <c r="C187" s="422"/>
-      <c r="D187" s="423"/>
+      <c r="C187" s="400"/>
+      <c r="D187" s="401"/>
       <c r="E187" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F187" s="397" t="s">
+      <c r="F187" s="402" t="s">
         <v>160</v>
       </c>
-      <c r="G187" s="398"/>
-      <c r="H187" s="399"/>
+      <c r="G187" s="403"/>
+      <c r="H187" s="404"/>
       <c r="I187" s="32"/>
     </row>
     <row r="188" spans="1:14" ht="12" customHeight="1">
@@ -20827,11 +20801,11 @@
       <c r="E188" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F188" s="417" t="s">
+      <c r="F188" s="392" t="s">
         <v>161</v>
       </c>
-      <c r="G188" s="418"/>
-      <c r="H188" s="419"/>
+      <c r="G188" s="393"/>
+      <c r="H188" s="394"/>
       <c r="I188" s="32"/>
       <c r="J188" s="10"/>
     </row>
@@ -20851,11 +20825,11 @@
       <c r="E189" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F189" s="417" t="s">
+      <c r="F189" s="392" t="s">
         <v>162</v>
       </c>
-      <c r="G189" s="418"/>
-      <c r="H189" s="419"/>
+      <c r="G189" s="393"/>
+      <c r="H189" s="394"/>
       <c r="I189" s="32"/>
       <c r="J189" s="10"/>
     </row>
@@ -20875,11 +20849,11 @@
       <c r="E190" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="F190" s="417" t="s">
+      <c r="F190" s="392" t="s">
         <v>163</v>
       </c>
-      <c r="G190" s="418"/>
-      <c r="H190" s="419"/>
+      <c r="G190" s="393"/>
+      <c r="H190" s="394"/>
       <c r="I190" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -20942,104 +20916,63 @@
     </row>
   </sheetData>
   <mergeCells count="169">
-    <mergeCell ref="F188:H188"/>
-    <mergeCell ref="F189:H189"/>
-    <mergeCell ref="F190:H190"/>
-    <mergeCell ref="C180:H180"/>
-    <mergeCell ref="C181:H181"/>
-    <mergeCell ref="C182:D183"/>
-    <mergeCell ref="E182:H182"/>
-    <mergeCell ref="F183:H183"/>
-    <mergeCell ref="C185:D187"/>
-    <mergeCell ref="E185:H185"/>
-    <mergeCell ref="F186:H186"/>
-    <mergeCell ref="F187:H187"/>
-    <mergeCell ref="C174:H174"/>
-    <mergeCell ref="C175:D177"/>
-    <mergeCell ref="E175:H175"/>
-    <mergeCell ref="F176:H176"/>
-    <mergeCell ref="F177:H177"/>
-    <mergeCell ref="F178:H178"/>
-    <mergeCell ref="F167:H167"/>
-    <mergeCell ref="F168:H168"/>
-    <mergeCell ref="C170:H170"/>
-    <mergeCell ref="C171:H171"/>
-    <mergeCell ref="C172:H172"/>
-    <mergeCell ref="C173:H173"/>
-    <mergeCell ref="C162:H162"/>
-    <mergeCell ref="C163:H163"/>
-    <mergeCell ref="C164:H164"/>
-    <mergeCell ref="C165:D166"/>
-    <mergeCell ref="E165:H165"/>
-    <mergeCell ref="F166:H166"/>
-    <mergeCell ref="F155:H155"/>
-    <mergeCell ref="F156:H156"/>
-    <mergeCell ref="F157:H157"/>
-    <mergeCell ref="F158:H158"/>
-    <mergeCell ref="C160:H160"/>
-    <mergeCell ref="C161:H161"/>
-    <mergeCell ref="F149:H149"/>
-    <mergeCell ref="F150:H150"/>
-    <mergeCell ref="F151:H151"/>
-    <mergeCell ref="C153:D154"/>
-    <mergeCell ref="E153:H153"/>
-    <mergeCell ref="F154:H154"/>
-    <mergeCell ref="C143:H143"/>
-    <mergeCell ref="E144:H144"/>
-    <mergeCell ref="F145:H145"/>
-    <mergeCell ref="F146:H146"/>
-    <mergeCell ref="F147:H147"/>
-    <mergeCell ref="F148:H148"/>
-    <mergeCell ref="F137:H137"/>
-    <mergeCell ref="F138:H138"/>
-    <mergeCell ref="C140:D142"/>
-    <mergeCell ref="E140:H140"/>
-    <mergeCell ref="E141:E142"/>
-    <mergeCell ref="F141:H141"/>
-    <mergeCell ref="F142:H142"/>
-    <mergeCell ref="C132:D135"/>
-    <mergeCell ref="E132:H132"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="F134:H134"/>
-    <mergeCell ref="F135:H135"/>
-    <mergeCell ref="F136:H136"/>
-    <mergeCell ref="C126:H126"/>
-    <mergeCell ref="C127:D128"/>
-    <mergeCell ref="E127:H127"/>
-    <mergeCell ref="F128:H128"/>
-    <mergeCell ref="C130:H130"/>
-    <mergeCell ref="C131:H131"/>
-    <mergeCell ref="C120:D121"/>
-    <mergeCell ref="E120:H120"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="F122:H122"/>
-    <mergeCell ref="F123:H123"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="C115:H115"/>
-    <mergeCell ref="C116:D117"/>
-    <mergeCell ref="E116:H116"/>
-    <mergeCell ref="F117:H117"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="F110:H110"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="E112:H112"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="C104:H104"/>
-    <mergeCell ref="C105:H105"/>
-    <mergeCell ref="C106:D107"/>
-    <mergeCell ref="E106:H106"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="F97:H97"/>
-    <mergeCell ref="F98:H98"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:H22"/>
+    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:D35"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:D39"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="C44:H44"/>
+    <mergeCell ref="C45:D49"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="C54:D57"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="F58:H58"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="C50:D51"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="C78:D79"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="F80:H80"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="C60:H60"/>
+    <mergeCell ref="C61:D63"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="G70:H70"/>
     <mergeCell ref="F88:H88"/>
     <mergeCell ref="F89:H89"/>
     <mergeCell ref="F90:H90"/>
@@ -21054,63 +20987,104 @@
     <mergeCell ref="F85:H85"/>
     <mergeCell ref="F86:H86"/>
     <mergeCell ref="F87:H87"/>
-    <mergeCell ref="G74:H74"/>
-    <mergeCell ref="C78:D79"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="F80:H80"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="C60:H60"/>
-    <mergeCell ref="C61:D63"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="C54:D57"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="F58:H58"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="C50:D51"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="C44:H44"/>
-    <mergeCell ref="C45:D49"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:D35"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C37:D39"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C20:H22"/>
-    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="C104:H104"/>
+    <mergeCell ref="C105:H105"/>
+    <mergeCell ref="C106:D107"/>
+    <mergeCell ref="E106:H106"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="F97:H97"/>
+    <mergeCell ref="F98:H98"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="C115:H115"/>
+    <mergeCell ref="C116:D117"/>
+    <mergeCell ref="E116:H116"/>
+    <mergeCell ref="F117:H117"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="F110:H110"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="E112:H112"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="C127:D128"/>
+    <mergeCell ref="E127:H127"/>
+    <mergeCell ref="F128:H128"/>
+    <mergeCell ref="C130:H130"/>
+    <mergeCell ref="C131:H131"/>
+    <mergeCell ref="C120:D121"/>
+    <mergeCell ref="E120:H120"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="F122:H122"/>
+    <mergeCell ref="F123:H123"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="F137:H137"/>
+    <mergeCell ref="F138:H138"/>
+    <mergeCell ref="C140:D142"/>
+    <mergeCell ref="E140:H140"/>
+    <mergeCell ref="E141:E142"/>
+    <mergeCell ref="F141:H141"/>
+    <mergeCell ref="F142:H142"/>
+    <mergeCell ref="C132:D135"/>
+    <mergeCell ref="E132:H132"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="F134:H134"/>
+    <mergeCell ref="F135:H135"/>
+    <mergeCell ref="F136:H136"/>
+    <mergeCell ref="F149:H149"/>
+    <mergeCell ref="F150:H150"/>
+    <mergeCell ref="F151:H151"/>
+    <mergeCell ref="C153:D154"/>
+    <mergeCell ref="E153:H153"/>
+    <mergeCell ref="F154:H154"/>
+    <mergeCell ref="C143:H143"/>
+    <mergeCell ref="E144:H144"/>
+    <mergeCell ref="F145:H145"/>
+    <mergeCell ref="F146:H146"/>
+    <mergeCell ref="F147:H147"/>
+    <mergeCell ref="F148:H148"/>
+    <mergeCell ref="C162:H162"/>
+    <mergeCell ref="C163:H163"/>
+    <mergeCell ref="C164:H164"/>
+    <mergeCell ref="C165:D166"/>
+    <mergeCell ref="E165:H165"/>
+    <mergeCell ref="F166:H166"/>
+    <mergeCell ref="F155:H155"/>
+    <mergeCell ref="F156:H156"/>
+    <mergeCell ref="F157:H157"/>
+    <mergeCell ref="F158:H158"/>
+    <mergeCell ref="C160:H160"/>
+    <mergeCell ref="C161:H161"/>
+    <mergeCell ref="C174:H174"/>
+    <mergeCell ref="C175:D177"/>
+    <mergeCell ref="E175:H175"/>
+    <mergeCell ref="F176:H176"/>
+    <mergeCell ref="F177:H177"/>
+    <mergeCell ref="F178:H178"/>
+    <mergeCell ref="F167:H167"/>
+    <mergeCell ref="F168:H168"/>
+    <mergeCell ref="C170:H170"/>
+    <mergeCell ref="C171:H171"/>
+    <mergeCell ref="C172:H172"/>
+    <mergeCell ref="C173:H173"/>
+    <mergeCell ref="F188:H188"/>
+    <mergeCell ref="F189:H189"/>
+    <mergeCell ref="F190:H190"/>
+    <mergeCell ref="C180:H180"/>
+    <mergeCell ref="C181:H181"/>
+    <mergeCell ref="C182:D183"/>
+    <mergeCell ref="E182:H182"/>
+    <mergeCell ref="F183:H183"/>
+    <mergeCell ref="C185:D187"/>
+    <mergeCell ref="E185:H185"/>
+    <mergeCell ref="F186:H186"/>
+    <mergeCell ref="F187:H187"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
@@ -21236,7 +21210,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="206" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C7" s="207" t="s">
         <v>269</v>
@@ -21270,7 +21244,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="206" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C8" s="207" t="s">
         <v>274</v>
@@ -21304,7 +21278,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="206" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="C9" s="207" t="s">
         <v>274</v>
@@ -21330,7 +21304,7 @@
         <v>310</v>
       </c>
       <c r="J9" s="270" t="s">
-        <v>417</v>
+        <v>454</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -21366,7 +21340,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="206" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C11" s="207" t="s">
         <v>274</v>
@@ -21428,7 +21402,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="210" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C13" s="213" t="s">
         <v>270</v>
@@ -21462,7 +21436,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="210" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C14" s="194" t="s">
         <v>272</v>
@@ -21496,7 +21470,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="210" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C15" s="213" t="s">
         <v>272</v>
@@ -21530,7 +21504,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="255" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C16" s="249"/>
       <c r="D16" s="251"/>
@@ -21544,7 +21518,7 @@
         <v>312</v>
       </c>
       <c r="J16" s="272" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="214" customFormat="1" ht="30">
@@ -21552,7 +21526,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="244" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C17" s="243" t="s">
         <v>271</v>
@@ -21584,7 +21558,7 @@
     <row r="18" spans="1:10" ht="42.75">
       <c r="A18" s="202"/>
       <c r="B18" s="203" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C18" s="204"/>
       <c r="D18" s="181">
@@ -21593,15 +21567,15 @@
       </c>
       <c r="E18" s="221">
         <f t="shared" si="3"/>
-        <v>4100000</v>
+        <v>3900000</v>
       </c>
       <c r="F18" s="222">
         <f t="shared" si="3"/>
-        <v>3299100</v>
+        <v>3140700</v>
       </c>
       <c r="G18" s="181">
         <f t="shared" si="3"/>
-        <v>49200</v>
+        <v>46800</v>
       </c>
       <c r="H18" s="181"/>
       <c r="I18" s="181"/>
@@ -21612,7 +21586,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="244" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="C19" s="243" t="s">
         <v>270</v>
@@ -21655,15 +21629,15 @@
         <v>1</v>
       </c>
       <c r="E20" s="223">
-        <v>1200000</v>
+        <v>1000000</v>
       </c>
       <c r="F20" s="224">
         <f>IF(E20&gt;0,E20-MIN(E20,4250000)*10%-MIN(E20,1700000)*2%-MAX(0,E20-MIN(E20,4250000)*10%-MIN(E20,1700000)*2%-129750)*10%,0)</f>
-        <v>963375</v>
+        <v>804975</v>
       </c>
       <c r="G20" s="177">
         <f>D20*E20*12/1000</f>
-        <v>14400</v>
+        <v>12000</v>
       </c>
       <c r="H20" s="177" t="s">
         <v>308</v>
@@ -21680,7 +21654,7 @@
         <v>3</v>
       </c>
       <c r="B21" s="244" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C21" s="243" t="s">
         <v>272</v>
@@ -21776,7 +21750,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="248" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C24" s="243" t="s">
         <v>270</v>
@@ -21810,7 +21784,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="183" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C25" s="194" t="s">
         <v>272</v>
@@ -21844,7 +21818,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="183" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C26" s="194" t="s">
         <v>272</v>
@@ -21870,7 +21844,7 @@
         <v>312</v>
       </c>
       <c r="J26" s="270" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="214" customFormat="1" ht="30">
@@ -21878,7 +21852,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="287" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C27" s="286" t="s">
         <v>272</v>
@@ -21901,7 +21875,7 @@
         <v>308</v>
       </c>
       <c r="I27" s="291" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J27" s="292" t="s">
         <v>323</v>
@@ -21912,7 +21886,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="183" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C28" s="194" t="s">
         <v>272</v>
@@ -21938,7 +21912,7 @@
         <v>312</v>
       </c>
       <c r="J28" s="270" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="30">
@@ -21946,7 +21920,7 @@
         <v>6</v>
       </c>
       <c r="B29" s="183" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C29" s="194" t="s">
         <v>272</v>
@@ -21972,7 +21946,7 @@
         <v>312</v>
       </c>
       <c r="J29" s="270" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="30">
@@ -21980,7 +21954,7 @@
         <v>7</v>
       </c>
       <c r="B30" s="293" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C30" s="213" t="s">
         <v>271</v>
@@ -22014,7 +21988,7 @@
         <v>8</v>
       </c>
       <c r="B31" s="294" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C31" s="286" t="s">
         <v>271</v>
@@ -22037,7 +22011,7 @@
         <v>308</v>
       </c>
       <c r="I31" s="291" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J31" s="292" t="s">
         <v>323</v>
@@ -22048,7 +22022,7 @@
         <v>9</v>
       </c>
       <c r="B32" s="244" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C32" s="243" t="s">
         <v>271</v>
@@ -22082,7 +22056,7 @@
         <v>10</v>
       </c>
       <c r="B33" s="244" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C33" s="243" t="s">
         <v>271</v>
@@ -22144,7 +22118,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="183" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C35" s="192" t="s">
         <v>270</v>
@@ -22170,7 +22144,7 @@
         <v>312</v>
       </c>
       <c r="J35" s="270" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="30">
@@ -22228,7 +22202,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="176" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C38" s="193" t="s">
         <v>270</v>
@@ -22262,7 +22236,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="210" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C39" s="194" t="s">
         <v>272</v>
@@ -22288,7 +22262,7 @@
         <v>312</v>
       </c>
       <c r="J39" s="273" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="212" customFormat="1" ht="30">
@@ -22344,7 +22318,7 @@
         <v>5</v>
       </c>
       <c r="B42" s="210" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C42" s="213" t="s">
         <v>271</v>
@@ -22378,7 +22352,7 @@
         <v>6</v>
       </c>
       <c r="B43" s="176" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C43" s="194" t="s">
         <v>272</v>
@@ -22412,7 +22386,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="176" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C44" s="195" t="s">
         <v>271</v>
@@ -22481,11 +22455,11 @@
       </c>
       <c r="E46" s="231">
         <f t="shared" si="9"/>
-        <v>2100000</v>
+        <v>3393100</v>
       </c>
       <c r="F46" s="232">
         <f t="shared" si="9"/>
-        <v>1689150</v>
+        <v>2739235.2</v>
       </c>
       <c r="G46" s="167">
         <f t="shared" si="9"/>
@@ -22572,8 +22546,13 @@
       </c>
       <c r="C49" s="249"/>
       <c r="D49" s="256"/>
-      <c r="E49" s="252"/>
-      <c r="F49" s="253"/>
+      <c r="E49" s="252">
+        <v>867500</v>
+      </c>
+      <c r="F49" s="253">
+        <f>IF(E49&gt;0,E49-MIN(E49,4250000)*10%-MIN(E49,1700000)*2%-MAX(0,E49-MIN(E49,4250000)*10%-MIN(E49,1700000)*2%-129750)*10%,0)</f>
+        <v>700035</v>
+      </c>
       <c r="G49" s="251"/>
       <c r="H49" s="251" t="s">
         <v>305</v>
@@ -22594,8 +22573,13 @@
       </c>
       <c r="C50" s="249"/>
       <c r="D50" s="251"/>
-      <c r="E50" s="257"/>
-      <c r="F50" s="258"/>
+      <c r="E50" s="257">
+        <v>425600</v>
+      </c>
+      <c r="F50" s="258">
+        <f>IF(E50&gt;0,E50-MIN(E50,4250000)*10%-MIN(E50,1700000)*2%-MAX(0,E50-MIN(E50,4250000)*10%-MIN(E50,1700000)*2%-129750)*10%,0)</f>
+        <v>350050.2</v>
+      </c>
       <c r="G50" s="256"/>
       <c r="H50" s="256" t="s">
         <v>305</v>
@@ -22619,15 +22603,15 @@
       </c>
       <c r="E51" s="233">
         <f t="shared" si="10"/>
-        <v>31200000</v>
+        <v>32293100</v>
       </c>
       <c r="F51" s="235">
         <f t="shared" si="10"/>
-        <v>25099650</v>
+        <v>25991335.199999999</v>
       </c>
       <c r="G51" s="234">
         <f t="shared" si="10"/>
-        <v>374400</v>
+        <v>372000</v>
       </c>
       <c r="H51" s="234"/>
       <c r="I51" s="234"/>
@@ -22636,7 +22620,7 @@
     <row r="52" spans="1:10" ht="45">
       <c r="A52" s="241"/>
       <c r="B52" s="217" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C52" s="186"/>
       <c r="D52" s="1"/>
@@ -29836,7 +29820,7 @@
     </row>
     <row r="11" spans="1:6" ht="76.5">
       <c r="A11" s="278" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>354</v>
@@ -29856,7 +29840,7 @@
     </row>
     <row r="12" spans="1:6" ht="51">
       <c r="A12" s="278" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B12" s="280" t="s">
         <v>359</v>
@@ -30141,12 +30125,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="A26:F26"/>
@@ -30154,6 +30132,12 @@
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>

--- a/TAZA/_документы/Штатка Фонда и проектного офиса.xlsx
+++ b/TAZA/_документы/Штатка Фонда и проектного офиса.xlsx
@@ -5606,6 +5606,42 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5618,48 +5654,90 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="34" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5669,18 +5747,69 @@
     <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="33" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="34" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="35" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="32" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="39" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="3" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="10" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="2" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="17" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="32" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5690,139 +5819,19 @@
     <xf numFmtId="0" fontId="46" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="32" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="10" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="2" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="17" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="39" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="3" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="33" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="34" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="35" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="34" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5837,43 +5846,145 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="2" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="2" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="2" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="2" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5882,24 +5993,6 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5950,99 +6043,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6384,7 +6384,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6442,7 +6442,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6497,7 +6497,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10274,26 +10274,26 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="310" t="s">
+      <c r="A2" s="302" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="310"/>
+      <c r="B2" s="302"/>
       <c r="C2" s="132" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="315" t="s">
+      <c r="A3" s="303" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="316"/>
+      <c r="B3" s="304"/>
       <c r="C3" s="133"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="315" t="s">
+      <c r="A4" s="303" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="316" t="s">
+      <c r="B4" s="304" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="133"/>
@@ -10306,24 +10306,24 @@
       <c r="C5" s="133"/>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
-      <c r="A6" s="315" t="s">
+      <c r="A6" s="303" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="316"/>
+      <c r="B6" s="304"/>
       <c r="C6" s="134"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
-      <c r="A7" s="315" t="s">
+      <c r="A7" s="303" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="316"/>
+      <c r="B7" s="304"/>
       <c r="C7" s="135"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="306" t="s">
+      <c r="A8" s="305" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="307"/>
+      <c r="B8" s="306"/>
       <c r="C8" s="131">
         <f>SUM(C3:C7)</f>
         <v>0</v>
@@ -10333,17 +10333,17 @@
       <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="317" t="s">
+      <c r="A10" s="307" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="317"/>
-      <c r="C10" s="317"/>
+      <c r="B10" s="307"/>
+      <c r="C10" s="307"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="310" t="s">
+      <c r="A11" s="302" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="310"/>
+      <c r="B11" s="302"/>
       <c r="C11" s="132" t="s">
         <v>1</v>
       </c>
@@ -10370,10 +10370,10 @@
       <c r="C14" s="136"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="306" t="s">
+      <c r="A15" s="305" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="307"/>
+      <c r="B15" s="306"/>
       <c r="C15" s="130">
         <f>SUM(C12:C14)</f>
         <v>0</v>
@@ -10403,10 +10403,10 @@
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="310" t="s">
+      <c r="A20" s="302" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="310"/>
+      <c r="B20" s="302"/>
       <c r="C20" s="132" t="s">
         <v>1</v>
       </c>
@@ -10451,17 +10451,17 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="311" t="s">
+      <c r="A26" s="310" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="312"/>
-      <c r="C26" s="313"/>
+      <c r="B26" s="311"/>
+      <c r="C26" s="312"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="310" t="s">
+      <c r="A27" s="302" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="310"/>
+      <c r="B27" s="302"/>
       <c r="C27" s="138"/>
     </row>
     <row r="28" spans="1:4">
@@ -10478,17 +10478,17 @@
       <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="314" t="s">
+      <c r="A30" s="313" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="314"/>
+      <c r="B30" s="313"/>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="310" t="s">
+      <c r="A31" s="302" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="310"/>
+      <c r="B31" s="302"/>
       <c r="C31" s="132" t="s">
         <v>1</v>
       </c>
@@ -10525,8 +10525,8 @@
       <c r="D35" s="3"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="302"/>
-      <c r="B36" s="303"/>
+      <c r="A36" s="314"/>
+      <c r="B36" s="315"/>
       <c r="C36" s="144">
         <f>SUM(C32:C35)</f>
         <v>0</v>
@@ -10538,10 +10538,10 @@
       <c r="C37" s="8"/>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="304" t="s">
+      <c r="A38" s="316" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="305"/>
+      <c r="B38" s="317"/>
       <c r="C38" s="145">
         <f>C28-C36</f>
         <v>0</v>
@@ -10564,6 +10564,23 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
@@ -10576,23 +10593,6 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10860,11 +10860,11 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1"/>
-      <c r="B19" s="310" t="s">
+      <c r="B19" s="302" t="s">
         <v>259</v>
       </c>
-      <c r="C19" s="310"/>
-      <c r="D19" s="310"/>
+      <c r="C19" s="302"/>
+      <c r="D19" s="302"/>
       <c r="E19" s="162" t="e">
         <f>E15/E18</f>
         <v>#REF!</v>
@@ -10941,17 +10941,17 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="358" t="s">
+      <c r="B1" s="320" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="358"/>
-      <c r="D1" s="358"/>
-      <c r="E1" s="358"/>
-      <c r="F1" s="358"/>
-      <c r="G1" s="358"/>
-      <c r="H1" s="358"/>
-      <c r="I1" s="358"/>
-      <c r="J1" s="358"/>
+      <c r="C1" s="320"/>
+      <c r="D1" s="320"/>
+      <c r="E1" s="320"/>
+      <c r="F1" s="320"/>
+      <c r="G1" s="320"/>
+      <c r="H1" s="320"/>
+      <c r="I1" s="320"/>
+      <c r="J1" s="320"/>
       <c r="K1" s="85"/>
       <c r="O1" s="51"/>
     </row>
@@ -10989,17 +10989,17 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="359" t="s">
+      <c r="B3" s="321" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
+      <c r="C3" s="321"/>
+      <c r="D3" s="321"/>
+      <c r="E3" s="321"/>
+      <c r="F3" s="321"/>
+      <c r="G3" s="321"/>
+      <c r="H3" s="321"/>
+      <c r="I3" s="321"/>
+      <c r="J3" s="321"/>
       <c r="K3" s="88"/>
       <c r="O3" s="51"/>
     </row>
@@ -11007,17 +11007,17 @@
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="360" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="360"/>
-      <c r="D4" s="360"/>
-      <c r="E4" s="360"/>
-      <c r="F4" s="360"/>
-      <c r="G4" s="360"/>
-      <c r="H4" s="360"/>
-      <c r="I4" s="360"/>
-      <c r="J4" s="360"/>
+      <c r="B4" s="322" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="322"/>
+      <c r="D4" s="322"/>
+      <c r="E4" s="322"/>
+      <c r="F4" s="322"/>
+      <c r="G4" s="322"/>
+      <c r="H4" s="322"/>
+      <c r="I4" s="322"/>
+      <c r="J4" s="322"/>
       <c r="K4" s="89"/>
       <c r="O4" s="51"/>
     </row>
@@ -11025,17 +11025,17 @@
       <c r="A5" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="361" t="s">
+      <c r="B5" s="323" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="361"/>
-      <c r="D5" s="361"/>
-      <c r="E5" s="361"/>
-      <c r="F5" s="361"/>
-      <c r="G5" s="361"/>
-      <c r="H5" s="361"/>
-      <c r="I5" s="361"/>
-      <c r="J5" s="361"/>
+      <c r="C5" s="323"/>
+      <c r="D5" s="323"/>
+      <c r="E5" s="323"/>
+      <c r="F5" s="323"/>
+      <c r="G5" s="323"/>
+      <c r="H5" s="323"/>
+      <c r="I5" s="323"/>
+      <c r="J5" s="323"/>
       <c r="K5" s="90"/>
       <c r="O5" s="51"/>
     </row>
@@ -11043,17 +11043,17 @@
       <c r="A6" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="361" t="s">
+      <c r="B6" s="323" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="361"/>
-      <c r="D6" s="361"/>
-      <c r="E6" s="361"/>
-      <c r="F6" s="361"/>
-      <c r="G6" s="361"/>
-      <c r="H6" s="361"/>
-      <c r="I6" s="361"/>
-      <c r="J6" s="361"/>
+      <c r="C6" s="323"/>
+      <c r="D6" s="323"/>
+      <c r="E6" s="323"/>
+      <c r="F6" s="323"/>
+      <c r="G6" s="323"/>
+      <c r="H6" s="323"/>
+      <c r="I6" s="323"/>
+      <c r="J6" s="323"/>
       <c r="K6" s="90"/>
       <c r="O6" s="51"/>
     </row>
@@ -11061,15 +11061,15 @@
       <c r="A7" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="362" t="s">
+      <c r="B7" s="324" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="362"/>
-      <c r="D7" s="362"/>
-      <c r="E7" s="362"/>
-      <c r="F7" s="362"/>
-      <c r="G7" s="362"/>
-      <c r="H7" s="362"/>
+      <c r="C7" s="324"/>
+      <c r="D7" s="324"/>
+      <c r="E7" s="324"/>
+      <c r="F7" s="324"/>
+      <c r="G7" s="324"/>
+      <c r="H7" s="324"/>
       <c r="I7" s="91"/>
       <c r="J7" s="71" t="s">
         <v>50</v>
@@ -11095,51 +11095,51 @@
       <c r="A22" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="363" t="s">
+      <c r="B22" s="325" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="366" t="s">
+      <c r="C22" s="328" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="367"/>
-      <c r="E22" s="367"/>
-      <c r="F22" s="367"/>
-      <c r="G22" s="368"/>
+      <c r="D22" s="329"/>
+      <c r="E22" s="329"/>
+      <c r="F22" s="329"/>
+      <c r="G22" s="330"/>
       <c r="H22" s="93"/>
-      <c r="I22" s="367" t="s">
+      <c r="I22" s="329" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="368"/>
+      <c r="J22" s="330"/>
       <c r="K22" s="94"/>
     </row>
     <row r="23" spans="1:16" ht="12" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="364"/>
-      <c r="C23" s="369"/>
-      <c r="D23" s="370"/>
-      <c r="E23" s="370"/>
-      <c r="F23" s="370"/>
-      <c r="G23" s="371"/>
+      <c r="B23" s="326"/>
+      <c r="C23" s="331"/>
+      <c r="D23" s="332"/>
+      <c r="E23" s="332"/>
+      <c r="F23" s="332"/>
+      <c r="G23" s="333"/>
       <c r="H23" s="95"/>
-      <c r="I23" s="370"/>
-      <c r="J23" s="371"/>
+      <c r="I23" s="332"/>
+      <c r="J23" s="333"/>
       <c r="K23" s="94"/>
     </row>
     <row r="24" spans="1:16" ht="24" customHeight="1">
       <c r="A24" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="365"/>
-      <c r="C24" s="372"/>
-      <c r="D24" s="373"/>
-      <c r="E24" s="373"/>
-      <c r="F24" s="373"/>
-      <c r="G24" s="374"/>
+      <c r="B24" s="327"/>
+      <c r="C24" s="334"/>
+      <c r="D24" s="335"/>
+      <c r="E24" s="335"/>
+      <c r="F24" s="335"/>
+      <c r="G24" s="336"/>
       <c r="H24" s="96"/>
-      <c r="I24" s="373"/>
-      <c r="J24" s="374"/>
+      <c r="I24" s="335"/>
+      <c r="J24" s="336"/>
       <c r="K24" s="94"/>
     </row>
     <row r="25" spans="1:16" ht="15.75" hidden="1" customHeight="1"/>
@@ -11181,13 +11181,13 @@
       <c r="B29" s="58">
         <v>1</v>
       </c>
-      <c r="C29" s="324" t="s">
+      <c r="C29" s="337" t="s">
         <v>202</v>
       </c>
-      <c r="D29" s="325"/>
-      <c r="E29" s="325"/>
-      <c r="F29" s="325"/>
-      <c r="G29" s="326"/>
+      <c r="D29" s="338"/>
+      <c r="E29" s="338"/>
+      <c r="F29" s="338"/>
+      <c r="G29" s="339"/>
       <c r="H29" s="97"/>
       <c r="I29" s="97" t="e">
         <f>I35+I44+I46+I47+I50+#REF!+I68+I71+I72+I73+I77+I89+I97+I101+I106+I108+I116+I131+I142+I146+I147+I154+I32+I34+#REF!+#REF!+I151+#REF!+I98+I113+I155</f>
@@ -11204,15 +11204,15 @@
       <c r="B30" s="58">
         <v>2</v>
       </c>
-      <c r="C30" s="333" t="s">
+      <c r="C30" s="340" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="324" t="s">
+      <c r="D30" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="325"/>
-      <c r="F30" s="325"/>
-      <c r="G30" s="326"/>
+      <c r="E30" s="338"/>
+      <c r="F30" s="338"/>
+      <c r="G30" s="339"/>
       <c r="H30" s="97"/>
       <c r="I30" s="97"/>
       <c r="J30" s="99" t="e">
@@ -11232,15 +11232,15 @@
       <c r="B31" s="58">
         <v>3</v>
       </c>
-      <c r="C31" s="334"/>
+      <c r="C31" s="341"/>
       <c r="D31" s="343" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="320" t="s">
+      <c r="E31" s="346" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="321"/>
-      <c r="G31" s="322"/>
+      <c r="F31" s="347"/>
+      <c r="G31" s="348"/>
       <c r="H31" s="72"/>
       <c r="I31" s="72"/>
       <c r="J31" s="100"/>
@@ -11257,13 +11257,13 @@
       <c r="B32" s="58">
         <v>4</v>
       </c>
-      <c r="C32" s="334"/>
+      <c r="C32" s="341"/>
       <c r="D32" s="344"/>
-      <c r="E32" s="320" t="s">
+      <c r="E32" s="346" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="321"/>
-      <c r="G32" s="322"/>
+      <c r="F32" s="347"/>
+      <c r="G32" s="348"/>
       <c r="H32" s="72"/>
       <c r="I32" s="72"/>
       <c r="J32" s="81" t="e">
@@ -11283,13 +11283,13 @@
       <c r="B33" s="58">
         <v>5</v>
       </c>
-      <c r="C33" s="334"/>
+      <c r="C33" s="341"/>
       <c r="D33" s="344"/>
-      <c r="E33" s="353" t="s">
+      <c r="E33" s="349" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="354"/>
-      <c r="G33" s="355"/>
+      <c r="F33" s="350"/>
+      <c r="G33" s="351"/>
       <c r="H33" s="72"/>
       <c r="I33" s="72"/>
       <c r="J33" s="81"/>
@@ -11302,13 +11302,13 @@
       <c r="B34" s="58">
         <v>6</v>
       </c>
-      <c r="C34" s="350"/>
-      <c r="D34" s="352"/>
-      <c r="E34" s="330" t="s">
+      <c r="C34" s="342"/>
+      <c r="D34" s="345"/>
+      <c r="E34" s="353" t="s">
         <v>170</v>
       </c>
-      <c r="F34" s="330"/>
-      <c r="G34" s="330"/>
+      <c r="F34" s="353"/>
+      <c r="G34" s="353"/>
       <c r="H34" s="72"/>
       <c r="I34" s="72"/>
       <c r="J34" s="81" t="e">
@@ -11324,15 +11324,15 @@
       <c r="B35" s="58">
         <v>7</v>
       </c>
-      <c r="C35" s="333" t="s">
+      <c r="C35" s="340" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="324" t="s">
+      <c r="D35" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E35" s="356"/>
-      <c r="F35" s="356"/>
-      <c r="G35" s="357"/>
+      <c r="E35" s="354"/>
+      <c r="F35" s="354"/>
+      <c r="G35" s="355"/>
       <c r="H35" s="97"/>
       <c r="I35" s="101">
         <f>I36+I37</f>
@@ -11348,15 +11348,15 @@
       <c r="B36" s="58">
         <v>8</v>
       </c>
-      <c r="C36" s="334"/>
+      <c r="C36" s="341"/>
       <c r="D36" s="343" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="337" t="s">
+      <c r="E36" s="356" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="338"/>
-      <c r="G36" s="339"/>
+      <c r="F36" s="357"/>
+      <c r="G36" s="358"/>
       <c r="H36" s="72"/>
       <c r="I36" s="72"/>
       <c r="J36" s="81" t="e">
@@ -11373,13 +11373,13 @@
       <c r="B37" s="58">
         <v>9</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="351"/>
-      <c r="E37" s="337" t="s">
+      <c r="C37" s="342"/>
+      <c r="D37" s="352"/>
+      <c r="E37" s="356" t="s">
         <v>173</v>
       </c>
-      <c r="F37" s="338"/>
-      <c r="G37" s="339"/>
+      <c r="F37" s="357"/>
+      <c r="G37" s="358"/>
       <c r="H37" s="72"/>
       <c r="I37" s="72"/>
       <c r="J37" s="81" t="e">
@@ -11396,13 +11396,13 @@
       <c r="B38" s="58">
         <v>10</v>
       </c>
-      <c r="C38" s="324" t="s">
+      <c r="C38" s="337" t="s">
         <v>203</v>
       </c>
-      <c r="D38" s="325"/>
-      <c r="E38" s="325"/>
-      <c r="F38" s="325"/>
-      <c r="G38" s="326"/>
+      <c r="D38" s="338"/>
+      <c r="E38" s="338"/>
+      <c r="F38" s="338"/>
+      <c r="G38" s="339"/>
       <c r="H38" s="97"/>
       <c r="I38" s="97"/>
       <c r="J38" s="102"/>
@@ -11415,15 +11415,15 @@
       <c r="B39" s="58">
         <v>11</v>
       </c>
-      <c r="C39" s="333" t="s">
+      <c r="C39" s="340" t="s">
         <v>186</v>
       </c>
-      <c r="D39" s="324" t="s">
+      <c r="D39" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E39" s="325"/>
-      <c r="F39" s="325"/>
-      <c r="G39" s="326"/>
+      <c r="E39" s="338"/>
+      <c r="F39" s="338"/>
+      <c r="G39" s="339"/>
       <c r="H39" s="97"/>
       <c r="I39" s="97"/>
       <c r="J39" s="102"/>
@@ -11436,15 +11436,15 @@
       <c r="B40" s="58">
         <v>12</v>
       </c>
-      <c r="C40" s="334"/>
+      <c r="C40" s="341"/>
       <c r="D40" s="343" t="s">
         <v>55</v>
       </c>
-      <c r="E40" s="320" t="s">
+      <c r="E40" s="346" t="s">
         <v>128</v>
       </c>
-      <c r="F40" s="321"/>
-      <c r="G40" s="322"/>
+      <c r="F40" s="347"/>
+      <c r="G40" s="348"/>
       <c r="H40" s="72"/>
       <c r="I40" s="72"/>
       <c r="J40" s="81" t="e">
@@ -11460,13 +11460,13 @@
       <c r="B41" s="58">
         <v>13</v>
       </c>
-      <c r="C41" s="350"/>
-      <c r="D41" s="351"/>
-      <c r="E41" s="320" t="s">
+      <c r="C41" s="342"/>
+      <c r="D41" s="352"/>
+      <c r="E41" s="346" t="s">
         <v>129</v>
       </c>
-      <c r="F41" s="321"/>
-      <c r="G41" s="322"/>
+      <c r="F41" s="347"/>
+      <c r="G41" s="348"/>
       <c r="H41" s="72"/>
       <c r="I41" s="72"/>
       <c r="J41" s="81" t="e">
@@ -11482,15 +11482,15 @@
       <c r="B42" s="58">
         <v>14</v>
       </c>
-      <c r="C42" s="333" t="s">
+      <c r="C42" s="340" t="s">
         <v>204</v>
       </c>
-      <c r="D42" s="324" t="s">
+      <c r="D42" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E42" s="325"/>
-      <c r="F42" s="325"/>
-      <c r="G42" s="326"/>
+      <c r="E42" s="338"/>
+      <c r="F42" s="338"/>
+      <c r="G42" s="339"/>
       <c r="H42" s="97"/>
       <c r="I42" s="97"/>
       <c r="J42" s="102"/>
@@ -11503,15 +11503,15 @@
       <c r="B43" s="58">
         <v>15</v>
       </c>
-      <c r="C43" s="334"/>
+      <c r="C43" s="341"/>
       <c r="D43" s="343" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="320" t="s">
+      <c r="E43" s="346" t="s">
         <v>128</v>
       </c>
-      <c r="F43" s="321"/>
-      <c r="G43" s="322"/>
+      <c r="F43" s="347"/>
+      <c r="G43" s="348"/>
       <c r="H43" s="72"/>
       <c r="I43" s="72"/>
       <c r="J43" s="81" t="e">
@@ -11527,13 +11527,13 @@
       <c r="B44" s="58">
         <v>16</v>
       </c>
-      <c r="C44" s="350"/>
-      <c r="D44" s="351"/>
-      <c r="E44" s="320" t="s">
+      <c r="C44" s="342"/>
+      <c r="D44" s="352"/>
+      <c r="E44" s="346" t="s">
         <v>129</v>
       </c>
-      <c r="F44" s="321"/>
-      <c r="G44" s="322"/>
+      <c r="F44" s="347"/>
+      <c r="G44" s="348"/>
       <c r="H44" s="72"/>
       <c r="I44" s="72"/>
       <c r="J44" s="81" t="e">
@@ -11549,15 +11549,15 @@
       <c r="B45" s="58">
         <v>17</v>
       </c>
-      <c r="C45" s="333" t="s">
+      <c r="C45" s="340" t="s">
         <v>62</v>
       </c>
-      <c r="D45" s="324" t="s">
+      <c r="D45" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="325"/>
-      <c r="F45" s="325"/>
-      <c r="G45" s="326"/>
+      <c r="E45" s="338"/>
+      <c r="F45" s="338"/>
+      <c r="G45" s="339"/>
       <c r="H45" s="97"/>
       <c r="I45" s="97"/>
       <c r="J45" s="102"/>
@@ -11570,15 +11570,15 @@
       <c r="B46" s="58">
         <v>18</v>
       </c>
-      <c r="C46" s="334"/>
+      <c r="C46" s="341"/>
       <c r="D46" s="343" t="s">
         <v>55</v>
       </c>
-      <c r="E46" s="320" t="s">
+      <c r="E46" s="346" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="321"/>
-      <c r="G46" s="322"/>
+      <c r="F46" s="347"/>
+      <c r="G46" s="348"/>
       <c r="H46" s="72"/>
       <c r="I46" s="72"/>
       <c r="J46" s="81" t="e">
@@ -11594,13 +11594,13 @@
       <c r="B47" s="58">
         <v>19</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="320" t="s">
+      <c r="C47" s="342"/>
+      <c r="D47" s="352"/>
+      <c r="E47" s="346" t="s">
         <v>64</v>
       </c>
-      <c r="F47" s="321"/>
-      <c r="G47" s="322"/>
+      <c r="F47" s="347"/>
+      <c r="G47" s="348"/>
       <c r="H47" s="72"/>
       <c r="I47" s="72"/>
       <c r="J47" s="81" t="e">
@@ -11616,15 +11616,15 @@
       <c r="B48" s="58">
         <v>20</v>
       </c>
-      <c r="C48" s="333" t="s">
+      <c r="C48" s="340" t="s">
         <v>205</v>
       </c>
-      <c r="D48" s="324" t="s">
+      <c r="D48" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="325"/>
-      <c r="F48" s="325"/>
-      <c r="G48" s="326"/>
+      <c r="E48" s="338"/>
+      <c r="F48" s="338"/>
+      <c r="G48" s="339"/>
       <c r="H48" s="97"/>
       <c r="I48" s="97"/>
       <c r="J48" s="102"/>
@@ -11637,15 +11637,15 @@
       <c r="B49" s="58">
         <v>21</v>
       </c>
-      <c r="C49" s="334"/>
+      <c r="C49" s="341"/>
       <c r="D49" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="335" t="s">
-        <v>44</v>
-      </c>
-      <c r="F49" s="336"/>
-      <c r="G49" s="336"/>
+      <c r="E49" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" s="360"/>
+      <c r="G49" s="360"/>
       <c r="H49" s="104"/>
       <c r="I49" s="104"/>
       <c r="J49" s="81"/>
@@ -11664,11 +11664,11 @@
       <c r="D50" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E50" s="320" t="s">
+      <c r="E50" s="346" t="s">
         <v>206</v>
       </c>
-      <c r="F50" s="321"/>
-      <c r="G50" s="322"/>
+      <c r="F50" s="347"/>
+      <c r="G50" s="348"/>
       <c r="H50" s="72"/>
       <c r="I50" s="72"/>
       <c r="J50" s="81" t="e">
@@ -11691,11 +11691,11 @@
       <c r="D51" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E51" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="321"/>
-      <c r="G51" s="322"/>
+      <c r="E51" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="347"/>
+      <c r="G51" s="348"/>
       <c r="H51" s="72"/>
       <c r="I51" s="72"/>
       <c r="J51" s="81"/>
@@ -11709,15 +11709,15 @@
       <c r="B52" s="58">
         <v>24</v>
       </c>
-      <c r="C52" s="333" t="s">
+      <c r="C52" s="340" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="324" t="s">
+      <c r="D52" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E52" s="325"/>
-      <c r="F52" s="325"/>
-      <c r="G52" s="326"/>
+      <c r="E52" s="338"/>
+      <c r="F52" s="338"/>
+      <c r="G52" s="339"/>
       <c r="H52" s="97"/>
       <c r="I52" s="97"/>
       <c r="J52" s="102"/>
@@ -11730,15 +11730,15 @@
       <c r="B53" s="58">
         <v>25</v>
       </c>
-      <c r="C53" s="334"/>
+      <c r="C53" s="341"/>
       <c r="D53" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E53" s="320" t="s">
+      <c r="E53" s="346" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="321"/>
-      <c r="G53" s="322"/>
+      <c r="F53" s="347"/>
+      <c r="G53" s="348"/>
       <c r="H53" s="72"/>
       <c r="I53" s="72"/>
       <c r="J53" s="81"/>
@@ -11757,11 +11757,11 @@
       <c r="D54" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E54" s="320" t="s">
+      <c r="E54" s="346" t="s">
         <v>207</v>
       </c>
-      <c r="F54" s="321"/>
-      <c r="G54" s="322"/>
+      <c r="F54" s="347"/>
+      <c r="G54" s="348"/>
       <c r="H54" s="72"/>
       <c r="I54" s="72"/>
       <c r="J54" s="81" t="e">
@@ -11778,15 +11778,15 @@
       <c r="B55" s="58">
         <v>30</v>
       </c>
-      <c r="C55" s="333" t="s">
+      <c r="C55" s="340" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="324" t="s">
+      <c r="D55" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="325"/>
-      <c r="F55" s="325"/>
-      <c r="G55" s="326"/>
+      <c r="E55" s="338"/>
+      <c r="F55" s="338"/>
+      <c r="G55" s="339"/>
       <c r="H55" s="97"/>
       <c r="I55" s="97"/>
       <c r="J55" s="102"/>
@@ -11799,15 +11799,15 @@
       <c r="B56" s="58">
         <v>31</v>
       </c>
-      <c r="C56" s="334"/>
+      <c r="C56" s="341"/>
       <c r="D56" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="320" t="s">
+      <c r="E56" s="346" t="s">
         <v>146</v>
       </c>
-      <c r="F56" s="321"/>
-      <c r="G56" s="322"/>
+      <c r="F56" s="347"/>
+      <c r="G56" s="348"/>
       <c r="H56" s="72"/>
       <c r="I56" s="72"/>
       <c r="J56" s="81"/>
@@ -11820,15 +11820,15 @@
       <c r="B57" s="58">
         <v>32</v>
       </c>
-      <c r="C57" s="334"/>
+      <c r="C57" s="341"/>
       <c r="D57" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="320" t="s">
+      <c r="E57" s="346" t="s">
         <v>147</v>
       </c>
-      <c r="F57" s="321"/>
-      <c r="G57" s="322"/>
+      <c r="F57" s="347"/>
+      <c r="G57" s="348"/>
       <c r="H57" s="72"/>
       <c r="I57" s="72"/>
       <c r="J57" s="81"/>
@@ -11847,11 +11847,11 @@
       <c r="D58" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="320" t="s">
+      <c r="E58" s="346" t="s">
         <v>148</v>
       </c>
-      <c r="F58" s="321"/>
-      <c r="G58" s="322"/>
+      <c r="F58" s="347"/>
+      <c r="G58" s="348"/>
       <c r="H58" s="72"/>
       <c r="I58" s="72"/>
       <c r="J58" s="81"/>
@@ -11870,11 +11870,11 @@
       <c r="D59" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E59" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F59" s="321"/>
-      <c r="G59" s="322"/>
+      <c r="E59" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F59" s="347"/>
+      <c r="G59" s="348"/>
       <c r="H59" s="72"/>
       <c r="I59" s="72"/>
       <c r="J59" s="81"/>
@@ -11888,15 +11888,15 @@
       <c r="B60" s="58">
         <v>35</v>
       </c>
-      <c r="C60" s="333" t="s">
+      <c r="C60" s="340" t="s">
         <v>190</v>
       </c>
-      <c r="D60" s="324" t="s">
+      <c r="D60" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E60" s="325"/>
-      <c r="F60" s="325"/>
-      <c r="G60" s="326"/>
+      <c r="E60" s="338"/>
+      <c r="F60" s="338"/>
+      <c r="G60" s="339"/>
       <c r="H60" s="97"/>
       <c r="I60" s="97"/>
       <c r="J60" s="102"/>
@@ -11909,15 +11909,15 @@
       <c r="B61" s="58">
         <v>36</v>
       </c>
-      <c r="C61" s="334"/>
+      <c r="C61" s="341"/>
       <c r="D61" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E61" s="320" t="s">
+      <c r="E61" s="346" t="s">
         <v>128</v>
       </c>
-      <c r="F61" s="321"/>
-      <c r="G61" s="322"/>
+      <c r="F61" s="347"/>
+      <c r="G61" s="348"/>
       <c r="H61" s="72"/>
       <c r="I61" s="72"/>
       <c r="J61" s="81"/>
@@ -11930,15 +11930,15 @@
       <c r="B62" s="58">
         <v>37</v>
       </c>
-      <c r="C62" s="334"/>
+      <c r="C62" s="341"/>
       <c r="D62" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E62" s="320" t="s">
+      <c r="E62" s="346" t="s">
         <v>154</v>
       </c>
-      <c r="F62" s="321"/>
-      <c r="G62" s="322"/>
+      <c r="F62" s="347"/>
+      <c r="G62" s="348"/>
       <c r="H62" s="72"/>
       <c r="I62" s="72"/>
       <c r="J62" s="81"/>
@@ -11957,11 +11957,11 @@
       <c r="D63" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E63" s="320" t="s">
+      <c r="E63" s="346" t="s">
         <v>208</v>
       </c>
-      <c r="F63" s="321"/>
-      <c r="G63" s="322"/>
+      <c r="F63" s="347"/>
+      <c r="G63" s="348"/>
       <c r="H63" s="72"/>
       <c r="I63" s="72"/>
       <c r="J63" s="81"/>
@@ -11980,11 +11980,11 @@
       <c r="D64" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E64" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F64" s="321"/>
-      <c r="G64" s="322"/>
+      <c r="E64" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F64" s="347"/>
+      <c r="G64" s="348"/>
       <c r="H64" s="72"/>
       <c r="I64" s="72"/>
       <c r="J64" s="81"/>
@@ -11998,15 +11998,15 @@
       <c r="B65" s="58">
         <v>40</v>
       </c>
-      <c r="C65" s="333" t="s">
+      <c r="C65" s="340" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="324" t="s">
+      <c r="D65" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E65" s="325"/>
-      <c r="F65" s="325"/>
-      <c r="G65" s="326"/>
+      <c r="E65" s="338"/>
+      <c r="F65" s="338"/>
+      <c r="G65" s="339"/>
       <c r="H65" s="97"/>
       <c r="I65" s="97"/>
       <c r="J65" s="102"/>
@@ -12019,17 +12019,17 @@
       <c r="B66" s="58">
         <v>41</v>
       </c>
-      <c r="C66" s="334"/>
+      <c r="C66" s="341"/>
       <c r="D66" s="66" t="s">
         <v>55</v>
       </c>
       <c r="E66" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="F66" s="324" t="s">
+      <c r="F66" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="G66" s="326"/>
+      <c r="G66" s="339"/>
       <c r="H66" s="97"/>
       <c r="I66" s="97"/>
       <c r="J66" s="102"/>
@@ -12042,7 +12042,7 @@
       <c r="B67" s="58">
         <v>42</v>
       </c>
-      <c r="C67" s="334"/>
+      <c r="C67" s="341"/>
       <c r="D67" s="67" t="s">
         <v>44</v>
       </c>
@@ -12135,10 +12135,10 @@
       <c r="E70" s="103" t="s">
         <v>210</v>
       </c>
-      <c r="F70" s="324" t="s">
+      <c r="F70" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="G70" s="326"/>
+      <c r="G70" s="339"/>
       <c r="H70" s="97"/>
       <c r="I70" s="97"/>
       <c r="J70" s="102"/>
@@ -12307,10 +12307,10 @@
       <c r="E76" s="103" t="s">
         <v>214</v>
       </c>
-      <c r="F76" s="324" t="s">
+      <c r="F76" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="G76" s="326"/>
+      <c r="G76" s="339"/>
       <c r="H76" s="97"/>
       <c r="I76" s="97"/>
       <c r="J76" s="102"/>
@@ -12412,13 +12412,13 @@
       <c r="D80" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E80" s="345" t="s">
+      <c r="E80" s="361" t="s">
         <v>216</v>
       </c>
-      <c r="F80" s="324" t="s">
+      <c r="F80" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="G80" s="326"/>
+      <c r="G80" s="339"/>
       <c r="H80" s="97"/>
       <c r="I80" s="97"/>
       <c r="J80" s="102"/>
@@ -12438,15 +12438,15 @@
       <c r="D81" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E81" s="346"/>
+      <c r="E81" s="362"/>
       <c r="F81" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="G81" s="347" t="s">
+      <c r="G81" s="363" t="s">
         <v>136</v>
       </c>
-      <c r="H81" s="348"/>
-      <c r="I81" s="349"/>
+      <c r="H81" s="364"/>
+      <c r="I81" s="365"/>
       <c r="J81" s="81" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -12525,13 +12525,13 @@
       <c r="D84" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E84" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F84" s="324" t="s">
+      <c r="E84" s="361" t="s">
+        <v>44</v>
+      </c>
+      <c r="F84" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="G84" s="326"/>
+      <c r="G84" s="339"/>
       <c r="H84" s="97"/>
       <c r="I84" s="97"/>
       <c r="J84" s="102"/>
@@ -12551,7 +12551,7 @@
       <c r="D85" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E85" s="346"/>
+      <c r="E85" s="362"/>
       <c r="F85" s="66" t="s">
         <v>55</v>
       </c>
@@ -12600,15 +12600,15 @@
       <c r="B87" s="58">
         <v>62</v>
       </c>
-      <c r="C87" s="333" t="s">
+      <c r="C87" s="340" t="s">
         <v>144</v>
       </c>
-      <c r="D87" s="324" t="s">
+      <c r="D87" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E87" s="325"/>
-      <c r="F87" s="325"/>
-      <c r="G87" s="326"/>
+      <c r="E87" s="338"/>
+      <c r="F87" s="338"/>
+      <c r="G87" s="339"/>
       <c r="H87" s="97"/>
       <c r="I87" s="110"/>
       <c r="J87" s="102"/>
@@ -12621,15 +12621,15 @@
       <c r="B88" s="58">
         <v>63</v>
       </c>
-      <c r="C88" s="334"/>
+      <c r="C88" s="341"/>
       <c r="D88" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E88" s="335" t="s">
-        <v>44</v>
-      </c>
-      <c r="F88" s="336"/>
-      <c r="G88" s="336"/>
+      <c r="E88" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="F88" s="360"/>
+      <c r="G88" s="360"/>
       <c r="H88" s="104"/>
       <c r="I88" s="104"/>
       <c r="J88" s="81" t="e">
@@ -12651,11 +12651,11 @@
       <c r="D89" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F89" s="321"/>
-      <c r="G89" s="322"/>
+      <c r="E89" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F89" s="347"/>
+      <c r="G89" s="348"/>
       <c r="H89" s="72"/>
       <c r="I89" s="109"/>
       <c r="J89" s="81"/>
@@ -12675,11 +12675,11 @@
       <c r="D90" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E90" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F90" s="321"/>
-      <c r="G90" s="322"/>
+      <c r="E90" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F90" s="347"/>
+      <c r="G90" s="348"/>
       <c r="H90" s="72"/>
       <c r="I90" s="109"/>
       <c r="J90" s="81"/>
@@ -12693,15 +12693,15 @@
       <c r="B91" s="58">
         <v>66</v>
       </c>
-      <c r="C91" s="333" t="s">
+      <c r="C91" s="340" t="s">
         <v>189</v>
       </c>
-      <c r="D91" s="324" t="s">
+      <c r="D91" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="325"/>
-      <c r="F91" s="325"/>
-      <c r="G91" s="326"/>
+      <c r="E91" s="338"/>
+      <c r="F91" s="338"/>
+      <c r="G91" s="339"/>
       <c r="H91" s="97"/>
       <c r="I91" s="110"/>
       <c r="J91" s="102"/>
@@ -12714,15 +12714,15 @@
       <c r="B92" s="58">
         <v>67</v>
       </c>
-      <c r="C92" s="334"/>
+      <c r="C92" s="341"/>
       <c r="D92" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E92" s="335" t="s">
-        <v>44</v>
-      </c>
-      <c r="F92" s="336"/>
-      <c r="G92" s="336"/>
+      <c r="E92" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="F92" s="360"/>
+      <c r="G92" s="360"/>
       <c r="H92" s="104"/>
       <c r="I92" s="104"/>
       <c r="J92" s="81"/>
@@ -12741,11 +12741,11 @@
       <c r="D93" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F93" s="321"/>
-      <c r="G93" s="322"/>
+      <c r="E93" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F93" s="347"/>
+      <c r="G93" s="348"/>
       <c r="H93" s="72"/>
       <c r="I93" s="109"/>
       <c r="J93" s="81"/>
@@ -12765,11 +12765,11 @@
       <c r="D94" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E94" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F94" s="321"/>
-      <c r="G94" s="322"/>
+      <c r="E94" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F94" s="347"/>
+      <c r="G94" s="348"/>
       <c r="H94" s="72"/>
       <c r="I94" s="109"/>
       <c r="J94" s="81"/>
@@ -12783,15 +12783,15 @@
       <c r="B95" s="58">
         <v>70</v>
       </c>
-      <c r="C95" s="333" t="s">
+      <c r="C95" s="340" t="s">
         <v>137</v>
       </c>
-      <c r="D95" s="324" t="s">
+      <c r="D95" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E95" s="325"/>
-      <c r="F95" s="325"/>
-      <c r="G95" s="326"/>
+      <c r="E95" s="338"/>
+      <c r="F95" s="338"/>
+      <c r="G95" s="339"/>
       <c r="H95" s="97"/>
       <c r="I95" s="110"/>
       <c r="J95" s="102"/>
@@ -12804,15 +12804,15 @@
       <c r="B96" s="58">
         <v>71</v>
       </c>
-      <c r="C96" s="334"/>
+      <c r="C96" s="341"/>
       <c r="D96" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E96" s="335" t="s">
-        <v>44</v>
-      </c>
-      <c r="F96" s="336"/>
-      <c r="G96" s="336"/>
+      <c r="E96" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="F96" s="360"/>
+      <c r="G96" s="360"/>
       <c r="H96" s="104"/>
       <c r="I96" s="104"/>
       <c r="J96" s="81"/>
@@ -12831,11 +12831,11 @@
       <c r="D97" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E97" s="320" t="s">
+      <c r="E97" s="346" t="s">
         <v>217</v>
       </c>
-      <c r="F97" s="321"/>
-      <c r="G97" s="322"/>
+      <c r="F97" s="347"/>
+      <c r="G97" s="348"/>
       <c r="H97" s="72"/>
       <c r="I97" s="109"/>
       <c r="J97" s="81" t="e">
@@ -12850,11 +12850,11 @@
       <c r="B98" s="58"/>
       <c r="C98" s="77"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="320" t="s">
+      <c r="E98" s="346" t="s">
         <v>218</v>
       </c>
-      <c r="F98" s="321"/>
-      <c r="G98" s="322"/>
+      <c r="F98" s="347"/>
+      <c r="G98" s="348"/>
       <c r="H98" s="72"/>
       <c r="I98" s="109"/>
       <c r="J98" s="81"/>
@@ -12866,9 +12866,9 @@
       <c r="B99" s="58"/>
       <c r="C99" s="77"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="320"/>
-      <c r="F99" s="321"/>
-      <c r="G99" s="322"/>
+      <c r="E99" s="346"/>
+      <c r="F99" s="347"/>
+      <c r="G99" s="348"/>
       <c r="H99" s="72"/>
       <c r="I99" s="109"/>
       <c r="J99" s="81"/>
@@ -12888,11 +12888,11 @@
       <c r="D100" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E100" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F100" s="321"/>
-      <c r="G100" s="322"/>
+      <c r="E100" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F100" s="347"/>
+      <c r="G100" s="348"/>
       <c r="H100" s="72"/>
       <c r="I100" s="109"/>
       <c r="J100" s="81"/>
@@ -12906,15 +12906,15 @@
       <c r="B101" s="58">
         <v>75</v>
       </c>
-      <c r="C101" s="333" t="s">
+      <c r="C101" s="340" t="s">
         <v>17</v>
       </c>
-      <c r="D101" s="324" t="s">
+      <c r="D101" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E101" s="325"/>
-      <c r="F101" s="325"/>
-      <c r="G101" s="326"/>
+      <c r="E101" s="338"/>
+      <c r="F101" s="338"/>
+      <c r="G101" s="339"/>
       <c r="H101" s="97"/>
       <c r="I101" s="111">
         <f>I102+I103+I104</f>
@@ -12930,15 +12930,15 @@
       <c r="B102" s="58">
         <v>76</v>
       </c>
-      <c r="C102" s="334"/>
+      <c r="C102" s="341"/>
       <c r="D102" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E102" s="337" t="s">
+      <c r="E102" s="356" t="s">
         <v>219</v>
       </c>
-      <c r="F102" s="338"/>
-      <c r="G102" s="339"/>
+      <c r="F102" s="357"/>
+      <c r="G102" s="358"/>
       <c r="H102" s="72"/>
       <c r="I102" s="109"/>
       <c r="J102" s="81">
@@ -12954,15 +12954,15 @@
       <c r="B103" s="58">
         <v>77</v>
       </c>
-      <c r="C103" s="334"/>
+      <c r="C103" s="341"/>
       <c r="D103" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E103" s="337" t="s">
+      <c r="E103" s="356" t="s">
         <v>220</v>
       </c>
-      <c r="F103" s="338"/>
-      <c r="G103" s="339"/>
+      <c r="F103" s="357"/>
+      <c r="G103" s="358"/>
       <c r="H103" s="72"/>
       <c r="I103" s="72"/>
       <c r="J103" s="81">
@@ -12984,11 +12984,11 @@
       <c r="D104" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E104" s="337" t="s">
+      <c r="E104" s="356" t="s">
         <v>221</v>
       </c>
-      <c r="F104" s="338"/>
-      <c r="G104" s="339"/>
+      <c r="F104" s="357"/>
+      <c r="G104" s="358"/>
       <c r="H104" s="72"/>
       <c r="I104" s="72"/>
       <c r="J104" s="81">
@@ -13004,13 +13004,13 @@
       <c r="B105" s="58">
         <v>83</v>
       </c>
-      <c r="C105" s="324" t="s">
+      <c r="C105" s="337" t="s">
         <v>7</v>
       </c>
-      <c r="D105" s="325"/>
-      <c r="E105" s="325"/>
-      <c r="F105" s="325"/>
-      <c r="G105" s="326"/>
+      <c r="D105" s="338"/>
+      <c r="E105" s="338"/>
+      <c r="F105" s="338"/>
+      <c r="G105" s="339"/>
       <c r="H105" s="97"/>
       <c r="I105" s="97"/>
       <c r="J105" s="102" t="e">
@@ -13026,13 +13026,13 @@
       <c r="B106" s="58">
         <v>84</v>
       </c>
-      <c r="C106" s="324" t="s">
+      <c r="C106" s="337" t="s">
         <v>222</v>
       </c>
-      <c r="D106" s="325"/>
-      <c r="E106" s="325"/>
-      <c r="F106" s="325"/>
-      <c r="G106" s="326"/>
+      <c r="D106" s="338"/>
+      <c r="E106" s="338"/>
+      <c r="F106" s="338"/>
+      <c r="G106" s="339"/>
       <c r="H106" s="97"/>
       <c r="I106" s="101"/>
       <c r="J106" s="102" t="e">
@@ -13048,15 +13048,15 @@
       <c r="B107" s="58">
         <v>85</v>
       </c>
-      <c r="C107" s="333" t="s">
+      <c r="C107" s="340" t="s">
         <v>223</v>
       </c>
-      <c r="D107" s="324" t="s">
+      <c r="D107" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E107" s="325"/>
-      <c r="F107" s="325"/>
-      <c r="G107" s="326"/>
+      <c r="E107" s="338"/>
+      <c r="F107" s="338"/>
+      <c r="G107" s="339"/>
       <c r="H107" s="97"/>
       <c r="I107" s="97"/>
       <c r="J107" s="102"/>
@@ -13069,15 +13069,15 @@
       <c r="B108" s="58">
         <v>86</v>
       </c>
-      <c r="C108" s="334"/>
+      <c r="C108" s="341"/>
       <c r="D108" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E108" s="337" t="s">
+      <c r="E108" s="356" t="s">
         <v>224</v>
       </c>
-      <c r="F108" s="338"/>
-      <c r="G108" s="339"/>
+      <c r="F108" s="357"/>
+      <c r="G108" s="358"/>
       <c r="H108" s="72"/>
       <c r="I108" s="63"/>
       <c r="J108" s="81" t="e">
@@ -13099,11 +13099,11 @@
       <c r="D109" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E109" s="320" t="s">
+      <c r="E109" s="346" t="s">
         <v>225</v>
       </c>
-      <c r="F109" s="321"/>
-      <c r="G109" s="322"/>
+      <c r="F109" s="347"/>
+      <c r="G109" s="348"/>
       <c r="H109" s="72"/>
       <c r="I109" s="63"/>
       <c r="J109" s="81"/>
@@ -13123,11 +13123,11 @@
       <c r="D110" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E110" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F110" s="321"/>
-      <c r="G110" s="322"/>
+      <c r="E110" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F110" s="347"/>
+      <c r="G110" s="348"/>
       <c r="H110" s="72"/>
       <c r="I110" s="72"/>
       <c r="J110" s="81"/>
@@ -13141,15 +13141,15 @@
       <c r="B111" s="58">
         <v>89</v>
       </c>
-      <c r="C111" s="333" t="s">
+      <c r="C111" s="340" t="s">
         <v>192</v>
       </c>
-      <c r="D111" s="324" t="s">
+      <c r="D111" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E111" s="325"/>
-      <c r="F111" s="325"/>
-      <c r="G111" s="326"/>
+      <c r="E111" s="338"/>
+      <c r="F111" s="338"/>
+      <c r="G111" s="339"/>
       <c r="H111" s="97"/>
       <c r="I111" s="97"/>
       <c r="J111" s="102"/>
@@ -13162,15 +13162,15 @@
       <c r="B112" s="58">
         <v>90</v>
       </c>
-      <c r="C112" s="334"/>
+      <c r="C112" s="341"/>
       <c r="D112" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E112" s="337" t="s">
+      <c r="E112" s="356" t="s">
         <v>226</v>
       </c>
-      <c r="F112" s="338"/>
-      <c r="G112" s="339"/>
+      <c r="F112" s="357"/>
+      <c r="G112" s="358"/>
       <c r="H112" s="72"/>
       <c r="I112" s="72"/>
       <c r="J112" s="81"/>
@@ -13189,11 +13189,11 @@
       <c r="D113" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E113" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F113" s="321"/>
-      <c r="G113" s="322"/>
+      <c r="E113" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F113" s="347"/>
+      <c r="G113" s="348"/>
       <c r="H113" s="72"/>
       <c r="I113" s="72"/>
       <c r="J113" s="81"/>
@@ -13206,15 +13206,15 @@
       <c r="B114" s="58">
         <v>92</v>
       </c>
-      <c r="C114" s="333" t="s">
+      <c r="C114" s="340" t="s">
         <v>191</v>
       </c>
-      <c r="D114" s="324" t="s">
+      <c r="D114" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E114" s="325"/>
-      <c r="F114" s="325"/>
-      <c r="G114" s="326"/>
+      <c r="E114" s="338"/>
+      <c r="F114" s="338"/>
+      <c r="G114" s="339"/>
       <c r="H114" s="97"/>
       <c r="I114" s="97"/>
       <c r="J114" s="102"/>
@@ -13227,15 +13227,15 @@
       <c r="B115" s="58">
         <v>93</v>
       </c>
-      <c r="C115" s="334"/>
+      <c r="C115" s="341"/>
       <c r="D115" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E115" s="335" t="s">
-        <v>44</v>
-      </c>
-      <c r="F115" s="336"/>
-      <c r="G115" s="336"/>
+      <c r="E115" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="F115" s="360"/>
+      <c r="G115" s="360"/>
       <c r="H115" s="104"/>
       <c r="I115" s="104"/>
       <c r="J115" s="112"/>
@@ -13254,11 +13254,11 @@
       <c r="D116" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E116" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F116" s="321"/>
-      <c r="G116" s="322"/>
+      <c r="E116" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F116" s="347"/>
+      <c r="G116" s="348"/>
       <c r="H116" s="72"/>
       <c r="I116" s="63"/>
       <c r="J116" s="81"/>
@@ -13278,11 +13278,11 @@
       <c r="D117" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E117" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F117" s="321"/>
-      <c r="G117" s="322"/>
+      <c r="E117" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F117" s="347"/>
+      <c r="G117" s="348"/>
       <c r="H117" s="72"/>
       <c r="I117" s="72"/>
       <c r="J117" s="81"/>
@@ -13296,15 +13296,15 @@
       <c r="B118" s="58">
         <v>96</v>
       </c>
-      <c r="C118" s="333" t="s">
+      <c r="C118" s="340" t="s">
         <v>149</v>
       </c>
-      <c r="D118" s="324" t="s">
+      <c r="D118" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E118" s="325"/>
-      <c r="F118" s="325"/>
-      <c r="G118" s="326"/>
+      <c r="E118" s="338"/>
+      <c r="F118" s="338"/>
+      <c r="G118" s="339"/>
       <c r="H118" s="97"/>
       <c r="I118" s="97"/>
       <c r="J118" s="102"/>
@@ -13317,15 +13317,15 @@
       <c r="B119" s="58">
         <v>97</v>
       </c>
-      <c r="C119" s="334"/>
+      <c r="C119" s="341"/>
       <c r="D119" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E119" s="337" t="s">
+      <c r="E119" s="356" t="s">
         <v>227</v>
       </c>
-      <c r="F119" s="338"/>
-      <c r="G119" s="339"/>
+      <c r="F119" s="357"/>
+      <c r="G119" s="358"/>
       <c r="H119" s="72"/>
       <c r="I119" s="72"/>
       <c r="J119" s="81"/>
@@ -13344,11 +13344,11 @@
       <c r="D120" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E120" s="337" t="s">
+      <c r="E120" s="356" t="s">
         <v>228</v>
       </c>
-      <c r="F120" s="338"/>
-      <c r="G120" s="339"/>
+      <c r="F120" s="357"/>
+      <c r="G120" s="358"/>
       <c r="H120" s="72"/>
       <c r="I120" s="72"/>
       <c r="J120" s="81"/>
@@ -13367,11 +13367,11 @@
       <c r="D121" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E121" s="337" t="s">
+      <c r="E121" s="356" t="s">
         <v>229</v>
       </c>
-      <c r="F121" s="338"/>
-      <c r="G121" s="339"/>
+      <c r="F121" s="357"/>
+      <c r="G121" s="358"/>
       <c r="H121" s="72"/>
       <c r="I121" s="72"/>
       <c r="J121" s="81"/>
@@ -13390,11 +13390,11 @@
       <c r="D122" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E122" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F122" s="321"/>
-      <c r="G122" s="322"/>
+      <c r="E122" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F122" s="347"/>
+      <c r="G122" s="348"/>
       <c r="H122" s="72"/>
       <c r="I122" s="72"/>
       <c r="J122" s="81"/>
@@ -13408,15 +13408,15 @@
       <c r="B123" s="58">
         <v>101</v>
       </c>
-      <c r="C123" s="333" t="s">
+      <c r="C123" s="340" t="s">
         <v>230</v>
       </c>
-      <c r="D123" s="324" t="s">
+      <c r="D123" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E123" s="325"/>
-      <c r="F123" s="325"/>
-      <c r="G123" s="326"/>
+      <c r="E123" s="338"/>
+      <c r="F123" s="338"/>
+      <c r="G123" s="339"/>
       <c r="H123" s="97"/>
       <c r="I123" s="97"/>
       <c r="J123" s="102"/>
@@ -13429,17 +13429,17 @@
       <c r="B124" s="58">
         <v>102</v>
       </c>
-      <c r="C124" s="334"/>
+      <c r="C124" s="341"/>
       <c r="D124" s="66" t="s">
         <v>55</v>
       </c>
       <c r="E124" s="343" t="s">
         <v>231</v>
       </c>
-      <c r="F124" s="324" t="s">
+      <c r="F124" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="G124" s="326"/>
+      <c r="G124" s="339"/>
       <c r="H124" s="97"/>
       <c r="I124" s="97"/>
       <c r="J124" s="102"/>
@@ -13452,7 +13452,7 @@
       <c r="B125" s="58">
         <v>103</v>
       </c>
-      <c r="C125" s="334"/>
+      <c r="C125" s="341"/>
       <c r="D125" s="67" t="s">
         <v>44</v>
       </c>
@@ -13475,7 +13475,7 @@
       <c r="B126" s="58">
         <v>104</v>
       </c>
-      <c r="C126" s="334"/>
+      <c r="C126" s="341"/>
       <c r="D126" s="67" t="s">
         <v>44</v>
       </c>
@@ -13561,11 +13561,11 @@
       <c r="D129" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E129" s="337" t="s">
+      <c r="E129" s="356" t="s">
         <v>234</v>
       </c>
-      <c r="F129" s="338"/>
-      <c r="G129" s="339"/>
+      <c r="F129" s="357"/>
+      <c r="G129" s="358"/>
       <c r="H129" s="72"/>
       <c r="I129" s="72"/>
       <c r="J129" s="81"/>
@@ -13584,11 +13584,11 @@
       <c r="D130" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E130" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F130" s="321"/>
-      <c r="G130" s="322"/>
+      <c r="E130" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F130" s="347"/>
+      <c r="G130" s="348"/>
       <c r="H130" s="72"/>
       <c r="I130" s="72"/>
       <c r="J130" s="81"/>
@@ -13602,15 +13602,15 @@
       <c r="B131" s="58">
         <v>109</v>
       </c>
-      <c r="C131" s="333" t="s">
+      <c r="C131" s="340" t="s">
         <v>175</v>
       </c>
-      <c r="D131" s="324" t="s">
+      <c r="D131" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E131" s="325"/>
-      <c r="F131" s="325"/>
-      <c r="G131" s="326"/>
+      <c r="E131" s="338"/>
+      <c r="F131" s="338"/>
+      <c r="G131" s="339"/>
       <c r="H131" s="97"/>
       <c r="I131" s="101">
         <f>SUM(I132:I136)</f>
@@ -13626,15 +13626,15 @@
       <c r="B132" s="58">
         <v>110</v>
       </c>
-      <c r="C132" s="334"/>
+      <c r="C132" s="341"/>
       <c r="D132" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E132" s="337" t="s">
+      <c r="E132" s="356" t="s">
         <v>91</v>
       </c>
-      <c r="F132" s="338"/>
-      <c r="G132" s="339"/>
+      <c r="F132" s="357"/>
+      <c r="G132" s="358"/>
       <c r="H132" s="72"/>
       <c r="I132" s="72"/>
       <c r="J132" s="81" t="e">
@@ -13650,15 +13650,15 @@
       <c r="B133" s="58">
         <v>111</v>
       </c>
-      <c r="C133" s="334"/>
+      <c r="C133" s="341"/>
       <c r="D133" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E133" s="337" t="s">
+      <c r="E133" s="356" t="s">
         <v>235</v>
       </c>
-      <c r="F133" s="338"/>
-      <c r="G133" s="339"/>
+      <c r="F133" s="357"/>
+      <c r="G133" s="358"/>
       <c r="H133" s="72"/>
       <c r="I133" s="72"/>
       <c r="J133" s="81" t="e">
@@ -13680,11 +13680,11 @@
       <c r="D134" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E134" s="337" t="s">
+      <c r="E134" s="356" t="s">
         <v>11</v>
       </c>
-      <c r="F134" s="338"/>
-      <c r="G134" s="339"/>
+      <c r="F134" s="357"/>
+      <c r="G134" s="358"/>
       <c r="H134" s="72"/>
       <c r="I134" s="72"/>
       <c r="J134" s="81" t="e">
@@ -13706,11 +13706,11 @@
       <c r="D135" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E135" s="337" t="s">
+      <c r="E135" s="356" t="s">
         <v>9</v>
       </c>
-      <c r="F135" s="338"/>
-      <c r="G135" s="339"/>
+      <c r="F135" s="357"/>
+      <c r="G135" s="358"/>
       <c r="H135" s="72"/>
       <c r="I135" s="72"/>
       <c r="J135" s="81" t="e">
@@ -13732,11 +13732,11 @@
       <c r="D136" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E136" s="330" t="s">
+      <c r="E136" s="353" t="s">
         <v>236</v>
       </c>
-      <c r="F136" s="330"/>
-      <c r="G136" s="330"/>
+      <c r="F136" s="353"/>
+      <c r="G136" s="353"/>
       <c r="H136" s="72"/>
       <c r="I136" s="72"/>
       <c r="J136" s="81" t="e">
@@ -13759,11 +13759,11 @@
       <c r="D137" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E137" s="340" t="s">
-        <v>44</v>
-      </c>
-      <c r="F137" s="341"/>
-      <c r="G137" s="342"/>
+      <c r="E137" s="366" t="s">
+        <v>44</v>
+      </c>
+      <c r="F137" s="367"/>
+      <c r="G137" s="368"/>
       <c r="H137" s="115"/>
       <c r="I137" s="115"/>
       <c r="J137" s="116"/>
@@ -13777,15 +13777,15 @@
       <c r="B138" s="58">
         <v>118</v>
       </c>
-      <c r="C138" s="333" t="s">
+      <c r="C138" s="340" t="s">
         <v>237</v>
       </c>
-      <c r="D138" s="324" t="s">
+      <c r="D138" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E138" s="325"/>
-      <c r="F138" s="325"/>
-      <c r="G138" s="326"/>
+      <c r="E138" s="338"/>
+      <c r="F138" s="338"/>
+      <c r="G138" s="339"/>
       <c r="H138" s="97"/>
       <c r="I138" s="117"/>
       <c r="J138" s="118"/>
@@ -13798,15 +13798,15 @@
       <c r="B139" s="58">
         <v>119</v>
       </c>
-      <c r="C139" s="334"/>
+      <c r="C139" s="341"/>
       <c r="D139" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E139" s="337" t="s">
+      <c r="E139" s="356" t="s">
         <v>19</v>
       </c>
-      <c r="F139" s="338"/>
-      <c r="G139" s="339"/>
+      <c r="F139" s="357"/>
+      <c r="G139" s="358"/>
       <c r="H139" s="109"/>
       <c r="I139" s="113"/>
       <c r="J139" s="81" t="e">
@@ -13831,10 +13831,10 @@
       <c r="E140" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="F140" s="324" t="s">
+      <c r="F140" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="G140" s="326"/>
+      <c r="G140" s="339"/>
       <c r="H140" s="110"/>
       <c r="I140" s="97"/>
       <c r="J140" s="102"/>
@@ -13856,7 +13856,7 @@
       <c r="E141" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F141" s="331" t="s">
+      <c r="F141" s="373" t="s">
         <v>55</v>
       </c>
       <c r="G141" s="108" t="s">
@@ -13883,7 +13883,7 @@
       <c r="E142" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F142" s="332"/>
+      <c r="F142" s="374"/>
       <c r="G142" s="60" t="s">
         <v>238</v>
       </c>
@@ -13934,10 +13934,10 @@
       <c r="E144" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="F144" s="324" t="s">
+      <c r="F144" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="G144" s="326"/>
+      <c r="G144" s="339"/>
       <c r="H144" s="97"/>
       <c r="I144" s="110"/>
       <c r="J144" s="102"/>
@@ -13959,7 +13959,7 @@
       <c r="E145" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F145" s="331" t="s">
+      <c r="F145" s="373" t="s">
         <v>55</v>
       </c>
       <c r="G145" s="108" t="s">
@@ -13986,7 +13986,7 @@
       <c r="E146" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F146" s="332"/>
+      <c r="F146" s="374"/>
       <c r="G146" s="60" t="s">
         <v>18</v>
       </c>
@@ -14056,15 +14056,15 @@
       <c r="B149" s="58">
         <v>129</v>
       </c>
-      <c r="C149" s="333" t="s">
+      <c r="C149" s="340" t="s">
         <v>239</v>
       </c>
-      <c r="D149" s="324" t="s">
+      <c r="D149" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E149" s="325"/>
-      <c r="F149" s="325"/>
-      <c r="G149" s="326"/>
+      <c r="E149" s="338"/>
+      <c r="F149" s="338"/>
+      <c r="G149" s="339"/>
       <c r="H149" s="97"/>
       <c r="I149" s="110"/>
       <c r="J149" s="102"/>
@@ -14077,15 +14077,15 @@
       <c r="B150" s="121">
         <v>130</v>
       </c>
-      <c r="C150" s="334"/>
+      <c r="C150" s="341"/>
       <c r="D150" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E150" s="335" t="s">
-        <v>44</v>
-      </c>
-      <c r="F150" s="336"/>
-      <c r="G150" s="336"/>
+      <c r="E150" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="F150" s="360"/>
+      <c r="G150" s="360"/>
       <c r="H150" s="104"/>
       <c r="I150" s="104"/>
       <c r="J150" s="81"/>
@@ -14104,11 +14104,11 @@
       <c r="D151" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E151" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F151" s="321"/>
-      <c r="G151" s="322"/>
+      <c r="E151" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F151" s="347"/>
+      <c r="G151" s="348"/>
       <c r="H151" s="72"/>
       <c r="I151" s="109"/>
       <c r="J151" s="81"/>
@@ -14122,15 +14122,15 @@
       <c r="B152" s="58">
         <v>132</v>
       </c>
-      <c r="C152" s="323" t="s">
+      <c r="C152" s="369" t="s">
         <v>240</v>
       </c>
-      <c r="D152" s="324" t="s">
+      <c r="D152" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E152" s="325"/>
-      <c r="F152" s="325"/>
-      <c r="G152" s="326"/>
+      <c r="E152" s="338"/>
+      <c r="F152" s="338"/>
+      <c r="G152" s="339"/>
       <c r="H152" s="97"/>
       <c r="I152" s="110"/>
       <c r="J152" s="102"/>
@@ -14143,15 +14143,15 @@
       <c r="B153" s="58">
         <v>133</v>
       </c>
-      <c r="C153" s="323"/>
+      <c r="C153" s="369"/>
       <c r="D153" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E153" s="327" t="s">
+      <c r="E153" s="370" t="s">
         <v>241</v>
       </c>
-      <c r="F153" s="328"/>
-      <c r="G153" s="329"/>
+      <c r="F153" s="371"/>
+      <c r="G153" s="372"/>
       <c r="H153" s="122"/>
       <c r="I153" s="123"/>
       <c r="J153" s="81"/>
@@ -14170,11 +14170,11 @@
       <c r="D154" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E154" s="330" t="s">
+      <c r="E154" s="353" t="s">
         <v>198</v>
       </c>
-      <c r="F154" s="330"/>
-      <c r="G154" s="330"/>
+      <c r="F154" s="353"/>
+      <c r="G154" s="353"/>
       <c r="H154" s="72"/>
       <c r="I154" s="120" t="e">
         <f>SUM(#REF!)</f>
@@ -14200,15 +14200,120 @@
     </row>
   </sheetData>
   <mergeCells count="142">
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:G24"/>
-    <mergeCell ref="I22:J24"/>
+    <mergeCell ref="E151:G151"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:G152"/>
+    <mergeCell ref="E153:G153"/>
+    <mergeCell ref="E154:G154"/>
+    <mergeCell ref="F140:G140"/>
+    <mergeCell ref="F141:F142"/>
+    <mergeCell ref="F144:G144"/>
+    <mergeCell ref="F145:F146"/>
+    <mergeCell ref="C149:C150"/>
+    <mergeCell ref="D149:G149"/>
+    <mergeCell ref="E150:G150"/>
+    <mergeCell ref="E134:G134"/>
+    <mergeCell ref="E135:G135"/>
+    <mergeCell ref="E136:G136"/>
+    <mergeCell ref="E137:G137"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:G138"/>
+    <mergeCell ref="E139:G139"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="E130:G130"/>
+    <mergeCell ref="C131:C133"/>
+    <mergeCell ref="D131:G131"/>
+    <mergeCell ref="E132:G132"/>
+    <mergeCell ref="E133:G133"/>
+    <mergeCell ref="E121:G121"/>
+    <mergeCell ref="E122:G122"/>
+    <mergeCell ref="C123:C126"/>
+    <mergeCell ref="D123:G123"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="E116:G116"/>
+    <mergeCell ref="E117:G117"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:G118"/>
+    <mergeCell ref="E119:G119"/>
+    <mergeCell ref="E120:G120"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="D111:G111"/>
+    <mergeCell ref="E112:G112"/>
+    <mergeCell ref="E113:G113"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:G114"/>
+    <mergeCell ref="E115:G115"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="D107:G107"/>
+    <mergeCell ref="E108:G108"/>
+    <mergeCell ref="E109:G109"/>
+    <mergeCell ref="E110:G110"/>
+    <mergeCell ref="E104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="E98:G98"/>
+    <mergeCell ref="E99:G99"/>
+    <mergeCell ref="E100:G100"/>
+    <mergeCell ref="C101:C103"/>
+    <mergeCell ref="D101:G101"/>
+    <mergeCell ref="E102:G102"/>
+    <mergeCell ref="E103:G103"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="E94:G94"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:G95"/>
+    <mergeCell ref="E96:G96"/>
+    <mergeCell ref="E97:G97"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:G87"/>
+    <mergeCell ref="E88:G88"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="E90:G90"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="D91:G91"/>
+    <mergeCell ref="E92:G92"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="G81:I81"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="C65:C67"/>
+    <mergeCell ref="D65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D55:G55"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="E47:G47"/>
     <mergeCell ref="C29:G29"/>
     <mergeCell ref="C30:C34"/>
     <mergeCell ref="D30:G30"/>
@@ -14228,120 +14333,15 @@
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="E36:G36"/>
     <mergeCell ref="E37:G37"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:G48"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:G46"/>
-    <mergeCell ref="E47:G47"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="D60:G60"/>
-    <mergeCell ref="E61:G61"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D55:G55"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="G81:I81"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="E64:G64"/>
-    <mergeCell ref="C65:C67"/>
-    <mergeCell ref="D65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="E94:G94"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="D95:G95"/>
-    <mergeCell ref="E96:G96"/>
-    <mergeCell ref="E97:G97"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:G87"/>
-    <mergeCell ref="E88:G88"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="E90:G90"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="D91:G91"/>
-    <mergeCell ref="E92:G92"/>
-    <mergeCell ref="E104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="E98:G98"/>
-    <mergeCell ref="E99:G99"/>
-    <mergeCell ref="E100:G100"/>
-    <mergeCell ref="C101:C103"/>
-    <mergeCell ref="D101:G101"/>
-    <mergeCell ref="E102:G102"/>
-    <mergeCell ref="E103:G103"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="D111:G111"/>
-    <mergeCell ref="E112:G112"/>
-    <mergeCell ref="E113:G113"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="D114:G114"/>
-    <mergeCell ref="E115:G115"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="D107:G107"/>
-    <mergeCell ref="E108:G108"/>
-    <mergeCell ref="E109:G109"/>
-    <mergeCell ref="E110:G110"/>
-    <mergeCell ref="E121:G121"/>
-    <mergeCell ref="E122:G122"/>
-    <mergeCell ref="C123:C126"/>
-    <mergeCell ref="D123:G123"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="E116:G116"/>
-    <mergeCell ref="E117:G117"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:G118"/>
-    <mergeCell ref="E119:G119"/>
-    <mergeCell ref="E120:G120"/>
-    <mergeCell ref="E134:G134"/>
-    <mergeCell ref="E135:G135"/>
-    <mergeCell ref="E136:G136"/>
-    <mergeCell ref="E137:G137"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:G138"/>
-    <mergeCell ref="E139:G139"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="E130:G130"/>
-    <mergeCell ref="C131:C133"/>
-    <mergeCell ref="D131:G131"/>
-    <mergeCell ref="E132:G132"/>
-    <mergeCell ref="E133:G133"/>
-    <mergeCell ref="E151:G151"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D152:G152"/>
-    <mergeCell ref="E153:G153"/>
-    <mergeCell ref="E154:G154"/>
-    <mergeCell ref="F140:G140"/>
-    <mergeCell ref="F141:F142"/>
-    <mergeCell ref="F144:G144"/>
-    <mergeCell ref="F145:F146"/>
-    <mergeCell ref="C149:C150"/>
-    <mergeCell ref="D149:G149"/>
-    <mergeCell ref="E150:G150"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:G24"/>
+    <mergeCell ref="I22:J24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="64" orientation="portrait" r:id="rId1"/>
@@ -14371,15 +14371,15 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="358" t="s">
+      <c r="B1" s="320" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="358"/>
-      <c r="D1" s="358"/>
-      <c r="E1" s="358"/>
-      <c r="F1" s="358"/>
-      <c r="G1" s="358"/>
-      <c r="H1" s="358"/>
+      <c r="C1" s="320"/>
+      <c r="D1" s="320"/>
+      <c r="E1" s="320"/>
+      <c r="F1" s="320"/>
+      <c r="G1" s="320"/>
+      <c r="H1" s="320"/>
       <c r="L1" s="51"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1">
@@ -14413,30 +14413,30 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="359" t="s">
+      <c r="B3" s="321" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
+      <c r="C3" s="321"/>
+      <c r="D3" s="321"/>
+      <c r="E3" s="321"/>
+      <c r="F3" s="321"/>
+      <c r="G3" s="321"/>
+      <c r="H3" s="321"/>
       <c r="L3" s="51"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="360" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="360"/>
-      <c r="D4" s="360"/>
-      <c r="E4" s="360"/>
-      <c r="F4" s="360"/>
-      <c r="G4" s="360"/>
-      <c r="H4" s="360"/>
+      <c r="B4" s="322" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="322"/>
+      <c r="D4" s="322"/>
+      <c r="E4" s="322"/>
+      <c r="F4" s="322"/>
+      <c r="G4" s="322"/>
+      <c r="H4" s="322"/>
       <c r="L4" s="51"/>
       <c r="M4" s="53"/>
     </row>
@@ -14458,40 +14458,40 @@
       <c r="A19" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="383" t="s">
+      <c r="B19" s="375" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="366" t="s">
+      <c r="C19" s="328" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="367"/>
-      <c r="E19" s="367"/>
-      <c r="F19" s="367"/>
-      <c r="G19" s="368"/>
+      <c r="D19" s="329"/>
+      <c r="E19" s="329"/>
+      <c r="F19" s="329"/>
+      <c r="G19" s="330"/>
       <c r="H19" s="55"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1">
       <c r="A20" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="364"/>
-      <c r="C20" s="369"/>
-      <c r="D20" s="370"/>
-      <c r="E20" s="370"/>
-      <c r="F20" s="370"/>
-      <c r="G20" s="371"/>
+      <c r="B20" s="326"/>
+      <c r="C20" s="331"/>
+      <c r="D20" s="332"/>
+      <c r="E20" s="332"/>
+      <c r="F20" s="332"/>
+      <c r="G20" s="333"/>
       <c r="H20" s="55"/>
     </row>
     <row r="21" spans="1:13" ht="24" customHeight="1">
       <c r="A21" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="365"/>
-      <c r="C21" s="372"/>
-      <c r="D21" s="373"/>
-      <c r="E21" s="373"/>
-      <c r="F21" s="373"/>
-      <c r="G21" s="374"/>
+      <c r="B21" s="327"/>
+      <c r="C21" s="334"/>
+      <c r="D21" s="335"/>
+      <c r="E21" s="335"/>
+      <c r="F21" s="335"/>
+      <c r="G21" s="336"/>
       <c r="H21" s="57" t="s">
         <v>52</v>
       </c>
@@ -14507,17 +14507,17 @@
       <c r="B25" s="57">
         <v>1</v>
       </c>
-      <c r="C25" s="384">
+      <c r="C25" s="376">
         <v>2</v>
       </c>
-      <c r="D25" s="385"/>
+      <c r="D25" s="377"/>
       <c r="E25" s="57">
         <v>3</v>
       </c>
-      <c r="F25" s="384">
+      <c r="F25" s="376">
         <v>4</v>
       </c>
-      <c r="G25" s="385"/>
+      <c r="G25" s="377"/>
       <c r="H25" s="57">
         <v>8</v>
       </c>
@@ -14573,15 +14573,15 @@
       <c r="B29" s="58">
         <v>2</v>
       </c>
-      <c r="C29" s="375" t="s">
+      <c r="C29" s="378" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="376"/>
-      <c r="E29" s="324" t="s">
+      <c r="D29" s="379"/>
+      <c r="E29" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F29" s="325"/>
-      <c r="G29" s="326"/>
+      <c r="F29" s="338"/>
+      <c r="G29" s="339"/>
       <c r="H29" s="64"/>
       <c r="I29" s="49"/>
       <c r="M29" s="65"/>
@@ -14593,15 +14593,15 @@
       <c r="B30" s="58">
         <v>3</v>
       </c>
-      <c r="C30" s="377"/>
-      <c r="D30" s="378"/>
+      <c r="C30" s="380"/>
+      <c r="D30" s="381"/>
       <c r="E30" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="337" t="s">
+      <c r="F30" s="356" t="s">
         <v>56</v>
       </c>
-      <c r="G30" s="339"/>
+      <c r="G30" s="358"/>
       <c r="H30" s="72" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14616,15 +14616,15 @@
       <c r="B31" s="58">
         <v>4</v>
       </c>
-      <c r="C31" s="377"/>
-      <c r="D31" s="378"/>
+      <c r="C31" s="380"/>
+      <c r="D31" s="381"/>
       <c r="E31" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="337" t="s">
+      <c r="F31" s="356" t="s">
         <v>57</v>
       </c>
-      <c r="G31" s="339"/>
+      <c r="G31" s="358"/>
       <c r="H31" s="64"/>
       <c r="I31" s="49"/>
       <c r="M31" s="53"/>
@@ -14636,15 +14636,15 @@
       <c r="B32" s="58">
         <v>5</v>
       </c>
-      <c r="C32" s="377"/>
-      <c r="D32" s="378"/>
+      <c r="C32" s="380"/>
+      <c r="D32" s="381"/>
       <c r="E32" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="337" t="s">
+      <c r="F32" s="356" t="s">
         <v>58</v>
       </c>
-      <c r="G32" s="339"/>
+      <c r="G32" s="358"/>
       <c r="H32" s="64"/>
       <c r="I32" s="49"/>
     </row>
@@ -14664,10 +14664,10 @@
       <c r="E33" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F33" s="320" t="s">
+      <c r="F33" s="346" t="s">
         <v>170</v>
       </c>
-      <c r="G33" s="322"/>
+      <c r="G33" s="348"/>
       <c r="H33" s="64"/>
       <c r="I33" s="49"/>
       <c r="J33" s="49"/>
@@ -14688,10 +14688,10 @@
       <c r="E34" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G34" s="322"/>
+      <c r="F34" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="348"/>
       <c r="H34" s="64"/>
       <c r="I34" s="49"/>
       <c r="J34" s="49"/>
@@ -14704,15 +14704,15 @@
       <c r="B35" s="58">
         <v>8</v>
       </c>
-      <c r="C35" s="375" t="s">
+      <c r="C35" s="378" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="376"/>
-      <c r="E35" s="324" t="s">
+      <c r="D35" s="379"/>
+      <c r="E35" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F35" s="325"/>
-      <c r="G35" s="326"/>
+      <c r="F35" s="338"/>
+      <c r="G35" s="339"/>
       <c r="H35" s="64"/>
       <c r="I35" s="49"/>
     </row>
@@ -14723,15 +14723,15 @@
       <c r="B36" s="58">
         <v>9</v>
       </c>
-      <c r="C36" s="377"/>
-      <c r="D36" s="378"/>
-      <c r="E36" s="331" t="s">
+      <c r="C36" s="380"/>
+      <c r="D36" s="381"/>
+      <c r="E36" s="373" t="s">
         <v>55</v>
       </c>
-      <c r="F36" s="337" t="s">
+      <c r="F36" s="356" t="s">
         <v>172</v>
       </c>
-      <c r="G36" s="339"/>
+      <c r="G36" s="358"/>
       <c r="H36" s="72" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -14746,13 +14746,13 @@
       <c r="B37" s="58">
         <v>10</v>
       </c>
-      <c r="C37" s="381"/>
-      <c r="D37" s="382"/>
-      <c r="E37" s="332"/>
-      <c r="F37" s="337" t="s">
+      <c r="C37" s="382"/>
+      <c r="D37" s="383"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="356" t="s">
         <v>173</v>
       </c>
-      <c r="G37" s="339"/>
+      <c r="G37" s="358"/>
       <c r="H37" s="64"/>
       <c r="I37" s="49"/>
     </row>
@@ -14763,15 +14763,15 @@
       <c r="B38" s="58">
         <v>11</v>
       </c>
-      <c r="C38" s="375" t="s">
+      <c r="C38" s="378" t="s">
         <v>174</v>
       </c>
-      <c r="D38" s="376"/>
-      <c r="E38" s="324" t="s">
+      <c r="D38" s="379"/>
+      <c r="E38" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F38" s="325"/>
-      <c r="G38" s="326"/>
+      <c r="F38" s="338"/>
+      <c r="G38" s="339"/>
       <c r="H38" s="64"/>
       <c r="I38" s="49"/>
     </row>
@@ -14782,15 +14782,15 @@
       <c r="B39" s="58">
         <v>12</v>
       </c>
-      <c r="C39" s="377"/>
-      <c r="D39" s="378"/>
+      <c r="C39" s="380"/>
+      <c r="D39" s="381"/>
       <c r="E39" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="G39" s="380"/>
+      <c r="F39" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="G39" s="385"/>
       <c r="H39" s="64"/>
       <c r="I39" s="49"/>
     </row>
@@ -14810,10 +14810,10 @@
       <c r="E40" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G40" s="322"/>
+      <c r="F40" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="G40" s="348"/>
       <c r="H40" s="64"/>
       <c r="I40" s="49"/>
       <c r="J40" s="49"/>
@@ -14825,15 +14825,15 @@
       <c r="B41" s="58">
         <v>14</v>
       </c>
-      <c r="C41" s="375" t="s">
+      <c r="C41" s="378" t="s">
         <v>175</v>
       </c>
-      <c r="D41" s="376"/>
-      <c r="E41" s="324" t="s">
+      <c r="D41" s="379"/>
+      <c r="E41" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F41" s="325"/>
-      <c r="G41" s="326"/>
+      <c r="F41" s="338"/>
+      <c r="G41" s="339"/>
       <c r="H41" s="64"/>
       <c r="I41" s="49"/>
     </row>
@@ -14844,15 +14844,15 @@
       <c r="B42" s="58">
         <v>15</v>
       </c>
-      <c r="C42" s="377"/>
-      <c r="D42" s="378"/>
+      <c r="C42" s="380"/>
+      <c r="D42" s="381"/>
       <c r="E42" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="337" t="s">
+      <c r="F42" s="356" t="s">
         <v>91</v>
       </c>
-      <c r="G42" s="339"/>
+      <c r="G42" s="358"/>
       <c r="H42" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14875,10 +14875,10 @@
       <c r="E43" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F43" s="320" t="s">
+      <c r="F43" s="346" t="s">
         <v>176</v>
       </c>
-      <c r="G43" s="322"/>
+      <c r="G43" s="348"/>
       <c r="H43" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14902,10 +14902,10 @@
       <c r="E44" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F44" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G44" s="322"/>
+      <c r="F44" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" s="348"/>
       <c r="H44" s="64"/>
       <c r="I44" s="49"/>
       <c r="J44" s="49"/>
@@ -14917,15 +14917,15 @@
       <c r="B45" s="58">
         <v>18</v>
       </c>
-      <c r="C45" s="375" t="s">
+      <c r="C45" s="378" t="s">
         <v>177</v>
       </c>
-      <c r="D45" s="376"/>
-      <c r="E45" s="324" t="s">
+      <c r="D45" s="379"/>
+      <c r="E45" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="325"/>
-      <c r="G45" s="326"/>
+      <c r="F45" s="338"/>
+      <c r="G45" s="339"/>
       <c r="H45" s="64"/>
       <c r="I45" s="49"/>
     </row>
@@ -14936,15 +14936,15 @@
       <c r="B46" s="58">
         <v>19</v>
       </c>
-      <c r="C46" s="377"/>
-      <c r="D46" s="378"/>
+      <c r="C46" s="380"/>
+      <c r="D46" s="381"/>
       <c r="E46" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="G46" s="380"/>
+      <c r="F46" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" s="385"/>
       <c r="H46" s="64"/>
       <c r="I46" s="49"/>
     </row>
@@ -14964,8 +14964,8 @@
       <c r="E47" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F47" s="320"/>
-      <c r="G47" s="322"/>
+      <c r="F47" s="346"/>
+      <c r="G47" s="348"/>
       <c r="H47" s="64"/>
       <c r="I47" s="49"/>
       <c r="J47" s="49"/>
@@ -14986,10 +14986,10 @@
       <c r="E48" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F48" s="320" t="s">
+      <c r="F48" s="346" t="s">
         <v>178</v>
       </c>
-      <c r="G48" s="322"/>
+      <c r="G48" s="348"/>
       <c r="H48" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15013,10 +15013,10 @@
       <c r="E49" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F49" s="320" t="s">
+      <c r="F49" s="346" t="s">
         <v>8</v>
       </c>
-      <c r="G49" s="322"/>
+      <c r="G49" s="348"/>
       <c r="H49" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15031,13 +15031,13 @@
       <c r="B50" s="58">
         <v>24</v>
       </c>
-      <c r="C50" s="324" t="s">
+      <c r="C50" s="337" t="s">
         <v>179</v>
       </c>
-      <c r="D50" s="325"/>
-      <c r="E50" s="325"/>
-      <c r="F50" s="325"/>
-      <c r="G50" s="326"/>
+      <c r="D50" s="338"/>
+      <c r="E50" s="338"/>
+      <c r="F50" s="338"/>
+      <c r="G50" s="339"/>
       <c r="H50" s="64"/>
       <c r="I50" s="49"/>
     </row>
@@ -15048,13 +15048,13 @@
       <c r="B51" s="58">
         <v>25</v>
       </c>
-      <c r="C51" s="324" t="s">
+      <c r="C51" s="337" t="s">
         <v>180</v>
       </c>
-      <c r="D51" s="325"/>
-      <c r="E51" s="325"/>
-      <c r="F51" s="325"/>
-      <c r="G51" s="326"/>
+      <c r="D51" s="338"/>
+      <c r="E51" s="338"/>
+      <c r="F51" s="338"/>
+      <c r="G51" s="339"/>
       <c r="H51" s="64" t="e">
         <f>нак.расх.!G29-зат.осн.про.!H75-зат.осн.про.!H99</f>
         <v>#REF!</v>
@@ -15100,15 +15100,15 @@
       <c r="B53" s="58">
         <v>2</v>
       </c>
-      <c r="C53" s="375" t="s">
+      <c r="C53" s="378" t="s">
         <v>54</v>
       </c>
-      <c r="D53" s="376"/>
-      <c r="E53" s="324" t="s">
+      <c r="D53" s="379"/>
+      <c r="E53" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F53" s="325"/>
-      <c r="G53" s="326"/>
+      <c r="F53" s="338"/>
+      <c r="G53" s="339"/>
       <c r="H53" s="64"/>
       <c r="I53" s="49"/>
       <c r="M53" s="53" t="e">
@@ -15123,15 +15123,15 @@
       <c r="B54" s="58">
         <v>3</v>
       </c>
-      <c r="C54" s="377"/>
-      <c r="D54" s="378"/>
+      <c r="C54" s="380"/>
+      <c r="D54" s="381"/>
       <c r="E54" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F54" s="337" t="s">
+      <c r="F54" s="356" t="s">
         <v>56</v>
       </c>
-      <c r="G54" s="339"/>
+      <c r="G54" s="358"/>
       <c r="H54" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15145,15 +15145,15 @@
       <c r="B55" s="58">
         <v>4</v>
       </c>
-      <c r="C55" s="377"/>
-      <c r="D55" s="378"/>
+      <c r="C55" s="380"/>
+      <c r="D55" s="381"/>
       <c r="E55" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F55" s="337" t="s">
+      <c r="F55" s="356" t="s">
         <v>57</v>
       </c>
-      <c r="G55" s="339"/>
+      <c r="G55" s="358"/>
       <c r="H55" s="64"/>
       <c r="I55" s="49"/>
     </row>
@@ -15164,15 +15164,15 @@
       <c r="B56" s="58">
         <v>5</v>
       </c>
-      <c r="C56" s="377"/>
-      <c r="D56" s="378"/>
+      <c r="C56" s="380"/>
+      <c r="D56" s="381"/>
       <c r="E56" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="337" t="s">
+      <c r="F56" s="356" t="s">
         <v>58</v>
       </c>
-      <c r="G56" s="339"/>
+      <c r="G56" s="358"/>
       <c r="H56" s="64"/>
       <c r="I56" s="49"/>
     </row>
@@ -15192,10 +15192,10 @@
       <c r="E57" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="320" t="s">
+      <c r="F57" s="346" t="s">
         <v>170</v>
       </c>
-      <c r="G57" s="322"/>
+      <c r="G57" s="348"/>
       <c r="H57" s="64"/>
       <c r="I57" s="49"/>
       <c r="J57" s="49"/>
@@ -15216,10 +15216,10 @@
       <c r="E58" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F58" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G58" s="322"/>
+      <c r="F58" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="G58" s="348"/>
       <c r="H58" s="64"/>
       <c r="I58" s="49"/>
     </row>
@@ -15230,15 +15230,15 @@
       <c r="B59" s="58">
         <v>8</v>
       </c>
-      <c r="C59" s="375" t="s">
+      <c r="C59" s="378" t="s">
         <v>171</v>
       </c>
-      <c r="D59" s="376"/>
-      <c r="E59" s="324" t="s">
+      <c r="D59" s="379"/>
+      <c r="E59" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F59" s="325"/>
-      <c r="G59" s="326"/>
+      <c r="F59" s="338"/>
+      <c r="G59" s="339"/>
       <c r="H59" s="64"/>
       <c r="I59" s="49"/>
     </row>
@@ -15249,15 +15249,15 @@
       <c r="B60" s="58">
         <v>9</v>
       </c>
-      <c r="C60" s="377"/>
-      <c r="D60" s="378"/>
-      <c r="E60" s="331" t="s">
+      <c r="C60" s="380"/>
+      <c r="D60" s="381"/>
+      <c r="E60" s="373" t="s">
         <v>55</v>
       </c>
-      <c r="F60" s="337" t="s">
+      <c r="F60" s="356" t="s">
         <v>172</v>
       </c>
-      <c r="G60" s="339"/>
+      <c r="G60" s="358"/>
       <c r="H60" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15271,13 +15271,13 @@
       <c r="B61" s="58">
         <v>10</v>
       </c>
-      <c r="C61" s="381"/>
-      <c r="D61" s="382"/>
-      <c r="E61" s="332"/>
-      <c r="F61" s="337" t="s">
+      <c r="C61" s="382"/>
+      <c r="D61" s="383"/>
+      <c r="E61" s="374"/>
+      <c r="F61" s="356" t="s">
         <v>173</v>
       </c>
-      <c r="G61" s="339"/>
+      <c r="G61" s="358"/>
       <c r="H61" s="64"/>
       <c r="I61" s="49"/>
     </row>
@@ -15288,15 +15288,15 @@
       <c r="B62" s="58">
         <v>11</v>
       </c>
-      <c r="C62" s="375" t="s">
+      <c r="C62" s="378" t="s">
         <v>174</v>
       </c>
-      <c r="D62" s="376"/>
-      <c r="E62" s="324" t="s">
+      <c r="D62" s="379"/>
+      <c r="E62" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F62" s="325"/>
-      <c r="G62" s="326"/>
+      <c r="F62" s="338"/>
+      <c r="G62" s="339"/>
       <c r="H62" s="64"/>
       <c r="I62" s="49"/>
     </row>
@@ -15307,15 +15307,15 @@
       <c r="B63" s="58">
         <v>12</v>
       </c>
-      <c r="C63" s="377"/>
-      <c r="D63" s="378"/>
+      <c r="C63" s="380"/>
+      <c r="D63" s="381"/>
       <c r="E63" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F63" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="G63" s="380"/>
+      <c r="F63" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="G63" s="385"/>
       <c r="H63" s="64"/>
       <c r="I63" s="49"/>
       <c r="J63" s="49"/>
@@ -15336,10 +15336,10 @@
       <c r="E64" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F64" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G64" s="322"/>
+      <c r="F64" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="G64" s="348"/>
       <c r="H64" s="64"/>
       <c r="I64" s="49"/>
     </row>
@@ -15350,15 +15350,15 @@
       <c r="B65" s="58">
         <v>14</v>
       </c>
-      <c r="C65" s="375" t="s">
+      <c r="C65" s="378" t="s">
         <v>175</v>
       </c>
-      <c r="D65" s="376"/>
-      <c r="E65" s="324" t="s">
+      <c r="D65" s="379"/>
+      <c r="E65" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="325"/>
-      <c r="G65" s="326"/>
+      <c r="F65" s="338"/>
+      <c r="G65" s="339"/>
       <c r="H65" s="64"/>
       <c r="I65" s="49"/>
     </row>
@@ -15369,15 +15369,15 @@
       <c r="B66" s="58">
         <v>15</v>
       </c>
-      <c r="C66" s="377"/>
-      <c r="D66" s="378"/>
+      <c r="C66" s="380"/>
+      <c r="D66" s="381"/>
       <c r="E66" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F66" s="337" t="s">
+      <c r="F66" s="356" t="s">
         <v>91</v>
       </c>
-      <c r="G66" s="339"/>
+      <c r="G66" s="358"/>
       <c r="H66" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15401,10 +15401,10 @@
       <c r="E67" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="320" t="s">
+      <c r="F67" s="346" t="s">
         <v>176</v>
       </c>
-      <c r="G67" s="322"/>
+      <c r="G67" s="348"/>
       <c r="H67" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15427,10 +15427,10 @@
       <c r="E68" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F68" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G68" s="322"/>
+      <c r="F68" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="G68" s="348"/>
       <c r="H68" s="64"/>
       <c r="I68" s="49"/>
     </row>
@@ -15441,15 +15441,15 @@
       <c r="B69" s="58">
         <v>18</v>
       </c>
-      <c r="C69" s="375" t="s">
+      <c r="C69" s="378" t="s">
         <v>177</v>
       </c>
-      <c r="D69" s="376"/>
-      <c r="E69" s="324" t="s">
+      <c r="D69" s="379"/>
+      <c r="E69" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="325"/>
-      <c r="G69" s="326"/>
+      <c r="F69" s="338"/>
+      <c r="G69" s="339"/>
       <c r="H69" s="64"/>
       <c r="I69" s="49"/>
       <c r="J69" s="49"/>
@@ -15461,15 +15461,15 @@
       <c r="B70" s="58">
         <v>19</v>
       </c>
-      <c r="C70" s="377"/>
-      <c r="D70" s="378"/>
+      <c r="C70" s="380"/>
+      <c r="D70" s="381"/>
       <c r="E70" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F70" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="G70" s="380"/>
+      <c r="F70" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="G70" s="385"/>
       <c r="H70" s="64"/>
       <c r="I70" s="49"/>
     </row>
@@ -15489,8 +15489,8 @@
       <c r="E71" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F71" s="320"/>
-      <c r="G71" s="322"/>
+      <c r="F71" s="346"/>
+      <c r="G71" s="348"/>
       <c r="H71" s="64"/>
       <c r="I71" s="49"/>
     </row>
@@ -15507,10 +15507,10 @@
       <c r="E72" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F72" s="320" t="s">
+      <c r="F72" s="346" t="s">
         <v>178</v>
       </c>
-      <c r="G72" s="322"/>
+      <c r="G72" s="348"/>
       <c r="H72" s="64"/>
       <c r="I72" s="49"/>
       <c r="J72" s="49"/>
@@ -15533,10 +15533,10 @@
       <c r="E73" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F73" s="320" t="s">
+      <c r="F73" s="346" t="s">
         <v>8</v>
       </c>
-      <c r="G73" s="322"/>
+      <c r="G73" s="348"/>
       <c r="H73" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15550,13 +15550,13 @@
       <c r="B74" s="58">
         <v>24</v>
       </c>
-      <c r="C74" s="324" t="s">
+      <c r="C74" s="337" t="s">
         <v>179</v>
       </c>
-      <c r="D74" s="325"/>
-      <c r="E74" s="325"/>
-      <c r="F74" s="325"/>
-      <c r="G74" s="326"/>
+      <c r="D74" s="338"/>
+      <c r="E74" s="338"/>
+      <c r="F74" s="338"/>
+      <c r="G74" s="339"/>
       <c r="H74" s="64"/>
       <c r="I74" s="49"/>
       <c r="J74" s="49"/>
@@ -15567,13 +15567,13 @@
       <c r="B75" s="58">
         <v>25</v>
       </c>
-      <c r="C75" s="324" t="s">
+      <c r="C75" s="337" t="s">
         <v>180</v>
       </c>
-      <c r="D75" s="325"/>
-      <c r="E75" s="325"/>
-      <c r="F75" s="325"/>
-      <c r="G75" s="326"/>
+      <c r="D75" s="338"/>
+      <c r="E75" s="338"/>
+      <c r="F75" s="338"/>
+      <c r="G75" s="339"/>
       <c r="H75" s="64" t="e">
         <f>нак.расх.!G29*4%</f>
         <v>#REF!</v>
@@ -15619,15 +15619,15 @@
       <c r="B77" s="58">
         <v>2</v>
       </c>
-      <c r="C77" s="375" t="s">
+      <c r="C77" s="378" t="s">
         <v>54</v>
       </c>
-      <c r="D77" s="376"/>
-      <c r="E77" s="324" t="s">
+      <c r="D77" s="379"/>
+      <c r="E77" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F77" s="325"/>
-      <c r="G77" s="326"/>
+      <c r="F77" s="338"/>
+      <c r="G77" s="339"/>
       <c r="H77" s="64"/>
       <c r="M77" s="53" t="e">
         <f>H76-M76</f>
@@ -15638,15 +15638,15 @@
       <c r="B78" s="58">
         <v>3</v>
       </c>
-      <c r="C78" s="377"/>
-      <c r="D78" s="378"/>
+      <c r="C78" s="380"/>
+      <c r="D78" s="381"/>
       <c r="E78" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F78" s="337" t="s">
+      <c r="F78" s="356" t="s">
         <v>56</v>
       </c>
-      <c r="G78" s="339"/>
+      <c r="G78" s="358"/>
       <c r="H78" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15656,30 +15656,30 @@
       <c r="B79" s="58">
         <v>4</v>
       </c>
-      <c r="C79" s="377"/>
-      <c r="D79" s="378"/>
+      <c r="C79" s="380"/>
+      <c r="D79" s="381"/>
       <c r="E79" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F79" s="337" t="s">
+      <c r="F79" s="356" t="s">
         <v>57</v>
       </c>
-      <c r="G79" s="339"/>
+      <c r="G79" s="358"/>
       <c r="H79" s="64"/>
     </row>
     <row r="80" spans="1:13" ht="15.75" customHeight="1">
       <c r="B80" s="58">
         <v>5</v>
       </c>
-      <c r="C80" s="377"/>
-      <c r="D80" s="378"/>
+      <c r="C80" s="380"/>
+      <c r="D80" s="381"/>
       <c r="E80" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F80" s="337" t="s">
+      <c r="F80" s="356" t="s">
         <v>58</v>
       </c>
-      <c r="G80" s="339"/>
+      <c r="G80" s="358"/>
       <c r="H80" s="64"/>
     </row>
     <row r="81" spans="2:8" ht="15.75" customHeight="1">
@@ -15695,10 +15695,10 @@
       <c r="E81" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="320" t="s">
+      <c r="F81" s="346" t="s">
         <v>170</v>
       </c>
-      <c r="G81" s="322"/>
+      <c r="G81" s="348"/>
       <c r="H81" s="64"/>
     </row>
     <row r="82" spans="2:8" ht="15.75" customHeight="1">
@@ -15714,40 +15714,40 @@
       <c r="E82" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G82" s="322"/>
+      <c r="F82" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="G82" s="348"/>
       <c r="H82" s="64"/>
     </row>
     <row r="83" spans="2:8" ht="15.75" customHeight="1">
       <c r="B83" s="58">
         <v>8</v>
       </c>
-      <c r="C83" s="375" t="s">
+      <c r="C83" s="378" t="s">
         <v>171</v>
       </c>
-      <c r="D83" s="376"/>
-      <c r="E83" s="324" t="s">
+      <c r="D83" s="379"/>
+      <c r="E83" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F83" s="325"/>
-      <c r="G83" s="326"/>
+      <c r="F83" s="338"/>
+      <c r="G83" s="339"/>
       <c r="H83" s="64"/>
     </row>
     <row r="84" spans="2:8" ht="15.75" customHeight="1">
       <c r="B84" s="58">
         <v>9</v>
       </c>
-      <c r="C84" s="377"/>
-      <c r="D84" s="378"/>
-      <c r="E84" s="331" t="s">
+      <c r="C84" s="380"/>
+      <c r="D84" s="381"/>
+      <c r="E84" s="373" t="s">
         <v>55</v>
       </c>
-      <c r="F84" s="337" t="s">
+      <c r="F84" s="356" t="s">
         <v>172</v>
       </c>
-      <c r="G84" s="339"/>
+      <c r="G84" s="358"/>
       <c r="H84" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15757,43 +15757,43 @@
       <c r="B85" s="58">
         <v>10</v>
       </c>
-      <c r="C85" s="381"/>
-      <c r="D85" s="382"/>
-      <c r="E85" s="332"/>
-      <c r="F85" s="337" t="s">
+      <c r="C85" s="382"/>
+      <c r="D85" s="383"/>
+      <c r="E85" s="374"/>
+      <c r="F85" s="356" t="s">
         <v>173</v>
       </c>
-      <c r="G85" s="339"/>
+      <c r="G85" s="358"/>
       <c r="H85" s="64"/>
     </row>
     <row r="86" spans="2:8" ht="15.75" customHeight="1">
       <c r="B86" s="58">
         <v>11</v>
       </c>
-      <c r="C86" s="375" t="s">
+      <c r="C86" s="378" t="s">
         <v>174</v>
       </c>
-      <c r="D86" s="376"/>
-      <c r="E86" s="324" t="s">
+      <c r="D86" s="379"/>
+      <c r="E86" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F86" s="325"/>
-      <c r="G86" s="326"/>
+      <c r="F86" s="338"/>
+      <c r="G86" s="339"/>
       <c r="H86" s="64"/>
     </row>
     <row r="87" spans="2:8" ht="15.75" customHeight="1">
       <c r="B87" s="58">
         <v>12</v>
       </c>
-      <c r="C87" s="377"/>
-      <c r="D87" s="378"/>
+      <c r="C87" s="380"/>
+      <c r="D87" s="381"/>
       <c r="E87" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F87" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="G87" s="380"/>
+      <c r="F87" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="G87" s="385"/>
       <c r="H87" s="64"/>
     </row>
     <row r="88" spans="2:8" ht="15.75" customHeight="1">
@@ -15809,40 +15809,40 @@
       <c r="E88" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G88" s="322"/>
+      <c r="F88" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="G88" s="348"/>
       <c r="H88" s="64"/>
     </row>
     <row r="89" spans="2:8" ht="15.75" customHeight="1">
       <c r="B89" s="58">
         <v>14</v>
       </c>
-      <c r="C89" s="375" t="s">
+      <c r="C89" s="378" t="s">
         <v>175</v>
       </c>
-      <c r="D89" s="376"/>
-      <c r="E89" s="324" t="s">
+      <c r="D89" s="379"/>
+      <c r="E89" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F89" s="325"/>
-      <c r="G89" s="326"/>
+      <c r="F89" s="338"/>
+      <c r="G89" s="339"/>
       <c r="H89" s="64"/>
     </row>
     <row r="90" spans="2:8" ht="15.75" customHeight="1">
       <c r="B90" s="58">
         <v>15</v>
       </c>
-      <c r="C90" s="377"/>
-      <c r="D90" s="378"/>
+      <c r="C90" s="380"/>
+      <c r="D90" s="381"/>
       <c r="E90" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F90" s="337" t="s">
+      <c r="F90" s="356" t="s">
         <v>91</v>
       </c>
-      <c r="G90" s="339"/>
+      <c r="G90" s="358"/>
       <c r="H90" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15861,10 +15861,10 @@
       <c r="E91" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F91" s="320" t="s">
+      <c r="F91" s="346" t="s">
         <v>176</v>
       </c>
-      <c r="G91" s="322"/>
+      <c r="G91" s="348"/>
       <c r="H91" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15883,40 +15883,40 @@
       <c r="E92" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F92" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G92" s="322"/>
+      <c r="F92" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="G92" s="348"/>
       <c r="H92" s="64"/>
     </row>
     <row r="93" spans="2:8" ht="15.75" customHeight="1">
       <c r="B93" s="58">
         <v>18</v>
       </c>
-      <c r="C93" s="375" t="s">
+      <c r="C93" s="378" t="s">
         <v>177</v>
       </c>
-      <c r="D93" s="376"/>
-      <c r="E93" s="324" t="s">
+      <c r="D93" s="379"/>
+      <c r="E93" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="F93" s="325"/>
-      <c r="G93" s="326"/>
+      <c r="F93" s="338"/>
+      <c r="G93" s="339"/>
       <c r="H93" s="64"/>
     </row>
     <row r="94" spans="2:8" ht="15.75" customHeight="1">
       <c r="B94" s="58">
         <v>19</v>
       </c>
-      <c r="C94" s="377"/>
-      <c r="D94" s="378"/>
+      <c r="C94" s="380"/>
+      <c r="D94" s="381"/>
       <c r="E94" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F94" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="G94" s="380"/>
+      <c r="F94" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="G94" s="385"/>
       <c r="H94" s="64"/>
     </row>
     <row r="95" spans="2:8" ht="15.75" customHeight="1">
@@ -15932,8 +15932,8 @@
       <c r="E95" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F95" s="320"/>
-      <c r="G95" s="322"/>
+      <c r="F95" s="346"/>
+      <c r="G95" s="348"/>
       <c r="H95" s="64"/>
     </row>
     <row r="96" spans="2:8" ht="32.25" customHeight="1">
@@ -15949,10 +15949,10 @@
       <c r="E96" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F96" s="320" t="s">
+      <c r="F96" s="346" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="322"/>
+      <c r="G96" s="348"/>
       <c r="H96" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15971,34 +15971,34 @@
       <c r="E97" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F97" s="320"/>
-      <c r="G97" s="322"/>
+      <c r="F97" s="346"/>
+      <c r="G97" s="348"/>
       <c r="H97" s="64"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1">
       <c r="B98" s="58">
         <v>24</v>
       </c>
-      <c r="C98" s="324" t="s">
+      <c r="C98" s="337" t="s">
         <v>179</v>
       </c>
-      <c r="D98" s="325"/>
-      <c r="E98" s="325"/>
-      <c r="F98" s="325"/>
-      <c r="G98" s="326"/>
+      <c r="D98" s="338"/>
+      <c r="E98" s="338"/>
+      <c r="F98" s="338"/>
+      <c r="G98" s="339"/>
       <c r="H98" s="64"/>
     </row>
     <row r="99" spans="2:8" ht="15.75" customHeight="1">
       <c r="B99" s="58">
         <v>25</v>
       </c>
-      <c r="C99" s="324" t="s">
+      <c r="C99" s="337" t="s">
         <v>180</v>
       </c>
-      <c r="D99" s="325"/>
-      <c r="E99" s="325"/>
-      <c r="F99" s="325"/>
-      <c r="G99" s="326"/>
+      <c r="D99" s="338"/>
+      <c r="E99" s="338"/>
+      <c r="F99" s="338"/>
+      <c r="G99" s="339"/>
       <c r="H99" s="64" t="e">
         <f>нак.расх.!G29*16%</f>
         <v>#REF!</v>
@@ -16006,6 +16006,87 @@
     </row>
   </sheetData>
   <mergeCells count="94">
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="C93:D94"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="C86:D87"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="C89:D90"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="C83:D85"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C77:D80"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="C62:D63"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="C65:D66"/>
+    <mergeCell ref="E65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="C69:D70"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="C59:D61"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C53:D56"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="C45:D46"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="C35:D37"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B3:H3"/>
@@ -16019,87 +16100,6 @@
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="C35:D37"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="C41:D42"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="C45:D46"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C53:D56"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="C59:D61"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="C62:D63"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="C65:D66"/>
-    <mergeCell ref="E65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="C69:D70"/>
-    <mergeCell ref="E69:G69"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C77:D80"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="C83:D85"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="C86:D87"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="C89:D90"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="C93:D94"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="F95:G95"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="76" orientation="portrait" r:id="rId1"/>
@@ -16128,14 +16128,14 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="358" t="s">
+      <c r="B1" s="320" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="358"/>
-      <c r="D1" s="358"/>
-      <c r="E1" s="358"/>
-      <c r="F1" s="358"/>
-      <c r="G1" s="358"/>
+      <c r="C1" s="320"/>
+      <c r="D1" s="320"/>
+      <c r="E1" s="320"/>
+      <c r="F1" s="320"/>
+      <c r="G1" s="320"/>
       <c r="K1" s="51"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1">
@@ -16166,69 +16166,69 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="358" t="s">
+      <c r="B3" s="320" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="358"/>
-      <c r="D3" s="358"/>
-      <c r="E3" s="358"/>
-      <c r="F3" s="358"/>
-      <c r="G3" s="358"/>
+      <c r="C3" s="320"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="320"/>
+      <c r="G3" s="320"/>
       <c r="K3" s="51"/>
     </row>
     <row r="4" spans="1:11" ht="14.25" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="360" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="360"/>
-      <c r="D4" s="360"/>
-      <c r="E4" s="360"/>
-      <c r="F4" s="360"/>
-      <c r="G4" s="360"/>
+      <c r="B4" s="322" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="322"/>
+      <c r="D4" s="322"/>
+      <c r="E4" s="322"/>
+      <c r="F4" s="322"/>
+      <c r="G4" s="322"/>
       <c r="K4" s="51"/>
     </row>
     <row r="5" spans="1:11" ht="24.75" customHeight="1">
       <c r="A5" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="361" t="s">
+      <c r="B5" s="323" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="361"/>
-      <c r="D5" s="361"/>
-      <c r="E5" s="361"/>
-      <c r="F5" s="361"/>
-      <c r="G5" s="361"/>
+      <c r="C5" s="323"/>
+      <c r="D5" s="323"/>
+      <c r="E5" s="323"/>
+      <c r="F5" s="323"/>
+      <c r="G5" s="323"/>
       <c r="K5" s="51"/>
     </row>
     <row r="6" spans="1:11" ht="12" customHeight="1">
       <c r="A6" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="361" t="s">
+      <c r="B6" s="323" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="361"/>
-      <c r="D6" s="361"/>
-      <c r="E6" s="361"/>
-      <c r="F6" s="361"/>
-      <c r="G6" s="361"/>
+      <c r="C6" s="323"/>
+      <c r="D6" s="323"/>
+      <c r="E6" s="323"/>
+      <c r="F6" s="323"/>
+      <c r="G6" s="323"/>
       <c r="K6" s="51"/>
     </row>
     <row r="7" spans="1:11" ht="12" customHeight="1">
       <c r="A7" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="362" t="s">
+      <c r="B7" s="324" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="362"/>
-      <c r="D7" s="362"/>
-      <c r="E7" s="362"/>
-      <c r="F7" s="362"/>
+      <c r="C7" s="324"/>
+      <c r="D7" s="324"/>
+      <c r="E7" s="324"/>
+      <c r="F7" s="324"/>
       <c r="G7" s="71" t="s">
         <v>50</v>
       </c>
@@ -16252,37 +16252,37 @@
       <c r="A22" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="363" t="s">
+      <c r="B22" s="325" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="366" t="s">
+      <c r="C22" s="328" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="367"/>
-      <c r="E22" s="367"/>
-      <c r="F22" s="368"/>
+      <c r="D22" s="329"/>
+      <c r="E22" s="329"/>
+      <c r="F22" s="330"/>
       <c r="G22" s="55"/>
     </row>
     <row r="23" spans="1:12" ht="12" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="364"/>
-      <c r="C23" s="369"/>
-      <c r="D23" s="370"/>
-      <c r="E23" s="370"/>
-      <c r="F23" s="371"/>
+      <c r="B23" s="326"/>
+      <c r="C23" s="331"/>
+      <c r="D23" s="332"/>
+      <c r="E23" s="332"/>
+      <c r="F23" s="333"/>
       <c r="G23" s="55"/>
     </row>
     <row r="24" spans="1:12" ht="24" customHeight="1">
       <c r="A24" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="365"/>
-      <c r="C24" s="372"/>
-      <c r="D24" s="373"/>
-      <c r="E24" s="373"/>
-      <c r="F24" s="374"/>
+      <c r="B24" s="327"/>
+      <c r="C24" s="334"/>
+      <c r="D24" s="335"/>
+      <c r="E24" s="335"/>
+      <c r="F24" s="336"/>
       <c r="G24" s="57" t="s">
         <v>52</v>
       </c>
@@ -16303,10 +16303,10 @@
       <c r="D28" s="57">
         <v>3</v>
       </c>
-      <c r="E28" s="384">
+      <c r="E28" s="376">
         <v>4</v>
       </c>
-      <c r="F28" s="385"/>
+      <c r="F28" s="377"/>
       <c r="G28" s="57">
         <v>8</v>
       </c>
@@ -16318,12 +16318,12 @@
       <c r="B29" s="58">
         <v>1</v>
       </c>
-      <c r="C29" s="324" t="s">
+      <c r="C29" s="337" t="s">
         <v>184</v>
       </c>
-      <c r="D29" s="325"/>
-      <c r="E29" s="325"/>
-      <c r="F29" s="325"/>
+      <c r="D29" s="338"/>
+      <c r="E29" s="338"/>
+      <c r="F29" s="338"/>
       <c r="G29" s="72" t="e">
         <f>SUM(G30:G77)</f>
         <v>#REF!</v>
@@ -16343,11 +16343,11 @@
       <c r="C30" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="324" t="s">
+      <c r="D30" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="325"/>
-      <c r="F30" s="325"/>
+      <c r="E30" s="338"/>
+      <c r="F30" s="338"/>
       <c r="G30" s="74"/>
       <c r="L30" s="53" t="e">
         <f>G29-L29</f>
@@ -16367,10 +16367,10 @@
       <c r="D31" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="337" t="s">
+      <c r="E31" s="356" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="338"/>
+      <c r="F31" s="357"/>
       <c r="G31" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16390,10 +16390,10 @@
       <c r="D32" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="337" t="s">
+      <c r="E32" s="356" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="338"/>
+      <c r="F32" s="357"/>
       <c r="G32" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16413,10 +16413,10 @@
       <c r="D33" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E33" s="337" t="s">
+      <c r="E33" s="356" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="338"/>
+      <c r="F33" s="357"/>
       <c r="G33" s="74"/>
     </row>
     <row r="34" spans="1:13" ht="12" customHeight="1">
@@ -16473,10 +16473,10 @@
       <c r="D36" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E36" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="321"/>
+      <c r="E36" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="347"/>
       <c r="G36" s="74"/>
       <c r="H36" s="49"/>
     </row>
@@ -16490,11 +16490,11 @@
       <c r="C37" s="73" t="s">
         <v>171</v>
       </c>
-      <c r="D37" s="324" t="s">
+      <c r="D37" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E37" s="325"/>
-      <c r="F37" s="325"/>
+      <c r="E37" s="338"/>
+      <c r="F37" s="338"/>
       <c r="G37" s="74"/>
     </row>
     <row r="38" spans="1:13" ht="12" customHeight="1">
@@ -16510,10 +16510,10 @@
       <c r="D38" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E38" s="337" t="s">
+      <c r="E38" s="356" t="s">
         <v>172</v>
       </c>
-      <c r="F38" s="338"/>
+      <c r="F38" s="357"/>
       <c r="G38" s="74" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -16533,10 +16533,10 @@
       <c r="D39" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="337" t="s">
+      <c r="E39" s="356" t="s">
         <v>173</v>
       </c>
-      <c r="F39" s="338"/>
+      <c r="F39" s="357"/>
       <c r="G39" s="74"/>
     </row>
     <row r="40" spans="1:13" ht="12" customHeight="1">
@@ -16546,14 +16546,14 @@
       <c r="B40" s="58">
         <v>26</v>
       </c>
-      <c r="C40" s="333" t="s">
+      <c r="C40" s="340" t="s">
         <v>174</v>
       </c>
-      <c r="D40" s="324" t="s">
+      <c r="D40" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E40" s="325"/>
-      <c r="F40" s="325"/>
+      <c r="E40" s="338"/>
+      <c r="F40" s="338"/>
       <c r="G40" s="74"/>
     </row>
     <row r="41" spans="1:13" ht="12" customHeight="1">
@@ -16563,14 +16563,14 @@
       <c r="B41" s="58">
         <v>27</v>
       </c>
-      <c r="C41" s="334"/>
+      <c r="C41" s="341"/>
       <c r="D41" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="F41" s="387"/>
+      <c r="E41" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="386"/>
       <c r="G41" s="74"/>
     </row>
     <row r="42" spans="1:13" ht="12" customHeight="1">
@@ -16586,10 +16586,10 @@
       <c r="D42" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E42" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="321"/>
+      <c r="E42" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" s="347"/>
       <c r="G42" s="74"/>
       <c r="H42" s="49"/>
     </row>
@@ -16600,14 +16600,14 @@
       <c r="B43" s="58">
         <v>29</v>
       </c>
-      <c r="C43" s="333" t="s">
+      <c r="C43" s="340" t="s">
         <v>186</v>
       </c>
-      <c r="D43" s="324" t="s">
+      <c r="D43" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="325"/>
-      <c r="F43" s="325"/>
+      <c r="E43" s="338"/>
+      <c r="F43" s="338"/>
       <c r="G43" s="74"/>
     </row>
     <row r="44" spans="1:13" ht="12" customHeight="1">
@@ -16617,14 +16617,14 @@
       <c r="B44" s="58">
         <v>30</v>
       </c>
-      <c r="C44" s="334"/>
+      <c r="C44" s="341"/>
       <c r="D44" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E44" s="320" t="s">
+      <c r="E44" s="346" t="s">
         <v>128</v>
       </c>
-      <c r="F44" s="321"/>
+      <c r="F44" s="347"/>
       <c r="G44" s="74"/>
     </row>
     <row r="45" spans="1:13" ht="18.75" customHeight="1">
@@ -16634,14 +16634,14 @@
       <c r="B45" s="58">
         <v>31</v>
       </c>
-      <c r="C45" s="350"/>
+      <c r="C45" s="342"/>
       <c r="D45" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E45" s="390" t="s">
+      <c r="E45" s="387" t="s">
         <v>129</v>
       </c>
-      <c r="F45" s="391"/>
+      <c r="F45" s="388"/>
       <c r="G45" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16656,12 +16656,12 @@
       <c r="B46" s="58">
         <v>32</v>
       </c>
-      <c r="C46" s="324" t="s">
+      <c r="C46" s="337" t="s">
         <v>20</v>
       </c>
-      <c r="D46" s="325"/>
-      <c r="E46" s="325"/>
-      <c r="F46" s="325"/>
+      <c r="D46" s="338"/>
+      <c r="E46" s="338"/>
+      <c r="F46" s="338"/>
       <c r="G46" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16678,11 +16678,11 @@
       <c r="C47" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="D47" s="324" t="s">
+      <c r="D47" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E47" s="325"/>
-      <c r="F47" s="325"/>
+      <c r="E47" s="338"/>
+      <c r="F47" s="338"/>
       <c r="G47" s="74"/>
       <c r="L47" s="53"/>
     </row>
@@ -16699,10 +16699,10 @@
       <c r="D48" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E48" s="337" t="s">
+      <c r="E48" s="356" t="s">
         <v>63</v>
       </c>
-      <c r="F48" s="338"/>
+      <c r="F48" s="357"/>
       <c r="G48" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16721,10 +16721,10 @@
       <c r="D49" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E49" s="337" t="s">
+      <c r="E49" s="356" t="s">
         <v>64</v>
       </c>
-      <c r="F49" s="338"/>
+      <c r="F49" s="357"/>
       <c r="G49" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16737,14 +16737,14 @@
       <c r="B50" s="58">
         <v>36</v>
       </c>
-      <c r="C50" s="333" t="s">
+      <c r="C50" s="340" t="s">
         <v>187</v>
       </c>
-      <c r="D50" s="324" t="s">
+      <c r="D50" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E50" s="325"/>
-      <c r="F50" s="325"/>
+      <c r="E50" s="338"/>
+      <c r="F50" s="338"/>
       <c r="G50" s="74"/>
     </row>
     <row r="51" spans="1:8" ht="12" customHeight="1">
@@ -16754,14 +16754,14 @@
       <c r="B51" s="58">
         <v>37</v>
       </c>
-      <c r="C51" s="334"/>
+      <c r="C51" s="341"/>
       <c r="D51" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E51" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="387"/>
+      <c r="E51" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="386"/>
       <c r="G51" s="74"/>
     </row>
     <row r="52" spans="1:8" ht="24.75" customHeight="1">
@@ -16777,10 +16777,10 @@
       <c r="D52" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E52" s="320" t="s">
+      <c r="E52" s="346" t="s">
         <v>188</v>
       </c>
-      <c r="F52" s="321"/>
+      <c r="F52" s="347"/>
       <c r="G52" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16794,12 +16794,12 @@
       <c r="B53" s="58">
         <v>43</v>
       </c>
-      <c r="C53" s="324" t="s">
+      <c r="C53" s="337" t="s">
         <v>16</v>
       </c>
-      <c r="D53" s="325"/>
-      <c r="E53" s="325"/>
-      <c r="F53" s="325"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
       <c r="G53" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16812,12 +16812,12 @@
       <c r="B54" s="58">
         <v>44</v>
       </c>
-      <c r="C54" s="324" t="s">
+      <c r="C54" s="337" t="s">
         <v>14</v>
       </c>
-      <c r="D54" s="325"/>
-      <c r="E54" s="325"/>
-      <c r="F54" s="325"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
       <c r="G54" s="74"/>
     </row>
     <row r="55" spans="1:8" ht="12" customHeight="1">
@@ -16830,11 +16830,11 @@
       <c r="C55" s="73" t="s">
         <v>137</v>
       </c>
-      <c r="D55" s="324" t="s">
+      <c r="D55" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="325"/>
-      <c r="F55" s="325"/>
+      <c r="E55" s="338"/>
+      <c r="F55" s="338"/>
       <c r="G55" s="74"/>
     </row>
     <row r="56" spans="1:8" ht="12" customHeight="1">
@@ -16850,10 +16850,10 @@
       <c r="D56" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="F56" s="387"/>
+      <c r="E56" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" s="386"/>
       <c r="G56" s="74"/>
     </row>
     <row r="57" spans="1:8" ht="24.75" customHeight="1">
@@ -16869,10 +16869,10 @@
       <c r="D57" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="320" t="s">
+      <c r="E57" s="346" t="s">
         <v>4</v>
       </c>
-      <c r="F57" s="321"/>
+      <c r="F57" s="347"/>
       <c r="G57" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16892,10 +16892,10 @@
       <c r="D58" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F58" s="321"/>
+      <c r="E58" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F58" s="347"/>
       <c r="G58" s="74"/>
       <c r="H58" s="49"/>
     </row>
@@ -16906,12 +16906,12 @@
       <c r="B59" s="58">
         <v>51</v>
       </c>
-      <c r="C59" s="324" t="s">
+      <c r="C59" s="337" t="s">
         <v>189</v>
       </c>
-      <c r="D59" s="325"/>
-      <c r="E59" s="325"/>
-      <c r="F59" s="325"/>
+      <c r="D59" s="338"/>
+      <c r="E59" s="338"/>
+      <c r="F59" s="338"/>
       <c r="G59" s="74"/>
     </row>
     <row r="60" spans="1:8" ht="12" customHeight="1">
@@ -16921,12 +16921,12 @@
       <c r="B60" s="58">
         <v>52</v>
       </c>
-      <c r="C60" s="324" t="s">
+      <c r="C60" s="337" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="325"/>
-      <c r="E60" s="325"/>
-      <c r="F60" s="325"/>
+      <c r="D60" s="338"/>
+      <c r="E60" s="338"/>
+      <c r="F60" s="338"/>
       <c r="G60" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16939,12 +16939,12 @@
       <c r="B61" s="58">
         <v>53</v>
       </c>
-      <c r="C61" s="324" t="s">
+      <c r="C61" s="337" t="s">
         <v>190</v>
       </c>
-      <c r="D61" s="325"/>
-      <c r="E61" s="325"/>
-      <c r="F61" s="325"/>
+      <c r="D61" s="338"/>
+      <c r="E61" s="338"/>
+      <c r="F61" s="338"/>
       <c r="G61" s="74"/>
     </row>
     <row r="62" spans="1:8" ht="12" customHeight="1">
@@ -16954,12 +16954,12 @@
       <c r="B62" s="58">
         <v>54</v>
       </c>
-      <c r="C62" s="324" t="s">
+      <c r="C62" s="337" t="s">
         <v>191</v>
       </c>
-      <c r="D62" s="325"/>
-      <c r="E62" s="325"/>
-      <c r="F62" s="325"/>
+      <c r="D62" s="338"/>
+      <c r="E62" s="338"/>
+      <c r="F62" s="338"/>
       <c r="G62" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16972,12 +16972,12 @@
       <c r="B63" s="58">
         <v>55</v>
       </c>
-      <c r="C63" s="324" t="s">
+      <c r="C63" s="337" t="s">
         <v>192</v>
       </c>
-      <c r="D63" s="325"/>
-      <c r="E63" s="325"/>
-      <c r="F63" s="325"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
       <c r="G63" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16990,14 +16990,14 @@
       <c r="B64" s="58">
         <v>56</v>
       </c>
-      <c r="C64" s="333" t="s">
+      <c r="C64" s="340" t="s">
         <v>175</v>
       </c>
-      <c r="D64" s="324" t="s">
+      <c r="D64" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E64" s="325"/>
-      <c r="F64" s="325"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
       <c r="G64" s="74"/>
     </row>
     <row r="65" spans="1:11" ht="12" customHeight="1">
@@ -17007,14 +17007,14 @@
       <c r="B65" s="58">
         <v>57</v>
       </c>
-      <c r="C65" s="334"/>
+      <c r="C65" s="341"/>
       <c r="D65" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E65" s="337" t="s">
+      <c r="E65" s="356" t="s">
         <v>91</v>
       </c>
-      <c r="F65" s="338"/>
+      <c r="F65" s="357"/>
       <c r="G65" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17033,10 +17033,10 @@
       <c r="D66" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E66" s="320" t="s">
+      <c r="E66" s="346" t="s">
         <v>193</v>
       </c>
-      <c r="F66" s="321"/>
+      <c r="F66" s="347"/>
       <c r="G66" s="74"/>
       <c r="H66" s="49"/>
     </row>
@@ -17047,14 +17047,14 @@
       <c r="B67" s="58">
         <v>59</v>
       </c>
-      <c r="C67" s="333" t="s">
+      <c r="C67" s="340" t="s">
         <v>102</v>
       </c>
-      <c r="D67" s="324" t="s">
+      <c r="D67" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E67" s="325"/>
-      <c r="F67" s="325"/>
+      <c r="E67" s="338"/>
+      <c r="F67" s="338"/>
       <c r="G67" s="74"/>
     </row>
     <row r="68" spans="1:11" ht="12" customHeight="1">
@@ -17064,14 +17064,14 @@
       <c r="B68" s="58">
         <v>60</v>
       </c>
-      <c r="C68" s="334"/>
+      <c r="C68" s="341"/>
       <c r="D68" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E68" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="F68" s="387"/>
+      <c r="E68" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="F68" s="386"/>
       <c r="G68" s="74"/>
     </row>
     <row r="69" spans="1:11" ht="12" customHeight="1">
@@ -17087,10 +17087,10 @@
       <c r="D69" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E69" s="320" t="s">
+      <c r="E69" s="346" t="s">
         <v>194</v>
       </c>
-      <c r="F69" s="321"/>
+      <c r="F69" s="347"/>
       <c r="G69" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17110,10 +17110,10 @@
       <c r="D70" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E70" s="320" t="s">
+      <c r="E70" s="346" t="s">
         <v>195</v>
       </c>
-      <c r="F70" s="321"/>
+      <c r="F70" s="347"/>
       <c r="G70" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17133,10 +17133,10 @@
       <c r="D71" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E71" s="388" t="s">
+      <c r="E71" s="389" t="s">
         <v>196</v>
       </c>
-      <c r="F71" s="389"/>
+      <c r="F71" s="390"/>
       <c r="G71" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17148,10 +17148,10 @@
       <c r="B72" s="58"/>
       <c r="C72" s="77"/>
       <c r="D72" s="70"/>
-      <c r="E72" s="388" t="s">
+      <c r="E72" s="389" t="s">
         <v>13</v>
       </c>
-      <c r="F72" s="389"/>
+      <c r="F72" s="390"/>
       <c r="G72" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17163,10 +17163,10 @@
       <c r="B73" s="58"/>
       <c r="C73" s="77"/>
       <c r="D73" s="70"/>
-      <c r="E73" s="388" t="s">
+      <c r="E73" s="389" t="s">
         <v>8</v>
       </c>
-      <c r="F73" s="389"/>
+      <c r="F73" s="390"/>
       <c r="G73" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17186,10 +17186,10 @@
       <c r="D74" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E74" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F74" s="321"/>
+      <c r="E74" s="346" t="s">
+        <v>44</v>
+      </c>
+      <c r="F74" s="347"/>
       <c r="G74" s="74"/>
       <c r="H74" s="49"/>
     </row>
@@ -17200,14 +17200,14 @@
       <c r="B75" s="58">
         <v>65</v>
       </c>
-      <c r="C75" s="333" t="s">
+      <c r="C75" s="340" t="s">
         <v>197</v>
       </c>
-      <c r="D75" s="324" t="s">
+      <c r="D75" s="337" t="s">
         <v>5</v>
       </c>
-      <c r="E75" s="325"/>
-      <c r="F75" s="325"/>
+      <c r="E75" s="338"/>
+      <c r="F75" s="338"/>
       <c r="G75" s="74"/>
     </row>
     <row r="76" spans="1:11" ht="12" customHeight="1">
@@ -17217,14 +17217,14 @@
       <c r="B76" s="58">
         <v>66</v>
       </c>
-      <c r="C76" s="334"/>
+      <c r="C76" s="341"/>
       <c r="D76" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E76" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="F76" s="387"/>
+      <c r="E76" s="384" t="s">
+        <v>44</v>
+      </c>
+      <c r="F76" s="386"/>
       <c r="G76" s="74"/>
     </row>
     <row r="77" spans="1:11" ht="12" customHeight="1">
@@ -17240,10 +17240,10 @@
       <c r="D77" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E77" s="320" t="s">
+      <c r="E77" s="346" t="s">
         <v>198</v>
       </c>
-      <c r="F77" s="321"/>
+      <c r="F77" s="347"/>
       <c r="G77" s="81" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -17302,13 +17302,13 @@
       <c r="K79" s="51"/>
     </row>
     <row r="80" spans="1:11" ht="15" customHeight="1">
-      <c r="B80" s="386" t="s">
+      <c r="B80" s="391" t="s">
         <v>199</v>
       </c>
-      <c r="C80" s="386"/>
-      <c r="D80" s="386"/>
-      <c r="E80" s="386"/>
-      <c r="F80" s="386"/>
+      <c r="C80" s="391"/>
+      <c r="D80" s="391"/>
+      <c r="E80" s="391"/>
+      <c r="F80" s="391"/>
       <c r="G80" s="83"/>
       <c r="H80" s="83"/>
       <c r="I80" s="82"/>
@@ -17316,13 +17316,13 @@
       <c r="K80" s="51"/>
     </row>
     <row r="81" spans="2:11" ht="15" customHeight="1">
-      <c r="B81" s="386" t="s">
-        <v>44</v>
-      </c>
-      <c r="C81" s="386"/>
-      <c r="D81" s="386"/>
-      <c r="E81" s="386"/>
-      <c r="F81" s="386"/>
+      <c r="B81" s="391" t="s">
+        <v>44</v>
+      </c>
+      <c r="C81" s="391"/>
+      <c r="D81" s="391"/>
+      <c r="E81" s="391"/>
+      <c r="F81" s="391"/>
       <c r="G81" s="84"/>
       <c r="H81" s="84"/>
       <c r="I81" s="83"/>
@@ -17332,14 +17332,14 @@
     <row r="82" spans="2:11" ht="15.75" hidden="1" customHeight="1"/>
     <row r="83" spans="2:11" ht="15.75" hidden="1" customHeight="1"/>
     <row r="84" spans="2:11" ht="15" customHeight="1">
-      <c r="B84" s="386" t="s">
+      <c r="B84" s="391" t="s">
         <v>200</v>
       </c>
-      <c r="C84" s="386"/>
-      <c r="D84" s="386"/>
-      <c r="E84" s="386"/>
-      <c r="F84" s="386"/>
-      <c r="G84" s="386"/>
+      <c r="C84" s="391"/>
+      <c r="D84" s="391"/>
+      <c r="E84" s="391"/>
+      <c r="F84" s="391"/>
+      <c r="G84" s="391"/>
       <c r="H84" s="83"/>
       <c r="I84" s="83"/>
       <c r="J84" s="83"/>
@@ -17368,51 +17368,13 @@
     <row r="105" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:F24"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="C63:F63"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="C53:F53"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C59:F59"/>
-    <mergeCell ref="C60:F60"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="B84:G84"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
     <mergeCell ref="E74:F74"/>
     <mergeCell ref="C64:C65"/>
     <mergeCell ref="D64:F64"/>
@@ -17426,13 +17388,51 @@
     <mergeCell ref="E71:F71"/>
     <mergeCell ref="E72:F72"/>
     <mergeCell ref="E73:F73"/>
-    <mergeCell ref="B84:G84"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C59:F59"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:F24"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Наименование на государственном языке заполняется автоматически в соответствии с КТРУ" sqref="B76 B49:B50 B95:B96"/>
@@ -17468,79 +17468,79 @@
       <c r="A1" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="400" t="s">
+      <c r="B1" s="431" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="400"/>
-      <c r="D1" s="400"/>
-      <c r="E1" s="400"/>
-      <c r="F1" s="400"/>
-      <c r="G1" s="400"/>
-      <c r="H1" s="400"/>
-      <c r="I1" s="400"/>
+      <c r="C1" s="431"/>
+      <c r="D1" s="431"/>
+      <c r="E1" s="431"/>
+      <c r="F1" s="431"/>
+      <c r="G1" s="431"/>
+      <c r="H1" s="431"/>
+      <c r="I1" s="431"/>
       <c r="M1" s="12"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1">
       <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="401" t="s">
+      <c r="B2" s="432" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="401"/>
-      <c r="D2" s="401"/>
-      <c r="E2" s="401"/>
-      <c r="F2" s="401"/>
-      <c r="G2" s="401"/>
-      <c r="H2" s="401"/>
-      <c r="I2" s="401"/>
+      <c r="C2" s="432"/>
+      <c r="D2" s="432"/>
+      <c r="E2" s="432"/>
+      <c r="F2" s="432"/>
+      <c r="G2" s="432"/>
+      <c r="H2" s="432"/>
+      <c r="I2" s="432"/>
       <c r="M2" s="12"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="402" t="s">
+      <c r="B3" s="433" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="402"/>
-      <c r="D3" s="402"/>
-      <c r="E3" s="402"/>
-      <c r="F3" s="402"/>
-      <c r="G3" s="402"/>
-      <c r="H3" s="402"/>
-      <c r="I3" s="402"/>
+      <c r="C3" s="433"/>
+      <c r="D3" s="433"/>
+      <c r="E3" s="433"/>
+      <c r="F3" s="433"/>
+      <c r="G3" s="433"/>
+      <c r="H3" s="433"/>
+      <c r="I3" s="433"/>
       <c r="M3" s="12"/>
     </row>
     <row r="4" spans="1:13" ht="30" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="402" t="s">
+      <c r="B4" s="433" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="402"/>
-      <c r="D4" s="402"/>
-      <c r="E4" s="402"/>
-      <c r="F4" s="402"/>
-      <c r="G4" s="402"/>
-      <c r="H4" s="402"/>
-      <c r="I4" s="402"/>
+      <c r="C4" s="433"/>
+      <c r="D4" s="433"/>
+      <c r="E4" s="433"/>
+      <c r="F4" s="433"/>
+      <c r="G4" s="433"/>
+      <c r="H4" s="433"/>
+      <c r="I4" s="433"/>
       <c r="M4" s="12"/>
     </row>
     <row r="5" spans="1:13" ht="12" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="403" t="s">
+      <c r="B5" s="434" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="403"/>
-      <c r="D5" s="403"/>
-      <c r="E5" s="403"/>
-      <c r="F5" s="403"/>
-      <c r="G5" s="403"/>
-      <c r="H5" s="403"/>
+      <c r="C5" s="434"/>
+      <c r="D5" s="434"/>
+      <c r="E5" s="434"/>
+      <c r="F5" s="434"/>
+      <c r="G5" s="434"/>
+      <c r="H5" s="434"/>
       <c r="I5" s="13" t="s">
         <v>50</v>
       </c>
@@ -17564,18 +17564,18 @@
       <c r="A20" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="404" t="s">
+      <c r="B20" s="435" t="s">
         <v>0</v>
       </c>
-      <c r="C20" s="407" t="s">
+      <c r="C20" s="438" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="408"/>
-      <c r="E20" s="408"/>
-      <c r="F20" s="408"/>
-      <c r="G20" s="408"/>
-      <c r="H20" s="409"/>
-      <c r="I20" s="416" t="s">
+      <c r="D20" s="439"/>
+      <c r="E20" s="439"/>
+      <c r="F20" s="439"/>
+      <c r="G20" s="439"/>
+      <c r="H20" s="440"/>
+      <c r="I20" s="447" t="s">
         <v>52</v>
       </c>
       <c r="J20" s="10"/>
@@ -17588,14 +17588,14 @@
       <c r="A21" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="405"/>
-      <c r="C21" s="410"/>
-      <c r="D21" s="411"/>
-      <c r="E21" s="411"/>
-      <c r="F21" s="411"/>
-      <c r="G21" s="411"/>
-      <c r="H21" s="412"/>
-      <c r="I21" s="405"/>
+      <c r="B21" s="436"/>
+      <c r="C21" s="441"/>
+      <c r="D21" s="442"/>
+      <c r="E21" s="442"/>
+      <c r="F21" s="442"/>
+      <c r="G21" s="442"/>
+      <c r="H21" s="443"/>
+      <c r="I21" s="436"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
@@ -17605,14 +17605,14 @@
       <c r="A22" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="406"/>
-      <c r="C22" s="413"/>
-      <c r="D22" s="414"/>
-      <c r="E22" s="414"/>
-      <c r="F22" s="414"/>
-      <c r="G22" s="414"/>
-      <c r="H22" s="415"/>
-      <c r="I22" s="406"/>
+      <c r="B22" s="437"/>
+      <c r="C22" s="444"/>
+      <c r="D22" s="445"/>
+      <c r="E22" s="445"/>
+      <c r="F22" s="445"/>
+      <c r="G22" s="445"/>
+      <c r="H22" s="446"/>
+      <c r="I22" s="437"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
@@ -17628,10 +17628,10 @@
       <c r="B26" s="18">
         <v>1</v>
       </c>
-      <c r="C26" s="392">
+      <c r="C26" s="429">
         <v>2</v>
       </c>
-      <c r="D26" s="393"/>
+      <c r="D26" s="430"/>
       <c r="E26" s="18">
         <v>3</v>
       </c>
@@ -17655,14 +17655,14 @@
       <c r="B27" s="19">
         <v>1</v>
       </c>
-      <c r="C27" s="394" t="s">
+      <c r="C27" s="395" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="395"/>
-      <c r="E27" s="395"/>
-      <c r="F27" s="395"/>
-      <c r="G27" s="395"/>
-      <c r="H27" s="396"/>
+      <c r="D27" s="396"/>
+      <c r="E27" s="396"/>
+      <c r="F27" s="396"/>
+      <c r="G27" s="396"/>
+      <c r="H27" s="397"/>
       <c r="I27" s="20"/>
       <c r="N27" s="16"/>
     </row>
@@ -17679,12 +17679,12 @@
       <c r="D28" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="394" t="s">
+      <c r="E28" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F28" s="395"/>
-      <c r="G28" s="395"/>
-      <c r="H28" s="396"/>
+      <c r="F28" s="396"/>
+      <c r="G28" s="396"/>
+      <c r="H28" s="397"/>
       <c r="I28" s="20" t="e">
         <f>SUM(I29:I190)</f>
         <v>#REF!</v>
@@ -17710,11 +17710,11 @@
       <c r="E29" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="397" t="s">
+      <c r="F29" s="402" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="398"/>
-      <c r="H29" s="399"/>
+      <c r="G29" s="403"/>
+      <c r="H29" s="404"/>
       <c r="I29" s="20" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17740,11 +17740,11 @@
       <c r="E30" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="397" t="s">
+      <c r="F30" s="402" t="s">
         <v>57</v>
       </c>
-      <c r="G30" s="398"/>
-      <c r="H30" s="399"/>
+      <c r="G30" s="403"/>
+      <c r="H30" s="404"/>
       <c r="I30" s="20" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17767,11 +17767,11 @@
       <c r="E31" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="397" t="s">
+      <c r="F31" s="402" t="s">
         <v>58</v>
       </c>
-      <c r="G31" s="398"/>
-      <c r="H31" s="399"/>
+      <c r="G31" s="403"/>
+      <c r="H31" s="404"/>
       <c r="I31" s="20"/>
     </row>
     <row r="32" spans="1:14" ht="12" customHeight="1">
@@ -17790,11 +17790,11 @@
       <c r="E32" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="417" t="s">
+      <c r="F32" s="392" t="s">
         <v>59</v>
       </c>
-      <c r="G32" s="418"/>
-      <c r="H32" s="419"/>
+      <c r="G32" s="393"/>
+      <c r="H32" s="394"/>
       <c r="I32" s="20" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -17820,16 +17820,16 @@
       <c r="B34" s="21">
         <v>7</v>
       </c>
-      <c r="C34" s="420" t="s">
+      <c r="C34" s="398" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="421"/>
-      <c r="E34" s="394" t="s">
+      <c r="D34" s="399"/>
+      <c r="E34" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="395"/>
-      <c r="G34" s="395"/>
-      <c r="H34" s="396"/>
+      <c r="F34" s="396"/>
+      <c r="G34" s="396"/>
+      <c r="H34" s="397"/>
       <c r="I34" s="32"/>
     </row>
     <row r="35" spans="1:15" ht="12" customHeight="1">
@@ -17839,16 +17839,16 @@
       <c r="B35" s="21">
         <v>8</v>
       </c>
-      <c r="C35" s="422"/>
-      <c r="D35" s="423"/>
+      <c r="C35" s="400"/>
+      <c r="D35" s="401"/>
       <c r="E35" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F35" s="397" t="s">
-        <v>44</v>
-      </c>
-      <c r="G35" s="398"/>
-      <c r="H35" s="399"/>
+      <c r="F35" s="402" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" s="403"/>
+      <c r="H35" s="404"/>
       <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:15" hidden="1">
@@ -17861,16 +17861,16 @@
       <c r="B37" s="21">
         <v>10</v>
       </c>
-      <c r="C37" s="424" t="s">
+      <c r="C37" s="408" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="425"/>
-      <c r="E37" s="394" t="s">
+      <c r="D37" s="409"/>
+      <c r="E37" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F37" s="395"/>
-      <c r="G37" s="395"/>
-      <c r="H37" s="396"/>
+      <c r="F37" s="396"/>
+      <c r="G37" s="396"/>
+      <c r="H37" s="397"/>
       <c r="I37" s="32"/>
     </row>
     <row r="38" spans="1:15" ht="12" customHeight="1">
@@ -17880,16 +17880,16 @@
       <c r="B38" s="21">
         <v>11</v>
       </c>
-      <c r="C38" s="426"/>
-      <c r="D38" s="427"/>
-      <c r="E38" s="430" t="s">
+      <c r="C38" s="410"/>
+      <c r="D38" s="411"/>
+      <c r="E38" s="414" t="s">
         <v>55</v>
       </c>
-      <c r="F38" s="397" t="s">
+      <c r="F38" s="402" t="s">
         <v>63</v>
       </c>
-      <c r="G38" s="398"/>
-      <c r="H38" s="399"/>
+      <c r="G38" s="403"/>
+      <c r="H38" s="404"/>
       <c r="I38" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17902,14 +17902,14 @@
       <c r="B39" s="21">
         <v>12</v>
       </c>
-      <c r="C39" s="428"/>
-      <c r="D39" s="429"/>
-      <c r="E39" s="431"/>
-      <c r="F39" s="397" t="s">
+      <c r="C39" s="412"/>
+      <c r="D39" s="413"/>
+      <c r="E39" s="415"/>
+      <c r="F39" s="402" t="s">
         <v>64</v>
       </c>
-      <c r="G39" s="398"/>
-      <c r="H39" s="399"/>
+      <c r="G39" s="403"/>
+      <c r="H39" s="404"/>
       <c r="I39" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17922,16 +17922,16 @@
       <c r="B40" s="21">
         <v>13</v>
       </c>
-      <c r="C40" s="420" t="s">
+      <c r="C40" s="398" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="421"/>
-      <c r="E40" s="394" t="s">
+      <c r="D40" s="399"/>
+      <c r="E40" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F40" s="395"/>
-      <c r="G40" s="395"/>
-      <c r="H40" s="396"/>
+      <c r="F40" s="396"/>
+      <c r="G40" s="396"/>
+      <c r="H40" s="397"/>
       <c r="I40" s="32"/>
     </row>
     <row r="41" spans="1:15" ht="17.25" customHeight="1">
@@ -17941,16 +17941,16 @@
       <c r="B41" s="21">
         <v>14</v>
       </c>
-      <c r="C41" s="422"/>
-      <c r="D41" s="423"/>
+      <c r="C41" s="400"/>
+      <c r="D41" s="401"/>
       <c r="E41" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F41" s="397" t="s">
-        <v>44</v>
-      </c>
-      <c r="G41" s="398"/>
-      <c r="H41" s="399"/>
+      <c r="F41" s="402" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" s="403"/>
+      <c r="H41" s="404"/>
       <c r="I41" s="32"/>
     </row>
     <row r="42" spans="1:15" ht="12" customHeight="1">
@@ -17969,11 +17969,11 @@
       <c r="E42" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F42" s="417" t="s">
+      <c r="F42" s="392" t="s">
         <v>66</v>
       </c>
-      <c r="G42" s="418"/>
-      <c r="H42" s="419"/>
+      <c r="G42" s="393"/>
+      <c r="H42" s="394"/>
       <c r="I42" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17990,14 +17990,14 @@
       <c r="B44" s="21">
         <v>17</v>
       </c>
-      <c r="C44" s="394" t="s">
+      <c r="C44" s="395" t="s">
         <v>67</v>
       </c>
-      <c r="D44" s="395"/>
-      <c r="E44" s="395"/>
-      <c r="F44" s="395"/>
-      <c r="G44" s="395"/>
-      <c r="H44" s="396"/>
+      <c r="D44" s="396"/>
+      <c r="E44" s="396"/>
+      <c r="F44" s="396"/>
+      <c r="G44" s="396"/>
+      <c r="H44" s="397"/>
       <c r="I44" s="32"/>
     </row>
     <row r="45" spans="1:15" ht="12" customHeight="1">
@@ -18007,16 +18007,16 @@
       <c r="B45" s="21">
         <v>18</v>
       </c>
-      <c r="C45" s="432" t="s">
+      <c r="C45" s="423" t="s">
         <v>68</v>
       </c>
-      <c r="D45" s="433"/>
-      <c r="E45" s="394" t="s">
+      <c r="D45" s="424"/>
+      <c r="E45" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="395"/>
-      <c r="G45" s="395"/>
-      <c r="H45" s="396"/>
+      <c r="F45" s="396"/>
+      <c r="G45" s="396"/>
+      <c r="H45" s="397"/>
       <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:15" ht="30" customHeight="1">
@@ -18026,16 +18026,16 @@
       <c r="B46" s="21">
         <v>19</v>
       </c>
-      <c r="C46" s="434"/>
-      <c r="D46" s="435"/>
-      <c r="E46" s="430" t="s">
+      <c r="C46" s="425"/>
+      <c r="D46" s="426"/>
+      <c r="E46" s="414" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="397" t="s">
+      <c r="F46" s="402" t="s">
         <v>69</v>
       </c>
-      <c r="G46" s="398"/>
-      <c r="H46" s="399"/>
+      <c r="G46" s="403"/>
+      <c r="H46" s="404"/>
       <c r="I46" s="127" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18050,14 +18050,14 @@
       <c r="B47" s="21">
         <v>20</v>
       </c>
-      <c r="C47" s="434"/>
-      <c r="D47" s="435"/>
-      <c r="E47" s="438"/>
-      <c r="F47" s="397" t="s">
+      <c r="C47" s="425"/>
+      <c r="D47" s="426"/>
+      <c r="E47" s="416"/>
+      <c r="F47" s="402" t="s">
         <v>70</v>
       </c>
-      <c r="G47" s="398"/>
-      <c r="H47" s="399"/>
+      <c r="G47" s="403"/>
+      <c r="H47" s="404"/>
       <c r="I47" s="127" t="e">
         <f>#REF!+#REF!-#REF!</f>
         <v>#REF!</v>
@@ -18072,14 +18072,14 @@
       <c r="B48" s="21">
         <v>21</v>
       </c>
-      <c r="C48" s="434"/>
-      <c r="D48" s="435"/>
-      <c r="E48" s="438"/>
-      <c r="F48" s="397" t="s">
+      <c r="C48" s="425"/>
+      <c r="D48" s="426"/>
+      <c r="E48" s="416"/>
+      <c r="F48" s="402" t="s">
         <v>71</v>
       </c>
-      <c r="G48" s="398"/>
-      <c r="H48" s="399"/>
+      <c r="G48" s="403"/>
+      <c r="H48" s="404"/>
       <c r="I48" s="127" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18093,14 +18093,14 @@
       <c r="B49" s="21">
         <v>22</v>
       </c>
-      <c r="C49" s="436"/>
-      <c r="D49" s="437"/>
-      <c r="E49" s="431"/>
-      <c r="F49" s="397" t="s">
+      <c r="C49" s="427"/>
+      <c r="D49" s="428"/>
+      <c r="E49" s="415"/>
+      <c r="F49" s="402" t="s">
         <v>72</v>
       </c>
-      <c r="G49" s="398"/>
-      <c r="H49" s="399"/>
+      <c r="G49" s="403"/>
+      <c r="H49" s="404"/>
       <c r="I49" s="34" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18114,16 +18114,16 @@
       <c r="B50" s="21">
         <v>23</v>
       </c>
-      <c r="C50" s="439" t="s">
+      <c r="C50" s="419" t="s">
         <v>73</v>
       </c>
-      <c r="D50" s="440"/>
-      <c r="E50" s="394" t="s">
+      <c r="D50" s="420"/>
+      <c r="E50" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F50" s="395"/>
-      <c r="G50" s="395"/>
-      <c r="H50" s="396"/>
+      <c r="F50" s="396"/>
+      <c r="G50" s="396"/>
+      <c r="H50" s="397"/>
       <c r="I50" s="32"/>
     </row>
     <row r="51" spans="1:14" ht="12" customHeight="1">
@@ -18133,16 +18133,16 @@
       <c r="B51" s="21">
         <v>24</v>
       </c>
-      <c r="C51" s="441"/>
-      <c r="D51" s="442"/>
+      <c r="C51" s="421"/>
+      <c r="D51" s="422"/>
       <c r="E51" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="397" t="s">
+      <c r="F51" s="402" t="s">
         <v>23</v>
       </c>
-      <c r="G51" s="398"/>
-      <c r="H51" s="399"/>
+      <c r="G51" s="403"/>
+      <c r="H51" s="404"/>
       <c r="I51" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18165,11 +18165,11 @@
       <c r="E52" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="397" t="s">
+      <c r="F52" s="402" t="s">
         <v>74</v>
       </c>
-      <c r="G52" s="398"/>
-      <c r="H52" s="399"/>
+      <c r="G52" s="403"/>
+      <c r="H52" s="404"/>
       <c r="I52" s="32"/>
       <c r="N52" s="35"/>
     </row>
@@ -18183,16 +18183,16 @@
       <c r="B54" s="21">
         <v>27</v>
       </c>
-      <c r="C54" s="420" t="s">
+      <c r="C54" s="398" t="s">
         <v>75</v>
       </c>
-      <c r="D54" s="421"/>
-      <c r="E54" s="394" t="s">
+      <c r="D54" s="399"/>
+      <c r="E54" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F54" s="395"/>
-      <c r="G54" s="395"/>
-      <c r="H54" s="396"/>
+      <c r="F54" s="396"/>
+      <c r="G54" s="396"/>
+      <c r="H54" s="397"/>
       <c r="I54" s="32"/>
     </row>
     <row r="55" spans="1:14" ht="12" customHeight="1">
@@ -18202,16 +18202,16 @@
       <c r="B55" s="21">
         <v>28</v>
       </c>
-      <c r="C55" s="422"/>
-      <c r="D55" s="423"/>
+      <c r="C55" s="400"/>
+      <c r="D55" s="401"/>
       <c r="E55" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F55" s="397" t="s">
+      <c r="F55" s="402" t="s">
         <v>76</v>
       </c>
-      <c r="G55" s="398"/>
-      <c r="H55" s="399"/>
+      <c r="G55" s="403"/>
+      <c r="H55" s="404"/>
       <c r="I55" s="32"/>
     </row>
     <row r="56" spans="1:14" ht="12" customHeight="1">
@@ -18221,16 +18221,16 @@
       <c r="B56" s="21">
         <v>29</v>
       </c>
-      <c r="C56" s="422"/>
-      <c r="D56" s="423"/>
+      <c r="C56" s="400"/>
+      <c r="D56" s="401"/>
       <c r="E56" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="397" t="s">
+      <c r="F56" s="402" t="s">
         <v>77</v>
       </c>
-      <c r="G56" s="398"/>
-      <c r="H56" s="399"/>
+      <c r="G56" s="403"/>
+      <c r="H56" s="404"/>
       <c r="I56" s="32"/>
     </row>
     <row r="57" spans="1:14" ht="12" customHeight="1">
@@ -18240,16 +18240,16 @@
       <c r="B57" s="21">
         <v>30</v>
       </c>
-      <c r="C57" s="422"/>
-      <c r="D57" s="423"/>
+      <c r="C57" s="400"/>
+      <c r="D57" s="401"/>
       <c r="E57" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="397" t="s">
+      <c r="F57" s="402" t="s">
         <v>78</v>
       </c>
-      <c r="G57" s="398"/>
-      <c r="H57" s="399"/>
+      <c r="G57" s="403"/>
+      <c r="H57" s="404"/>
       <c r="I57" s="32"/>
     </row>
     <row r="58" spans="1:14" ht="12" customHeight="1">
@@ -18268,11 +18268,11 @@
       <c r="E58" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F58" s="397" t="s">
+      <c r="F58" s="402" t="s">
         <v>79</v>
       </c>
-      <c r="G58" s="398"/>
-      <c r="H58" s="399"/>
+      <c r="G58" s="403"/>
+      <c r="H58" s="404"/>
       <c r="I58" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18288,14 +18288,14 @@
       <c r="B60" s="21">
         <v>33</v>
       </c>
-      <c r="C60" s="394" t="s">
+      <c r="C60" s="395" t="s">
         <v>80</v>
       </c>
-      <c r="D60" s="395"/>
-      <c r="E60" s="395"/>
-      <c r="F60" s="395"/>
-      <c r="G60" s="395"/>
-      <c r="H60" s="396"/>
+      <c r="D60" s="396"/>
+      <c r="E60" s="396"/>
+      <c r="F60" s="396"/>
+      <c r="G60" s="396"/>
+      <c r="H60" s="397"/>
       <c r="I60" s="32"/>
     </row>
     <row r="61" spans="1:14" ht="12" customHeight="1">
@@ -18305,16 +18305,16 @@
       <c r="B61" s="21">
         <v>34</v>
       </c>
-      <c r="C61" s="420" t="s">
+      <c r="C61" s="398" t="s">
         <v>81</v>
       </c>
-      <c r="D61" s="421"/>
-      <c r="E61" s="394" t="s">
+      <c r="D61" s="399"/>
+      <c r="E61" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F61" s="395"/>
-      <c r="G61" s="395"/>
-      <c r="H61" s="396"/>
+      <c r="F61" s="396"/>
+      <c r="G61" s="396"/>
+      <c r="H61" s="397"/>
       <c r="I61" s="32"/>
     </row>
     <row r="62" spans="1:14" ht="12" customHeight="1">
@@ -18324,18 +18324,18 @@
       <c r="B62" s="21">
         <v>35</v>
       </c>
-      <c r="C62" s="422"/>
-      <c r="D62" s="423"/>
+      <c r="C62" s="400"/>
+      <c r="D62" s="401"/>
       <c r="E62" s="26" t="s">
         <v>55</v>
       </c>
       <c r="F62" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G62" s="443" t="s">
+      <c r="G62" s="417" t="s">
         <v>5</v>
       </c>
-      <c r="H62" s="444"/>
+      <c r="H62" s="418"/>
       <c r="I62" s="32"/>
     </row>
     <row r="63" spans="1:14" ht="12" customHeight="1">
@@ -18345,8 +18345,8 @@
       <c r="B63" s="21">
         <v>36</v>
       </c>
-      <c r="C63" s="422"/>
-      <c r="D63" s="423"/>
+      <c r="C63" s="400"/>
+      <c r="D63" s="401"/>
       <c r="E63" s="27" t="s">
         <v>44</v>
       </c>
@@ -18410,10 +18410,10 @@
       <c r="F66" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="G66" s="443" t="s">
+      <c r="G66" s="417" t="s">
         <v>5</v>
       </c>
-      <c r="H66" s="444"/>
+      <c r="H66" s="418"/>
       <c r="I66" s="32"/>
     </row>
     <row r="67" spans="1:14" ht="12" customHeight="1">
@@ -18492,10 +18492,10 @@
       <c r="F70" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G70" s="443" t="s">
+      <c r="G70" s="417" t="s">
         <v>5</v>
       </c>
-      <c r="H70" s="444"/>
+      <c r="H70" s="418"/>
       <c r="I70" s="32"/>
     </row>
     <row r="71" spans="1:14" ht="12" customHeight="1">
@@ -18574,10 +18574,10 @@
       <c r="F74" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="G74" s="443" t="s">
+      <c r="G74" s="417" t="s">
         <v>5</v>
       </c>
-      <c r="H74" s="444"/>
+      <c r="H74" s="418"/>
       <c r="I74" s="32"/>
     </row>
     <row r="75" spans="1:14" ht="12" customHeight="1">
@@ -18644,16 +18644,16 @@
       <c r="B78" s="21">
         <v>51</v>
       </c>
-      <c r="C78" s="420" t="s">
+      <c r="C78" s="398" t="s">
         <v>88</v>
       </c>
-      <c r="D78" s="421"/>
-      <c r="E78" s="394" t="s">
+      <c r="D78" s="399"/>
+      <c r="E78" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F78" s="395"/>
-      <c r="G78" s="395"/>
-      <c r="H78" s="396"/>
+      <c r="F78" s="396"/>
+      <c r="G78" s="396"/>
+      <c r="H78" s="397"/>
       <c r="I78" s="32"/>
     </row>
     <row r="79" spans="1:14" ht="12" customHeight="1">
@@ -18663,16 +18663,16 @@
       <c r="B79" s="21">
         <v>52</v>
       </c>
-      <c r="C79" s="422"/>
-      <c r="D79" s="423"/>
+      <c r="C79" s="400"/>
+      <c r="D79" s="401"/>
       <c r="E79" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F79" s="397" t="s">
+      <c r="F79" s="402" t="s">
         <v>89</v>
       </c>
-      <c r="G79" s="398"/>
-      <c r="H79" s="399"/>
+      <c r="G79" s="403"/>
+      <c r="H79" s="404"/>
       <c r="I79" s="32"/>
     </row>
     <row r="80" spans="1:14" ht="12" customHeight="1">
@@ -18691,11 +18691,11 @@
       <c r="E80" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F80" s="397" t="s">
+      <c r="F80" s="402" t="s">
         <v>24</v>
       </c>
-      <c r="G80" s="398"/>
-      <c r="H80" s="399"/>
+      <c r="G80" s="403"/>
+      <c r="H80" s="404"/>
       <c r="I80" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18718,11 +18718,11 @@
       <c r="E81" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="397" t="s">
+      <c r="F81" s="402" t="s">
         <v>90</v>
       </c>
-      <c r="G81" s="398"/>
-      <c r="H81" s="399"/>
+      <c r="G81" s="403"/>
+      <c r="H81" s="404"/>
       <c r="I81" s="32"/>
       <c r="N81" s="35"/>
     </row>
@@ -18742,13 +18742,13 @@
       <c r="E82" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="430" t="s">
+      <c r="F82" s="414" t="s">
         <v>91</v>
       </c>
-      <c r="G82" s="443" t="s">
+      <c r="G82" s="417" t="s">
         <v>5</v>
       </c>
-      <c r="H82" s="444"/>
+      <c r="H82" s="418"/>
       <c r="I82" s="32"/>
     </row>
     <row r="83" spans="1:14" ht="24" customHeight="1">
@@ -18767,8 +18767,8 @@
       <c r="E83" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F83" s="438"/>
-      <c r="G83" s="430" t="s">
+      <c r="F83" s="416"/>
+      <c r="G83" s="414" t="s">
         <v>55</v>
       </c>
       <c r="H83" s="15" t="s">
@@ -18795,8 +18795,8 @@
       <c r="E84" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F84" s="431"/>
-      <c r="G84" s="431"/>
+      <c r="F84" s="415"/>
+      <c r="G84" s="415"/>
       <c r="H84" s="15" t="s">
         <v>92</v>
       </c>
@@ -18821,11 +18821,11 @@
       <c r="E85" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F85" s="397" t="s">
+      <c r="F85" s="402" t="s">
         <v>9</v>
       </c>
-      <c r="G85" s="398"/>
-      <c r="H85" s="399"/>
+      <c r="G85" s="403"/>
+      <c r="H85" s="404"/>
       <c r="I85" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18847,11 +18847,11 @@
       <c r="E86" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F86" s="397" t="s">
+      <c r="F86" s="402" t="s">
         <v>10</v>
       </c>
-      <c r="G86" s="398"/>
-      <c r="H86" s="399"/>
+      <c r="G86" s="403"/>
+      <c r="H86" s="404"/>
       <c r="I86" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18873,11 +18873,11 @@
       <c r="E87" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F87" s="397" t="s">
+      <c r="F87" s="402" t="s">
         <v>11</v>
       </c>
-      <c r="G87" s="398"/>
-      <c r="H87" s="399"/>
+      <c r="G87" s="403"/>
+      <c r="H87" s="404"/>
       <c r="I87" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18899,11 +18899,11 @@
       <c r="E88" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="397" t="s">
+      <c r="F88" s="402" t="s">
         <v>93</v>
       </c>
-      <c r="G88" s="398"/>
-      <c r="H88" s="399"/>
+      <c r="G88" s="403"/>
+      <c r="H88" s="404"/>
       <c r="I88" s="32"/>
     </row>
     <row r="89" spans="1:14" ht="12" customHeight="1">
@@ -18922,11 +18922,11 @@
       <c r="E89" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F89" s="417" t="s">
+      <c r="F89" s="392" t="s">
         <v>94</v>
       </c>
-      <c r="G89" s="418"/>
-      <c r="H89" s="419"/>
+      <c r="G89" s="393"/>
+      <c r="H89" s="394"/>
       <c r="I89" s="32"/>
       <c r="J89" s="10"/>
     </row>
@@ -18946,9 +18946,9 @@
       <c r="E90" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F90" s="417"/>
-      <c r="G90" s="418"/>
-      <c r="H90" s="419"/>
+      <c r="F90" s="392"/>
+      <c r="G90" s="393"/>
+      <c r="H90" s="394"/>
       <c r="I90" s="39"/>
       <c r="J90" s="10"/>
     </row>
@@ -18962,16 +18962,16 @@
       <c r="B92" s="21">
         <v>63</v>
       </c>
-      <c r="C92" s="420" t="s">
+      <c r="C92" s="398" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="421"/>
-      <c r="E92" s="394" t="s">
+      <c r="D92" s="399"/>
+      <c r="E92" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F92" s="395"/>
-      <c r="G92" s="395"/>
-      <c r="H92" s="396"/>
+      <c r="F92" s="396"/>
+      <c r="G92" s="396"/>
+      <c r="H92" s="397"/>
       <c r="I92" s="32"/>
     </row>
     <row r="93" spans="1:14" ht="12" customHeight="1">
@@ -18987,14 +18987,14 @@
       <c r="D93" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="430" t="s">
+      <c r="E93" s="414" t="s">
         <v>55</v>
       </c>
-      <c r="F93" s="397" t="s">
-        <v>44</v>
-      </c>
-      <c r="G93" s="398"/>
-      <c r="H93" s="399"/>
+      <c r="F93" s="402" t="s">
+        <v>44</v>
+      </c>
+      <c r="G93" s="403"/>
+      <c r="H93" s="404"/>
       <c r="I93" s="32"/>
     </row>
     <row r="94" spans="1:14" ht="12" customHeight="1">
@@ -19010,12 +19010,12 @@
       <c r="D94" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="E94" s="431"/>
-      <c r="F94" s="417" t="s">
+      <c r="E94" s="415"/>
+      <c r="F94" s="392" t="s">
         <v>96</v>
       </c>
-      <c r="G94" s="418"/>
-      <c r="H94" s="419"/>
+      <c r="G94" s="393"/>
+      <c r="H94" s="394"/>
       <c r="I94" s="32"/>
       <c r="J94" s="10"/>
     </row>
@@ -19029,16 +19029,16 @@
       <c r="B96" s="21">
         <v>66</v>
       </c>
-      <c r="C96" s="420" t="s">
+      <c r="C96" s="398" t="s">
         <v>97</v>
       </c>
-      <c r="D96" s="421"/>
-      <c r="E96" s="394" t="s">
+      <c r="D96" s="399"/>
+      <c r="E96" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F96" s="395"/>
-      <c r="G96" s="395"/>
-      <c r="H96" s="396"/>
+      <c r="F96" s="396"/>
+      <c r="G96" s="396"/>
+      <c r="H96" s="397"/>
       <c r="I96" s="32"/>
     </row>
     <row r="97" spans="1:10" ht="12" customHeight="1">
@@ -19057,11 +19057,11 @@
       <c r="E97" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F97" s="397" t="s">
+      <c r="F97" s="402" t="s">
         <v>98</v>
       </c>
-      <c r="G97" s="398"/>
-      <c r="H97" s="399"/>
+      <c r="G97" s="403"/>
+      <c r="H97" s="404"/>
       <c r="I97" s="32"/>
     </row>
     <row r="98" spans="1:10" ht="12" customHeight="1">
@@ -19080,11 +19080,11 @@
       <c r="E98" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F98" s="397" t="s">
+      <c r="F98" s="402" t="s">
         <v>99</v>
       </c>
-      <c r="G98" s="398"/>
-      <c r="H98" s="399"/>
+      <c r="G98" s="403"/>
+      <c r="H98" s="404"/>
       <c r="I98" s="32"/>
     </row>
     <row r="99" spans="1:10" ht="12" customHeight="1">
@@ -19103,11 +19103,11 @@
       <c r="E99" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F99" s="397" t="s">
+      <c r="F99" s="402" t="s">
         <v>12</v>
       </c>
-      <c r="G99" s="398"/>
-      <c r="H99" s="399"/>
+      <c r="G99" s="403"/>
+      <c r="H99" s="404"/>
       <c r="I99" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19129,11 +19129,11 @@
       <c r="E100" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F100" s="397" t="s">
+      <c r="F100" s="402" t="s">
         <v>100</v>
       </c>
-      <c r="G100" s="398"/>
-      <c r="H100" s="399"/>
+      <c r="G100" s="403"/>
+      <c r="H100" s="404"/>
       <c r="I100" s="32"/>
     </row>
     <row r="101" spans="1:10" ht="12" customHeight="1">
@@ -19152,11 +19152,11 @@
       <c r="E101" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F101" s="417" t="s">
-        <v>44</v>
-      </c>
-      <c r="G101" s="418"/>
-      <c r="H101" s="419"/>
+      <c r="F101" s="392" t="s">
+        <v>44</v>
+      </c>
+      <c r="G101" s="393"/>
+      <c r="H101" s="394"/>
       <c r="I101" s="32"/>
       <c r="J101" s="10"/>
     </row>
@@ -19176,11 +19176,11 @@
       <c r="E102" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F102" s="417" t="s">
-        <v>44</v>
-      </c>
-      <c r="G102" s="418"/>
-      <c r="H102" s="419"/>
+      <c r="F102" s="392" t="s">
+        <v>44</v>
+      </c>
+      <c r="G102" s="393"/>
+      <c r="H102" s="394"/>
       <c r="I102" s="32"/>
       <c r="J102" s="10"/>
     </row>
@@ -19194,14 +19194,14 @@
       <c r="B104" s="21">
         <v>72</v>
       </c>
-      <c r="C104" s="394" t="s">
+      <c r="C104" s="395" t="s">
         <v>19</v>
       </c>
-      <c r="D104" s="395"/>
-      <c r="E104" s="395"/>
-      <c r="F104" s="395"/>
-      <c r="G104" s="395"/>
-      <c r="H104" s="396"/>
+      <c r="D104" s="396"/>
+      <c r="E104" s="396"/>
+      <c r="F104" s="396"/>
+      <c r="G104" s="396"/>
+      <c r="H104" s="397"/>
       <c r="I104" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19214,14 +19214,14 @@
       <c r="B105" s="21">
         <v>73</v>
       </c>
-      <c r="C105" s="394" t="s">
+      <c r="C105" s="395" t="s">
         <v>101</v>
       </c>
-      <c r="D105" s="395"/>
-      <c r="E105" s="395"/>
-      <c r="F105" s="395"/>
-      <c r="G105" s="395"/>
-      <c r="H105" s="396"/>
+      <c r="D105" s="396"/>
+      <c r="E105" s="396"/>
+      <c r="F105" s="396"/>
+      <c r="G105" s="396"/>
+      <c r="H105" s="397"/>
       <c r="I105" s="32"/>
     </row>
     <row r="106" spans="1:10" ht="12" customHeight="1">
@@ -19231,16 +19231,16 @@
       <c r="B106" s="21">
         <v>74</v>
       </c>
-      <c r="C106" s="420" t="s">
+      <c r="C106" s="398" t="s">
         <v>102</v>
       </c>
-      <c r="D106" s="421"/>
-      <c r="E106" s="394" t="s">
+      <c r="D106" s="399"/>
+      <c r="E106" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F106" s="395"/>
-      <c r="G106" s="395"/>
-      <c r="H106" s="396"/>
+      <c r="F106" s="396"/>
+      <c r="G106" s="396"/>
+      <c r="H106" s="397"/>
       <c r="I106" s="32"/>
     </row>
     <row r="107" spans="1:10" ht="18.75" customHeight="1">
@@ -19250,16 +19250,16 @@
       <c r="B107" s="21">
         <v>75</v>
       </c>
-      <c r="C107" s="422"/>
-      <c r="D107" s="423"/>
+      <c r="C107" s="400"/>
+      <c r="D107" s="401"/>
       <c r="E107" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F107" s="397" t="s">
+      <c r="F107" s="402" t="s">
         <v>13</v>
       </c>
-      <c r="G107" s="398"/>
-      <c r="H107" s="399"/>
+      <c r="G107" s="403"/>
+      <c r="H107" s="404"/>
       <c r="I107" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19281,11 +19281,11 @@
       <c r="E108" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F108" s="417" t="s">
+      <c r="F108" s="392" t="s">
         <v>103</v>
       </c>
-      <c r="G108" s="418"/>
-      <c r="H108" s="419"/>
+      <c r="G108" s="393"/>
+      <c r="H108" s="394"/>
       <c r="I108" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19308,11 +19308,11 @@
       <c r="E109" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F109" s="417" t="s">
+      <c r="F109" s="392" t="s">
         <v>104</v>
       </c>
-      <c r="G109" s="418"/>
-      <c r="H109" s="419"/>
+      <c r="G109" s="393"/>
+      <c r="H109" s="394"/>
       <c r="I109" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19335,11 +19335,11 @@
       <c r="E110" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F110" s="417" t="s">
+      <c r="F110" s="392" t="s">
         <v>8</v>
       </c>
-      <c r="G110" s="418"/>
-      <c r="H110" s="419"/>
+      <c r="G110" s="393"/>
+      <c r="H110" s="394"/>
       <c r="I110" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19356,16 +19356,16 @@
       <c r="B112" s="21">
         <v>77</v>
       </c>
-      <c r="C112" s="420" t="s">
+      <c r="C112" s="398" t="s">
         <v>105</v>
       </c>
-      <c r="D112" s="421"/>
-      <c r="E112" s="394" t="s">
+      <c r="D112" s="399"/>
+      <c r="E112" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F112" s="395"/>
-      <c r="G112" s="395"/>
-      <c r="H112" s="396"/>
+      <c r="F112" s="396"/>
+      <c r="G112" s="396"/>
+      <c r="H112" s="397"/>
       <c r="I112" s="32"/>
     </row>
     <row r="113" spans="1:9" ht="12" customHeight="1">
@@ -19384,11 +19384,11 @@
       <c r="E113" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F113" s="397" t="s">
+      <c r="F113" s="402" t="s">
         <v>106</v>
       </c>
-      <c r="G113" s="398"/>
-      <c r="H113" s="399"/>
+      <c r="G113" s="403"/>
+      <c r="H113" s="404"/>
       <c r="I113" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19410,11 +19410,11 @@
       <c r="E114" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F114" s="397" t="s">
+      <c r="F114" s="402" t="s">
         <v>107</v>
       </c>
-      <c r="G114" s="398"/>
-      <c r="H114" s="399"/>
+      <c r="G114" s="403"/>
+      <c r="H114" s="404"/>
       <c r="I114" s="32"/>
     </row>
     <row r="115" spans="1:9" ht="12" customHeight="1">
@@ -19424,14 +19424,14 @@
       <c r="B115" s="21">
         <v>80</v>
       </c>
-      <c r="C115" s="394" t="s">
+      <c r="C115" s="395" t="s">
         <v>108</v>
       </c>
-      <c r="D115" s="395"/>
-      <c r="E115" s="395"/>
-      <c r="F115" s="395"/>
-      <c r="G115" s="395"/>
-      <c r="H115" s="396"/>
+      <c r="D115" s="396"/>
+      <c r="E115" s="396"/>
+      <c r="F115" s="396"/>
+      <c r="G115" s="396"/>
+      <c r="H115" s="397"/>
       <c r="I115" s="32"/>
     </row>
     <row r="116" spans="1:9" ht="12" customHeight="1">
@@ -19441,16 +19441,16 @@
       <c r="B116" s="21">
         <v>81</v>
       </c>
-      <c r="C116" s="420" t="s">
+      <c r="C116" s="398" t="s">
         <v>109</v>
       </c>
-      <c r="D116" s="421"/>
-      <c r="E116" s="394" t="s">
+      <c r="D116" s="399"/>
+      <c r="E116" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F116" s="395"/>
-      <c r="G116" s="395"/>
-      <c r="H116" s="396"/>
+      <c r="F116" s="396"/>
+      <c r="G116" s="396"/>
+      <c r="H116" s="397"/>
       <c r="I116" s="32"/>
     </row>
     <row r="117" spans="1:9" ht="12" customHeight="1">
@@ -19460,16 +19460,16 @@
       <c r="B117" s="21">
         <v>82</v>
       </c>
-      <c r="C117" s="422"/>
-      <c r="D117" s="423"/>
+      <c r="C117" s="400"/>
+      <c r="D117" s="401"/>
       <c r="E117" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F117" s="397" t="s">
+      <c r="F117" s="402" t="s">
         <v>110</v>
       </c>
-      <c r="G117" s="398"/>
-      <c r="H117" s="399"/>
+      <c r="G117" s="403"/>
+      <c r="H117" s="404"/>
       <c r="I117" s="32"/>
     </row>
     <row r="118" spans="1:9" ht="12" customHeight="1">
@@ -19488,11 +19488,11 @@
       <c r="E118" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F118" s="397" t="s">
+      <c r="F118" s="402" t="s">
         <v>111</v>
       </c>
-      <c r="G118" s="398"/>
-      <c r="H118" s="399"/>
+      <c r="G118" s="403"/>
+      <c r="H118" s="404"/>
       <c r="I118" s="32"/>
     </row>
     <row r="119" spans="1:9" hidden="1">
@@ -19505,16 +19505,16 @@
       <c r="B120" s="21">
         <v>85</v>
       </c>
-      <c r="C120" s="420" t="s">
+      <c r="C120" s="398" t="s">
         <v>112</v>
       </c>
-      <c r="D120" s="421"/>
-      <c r="E120" s="394" t="s">
+      <c r="D120" s="399"/>
+      <c r="E120" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F120" s="395"/>
-      <c r="G120" s="395"/>
-      <c r="H120" s="396"/>
+      <c r="F120" s="396"/>
+      <c r="G120" s="396"/>
+      <c r="H120" s="397"/>
       <c r="I120" s="32"/>
     </row>
     <row r="121" spans="1:9" ht="12" customHeight="1">
@@ -19524,16 +19524,16 @@
       <c r="B121" s="21">
         <v>86</v>
       </c>
-      <c r="C121" s="422"/>
-      <c r="D121" s="423"/>
+      <c r="C121" s="400"/>
+      <c r="D121" s="401"/>
       <c r="E121" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F121" s="397" t="s">
+      <c r="F121" s="402" t="s">
         <v>113</v>
       </c>
-      <c r="G121" s="398"/>
-      <c r="H121" s="399"/>
+      <c r="G121" s="403"/>
+      <c r="H121" s="404"/>
       <c r="I121" s="32"/>
     </row>
     <row r="122" spans="1:9" ht="12" customHeight="1">
@@ -19552,11 +19552,11 @@
       <c r="E122" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F122" s="397" t="s">
+      <c r="F122" s="402" t="s">
         <v>111</v>
       </c>
-      <c r="G122" s="398"/>
-      <c r="H122" s="399"/>
+      <c r="G122" s="403"/>
+      <c r="H122" s="404"/>
       <c r="I122" s="32"/>
     </row>
     <row r="123" spans="1:9" ht="12" customHeight="1">
@@ -19575,11 +19575,11 @@
       <c r="E123" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F123" s="397" t="s">
+      <c r="F123" s="402" t="s">
         <v>114</v>
       </c>
-      <c r="G123" s="398"/>
-      <c r="H123" s="399"/>
+      <c r="G123" s="403"/>
+      <c r="H123" s="404"/>
       <c r="I123" s="32"/>
     </row>
     <row r="124" spans="1:9" ht="12" customHeight="1">
@@ -19598,11 +19598,11 @@
       <c r="E124" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F124" s="397" t="s">
+      <c r="F124" s="402" t="s">
         <v>115</v>
       </c>
-      <c r="G124" s="398"/>
-      <c r="H124" s="399"/>
+      <c r="G124" s="403"/>
+      <c r="H124" s="404"/>
       <c r="I124" s="32"/>
     </row>
     <row r="125" spans="1:9" hidden="1">
@@ -19615,14 +19615,14 @@
       <c r="B126" s="21">
         <v>91</v>
       </c>
-      <c r="C126" s="394" t="s">
+      <c r="C126" s="395" t="s">
         <v>116</v>
       </c>
-      <c r="D126" s="395"/>
-      <c r="E126" s="395"/>
-      <c r="F126" s="395"/>
-      <c r="G126" s="395"/>
-      <c r="H126" s="396"/>
+      <c r="D126" s="396"/>
+      <c r="E126" s="396"/>
+      <c r="F126" s="396"/>
+      <c r="G126" s="396"/>
+      <c r="H126" s="397"/>
       <c r="I126" s="32"/>
     </row>
     <row r="127" spans="1:9" ht="12" customHeight="1">
@@ -19632,16 +19632,16 @@
       <c r="B127" s="21">
         <v>92</v>
       </c>
-      <c r="C127" s="420" t="s">
+      <c r="C127" s="398" t="s">
         <v>117</v>
       </c>
-      <c r="D127" s="421"/>
-      <c r="E127" s="394" t="s">
+      <c r="D127" s="399"/>
+      <c r="E127" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F127" s="395"/>
-      <c r="G127" s="395"/>
-      <c r="H127" s="396"/>
+      <c r="F127" s="396"/>
+      <c r="G127" s="396"/>
+      <c r="H127" s="397"/>
       <c r="I127" s="32"/>
     </row>
     <row r="128" spans="1:9" ht="12" customHeight="1">
@@ -19651,16 +19651,16 @@
       <c r="B128" s="21">
         <v>93</v>
       </c>
-      <c r="C128" s="422"/>
-      <c r="D128" s="423"/>
+      <c r="C128" s="400"/>
+      <c r="D128" s="401"/>
       <c r="E128" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F128" s="445" t="s">
-        <v>44</v>
-      </c>
-      <c r="G128" s="446"/>
-      <c r="H128" s="447"/>
+      <c r="F128" s="405" t="s">
+        <v>44</v>
+      </c>
+      <c r="G128" s="406"/>
+      <c r="H128" s="407"/>
       <c r="I128" s="40"/>
     </row>
     <row r="129" spans="1:14" hidden="1">
@@ -19673,14 +19673,14 @@
       <c r="B130" s="21">
         <v>95</v>
       </c>
-      <c r="C130" s="394" t="s">
+      <c r="C130" s="395" t="s">
         <v>118</v>
       </c>
-      <c r="D130" s="395"/>
-      <c r="E130" s="395"/>
-      <c r="F130" s="395"/>
-      <c r="G130" s="395"/>
-      <c r="H130" s="396"/>
+      <c r="D130" s="396"/>
+      <c r="E130" s="396"/>
+      <c r="F130" s="396"/>
+      <c r="G130" s="396"/>
+      <c r="H130" s="397"/>
       <c r="I130" s="32"/>
     </row>
     <row r="131" spans="1:14" ht="12" customHeight="1">
@@ -19690,14 +19690,14 @@
       <c r="B131" s="21">
         <v>96</v>
       </c>
-      <c r="C131" s="394" t="s">
+      <c r="C131" s="395" t="s">
         <v>119</v>
       </c>
-      <c r="D131" s="395"/>
-      <c r="E131" s="395"/>
-      <c r="F131" s="395"/>
-      <c r="G131" s="395"/>
-      <c r="H131" s="396"/>
+      <c r="D131" s="396"/>
+      <c r="E131" s="396"/>
+      <c r="F131" s="396"/>
+      <c r="G131" s="396"/>
+      <c r="H131" s="397"/>
       <c r="I131" s="32"/>
     </row>
     <row r="132" spans="1:14" ht="12" customHeight="1">
@@ -19707,16 +19707,16 @@
       <c r="B132" s="21">
         <v>97</v>
       </c>
-      <c r="C132" s="420" t="s">
+      <c r="C132" s="398" t="s">
         <v>120</v>
       </c>
-      <c r="D132" s="421"/>
-      <c r="E132" s="394" t="s">
+      <c r="D132" s="399"/>
+      <c r="E132" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F132" s="395"/>
-      <c r="G132" s="395"/>
-      <c r="H132" s="396"/>
+      <c r="F132" s="396"/>
+      <c r="G132" s="396"/>
+      <c r="H132" s="397"/>
       <c r="I132" s="32"/>
     </row>
     <row r="133" spans="1:14" ht="12" customHeight="1">
@@ -19726,16 +19726,16 @@
       <c r="B133" s="21">
         <v>98</v>
       </c>
-      <c r="C133" s="422"/>
-      <c r="D133" s="423"/>
+      <c r="C133" s="400"/>
+      <c r="D133" s="401"/>
       <c r="E133" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F133" s="397" t="s">
+      <c r="F133" s="402" t="s">
         <v>121</v>
       </c>
-      <c r="G133" s="398"/>
-      <c r="H133" s="399"/>
+      <c r="G133" s="403"/>
+      <c r="H133" s="404"/>
       <c r="I133" s="32"/>
     </row>
     <row r="134" spans="1:14" ht="12" customHeight="1">
@@ -19745,16 +19745,16 @@
       <c r="B134" s="21">
         <v>99</v>
       </c>
-      <c r="C134" s="422"/>
-      <c r="D134" s="423"/>
+      <c r="C134" s="400"/>
+      <c r="D134" s="401"/>
       <c r="E134" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F134" s="397" t="s">
+      <c r="F134" s="402" t="s">
         <v>122</v>
       </c>
-      <c r="G134" s="398"/>
-      <c r="H134" s="399"/>
+      <c r="G134" s="403"/>
+      <c r="H134" s="404"/>
       <c r="I134" s="32"/>
     </row>
     <row r="135" spans="1:14" ht="12" customHeight="1">
@@ -19764,16 +19764,16 @@
       <c r="B135" s="21">
         <v>100</v>
       </c>
-      <c r="C135" s="422"/>
-      <c r="D135" s="423"/>
+      <c r="C135" s="400"/>
+      <c r="D135" s="401"/>
       <c r="E135" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F135" s="397" t="s">
+      <c r="F135" s="402" t="s">
         <v>123</v>
       </c>
-      <c r="G135" s="398"/>
-      <c r="H135" s="399"/>
+      <c r="G135" s="403"/>
+      <c r="H135" s="404"/>
       <c r="I135" s="32"/>
     </row>
     <row r="136" spans="1:14" ht="12" customHeight="1">
@@ -19792,11 +19792,11 @@
       <c r="E136" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F136" s="397" t="s">
+      <c r="F136" s="402" t="s">
         <v>124</v>
       </c>
-      <c r="G136" s="398"/>
-      <c r="H136" s="399"/>
+      <c r="G136" s="403"/>
+      <c r="H136" s="404"/>
       <c r="I136" s="32"/>
     </row>
     <row r="137" spans="1:14" ht="12" customHeight="1">
@@ -19815,11 +19815,11 @@
       <c r="E137" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F137" s="397" t="s">
+      <c r="F137" s="402" t="s">
         <v>125</v>
       </c>
-      <c r="G137" s="398"/>
-      <c r="H137" s="399"/>
+      <c r="G137" s="403"/>
+      <c r="H137" s="404"/>
       <c r="I137" s="32"/>
     </row>
     <row r="138" spans="1:14" ht="12" customHeight="1">
@@ -19838,11 +19838,11 @@
       <c r="E138" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F138" s="397" t="s">
+      <c r="F138" s="402" t="s">
         <v>126</v>
       </c>
-      <c r="G138" s="398"/>
-      <c r="H138" s="399"/>
+      <c r="G138" s="403"/>
+      <c r="H138" s="404"/>
       <c r="I138" s="32"/>
     </row>
     <row r="139" spans="1:14" hidden="1">
@@ -19855,16 +19855,16 @@
       <c r="B140" s="21">
         <v>105</v>
       </c>
-      <c r="C140" s="424" t="s">
+      <c r="C140" s="408" t="s">
         <v>127</v>
       </c>
-      <c r="D140" s="425"/>
-      <c r="E140" s="394" t="s">
+      <c r="D140" s="409"/>
+      <c r="E140" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F140" s="395"/>
-      <c r="G140" s="395"/>
-      <c r="H140" s="396"/>
+      <c r="F140" s="396"/>
+      <c r="G140" s="396"/>
+      <c r="H140" s="397"/>
       <c r="I140" s="32"/>
     </row>
     <row r="141" spans="1:14" ht="12" customHeight="1">
@@ -19874,16 +19874,16 @@
       <c r="B141" s="21">
         <v>106</v>
       </c>
-      <c r="C141" s="426"/>
-      <c r="D141" s="427"/>
-      <c r="E141" s="430" t="s">
+      <c r="C141" s="410"/>
+      <c r="D141" s="411"/>
+      <c r="E141" s="414" t="s">
         <v>55</v>
       </c>
-      <c r="F141" s="397" t="s">
+      <c r="F141" s="402" t="s">
         <v>128</v>
       </c>
-      <c r="G141" s="398"/>
-      <c r="H141" s="399"/>
+      <c r="G141" s="403"/>
+      <c r="H141" s="404"/>
       <c r="I141" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -19896,14 +19896,14 @@
       <c r="B142" s="21">
         <v>107</v>
       </c>
-      <c r="C142" s="428"/>
-      <c r="D142" s="429"/>
-      <c r="E142" s="431"/>
-      <c r="F142" s="397" t="s">
+      <c r="C142" s="412"/>
+      <c r="D142" s="413"/>
+      <c r="E142" s="415"/>
+      <c r="F142" s="402" t="s">
         <v>129</v>
       </c>
-      <c r="G142" s="398"/>
-      <c r="H142" s="399"/>
+      <c r="G142" s="403"/>
+      <c r="H142" s="404"/>
       <c r="I142" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19917,14 +19917,14 @@
       <c r="B143" s="21">
         <v>108</v>
       </c>
-      <c r="C143" s="394" t="s">
+      <c r="C143" s="395" t="s">
         <v>22</v>
       </c>
-      <c r="D143" s="395"/>
-      <c r="E143" s="395"/>
-      <c r="F143" s="395"/>
-      <c r="G143" s="395"/>
-      <c r="H143" s="396"/>
+      <c r="D143" s="396"/>
+      <c r="E143" s="396"/>
+      <c r="F143" s="396"/>
+      <c r="G143" s="396"/>
+      <c r="H143" s="397"/>
       <c r="I143" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19944,12 +19944,12 @@
       <c r="D144" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E144" s="394" t="s">
+      <c r="E144" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F144" s="395"/>
-      <c r="G144" s="395"/>
-      <c r="H144" s="396"/>
+      <c r="F144" s="396"/>
+      <c r="G144" s="396"/>
+      <c r="H144" s="397"/>
       <c r="I144" s="32"/>
     </row>
     <row r="145" spans="1:10" ht="12" customHeight="1">
@@ -19968,11 +19968,11 @@
       <c r="E145" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F145" s="397" t="s">
+      <c r="F145" s="402" t="s">
         <v>131</v>
       </c>
-      <c r="G145" s="398"/>
-      <c r="H145" s="399"/>
+      <c r="G145" s="403"/>
+      <c r="H145" s="404"/>
       <c r="I145" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19994,11 +19994,11 @@
       <c r="E146" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F146" s="397" t="s">
+      <c r="F146" s="402" t="s">
         <v>132</v>
       </c>
-      <c r="G146" s="398"/>
-      <c r="H146" s="399"/>
+      <c r="G146" s="403"/>
+      <c r="H146" s="404"/>
       <c r="I146" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20020,11 +20020,11 @@
       <c r="E147" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F147" s="397" t="s">
+      <c r="F147" s="402" t="s">
         <v>64</v>
       </c>
-      <c r="G147" s="398"/>
-      <c r="H147" s="399"/>
+      <c r="G147" s="403"/>
+      <c r="H147" s="404"/>
       <c r="I147" s="32"/>
     </row>
     <row r="148" spans="1:10" ht="12" customHeight="1">
@@ -20043,11 +20043,11 @@
       <c r="E148" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F148" s="417" t="s">
+      <c r="F148" s="392" t="s">
         <v>133</v>
       </c>
-      <c r="G148" s="418"/>
-      <c r="H148" s="419"/>
+      <c r="G148" s="393"/>
+      <c r="H148" s="394"/>
       <c r="I148" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20070,11 +20070,11 @@
       <c r="E149" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F149" s="417" t="s">
+      <c r="F149" s="392" t="s">
         <v>134</v>
       </c>
-      <c r="G149" s="418"/>
-      <c r="H149" s="419"/>
+      <c r="G149" s="393"/>
+      <c r="H149" s="394"/>
       <c r="I149" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20097,11 +20097,11 @@
       <c r="E150" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F150" s="417" t="s">
+      <c r="F150" s="392" t="s">
         <v>135</v>
       </c>
-      <c r="G150" s="418"/>
-      <c r="H150" s="419"/>
+      <c r="G150" s="393"/>
+      <c r="H150" s="394"/>
       <c r="I150" s="32"/>
       <c r="J150" s="10"/>
     </row>
@@ -20121,11 +20121,11 @@
       <c r="E151" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F151" s="417" t="s">
+      <c r="F151" s="392" t="s">
         <v>136</v>
       </c>
-      <c r="G151" s="418"/>
-      <c r="H151" s="419"/>
+      <c r="G151" s="393"/>
+      <c r="H151" s="394"/>
       <c r="I151" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20142,16 +20142,16 @@
       <c r="B153" s="21">
         <v>114</v>
       </c>
-      <c r="C153" s="420" t="s">
+      <c r="C153" s="398" t="s">
         <v>137</v>
       </c>
-      <c r="D153" s="421"/>
-      <c r="E153" s="394" t="s">
+      <c r="D153" s="399"/>
+      <c r="E153" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F153" s="395"/>
-      <c r="G153" s="395"/>
-      <c r="H153" s="396"/>
+      <c r="F153" s="396"/>
+      <c r="G153" s="396"/>
+      <c r="H153" s="397"/>
       <c r="I153" s="32"/>
     </row>
     <row r="154" spans="1:10" ht="12" customHeight="1">
@@ -20161,16 +20161,16 @@
       <c r="B154" s="21">
         <v>115</v>
       </c>
-      <c r="C154" s="422"/>
-      <c r="D154" s="423"/>
+      <c r="C154" s="400"/>
+      <c r="D154" s="401"/>
       <c r="E154" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F154" s="445" t="s">
-        <v>44</v>
-      </c>
-      <c r="G154" s="446"/>
-      <c r="H154" s="447"/>
+      <c r="F154" s="405" t="s">
+        <v>44</v>
+      </c>
+      <c r="G154" s="406"/>
+      <c r="H154" s="407"/>
       <c r="I154" s="40"/>
     </row>
     <row r="155" spans="1:10" ht="12" customHeight="1">
@@ -20189,11 +20189,11 @@
       <c r="E155" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F155" s="417" t="s">
+      <c r="F155" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="G155" s="418"/>
-      <c r="H155" s="419"/>
+      <c r="G155" s="393"/>
+      <c r="H155" s="394"/>
       <c r="I155" s="32"/>
       <c r="J155" s="10"/>
     </row>
@@ -20213,11 +20213,11 @@
       <c r="E156" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F156" s="417" t="s">
+      <c r="F156" s="392" t="s">
         <v>138</v>
       </c>
-      <c r="G156" s="418"/>
-      <c r="H156" s="419"/>
+      <c r="G156" s="393"/>
+      <c r="H156" s="394"/>
       <c r="I156" s="32"/>
       <c r="J156" s="10"/>
     </row>
@@ -20237,11 +20237,11 @@
       <c r="E157" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F157" s="417" t="s">
+      <c r="F157" s="392" t="s">
         <v>139</v>
       </c>
-      <c r="G157" s="418"/>
-      <c r="H157" s="419"/>
+      <c r="G157" s="393"/>
+      <c r="H157" s="394"/>
       <c r="I157" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20264,9 +20264,9 @@
       <c r="E158" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F158" s="417"/>
-      <c r="G158" s="418"/>
-      <c r="H158" s="419"/>
+      <c r="F158" s="392"/>
+      <c r="G158" s="393"/>
+      <c r="H158" s="394"/>
       <c r="I158" s="32"/>
       <c r="J158" s="10"/>
     </row>
@@ -20280,14 +20280,14 @@
       <c r="B160" s="21">
         <v>117</v>
       </c>
-      <c r="C160" s="394" t="s">
+      <c r="C160" s="395" t="s">
         <v>140</v>
       </c>
-      <c r="D160" s="395"/>
-      <c r="E160" s="395"/>
-      <c r="F160" s="395"/>
-      <c r="G160" s="395"/>
-      <c r="H160" s="396"/>
+      <c r="D160" s="396"/>
+      <c r="E160" s="396"/>
+      <c r="F160" s="396"/>
+      <c r="G160" s="396"/>
+      <c r="H160" s="397"/>
       <c r="I160" s="32"/>
     </row>
     <row r="161" spans="1:9" ht="12" customHeight="1">
@@ -20297,14 +20297,14 @@
       <c r="B161" s="21">
         <v>118</v>
       </c>
-      <c r="C161" s="394" t="s">
+      <c r="C161" s="395" t="s">
         <v>141</v>
       </c>
-      <c r="D161" s="395"/>
-      <c r="E161" s="395"/>
-      <c r="F161" s="395"/>
-      <c r="G161" s="395"/>
-      <c r="H161" s="396"/>
+      <c r="D161" s="396"/>
+      <c r="E161" s="396"/>
+      <c r="F161" s="396"/>
+      <c r="G161" s="396"/>
+      <c r="H161" s="397"/>
       <c r="I161" s="42" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -20317,14 +20317,14 @@
       <c r="B162" s="21">
         <v>119</v>
       </c>
-      <c r="C162" s="394" t="s">
+      <c r="C162" s="395" t="s">
         <v>142</v>
       </c>
-      <c r="D162" s="395"/>
-      <c r="E162" s="395"/>
-      <c r="F162" s="395"/>
-      <c r="G162" s="395"/>
-      <c r="H162" s="396"/>
+      <c r="D162" s="396"/>
+      <c r="E162" s="396"/>
+      <c r="F162" s="396"/>
+      <c r="G162" s="396"/>
+      <c r="H162" s="397"/>
       <c r="I162" s="32"/>
     </row>
     <row r="163" spans="1:9" ht="12" customHeight="1">
@@ -20334,14 +20334,14 @@
       <c r="B163" s="21">
         <v>120</v>
       </c>
-      <c r="C163" s="394" t="s">
+      <c r="C163" s="395" t="s">
         <v>143</v>
       </c>
-      <c r="D163" s="395"/>
-      <c r="E163" s="395"/>
-      <c r="F163" s="395"/>
-      <c r="G163" s="395"/>
-      <c r="H163" s="396"/>
+      <c r="D163" s="396"/>
+      <c r="E163" s="396"/>
+      <c r="F163" s="396"/>
+      <c r="G163" s="396"/>
+      <c r="H163" s="397"/>
       <c r="I163" s="32"/>
     </row>
     <row r="164" spans="1:9" ht="12" customHeight="1">
@@ -20351,14 +20351,14 @@
       <c r="B164" s="21">
         <v>121</v>
       </c>
-      <c r="C164" s="394" t="s">
+      <c r="C164" s="395" t="s">
         <v>144</v>
       </c>
-      <c r="D164" s="395"/>
-      <c r="E164" s="395"/>
-      <c r="F164" s="395"/>
-      <c r="G164" s="395"/>
-      <c r="H164" s="396"/>
+      <c r="D164" s="396"/>
+      <c r="E164" s="396"/>
+      <c r="F164" s="396"/>
+      <c r="G164" s="396"/>
+      <c r="H164" s="397"/>
       <c r="I164" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20371,16 +20371,16 @@
       <c r="B165" s="21">
         <v>122</v>
       </c>
-      <c r="C165" s="420" t="s">
+      <c r="C165" s="398" t="s">
         <v>145</v>
       </c>
-      <c r="D165" s="421"/>
-      <c r="E165" s="394" t="s">
+      <c r="D165" s="399"/>
+      <c r="E165" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F165" s="395"/>
-      <c r="G165" s="395"/>
-      <c r="H165" s="396"/>
+      <c r="F165" s="396"/>
+      <c r="G165" s="396"/>
+      <c r="H165" s="397"/>
       <c r="I165" s="32"/>
     </row>
     <row r="166" spans="1:9" ht="12" customHeight="1">
@@ -20390,16 +20390,16 @@
       <c r="B166" s="21">
         <v>123</v>
       </c>
-      <c r="C166" s="422"/>
-      <c r="D166" s="423"/>
+      <c r="C166" s="400"/>
+      <c r="D166" s="401"/>
       <c r="E166" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F166" s="397" t="s">
+      <c r="F166" s="402" t="s">
         <v>146</v>
       </c>
-      <c r="G166" s="398"/>
-      <c r="H166" s="399"/>
+      <c r="G166" s="403"/>
+      <c r="H166" s="404"/>
       <c r="I166" s="32"/>
     </row>
     <row r="167" spans="1:9" ht="12" customHeight="1">
@@ -20418,11 +20418,11 @@
       <c r="E167" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F167" s="397" t="s">
+      <c r="F167" s="402" t="s">
         <v>147</v>
       </c>
-      <c r="G167" s="398"/>
-      <c r="H167" s="399"/>
+      <c r="G167" s="403"/>
+      <c r="H167" s="404"/>
       <c r="I167" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20444,11 +20444,11 @@
       <c r="E168" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F168" s="397" t="s">
+      <c r="F168" s="402" t="s">
         <v>148</v>
       </c>
-      <c r="G168" s="398"/>
-      <c r="H168" s="399"/>
+      <c r="G168" s="403"/>
+      <c r="H168" s="404"/>
       <c r="I168" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20464,14 +20464,14 @@
       <c r="B170" s="21">
         <v>127</v>
       </c>
-      <c r="C170" s="394" t="s">
+      <c r="C170" s="395" t="s">
         <v>17</v>
       </c>
-      <c r="D170" s="395"/>
-      <c r="E170" s="395"/>
-      <c r="F170" s="395"/>
-      <c r="G170" s="395"/>
-      <c r="H170" s="396"/>
+      <c r="D170" s="396"/>
+      <c r="E170" s="396"/>
+      <c r="F170" s="396"/>
+      <c r="G170" s="396"/>
+      <c r="H170" s="397"/>
       <c r="I170" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20484,14 +20484,14 @@
       <c r="B171" s="21">
         <v>128</v>
       </c>
-      <c r="C171" s="394" t="s">
+      <c r="C171" s="395" t="s">
         <v>149</v>
       </c>
-      <c r="D171" s="395"/>
-      <c r="E171" s="395"/>
-      <c r="F171" s="395"/>
-      <c r="G171" s="395"/>
-      <c r="H171" s="396"/>
+      <c r="D171" s="396"/>
+      <c r="E171" s="396"/>
+      <c r="F171" s="396"/>
+      <c r="G171" s="396"/>
+      <c r="H171" s="397"/>
       <c r="I171" s="32"/>
     </row>
     <row r="172" spans="1:9" ht="12" customHeight="1">
@@ -20501,14 +20501,14 @@
       <c r="B172" s="21">
         <v>129</v>
       </c>
-      <c r="C172" s="394" t="s">
+      <c r="C172" s="395" t="s">
         <v>150</v>
       </c>
-      <c r="D172" s="395"/>
-      <c r="E172" s="395"/>
-      <c r="F172" s="395"/>
-      <c r="G172" s="395"/>
-      <c r="H172" s="396"/>
+      <c r="D172" s="396"/>
+      <c r="E172" s="396"/>
+      <c r="F172" s="396"/>
+      <c r="G172" s="396"/>
+      <c r="H172" s="397"/>
       <c r="I172" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20521,14 +20521,14 @@
       <c r="B173" s="21">
         <v>130</v>
       </c>
-      <c r="C173" s="394" t="s">
+      <c r="C173" s="395" t="s">
         <v>151</v>
       </c>
-      <c r="D173" s="395"/>
-      <c r="E173" s="395"/>
-      <c r="F173" s="395"/>
-      <c r="G173" s="395"/>
-      <c r="H173" s="396"/>
+      <c r="D173" s="396"/>
+      <c r="E173" s="396"/>
+      <c r="F173" s="396"/>
+      <c r="G173" s="396"/>
+      <c r="H173" s="397"/>
       <c r="I173" s="32"/>
     </row>
     <row r="174" spans="1:9" ht="12" customHeight="1">
@@ -20538,14 +20538,14 @@
       <c r="B174" s="21">
         <v>131</v>
       </c>
-      <c r="C174" s="394" t="s">
+      <c r="C174" s="395" t="s">
         <v>152</v>
       </c>
-      <c r="D174" s="395"/>
-      <c r="E174" s="395"/>
-      <c r="F174" s="395"/>
-      <c r="G174" s="395"/>
-      <c r="H174" s="396"/>
+      <c r="D174" s="396"/>
+      <c r="E174" s="396"/>
+      <c r="F174" s="396"/>
+      <c r="G174" s="396"/>
+      <c r="H174" s="397"/>
       <c r="I174" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20558,16 +20558,16 @@
       <c r="B175" s="21">
         <v>132</v>
       </c>
-      <c r="C175" s="420" t="s">
+      <c r="C175" s="398" t="s">
         <v>153</v>
       </c>
-      <c r="D175" s="421"/>
-      <c r="E175" s="394" t="s">
+      <c r="D175" s="399"/>
+      <c r="E175" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F175" s="395"/>
-      <c r="G175" s="395"/>
-      <c r="H175" s="396"/>
+      <c r="F175" s="396"/>
+      <c r="G175" s="396"/>
+      <c r="H175" s="397"/>
       <c r="I175" s="32"/>
     </row>
     <row r="176" spans="1:9" ht="12" customHeight="1">
@@ -20577,16 +20577,16 @@
       <c r="B176" s="21">
         <v>133</v>
       </c>
-      <c r="C176" s="422"/>
-      <c r="D176" s="423"/>
+      <c r="C176" s="400"/>
+      <c r="D176" s="401"/>
       <c r="E176" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F176" s="397" t="s">
+      <c r="F176" s="402" t="s">
         <v>128</v>
       </c>
-      <c r="G176" s="398"/>
-      <c r="H176" s="399"/>
+      <c r="G176" s="403"/>
+      <c r="H176" s="404"/>
       <c r="I176" s="32"/>
     </row>
     <row r="177" spans="1:14" ht="12" customHeight="1">
@@ -20596,16 +20596,16 @@
       <c r="B177" s="21">
         <v>134</v>
       </c>
-      <c r="C177" s="422"/>
-      <c r="D177" s="423"/>
+      <c r="C177" s="400"/>
+      <c r="D177" s="401"/>
       <c r="E177" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F177" s="397" t="s">
+      <c r="F177" s="402" t="s">
         <v>154</v>
       </c>
-      <c r="G177" s="398"/>
-      <c r="H177" s="399"/>
+      <c r="G177" s="403"/>
+      <c r="H177" s="404"/>
       <c r="I177" s="32"/>
     </row>
     <row r="178" spans="1:14" ht="12" customHeight="1">
@@ -20624,11 +20624,11 @@
       <c r="E178" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F178" s="397" t="s">
+      <c r="F178" s="402" t="s">
         <v>155</v>
       </c>
-      <c r="G178" s="398"/>
-      <c r="H178" s="399"/>
+      <c r="G178" s="403"/>
+      <c r="H178" s="404"/>
       <c r="I178" s="32"/>
     </row>
     <row r="179" spans="1:14" hidden="1">
@@ -20641,14 +20641,14 @@
       <c r="B180" s="21">
         <v>137</v>
       </c>
-      <c r="C180" s="394" t="s">
+      <c r="C180" s="395" t="s">
         <v>156</v>
       </c>
-      <c r="D180" s="395"/>
-      <c r="E180" s="395"/>
-      <c r="F180" s="395"/>
-      <c r="G180" s="395"/>
-      <c r="H180" s="396"/>
+      <c r="D180" s="396"/>
+      <c r="E180" s="396"/>
+      <c r="F180" s="396"/>
+      <c r="G180" s="396"/>
+      <c r="H180" s="397"/>
       <c r="I180" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20661,14 +20661,14 @@
       <c r="B181" s="21">
         <v>138</v>
       </c>
-      <c r="C181" s="394" t="s">
+      <c r="C181" s="395" t="s">
         <v>21</v>
       </c>
-      <c r="D181" s="395"/>
-      <c r="E181" s="395"/>
-      <c r="F181" s="395"/>
-      <c r="G181" s="395"/>
-      <c r="H181" s="396"/>
+      <c r="D181" s="396"/>
+      <c r="E181" s="396"/>
+      <c r="F181" s="396"/>
+      <c r="G181" s="396"/>
+      <c r="H181" s="397"/>
       <c r="I181" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20681,16 +20681,16 @@
       <c r="B182" s="21">
         <v>139</v>
       </c>
-      <c r="C182" s="420" t="s">
+      <c r="C182" s="398" t="s">
         <v>157</v>
       </c>
-      <c r="D182" s="421"/>
-      <c r="E182" s="394" t="s">
+      <c r="D182" s="399"/>
+      <c r="E182" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F182" s="395"/>
-      <c r="G182" s="395"/>
-      <c r="H182" s="396"/>
+      <c r="F182" s="396"/>
+      <c r="G182" s="396"/>
+      <c r="H182" s="397"/>
       <c r="I182" s="32"/>
     </row>
     <row r="183" spans="1:14" ht="12" customHeight="1">
@@ -20700,16 +20700,16 @@
       <c r="B183" s="21">
         <v>140</v>
       </c>
-      <c r="C183" s="422"/>
-      <c r="D183" s="423"/>
+      <c r="C183" s="400"/>
+      <c r="D183" s="401"/>
       <c r="E183" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F183" s="397" t="s">
-        <v>44</v>
-      </c>
-      <c r="G183" s="398"/>
-      <c r="H183" s="399"/>
+      <c r="F183" s="402" t="s">
+        <v>44</v>
+      </c>
+      <c r="G183" s="403"/>
+      <c r="H183" s="404"/>
       <c r="I183" s="32"/>
     </row>
     <row r="184" spans="1:14" hidden="1">
@@ -20722,16 +20722,16 @@
       <c r="B185" s="21">
         <v>142</v>
       </c>
-      <c r="C185" s="420" t="s">
+      <c r="C185" s="398" t="s">
         <v>158</v>
       </c>
-      <c r="D185" s="421"/>
-      <c r="E185" s="394" t="s">
+      <c r="D185" s="399"/>
+      <c r="E185" s="395" t="s">
         <v>5</v>
       </c>
-      <c r="F185" s="395"/>
-      <c r="G185" s="395"/>
-      <c r="H185" s="396"/>
+      <c r="F185" s="396"/>
+      <c r="G185" s="396"/>
+      <c r="H185" s="397"/>
       <c r="I185" s="32"/>
     </row>
     <row r="186" spans="1:14" ht="12" customHeight="1">
@@ -20741,16 +20741,16 @@
       <c r="B186" s="21">
         <v>143</v>
       </c>
-      <c r="C186" s="422"/>
-      <c r="D186" s="423"/>
+      <c r="C186" s="400"/>
+      <c r="D186" s="401"/>
       <c r="E186" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F186" s="397" t="s">
+      <c r="F186" s="402" t="s">
         <v>159</v>
       </c>
-      <c r="G186" s="398"/>
-      <c r="H186" s="399"/>
+      <c r="G186" s="403"/>
+      <c r="H186" s="404"/>
       <c r="I186" s="32"/>
     </row>
     <row r="187" spans="1:14" ht="12" customHeight="1">
@@ -20760,16 +20760,16 @@
       <c r="B187" s="21">
         <v>144</v>
       </c>
-      <c r="C187" s="422"/>
-      <c r="D187" s="423"/>
+      <c r="C187" s="400"/>
+      <c r="D187" s="401"/>
       <c r="E187" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F187" s="397" t="s">
+      <c r="F187" s="402" t="s">
         <v>160</v>
       </c>
-      <c r="G187" s="398"/>
-      <c r="H187" s="399"/>
+      <c r="G187" s="403"/>
+      <c r="H187" s="404"/>
       <c r="I187" s="32"/>
     </row>
     <row r="188" spans="1:14" ht="12" customHeight="1">
@@ -20788,11 +20788,11 @@
       <c r="E188" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F188" s="417" t="s">
+      <c r="F188" s="392" t="s">
         <v>161</v>
       </c>
-      <c r="G188" s="418"/>
-      <c r="H188" s="419"/>
+      <c r="G188" s="393"/>
+      <c r="H188" s="394"/>
       <c r="I188" s="32"/>
       <c r="J188" s="10"/>
     </row>
@@ -20812,11 +20812,11 @@
       <c r="E189" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F189" s="417" t="s">
+      <c r="F189" s="392" t="s">
         <v>162</v>
       </c>
-      <c r="G189" s="418"/>
-      <c r="H189" s="419"/>
+      <c r="G189" s="393"/>
+      <c r="H189" s="394"/>
       <c r="I189" s="32"/>
       <c r="J189" s="10"/>
     </row>
@@ -20836,11 +20836,11 @@
       <c r="E190" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="F190" s="417" t="s">
+      <c r="F190" s="392" t="s">
         <v>163</v>
       </c>
-      <c r="G190" s="418"/>
-      <c r="H190" s="419"/>
+      <c r="G190" s="393"/>
+      <c r="H190" s="394"/>
       <c r="I190" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -20903,104 +20903,63 @@
     </row>
   </sheetData>
   <mergeCells count="169">
-    <mergeCell ref="F188:H188"/>
-    <mergeCell ref="F189:H189"/>
-    <mergeCell ref="F190:H190"/>
-    <mergeCell ref="C180:H180"/>
-    <mergeCell ref="C181:H181"/>
-    <mergeCell ref="C182:D183"/>
-    <mergeCell ref="E182:H182"/>
-    <mergeCell ref="F183:H183"/>
-    <mergeCell ref="C185:D187"/>
-    <mergeCell ref="E185:H185"/>
-    <mergeCell ref="F186:H186"/>
-    <mergeCell ref="F187:H187"/>
-    <mergeCell ref="C174:H174"/>
-    <mergeCell ref="C175:D177"/>
-    <mergeCell ref="E175:H175"/>
-    <mergeCell ref="F176:H176"/>
-    <mergeCell ref="F177:H177"/>
-    <mergeCell ref="F178:H178"/>
-    <mergeCell ref="F167:H167"/>
-    <mergeCell ref="F168:H168"/>
-    <mergeCell ref="C170:H170"/>
-    <mergeCell ref="C171:H171"/>
-    <mergeCell ref="C172:H172"/>
-    <mergeCell ref="C173:H173"/>
-    <mergeCell ref="C162:H162"/>
-    <mergeCell ref="C163:H163"/>
-    <mergeCell ref="C164:H164"/>
-    <mergeCell ref="C165:D166"/>
-    <mergeCell ref="E165:H165"/>
-    <mergeCell ref="F166:H166"/>
-    <mergeCell ref="F155:H155"/>
-    <mergeCell ref="F156:H156"/>
-    <mergeCell ref="F157:H157"/>
-    <mergeCell ref="F158:H158"/>
-    <mergeCell ref="C160:H160"/>
-    <mergeCell ref="C161:H161"/>
-    <mergeCell ref="F149:H149"/>
-    <mergeCell ref="F150:H150"/>
-    <mergeCell ref="F151:H151"/>
-    <mergeCell ref="C153:D154"/>
-    <mergeCell ref="E153:H153"/>
-    <mergeCell ref="F154:H154"/>
-    <mergeCell ref="C143:H143"/>
-    <mergeCell ref="E144:H144"/>
-    <mergeCell ref="F145:H145"/>
-    <mergeCell ref="F146:H146"/>
-    <mergeCell ref="F147:H147"/>
-    <mergeCell ref="F148:H148"/>
-    <mergeCell ref="F137:H137"/>
-    <mergeCell ref="F138:H138"/>
-    <mergeCell ref="C140:D142"/>
-    <mergeCell ref="E140:H140"/>
-    <mergeCell ref="E141:E142"/>
-    <mergeCell ref="F141:H141"/>
-    <mergeCell ref="F142:H142"/>
-    <mergeCell ref="C132:D135"/>
-    <mergeCell ref="E132:H132"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="F134:H134"/>
-    <mergeCell ref="F135:H135"/>
-    <mergeCell ref="F136:H136"/>
-    <mergeCell ref="C126:H126"/>
-    <mergeCell ref="C127:D128"/>
-    <mergeCell ref="E127:H127"/>
-    <mergeCell ref="F128:H128"/>
-    <mergeCell ref="C130:H130"/>
-    <mergeCell ref="C131:H131"/>
-    <mergeCell ref="C120:D121"/>
-    <mergeCell ref="E120:H120"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="F122:H122"/>
-    <mergeCell ref="F123:H123"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="C115:H115"/>
-    <mergeCell ref="C116:D117"/>
-    <mergeCell ref="E116:H116"/>
-    <mergeCell ref="F117:H117"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="F110:H110"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="E112:H112"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="C104:H104"/>
-    <mergeCell ref="C105:H105"/>
-    <mergeCell ref="C106:D107"/>
-    <mergeCell ref="E106:H106"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="F97:H97"/>
-    <mergeCell ref="F98:H98"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:H22"/>
+    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:D35"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:D39"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="C44:H44"/>
+    <mergeCell ref="C45:D49"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="C54:D57"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="F58:H58"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="C50:D51"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="C78:D79"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="F80:H80"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="C60:H60"/>
+    <mergeCell ref="C61:D63"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="G70:H70"/>
     <mergeCell ref="F88:H88"/>
     <mergeCell ref="F89:H89"/>
     <mergeCell ref="F90:H90"/>
@@ -21015,63 +20974,104 @@
     <mergeCell ref="F85:H85"/>
     <mergeCell ref="F86:H86"/>
     <mergeCell ref="F87:H87"/>
-    <mergeCell ref="G74:H74"/>
-    <mergeCell ref="C78:D79"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="F80:H80"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="C60:H60"/>
-    <mergeCell ref="C61:D63"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="C54:D57"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="F58:H58"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="C50:D51"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="C44:H44"/>
-    <mergeCell ref="C45:D49"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:D35"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C37:D39"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C20:H22"/>
-    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="C104:H104"/>
+    <mergeCell ref="C105:H105"/>
+    <mergeCell ref="C106:D107"/>
+    <mergeCell ref="E106:H106"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="F97:H97"/>
+    <mergeCell ref="F98:H98"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="C115:H115"/>
+    <mergeCell ref="C116:D117"/>
+    <mergeCell ref="E116:H116"/>
+    <mergeCell ref="F117:H117"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="F110:H110"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="E112:H112"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="C127:D128"/>
+    <mergeCell ref="E127:H127"/>
+    <mergeCell ref="F128:H128"/>
+    <mergeCell ref="C130:H130"/>
+    <mergeCell ref="C131:H131"/>
+    <mergeCell ref="C120:D121"/>
+    <mergeCell ref="E120:H120"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="F122:H122"/>
+    <mergeCell ref="F123:H123"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="F137:H137"/>
+    <mergeCell ref="F138:H138"/>
+    <mergeCell ref="C140:D142"/>
+    <mergeCell ref="E140:H140"/>
+    <mergeCell ref="E141:E142"/>
+    <mergeCell ref="F141:H141"/>
+    <mergeCell ref="F142:H142"/>
+    <mergeCell ref="C132:D135"/>
+    <mergeCell ref="E132:H132"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="F134:H134"/>
+    <mergeCell ref="F135:H135"/>
+    <mergeCell ref="F136:H136"/>
+    <mergeCell ref="F149:H149"/>
+    <mergeCell ref="F150:H150"/>
+    <mergeCell ref="F151:H151"/>
+    <mergeCell ref="C153:D154"/>
+    <mergeCell ref="E153:H153"/>
+    <mergeCell ref="F154:H154"/>
+    <mergeCell ref="C143:H143"/>
+    <mergeCell ref="E144:H144"/>
+    <mergeCell ref="F145:H145"/>
+    <mergeCell ref="F146:H146"/>
+    <mergeCell ref="F147:H147"/>
+    <mergeCell ref="F148:H148"/>
+    <mergeCell ref="C162:H162"/>
+    <mergeCell ref="C163:H163"/>
+    <mergeCell ref="C164:H164"/>
+    <mergeCell ref="C165:D166"/>
+    <mergeCell ref="E165:H165"/>
+    <mergeCell ref="F166:H166"/>
+    <mergeCell ref="F155:H155"/>
+    <mergeCell ref="F156:H156"/>
+    <mergeCell ref="F157:H157"/>
+    <mergeCell ref="F158:H158"/>
+    <mergeCell ref="C160:H160"/>
+    <mergeCell ref="C161:H161"/>
+    <mergeCell ref="C174:H174"/>
+    <mergeCell ref="C175:D177"/>
+    <mergeCell ref="E175:H175"/>
+    <mergeCell ref="F176:H176"/>
+    <mergeCell ref="F177:H177"/>
+    <mergeCell ref="F178:H178"/>
+    <mergeCell ref="F167:H167"/>
+    <mergeCell ref="F168:H168"/>
+    <mergeCell ref="C170:H170"/>
+    <mergeCell ref="C171:H171"/>
+    <mergeCell ref="C172:H172"/>
+    <mergeCell ref="C173:H173"/>
+    <mergeCell ref="F188:H188"/>
+    <mergeCell ref="F189:H189"/>
+    <mergeCell ref="F190:H190"/>
+    <mergeCell ref="C180:H180"/>
+    <mergeCell ref="C181:H181"/>
+    <mergeCell ref="C182:D183"/>
+    <mergeCell ref="E182:H182"/>
+    <mergeCell ref="F183:H183"/>
+    <mergeCell ref="C185:D187"/>
+    <mergeCell ref="E185:H185"/>
+    <mergeCell ref="F186:H186"/>
+    <mergeCell ref="F187:H187"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
@@ -21554,15 +21554,15 @@
       </c>
       <c r="E18" s="221">
         <f>SUM(E19:E22)</f>
-        <v>3400000</v>
+        <v>3030000</v>
       </c>
       <c r="F18" s="222">
         <f>SUM(F19:F22)</f>
-        <v>2744700</v>
+        <v>2451660</v>
       </c>
       <c r="G18" s="181">
         <f>SUM(G19:G22)</f>
-        <v>40800</v>
+        <v>36360</v>
       </c>
       <c r="H18" s="181"/>
       <c r="I18" s="181"/>
@@ -21603,70 +21603,70 @@
       </c>
     </row>
     <row r="20" spans="1:10" s="214" customFormat="1" ht="30">
-      <c r="A20" s="243">
+      <c r="A20" s="213">
         <v>2</v>
       </c>
-      <c r="B20" s="244" t="s">
+      <c r="B20" s="210" t="s">
         <v>438</v>
       </c>
-      <c r="C20" s="243" t="s">
+      <c r="C20" s="213" t="s">
         <v>272</v>
       </c>
-      <c r="D20" s="245">
+      <c r="D20" s="281">
         <v>1</v>
       </c>
-      <c r="E20" s="246">
-        <v>800000</v>
-      </c>
-      <c r="F20" s="247">
+      <c r="E20" s="282">
+        <v>615000</v>
+      </c>
+      <c r="F20" s="283">
         <f>IF(E20&gt;0,E20-MIN(E20,4250000)*10%-MIN(E20,1700000)*2%-MAX(0,E20-MIN(E20,4250000)*10%-MIN(E20,1700000)*2%-129750)*10%,0)</f>
-        <v>646575</v>
-      </c>
-      <c r="G20" s="245">
+        <v>500055</v>
+      </c>
+      <c r="G20" s="281">
         <f>D20*E20*12/1000</f>
-        <v>9600</v>
-      </c>
-      <c r="H20" s="245" t="s">
+        <v>7380</v>
+      </c>
+      <c r="H20" s="281" t="s">
         <v>308</v>
       </c>
-      <c r="I20" s="266" t="s">
-        <v>321</v>
-      </c>
-      <c r="J20" s="271" t="s">
+      <c r="I20" s="284" t="s">
+        <v>312</v>
+      </c>
+      <c r="J20" s="285" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="214" customFormat="1" ht="30">
-      <c r="A21" s="243">
+      <c r="A21" s="213">
         <v>3</v>
       </c>
-      <c r="B21" s="244" t="s">
+      <c r="B21" s="210" t="s">
         <v>454</v>
       </c>
-      <c r="C21" s="243" t="s">
+      <c r="C21" s="213" t="s">
         <v>272</v>
       </c>
-      <c r="D21" s="245">
+      <c r="D21" s="281">
         <v>1</v>
       </c>
-      <c r="E21" s="246">
-        <v>800000</v>
-      </c>
-      <c r="F21" s="247">
+      <c r="E21" s="282">
+        <v>615000</v>
+      </c>
+      <c r="F21" s="283">
         <f>IF(E21&gt;0,E21-MIN(E21,4250000)*10%-MIN(E21,1700000)*2%-MAX(0,E21-MIN(E21,4250000)*10%-MIN(E21,1700000)*2%-129750)*10%,0)</f>
-        <v>646575</v>
-      </c>
-      <c r="G21" s="245">
+        <v>500055</v>
+      </c>
+      <c r="G21" s="281">
         <f>D21*E21*12/1000</f>
-        <v>9600</v>
-      </c>
-      <c r="H21" s="245" t="s">
+        <v>7380</v>
+      </c>
+      <c r="H21" s="281" t="s">
         <v>308</v>
       </c>
-      <c r="I21" s="266" t="s">
-        <v>321</v>
-      </c>
-      <c r="J21" s="271" t="s">
+      <c r="I21" s="284" t="s">
+        <v>312</v>
+      </c>
+      <c r="J21" s="285" t="s">
         <v>455</v>
       </c>
     </row>
@@ -22590,15 +22590,15 @@
       </c>
       <c r="E51" s="233">
         <f>E6+E10+E12+E18+E23+E34+E37+E46</f>
-        <v>31793100</v>
+        <v>31423100</v>
       </c>
       <c r="F51" s="235">
         <f>F6+F10+F12+F18+F23+F34+F37+F46</f>
-        <v>25595335.199999999</v>
+        <v>25302295.199999999</v>
       </c>
       <c r="G51" s="234">
         <f>G6+G10+G12+G18+G23+G34+G37+G46</f>
-        <v>366000</v>
+        <v>361560</v>
       </c>
       <c r="H51" s="234"/>
       <c r="I51" s="234"/>
@@ -30112,12 +30112,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="A26:F26"/>
@@ -30125,6 +30119,12 @@
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>

--- a/TAZA/_документы/Штатка Фонда и проектного офиса.xlsx
+++ b/TAZA/_документы/Штатка Фонда и проектного офиса.xlsx
@@ -2159,9 +2159,6 @@
     <t>12.2026</t>
   </si>
   <si>
-    <t>*приход с 12.2026 и в 2027 году выделен сиреневым (с 12.2026 – Арманов, Мирам; остальные – с 02.2027)</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Заместитель Главного исполнительного директора Фонда / </t>
     </r>
@@ -2431,6 +2428,9 @@
   </si>
   <si>
     <t>Менеджер проектов – эколог (отходы, вода, воздух) / вакансия</t>
+  </si>
+  <si>
+    <t>*приход с 12.2026 и в 2027 году выделен сиреневым (с 12.2026 – Өміртай А.; остальные – с 02.2027)</t>
   </si>
 </sst>
 </file>
@@ -4739,7 +4739,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="451">
+  <cellXfs count="450">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -5537,9 +5537,6 @@
     <xf numFmtId="0" fontId="4" fillId="71" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="71" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="4" fillId="71" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5582,6 +5579,42 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5594,48 +5627,90 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="34" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5645,18 +5720,69 @@
     <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="33" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="34" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="35" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="32" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="39" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="3" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="10" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="2" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="17" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="32" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5666,139 +5792,19 @@
     <xf numFmtId="0" fontId="46" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="32" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="10" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="2" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="17" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="39" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="3" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="33" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="34" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="35" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="34" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5813,43 +5819,145 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="2" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="2" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="2" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="2" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5858,24 +5966,6 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5926,99 +6016,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6360,7 +6357,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6418,7 +6415,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6473,7 +6470,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10250,56 +10247,56 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="310" t="s">
+      <c r="A2" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="310"/>
+      <c r="B2" s="301"/>
       <c r="C2" s="132" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="315" t="s">
+      <c r="A3" s="302" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="316"/>
+      <c r="B3" s="303"/>
       <c r="C3" s="133"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="315" t="s">
+      <c r="A4" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="316" t="s">
+      <c r="B4" s="303" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="133"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="301" t="s">
+      <c r="A5" s="300" t="s">
         <v>242</v>
       </c>
-      <c r="B5" s="301"/>
+      <c r="B5" s="300"/>
       <c r="C5" s="133"/>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
-      <c r="A6" s="315" t="s">
+      <c r="A6" s="302" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="316"/>
+      <c r="B6" s="303"/>
       <c r="C6" s="134"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
-      <c r="A7" s="315" t="s">
+      <c r="A7" s="302" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="316"/>
+      <c r="B7" s="303"/>
       <c r="C7" s="135"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="306" t="s">
+      <c r="A8" s="304" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="307"/>
+      <c r="B8" s="305"/>
       <c r="C8" s="131">
         <f>SUM(C3:C7)</f>
         <v>0</v>
@@ -10309,47 +10306,47 @@
       <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="317" t="s">
+      <c r="A10" s="306" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="317"/>
-      <c r="C10" s="317"/>
+      <c r="B10" s="306"/>
+      <c r="C10" s="306"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="310" t="s">
+      <c r="A11" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="310"/>
+      <c r="B11" s="301"/>
       <c r="C11" s="132" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="301" t="s">
+      <c r="A12" s="300" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="301"/>
+      <c r="B12" s="300"/>
       <c r="C12" s="136"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="301" t="s">
+      <c r="A13" s="300" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="301"/>
+      <c r="B13" s="300"/>
       <c r="C13" s="136"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="301" t="s">
+      <c r="A14" s="300" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="301"/>
+      <c r="B14" s="300"/>
       <c r="C14" s="136"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="306" t="s">
+      <c r="A15" s="304" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="307"/>
+      <c r="B15" s="305"/>
       <c r="C15" s="130">
         <f>SUM(C12:C14)</f>
         <v>0</v>
@@ -10360,10 +10357,10 @@
       <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="308" t="s">
+      <c r="A17" s="307" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="309"/>
+      <c r="B17" s="308"/>
       <c r="C17" s="137">
         <f>C8-C15</f>
         <v>0</v>
@@ -10379,42 +10376,42 @@
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="310" t="s">
+      <c r="A20" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="310"/>
+      <c r="B20" s="301"/>
       <c r="C20" s="132" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="301" t="s">
+      <c r="A21" s="300" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="301"/>
+      <c r="B21" s="300"/>
       <c r="C21" s="138"/>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="301" t="s">
+      <c r="A22" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="301" t="s">
+      <c r="B22" s="300" t="s">
         <v>27</v>
       </c>
       <c r="C22" s="138"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="301" t="s">
+      <c r="A23" s="300" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="301"/>
+      <c r="B23" s="300"/>
       <c r="C23" s="138"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="301" t="s">
+      <c r="A24" s="300" t="s">
         <v>243</v>
       </c>
-      <c r="B24" s="301"/>
+      <c r="B24" s="300"/>
       <c r="C24" s="138"/>
       <c r="D24" s="4"/>
     </row>
@@ -10427,17 +10424,17 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="311" t="s">
+      <c r="A26" s="309" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="312"/>
-      <c r="C26" s="313"/>
+      <c r="B26" s="310"/>
+      <c r="C26" s="311"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="310" t="s">
+      <c r="A27" s="301" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="310"/>
+      <c r="B27" s="301"/>
       <c r="C27" s="138"/>
     </row>
     <row r="28" spans="1:4">
@@ -10454,55 +10451,55 @@
       <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="314" t="s">
+      <c r="A30" s="312" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="314"/>
+      <c r="B30" s="312"/>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="310" t="s">
+      <c r="A31" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="310"/>
+      <c r="B31" s="301"/>
       <c r="C31" s="132" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="301" t="s">
+      <c r="A32" s="300" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="301"/>
+      <c r="B32" s="300"/>
       <c r="C32" s="143"/>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="301" t="s">
+      <c r="A33" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="301" t="s">
+      <c r="B33" s="300" t="s">
         <v>27</v>
       </c>
       <c r="C33" s="143"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="301" t="s">
+      <c r="A34" s="300" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="301"/>
+      <c r="B34" s="300"/>
       <c r="C34" s="143"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="301" t="s">
+      <c r="A35" s="300" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="301"/>
+      <c r="B35" s="300"/>
       <c r="C35" s="143"/>
       <c r="D35" s="3"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="302"/>
-      <c r="B36" s="303"/>
+      <c r="A36" s="313"/>
+      <c r="B36" s="314"/>
       <c r="C36" s="144">
         <f>SUM(C32:C35)</f>
         <v>0</v>
@@ -10514,10 +10511,10 @@
       <c r="C37" s="8"/>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="304" t="s">
+      <c r="A38" s="315" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="305"/>
+      <c r="B38" s="316"/>
       <c r="C38" s="145">
         <f>C28-C36</f>
         <v>0</v>
@@ -10540,6 +10537,23 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
@@ -10552,23 +10566,6 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10589,38 +10586,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:7" ht="33" customHeight="1">
-      <c r="A3" s="318" t="s">
+      <c r="A3" s="317" t="s">
         <v>244</v>
       </c>
-      <c r="B3" s="318" t="s">
+      <c r="B3" s="317" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="318" t="s">
+      <c r="C3" s="317" t="s">
         <v>246</v>
       </c>
-      <c r="D3" s="318" t="s">
+      <c r="D3" s="317" t="s">
         <v>247</v>
       </c>
-      <c r="E3" s="318" t="s">
+      <c r="E3" s="317" t="s">
         <v>245</v>
       </c>
-      <c r="F3" s="318"/>
-      <c r="G3" s="318" t="s">
+      <c r="F3" s="317"/>
+      <c r="G3" s="317" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="53.25" customHeight="1">
-      <c r="A4" s="318"/>
-      <c r="B4" s="318"/>
-      <c r="C4" s="318"/>
-      <c r="D4" s="318"/>
+      <c r="A4" s="317"/>
+      <c r="B4" s="317"/>
+      <c r="C4" s="317"/>
+      <c r="D4" s="317"/>
       <c r="E4" s="146" t="s">
         <v>248</v>
       </c>
       <c r="F4" s="146" t="s">
         <v>249</v>
       </c>
-      <c r="G4" s="318"/>
+      <c r="G4" s="317"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="132">
@@ -10736,11 +10733,11 @@
     </row>
     <row r="13" spans="1:7" ht="18">
       <c r="A13" s="1"/>
-      <c r="B13" s="319" t="s">
+      <c r="B13" s="318" t="s">
         <v>258</v>
       </c>
-      <c r="C13" s="319"/>
-      <c r="D13" s="319"/>
+      <c r="C13" s="318"/>
+      <c r="D13" s="318"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -10836,11 +10833,11 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1"/>
-      <c r="B19" s="310" t="s">
+      <c r="B19" s="301" t="s">
         <v>259</v>
       </c>
-      <c r="C19" s="310"/>
-      <c r="D19" s="310"/>
+      <c r="C19" s="301"/>
+      <c r="D19" s="301"/>
       <c r="E19" s="162" t="e">
         <f>E15/E18</f>
         <v>#REF!</v>
@@ -10917,17 +10914,17 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="358" t="s">
+      <c r="B1" s="319" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="358"/>
-      <c r="D1" s="358"/>
-      <c r="E1" s="358"/>
-      <c r="F1" s="358"/>
-      <c r="G1" s="358"/>
-      <c r="H1" s="358"/>
-      <c r="I1" s="358"/>
-      <c r="J1" s="358"/>
+      <c r="C1" s="319"/>
+      <c r="D1" s="319"/>
+      <c r="E1" s="319"/>
+      <c r="F1" s="319"/>
+      <c r="G1" s="319"/>
+      <c r="H1" s="319"/>
+      <c r="I1" s="319"/>
+      <c r="J1" s="319"/>
       <c r="K1" s="85"/>
       <c r="O1" s="51"/>
     </row>
@@ -10965,17 +10962,17 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="359" t="s">
+      <c r="B3" s="320" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
+      <c r="C3" s="320"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="320"/>
+      <c r="G3" s="320"/>
+      <c r="H3" s="320"/>
+      <c r="I3" s="320"/>
+      <c r="J3" s="320"/>
       <c r="K3" s="88"/>
       <c r="O3" s="51"/>
     </row>
@@ -10983,17 +10980,17 @@
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="360" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="360"/>
-      <c r="D4" s="360"/>
-      <c r="E4" s="360"/>
-      <c r="F4" s="360"/>
-      <c r="G4" s="360"/>
-      <c r="H4" s="360"/>
-      <c r="I4" s="360"/>
-      <c r="J4" s="360"/>
+      <c r="B4" s="321" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="321"/>
+      <c r="D4" s="321"/>
+      <c r="E4" s="321"/>
+      <c r="F4" s="321"/>
+      <c r="G4" s="321"/>
+      <c r="H4" s="321"/>
+      <c r="I4" s="321"/>
+      <c r="J4" s="321"/>
       <c r="K4" s="89"/>
       <c r="O4" s="51"/>
     </row>
@@ -11001,17 +10998,17 @@
       <c r="A5" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="361" t="s">
+      <c r="B5" s="322" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="361"/>
-      <c r="D5" s="361"/>
-      <c r="E5" s="361"/>
-      <c r="F5" s="361"/>
-      <c r="G5" s="361"/>
-      <c r="H5" s="361"/>
-      <c r="I5" s="361"/>
-      <c r="J5" s="361"/>
+      <c r="C5" s="322"/>
+      <c r="D5" s="322"/>
+      <c r="E5" s="322"/>
+      <c r="F5" s="322"/>
+      <c r="G5" s="322"/>
+      <c r="H5" s="322"/>
+      <c r="I5" s="322"/>
+      <c r="J5" s="322"/>
       <c r="K5" s="90"/>
       <c r="O5" s="51"/>
     </row>
@@ -11019,17 +11016,17 @@
       <c r="A6" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="361" t="s">
+      <c r="B6" s="322" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="361"/>
-      <c r="D6" s="361"/>
-      <c r="E6" s="361"/>
-      <c r="F6" s="361"/>
-      <c r="G6" s="361"/>
-      <c r="H6" s="361"/>
-      <c r="I6" s="361"/>
-      <c r="J6" s="361"/>
+      <c r="C6" s="322"/>
+      <c r="D6" s="322"/>
+      <c r="E6" s="322"/>
+      <c r="F6" s="322"/>
+      <c r="G6" s="322"/>
+      <c r="H6" s="322"/>
+      <c r="I6" s="322"/>
+      <c r="J6" s="322"/>
       <c r="K6" s="90"/>
       <c r="O6" s="51"/>
     </row>
@@ -11037,15 +11034,15 @@
       <c r="A7" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="362" t="s">
+      <c r="B7" s="323" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="362"/>
-      <c r="D7" s="362"/>
-      <c r="E7" s="362"/>
-      <c r="F7" s="362"/>
-      <c r="G7" s="362"/>
-      <c r="H7" s="362"/>
+      <c r="C7" s="323"/>
+      <c r="D7" s="323"/>
+      <c r="E7" s="323"/>
+      <c r="F7" s="323"/>
+      <c r="G7" s="323"/>
+      <c r="H7" s="323"/>
       <c r="I7" s="91"/>
       <c r="J7" s="71" t="s">
         <v>50</v>
@@ -11071,51 +11068,51 @@
       <c r="A22" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="363" t="s">
+      <c r="B22" s="324" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="366" t="s">
+      <c r="C22" s="327" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="367"/>
-      <c r="E22" s="367"/>
-      <c r="F22" s="367"/>
-      <c r="G22" s="368"/>
+      <c r="D22" s="328"/>
+      <c r="E22" s="328"/>
+      <c r="F22" s="328"/>
+      <c r="G22" s="329"/>
       <c r="H22" s="93"/>
-      <c r="I22" s="367" t="s">
+      <c r="I22" s="328" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="368"/>
+      <c r="J22" s="329"/>
       <c r="K22" s="94"/>
     </row>
     <row r="23" spans="1:16" ht="12" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="364"/>
-      <c r="C23" s="369"/>
-      <c r="D23" s="370"/>
-      <c r="E23" s="370"/>
-      <c r="F23" s="370"/>
-      <c r="G23" s="371"/>
+      <c r="B23" s="325"/>
+      <c r="C23" s="330"/>
+      <c r="D23" s="331"/>
+      <c r="E23" s="331"/>
+      <c r="F23" s="331"/>
+      <c r="G23" s="332"/>
       <c r="H23" s="95"/>
-      <c r="I23" s="370"/>
-      <c r="J23" s="371"/>
+      <c r="I23" s="331"/>
+      <c r="J23" s="332"/>
       <c r="K23" s="94"/>
     </row>
     <row r="24" spans="1:16" ht="24" customHeight="1">
       <c r="A24" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="365"/>
-      <c r="C24" s="372"/>
-      <c r="D24" s="373"/>
-      <c r="E24" s="373"/>
-      <c r="F24" s="373"/>
-      <c r="G24" s="374"/>
+      <c r="B24" s="326"/>
+      <c r="C24" s="333"/>
+      <c r="D24" s="334"/>
+      <c r="E24" s="334"/>
+      <c r="F24" s="334"/>
+      <c r="G24" s="335"/>
       <c r="H24" s="96"/>
-      <c r="I24" s="373"/>
-      <c r="J24" s="374"/>
+      <c r="I24" s="334"/>
+      <c r="J24" s="335"/>
       <c r="K24" s="94"/>
     </row>
     <row r="25" spans="1:16" ht="15.75" hidden="1" customHeight="1"/>
@@ -11157,13 +11154,13 @@
       <c r="B29" s="58">
         <v>1</v>
       </c>
-      <c r="C29" s="324" t="s">
+      <c r="C29" s="336" t="s">
         <v>202</v>
       </c>
-      <c r="D29" s="325"/>
-      <c r="E29" s="325"/>
-      <c r="F29" s="325"/>
-      <c r="G29" s="326"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
+      <c r="G29" s="338"/>
       <c r="H29" s="97"/>
       <c r="I29" s="97" t="e">
         <f>I35+I44+I46+I47+I50+#REF!+I68+I71+I72+I73+I77+I89+I97+I101+I106+I108+I116+I131+I142+I146+I147+I154+I32+I34+#REF!+#REF!+I151+#REF!+I98+I113+I155</f>
@@ -11180,15 +11177,15 @@
       <c r="B30" s="58">
         <v>2</v>
       </c>
-      <c r="C30" s="333" t="s">
+      <c r="C30" s="339" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="324" t="s">
+      <c r="D30" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="325"/>
-      <c r="F30" s="325"/>
-      <c r="G30" s="326"/>
+      <c r="E30" s="337"/>
+      <c r="F30" s="337"/>
+      <c r="G30" s="338"/>
       <c r="H30" s="97"/>
       <c r="I30" s="97"/>
       <c r="J30" s="99" t="e">
@@ -11208,15 +11205,15 @@
       <c r="B31" s="58">
         <v>3</v>
       </c>
-      <c r="C31" s="334"/>
-      <c r="D31" s="343" t="s">
+      <c r="C31" s="340"/>
+      <c r="D31" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="320" t="s">
+      <c r="E31" s="345" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="321"/>
-      <c r="G31" s="322"/>
+      <c r="F31" s="346"/>
+      <c r="G31" s="347"/>
       <c r="H31" s="72"/>
       <c r="I31" s="72"/>
       <c r="J31" s="100"/>
@@ -11233,13 +11230,13 @@
       <c r="B32" s="58">
         <v>4</v>
       </c>
-      <c r="C32" s="334"/>
-      <c r="D32" s="344"/>
-      <c r="E32" s="320" t="s">
+      <c r="C32" s="340"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="345" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="321"/>
-      <c r="G32" s="322"/>
+      <c r="F32" s="346"/>
+      <c r="G32" s="347"/>
       <c r="H32" s="72"/>
       <c r="I32" s="72"/>
       <c r="J32" s="81" t="e">
@@ -11259,13 +11256,13 @@
       <c r="B33" s="58">
         <v>5</v>
       </c>
-      <c r="C33" s="334"/>
-      <c r="D33" s="344"/>
-      <c r="E33" s="353" t="s">
+      <c r="C33" s="340"/>
+      <c r="D33" s="343"/>
+      <c r="E33" s="348" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="354"/>
-      <c r="G33" s="355"/>
+      <c r="F33" s="349"/>
+      <c r="G33" s="350"/>
       <c r="H33" s="72"/>
       <c r="I33" s="72"/>
       <c r="J33" s="81"/>
@@ -11278,13 +11275,13 @@
       <c r="B34" s="58">
         <v>6</v>
       </c>
-      <c r="C34" s="350"/>
-      <c r="D34" s="352"/>
-      <c r="E34" s="330" t="s">
+      <c r="C34" s="341"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="352" t="s">
         <v>170</v>
       </c>
-      <c r="F34" s="330"/>
-      <c r="G34" s="330"/>
+      <c r="F34" s="352"/>
+      <c r="G34" s="352"/>
       <c r="H34" s="72"/>
       <c r="I34" s="72"/>
       <c r="J34" s="81" t="e">
@@ -11300,15 +11297,15 @@
       <c r="B35" s="58">
         <v>7</v>
       </c>
-      <c r="C35" s="333" t="s">
+      <c r="C35" s="339" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="324" t="s">
+      <c r="D35" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E35" s="356"/>
-      <c r="F35" s="356"/>
-      <c r="G35" s="357"/>
+      <c r="E35" s="353"/>
+      <c r="F35" s="353"/>
+      <c r="G35" s="354"/>
       <c r="H35" s="97"/>
       <c r="I35" s="101">
         <f>I36+I37</f>
@@ -11324,15 +11321,15 @@
       <c r="B36" s="58">
         <v>8</v>
       </c>
-      <c r="C36" s="334"/>
-      <c r="D36" s="343" t="s">
+      <c r="C36" s="340"/>
+      <c r="D36" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="337" t="s">
+      <c r="E36" s="355" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="338"/>
-      <c r="G36" s="339"/>
+      <c r="F36" s="356"/>
+      <c r="G36" s="357"/>
       <c r="H36" s="72"/>
       <c r="I36" s="72"/>
       <c r="J36" s="81" t="e">
@@ -11349,13 +11346,13 @@
       <c r="B37" s="58">
         <v>9</v>
       </c>
-      <c r="C37" s="350"/>
+      <c r="C37" s="341"/>
       <c r="D37" s="351"/>
-      <c r="E37" s="337" t="s">
+      <c r="E37" s="355" t="s">
         <v>173</v>
       </c>
-      <c r="F37" s="338"/>
-      <c r="G37" s="339"/>
+      <c r="F37" s="356"/>
+      <c r="G37" s="357"/>
       <c r="H37" s="72"/>
       <c r="I37" s="72"/>
       <c r="J37" s="81" t="e">
@@ -11372,13 +11369,13 @@
       <c r="B38" s="58">
         <v>10</v>
       </c>
-      <c r="C38" s="324" t="s">
+      <c r="C38" s="336" t="s">
         <v>203</v>
       </c>
-      <c r="D38" s="325"/>
-      <c r="E38" s="325"/>
-      <c r="F38" s="325"/>
-      <c r="G38" s="326"/>
+      <c r="D38" s="337"/>
+      <c r="E38" s="337"/>
+      <c r="F38" s="337"/>
+      <c r="G38" s="338"/>
       <c r="H38" s="97"/>
       <c r="I38" s="97"/>
       <c r="J38" s="102"/>
@@ -11391,15 +11388,15 @@
       <c r="B39" s="58">
         <v>11</v>
       </c>
-      <c r="C39" s="333" t="s">
+      <c r="C39" s="339" t="s">
         <v>186</v>
       </c>
-      <c r="D39" s="324" t="s">
+      <c r="D39" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E39" s="325"/>
-      <c r="F39" s="325"/>
-      <c r="G39" s="326"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
+      <c r="G39" s="338"/>
       <c r="H39" s="97"/>
       <c r="I39" s="97"/>
       <c r="J39" s="102"/>
@@ -11412,15 +11409,15 @@
       <c r="B40" s="58">
         <v>12</v>
       </c>
-      <c r="C40" s="334"/>
-      <c r="D40" s="343" t="s">
+      <c r="C40" s="340"/>
+      <c r="D40" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E40" s="320" t="s">
+      <c r="E40" s="345" t="s">
         <v>128</v>
       </c>
-      <c r="F40" s="321"/>
-      <c r="G40" s="322"/>
+      <c r="F40" s="346"/>
+      <c r="G40" s="347"/>
       <c r="H40" s="72"/>
       <c r="I40" s="72"/>
       <c r="J40" s="81" t="e">
@@ -11436,13 +11433,13 @@
       <c r="B41" s="58">
         <v>13</v>
       </c>
-      <c r="C41" s="350"/>
+      <c r="C41" s="341"/>
       <c r="D41" s="351"/>
-      <c r="E41" s="320" t="s">
+      <c r="E41" s="345" t="s">
         <v>129</v>
       </c>
-      <c r="F41" s="321"/>
-      <c r="G41" s="322"/>
+      <c r="F41" s="346"/>
+      <c r="G41" s="347"/>
       <c r="H41" s="72"/>
       <c r="I41" s="72"/>
       <c r="J41" s="81" t="e">
@@ -11458,15 +11455,15 @@
       <c r="B42" s="58">
         <v>14</v>
       </c>
-      <c r="C42" s="333" t="s">
+      <c r="C42" s="339" t="s">
         <v>204</v>
       </c>
-      <c r="D42" s="324" t="s">
+      <c r="D42" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E42" s="325"/>
-      <c r="F42" s="325"/>
-      <c r="G42" s="326"/>
+      <c r="E42" s="337"/>
+      <c r="F42" s="337"/>
+      <c r="G42" s="338"/>
       <c r="H42" s="97"/>
       <c r="I42" s="97"/>
       <c r="J42" s="102"/>
@@ -11479,15 +11476,15 @@
       <c r="B43" s="58">
         <v>15</v>
       </c>
-      <c r="C43" s="334"/>
-      <c r="D43" s="343" t="s">
+      <c r="C43" s="340"/>
+      <c r="D43" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="320" t="s">
+      <c r="E43" s="345" t="s">
         <v>128</v>
       </c>
-      <c r="F43" s="321"/>
-      <c r="G43" s="322"/>
+      <c r="F43" s="346"/>
+      <c r="G43" s="347"/>
       <c r="H43" s="72"/>
       <c r="I43" s="72"/>
       <c r="J43" s="81" t="e">
@@ -11503,13 +11500,13 @@
       <c r="B44" s="58">
         <v>16</v>
       </c>
-      <c r="C44" s="350"/>
+      <c r="C44" s="341"/>
       <c r="D44" s="351"/>
-      <c r="E44" s="320" t="s">
+      <c r="E44" s="345" t="s">
         <v>129</v>
       </c>
-      <c r="F44" s="321"/>
-      <c r="G44" s="322"/>
+      <c r="F44" s="346"/>
+      <c r="G44" s="347"/>
       <c r="H44" s="72"/>
       <c r="I44" s="72"/>
       <c r="J44" s="81" t="e">
@@ -11525,15 +11522,15 @@
       <c r="B45" s="58">
         <v>17</v>
       </c>
-      <c r="C45" s="333" t="s">
+      <c r="C45" s="339" t="s">
         <v>62</v>
       </c>
-      <c r="D45" s="324" t="s">
+      <c r="D45" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="325"/>
-      <c r="F45" s="325"/>
-      <c r="G45" s="326"/>
+      <c r="E45" s="337"/>
+      <c r="F45" s="337"/>
+      <c r="G45" s="338"/>
       <c r="H45" s="97"/>
       <c r="I45" s="97"/>
       <c r="J45" s="102"/>
@@ -11546,15 +11543,15 @@
       <c r="B46" s="58">
         <v>18</v>
       </c>
-      <c r="C46" s="334"/>
-      <c r="D46" s="343" t="s">
+      <c r="C46" s="340"/>
+      <c r="D46" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E46" s="320" t="s">
+      <c r="E46" s="345" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="321"/>
-      <c r="G46" s="322"/>
+      <c r="F46" s="346"/>
+      <c r="G46" s="347"/>
       <c r="H46" s="72"/>
       <c r="I46" s="72"/>
       <c r="J46" s="81" t="e">
@@ -11570,13 +11567,13 @@
       <c r="B47" s="58">
         <v>19</v>
       </c>
-      <c r="C47" s="350"/>
+      <c r="C47" s="341"/>
       <c r="D47" s="351"/>
-      <c r="E47" s="320" t="s">
+      <c r="E47" s="345" t="s">
         <v>64</v>
       </c>
-      <c r="F47" s="321"/>
-      <c r="G47" s="322"/>
+      <c r="F47" s="346"/>
+      <c r="G47" s="347"/>
       <c r="H47" s="72"/>
       <c r="I47" s="72"/>
       <c r="J47" s="81" t="e">
@@ -11592,15 +11589,15 @@
       <c r="B48" s="58">
         <v>20</v>
       </c>
-      <c r="C48" s="333" t="s">
+      <c r="C48" s="339" t="s">
         <v>205</v>
       </c>
-      <c r="D48" s="324" t="s">
+      <c r="D48" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="325"/>
-      <c r="F48" s="325"/>
-      <c r="G48" s="326"/>
+      <c r="E48" s="337"/>
+      <c r="F48" s="337"/>
+      <c r="G48" s="338"/>
       <c r="H48" s="97"/>
       <c r="I48" s="97"/>
       <c r="J48" s="102"/>
@@ -11613,15 +11610,15 @@
       <c r="B49" s="58">
         <v>21</v>
       </c>
-      <c r="C49" s="334"/>
+      <c r="C49" s="340"/>
       <c r="D49" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="335" t="s">
-        <v>44</v>
-      </c>
-      <c r="F49" s="336"/>
-      <c r="G49" s="336"/>
+      <c r="E49" s="358" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" s="359"/>
+      <c r="G49" s="359"/>
       <c r="H49" s="104"/>
       <c r="I49" s="104"/>
       <c r="J49" s="81"/>
@@ -11640,11 +11637,11 @@
       <c r="D50" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E50" s="320" t="s">
+      <c r="E50" s="345" t="s">
         <v>206</v>
       </c>
-      <c r="F50" s="321"/>
-      <c r="G50" s="322"/>
+      <c r="F50" s="346"/>
+      <c r="G50" s="347"/>
       <c r="H50" s="72"/>
       <c r="I50" s="72"/>
       <c r="J50" s="81" t="e">
@@ -11667,11 +11664,11 @@
       <c r="D51" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E51" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="321"/>
-      <c r="G51" s="322"/>
+      <c r="E51" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="346"/>
+      <c r="G51" s="347"/>
       <c r="H51" s="72"/>
       <c r="I51" s="72"/>
       <c r="J51" s="81"/>
@@ -11685,15 +11682,15 @@
       <c r="B52" s="58">
         <v>24</v>
       </c>
-      <c r="C52" s="333" t="s">
+      <c r="C52" s="339" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="324" t="s">
+      <c r="D52" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E52" s="325"/>
-      <c r="F52" s="325"/>
-      <c r="G52" s="326"/>
+      <c r="E52" s="337"/>
+      <c r="F52" s="337"/>
+      <c r="G52" s="338"/>
       <c r="H52" s="97"/>
       <c r="I52" s="97"/>
       <c r="J52" s="102"/>
@@ -11706,15 +11703,15 @@
       <c r="B53" s="58">
         <v>25</v>
       </c>
-      <c r="C53" s="334"/>
+      <c r="C53" s="340"/>
       <c r="D53" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E53" s="320" t="s">
+      <c r="E53" s="345" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="321"/>
-      <c r="G53" s="322"/>
+      <c r="F53" s="346"/>
+      <c r="G53" s="347"/>
       <c r="H53" s="72"/>
       <c r="I53" s="72"/>
       <c r="J53" s="81"/>
@@ -11733,11 +11730,11 @@
       <c r="D54" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E54" s="320" t="s">
+      <c r="E54" s="345" t="s">
         <v>207</v>
       </c>
-      <c r="F54" s="321"/>
-      <c r="G54" s="322"/>
+      <c r="F54" s="346"/>
+      <c r="G54" s="347"/>
       <c r="H54" s="72"/>
       <c r="I54" s="72"/>
       <c r="J54" s="81" t="e">
@@ -11754,15 +11751,15 @@
       <c r="B55" s="58">
         <v>30</v>
       </c>
-      <c r="C55" s="333" t="s">
+      <c r="C55" s="339" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="324" t="s">
+      <c r="D55" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="325"/>
-      <c r="F55" s="325"/>
-      <c r="G55" s="326"/>
+      <c r="E55" s="337"/>
+      <c r="F55" s="337"/>
+      <c r="G55" s="338"/>
       <c r="H55" s="97"/>
       <c r="I55" s="97"/>
       <c r="J55" s="102"/>
@@ -11775,15 +11772,15 @@
       <c r="B56" s="58">
         <v>31</v>
       </c>
-      <c r="C56" s="334"/>
+      <c r="C56" s="340"/>
       <c r="D56" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="320" t="s">
+      <c r="E56" s="345" t="s">
         <v>146</v>
       </c>
-      <c r="F56" s="321"/>
-      <c r="G56" s="322"/>
+      <c r="F56" s="346"/>
+      <c r="G56" s="347"/>
       <c r="H56" s="72"/>
       <c r="I56" s="72"/>
       <c r="J56" s="81"/>
@@ -11796,15 +11793,15 @@
       <c r="B57" s="58">
         <v>32</v>
       </c>
-      <c r="C57" s="334"/>
+      <c r="C57" s="340"/>
       <c r="D57" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="320" t="s">
+      <c r="E57" s="345" t="s">
         <v>147</v>
       </c>
-      <c r="F57" s="321"/>
-      <c r="G57" s="322"/>
+      <c r="F57" s="346"/>
+      <c r="G57" s="347"/>
       <c r="H57" s="72"/>
       <c r="I57" s="72"/>
       <c r="J57" s="81"/>
@@ -11823,11 +11820,11 @@
       <c r="D58" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="320" t="s">
+      <c r="E58" s="345" t="s">
         <v>148</v>
       </c>
-      <c r="F58" s="321"/>
-      <c r="G58" s="322"/>
+      <c r="F58" s="346"/>
+      <c r="G58" s="347"/>
       <c r="H58" s="72"/>
       <c r="I58" s="72"/>
       <c r="J58" s="81"/>
@@ -11846,11 +11843,11 @@
       <c r="D59" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E59" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F59" s="321"/>
-      <c r="G59" s="322"/>
+      <c r="E59" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F59" s="346"/>
+      <c r="G59" s="347"/>
       <c r="H59" s="72"/>
       <c r="I59" s="72"/>
       <c r="J59" s="81"/>
@@ -11864,15 +11861,15 @@
       <c r="B60" s="58">
         <v>35</v>
       </c>
-      <c r="C60" s="333" t="s">
+      <c r="C60" s="339" t="s">
         <v>190</v>
       </c>
-      <c r="D60" s="324" t="s">
+      <c r="D60" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E60" s="325"/>
-      <c r="F60" s="325"/>
-      <c r="G60" s="326"/>
+      <c r="E60" s="337"/>
+      <c r="F60" s="337"/>
+      <c r="G60" s="338"/>
       <c r="H60" s="97"/>
       <c r="I60" s="97"/>
       <c r="J60" s="102"/>
@@ -11885,15 +11882,15 @@
       <c r="B61" s="58">
         <v>36</v>
       </c>
-      <c r="C61" s="334"/>
+      <c r="C61" s="340"/>
       <c r="D61" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E61" s="320" t="s">
+      <c r="E61" s="345" t="s">
         <v>128</v>
       </c>
-      <c r="F61" s="321"/>
-      <c r="G61" s="322"/>
+      <c r="F61" s="346"/>
+      <c r="G61" s="347"/>
       <c r="H61" s="72"/>
       <c r="I61" s="72"/>
       <c r="J61" s="81"/>
@@ -11906,15 +11903,15 @@
       <c r="B62" s="58">
         <v>37</v>
       </c>
-      <c r="C62" s="334"/>
+      <c r="C62" s="340"/>
       <c r="D62" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E62" s="320" t="s">
+      <c r="E62" s="345" t="s">
         <v>154</v>
       </c>
-      <c r="F62" s="321"/>
-      <c r="G62" s="322"/>
+      <c r="F62" s="346"/>
+      <c r="G62" s="347"/>
       <c r="H62" s="72"/>
       <c r="I62" s="72"/>
       <c r="J62" s="81"/>
@@ -11933,11 +11930,11 @@
       <c r="D63" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E63" s="320" t="s">
+      <c r="E63" s="345" t="s">
         <v>208</v>
       </c>
-      <c r="F63" s="321"/>
-      <c r="G63" s="322"/>
+      <c r="F63" s="346"/>
+      <c r="G63" s="347"/>
       <c r="H63" s="72"/>
       <c r="I63" s="72"/>
       <c r="J63" s="81"/>
@@ -11956,11 +11953,11 @@
       <c r="D64" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E64" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F64" s="321"/>
-      <c r="G64" s="322"/>
+      <c r="E64" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F64" s="346"/>
+      <c r="G64" s="347"/>
       <c r="H64" s="72"/>
       <c r="I64" s="72"/>
       <c r="J64" s="81"/>
@@ -11974,15 +11971,15 @@
       <c r="B65" s="58">
         <v>40</v>
       </c>
-      <c r="C65" s="333" t="s">
+      <c r="C65" s="339" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="324" t="s">
+      <c r="D65" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E65" s="325"/>
-      <c r="F65" s="325"/>
-      <c r="G65" s="326"/>
+      <c r="E65" s="337"/>
+      <c r="F65" s="337"/>
+      <c r="G65" s="338"/>
       <c r="H65" s="97"/>
       <c r="I65" s="97"/>
       <c r="J65" s="102"/>
@@ -11995,17 +11992,17 @@
       <c r="B66" s="58">
         <v>41</v>
       </c>
-      <c r="C66" s="334"/>
+      <c r="C66" s="340"/>
       <c r="D66" s="66" t="s">
         <v>55</v>
       </c>
       <c r="E66" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="F66" s="324" t="s">
+      <c r="F66" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G66" s="326"/>
+      <c r="G66" s="338"/>
       <c r="H66" s="97"/>
       <c r="I66" s="97"/>
       <c r="J66" s="102"/>
@@ -12018,7 +12015,7 @@
       <c r="B67" s="58">
         <v>42</v>
       </c>
-      <c r="C67" s="334"/>
+      <c r="C67" s="340"/>
       <c r="D67" s="67" t="s">
         <v>44</v>
       </c>
@@ -12111,10 +12108,10 @@
       <c r="E70" s="103" t="s">
         <v>210</v>
       </c>
-      <c r="F70" s="324" t="s">
+      <c r="F70" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G70" s="326"/>
+      <c r="G70" s="338"/>
       <c r="H70" s="97"/>
       <c r="I70" s="97"/>
       <c r="J70" s="102"/>
@@ -12283,10 +12280,10 @@
       <c r="E76" s="103" t="s">
         <v>214</v>
       </c>
-      <c r="F76" s="324" t="s">
+      <c r="F76" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G76" s="326"/>
+      <c r="G76" s="338"/>
       <c r="H76" s="97"/>
       <c r="I76" s="97"/>
       <c r="J76" s="102"/>
@@ -12388,13 +12385,13 @@
       <c r="D80" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E80" s="345" t="s">
+      <c r="E80" s="360" t="s">
         <v>216</v>
       </c>
-      <c r="F80" s="324" t="s">
+      <c r="F80" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G80" s="326"/>
+      <c r="G80" s="338"/>
       <c r="H80" s="97"/>
       <c r="I80" s="97"/>
       <c r="J80" s="102"/>
@@ -12414,15 +12411,15 @@
       <c r="D81" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E81" s="346"/>
+      <c r="E81" s="361"/>
       <c r="F81" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="G81" s="347" t="s">
+      <c r="G81" s="362" t="s">
         <v>136</v>
       </c>
-      <c r="H81" s="348"/>
-      <c r="I81" s="349"/>
+      <c r="H81" s="363"/>
+      <c r="I81" s="364"/>
       <c r="J81" s="81" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -12501,13 +12498,13 @@
       <c r="D84" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E84" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F84" s="324" t="s">
+      <c r="E84" s="360" t="s">
+        <v>44</v>
+      </c>
+      <c r="F84" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G84" s="326"/>
+      <c r="G84" s="338"/>
       <c r="H84" s="97"/>
       <c r="I84" s="97"/>
       <c r="J84" s="102"/>
@@ -12527,7 +12524,7 @@
       <c r="D85" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E85" s="346"/>
+      <c r="E85" s="361"/>
       <c r="F85" s="66" t="s">
         <v>55</v>
       </c>
@@ -12576,15 +12573,15 @@
       <c r="B87" s="58">
         <v>62</v>
       </c>
-      <c r="C87" s="333" t="s">
+      <c r="C87" s="339" t="s">
         <v>144</v>
       </c>
-      <c r="D87" s="324" t="s">
+      <c r="D87" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E87" s="325"/>
-      <c r="F87" s="325"/>
-      <c r="G87" s="326"/>
+      <c r="E87" s="337"/>
+      <c r="F87" s="337"/>
+      <c r="G87" s="338"/>
       <c r="H87" s="97"/>
       <c r="I87" s="110"/>
       <c r="J87" s="102"/>
@@ -12597,15 +12594,15 @@
       <c r="B88" s="58">
         <v>63</v>
       </c>
-      <c r="C88" s="334"/>
+      <c r="C88" s="340"/>
       <c r="D88" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E88" s="335" t="s">
-        <v>44</v>
-      </c>
-      <c r="F88" s="336"/>
-      <c r="G88" s="336"/>
+      <c r="E88" s="358" t="s">
+        <v>44</v>
+      </c>
+      <c r="F88" s="359"/>
+      <c r="G88" s="359"/>
       <c r="H88" s="104"/>
       <c r="I88" s="104"/>
       <c r="J88" s="81" t="e">
@@ -12627,11 +12624,11 @@
       <c r="D89" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F89" s="321"/>
-      <c r="G89" s="322"/>
+      <c r="E89" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F89" s="346"/>
+      <c r="G89" s="347"/>
       <c r="H89" s="72"/>
       <c r="I89" s="109"/>
       <c r="J89" s="81"/>
@@ -12651,11 +12648,11 @@
       <c r="D90" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E90" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F90" s="321"/>
-      <c r="G90" s="322"/>
+      <c r="E90" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F90" s="346"/>
+      <c r="G90" s="347"/>
       <c r="H90" s="72"/>
       <c r="I90" s="109"/>
       <c r="J90" s="81"/>
@@ -12669,15 +12666,15 @@
       <c r="B91" s="58">
         <v>66</v>
       </c>
-      <c r="C91" s="333" t="s">
+      <c r="C91" s="339" t="s">
         <v>189</v>
       </c>
-      <c r="D91" s="324" t="s">
+      <c r="D91" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="325"/>
-      <c r="F91" s="325"/>
-      <c r="G91" s="326"/>
+      <c r="E91" s="337"/>
+      <c r="F91" s="337"/>
+      <c r="G91" s="338"/>
       <c r="H91" s="97"/>
       <c r="I91" s="110"/>
       <c r="J91" s="102"/>
@@ -12690,15 +12687,15 @@
       <c r="B92" s="58">
         <v>67</v>
       </c>
-      <c r="C92" s="334"/>
+      <c r="C92" s="340"/>
       <c r="D92" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E92" s="335" t="s">
-        <v>44</v>
-      </c>
-      <c r="F92" s="336"/>
-      <c r="G92" s="336"/>
+      <c r="E92" s="358" t="s">
+        <v>44</v>
+      </c>
+      <c r="F92" s="359"/>
+      <c r="G92" s="359"/>
       <c r="H92" s="104"/>
       <c r="I92" s="104"/>
       <c r="J92" s="81"/>
@@ -12717,11 +12714,11 @@
       <c r="D93" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F93" s="321"/>
-      <c r="G93" s="322"/>
+      <c r="E93" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F93" s="346"/>
+      <c r="G93" s="347"/>
       <c r="H93" s="72"/>
       <c r="I93" s="109"/>
       <c r="J93" s="81"/>
@@ -12741,11 +12738,11 @@
       <c r="D94" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E94" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F94" s="321"/>
-      <c r="G94" s="322"/>
+      <c r="E94" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F94" s="346"/>
+      <c r="G94" s="347"/>
       <c r="H94" s="72"/>
       <c r="I94" s="109"/>
       <c r="J94" s="81"/>
@@ -12759,15 +12756,15 @@
       <c r="B95" s="58">
         <v>70</v>
       </c>
-      <c r="C95" s="333" t="s">
+      <c r="C95" s="339" t="s">
         <v>137</v>
       </c>
-      <c r="D95" s="324" t="s">
+      <c r="D95" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E95" s="325"/>
-      <c r="F95" s="325"/>
-      <c r="G95" s="326"/>
+      <c r="E95" s="337"/>
+      <c r="F95" s="337"/>
+      <c r="G95" s="338"/>
       <c r="H95" s="97"/>
       <c r="I95" s="110"/>
       <c r="J95" s="102"/>
@@ -12780,15 +12777,15 @@
       <c r="B96" s="58">
         <v>71</v>
       </c>
-      <c r="C96" s="334"/>
+      <c r="C96" s="340"/>
       <c r="D96" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E96" s="335" t="s">
-        <v>44</v>
-      </c>
-      <c r="F96" s="336"/>
-      <c r="G96" s="336"/>
+      <c r="E96" s="358" t="s">
+        <v>44</v>
+      </c>
+      <c r="F96" s="359"/>
+      <c r="G96" s="359"/>
       <c r="H96" s="104"/>
       <c r="I96" s="104"/>
       <c r="J96" s="81"/>
@@ -12807,11 +12804,11 @@
       <c r="D97" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E97" s="320" t="s">
+      <c r="E97" s="345" t="s">
         <v>217</v>
       </c>
-      <c r="F97" s="321"/>
-      <c r="G97" s="322"/>
+      <c r="F97" s="346"/>
+      <c r="G97" s="347"/>
       <c r="H97" s="72"/>
       <c r="I97" s="109"/>
       <c r="J97" s="81" t="e">
@@ -12826,11 +12823,11 @@
       <c r="B98" s="58"/>
       <c r="C98" s="77"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="320" t="s">
+      <c r="E98" s="345" t="s">
         <v>218</v>
       </c>
-      <c r="F98" s="321"/>
-      <c r="G98" s="322"/>
+      <c r="F98" s="346"/>
+      <c r="G98" s="347"/>
       <c r="H98" s="72"/>
       <c r="I98" s="109"/>
       <c r="J98" s="81"/>
@@ -12842,9 +12839,9 @@
       <c r="B99" s="58"/>
       <c r="C99" s="77"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="320"/>
-      <c r="F99" s="321"/>
-      <c r="G99" s="322"/>
+      <c r="E99" s="345"/>
+      <c r="F99" s="346"/>
+      <c r="G99" s="347"/>
       <c r="H99" s="72"/>
       <c r="I99" s="109"/>
       <c r="J99" s="81"/>
@@ -12864,11 +12861,11 @@
       <c r="D100" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E100" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F100" s="321"/>
-      <c r="G100" s="322"/>
+      <c r="E100" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F100" s="346"/>
+      <c r="G100" s="347"/>
       <c r="H100" s="72"/>
       <c r="I100" s="109"/>
       <c r="J100" s="81"/>
@@ -12882,15 +12879,15 @@
       <c r="B101" s="58">
         <v>75</v>
       </c>
-      <c r="C101" s="333" t="s">
+      <c r="C101" s="339" t="s">
         <v>17</v>
       </c>
-      <c r="D101" s="324" t="s">
+      <c r="D101" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E101" s="325"/>
-      <c r="F101" s="325"/>
-      <c r="G101" s="326"/>
+      <c r="E101" s="337"/>
+      <c r="F101" s="337"/>
+      <c r="G101" s="338"/>
       <c r="H101" s="97"/>
       <c r="I101" s="111">
         <f>I102+I103+I104</f>
@@ -12906,15 +12903,15 @@
       <c r="B102" s="58">
         <v>76</v>
       </c>
-      <c r="C102" s="334"/>
+      <c r="C102" s="340"/>
       <c r="D102" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E102" s="337" t="s">
+      <c r="E102" s="355" t="s">
         <v>219</v>
       </c>
-      <c r="F102" s="338"/>
-      <c r="G102" s="339"/>
+      <c r="F102" s="356"/>
+      <c r="G102" s="357"/>
       <c r="H102" s="72"/>
       <c r="I102" s="109"/>
       <c r="J102" s="81">
@@ -12930,15 +12927,15 @@
       <c r="B103" s="58">
         <v>77</v>
       </c>
-      <c r="C103" s="334"/>
+      <c r="C103" s="340"/>
       <c r="D103" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E103" s="337" t="s">
+      <c r="E103" s="355" t="s">
         <v>220</v>
       </c>
-      <c r="F103" s="338"/>
-      <c r="G103" s="339"/>
+      <c r="F103" s="356"/>
+      <c r="G103" s="357"/>
       <c r="H103" s="72"/>
       <c r="I103" s="72"/>
       <c r="J103" s="81">
@@ -12960,11 +12957,11 @@
       <c r="D104" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E104" s="337" t="s">
+      <c r="E104" s="355" t="s">
         <v>221</v>
       </c>
-      <c r="F104" s="338"/>
-      <c r="G104" s="339"/>
+      <c r="F104" s="356"/>
+      <c r="G104" s="357"/>
       <c r="H104" s="72"/>
       <c r="I104" s="72"/>
       <c r="J104" s="81">
@@ -12980,13 +12977,13 @@
       <c r="B105" s="58">
         <v>83</v>
       </c>
-      <c r="C105" s="324" t="s">
+      <c r="C105" s="336" t="s">
         <v>7</v>
       </c>
-      <c r="D105" s="325"/>
-      <c r="E105" s="325"/>
-      <c r="F105" s="325"/>
-      <c r="G105" s="326"/>
+      <c r="D105" s="337"/>
+      <c r="E105" s="337"/>
+      <c r="F105" s="337"/>
+      <c r="G105" s="338"/>
       <c r="H105" s="97"/>
       <c r="I105" s="97"/>
       <c r="J105" s="102" t="e">
@@ -13002,13 +12999,13 @@
       <c r="B106" s="58">
         <v>84</v>
       </c>
-      <c r="C106" s="324" t="s">
+      <c r="C106" s="336" t="s">
         <v>222</v>
       </c>
-      <c r="D106" s="325"/>
-      <c r="E106" s="325"/>
-      <c r="F106" s="325"/>
-      <c r="G106" s="326"/>
+      <c r="D106" s="337"/>
+      <c r="E106" s="337"/>
+      <c r="F106" s="337"/>
+      <c r="G106" s="338"/>
       <c r="H106" s="97"/>
       <c r="I106" s="101"/>
       <c r="J106" s="102" t="e">
@@ -13024,15 +13021,15 @@
       <c r="B107" s="58">
         <v>85</v>
       </c>
-      <c r="C107" s="333" t="s">
+      <c r="C107" s="339" t="s">
         <v>223</v>
       </c>
-      <c r="D107" s="324" t="s">
+      <c r="D107" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E107" s="325"/>
-      <c r="F107" s="325"/>
-      <c r="G107" s="326"/>
+      <c r="E107" s="337"/>
+      <c r="F107" s="337"/>
+      <c r="G107" s="338"/>
       <c r="H107" s="97"/>
       <c r="I107" s="97"/>
       <c r="J107" s="102"/>
@@ -13045,15 +13042,15 @@
       <c r="B108" s="58">
         <v>86</v>
       </c>
-      <c r="C108" s="334"/>
+      <c r="C108" s="340"/>
       <c r="D108" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E108" s="337" t="s">
+      <c r="E108" s="355" t="s">
         <v>224</v>
       </c>
-      <c r="F108" s="338"/>
-      <c r="G108" s="339"/>
+      <c r="F108" s="356"/>
+      <c r="G108" s="357"/>
       <c r="H108" s="72"/>
       <c r="I108" s="63"/>
       <c r="J108" s="81" t="e">
@@ -13075,11 +13072,11 @@
       <c r="D109" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E109" s="320" t="s">
+      <c r="E109" s="345" t="s">
         <v>225</v>
       </c>
-      <c r="F109" s="321"/>
-      <c r="G109" s="322"/>
+      <c r="F109" s="346"/>
+      <c r="G109" s="347"/>
       <c r="H109" s="72"/>
       <c r="I109" s="63"/>
       <c r="J109" s="81"/>
@@ -13099,11 +13096,11 @@
       <c r="D110" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E110" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F110" s="321"/>
-      <c r="G110" s="322"/>
+      <c r="E110" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F110" s="346"/>
+      <c r="G110" s="347"/>
       <c r="H110" s="72"/>
       <c r="I110" s="72"/>
       <c r="J110" s="81"/>
@@ -13117,15 +13114,15 @@
       <c r="B111" s="58">
         <v>89</v>
       </c>
-      <c r="C111" s="333" t="s">
+      <c r="C111" s="339" t="s">
         <v>192</v>
       </c>
-      <c r="D111" s="324" t="s">
+      <c r="D111" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E111" s="325"/>
-      <c r="F111" s="325"/>
-      <c r="G111" s="326"/>
+      <c r="E111" s="337"/>
+      <c r="F111" s="337"/>
+      <c r="G111" s="338"/>
       <c r="H111" s="97"/>
       <c r="I111" s="97"/>
       <c r="J111" s="102"/>
@@ -13138,15 +13135,15 @@
       <c r="B112" s="58">
         <v>90</v>
       </c>
-      <c r="C112" s="334"/>
+      <c r="C112" s="340"/>
       <c r="D112" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E112" s="337" t="s">
+      <c r="E112" s="355" t="s">
         <v>226</v>
       </c>
-      <c r="F112" s="338"/>
-      <c r="G112" s="339"/>
+      <c r="F112" s="356"/>
+      <c r="G112" s="357"/>
       <c r="H112" s="72"/>
       <c r="I112" s="72"/>
       <c r="J112" s="81"/>
@@ -13165,11 +13162,11 @@
       <c r="D113" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E113" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F113" s="321"/>
-      <c r="G113" s="322"/>
+      <c r="E113" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F113" s="346"/>
+      <c r="G113" s="347"/>
       <c r="H113" s="72"/>
       <c r="I113" s="72"/>
       <c r="J113" s="81"/>
@@ -13182,15 +13179,15 @@
       <c r="B114" s="58">
         <v>92</v>
       </c>
-      <c r="C114" s="333" t="s">
+      <c r="C114" s="339" t="s">
         <v>191</v>
       </c>
-      <c r="D114" s="324" t="s">
+      <c r="D114" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E114" s="325"/>
-      <c r="F114" s="325"/>
-      <c r="G114" s="326"/>
+      <c r="E114" s="337"/>
+      <c r="F114" s="337"/>
+      <c r="G114" s="338"/>
       <c r="H114" s="97"/>
       <c r="I114" s="97"/>
       <c r="J114" s="102"/>
@@ -13203,15 +13200,15 @@
       <c r="B115" s="58">
         <v>93</v>
       </c>
-      <c r="C115" s="334"/>
+      <c r="C115" s="340"/>
       <c r="D115" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E115" s="335" t="s">
-        <v>44</v>
-      </c>
-      <c r="F115" s="336"/>
-      <c r="G115" s="336"/>
+      <c r="E115" s="358" t="s">
+        <v>44</v>
+      </c>
+      <c r="F115" s="359"/>
+      <c r="G115" s="359"/>
       <c r="H115" s="104"/>
       <c r="I115" s="104"/>
       <c r="J115" s="112"/>
@@ -13230,11 +13227,11 @@
       <c r="D116" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E116" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F116" s="321"/>
-      <c r="G116" s="322"/>
+      <c r="E116" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F116" s="346"/>
+      <c r="G116" s="347"/>
       <c r="H116" s="72"/>
       <c r="I116" s="63"/>
       <c r="J116" s="81"/>
@@ -13254,11 +13251,11 @@
       <c r="D117" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E117" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F117" s="321"/>
-      <c r="G117" s="322"/>
+      <c r="E117" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F117" s="346"/>
+      <c r="G117" s="347"/>
       <c r="H117" s="72"/>
       <c r="I117" s="72"/>
       <c r="J117" s="81"/>
@@ -13272,15 +13269,15 @@
       <c r="B118" s="58">
         <v>96</v>
       </c>
-      <c r="C118" s="333" t="s">
+      <c r="C118" s="339" t="s">
         <v>149</v>
       </c>
-      <c r="D118" s="324" t="s">
+      <c r="D118" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E118" s="325"/>
-      <c r="F118" s="325"/>
-      <c r="G118" s="326"/>
+      <c r="E118" s="337"/>
+      <c r="F118" s="337"/>
+      <c r="G118" s="338"/>
       <c r="H118" s="97"/>
       <c r="I118" s="97"/>
       <c r="J118" s="102"/>
@@ -13293,15 +13290,15 @@
       <c r="B119" s="58">
         <v>97</v>
       </c>
-      <c r="C119" s="334"/>
+      <c r="C119" s="340"/>
       <c r="D119" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E119" s="337" t="s">
+      <c r="E119" s="355" t="s">
         <v>227</v>
       </c>
-      <c r="F119" s="338"/>
-      <c r="G119" s="339"/>
+      <c r="F119" s="356"/>
+      <c r="G119" s="357"/>
       <c r="H119" s="72"/>
       <c r="I119" s="72"/>
       <c r="J119" s="81"/>
@@ -13320,11 +13317,11 @@
       <c r="D120" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E120" s="337" t="s">
+      <c r="E120" s="355" t="s">
         <v>228</v>
       </c>
-      <c r="F120" s="338"/>
-      <c r="G120" s="339"/>
+      <c r="F120" s="356"/>
+      <c r="G120" s="357"/>
       <c r="H120" s="72"/>
       <c r="I120" s="72"/>
       <c r="J120" s="81"/>
@@ -13343,11 +13340,11 @@
       <c r="D121" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E121" s="337" t="s">
+      <c r="E121" s="355" t="s">
         <v>229</v>
       </c>
-      <c r="F121" s="338"/>
-      <c r="G121" s="339"/>
+      <c r="F121" s="356"/>
+      <c r="G121" s="357"/>
       <c r="H121" s="72"/>
       <c r="I121" s="72"/>
       <c r="J121" s="81"/>
@@ -13366,11 +13363,11 @@
       <c r="D122" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E122" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F122" s="321"/>
-      <c r="G122" s="322"/>
+      <c r="E122" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F122" s="346"/>
+      <c r="G122" s="347"/>
       <c r="H122" s="72"/>
       <c r="I122" s="72"/>
       <c r="J122" s="81"/>
@@ -13384,15 +13381,15 @@
       <c r="B123" s="58">
         <v>101</v>
       </c>
-      <c r="C123" s="333" t="s">
+      <c r="C123" s="339" t="s">
         <v>230</v>
       </c>
-      <c r="D123" s="324" t="s">
+      <c r="D123" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E123" s="325"/>
-      <c r="F123" s="325"/>
-      <c r="G123" s="326"/>
+      <c r="E123" s="337"/>
+      <c r="F123" s="337"/>
+      <c r="G123" s="338"/>
       <c r="H123" s="97"/>
       <c r="I123" s="97"/>
       <c r="J123" s="102"/>
@@ -13405,17 +13402,17 @@
       <c r="B124" s="58">
         <v>102</v>
       </c>
-      <c r="C124" s="334"/>
+      <c r="C124" s="340"/>
       <c r="D124" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E124" s="343" t="s">
+      <c r="E124" s="342" t="s">
         <v>231</v>
       </c>
-      <c r="F124" s="324" t="s">
+      <c r="F124" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G124" s="326"/>
+      <c r="G124" s="338"/>
       <c r="H124" s="97"/>
       <c r="I124" s="97"/>
       <c r="J124" s="102"/>
@@ -13428,11 +13425,11 @@
       <c r="B125" s="58">
         <v>103</v>
       </c>
-      <c r="C125" s="334"/>
+      <c r="C125" s="340"/>
       <c r="D125" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E125" s="344"/>
+      <c r="E125" s="343"/>
       <c r="F125" s="66" t="s">
         <v>55</v>
       </c>
@@ -13451,7 +13448,7 @@
       <c r="B126" s="58">
         <v>104</v>
       </c>
-      <c r="C126" s="334"/>
+      <c r="C126" s="340"/>
       <c r="D126" s="67" t="s">
         <v>44</v>
       </c>
@@ -13537,11 +13534,11 @@
       <c r="D129" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E129" s="337" t="s">
+      <c r="E129" s="355" t="s">
         <v>234</v>
       </c>
-      <c r="F129" s="338"/>
-      <c r="G129" s="339"/>
+      <c r="F129" s="356"/>
+      <c r="G129" s="357"/>
       <c r="H129" s="72"/>
       <c r="I129" s="72"/>
       <c r="J129" s="81"/>
@@ -13560,11 +13557,11 @@
       <c r="D130" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E130" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F130" s="321"/>
-      <c r="G130" s="322"/>
+      <c r="E130" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F130" s="346"/>
+      <c r="G130" s="347"/>
       <c r="H130" s="72"/>
       <c r="I130" s="72"/>
       <c r="J130" s="81"/>
@@ -13578,15 +13575,15 @@
       <c r="B131" s="58">
         <v>109</v>
       </c>
-      <c r="C131" s="333" t="s">
+      <c r="C131" s="339" t="s">
         <v>175</v>
       </c>
-      <c r="D131" s="324" t="s">
+      <c r="D131" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E131" s="325"/>
-      <c r="F131" s="325"/>
-      <c r="G131" s="326"/>
+      <c r="E131" s="337"/>
+      <c r="F131" s="337"/>
+      <c r="G131" s="338"/>
       <c r="H131" s="97"/>
       <c r="I131" s="101">
         <f>SUM(I132:I136)</f>
@@ -13602,15 +13599,15 @@
       <c r="B132" s="58">
         <v>110</v>
       </c>
-      <c r="C132" s="334"/>
+      <c r="C132" s="340"/>
       <c r="D132" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E132" s="337" t="s">
+      <c r="E132" s="355" t="s">
         <v>91</v>
       </c>
-      <c r="F132" s="338"/>
-      <c r="G132" s="339"/>
+      <c r="F132" s="356"/>
+      <c r="G132" s="357"/>
       <c r="H132" s="72"/>
       <c r="I132" s="72"/>
       <c r="J132" s="81" t="e">
@@ -13626,15 +13623,15 @@
       <c r="B133" s="58">
         <v>111</v>
       </c>
-      <c r="C133" s="334"/>
+      <c r="C133" s="340"/>
       <c r="D133" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E133" s="337" t="s">
+      <c r="E133" s="355" t="s">
         <v>235</v>
       </c>
-      <c r="F133" s="338"/>
-      <c r="G133" s="339"/>
+      <c r="F133" s="356"/>
+      <c r="G133" s="357"/>
       <c r="H133" s="72"/>
       <c r="I133" s="72"/>
       <c r="J133" s="81" t="e">
@@ -13656,11 +13653,11 @@
       <c r="D134" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E134" s="337" t="s">
+      <c r="E134" s="355" t="s">
         <v>11</v>
       </c>
-      <c r="F134" s="338"/>
-      <c r="G134" s="339"/>
+      <c r="F134" s="356"/>
+      <c r="G134" s="357"/>
       <c r="H134" s="72"/>
       <c r="I134" s="72"/>
       <c r="J134" s="81" t="e">
@@ -13682,11 +13679,11 @@
       <c r="D135" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E135" s="337" t="s">
+      <c r="E135" s="355" t="s">
         <v>9</v>
       </c>
-      <c r="F135" s="338"/>
-      <c r="G135" s="339"/>
+      <c r="F135" s="356"/>
+      <c r="G135" s="357"/>
       <c r="H135" s="72"/>
       <c r="I135" s="72"/>
       <c r="J135" s="81" t="e">
@@ -13708,11 +13705,11 @@
       <c r="D136" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E136" s="330" t="s">
+      <c r="E136" s="352" t="s">
         <v>236</v>
       </c>
-      <c r="F136" s="330"/>
-      <c r="G136" s="330"/>
+      <c r="F136" s="352"/>
+      <c r="G136" s="352"/>
       <c r="H136" s="72"/>
       <c r="I136" s="72"/>
       <c r="J136" s="81" t="e">
@@ -13735,11 +13732,11 @@
       <c r="D137" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E137" s="340" t="s">
-        <v>44</v>
-      </c>
-      <c r="F137" s="341"/>
-      <c r="G137" s="342"/>
+      <c r="E137" s="365" t="s">
+        <v>44</v>
+      </c>
+      <c r="F137" s="366"/>
+      <c r="G137" s="367"/>
       <c r="H137" s="115"/>
       <c r="I137" s="115"/>
       <c r="J137" s="116"/>
@@ -13753,15 +13750,15 @@
       <c r="B138" s="58">
         <v>118</v>
       </c>
-      <c r="C138" s="333" t="s">
+      <c r="C138" s="339" t="s">
         <v>237</v>
       </c>
-      <c r="D138" s="324" t="s">
+      <c r="D138" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E138" s="325"/>
-      <c r="F138" s="325"/>
-      <c r="G138" s="326"/>
+      <c r="E138" s="337"/>
+      <c r="F138" s="337"/>
+      <c r="G138" s="338"/>
       <c r="H138" s="97"/>
       <c r="I138" s="117"/>
       <c r="J138" s="118"/>
@@ -13774,15 +13771,15 @@
       <c r="B139" s="58">
         <v>119</v>
       </c>
-      <c r="C139" s="334"/>
+      <c r="C139" s="340"/>
       <c r="D139" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E139" s="337" t="s">
+      <c r="E139" s="355" t="s">
         <v>19</v>
       </c>
-      <c r="F139" s="338"/>
-      <c r="G139" s="339"/>
+      <c r="F139" s="356"/>
+      <c r="G139" s="357"/>
       <c r="H139" s="109"/>
       <c r="I139" s="113"/>
       <c r="J139" s="81" t="e">
@@ -13807,10 +13804,10 @@
       <c r="E140" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="F140" s="324" t="s">
+      <c r="F140" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G140" s="326"/>
+      <c r="G140" s="338"/>
       <c r="H140" s="110"/>
       <c r="I140" s="97"/>
       <c r="J140" s="102"/>
@@ -13832,7 +13829,7 @@
       <c r="E141" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F141" s="331" t="s">
+      <c r="F141" s="372" t="s">
         <v>55</v>
       </c>
       <c r="G141" s="108" t="s">
@@ -13859,7 +13856,7 @@
       <c r="E142" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F142" s="332"/>
+      <c r="F142" s="373"/>
       <c r="G142" s="60" t="s">
         <v>238</v>
       </c>
@@ -13910,10 +13907,10 @@
       <c r="E144" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="F144" s="324" t="s">
+      <c r="F144" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G144" s="326"/>
+      <c r="G144" s="338"/>
       <c r="H144" s="97"/>
       <c r="I144" s="110"/>
       <c r="J144" s="102"/>
@@ -13935,7 +13932,7 @@
       <c r="E145" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F145" s="331" t="s">
+      <c r="F145" s="372" t="s">
         <v>55</v>
       </c>
       <c r="G145" s="108" t="s">
@@ -13962,7 +13959,7 @@
       <c r="E146" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F146" s="332"/>
+      <c r="F146" s="373"/>
       <c r="G146" s="60" t="s">
         <v>18</v>
       </c>
@@ -14032,15 +14029,15 @@
       <c r="B149" s="58">
         <v>129</v>
       </c>
-      <c r="C149" s="333" t="s">
+      <c r="C149" s="339" t="s">
         <v>239</v>
       </c>
-      <c r="D149" s="324" t="s">
+      <c r="D149" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E149" s="325"/>
-      <c r="F149" s="325"/>
-      <c r="G149" s="326"/>
+      <c r="E149" s="337"/>
+      <c r="F149" s="337"/>
+      <c r="G149" s="338"/>
       <c r="H149" s="97"/>
       <c r="I149" s="110"/>
       <c r="J149" s="102"/>
@@ -14053,15 +14050,15 @@
       <c r="B150" s="121">
         <v>130</v>
       </c>
-      <c r="C150" s="334"/>
+      <c r="C150" s="340"/>
       <c r="D150" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E150" s="335" t="s">
-        <v>44</v>
-      </c>
-      <c r="F150" s="336"/>
-      <c r="G150" s="336"/>
+      <c r="E150" s="358" t="s">
+        <v>44</v>
+      </c>
+      <c r="F150" s="359"/>
+      <c r="G150" s="359"/>
       <c r="H150" s="104"/>
       <c r="I150" s="104"/>
       <c r="J150" s="81"/>
@@ -14080,11 +14077,11 @@
       <c r="D151" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E151" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F151" s="321"/>
-      <c r="G151" s="322"/>
+      <c r="E151" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F151" s="346"/>
+      <c r="G151" s="347"/>
       <c r="H151" s="72"/>
       <c r="I151" s="109"/>
       <c r="J151" s="81"/>
@@ -14098,15 +14095,15 @@
       <c r="B152" s="58">
         <v>132</v>
       </c>
-      <c r="C152" s="323" t="s">
+      <c r="C152" s="368" t="s">
         <v>240</v>
       </c>
-      <c r="D152" s="324" t="s">
+      <c r="D152" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E152" s="325"/>
-      <c r="F152" s="325"/>
-      <c r="G152" s="326"/>
+      <c r="E152" s="337"/>
+      <c r="F152" s="337"/>
+      <c r="G152" s="338"/>
       <c r="H152" s="97"/>
       <c r="I152" s="110"/>
       <c r="J152" s="102"/>
@@ -14119,15 +14116,15 @@
       <c r="B153" s="58">
         <v>133</v>
       </c>
-      <c r="C153" s="323"/>
+      <c r="C153" s="368"/>
       <c r="D153" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E153" s="327" t="s">
+      <c r="E153" s="369" t="s">
         <v>241</v>
       </c>
-      <c r="F153" s="328"/>
-      <c r="G153" s="329"/>
+      <c r="F153" s="370"/>
+      <c r="G153" s="371"/>
       <c r="H153" s="122"/>
       <c r="I153" s="123"/>
       <c r="J153" s="81"/>
@@ -14146,11 +14143,11 @@
       <c r="D154" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E154" s="330" t="s">
+      <c r="E154" s="352" t="s">
         <v>198</v>
       </c>
-      <c r="F154" s="330"/>
-      <c r="G154" s="330"/>
+      <c r="F154" s="352"/>
+      <c r="G154" s="352"/>
       <c r="H154" s="72"/>
       <c r="I154" s="120" t="e">
         <f>SUM(#REF!)</f>
@@ -14176,15 +14173,120 @@
     </row>
   </sheetData>
   <mergeCells count="142">
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:G24"/>
-    <mergeCell ref="I22:J24"/>
+    <mergeCell ref="E151:G151"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:G152"/>
+    <mergeCell ref="E153:G153"/>
+    <mergeCell ref="E154:G154"/>
+    <mergeCell ref="F140:G140"/>
+    <mergeCell ref="F141:F142"/>
+    <mergeCell ref="F144:G144"/>
+    <mergeCell ref="F145:F146"/>
+    <mergeCell ref="C149:C150"/>
+    <mergeCell ref="D149:G149"/>
+    <mergeCell ref="E150:G150"/>
+    <mergeCell ref="E134:G134"/>
+    <mergeCell ref="E135:G135"/>
+    <mergeCell ref="E136:G136"/>
+    <mergeCell ref="E137:G137"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:G138"/>
+    <mergeCell ref="E139:G139"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="E130:G130"/>
+    <mergeCell ref="C131:C133"/>
+    <mergeCell ref="D131:G131"/>
+    <mergeCell ref="E132:G132"/>
+    <mergeCell ref="E133:G133"/>
+    <mergeCell ref="E121:G121"/>
+    <mergeCell ref="E122:G122"/>
+    <mergeCell ref="C123:C126"/>
+    <mergeCell ref="D123:G123"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="E116:G116"/>
+    <mergeCell ref="E117:G117"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:G118"/>
+    <mergeCell ref="E119:G119"/>
+    <mergeCell ref="E120:G120"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="D111:G111"/>
+    <mergeCell ref="E112:G112"/>
+    <mergeCell ref="E113:G113"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:G114"/>
+    <mergeCell ref="E115:G115"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="D107:G107"/>
+    <mergeCell ref="E108:G108"/>
+    <mergeCell ref="E109:G109"/>
+    <mergeCell ref="E110:G110"/>
+    <mergeCell ref="E104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="E98:G98"/>
+    <mergeCell ref="E99:G99"/>
+    <mergeCell ref="E100:G100"/>
+    <mergeCell ref="C101:C103"/>
+    <mergeCell ref="D101:G101"/>
+    <mergeCell ref="E102:G102"/>
+    <mergeCell ref="E103:G103"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="E94:G94"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:G95"/>
+    <mergeCell ref="E96:G96"/>
+    <mergeCell ref="E97:G97"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:G87"/>
+    <mergeCell ref="E88:G88"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="E90:G90"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="D91:G91"/>
+    <mergeCell ref="E92:G92"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="G81:I81"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="C65:C67"/>
+    <mergeCell ref="D65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D55:G55"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="E47:G47"/>
     <mergeCell ref="C29:G29"/>
     <mergeCell ref="C30:C34"/>
     <mergeCell ref="D30:G30"/>
@@ -14204,120 +14306,15 @@
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="E36:G36"/>
     <mergeCell ref="E37:G37"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:G48"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:G46"/>
-    <mergeCell ref="E47:G47"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="D60:G60"/>
-    <mergeCell ref="E61:G61"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D55:G55"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="G81:I81"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="E64:G64"/>
-    <mergeCell ref="C65:C67"/>
-    <mergeCell ref="D65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="E94:G94"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="D95:G95"/>
-    <mergeCell ref="E96:G96"/>
-    <mergeCell ref="E97:G97"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:G87"/>
-    <mergeCell ref="E88:G88"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="E90:G90"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="D91:G91"/>
-    <mergeCell ref="E92:G92"/>
-    <mergeCell ref="E104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="E98:G98"/>
-    <mergeCell ref="E99:G99"/>
-    <mergeCell ref="E100:G100"/>
-    <mergeCell ref="C101:C103"/>
-    <mergeCell ref="D101:G101"/>
-    <mergeCell ref="E102:G102"/>
-    <mergeCell ref="E103:G103"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="D111:G111"/>
-    <mergeCell ref="E112:G112"/>
-    <mergeCell ref="E113:G113"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="D114:G114"/>
-    <mergeCell ref="E115:G115"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="D107:G107"/>
-    <mergeCell ref="E108:G108"/>
-    <mergeCell ref="E109:G109"/>
-    <mergeCell ref="E110:G110"/>
-    <mergeCell ref="E121:G121"/>
-    <mergeCell ref="E122:G122"/>
-    <mergeCell ref="C123:C126"/>
-    <mergeCell ref="D123:G123"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="E116:G116"/>
-    <mergeCell ref="E117:G117"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:G118"/>
-    <mergeCell ref="E119:G119"/>
-    <mergeCell ref="E120:G120"/>
-    <mergeCell ref="E134:G134"/>
-    <mergeCell ref="E135:G135"/>
-    <mergeCell ref="E136:G136"/>
-    <mergeCell ref="E137:G137"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:G138"/>
-    <mergeCell ref="E139:G139"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="E130:G130"/>
-    <mergeCell ref="C131:C133"/>
-    <mergeCell ref="D131:G131"/>
-    <mergeCell ref="E132:G132"/>
-    <mergeCell ref="E133:G133"/>
-    <mergeCell ref="E151:G151"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D152:G152"/>
-    <mergeCell ref="E153:G153"/>
-    <mergeCell ref="E154:G154"/>
-    <mergeCell ref="F140:G140"/>
-    <mergeCell ref="F141:F142"/>
-    <mergeCell ref="F144:G144"/>
-    <mergeCell ref="F145:F146"/>
-    <mergeCell ref="C149:C150"/>
-    <mergeCell ref="D149:G149"/>
-    <mergeCell ref="E150:G150"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:G24"/>
+    <mergeCell ref="I22:J24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="64" orientation="portrait" r:id="rId1"/>
@@ -14347,15 +14344,15 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="358" t="s">
+      <c r="B1" s="319" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="358"/>
-      <c r="D1" s="358"/>
-      <c r="E1" s="358"/>
-      <c r="F1" s="358"/>
-      <c r="G1" s="358"/>
-      <c r="H1" s="358"/>
+      <c r="C1" s="319"/>
+      <c r="D1" s="319"/>
+      <c r="E1" s="319"/>
+      <c r="F1" s="319"/>
+      <c r="G1" s="319"/>
+      <c r="H1" s="319"/>
       <c r="L1" s="51"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1">
@@ -14389,30 +14386,30 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="359" t="s">
+      <c r="B3" s="320" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
+      <c r="C3" s="320"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="320"/>
+      <c r="G3" s="320"/>
+      <c r="H3" s="320"/>
       <c r="L3" s="51"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="360" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="360"/>
-      <c r="D4" s="360"/>
-      <c r="E4" s="360"/>
-      <c r="F4" s="360"/>
-      <c r="G4" s="360"/>
-      <c r="H4" s="360"/>
+      <c r="B4" s="321" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="321"/>
+      <c r="D4" s="321"/>
+      <c r="E4" s="321"/>
+      <c r="F4" s="321"/>
+      <c r="G4" s="321"/>
+      <c r="H4" s="321"/>
       <c r="L4" s="51"/>
       <c r="M4" s="53"/>
     </row>
@@ -14434,40 +14431,40 @@
       <c r="A19" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="383" t="s">
+      <c r="B19" s="374" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="366" t="s">
+      <c r="C19" s="327" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="367"/>
-      <c r="E19" s="367"/>
-      <c r="F19" s="367"/>
-      <c r="G19" s="368"/>
+      <c r="D19" s="328"/>
+      <c r="E19" s="328"/>
+      <c r="F19" s="328"/>
+      <c r="G19" s="329"/>
       <c r="H19" s="55"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1">
       <c r="A20" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="364"/>
-      <c r="C20" s="369"/>
-      <c r="D20" s="370"/>
-      <c r="E20" s="370"/>
-      <c r="F20" s="370"/>
-      <c r="G20" s="371"/>
+      <c r="B20" s="325"/>
+      <c r="C20" s="330"/>
+      <c r="D20" s="331"/>
+      <c r="E20" s="331"/>
+      <c r="F20" s="331"/>
+      <c r="G20" s="332"/>
       <c r="H20" s="55"/>
     </row>
     <row r="21" spans="1:13" ht="24" customHeight="1">
       <c r="A21" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="365"/>
-      <c r="C21" s="372"/>
-      <c r="D21" s="373"/>
-      <c r="E21" s="373"/>
-      <c r="F21" s="373"/>
-      <c r="G21" s="374"/>
+      <c r="B21" s="326"/>
+      <c r="C21" s="333"/>
+      <c r="D21" s="334"/>
+      <c r="E21" s="334"/>
+      <c r="F21" s="334"/>
+      <c r="G21" s="335"/>
       <c r="H21" s="57" t="s">
         <v>52</v>
       </c>
@@ -14483,17 +14480,17 @@
       <c r="B25" s="57">
         <v>1</v>
       </c>
-      <c r="C25" s="384">
+      <c r="C25" s="375">
         <v>2</v>
       </c>
-      <c r="D25" s="385"/>
+      <c r="D25" s="376"/>
       <c r="E25" s="57">
         <v>3</v>
       </c>
-      <c r="F25" s="384">
+      <c r="F25" s="375">
         <v>4</v>
       </c>
-      <c r="G25" s="385"/>
+      <c r="G25" s="376"/>
       <c r="H25" s="57">
         <v>8</v>
       </c>
@@ -14549,15 +14546,15 @@
       <c r="B29" s="58">
         <v>2</v>
       </c>
-      <c r="C29" s="375" t="s">
+      <c r="C29" s="377" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="376"/>
-      <c r="E29" s="324" t="s">
+      <c r="D29" s="378"/>
+      <c r="E29" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F29" s="325"/>
-      <c r="G29" s="326"/>
+      <c r="F29" s="337"/>
+      <c r="G29" s="338"/>
       <c r="H29" s="64"/>
       <c r="I29" s="49"/>
       <c r="M29" s="65"/>
@@ -14569,15 +14566,15 @@
       <c r="B30" s="58">
         <v>3</v>
       </c>
-      <c r="C30" s="377"/>
-      <c r="D30" s="378"/>
+      <c r="C30" s="379"/>
+      <c r="D30" s="380"/>
       <c r="E30" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="337" t="s">
+      <c r="F30" s="355" t="s">
         <v>56</v>
       </c>
-      <c r="G30" s="339"/>
+      <c r="G30" s="357"/>
       <c r="H30" s="72" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14592,15 +14589,15 @@
       <c r="B31" s="58">
         <v>4</v>
       </c>
-      <c r="C31" s="377"/>
-      <c r="D31" s="378"/>
+      <c r="C31" s="379"/>
+      <c r="D31" s="380"/>
       <c r="E31" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="337" t="s">
+      <c r="F31" s="355" t="s">
         <v>57</v>
       </c>
-      <c r="G31" s="339"/>
+      <c r="G31" s="357"/>
       <c r="H31" s="64"/>
       <c r="I31" s="49"/>
       <c r="M31" s="53"/>
@@ -14612,15 +14609,15 @@
       <c r="B32" s="58">
         <v>5</v>
       </c>
-      <c r="C32" s="377"/>
-      <c r="D32" s="378"/>
+      <c r="C32" s="379"/>
+      <c r="D32" s="380"/>
       <c r="E32" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="337" t="s">
+      <c r="F32" s="355" t="s">
         <v>58</v>
       </c>
-      <c r="G32" s="339"/>
+      <c r="G32" s="357"/>
       <c r="H32" s="64"/>
       <c r="I32" s="49"/>
     </row>
@@ -14640,10 +14637,10 @@
       <c r="E33" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F33" s="320" t="s">
+      <c r="F33" s="345" t="s">
         <v>170</v>
       </c>
-      <c r="G33" s="322"/>
+      <c r="G33" s="347"/>
       <c r="H33" s="64"/>
       <c r="I33" s="49"/>
       <c r="J33" s="49"/>
@@ -14664,10 +14661,10 @@
       <c r="E34" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G34" s="322"/>
+      <c r="F34" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="347"/>
       <c r="H34" s="64"/>
       <c r="I34" s="49"/>
       <c r="J34" s="49"/>
@@ -14680,15 +14677,15 @@
       <c r="B35" s="58">
         <v>8</v>
       </c>
-      <c r="C35" s="375" t="s">
+      <c r="C35" s="377" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="376"/>
-      <c r="E35" s="324" t="s">
+      <c r="D35" s="378"/>
+      <c r="E35" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F35" s="325"/>
-      <c r="G35" s="326"/>
+      <c r="F35" s="337"/>
+      <c r="G35" s="338"/>
       <c r="H35" s="64"/>
       <c r="I35" s="49"/>
     </row>
@@ -14699,15 +14696,15 @@
       <c r="B36" s="58">
         <v>9</v>
       </c>
-      <c r="C36" s="377"/>
-      <c r="D36" s="378"/>
-      <c r="E36" s="331" t="s">
+      <c r="C36" s="379"/>
+      <c r="D36" s="380"/>
+      <c r="E36" s="372" t="s">
         <v>55</v>
       </c>
-      <c r="F36" s="337" t="s">
+      <c r="F36" s="355" t="s">
         <v>172</v>
       </c>
-      <c r="G36" s="339"/>
+      <c r="G36" s="357"/>
       <c r="H36" s="72" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -14724,11 +14721,11 @@
       </c>
       <c r="C37" s="381"/>
       <c r="D37" s="382"/>
-      <c r="E37" s="332"/>
-      <c r="F37" s="337" t="s">
+      <c r="E37" s="373"/>
+      <c r="F37" s="355" t="s">
         <v>173</v>
       </c>
-      <c r="G37" s="339"/>
+      <c r="G37" s="357"/>
       <c r="H37" s="64"/>
       <c r="I37" s="49"/>
     </row>
@@ -14739,15 +14736,15 @@
       <c r="B38" s="58">
         <v>11</v>
       </c>
-      <c r="C38" s="375" t="s">
+      <c r="C38" s="377" t="s">
         <v>174</v>
       </c>
-      <c r="D38" s="376"/>
-      <c r="E38" s="324" t="s">
+      <c r="D38" s="378"/>
+      <c r="E38" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F38" s="325"/>
-      <c r="G38" s="326"/>
+      <c r="F38" s="337"/>
+      <c r="G38" s="338"/>
       <c r="H38" s="64"/>
       <c r="I38" s="49"/>
     </row>
@@ -14758,15 +14755,15 @@
       <c r="B39" s="58">
         <v>12</v>
       </c>
-      <c r="C39" s="377"/>
-      <c r="D39" s="378"/>
+      <c r="C39" s="379"/>
+      <c r="D39" s="380"/>
       <c r="E39" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="G39" s="380"/>
+      <c r="F39" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="G39" s="384"/>
       <c r="H39" s="64"/>
       <c r="I39" s="49"/>
     </row>
@@ -14786,10 +14783,10 @@
       <c r="E40" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G40" s="322"/>
+      <c r="F40" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G40" s="347"/>
       <c r="H40" s="64"/>
       <c r="I40" s="49"/>
       <c r="J40" s="49"/>
@@ -14801,15 +14798,15 @@
       <c r="B41" s="58">
         <v>14</v>
       </c>
-      <c r="C41" s="375" t="s">
+      <c r="C41" s="377" t="s">
         <v>175</v>
       </c>
-      <c r="D41" s="376"/>
-      <c r="E41" s="324" t="s">
+      <c r="D41" s="378"/>
+      <c r="E41" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F41" s="325"/>
-      <c r="G41" s="326"/>
+      <c r="F41" s="337"/>
+      <c r="G41" s="338"/>
       <c r="H41" s="64"/>
       <c r="I41" s="49"/>
     </row>
@@ -14820,15 +14817,15 @@
       <c r="B42" s="58">
         <v>15</v>
       </c>
-      <c r="C42" s="377"/>
-      <c r="D42" s="378"/>
+      <c r="C42" s="379"/>
+      <c r="D42" s="380"/>
       <c r="E42" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="337" t="s">
+      <c r="F42" s="355" t="s">
         <v>91</v>
       </c>
-      <c r="G42" s="339"/>
+      <c r="G42" s="357"/>
       <c r="H42" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14851,10 +14848,10 @@
       <c r="E43" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F43" s="320" t="s">
+      <c r="F43" s="345" t="s">
         <v>176</v>
       </c>
-      <c r="G43" s="322"/>
+      <c r="G43" s="347"/>
       <c r="H43" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14878,10 +14875,10 @@
       <c r="E44" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F44" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G44" s="322"/>
+      <c r="F44" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" s="347"/>
       <c r="H44" s="64"/>
       <c r="I44" s="49"/>
       <c r="J44" s="49"/>
@@ -14893,15 +14890,15 @@
       <c r="B45" s="58">
         <v>18</v>
       </c>
-      <c r="C45" s="375" t="s">
+      <c r="C45" s="377" t="s">
         <v>177</v>
       </c>
-      <c r="D45" s="376"/>
-      <c r="E45" s="324" t="s">
+      <c r="D45" s="378"/>
+      <c r="E45" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="325"/>
-      <c r="G45" s="326"/>
+      <c r="F45" s="337"/>
+      <c r="G45" s="338"/>
       <c r="H45" s="64"/>
       <c r="I45" s="49"/>
     </row>
@@ -14912,15 +14909,15 @@
       <c r="B46" s="58">
         <v>19</v>
       </c>
-      <c r="C46" s="377"/>
-      <c r="D46" s="378"/>
+      <c r="C46" s="379"/>
+      <c r="D46" s="380"/>
       <c r="E46" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="G46" s="380"/>
+      <c r="F46" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" s="384"/>
       <c r="H46" s="64"/>
       <c r="I46" s="49"/>
     </row>
@@ -14940,8 +14937,8 @@
       <c r="E47" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F47" s="320"/>
-      <c r="G47" s="322"/>
+      <c r="F47" s="345"/>
+      <c r="G47" s="347"/>
       <c r="H47" s="64"/>
       <c r="I47" s="49"/>
       <c r="J47" s="49"/>
@@ -14962,10 +14959,10 @@
       <c r="E48" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F48" s="320" t="s">
+      <c r="F48" s="345" t="s">
         <v>178</v>
       </c>
-      <c r="G48" s="322"/>
+      <c r="G48" s="347"/>
       <c r="H48" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14989,10 +14986,10 @@
       <c r="E49" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F49" s="320" t="s">
+      <c r="F49" s="345" t="s">
         <v>8</v>
       </c>
-      <c r="G49" s="322"/>
+      <c r="G49" s="347"/>
       <c r="H49" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15007,13 +15004,13 @@
       <c r="B50" s="58">
         <v>24</v>
       </c>
-      <c r="C50" s="324" t="s">
+      <c r="C50" s="336" t="s">
         <v>179</v>
       </c>
-      <c r="D50" s="325"/>
-      <c r="E50" s="325"/>
-      <c r="F50" s="325"/>
-      <c r="G50" s="326"/>
+      <c r="D50" s="337"/>
+      <c r="E50" s="337"/>
+      <c r="F50" s="337"/>
+      <c r="G50" s="338"/>
       <c r="H50" s="64"/>
       <c r="I50" s="49"/>
     </row>
@@ -15024,13 +15021,13 @@
       <c r="B51" s="58">
         <v>25</v>
       </c>
-      <c r="C51" s="324" t="s">
+      <c r="C51" s="336" t="s">
         <v>180</v>
       </c>
-      <c r="D51" s="325"/>
-      <c r="E51" s="325"/>
-      <c r="F51" s="325"/>
-      <c r="G51" s="326"/>
+      <c r="D51" s="337"/>
+      <c r="E51" s="337"/>
+      <c r="F51" s="337"/>
+      <c r="G51" s="338"/>
       <c r="H51" s="64" t="e">
         <f>нак.расх.!G29-зат.осн.про.!H75-зат.осн.про.!H99</f>
         <v>#REF!</v>
@@ -15076,15 +15073,15 @@
       <c r="B53" s="58">
         <v>2</v>
       </c>
-      <c r="C53" s="375" t="s">
+      <c r="C53" s="377" t="s">
         <v>54</v>
       </c>
-      <c r="D53" s="376"/>
-      <c r="E53" s="324" t="s">
+      <c r="D53" s="378"/>
+      <c r="E53" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F53" s="325"/>
-      <c r="G53" s="326"/>
+      <c r="F53" s="337"/>
+      <c r="G53" s="338"/>
       <c r="H53" s="64"/>
       <c r="I53" s="49"/>
       <c r="M53" s="53" t="e">
@@ -15099,15 +15096,15 @@
       <c r="B54" s="58">
         <v>3</v>
       </c>
-      <c r="C54" s="377"/>
-      <c r="D54" s="378"/>
+      <c r="C54" s="379"/>
+      <c r="D54" s="380"/>
       <c r="E54" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F54" s="337" t="s">
+      <c r="F54" s="355" t="s">
         <v>56</v>
       </c>
-      <c r="G54" s="339"/>
+      <c r="G54" s="357"/>
       <c r="H54" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15121,15 +15118,15 @@
       <c r="B55" s="58">
         <v>4</v>
       </c>
-      <c r="C55" s="377"/>
-      <c r="D55" s="378"/>
+      <c r="C55" s="379"/>
+      <c r="D55" s="380"/>
       <c r="E55" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F55" s="337" t="s">
+      <c r="F55" s="355" t="s">
         <v>57</v>
       </c>
-      <c r="G55" s="339"/>
+      <c r="G55" s="357"/>
       <c r="H55" s="64"/>
       <c r="I55" s="49"/>
     </row>
@@ -15140,15 +15137,15 @@
       <c r="B56" s="58">
         <v>5</v>
       </c>
-      <c r="C56" s="377"/>
-      <c r="D56" s="378"/>
+      <c r="C56" s="379"/>
+      <c r="D56" s="380"/>
       <c r="E56" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="337" t="s">
+      <c r="F56" s="355" t="s">
         <v>58</v>
       </c>
-      <c r="G56" s="339"/>
+      <c r="G56" s="357"/>
       <c r="H56" s="64"/>
       <c r="I56" s="49"/>
     </row>
@@ -15168,10 +15165,10 @@
       <c r="E57" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="320" t="s">
+      <c r="F57" s="345" t="s">
         <v>170</v>
       </c>
-      <c r="G57" s="322"/>
+      <c r="G57" s="347"/>
       <c r="H57" s="64"/>
       <c r="I57" s="49"/>
       <c r="J57" s="49"/>
@@ -15192,10 +15189,10 @@
       <c r="E58" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F58" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G58" s="322"/>
+      <c r="F58" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G58" s="347"/>
       <c r="H58" s="64"/>
       <c r="I58" s="49"/>
     </row>
@@ -15206,15 +15203,15 @@
       <c r="B59" s="58">
         <v>8</v>
       </c>
-      <c r="C59" s="375" t="s">
+      <c r="C59" s="377" t="s">
         <v>171</v>
       </c>
-      <c r="D59" s="376"/>
-      <c r="E59" s="324" t="s">
+      <c r="D59" s="378"/>
+      <c r="E59" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F59" s="325"/>
-      <c r="G59" s="326"/>
+      <c r="F59" s="337"/>
+      <c r="G59" s="338"/>
       <c r="H59" s="64"/>
       <c r="I59" s="49"/>
     </row>
@@ -15225,15 +15222,15 @@
       <c r="B60" s="58">
         <v>9</v>
       </c>
-      <c r="C60" s="377"/>
-      <c r="D60" s="378"/>
-      <c r="E60" s="331" t="s">
+      <c r="C60" s="379"/>
+      <c r="D60" s="380"/>
+      <c r="E60" s="372" t="s">
         <v>55</v>
       </c>
-      <c r="F60" s="337" t="s">
+      <c r="F60" s="355" t="s">
         <v>172</v>
       </c>
-      <c r="G60" s="339"/>
+      <c r="G60" s="357"/>
       <c r="H60" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15249,11 +15246,11 @@
       </c>
       <c r="C61" s="381"/>
       <c r="D61" s="382"/>
-      <c r="E61" s="332"/>
-      <c r="F61" s="337" t="s">
+      <c r="E61" s="373"/>
+      <c r="F61" s="355" t="s">
         <v>173</v>
       </c>
-      <c r="G61" s="339"/>
+      <c r="G61" s="357"/>
       <c r="H61" s="64"/>
       <c r="I61" s="49"/>
     </row>
@@ -15264,15 +15261,15 @@
       <c r="B62" s="58">
         <v>11</v>
       </c>
-      <c r="C62" s="375" t="s">
+      <c r="C62" s="377" t="s">
         <v>174</v>
       </c>
-      <c r="D62" s="376"/>
-      <c r="E62" s="324" t="s">
+      <c r="D62" s="378"/>
+      <c r="E62" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F62" s="325"/>
-      <c r="G62" s="326"/>
+      <c r="F62" s="337"/>
+      <c r="G62" s="338"/>
       <c r="H62" s="64"/>
       <c r="I62" s="49"/>
     </row>
@@ -15283,15 +15280,15 @@
       <c r="B63" s="58">
         <v>12</v>
       </c>
-      <c r="C63" s="377"/>
-      <c r="D63" s="378"/>
+      <c r="C63" s="379"/>
+      <c r="D63" s="380"/>
       <c r="E63" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F63" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="G63" s="380"/>
+      <c r="F63" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="G63" s="384"/>
       <c r="H63" s="64"/>
       <c r="I63" s="49"/>
       <c r="J63" s="49"/>
@@ -15312,10 +15309,10 @@
       <c r="E64" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F64" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G64" s="322"/>
+      <c r="F64" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G64" s="347"/>
       <c r="H64" s="64"/>
       <c r="I64" s="49"/>
     </row>
@@ -15326,15 +15323,15 @@
       <c r="B65" s="58">
         <v>14</v>
       </c>
-      <c r="C65" s="375" t="s">
+      <c r="C65" s="377" t="s">
         <v>175</v>
       </c>
-      <c r="D65" s="376"/>
-      <c r="E65" s="324" t="s">
+      <c r="D65" s="378"/>
+      <c r="E65" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="325"/>
-      <c r="G65" s="326"/>
+      <c r="F65" s="337"/>
+      <c r="G65" s="338"/>
       <c r="H65" s="64"/>
       <c r="I65" s="49"/>
     </row>
@@ -15345,15 +15342,15 @@
       <c r="B66" s="58">
         <v>15</v>
       </c>
-      <c r="C66" s="377"/>
-      <c r="D66" s="378"/>
+      <c r="C66" s="379"/>
+      <c r="D66" s="380"/>
       <c r="E66" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F66" s="337" t="s">
+      <c r="F66" s="355" t="s">
         <v>91</v>
       </c>
-      <c r="G66" s="339"/>
+      <c r="G66" s="357"/>
       <c r="H66" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15377,10 +15374,10 @@
       <c r="E67" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="320" t="s">
+      <c r="F67" s="345" t="s">
         <v>176</v>
       </c>
-      <c r="G67" s="322"/>
+      <c r="G67" s="347"/>
       <c r="H67" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15403,10 +15400,10 @@
       <c r="E68" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F68" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G68" s="322"/>
+      <c r="F68" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G68" s="347"/>
       <c r="H68" s="64"/>
       <c r="I68" s="49"/>
     </row>
@@ -15417,15 +15414,15 @@
       <c r="B69" s="58">
         <v>18</v>
       </c>
-      <c r="C69" s="375" t="s">
+      <c r="C69" s="377" t="s">
         <v>177</v>
       </c>
-      <c r="D69" s="376"/>
-      <c r="E69" s="324" t="s">
+      <c r="D69" s="378"/>
+      <c r="E69" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="325"/>
-      <c r="G69" s="326"/>
+      <c r="F69" s="337"/>
+      <c r="G69" s="338"/>
       <c r="H69" s="64"/>
       <c r="I69" s="49"/>
       <c r="J69" s="49"/>
@@ -15437,15 +15434,15 @@
       <c r="B70" s="58">
         <v>19</v>
       </c>
-      <c r="C70" s="377"/>
-      <c r="D70" s="378"/>
+      <c r="C70" s="379"/>
+      <c r="D70" s="380"/>
       <c r="E70" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F70" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="G70" s="380"/>
+      <c r="F70" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="G70" s="384"/>
       <c r="H70" s="64"/>
       <c r="I70" s="49"/>
     </row>
@@ -15465,8 +15462,8 @@
       <c r="E71" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F71" s="320"/>
-      <c r="G71" s="322"/>
+      <c r="F71" s="345"/>
+      <c r="G71" s="347"/>
       <c r="H71" s="64"/>
       <c r="I71" s="49"/>
     </row>
@@ -15483,10 +15480,10 @@
       <c r="E72" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F72" s="320" t="s">
+      <c r="F72" s="345" t="s">
         <v>178</v>
       </c>
-      <c r="G72" s="322"/>
+      <c r="G72" s="347"/>
       <c r="H72" s="64"/>
       <c r="I72" s="49"/>
       <c r="J72" s="49"/>
@@ -15509,10 +15506,10 @@
       <c r="E73" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F73" s="320" t="s">
+      <c r="F73" s="345" t="s">
         <v>8</v>
       </c>
-      <c r="G73" s="322"/>
+      <c r="G73" s="347"/>
       <c r="H73" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15526,13 +15523,13 @@
       <c r="B74" s="58">
         <v>24</v>
       </c>
-      <c r="C74" s="324" t="s">
+      <c r="C74" s="336" t="s">
         <v>179</v>
       </c>
-      <c r="D74" s="325"/>
-      <c r="E74" s="325"/>
-      <c r="F74" s="325"/>
-      <c r="G74" s="326"/>
+      <c r="D74" s="337"/>
+      <c r="E74" s="337"/>
+      <c r="F74" s="337"/>
+      <c r="G74" s="338"/>
       <c r="H74" s="64"/>
       <c r="I74" s="49"/>
       <c r="J74" s="49"/>
@@ -15543,13 +15540,13 @@
       <c r="B75" s="58">
         <v>25</v>
       </c>
-      <c r="C75" s="324" t="s">
+      <c r="C75" s="336" t="s">
         <v>180</v>
       </c>
-      <c r="D75" s="325"/>
-      <c r="E75" s="325"/>
-      <c r="F75" s="325"/>
-      <c r="G75" s="326"/>
+      <c r="D75" s="337"/>
+      <c r="E75" s="337"/>
+      <c r="F75" s="337"/>
+      <c r="G75" s="338"/>
       <c r="H75" s="64" t="e">
         <f>нак.расх.!G29*4%</f>
         <v>#REF!</v>
@@ -15595,15 +15592,15 @@
       <c r="B77" s="58">
         <v>2</v>
       </c>
-      <c r="C77" s="375" t="s">
+      <c r="C77" s="377" t="s">
         <v>54</v>
       </c>
-      <c r="D77" s="376"/>
-      <c r="E77" s="324" t="s">
+      <c r="D77" s="378"/>
+      <c r="E77" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F77" s="325"/>
-      <c r="G77" s="326"/>
+      <c r="F77" s="337"/>
+      <c r="G77" s="338"/>
       <c r="H77" s="64"/>
       <c r="M77" s="53" t="e">
         <f>H76-M76</f>
@@ -15614,15 +15611,15 @@
       <c r="B78" s="58">
         <v>3</v>
       </c>
-      <c r="C78" s="377"/>
-      <c r="D78" s="378"/>
+      <c r="C78" s="379"/>
+      <c r="D78" s="380"/>
       <c r="E78" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F78" s="337" t="s">
+      <c r="F78" s="355" t="s">
         <v>56</v>
       </c>
-      <c r="G78" s="339"/>
+      <c r="G78" s="357"/>
       <c r="H78" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15632,30 +15629,30 @@
       <c r="B79" s="58">
         <v>4</v>
       </c>
-      <c r="C79" s="377"/>
-      <c r="D79" s="378"/>
+      <c r="C79" s="379"/>
+      <c r="D79" s="380"/>
       <c r="E79" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F79" s="337" t="s">
+      <c r="F79" s="355" t="s">
         <v>57</v>
       </c>
-      <c r="G79" s="339"/>
+      <c r="G79" s="357"/>
       <c r="H79" s="64"/>
     </row>
     <row r="80" spans="1:13" ht="15.75" customHeight="1">
       <c r="B80" s="58">
         <v>5</v>
       </c>
-      <c r="C80" s="377"/>
-      <c r="D80" s="378"/>
+      <c r="C80" s="379"/>
+      <c r="D80" s="380"/>
       <c r="E80" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F80" s="337" t="s">
+      <c r="F80" s="355" t="s">
         <v>58</v>
       </c>
-      <c r="G80" s="339"/>
+      <c r="G80" s="357"/>
       <c r="H80" s="64"/>
     </row>
     <row r="81" spans="2:8" ht="15.75" customHeight="1">
@@ -15671,10 +15668,10 @@
       <c r="E81" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="320" t="s">
+      <c r="F81" s="345" t="s">
         <v>170</v>
       </c>
-      <c r="G81" s="322"/>
+      <c r="G81" s="347"/>
       <c r="H81" s="64"/>
     </row>
     <row r="82" spans="2:8" ht="15.75" customHeight="1">
@@ -15690,40 +15687,40 @@
       <c r="E82" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G82" s="322"/>
+      <c r="F82" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G82" s="347"/>
       <c r="H82" s="64"/>
     </row>
     <row r="83" spans="2:8" ht="15.75" customHeight="1">
       <c r="B83" s="58">
         <v>8</v>
       </c>
-      <c r="C83" s="375" t="s">
+      <c r="C83" s="377" t="s">
         <v>171</v>
       </c>
-      <c r="D83" s="376"/>
-      <c r="E83" s="324" t="s">
+      <c r="D83" s="378"/>
+      <c r="E83" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F83" s="325"/>
-      <c r="G83" s="326"/>
+      <c r="F83" s="337"/>
+      <c r="G83" s="338"/>
       <c r="H83" s="64"/>
     </row>
     <row r="84" spans="2:8" ht="15.75" customHeight="1">
       <c r="B84" s="58">
         <v>9</v>
       </c>
-      <c r="C84" s="377"/>
-      <c r="D84" s="378"/>
-      <c r="E84" s="331" t="s">
+      <c r="C84" s="379"/>
+      <c r="D84" s="380"/>
+      <c r="E84" s="372" t="s">
         <v>55</v>
       </c>
-      <c r="F84" s="337" t="s">
+      <c r="F84" s="355" t="s">
         <v>172</v>
       </c>
-      <c r="G84" s="339"/>
+      <c r="G84" s="357"/>
       <c r="H84" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15735,41 +15732,41 @@
       </c>
       <c r="C85" s="381"/>
       <c r="D85" s="382"/>
-      <c r="E85" s="332"/>
-      <c r="F85" s="337" t="s">
+      <c r="E85" s="373"/>
+      <c r="F85" s="355" t="s">
         <v>173</v>
       </c>
-      <c r="G85" s="339"/>
+      <c r="G85" s="357"/>
       <c r="H85" s="64"/>
     </row>
     <row r="86" spans="2:8" ht="15.75" customHeight="1">
       <c r="B86" s="58">
         <v>11</v>
       </c>
-      <c r="C86" s="375" t="s">
+      <c r="C86" s="377" t="s">
         <v>174</v>
       </c>
-      <c r="D86" s="376"/>
-      <c r="E86" s="324" t="s">
+      <c r="D86" s="378"/>
+      <c r="E86" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F86" s="325"/>
-      <c r="G86" s="326"/>
+      <c r="F86" s="337"/>
+      <c r="G86" s="338"/>
       <c r="H86" s="64"/>
     </row>
     <row r="87" spans="2:8" ht="15.75" customHeight="1">
       <c r="B87" s="58">
         <v>12</v>
       </c>
-      <c r="C87" s="377"/>
-      <c r="D87" s="378"/>
+      <c r="C87" s="379"/>
+      <c r="D87" s="380"/>
       <c r="E87" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F87" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="G87" s="380"/>
+      <c r="F87" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="G87" s="384"/>
       <c r="H87" s="64"/>
     </row>
     <row r="88" spans="2:8" ht="15.75" customHeight="1">
@@ -15785,40 +15782,40 @@
       <c r="E88" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G88" s="322"/>
+      <c r="F88" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G88" s="347"/>
       <c r="H88" s="64"/>
     </row>
     <row r="89" spans="2:8" ht="15.75" customHeight="1">
       <c r="B89" s="58">
         <v>14</v>
       </c>
-      <c r="C89" s="375" t="s">
+      <c r="C89" s="377" t="s">
         <v>175</v>
       </c>
-      <c r="D89" s="376"/>
-      <c r="E89" s="324" t="s">
+      <c r="D89" s="378"/>
+      <c r="E89" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F89" s="325"/>
-      <c r="G89" s="326"/>
+      <c r="F89" s="337"/>
+      <c r="G89" s="338"/>
       <c r="H89" s="64"/>
     </row>
     <row r="90" spans="2:8" ht="15.75" customHeight="1">
       <c r="B90" s="58">
         <v>15</v>
       </c>
-      <c r="C90" s="377"/>
-      <c r="D90" s="378"/>
+      <c r="C90" s="379"/>
+      <c r="D90" s="380"/>
       <c r="E90" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F90" s="337" t="s">
+      <c r="F90" s="355" t="s">
         <v>91</v>
       </c>
-      <c r="G90" s="339"/>
+      <c r="G90" s="357"/>
       <c r="H90" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15837,10 +15834,10 @@
       <c r="E91" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F91" s="320" t="s">
+      <c r="F91" s="345" t="s">
         <v>176</v>
       </c>
-      <c r="G91" s="322"/>
+      <c r="G91" s="347"/>
       <c r="H91" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15859,40 +15856,40 @@
       <c r="E92" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F92" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="G92" s="322"/>
+      <c r="F92" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G92" s="347"/>
       <c r="H92" s="64"/>
     </row>
     <row r="93" spans="2:8" ht="15.75" customHeight="1">
       <c r="B93" s="58">
         <v>18</v>
       </c>
-      <c r="C93" s="375" t="s">
+      <c r="C93" s="377" t="s">
         <v>177</v>
       </c>
-      <c r="D93" s="376"/>
-      <c r="E93" s="324" t="s">
+      <c r="D93" s="378"/>
+      <c r="E93" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F93" s="325"/>
-      <c r="G93" s="326"/>
+      <c r="F93" s="337"/>
+      <c r="G93" s="338"/>
       <c r="H93" s="64"/>
     </row>
     <row r="94" spans="2:8" ht="15.75" customHeight="1">
       <c r="B94" s="58">
         <v>19</v>
       </c>
-      <c r="C94" s="377"/>
-      <c r="D94" s="378"/>
+      <c r="C94" s="379"/>
+      <c r="D94" s="380"/>
       <c r="E94" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F94" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="G94" s="380"/>
+      <c r="F94" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="G94" s="384"/>
       <c r="H94" s="64"/>
     </row>
     <row r="95" spans="2:8" ht="15.75" customHeight="1">
@@ -15908,8 +15905,8 @@
       <c r="E95" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F95" s="320"/>
-      <c r="G95" s="322"/>
+      <c r="F95" s="345"/>
+      <c r="G95" s="347"/>
       <c r="H95" s="64"/>
     </row>
     <row r="96" spans="2:8" ht="32.25" customHeight="1">
@@ -15925,10 +15922,10 @@
       <c r="E96" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F96" s="320" t="s">
+      <c r="F96" s="345" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="322"/>
+      <c r="G96" s="347"/>
       <c r="H96" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15947,34 +15944,34 @@
       <c r="E97" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F97" s="320"/>
-      <c r="G97" s="322"/>
+      <c r="F97" s="345"/>
+      <c r="G97" s="347"/>
       <c r="H97" s="64"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1">
       <c r="B98" s="58">
         <v>24</v>
       </c>
-      <c r="C98" s="324" t="s">
+      <c r="C98" s="336" t="s">
         <v>179</v>
       </c>
-      <c r="D98" s="325"/>
-      <c r="E98" s="325"/>
-      <c r="F98" s="325"/>
-      <c r="G98" s="326"/>
+      <c r="D98" s="337"/>
+      <c r="E98" s="337"/>
+      <c r="F98" s="337"/>
+      <c r="G98" s="338"/>
       <c r="H98" s="64"/>
     </row>
     <row r="99" spans="2:8" ht="15.75" customHeight="1">
       <c r="B99" s="58">
         <v>25</v>
       </c>
-      <c r="C99" s="324" t="s">
+      <c r="C99" s="336" t="s">
         <v>180</v>
       </c>
-      <c r="D99" s="325"/>
-      <c r="E99" s="325"/>
-      <c r="F99" s="325"/>
-      <c r="G99" s="326"/>
+      <c r="D99" s="337"/>
+      <c r="E99" s="337"/>
+      <c r="F99" s="337"/>
+      <c r="G99" s="338"/>
       <c r="H99" s="64" t="e">
         <f>нак.расх.!G29*16%</f>
         <v>#REF!</v>
@@ -15982,6 +15979,87 @@
     </row>
   </sheetData>
   <mergeCells count="94">
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="C93:D94"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="C86:D87"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="C89:D90"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="C83:D85"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C77:D80"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="C62:D63"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="C65:D66"/>
+    <mergeCell ref="E65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="C69:D70"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="C59:D61"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C53:D56"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="C45:D46"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="C35:D37"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B3:H3"/>
@@ -15995,87 +16073,6 @@
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="C35:D37"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="C41:D42"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="C45:D46"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C53:D56"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="C59:D61"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="C62:D63"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="C65:D66"/>
-    <mergeCell ref="E65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="C69:D70"/>
-    <mergeCell ref="E69:G69"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C77:D80"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="C83:D85"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="C86:D87"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="C89:D90"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="C93:D94"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="F95:G95"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="76" orientation="portrait" r:id="rId1"/>
@@ -16104,14 +16101,14 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="358" t="s">
+      <c r="B1" s="319" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="358"/>
-      <c r="D1" s="358"/>
-      <c r="E1" s="358"/>
-      <c r="F1" s="358"/>
-      <c r="G1" s="358"/>
+      <c r="C1" s="319"/>
+      <c r="D1" s="319"/>
+      <c r="E1" s="319"/>
+      <c r="F1" s="319"/>
+      <c r="G1" s="319"/>
       <c r="K1" s="51"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1">
@@ -16142,69 +16139,69 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="358" t="s">
+      <c r="B3" s="319" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="358"/>
-      <c r="D3" s="358"/>
-      <c r="E3" s="358"/>
-      <c r="F3" s="358"/>
-      <c r="G3" s="358"/>
+      <c r="C3" s="319"/>
+      <c r="D3" s="319"/>
+      <c r="E3" s="319"/>
+      <c r="F3" s="319"/>
+      <c r="G3" s="319"/>
       <c r="K3" s="51"/>
     </row>
     <row r="4" spans="1:11" ht="14.25" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="360" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="360"/>
-      <c r="D4" s="360"/>
-      <c r="E4" s="360"/>
-      <c r="F4" s="360"/>
-      <c r="G4" s="360"/>
+      <c r="B4" s="321" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="321"/>
+      <c r="D4" s="321"/>
+      <c r="E4" s="321"/>
+      <c r="F4" s="321"/>
+      <c r="G4" s="321"/>
       <c r="K4" s="51"/>
     </row>
     <row r="5" spans="1:11" ht="24.75" customHeight="1">
       <c r="A5" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="361" t="s">
+      <c r="B5" s="322" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="361"/>
-      <c r="D5" s="361"/>
-      <c r="E5" s="361"/>
-      <c r="F5" s="361"/>
-      <c r="G5" s="361"/>
+      <c r="C5" s="322"/>
+      <c r="D5" s="322"/>
+      <c r="E5" s="322"/>
+      <c r="F5" s="322"/>
+      <c r="G5" s="322"/>
       <c r="K5" s="51"/>
     </row>
     <row r="6" spans="1:11" ht="12" customHeight="1">
       <c r="A6" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="361" t="s">
+      <c r="B6" s="322" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="361"/>
-      <c r="D6" s="361"/>
-      <c r="E6" s="361"/>
-      <c r="F6" s="361"/>
-      <c r="G6" s="361"/>
+      <c r="C6" s="322"/>
+      <c r="D6" s="322"/>
+      <c r="E6" s="322"/>
+      <c r="F6" s="322"/>
+      <c r="G6" s="322"/>
       <c r="K6" s="51"/>
     </row>
     <row r="7" spans="1:11" ht="12" customHeight="1">
       <c r="A7" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="362" t="s">
+      <c r="B7" s="323" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="362"/>
-      <c r="D7" s="362"/>
-      <c r="E7" s="362"/>
-      <c r="F7" s="362"/>
+      <c r="C7" s="323"/>
+      <c r="D7" s="323"/>
+      <c r="E7" s="323"/>
+      <c r="F7" s="323"/>
       <c r="G7" s="71" t="s">
         <v>50</v>
       </c>
@@ -16228,37 +16225,37 @@
       <c r="A22" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="363" t="s">
+      <c r="B22" s="324" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="366" t="s">
+      <c r="C22" s="327" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="367"/>
-      <c r="E22" s="367"/>
-      <c r="F22" s="368"/>
+      <c r="D22" s="328"/>
+      <c r="E22" s="328"/>
+      <c r="F22" s="329"/>
       <c r="G22" s="55"/>
     </row>
     <row r="23" spans="1:12" ht="12" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="364"/>
-      <c r="C23" s="369"/>
-      <c r="D23" s="370"/>
-      <c r="E23" s="370"/>
-      <c r="F23" s="371"/>
+      <c r="B23" s="325"/>
+      <c r="C23" s="330"/>
+      <c r="D23" s="331"/>
+      <c r="E23" s="331"/>
+      <c r="F23" s="332"/>
       <c r="G23" s="55"/>
     </row>
     <row r="24" spans="1:12" ht="24" customHeight="1">
       <c r="A24" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="365"/>
-      <c r="C24" s="372"/>
-      <c r="D24" s="373"/>
-      <c r="E24" s="373"/>
-      <c r="F24" s="374"/>
+      <c r="B24" s="326"/>
+      <c r="C24" s="333"/>
+      <c r="D24" s="334"/>
+      <c r="E24" s="334"/>
+      <c r="F24" s="335"/>
       <c r="G24" s="57" t="s">
         <v>52</v>
       </c>
@@ -16279,10 +16276,10 @@
       <c r="D28" s="57">
         <v>3</v>
       </c>
-      <c r="E28" s="384">
+      <c r="E28" s="375">
         <v>4</v>
       </c>
-      <c r="F28" s="385"/>
+      <c r="F28" s="376"/>
       <c r="G28" s="57">
         <v>8</v>
       </c>
@@ -16294,12 +16291,12 @@
       <c r="B29" s="58">
         <v>1</v>
       </c>
-      <c r="C29" s="324" t="s">
+      <c r="C29" s="336" t="s">
         <v>184</v>
       </c>
-      <c r="D29" s="325"/>
-      <c r="E29" s="325"/>
-      <c r="F29" s="325"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
       <c r="G29" s="72" t="e">
         <f>SUM(G30:G77)</f>
         <v>#REF!</v>
@@ -16319,11 +16316,11 @@
       <c r="C30" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="324" t="s">
+      <c r="D30" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="325"/>
-      <c r="F30" s="325"/>
+      <c r="E30" s="337"/>
+      <c r="F30" s="337"/>
       <c r="G30" s="74"/>
       <c r="L30" s="53" t="e">
         <f>G29-L29</f>
@@ -16343,10 +16340,10 @@
       <c r="D31" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="337" t="s">
+      <c r="E31" s="355" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="338"/>
+      <c r="F31" s="356"/>
       <c r="G31" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16366,10 +16363,10 @@
       <c r="D32" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="337" t="s">
+      <c r="E32" s="355" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="338"/>
+      <c r="F32" s="356"/>
       <c r="G32" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16389,10 +16386,10 @@
       <c r="D33" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E33" s="337" t="s">
+      <c r="E33" s="355" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="338"/>
+      <c r="F33" s="356"/>
       <c r="G33" s="74"/>
     </row>
     <row r="34" spans="1:13" ht="12" customHeight="1">
@@ -16449,10 +16446,10 @@
       <c r="D36" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E36" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="321"/>
+      <c r="E36" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="346"/>
       <c r="G36" s="74"/>
       <c r="H36" s="49"/>
     </row>
@@ -16466,11 +16463,11 @@
       <c r="C37" s="73" t="s">
         <v>171</v>
       </c>
-      <c r="D37" s="324" t="s">
+      <c r="D37" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E37" s="325"/>
-      <c r="F37" s="325"/>
+      <c r="E37" s="337"/>
+      <c r="F37" s="337"/>
       <c r="G37" s="74"/>
     </row>
     <row r="38" spans="1:13" ht="12" customHeight="1">
@@ -16486,10 +16483,10 @@
       <c r="D38" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E38" s="337" t="s">
+      <c r="E38" s="355" t="s">
         <v>172</v>
       </c>
-      <c r="F38" s="338"/>
+      <c r="F38" s="356"/>
       <c r="G38" s="74" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -16509,10 +16506,10 @@
       <c r="D39" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="337" t="s">
+      <c r="E39" s="355" t="s">
         <v>173</v>
       </c>
-      <c r="F39" s="338"/>
+      <c r="F39" s="356"/>
       <c r="G39" s="74"/>
     </row>
     <row r="40" spans="1:13" ht="12" customHeight="1">
@@ -16522,14 +16519,14 @@
       <c r="B40" s="58">
         <v>26</v>
       </c>
-      <c r="C40" s="333" t="s">
+      <c r="C40" s="339" t="s">
         <v>174</v>
       </c>
-      <c r="D40" s="324" t="s">
+      <c r="D40" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E40" s="325"/>
-      <c r="F40" s="325"/>
+      <c r="E40" s="337"/>
+      <c r="F40" s="337"/>
       <c r="G40" s="74"/>
     </row>
     <row r="41" spans="1:13" ht="12" customHeight="1">
@@ -16539,14 +16536,14 @@
       <c r="B41" s="58">
         <v>27</v>
       </c>
-      <c r="C41" s="334"/>
+      <c r="C41" s="340"/>
       <c r="D41" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="F41" s="387"/>
+      <c r="E41" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="385"/>
       <c r="G41" s="74"/>
     </row>
     <row r="42" spans="1:13" ht="12" customHeight="1">
@@ -16562,10 +16559,10 @@
       <c r="D42" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E42" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="321"/>
+      <c r="E42" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" s="346"/>
       <c r="G42" s="74"/>
       <c r="H42" s="49"/>
     </row>
@@ -16576,14 +16573,14 @@
       <c r="B43" s="58">
         <v>29</v>
       </c>
-      <c r="C43" s="333" t="s">
+      <c r="C43" s="339" t="s">
         <v>186</v>
       </c>
-      <c r="D43" s="324" t="s">
+      <c r="D43" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="325"/>
-      <c r="F43" s="325"/>
+      <c r="E43" s="337"/>
+      <c r="F43" s="337"/>
       <c r="G43" s="74"/>
     </row>
     <row r="44" spans="1:13" ht="12" customHeight="1">
@@ -16593,14 +16590,14 @@
       <c r="B44" s="58">
         <v>30</v>
       </c>
-      <c r="C44" s="334"/>
+      <c r="C44" s="340"/>
       <c r="D44" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E44" s="320" t="s">
+      <c r="E44" s="345" t="s">
         <v>128</v>
       </c>
-      <c r="F44" s="321"/>
+      <c r="F44" s="346"/>
       <c r="G44" s="74"/>
     </row>
     <row r="45" spans="1:13" ht="18.75" customHeight="1">
@@ -16610,14 +16607,14 @@
       <c r="B45" s="58">
         <v>31</v>
       </c>
-      <c r="C45" s="350"/>
+      <c r="C45" s="341"/>
       <c r="D45" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E45" s="390" t="s">
+      <c r="E45" s="386" t="s">
         <v>129</v>
       </c>
-      <c r="F45" s="391"/>
+      <c r="F45" s="387"/>
       <c r="G45" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16632,12 +16629,12 @@
       <c r="B46" s="58">
         <v>32</v>
       </c>
-      <c r="C46" s="324" t="s">
+      <c r="C46" s="336" t="s">
         <v>20</v>
       </c>
-      <c r="D46" s="325"/>
-      <c r="E46" s="325"/>
-      <c r="F46" s="325"/>
+      <c r="D46" s="337"/>
+      <c r="E46" s="337"/>
+      <c r="F46" s="337"/>
       <c r="G46" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16654,11 +16651,11 @@
       <c r="C47" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="D47" s="324" t="s">
+      <c r="D47" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E47" s="325"/>
-      <c r="F47" s="325"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
       <c r="G47" s="74"/>
       <c r="L47" s="53"/>
     </row>
@@ -16675,10 +16672,10 @@
       <c r="D48" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E48" s="337" t="s">
+      <c r="E48" s="355" t="s">
         <v>63</v>
       </c>
-      <c r="F48" s="338"/>
+      <c r="F48" s="356"/>
       <c r="G48" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16697,10 +16694,10 @@
       <c r="D49" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E49" s="337" t="s">
+      <c r="E49" s="355" t="s">
         <v>64</v>
       </c>
-      <c r="F49" s="338"/>
+      <c r="F49" s="356"/>
       <c r="G49" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16713,14 +16710,14 @@
       <c r="B50" s="58">
         <v>36</v>
       </c>
-      <c r="C50" s="333" t="s">
+      <c r="C50" s="339" t="s">
         <v>187</v>
       </c>
-      <c r="D50" s="324" t="s">
+      <c r="D50" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E50" s="325"/>
-      <c r="F50" s="325"/>
+      <c r="E50" s="337"/>
+      <c r="F50" s="337"/>
       <c r="G50" s="74"/>
     </row>
     <row r="51" spans="1:8" ht="12" customHeight="1">
@@ -16730,14 +16727,14 @@
       <c r="B51" s="58">
         <v>37</v>
       </c>
-      <c r="C51" s="334"/>
+      <c r="C51" s="340"/>
       <c r="D51" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E51" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="387"/>
+      <c r="E51" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="385"/>
       <c r="G51" s="74"/>
     </row>
     <row r="52" spans="1:8" ht="24.75" customHeight="1">
@@ -16753,10 +16750,10 @@
       <c r="D52" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E52" s="320" t="s">
+      <c r="E52" s="345" t="s">
         <v>188</v>
       </c>
-      <c r="F52" s="321"/>
+      <c r="F52" s="346"/>
       <c r="G52" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16770,12 +16767,12 @@
       <c r="B53" s="58">
         <v>43</v>
       </c>
-      <c r="C53" s="324" t="s">
+      <c r="C53" s="336" t="s">
         <v>16</v>
       </c>
-      <c r="D53" s="325"/>
-      <c r="E53" s="325"/>
-      <c r="F53" s="325"/>
+      <c r="D53" s="337"/>
+      <c r="E53" s="337"/>
+      <c r="F53" s="337"/>
       <c r="G53" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16788,12 +16785,12 @@
       <c r="B54" s="58">
         <v>44</v>
       </c>
-      <c r="C54" s="324" t="s">
+      <c r="C54" s="336" t="s">
         <v>14</v>
       </c>
-      <c r="D54" s="325"/>
-      <c r="E54" s="325"/>
-      <c r="F54" s="325"/>
+      <c r="D54" s="337"/>
+      <c r="E54" s="337"/>
+      <c r="F54" s="337"/>
       <c r="G54" s="74"/>
     </row>
     <row r="55" spans="1:8" ht="12" customHeight="1">
@@ -16806,11 +16803,11 @@
       <c r="C55" s="73" t="s">
         <v>137</v>
       </c>
-      <c r="D55" s="324" t="s">
+      <c r="D55" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="325"/>
-      <c r="F55" s="325"/>
+      <c r="E55" s="337"/>
+      <c r="F55" s="337"/>
       <c r="G55" s="74"/>
     </row>
     <row r="56" spans="1:8" ht="12" customHeight="1">
@@ -16826,10 +16823,10 @@
       <c r="D56" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="F56" s="387"/>
+      <c r="E56" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" s="385"/>
       <c r="G56" s="74"/>
     </row>
     <row r="57" spans="1:8" ht="24.75" customHeight="1">
@@ -16845,10 +16842,10 @@
       <c r="D57" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="320" t="s">
+      <c r="E57" s="345" t="s">
         <v>4</v>
       </c>
-      <c r="F57" s="321"/>
+      <c r="F57" s="346"/>
       <c r="G57" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16868,10 +16865,10 @@
       <c r="D58" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F58" s="321"/>
+      <c r="E58" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F58" s="346"/>
       <c r="G58" s="74"/>
       <c r="H58" s="49"/>
     </row>
@@ -16882,12 +16879,12 @@
       <c r="B59" s="58">
         <v>51</v>
       </c>
-      <c r="C59" s="324" t="s">
+      <c r="C59" s="336" t="s">
         <v>189</v>
       </c>
-      <c r="D59" s="325"/>
-      <c r="E59" s="325"/>
-      <c r="F59" s="325"/>
+      <c r="D59" s="337"/>
+      <c r="E59" s="337"/>
+      <c r="F59" s="337"/>
       <c r="G59" s="74"/>
     </row>
     <row r="60" spans="1:8" ht="12" customHeight="1">
@@ -16897,12 +16894,12 @@
       <c r="B60" s="58">
         <v>52</v>
       </c>
-      <c r="C60" s="324" t="s">
+      <c r="C60" s="336" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="325"/>
-      <c r="E60" s="325"/>
-      <c r="F60" s="325"/>
+      <c r="D60" s="337"/>
+      <c r="E60" s="337"/>
+      <c r="F60" s="337"/>
       <c r="G60" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16915,12 +16912,12 @@
       <c r="B61" s="58">
         <v>53</v>
       </c>
-      <c r="C61" s="324" t="s">
+      <c r="C61" s="336" t="s">
         <v>190</v>
       </c>
-      <c r="D61" s="325"/>
-      <c r="E61" s="325"/>
-      <c r="F61" s="325"/>
+      <c r="D61" s="337"/>
+      <c r="E61" s="337"/>
+      <c r="F61" s="337"/>
       <c r="G61" s="74"/>
     </row>
     <row r="62" spans="1:8" ht="12" customHeight="1">
@@ -16930,12 +16927,12 @@
       <c r="B62" s="58">
         <v>54</v>
       </c>
-      <c r="C62" s="324" t="s">
+      <c r="C62" s="336" t="s">
         <v>191</v>
       </c>
-      <c r="D62" s="325"/>
-      <c r="E62" s="325"/>
-      <c r="F62" s="325"/>
+      <c r="D62" s="337"/>
+      <c r="E62" s="337"/>
+      <c r="F62" s="337"/>
       <c r="G62" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16948,12 +16945,12 @@
       <c r="B63" s="58">
         <v>55</v>
       </c>
-      <c r="C63" s="324" t="s">
+      <c r="C63" s="336" t="s">
         <v>192</v>
       </c>
-      <c r="D63" s="325"/>
-      <c r="E63" s="325"/>
-      <c r="F63" s="325"/>
+      <c r="D63" s="337"/>
+      <c r="E63" s="337"/>
+      <c r="F63" s="337"/>
       <c r="G63" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16966,14 +16963,14 @@
       <c r="B64" s="58">
         <v>56</v>
       </c>
-      <c r="C64" s="333" t="s">
+      <c r="C64" s="339" t="s">
         <v>175</v>
       </c>
-      <c r="D64" s="324" t="s">
+      <c r="D64" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E64" s="325"/>
-      <c r="F64" s="325"/>
+      <c r="E64" s="337"/>
+      <c r="F64" s="337"/>
       <c r="G64" s="74"/>
     </row>
     <row r="65" spans="1:11" ht="12" customHeight="1">
@@ -16983,14 +16980,14 @@
       <c r="B65" s="58">
         <v>57</v>
       </c>
-      <c r="C65" s="334"/>
+      <c r="C65" s="340"/>
       <c r="D65" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E65" s="337" t="s">
+      <c r="E65" s="355" t="s">
         <v>91</v>
       </c>
-      <c r="F65" s="338"/>
+      <c r="F65" s="356"/>
       <c r="G65" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17009,10 +17006,10 @@
       <c r="D66" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E66" s="320" t="s">
+      <c r="E66" s="345" t="s">
         <v>193</v>
       </c>
-      <c r="F66" s="321"/>
+      <c r="F66" s="346"/>
       <c r="G66" s="74"/>
       <c r="H66" s="49"/>
     </row>
@@ -17023,14 +17020,14 @@
       <c r="B67" s="58">
         <v>59</v>
       </c>
-      <c r="C67" s="333" t="s">
+      <c r="C67" s="339" t="s">
         <v>102</v>
       </c>
-      <c r="D67" s="324" t="s">
+      <c r="D67" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E67" s="325"/>
-      <c r="F67" s="325"/>
+      <c r="E67" s="337"/>
+      <c r="F67" s="337"/>
       <c r="G67" s="74"/>
     </row>
     <row r="68" spans="1:11" ht="12" customHeight="1">
@@ -17040,14 +17037,14 @@
       <c r="B68" s="58">
         <v>60</v>
       </c>
-      <c r="C68" s="334"/>
+      <c r="C68" s="340"/>
       <c r="D68" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E68" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="F68" s="387"/>
+      <c r="E68" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="F68" s="385"/>
       <c r="G68" s="74"/>
     </row>
     <row r="69" spans="1:11" ht="12" customHeight="1">
@@ -17063,10 +17060,10 @@
       <c r="D69" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E69" s="320" t="s">
+      <c r="E69" s="345" t="s">
         <v>194</v>
       </c>
-      <c r="F69" s="321"/>
+      <c r="F69" s="346"/>
       <c r="G69" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17086,10 +17083,10 @@
       <c r="D70" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E70" s="320" t="s">
+      <c r="E70" s="345" t="s">
         <v>195</v>
       </c>
-      <c r="F70" s="321"/>
+      <c r="F70" s="346"/>
       <c r="G70" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17162,10 +17159,10 @@
       <c r="D74" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E74" s="320" t="s">
-        <v>44</v>
-      </c>
-      <c r="F74" s="321"/>
+      <c r="E74" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F74" s="346"/>
       <c r="G74" s="74"/>
       <c r="H74" s="49"/>
     </row>
@@ -17176,14 +17173,14 @@
       <c r="B75" s="58">
         <v>65</v>
       </c>
-      <c r="C75" s="333" t="s">
+      <c r="C75" s="339" t="s">
         <v>197</v>
       </c>
-      <c r="D75" s="324" t="s">
+      <c r="D75" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E75" s="325"/>
-      <c r="F75" s="325"/>
+      <c r="E75" s="337"/>
+      <c r="F75" s="337"/>
       <c r="G75" s="74"/>
     </row>
     <row r="76" spans="1:11" ht="12" customHeight="1">
@@ -17193,14 +17190,14 @@
       <c r="B76" s="58">
         <v>66</v>
       </c>
-      <c r="C76" s="334"/>
+      <c r="C76" s="340"/>
       <c r="D76" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E76" s="379" t="s">
-        <v>44</v>
-      </c>
-      <c r="F76" s="387"/>
+      <c r="E76" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="F76" s="385"/>
       <c r="G76" s="74"/>
     </row>
     <row r="77" spans="1:11" ht="12" customHeight="1">
@@ -17216,10 +17213,10 @@
       <c r="D77" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E77" s="320" t="s">
+      <c r="E77" s="345" t="s">
         <v>198</v>
       </c>
-      <c r="F77" s="321"/>
+      <c r="F77" s="346"/>
       <c r="G77" s="81" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -17278,13 +17275,13 @@
       <c r="K79" s="51"/>
     </row>
     <row r="80" spans="1:11" ht="15" customHeight="1">
-      <c r="B80" s="386" t="s">
+      <c r="B80" s="390" t="s">
         <v>199</v>
       </c>
-      <c r="C80" s="386"/>
-      <c r="D80" s="386"/>
-      <c r="E80" s="386"/>
-      <c r="F80" s="386"/>
+      <c r="C80" s="390"/>
+      <c r="D80" s="390"/>
+      <c r="E80" s="390"/>
+      <c r="F80" s="390"/>
       <c r="G80" s="83"/>
       <c r="H80" s="83"/>
       <c r="I80" s="82"/>
@@ -17292,13 +17289,13 @@
       <c r="K80" s="51"/>
     </row>
     <row r="81" spans="2:11" ht="15" customHeight="1">
-      <c r="B81" s="386" t="s">
-        <v>44</v>
-      </c>
-      <c r="C81" s="386"/>
-      <c r="D81" s="386"/>
-      <c r="E81" s="386"/>
-      <c r="F81" s="386"/>
+      <c r="B81" s="390" t="s">
+        <v>44</v>
+      </c>
+      <c r="C81" s="390"/>
+      <c r="D81" s="390"/>
+      <c r="E81" s="390"/>
+      <c r="F81" s="390"/>
       <c r="G81" s="84"/>
       <c r="H81" s="84"/>
       <c r="I81" s="83"/>
@@ -17308,14 +17305,14 @@
     <row r="82" spans="2:11" ht="15.75" hidden="1" customHeight="1"/>
     <row r="83" spans="2:11" ht="15.75" hidden="1" customHeight="1"/>
     <row r="84" spans="2:11" ht="15" customHeight="1">
-      <c r="B84" s="386" t="s">
+      <c r="B84" s="390" t="s">
         <v>200</v>
       </c>
-      <c r="C84" s="386"/>
-      <c r="D84" s="386"/>
-      <c r="E84" s="386"/>
-      <c r="F84" s="386"/>
-      <c r="G84" s="386"/>
+      <c r="C84" s="390"/>
+      <c r="D84" s="390"/>
+      <c r="E84" s="390"/>
+      <c r="F84" s="390"/>
+      <c r="G84" s="390"/>
       <c r="H84" s="83"/>
       <c r="I84" s="83"/>
       <c r="J84" s="83"/>
@@ -17344,51 +17341,13 @@
     <row r="105" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:F24"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="C63:F63"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="C53:F53"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C59:F59"/>
-    <mergeCell ref="C60:F60"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="B84:G84"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
     <mergeCell ref="E74:F74"/>
     <mergeCell ref="C64:C65"/>
     <mergeCell ref="D64:F64"/>
@@ -17402,13 +17361,51 @@
     <mergeCell ref="E71:F71"/>
     <mergeCell ref="E72:F72"/>
     <mergeCell ref="E73:F73"/>
-    <mergeCell ref="B84:G84"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C59:F59"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:F24"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Наименование на государственном языке заполняется автоматически в соответствии с КТРУ" sqref="B76 B49:B50 B95:B96"/>
@@ -17444,79 +17441,79 @@
       <c r="A1" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="400" t="s">
+      <c r="B1" s="430" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="400"/>
-      <c r="D1" s="400"/>
-      <c r="E1" s="400"/>
-      <c r="F1" s="400"/>
-      <c r="G1" s="400"/>
-      <c r="H1" s="400"/>
-      <c r="I1" s="400"/>
+      <c r="C1" s="430"/>
+      <c r="D1" s="430"/>
+      <c r="E1" s="430"/>
+      <c r="F1" s="430"/>
+      <c r="G1" s="430"/>
+      <c r="H1" s="430"/>
+      <c r="I1" s="430"/>
       <c r="M1" s="12"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1">
       <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="401" t="s">
+      <c r="B2" s="431" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="401"/>
-      <c r="D2" s="401"/>
-      <c r="E2" s="401"/>
-      <c r="F2" s="401"/>
-      <c r="G2" s="401"/>
-      <c r="H2" s="401"/>
-      <c r="I2" s="401"/>
+      <c r="C2" s="431"/>
+      <c r="D2" s="431"/>
+      <c r="E2" s="431"/>
+      <c r="F2" s="431"/>
+      <c r="G2" s="431"/>
+      <c r="H2" s="431"/>
+      <c r="I2" s="431"/>
       <c r="M2" s="12"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="402" t="s">
+      <c r="B3" s="432" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="402"/>
-      <c r="D3" s="402"/>
-      <c r="E3" s="402"/>
-      <c r="F3" s="402"/>
-      <c r="G3" s="402"/>
-      <c r="H3" s="402"/>
-      <c r="I3" s="402"/>
+      <c r="C3" s="432"/>
+      <c r="D3" s="432"/>
+      <c r="E3" s="432"/>
+      <c r="F3" s="432"/>
+      <c r="G3" s="432"/>
+      <c r="H3" s="432"/>
+      <c r="I3" s="432"/>
       <c r="M3" s="12"/>
     </row>
     <row r="4" spans="1:13" ht="30" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="402" t="s">
+      <c r="B4" s="432" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="402"/>
-      <c r="D4" s="402"/>
-      <c r="E4" s="402"/>
-      <c r="F4" s="402"/>
-      <c r="G4" s="402"/>
-      <c r="H4" s="402"/>
-      <c r="I4" s="402"/>
+      <c r="C4" s="432"/>
+      <c r="D4" s="432"/>
+      <c r="E4" s="432"/>
+      <c r="F4" s="432"/>
+      <c r="G4" s="432"/>
+      <c r="H4" s="432"/>
+      <c r="I4" s="432"/>
       <c r="M4" s="12"/>
     </row>
     <row r="5" spans="1:13" ht="12" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="403" t="s">
+      <c r="B5" s="433" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="403"/>
-      <c r="D5" s="403"/>
-      <c r="E5" s="403"/>
-      <c r="F5" s="403"/>
-      <c r="G5" s="403"/>
-      <c r="H5" s="403"/>
+      <c r="C5" s="433"/>
+      <c r="D5" s="433"/>
+      <c r="E5" s="433"/>
+      <c r="F5" s="433"/>
+      <c r="G5" s="433"/>
+      <c r="H5" s="433"/>
       <c r="I5" s="13" t="s">
         <v>50</v>
       </c>
@@ -17540,18 +17537,18 @@
       <c r="A20" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="404" t="s">
+      <c r="B20" s="434" t="s">
         <v>0</v>
       </c>
-      <c r="C20" s="407" t="s">
+      <c r="C20" s="437" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="408"/>
-      <c r="E20" s="408"/>
-      <c r="F20" s="408"/>
-      <c r="G20" s="408"/>
-      <c r="H20" s="409"/>
-      <c r="I20" s="416" t="s">
+      <c r="D20" s="438"/>
+      <c r="E20" s="438"/>
+      <c r="F20" s="438"/>
+      <c r="G20" s="438"/>
+      <c r="H20" s="439"/>
+      <c r="I20" s="446" t="s">
         <v>52</v>
       </c>
       <c r="J20" s="10"/>
@@ -17564,14 +17561,14 @@
       <c r="A21" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="405"/>
-      <c r="C21" s="410"/>
-      <c r="D21" s="411"/>
-      <c r="E21" s="411"/>
-      <c r="F21" s="411"/>
-      <c r="G21" s="411"/>
-      <c r="H21" s="412"/>
-      <c r="I21" s="405"/>
+      <c r="B21" s="435"/>
+      <c r="C21" s="440"/>
+      <c r="D21" s="441"/>
+      <c r="E21" s="441"/>
+      <c r="F21" s="441"/>
+      <c r="G21" s="441"/>
+      <c r="H21" s="442"/>
+      <c r="I21" s="435"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
@@ -17581,14 +17578,14 @@
       <c r="A22" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="406"/>
-      <c r="C22" s="413"/>
-      <c r="D22" s="414"/>
-      <c r="E22" s="414"/>
-      <c r="F22" s="414"/>
-      <c r="G22" s="414"/>
-      <c r="H22" s="415"/>
-      <c r="I22" s="406"/>
+      <c r="B22" s="436"/>
+      <c r="C22" s="443"/>
+      <c r="D22" s="444"/>
+      <c r="E22" s="444"/>
+      <c r="F22" s="444"/>
+      <c r="G22" s="444"/>
+      <c r="H22" s="445"/>
+      <c r="I22" s="436"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
@@ -17604,10 +17601,10 @@
       <c r="B26" s="18">
         <v>1</v>
       </c>
-      <c r="C26" s="392">
+      <c r="C26" s="428">
         <v>2</v>
       </c>
-      <c r="D26" s="393"/>
+      <c r="D26" s="429"/>
       <c r="E26" s="18">
         <v>3</v>
       </c>
@@ -17686,11 +17683,11 @@
       <c r="E29" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="397" t="s">
+      <c r="F29" s="401" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="398"/>
-      <c r="H29" s="399"/>
+      <c r="G29" s="402"/>
+      <c r="H29" s="403"/>
       <c r="I29" s="20" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17716,11 +17713,11 @@
       <c r="E30" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="397" t="s">
+      <c r="F30" s="401" t="s">
         <v>57</v>
       </c>
-      <c r="G30" s="398"/>
-      <c r="H30" s="399"/>
+      <c r="G30" s="402"/>
+      <c r="H30" s="403"/>
       <c r="I30" s="20" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17743,11 +17740,11 @@
       <c r="E31" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="397" t="s">
+      <c r="F31" s="401" t="s">
         <v>58</v>
       </c>
-      <c r="G31" s="398"/>
-      <c r="H31" s="399"/>
+      <c r="G31" s="402"/>
+      <c r="H31" s="403"/>
       <c r="I31" s="20"/>
     </row>
     <row r="32" spans="1:14" ht="12" customHeight="1">
@@ -17766,11 +17763,11 @@
       <c r="E32" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="417" t="s">
+      <c r="F32" s="391" t="s">
         <v>59</v>
       </c>
-      <c r="G32" s="418"/>
-      <c r="H32" s="419"/>
+      <c r="G32" s="392"/>
+      <c r="H32" s="393"/>
       <c r="I32" s="20" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -17796,10 +17793,10 @@
       <c r="B34" s="21">
         <v>7</v>
       </c>
-      <c r="C34" s="420" t="s">
+      <c r="C34" s="397" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="421"/>
+      <c r="D34" s="398"/>
       <c r="E34" s="394" t="s">
         <v>5</v>
       </c>
@@ -17815,16 +17812,16 @@
       <c r="B35" s="21">
         <v>8</v>
       </c>
-      <c r="C35" s="422"/>
-      <c r="D35" s="423"/>
+      <c r="C35" s="399"/>
+      <c r="D35" s="400"/>
       <c r="E35" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F35" s="397" t="s">
-        <v>44</v>
-      </c>
-      <c r="G35" s="398"/>
-      <c r="H35" s="399"/>
+      <c r="F35" s="401" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" s="402"/>
+      <c r="H35" s="403"/>
       <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:15" hidden="1">
@@ -17837,10 +17834,10 @@
       <c r="B37" s="21">
         <v>10</v>
       </c>
-      <c r="C37" s="424" t="s">
+      <c r="C37" s="407" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="425"/>
+      <c r="D37" s="408"/>
       <c r="E37" s="394" t="s">
         <v>5</v>
       </c>
@@ -17856,16 +17853,16 @@
       <c r="B38" s="21">
         <v>11</v>
       </c>
-      <c r="C38" s="426"/>
-      <c r="D38" s="427"/>
-      <c r="E38" s="430" t="s">
+      <c r="C38" s="409"/>
+      <c r="D38" s="410"/>
+      <c r="E38" s="413" t="s">
         <v>55</v>
       </c>
-      <c r="F38" s="397" t="s">
+      <c r="F38" s="401" t="s">
         <v>63</v>
       </c>
-      <c r="G38" s="398"/>
-      <c r="H38" s="399"/>
+      <c r="G38" s="402"/>
+      <c r="H38" s="403"/>
       <c r="I38" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17878,14 +17875,14 @@
       <c r="B39" s="21">
         <v>12</v>
       </c>
-      <c r="C39" s="428"/>
-      <c r="D39" s="429"/>
-      <c r="E39" s="431"/>
-      <c r="F39" s="397" t="s">
+      <c r="C39" s="411"/>
+      <c r="D39" s="412"/>
+      <c r="E39" s="414"/>
+      <c r="F39" s="401" t="s">
         <v>64</v>
       </c>
-      <c r="G39" s="398"/>
-      <c r="H39" s="399"/>
+      <c r="G39" s="402"/>
+      <c r="H39" s="403"/>
       <c r="I39" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17898,10 +17895,10 @@
       <c r="B40" s="21">
         <v>13</v>
       </c>
-      <c r="C40" s="420" t="s">
+      <c r="C40" s="397" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="421"/>
+      <c r="D40" s="398"/>
       <c r="E40" s="394" t="s">
         <v>5</v>
       </c>
@@ -17917,16 +17914,16 @@
       <c r="B41" s="21">
         <v>14</v>
       </c>
-      <c r="C41" s="422"/>
-      <c r="D41" s="423"/>
+      <c r="C41" s="399"/>
+      <c r="D41" s="400"/>
       <c r="E41" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F41" s="397" t="s">
-        <v>44</v>
-      </c>
-      <c r="G41" s="398"/>
-      <c r="H41" s="399"/>
+      <c r="F41" s="401" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" s="402"/>
+      <c r="H41" s="403"/>
       <c r="I41" s="32"/>
     </row>
     <row r="42" spans="1:15" ht="12" customHeight="1">
@@ -17945,11 +17942,11 @@
       <c r="E42" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F42" s="417" t="s">
+      <c r="F42" s="391" t="s">
         <v>66</v>
       </c>
-      <c r="G42" s="418"/>
-      <c r="H42" s="419"/>
+      <c r="G42" s="392"/>
+      <c r="H42" s="393"/>
       <c r="I42" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17983,10 +17980,10 @@
       <c r="B45" s="21">
         <v>18</v>
       </c>
-      <c r="C45" s="432" t="s">
+      <c r="C45" s="422" t="s">
         <v>68</v>
       </c>
-      <c r="D45" s="433"/>
+      <c r="D45" s="423"/>
       <c r="E45" s="394" t="s">
         <v>5</v>
       </c>
@@ -18002,16 +17999,16 @@
       <c r="B46" s="21">
         <v>19</v>
       </c>
-      <c r="C46" s="434"/>
-      <c r="D46" s="435"/>
-      <c r="E46" s="430" t="s">
+      <c r="C46" s="424"/>
+      <c r="D46" s="425"/>
+      <c r="E46" s="413" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="397" t="s">
+      <c r="F46" s="401" t="s">
         <v>69</v>
       </c>
-      <c r="G46" s="398"/>
-      <c r="H46" s="399"/>
+      <c r="G46" s="402"/>
+      <c r="H46" s="403"/>
       <c r="I46" s="127" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18026,14 +18023,14 @@
       <c r="B47" s="21">
         <v>20</v>
       </c>
-      <c r="C47" s="434"/>
-      <c r="D47" s="435"/>
-      <c r="E47" s="438"/>
-      <c r="F47" s="397" t="s">
+      <c r="C47" s="424"/>
+      <c r="D47" s="425"/>
+      <c r="E47" s="415"/>
+      <c r="F47" s="401" t="s">
         <v>70</v>
       </c>
-      <c r="G47" s="398"/>
-      <c r="H47" s="399"/>
+      <c r="G47" s="402"/>
+      <c r="H47" s="403"/>
       <c r="I47" s="127" t="e">
         <f>#REF!+#REF!-#REF!</f>
         <v>#REF!</v>
@@ -18048,14 +18045,14 @@
       <c r="B48" s="21">
         <v>21</v>
       </c>
-      <c r="C48" s="434"/>
-      <c r="D48" s="435"/>
-      <c r="E48" s="438"/>
-      <c r="F48" s="397" t="s">
+      <c r="C48" s="424"/>
+      <c r="D48" s="425"/>
+      <c r="E48" s="415"/>
+      <c r="F48" s="401" t="s">
         <v>71</v>
       </c>
-      <c r="G48" s="398"/>
-      <c r="H48" s="399"/>
+      <c r="G48" s="402"/>
+      <c r="H48" s="403"/>
       <c r="I48" s="127" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18069,14 +18066,14 @@
       <c r="B49" s="21">
         <v>22</v>
       </c>
-      <c r="C49" s="436"/>
-      <c r="D49" s="437"/>
-      <c r="E49" s="431"/>
-      <c r="F49" s="397" t="s">
+      <c r="C49" s="426"/>
+      <c r="D49" s="427"/>
+      <c r="E49" s="414"/>
+      <c r="F49" s="401" t="s">
         <v>72</v>
       </c>
-      <c r="G49" s="398"/>
-      <c r="H49" s="399"/>
+      <c r="G49" s="402"/>
+      <c r="H49" s="403"/>
       <c r="I49" s="34" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18090,10 +18087,10 @@
       <c r="B50" s="21">
         <v>23</v>
       </c>
-      <c r="C50" s="439" t="s">
+      <c r="C50" s="418" t="s">
         <v>73</v>
       </c>
-      <c r="D50" s="440"/>
+      <c r="D50" s="419"/>
       <c r="E50" s="394" t="s">
         <v>5</v>
       </c>
@@ -18109,16 +18106,16 @@
       <c r="B51" s="21">
         <v>24</v>
       </c>
-      <c r="C51" s="441"/>
-      <c r="D51" s="442"/>
+      <c r="C51" s="420"/>
+      <c r="D51" s="421"/>
       <c r="E51" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="397" t="s">
+      <c r="F51" s="401" t="s">
         <v>23</v>
       </c>
-      <c r="G51" s="398"/>
-      <c r="H51" s="399"/>
+      <c r="G51" s="402"/>
+      <c r="H51" s="403"/>
       <c r="I51" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18141,11 +18138,11 @@
       <c r="E52" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="397" t="s">
+      <c r="F52" s="401" t="s">
         <v>74</v>
       </c>
-      <c r="G52" s="398"/>
-      <c r="H52" s="399"/>
+      <c r="G52" s="402"/>
+      <c r="H52" s="403"/>
       <c r="I52" s="32"/>
       <c r="N52" s="35"/>
     </row>
@@ -18159,10 +18156,10 @@
       <c r="B54" s="21">
         <v>27</v>
       </c>
-      <c r="C54" s="420" t="s">
+      <c r="C54" s="397" t="s">
         <v>75</v>
       </c>
-      <c r="D54" s="421"/>
+      <c r="D54" s="398"/>
       <c r="E54" s="394" t="s">
         <v>5</v>
       </c>
@@ -18178,16 +18175,16 @@
       <c r="B55" s="21">
         <v>28</v>
       </c>
-      <c r="C55" s="422"/>
-      <c r="D55" s="423"/>
+      <c r="C55" s="399"/>
+      <c r="D55" s="400"/>
       <c r="E55" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F55" s="397" t="s">
+      <c r="F55" s="401" t="s">
         <v>76</v>
       </c>
-      <c r="G55" s="398"/>
-      <c r="H55" s="399"/>
+      <c r="G55" s="402"/>
+      <c r="H55" s="403"/>
       <c r="I55" s="32"/>
     </row>
     <row r="56" spans="1:14" ht="12" customHeight="1">
@@ -18197,16 +18194,16 @@
       <c r="B56" s="21">
         <v>29</v>
       </c>
-      <c r="C56" s="422"/>
-      <c r="D56" s="423"/>
+      <c r="C56" s="399"/>
+      <c r="D56" s="400"/>
       <c r="E56" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="397" t="s">
+      <c r="F56" s="401" t="s">
         <v>77</v>
       </c>
-      <c r="G56" s="398"/>
-      <c r="H56" s="399"/>
+      <c r="G56" s="402"/>
+      <c r="H56" s="403"/>
       <c r="I56" s="32"/>
     </row>
     <row r="57" spans="1:14" ht="12" customHeight="1">
@@ -18216,16 +18213,16 @@
       <c r="B57" s="21">
         <v>30</v>
       </c>
-      <c r="C57" s="422"/>
-      <c r="D57" s="423"/>
+      <c r="C57" s="399"/>
+      <c r="D57" s="400"/>
       <c r="E57" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="397" t="s">
+      <c r="F57" s="401" t="s">
         <v>78</v>
       </c>
-      <c r="G57" s="398"/>
-      <c r="H57" s="399"/>
+      <c r="G57" s="402"/>
+      <c r="H57" s="403"/>
       <c r="I57" s="32"/>
     </row>
     <row r="58" spans="1:14" ht="12" customHeight="1">
@@ -18244,11 +18241,11 @@
       <c r="E58" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F58" s="397" t="s">
+      <c r="F58" s="401" t="s">
         <v>79</v>
       </c>
-      <c r="G58" s="398"/>
-      <c r="H58" s="399"/>
+      <c r="G58" s="402"/>
+      <c r="H58" s="403"/>
       <c r="I58" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18281,10 +18278,10 @@
       <c r="B61" s="21">
         <v>34</v>
       </c>
-      <c r="C61" s="420" t="s">
+      <c r="C61" s="397" t="s">
         <v>81</v>
       </c>
-      <c r="D61" s="421"/>
+      <c r="D61" s="398"/>
       <c r="E61" s="394" t="s">
         <v>5</v>
       </c>
@@ -18300,18 +18297,18 @@
       <c r="B62" s="21">
         <v>35</v>
       </c>
-      <c r="C62" s="422"/>
-      <c r="D62" s="423"/>
+      <c r="C62" s="399"/>
+      <c r="D62" s="400"/>
       <c r="E62" s="26" t="s">
         <v>55</v>
       </c>
       <c r="F62" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G62" s="443" t="s">
+      <c r="G62" s="416" t="s">
         <v>5</v>
       </c>
-      <c r="H62" s="444"/>
+      <c r="H62" s="417"/>
       <c r="I62" s="32"/>
     </row>
     <row r="63" spans="1:14" ht="12" customHeight="1">
@@ -18321,8 +18318,8 @@
       <c r="B63" s="21">
         <v>36</v>
       </c>
-      <c r="C63" s="422"/>
-      <c r="D63" s="423"/>
+      <c r="C63" s="399"/>
+      <c r="D63" s="400"/>
       <c r="E63" s="27" t="s">
         <v>44</v>
       </c>
@@ -18386,10 +18383,10 @@
       <c r="F66" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="G66" s="443" t="s">
+      <c r="G66" s="416" t="s">
         <v>5</v>
       </c>
-      <c r="H66" s="444"/>
+      <c r="H66" s="417"/>
       <c r="I66" s="32"/>
     </row>
     <row r="67" spans="1:14" ht="12" customHeight="1">
@@ -18468,10 +18465,10 @@
       <c r="F70" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G70" s="443" t="s">
+      <c r="G70" s="416" t="s">
         <v>5</v>
       </c>
-      <c r="H70" s="444"/>
+      <c r="H70" s="417"/>
       <c r="I70" s="32"/>
     </row>
     <row r="71" spans="1:14" ht="12" customHeight="1">
@@ -18550,10 +18547,10 @@
       <c r="F74" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="G74" s="443" t="s">
+      <c r="G74" s="416" t="s">
         <v>5</v>
       </c>
-      <c r="H74" s="444"/>
+      <c r="H74" s="417"/>
       <c r="I74" s="32"/>
     </row>
     <row r="75" spans="1:14" ht="12" customHeight="1">
@@ -18620,10 +18617,10 @@
       <c r="B78" s="21">
         <v>51</v>
       </c>
-      <c r="C78" s="420" t="s">
+      <c r="C78" s="397" t="s">
         <v>88</v>
       </c>
-      <c r="D78" s="421"/>
+      <c r="D78" s="398"/>
       <c r="E78" s="394" t="s">
         <v>5</v>
       </c>
@@ -18639,16 +18636,16 @@
       <c r="B79" s="21">
         <v>52</v>
       </c>
-      <c r="C79" s="422"/>
-      <c r="D79" s="423"/>
+      <c r="C79" s="399"/>
+      <c r="D79" s="400"/>
       <c r="E79" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F79" s="397" t="s">
+      <c r="F79" s="401" t="s">
         <v>89</v>
       </c>
-      <c r="G79" s="398"/>
-      <c r="H79" s="399"/>
+      <c r="G79" s="402"/>
+      <c r="H79" s="403"/>
       <c r="I79" s="32"/>
     </row>
     <row r="80" spans="1:14" ht="12" customHeight="1">
@@ -18667,11 +18664,11 @@
       <c r="E80" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F80" s="397" t="s">
+      <c r="F80" s="401" t="s">
         <v>24</v>
       </c>
-      <c r="G80" s="398"/>
-      <c r="H80" s="399"/>
+      <c r="G80" s="402"/>
+      <c r="H80" s="403"/>
       <c r="I80" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18694,11 +18691,11 @@
       <c r="E81" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="397" t="s">
+      <c r="F81" s="401" t="s">
         <v>90</v>
       </c>
-      <c r="G81" s="398"/>
-      <c r="H81" s="399"/>
+      <c r="G81" s="402"/>
+      <c r="H81" s="403"/>
       <c r="I81" s="32"/>
       <c r="N81" s="35"/>
     </row>
@@ -18718,13 +18715,13 @@
       <c r="E82" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="430" t="s">
+      <c r="F82" s="413" t="s">
         <v>91</v>
       </c>
-      <c r="G82" s="443" t="s">
+      <c r="G82" s="416" t="s">
         <v>5</v>
       </c>
-      <c r="H82" s="444"/>
+      <c r="H82" s="417"/>
       <c r="I82" s="32"/>
     </row>
     <row r="83" spans="1:14" ht="24" customHeight="1">
@@ -18743,8 +18740,8 @@
       <c r="E83" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F83" s="438"/>
-      <c r="G83" s="430" t="s">
+      <c r="F83" s="415"/>
+      <c r="G83" s="413" t="s">
         <v>55</v>
       </c>
       <c r="H83" s="15" t="s">
@@ -18771,8 +18768,8 @@
       <c r="E84" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F84" s="431"/>
-      <c r="G84" s="431"/>
+      <c r="F84" s="414"/>
+      <c r="G84" s="414"/>
       <c r="H84" s="15" t="s">
         <v>92</v>
       </c>
@@ -18797,11 +18794,11 @@
       <c r="E85" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F85" s="397" t="s">
+      <c r="F85" s="401" t="s">
         <v>9</v>
       </c>
-      <c r="G85" s="398"/>
-      <c r="H85" s="399"/>
+      <c r="G85" s="402"/>
+      <c r="H85" s="403"/>
       <c r="I85" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18823,11 +18820,11 @@
       <c r="E86" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F86" s="397" t="s">
+      <c r="F86" s="401" t="s">
         <v>10</v>
       </c>
-      <c r="G86" s="398"/>
-      <c r="H86" s="399"/>
+      <c r="G86" s="402"/>
+      <c r="H86" s="403"/>
       <c r="I86" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18849,11 +18846,11 @@
       <c r="E87" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F87" s="397" t="s">
+      <c r="F87" s="401" t="s">
         <v>11</v>
       </c>
-      <c r="G87" s="398"/>
-      <c r="H87" s="399"/>
+      <c r="G87" s="402"/>
+      <c r="H87" s="403"/>
       <c r="I87" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18875,11 +18872,11 @@
       <c r="E88" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="397" t="s">
+      <c r="F88" s="401" t="s">
         <v>93</v>
       </c>
-      <c r="G88" s="398"/>
-      <c r="H88" s="399"/>
+      <c r="G88" s="402"/>
+      <c r="H88" s="403"/>
       <c r="I88" s="32"/>
     </row>
     <row r="89" spans="1:14" ht="12" customHeight="1">
@@ -18898,11 +18895,11 @@
       <c r="E89" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F89" s="417" t="s">
+      <c r="F89" s="391" t="s">
         <v>94</v>
       </c>
-      <c r="G89" s="418"/>
-      <c r="H89" s="419"/>
+      <c r="G89" s="392"/>
+      <c r="H89" s="393"/>
       <c r="I89" s="32"/>
       <c r="J89" s="10"/>
     </row>
@@ -18922,9 +18919,9 @@
       <c r="E90" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F90" s="417"/>
-      <c r="G90" s="418"/>
-      <c r="H90" s="419"/>
+      <c r="F90" s="391"/>
+      <c r="G90" s="392"/>
+      <c r="H90" s="393"/>
       <c r="I90" s="39"/>
       <c r="J90" s="10"/>
     </row>
@@ -18938,10 +18935,10 @@
       <c r="B92" s="21">
         <v>63</v>
       </c>
-      <c r="C92" s="420" t="s">
+      <c r="C92" s="397" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="421"/>
+      <c r="D92" s="398"/>
       <c r="E92" s="394" t="s">
         <v>5</v>
       </c>
@@ -18963,14 +18960,14 @@
       <c r="D93" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="430" t="s">
+      <c r="E93" s="413" t="s">
         <v>55</v>
       </c>
-      <c r="F93" s="397" t="s">
-        <v>44</v>
-      </c>
-      <c r="G93" s="398"/>
-      <c r="H93" s="399"/>
+      <c r="F93" s="401" t="s">
+        <v>44</v>
+      </c>
+      <c r="G93" s="402"/>
+      <c r="H93" s="403"/>
       <c r="I93" s="32"/>
     </row>
     <row r="94" spans="1:14" ht="12" customHeight="1">
@@ -18986,12 +18983,12 @@
       <c r="D94" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="E94" s="431"/>
-      <c r="F94" s="417" t="s">
+      <c r="E94" s="414"/>
+      <c r="F94" s="391" t="s">
         <v>96</v>
       </c>
-      <c r="G94" s="418"/>
-      <c r="H94" s="419"/>
+      <c r="G94" s="392"/>
+      <c r="H94" s="393"/>
       <c r="I94" s="32"/>
       <c r="J94" s="10"/>
     </row>
@@ -19005,10 +19002,10 @@
       <c r="B96" s="21">
         <v>66</v>
       </c>
-      <c r="C96" s="420" t="s">
+      <c r="C96" s="397" t="s">
         <v>97</v>
       </c>
-      <c r="D96" s="421"/>
+      <c r="D96" s="398"/>
       <c r="E96" s="394" t="s">
         <v>5</v>
       </c>
@@ -19033,11 +19030,11 @@
       <c r="E97" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F97" s="397" t="s">
+      <c r="F97" s="401" t="s">
         <v>98</v>
       </c>
-      <c r="G97" s="398"/>
-      <c r="H97" s="399"/>
+      <c r="G97" s="402"/>
+      <c r="H97" s="403"/>
       <c r="I97" s="32"/>
     </row>
     <row r="98" spans="1:10" ht="12" customHeight="1">
@@ -19056,11 +19053,11 @@
       <c r="E98" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F98" s="397" t="s">
+      <c r="F98" s="401" t="s">
         <v>99</v>
       </c>
-      <c r="G98" s="398"/>
-      <c r="H98" s="399"/>
+      <c r="G98" s="402"/>
+      <c r="H98" s="403"/>
       <c r="I98" s="32"/>
     </row>
     <row r="99" spans="1:10" ht="12" customHeight="1">
@@ -19079,11 +19076,11 @@
       <c r="E99" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F99" s="397" t="s">
+      <c r="F99" s="401" t="s">
         <v>12</v>
       </c>
-      <c r="G99" s="398"/>
-      <c r="H99" s="399"/>
+      <c r="G99" s="402"/>
+      <c r="H99" s="403"/>
       <c r="I99" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19105,11 +19102,11 @@
       <c r="E100" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F100" s="397" t="s">
+      <c r="F100" s="401" t="s">
         <v>100</v>
       </c>
-      <c r="G100" s="398"/>
-      <c r="H100" s="399"/>
+      <c r="G100" s="402"/>
+      <c r="H100" s="403"/>
       <c r="I100" s="32"/>
     </row>
     <row r="101" spans="1:10" ht="12" customHeight="1">
@@ -19128,11 +19125,11 @@
       <c r="E101" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F101" s="417" t="s">
-        <v>44</v>
-      </c>
-      <c r="G101" s="418"/>
-      <c r="H101" s="419"/>
+      <c r="F101" s="391" t="s">
+        <v>44</v>
+      </c>
+      <c r="G101" s="392"/>
+      <c r="H101" s="393"/>
       <c r="I101" s="32"/>
       <c r="J101" s="10"/>
     </row>
@@ -19152,11 +19149,11 @@
       <c r="E102" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F102" s="417" t="s">
-        <v>44</v>
-      </c>
-      <c r="G102" s="418"/>
-      <c r="H102" s="419"/>
+      <c r="F102" s="391" t="s">
+        <v>44</v>
+      </c>
+      <c r="G102" s="392"/>
+      <c r="H102" s="393"/>
       <c r="I102" s="32"/>
       <c r="J102" s="10"/>
     </row>
@@ -19207,10 +19204,10 @@
       <c r="B106" s="21">
         <v>74</v>
       </c>
-      <c r="C106" s="420" t="s">
+      <c r="C106" s="397" t="s">
         <v>102</v>
       </c>
-      <c r="D106" s="421"/>
+      <c r="D106" s="398"/>
       <c r="E106" s="394" t="s">
         <v>5</v>
       </c>
@@ -19226,16 +19223,16 @@
       <c r="B107" s="21">
         <v>75</v>
       </c>
-      <c r="C107" s="422"/>
-      <c r="D107" s="423"/>
+      <c r="C107" s="399"/>
+      <c r="D107" s="400"/>
       <c r="E107" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F107" s="397" t="s">
+      <c r="F107" s="401" t="s">
         <v>13</v>
       </c>
-      <c r="G107" s="398"/>
-      <c r="H107" s="399"/>
+      <c r="G107" s="402"/>
+      <c r="H107" s="403"/>
       <c r="I107" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19257,11 +19254,11 @@
       <c r="E108" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F108" s="417" t="s">
+      <c r="F108" s="391" t="s">
         <v>103</v>
       </c>
-      <c r="G108" s="418"/>
-      <c r="H108" s="419"/>
+      <c r="G108" s="392"/>
+      <c r="H108" s="393"/>
       <c r="I108" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19284,11 +19281,11 @@
       <c r="E109" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F109" s="417" t="s">
+      <c r="F109" s="391" t="s">
         <v>104</v>
       </c>
-      <c r="G109" s="418"/>
-      <c r="H109" s="419"/>
+      <c r="G109" s="392"/>
+      <c r="H109" s="393"/>
       <c r="I109" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19311,11 +19308,11 @@
       <c r="E110" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F110" s="417" t="s">
+      <c r="F110" s="391" t="s">
         <v>8</v>
       </c>
-      <c r="G110" s="418"/>
-      <c r="H110" s="419"/>
+      <c r="G110" s="392"/>
+      <c r="H110" s="393"/>
       <c r="I110" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19332,10 +19329,10 @@
       <c r="B112" s="21">
         <v>77</v>
       </c>
-      <c r="C112" s="420" t="s">
+      <c r="C112" s="397" t="s">
         <v>105</v>
       </c>
-      <c r="D112" s="421"/>
+      <c r="D112" s="398"/>
       <c r="E112" s="394" t="s">
         <v>5</v>
       </c>
@@ -19360,11 +19357,11 @@
       <c r="E113" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F113" s="397" t="s">
+      <c r="F113" s="401" t="s">
         <v>106</v>
       </c>
-      <c r="G113" s="398"/>
-      <c r="H113" s="399"/>
+      <c r="G113" s="402"/>
+      <c r="H113" s="403"/>
       <c r="I113" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19386,11 +19383,11 @@
       <c r="E114" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F114" s="397" t="s">
+      <c r="F114" s="401" t="s">
         <v>107</v>
       </c>
-      <c r="G114" s="398"/>
-      <c r="H114" s="399"/>
+      <c r="G114" s="402"/>
+      <c r="H114" s="403"/>
       <c r="I114" s="32"/>
     </row>
     <row r="115" spans="1:9" ht="12" customHeight="1">
@@ -19417,10 +19414,10 @@
       <c r="B116" s="21">
         <v>81</v>
       </c>
-      <c r="C116" s="420" t="s">
+      <c r="C116" s="397" t="s">
         <v>109</v>
       </c>
-      <c r="D116" s="421"/>
+      <c r="D116" s="398"/>
       <c r="E116" s="394" t="s">
         <v>5</v>
       </c>
@@ -19436,16 +19433,16 @@
       <c r="B117" s="21">
         <v>82</v>
       </c>
-      <c r="C117" s="422"/>
-      <c r="D117" s="423"/>
+      <c r="C117" s="399"/>
+      <c r="D117" s="400"/>
       <c r="E117" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F117" s="397" t="s">
+      <c r="F117" s="401" t="s">
         <v>110</v>
       </c>
-      <c r="G117" s="398"/>
-      <c r="H117" s="399"/>
+      <c r="G117" s="402"/>
+      <c r="H117" s="403"/>
       <c r="I117" s="32"/>
     </row>
     <row r="118" spans="1:9" ht="12" customHeight="1">
@@ -19464,11 +19461,11 @@
       <c r="E118" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F118" s="397" t="s">
+      <c r="F118" s="401" t="s">
         <v>111</v>
       </c>
-      <c r="G118" s="398"/>
-      <c r="H118" s="399"/>
+      <c r="G118" s="402"/>
+      <c r="H118" s="403"/>
       <c r="I118" s="32"/>
     </row>
     <row r="119" spans="1:9" hidden="1">
@@ -19481,10 +19478,10 @@
       <c r="B120" s="21">
         <v>85</v>
       </c>
-      <c r="C120" s="420" t="s">
+      <c r="C120" s="397" t="s">
         <v>112</v>
       </c>
-      <c r="D120" s="421"/>
+      <c r="D120" s="398"/>
       <c r="E120" s="394" t="s">
         <v>5</v>
       </c>
@@ -19500,16 +19497,16 @@
       <c r="B121" s="21">
         <v>86</v>
       </c>
-      <c r="C121" s="422"/>
-      <c r="D121" s="423"/>
+      <c r="C121" s="399"/>
+      <c r="D121" s="400"/>
       <c r="E121" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F121" s="397" t="s">
+      <c r="F121" s="401" t="s">
         <v>113</v>
       </c>
-      <c r="G121" s="398"/>
-      <c r="H121" s="399"/>
+      <c r="G121" s="402"/>
+      <c r="H121" s="403"/>
       <c r="I121" s="32"/>
     </row>
     <row r="122" spans="1:9" ht="12" customHeight="1">
@@ -19528,11 +19525,11 @@
       <c r="E122" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F122" s="397" t="s">
+      <c r="F122" s="401" t="s">
         <v>111</v>
       </c>
-      <c r="G122" s="398"/>
-      <c r="H122" s="399"/>
+      <c r="G122" s="402"/>
+      <c r="H122" s="403"/>
       <c r="I122" s="32"/>
     </row>
     <row r="123" spans="1:9" ht="12" customHeight="1">
@@ -19551,11 +19548,11 @@
       <c r="E123" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F123" s="397" t="s">
+      <c r="F123" s="401" t="s">
         <v>114</v>
       </c>
-      <c r="G123" s="398"/>
-      <c r="H123" s="399"/>
+      <c r="G123" s="402"/>
+      <c r="H123" s="403"/>
       <c r="I123" s="32"/>
     </row>
     <row r="124" spans="1:9" ht="12" customHeight="1">
@@ -19574,11 +19571,11 @@
       <c r="E124" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F124" s="397" t="s">
+      <c r="F124" s="401" t="s">
         <v>115</v>
       </c>
-      <c r="G124" s="398"/>
-      <c r="H124" s="399"/>
+      <c r="G124" s="402"/>
+      <c r="H124" s="403"/>
       <c r="I124" s="32"/>
     </row>
     <row r="125" spans="1:9" hidden="1">
@@ -19608,10 +19605,10 @@
       <c r="B127" s="21">
         <v>92</v>
       </c>
-      <c r="C127" s="420" t="s">
+      <c r="C127" s="397" t="s">
         <v>117</v>
       </c>
-      <c r="D127" s="421"/>
+      <c r="D127" s="398"/>
       <c r="E127" s="394" t="s">
         <v>5</v>
       </c>
@@ -19627,16 +19624,16 @@
       <c r="B128" s="21">
         <v>93</v>
       </c>
-      <c r="C128" s="422"/>
-      <c r="D128" s="423"/>
+      <c r="C128" s="399"/>
+      <c r="D128" s="400"/>
       <c r="E128" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F128" s="445" t="s">
-        <v>44</v>
-      </c>
-      <c r="G128" s="446"/>
-      <c r="H128" s="447"/>
+      <c r="F128" s="404" t="s">
+        <v>44</v>
+      </c>
+      <c r="G128" s="405"/>
+      <c r="H128" s="406"/>
       <c r="I128" s="40"/>
     </row>
     <row r="129" spans="1:14" hidden="1">
@@ -19683,10 +19680,10 @@
       <c r="B132" s="21">
         <v>97</v>
       </c>
-      <c r="C132" s="420" t="s">
+      <c r="C132" s="397" t="s">
         <v>120</v>
       </c>
-      <c r="D132" s="421"/>
+      <c r="D132" s="398"/>
       <c r="E132" s="394" t="s">
         <v>5</v>
       </c>
@@ -19702,16 +19699,16 @@
       <c r="B133" s="21">
         <v>98</v>
       </c>
-      <c r="C133" s="422"/>
-      <c r="D133" s="423"/>
+      <c r="C133" s="399"/>
+      <c r="D133" s="400"/>
       <c r="E133" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F133" s="397" t="s">
+      <c r="F133" s="401" t="s">
         <v>121</v>
       </c>
-      <c r="G133" s="398"/>
-      <c r="H133" s="399"/>
+      <c r="G133" s="402"/>
+      <c r="H133" s="403"/>
       <c r="I133" s="32"/>
     </row>
     <row r="134" spans="1:14" ht="12" customHeight="1">
@@ -19721,16 +19718,16 @@
       <c r="B134" s="21">
         <v>99</v>
       </c>
-      <c r="C134" s="422"/>
-      <c r="D134" s="423"/>
+      <c r="C134" s="399"/>
+      <c r="D134" s="400"/>
       <c r="E134" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F134" s="397" t="s">
+      <c r="F134" s="401" t="s">
         <v>122</v>
       </c>
-      <c r="G134" s="398"/>
-      <c r="H134" s="399"/>
+      <c r="G134" s="402"/>
+      <c r="H134" s="403"/>
       <c r="I134" s="32"/>
     </row>
     <row r="135" spans="1:14" ht="12" customHeight="1">
@@ -19740,16 +19737,16 @@
       <c r="B135" s="21">
         <v>100</v>
       </c>
-      <c r="C135" s="422"/>
-      <c r="D135" s="423"/>
+      <c r="C135" s="399"/>
+      <c r="D135" s="400"/>
       <c r="E135" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F135" s="397" t="s">
+      <c r="F135" s="401" t="s">
         <v>123</v>
       </c>
-      <c r="G135" s="398"/>
-      <c r="H135" s="399"/>
+      <c r="G135" s="402"/>
+      <c r="H135" s="403"/>
       <c r="I135" s="32"/>
     </row>
     <row r="136" spans="1:14" ht="12" customHeight="1">
@@ -19768,11 +19765,11 @@
       <c r="E136" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F136" s="397" t="s">
+      <c r="F136" s="401" t="s">
         <v>124</v>
       </c>
-      <c r="G136" s="398"/>
-      <c r="H136" s="399"/>
+      <c r="G136" s="402"/>
+      <c r="H136" s="403"/>
       <c r="I136" s="32"/>
     </row>
     <row r="137" spans="1:14" ht="12" customHeight="1">
@@ -19791,11 +19788,11 @@
       <c r="E137" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F137" s="397" t="s">
+      <c r="F137" s="401" t="s">
         <v>125</v>
       </c>
-      <c r="G137" s="398"/>
-      <c r="H137" s="399"/>
+      <c r="G137" s="402"/>
+      <c r="H137" s="403"/>
       <c r="I137" s="32"/>
     </row>
     <row r="138" spans="1:14" ht="12" customHeight="1">
@@ -19814,11 +19811,11 @@
       <c r="E138" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F138" s="397" t="s">
+      <c r="F138" s="401" t="s">
         <v>126</v>
       </c>
-      <c r="G138" s="398"/>
-      <c r="H138" s="399"/>
+      <c r="G138" s="402"/>
+      <c r="H138" s="403"/>
       <c r="I138" s="32"/>
     </row>
     <row r="139" spans="1:14" hidden="1">
@@ -19831,10 +19828,10 @@
       <c r="B140" s="21">
         <v>105</v>
       </c>
-      <c r="C140" s="424" t="s">
+      <c r="C140" s="407" t="s">
         <v>127</v>
       </c>
-      <c r="D140" s="425"/>
+      <c r="D140" s="408"/>
       <c r="E140" s="394" t="s">
         <v>5</v>
       </c>
@@ -19850,16 +19847,16 @@
       <c r="B141" s="21">
         <v>106</v>
       </c>
-      <c r="C141" s="426"/>
-      <c r="D141" s="427"/>
-      <c r="E141" s="430" t="s">
+      <c r="C141" s="409"/>
+      <c r="D141" s="410"/>
+      <c r="E141" s="413" t="s">
         <v>55</v>
       </c>
-      <c r="F141" s="397" t="s">
+      <c r="F141" s="401" t="s">
         <v>128</v>
       </c>
-      <c r="G141" s="398"/>
-      <c r="H141" s="399"/>
+      <c r="G141" s="402"/>
+      <c r="H141" s="403"/>
       <c r="I141" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -19872,14 +19869,14 @@
       <c r="B142" s="21">
         <v>107</v>
       </c>
-      <c r="C142" s="428"/>
-      <c r="D142" s="429"/>
-      <c r="E142" s="431"/>
-      <c r="F142" s="397" t="s">
+      <c r="C142" s="411"/>
+      <c r="D142" s="412"/>
+      <c r="E142" s="414"/>
+      <c r="F142" s="401" t="s">
         <v>129</v>
       </c>
-      <c r="G142" s="398"/>
-      <c r="H142" s="399"/>
+      <c r="G142" s="402"/>
+      <c r="H142" s="403"/>
       <c r="I142" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19944,11 +19941,11 @@
       <c r="E145" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F145" s="397" t="s">
+      <c r="F145" s="401" t="s">
         <v>131</v>
       </c>
-      <c r="G145" s="398"/>
-      <c r="H145" s="399"/>
+      <c r="G145" s="402"/>
+      <c r="H145" s="403"/>
       <c r="I145" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19970,11 +19967,11 @@
       <c r="E146" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F146" s="397" t="s">
+      <c r="F146" s="401" t="s">
         <v>132</v>
       </c>
-      <c r="G146" s="398"/>
-      <c r="H146" s="399"/>
+      <c r="G146" s="402"/>
+      <c r="H146" s="403"/>
       <c r="I146" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19996,11 +19993,11 @@
       <c r="E147" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F147" s="397" t="s">
+      <c r="F147" s="401" t="s">
         <v>64</v>
       </c>
-      <c r="G147" s="398"/>
-      <c r="H147" s="399"/>
+      <c r="G147" s="402"/>
+      <c r="H147" s="403"/>
       <c r="I147" s="32"/>
     </row>
     <row r="148" spans="1:10" ht="12" customHeight="1">
@@ -20019,11 +20016,11 @@
       <c r="E148" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F148" s="417" t="s">
+      <c r="F148" s="391" t="s">
         <v>133</v>
       </c>
-      <c r="G148" s="418"/>
-      <c r="H148" s="419"/>
+      <c r="G148" s="392"/>
+      <c r="H148" s="393"/>
       <c r="I148" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20046,11 +20043,11 @@
       <c r="E149" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F149" s="417" t="s">
+      <c r="F149" s="391" t="s">
         <v>134</v>
       </c>
-      <c r="G149" s="418"/>
-      <c r="H149" s="419"/>
+      <c r="G149" s="392"/>
+      <c r="H149" s="393"/>
       <c r="I149" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20073,11 +20070,11 @@
       <c r="E150" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F150" s="417" t="s">
+      <c r="F150" s="391" t="s">
         <v>135</v>
       </c>
-      <c r="G150" s="418"/>
-      <c r="H150" s="419"/>
+      <c r="G150" s="392"/>
+      <c r="H150" s="393"/>
       <c r="I150" s="32"/>
       <c r="J150" s="10"/>
     </row>
@@ -20097,11 +20094,11 @@
       <c r="E151" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F151" s="417" t="s">
+      <c r="F151" s="391" t="s">
         <v>136</v>
       </c>
-      <c r="G151" s="418"/>
-      <c r="H151" s="419"/>
+      <c r="G151" s="392"/>
+      <c r="H151" s="393"/>
       <c r="I151" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20118,10 +20115,10 @@
       <c r="B153" s="21">
         <v>114</v>
       </c>
-      <c r="C153" s="420" t="s">
+      <c r="C153" s="397" t="s">
         <v>137</v>
       </c>
-      <c r="D153" s="421"/>
+      <c r="D153" s="398"/>
       <c r="E153" s="394" t="s">
         <v>5</v>
       </c>
@@ -20137,16 +20134,16 @@
       <c r="B154" s="21">
         <v>115</v>
       </c>
-      <c r="C154" s="422"/>
-      <c r="D154" s="423"/>
+      <c r="C154" s="399"/>
+      <c r="D154" s="400"/>
       <c r="E154" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F154" s="445" t="s">
-        <v>44</v>
-      </c>
-      <c r="G154" s="446"/>
-      <c r="H154" s="447"/>
+      <c r="F154" s="404" t="s">
+        <v>44</v>
+      </c>
+      <c r="G154" s="405"/>
+      <c r="H154" s="406"/>
       <c r="I154" s="40"/>
     </row>
     <row r="155" spans="1:10" ht="12" customHeight="1">
@@ -20165,11 +20162,11 @@
       <c r="E155" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F155" s="417" t="s">
+      <c r="F155" s="391" t="s">
         <v>4</v>
       </c>
-      <c r="G155" s="418"/>
-      <c r="H155" s="419"/>
+      <c r="G155" s="392"/>
+      <c r="H155" s="393"/>
       <c r="I155" s="32"/>
       <c r="J155" s="10"/>
     </row>
@@ -20189,11 +20186,11 @@
       <c r="E156" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F156" s="417" t="s">
+      <c r="F156" s="391" t="s">
         <v>138</v>
       </c>
-      <c r="G156" s="418"/>
-      <c r="H156" s="419"/>
+      <c r="G156" s="392"/>
+      <c r="H156" s="393"/>
       <c r="I156" s="32"/>
       <c r="J156" s="10"/>
     </row>
@@ -20213,11 +20210,11 @@
       <c r="E157" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F157" s="417" t="s">
+      <c r="F157" s="391" t="s">
         <v>139</v>
       </c>
-      <c r="G157" s="418"/>
-      <c r="H157" s="419"/>
+      <c r="G157" s="392"/>
+      <c r="H157" s="393"/>
       <c r="I157" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20240,9 +20237,9 @@
       <c r="E158" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F158" s="417"/>
-      <c r="G158" s="418"/>
-      <c r="H158" s="419"/>
+      <c r="F158" s="391"/>
+      <c r="G158" s="392"/>
+      <c r="H158" s="393"/>
       <c r="I158" s="32"/>
       <c r="J158" s="10"/>
     </row>
@@ -20347,10 +20344,10 @@
       <c r="B165" s="21">
         <v>122</v>
       </c>
-      <c r="C165" s="420" t="s">
+      <c r="C165" s="397" t="s">
         <v>145</v>
       </c>
-      <c r="D165" s="421"/>
+      <c r="D165" s="398"/>
       <c r="E165" s="394" t="s">
         <v>5</v>
       </c>
@@ -20366,16 +20363,16 @@
       <c r="B166" s="21">
         <v>123</v>
       </c>
-      <c r="C166" s="422"/>
-      <c r="D166" s="423"/>
+      <c r="C166" s="399"/>
+      <c r="D166" s="400"/>
       <c r="E166" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F166" s="397" t="s">
+      <c r="F166" s="401" t="s">
         <v>146</v>
       </c>
-      <c r="G166" s="398"/>
-      <c r="H166" s="399"/>
+      <c r="G166" s="402"/>
+      <c r="H166" s="403"/>
       <c r="I166" s="32"/>
     </row>
     <row r="167" spans="1:9" ht="12" customHeight="1">
@@ -20394,11 +20391,11 @@
       <c r="E167" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F167" s="397" t="s">
+      <c r="F167" s="401" t="s">
         <v>147</v>
       </c>
-      <c r="G167" s="398"/>
-      <c r="H167" s="399"/>
+      <c r="G167" s="402"/>
+      <c r="H167" s="403"/>
       <c r="I167" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20420,11 +20417,11 @@
       <c r="E168" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F168" s="397" t="s">
+      <c r="F168" s="401" t="s">
         <v>148</v>
       </c>
-      <c r="G168" s="398"/>
-      <c r="H168" s="399"/>
+      <c r="G168" s="402"/>
+      <c r="H168" s="403"/>
       <c r="I168" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20534,10 +20531,10 @@
       <c r="B175" s="21">
         <v>132</v>
       </c>
-      <c r="C175" s="420" t="s">
+      <c r="C175" s="397" t="s">
         <v>153</v>
       </c>
-      <c r="D175" s="421"/>
+      <c r="D175" s="398"/>
       <c r="E175" s="394" t="s">
         <v>5</v>
       </c>
@@ -20553,16 +20550,16 @@
       <c r="B176" s="21">
         <v>133</v>
       </c>
-      <c r="C176" s="422"/>
-      <c r="D176" s="423"/>
+      <c r="C176" s="399"/>
+      <c r="D176" s="400"/>
       <c r="E176" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F176" s="397" t="s">
+      <c r="F176" s="401" t="s">
         <v>128</v>
       </c>
-      <c r="G176" s="398"/>
-      <c r="H176" s="399"/>
+      <c r="G176" s="402"/>
+      <c r="H176" s="403"/>
       <c r="I176" s="32"/>
     </row>
     <row r="177" spans="1:14" ht="12" customHeight="1">
@@ -20572,16 +20569,16 @@
       <c r="B177" s="21">
         <v>134</v>
       </c>
-      <c r="C177" s="422"/>
-      <c r="D177" s="423"/>
+      <c r="C177" s="399"/>
+      <c r="D177" s="400"/>
       <c r="E177" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F177" s="397" t="s">
+      <c r="F177" s="401" t="s">
         <v>154</v>
       </c>
-      <c r="G177" s="398"/>
-      <c r="H177" s="399"/>
+      <c r="G177" s="402"/>
+      <c r="H177" s="403"/>
       <c r="I177" s="32"/>
     </row>
     <row r="178" spans="1:14" ht="12" customHeight="1">
@@ -20600,11 +20597,11 @@
       <c r="E178" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F178" s="397" t="s">
+      <c r="F178" s="401" t="s">
         <v>155</v>
       </c>
-      <c r="G178" s="398"/>
-      <c r="H178" s="399"/>
+      <c r="G178" s="402"/>
+      <c r="H178" s="403"/>
       <c r="I178" s="32"/>
     </row>
     <row r="179" spans="1:14" hidden="1">
@@ -20657,10 +20654,10 @@
       <c r="B182" s="21">
         <v>139</v>
       </c>
-      <c r="C182" s="420" t="s">
+      <c r="C182" s="397" t="s">
         <v>157</v>
       </c>
-      <c r="D182" s="421"/>
+      <c r="D182" s="398"/>
       <c r="E182" s="394" t="s">
         <v>5</v>
       </c>
@@ -20676,16 +20673,16 @@
       <c r="B183" s="21">
         <v>140</v>
       </c>
-      <c r="C183" s="422"/>
-      <c r="D183" s="423"/>
+      <c r="C183" s="399"/>
+      <c r="D183" s="400"/>
       <c r="E183" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F183" s="397" t="s">
-        <v>44</v>
-      </c>
-      <c r="G183" s="398"/>
-      <c r="H183" s="399"/>
+      <c r="F183" s="401" t="s">
+        <v>44</v>
+      </c>
+      <c r="G183" s="402"/>
+      <c r="H183" s="403"/>
       <c r="I183" s="32"/>
     </row>
     <row r="184" spans="1:14" hidden="1">
@@ -20698,10 +20695,10 @@
       <c r="B185" s="21">
         <v>142</v>
       </c>
-      <c r="C185" s="420" t="s">
+      <c r="C185" s="397" t="s">
         <v>158</v>
       </c>
-      <c r="D185" s="421"/>
+      <c r="D185" s="398"/>
       <c r="E185" s="394" t="s">
         <v>5</v>
       </c>
@@ -20717,16 +20714,16 @@
       <c r="B186" s="21">
         <v>143</v>
       </c>
-      <c r="C186" s="422"/>
-      <c r="D186" s="423"/>
+      <c r="C186" s="399"/>
+      <c r="D186" s="400"/>
       <c r="E186" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F186" s="397" t="s">
+      <c r="F186" s="401" t="s">
         <v>159</v>
       </c>
-      <c r="G186" s="398"/>
-      <c r="H186" s="399"/>
+      <c r="G186" s="402"/>
+      <c r="H186" s="403"/>
       <c r="I186" s="32"/>
     </row>
     <row r="187" spans="1:14" ht="12" customHeight="1">
@@ -20736,16 +20733,16 @@
       <c r="B187" s="21">
         <v>144</v>
       </c>
-      <c r="C187" s="422"/>
-      <c r="D187" s="423"/>
+      <c r="C187" s="399"/>
+      <c r="D187" s="400"/>
       <c r="E187" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F187" s="397" t="s">
+      <c r="F187" s="401" t="s">
         <v>160</v>
       </c>
-      <c r="G187" s="398"/>
-      <c r="H187" s="399"/>
+      <c r="G187" s="402"/>
+      <c r="H187" s="403"/>
       <c r="I187" s="32"/>
     </row>
     <row r="188" spans="1:14" ht="12" customHeight="1">
@@ -20764,11 +20761,11 @@
       <c r="E188" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F188" s="417" t="s">
+      <c r="F188" s="391" t="s">
         <v>161</v>
       </c>
-      <c r="G188" s="418"/>
-      <c r="H188" s="419"/>
+      <c r="G188" s="392"/>
+      <c r="H188" s="393"/>
       <c r="I188" s="32"/>
       <c r="J188" s="10"/>
     </row>
@@ -20788,11 +20785,11 @@
       <c r="E189" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F189" s="417" t="s">
+      <c r="F189" s="391" t="s">
         <v>162</v>
       </c>
-      <c r="G189" s="418"/>
-      <c r="H189" s="419"/>
+      <c r="G189" s="392"/>
+      <c r="H189" s="393"/>
       <c r="I189" s="32"/>
       <c r="J189" s="10"/>
     </row>
@@ -20812,11 +20809,11 @@
       <c r="E190" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="F190" s="417" t="s">
+      <c r="F190" s="391" t="s">
         <v>163</v>
       </c>
-      <c r="G190" s="418"/>
-      <c r="H190" s="419"/>
+      <c r="G190" s="392"/>
+      <c r="H190" s="393"/>
       <c r="I190" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -20879,104 +20876,63 @@
     </row>
   </sheetData>
   <mergeCells count="169">
-    <mergeCell ref="F188:H188"/>
-    <mergeCell ref="F189:H189"/>
-    <mergeCell ref="F190:H190"/>
-    <mergeCell ref="C180:H180"/>
-    <mergeCell ref="C181:H181"/>
-    <mergeCell ref="C182:D183"/>
-    <mergeCell ref="E182:H182"/>
-    <mergeCell ref="F183:H183"/>
-    <mergeCell ref="C185:D187"/>
-    <mergeCell ref="E185:H185"/>
-    <mergeCell ref="F186:H186"/>
-    <mergeCell ref="F187:H187"/>
-    <mergeCell ref="C174:H174"/>
-    <mergeCell ref="C175:D177"/>
-    <mergeCell ref="E175:H175"/>
-    <mergeCell ref="F176:H176"/>
-    <mergeCell ref="F177:H177"/>
-    <mergeCell ref="F178:H178"/>
-    <mergeCell ref="F167:H167"/>
-    <mergeCell ref="F168:H168"/>
-    <mergeCell ref="C170:H170"/>
-    <mergeCell ref="C171:H171"/>
-    <mergeCell ref="C172:H172"/>
-    <mergeCell ref="C173:H173"/>
-    <mergeCell ref="C162:H162"/>
-    <mergeCell ref="C163:H163"/>
-    <mergeCell ref="C164:H164"/>
-    <mergeCell ref="C165:D166"/>
-    <mergeCell ref="E165:H165"/>
-    <mergeCell ref="F166:H166"/>
-    <mergeCell ref="F155:H155"/>
-    <mergeCell ref="F156:H156"/>
-    <mergeCell ref="F157:H157"/>
-    <mergeCell ref="F158:H158"/>
-    <mergeCell ref="C160:H160"/>
-    <mergeCell ref="C161:H161"/>
-    <mergeCell ref="F149:H149"/>
-    <mergeCell ref="F150:H150"/>
-    <mergeCell ref="F151:H151"/>
-    <mergeCell ref="C153:D154"/>
-    <mergeCell ref="E153:H153"/>
-    <mergeCell ref="F154:H154"/>
-    <mergeCell ref="C143:H143"/>
-    <mergeCell ref="E144:H144"/>
-    <mergeCell ref="F145:H145"/>
-    <mergeCell ref="F146:H146"/>
-    <mergeCell ref="F147:H147"/>
-    <mergeCell ref="F148:H148"/>
-    <mergeCell ref="F137:H137"/>
-    <mergeCell ref="F138:H138"/>
-    <mergeCell ref="C140:D142"/>
-    <mergeCell ref="E140:H140"/>
-    <mergeCell ref="E141:E142"/>
-    <mergeCell ref="F141:H141"/>
-    <mergeCell ref="F142:H142"/>
-    <mergeCell ref="C132:D135"/>
-    <mergeCell ref="E132:H132"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="F134:H134"/>
-    <mergeCell ref="F135:H135"/>
-    <mergeCell ref="F136:H136"/>
-    <mergeCell ref="C126:H126"/>
-    <mergeCell ref="C127:D128"/>
-    <mergeCell ref="E127:H127"/>
-    <mergeCell ref="F128:H128"/>
-    <mergeCell ref="C130:H130"/>
-    <mergeCell ref="C131:H131"/>
-    <mergeCell ref="C120:D121"/>
-    <mergeCell ref="E120:H120"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="F122:H122"/>
-    <mergeCell ref="F123:H123"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="C115:H115"/>
-    <mergeCell ref="C116:D117"/>
-    <mergeCell ref="E116:H116"/>
-    <mergeCell ref="F117:H117"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="F110:H110"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="E112:H112"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="C104:H104"/>
-    <mergeCell ref="C105:H105"/>
-    <mergeCell ref="C106:D107"/>
-    <mergeCell ref="E106:H106"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="F97:H97"/>
-    <mergeCell ref="F98:H98"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:H22"/>
+    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:D35"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:D39"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="C44:H44"/>
+    <mergeCell ref="C45:D49"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="C54:D57"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="F58:H58"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="C50:D51"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="C78:D79"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="F80:H80"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="C60:H60"/>
+    <mergeCell ref="C61:D63"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="G70:H70"/>
     <mergeCell ref="F88:H88"/>
     <mergeCell ref="F89:H89"/>
     <mergeCell ref="F90:H90"/>
@@ -20991,63 +20947,104 @@
     <mergeCell ref="F85:H85"/>
     <mergeCell ref="F86:H86"/>
     <mergeCell ref="F87:H87"/>
-    <mergeCell ref="G74:H74"/>
-    <mergeCell ref="C78:D79"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="F80:H80"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="C60:H60"/>
-    <mergeCell ref="C61:D63"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="C54:D57"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="F58:H58"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="C50:D51"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="C44:H44"/>
-    <mergeCell ref="C45:D49"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:D35"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C37:D39"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C20:H22"/>
-    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="C104:H104"/>
+    <mergeCell ref="C105:H105"/>
+    <mergeCell ref="C106:D107"/>
+    <mergeCell ref="E106:H106"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="F97:H97"/>
+    <mergeCell ref="F98:H98"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="C115:H115"/>
+    <mergeCell ref="C116:D117"/>
+    <mergeCell ref="E116:H116"/>
+    <mergeCell ref="F117:H117"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="F110:H110"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="E112:H112"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="C127:D128"/>
+    <mergeCell ref="E127:H127"/>
+    <mergeCell ref="F128:H128"/>
+    <mergeCell ref="C130:H130"/>
+    <mergeCell ref="C131:H131"/>
+    <mergeCell ref="C120:D121"/>
+    <mergeCell ref="E120:H120"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="F122:H122"/>
+    <mergeCell ref="F123:H123"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="F137:H137"/>
+    <mergeCell ref="F138:H138"/>
+    <mergeCell ref="C140:D142"/>
+    <mergeCell ref="E140:H140"/>
+    <mergeCell ref="E141:E142"/>
+    <mergeCell ref="F141:H141"/>
+    <mergeCell ref="F142:H142"/>
+    <mergeCell ref="C132:D135"/>
+    <mergeCell ref="E132:H132"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="F134:H134"/>
+    <mergeCell ref="F135:H135"/>
+    <mergeCell ref="F136:H136"/>
+    <mergeCell ref="F149:H149"/>
+    <mergeCell ref="F150:H150"/>
+    <mergeCell ref="F151:H151"/>
+    <mergeCell ref="C153:D154"/>
+    <mergeCell ref="E153:H153"/>
+    <mergeCell ref="F154:H154"/>
+    <mergeCell ref="C143:H143"/>
+    <mergeCell ref="E144:H144"/>
+    <mergeCell ref="F145:H145"/>
+    <mergeCell ref="F146:H146"/>
+    <mergeCell ref="F147:H147"/>
+    <mergeCell ref="F148:H148"/>
+    <mergeCell ref="C162:H162"/>
+    <mergeCell ref="C163:H163"/>
+    <mergeCell ref="C164:H164"/>
+    <mergeCell ref="C165:D166"/>
+    <mergeCell ref="E165:H165"/>
+    <mergeCell ref="F166:H166"/>
+    <mergeCell ref="F155:H155"/>
+    <mergeCell ref="F156:H156"/>
+    <mergeCell ref="F157:H157"/>
+    <mergeCell ref="F158:H158"/>
+    <mergeCell ref="C160:H160"/>
+    <mergeCell ref="C161:H161"/>
+    <mergeCell ref="C174:H174"/>
+    <mergeCell ref="C175:D177"/>
+    <mergeCell ref="E175:H175"/>
+    <mergeCell ref="F176:H176"/>
+    <mergeCell ref="F177:H177"/>
+    <mergeCell ref="F178:H178"/>
+    <mergeCell ref="F167:H167"/>
+    <mergeCell ref="F168:H168"/>
+    <mergeCell ref="C170:H170"/>
+    <mergeCell ref="C171:H171"/>
+    <mergeCell ref="C172:H172"/>
+    <mergeCell ref="C173:H173"/>
+    <mergeCell ref="F188:H188"/>
+    <mergeCell ref="F189:H189"/>
+    <mergeCell ref="F190:H190"/>
+    <mergeCell ref="C180:H180"/>
+    <mergeCell ref="C181:H181"/>
+    <mergeCell ref="C182:D183"/>
+    <mergeCell ref="E182:H182"/>
+    <mergeCell ref="F183:H183"/>
+    <mergeCell ref="C185:D187"/>
+    <mergeCell ref="E185:H185"/>
+    <mergeCell ref="F186:H186"/>
+    <mergeCell ref="F187:H187"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
@@ -21075,10 +21072,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="F1" s="448" t="s">
+      <c r="F1" s="447" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="448"/>
+      <c r="G1" s="447"/>
     </row>
     <row r="2" spans="1:10" ht="15.75">
       <c r="A2" s="242" t="s">
@@ -21173,7 +21170,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="206" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C7" s="207" t="s">
         <v>269</v>
@@ -21199,7 +21196,7 @@
         <v>309</v>
       </c>
       <c r="J7" s="270" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30">
@@ -21207,7 +21204,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="206" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C8" s="207" t="s">
         <v>274</v>
@@ -21241,7 +21238,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="206" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C9" s="207" t="s">
         <v>274</v>
@@ -21267,7 +21264,7 @@
         <v>309</v>
       </c>
       <c r="J9" s="270" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -21361,36 +21358,36 @@
       <c r="J12" s="267"/>
     </row>
     <row r="13" spans="1:10" ht="30">
-      <c r="A13" s="213">
+      <c r="A13" s="286">
         <v>1</v>
       </c>
-      <c r="B13" s="210" t="s">
-        <v>431</v>
-      </c>
-      <c r="C13" s="213" t="s">
+      <c r="B13" s="293" t="s">
+        <v>430</v>
+      </c>
+      <c r="C13" s="286" t="s">
         <v>270</v>
       </c>
-      <c r="D13" s="281">
+      <c r="D13" s="287">
         <v>1</v>
       </c>
-      <c r="E13" s="282">
+      <c r="E13" s="288">
         <v>1300000</v>
       </c>
-      <c r="F13" s="283">
+      <c r="F13" s="289">
         <f>IF(E13&gt;0,E13-MIN(E13,4250000)*10%-MIN(E13,1700000)*2%-MAX(0,E13-MIN(E13,4250000)*10%-MIN(E13,1700000)*2%-129750)*10%,0)</f>
         <v>1042575</v>
       </c>
-      <c r="G13" s="281">
+      <c r="G13" s="287">
         <f>D13*E13*12/1000</f>
         <v>15600</v>
       </c>
-      <c r="H13" s="281" t="s">
+      <c r="H13" s="287" t="s">
         <v>307</v>
       </c>
-      <c r="I13" s="284" t="s">
-        <v>311</v>
-      </c>
-      <c r="J13" s="285" t="s">
+      <c r="I13" s="290" t="s">
+        <v>428</v>
+      </c>
+      <c r="J13" s="291" t="s">
         <v>330</v>
       </c>
     </row>
@@ -21399,7 +21396,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="210" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C14" s="194" t="s">
         <v>272</v>
@@ -21433,7 +21430,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="210" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C15" s="213" t="s">
         <v>272</v>
@@ -21467,7 +21464,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="255" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C16" s="249"/>
       <c r="D16" s="251"/>
@@ -21489,7 +21486,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="244" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C17" s="243" t="s">
         <v>271</v>
@@ -21549,7 +21546,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="211" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C19" s="194" t="s">
         <v>272</v>
@@ -21583,7 +21580,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="210" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C20" s="213" t="s">
         <v>272</v>
@@ -21617,7 +21614,7 @@
         <v>3</v>
       </c>
       <c r="B21" s="210" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C21" s="213" t="s">
         <v>272</v>
@@ -21643,7 +21640,7 @@
         <v>311</v>
       </c>
       <c r="J21" s="285" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="214" customFormat="1" ht="30">
@@ -21651,7 +21648,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="244" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C22" s="243" t="s">
         <v>272</v>
@@ -21713,7 +21710,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="248" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C24" s="243" t="s">
         <v>270</v>
@@ -21747,7 +21744,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="183" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C25" s="194" t="s">
         <v>272</v>
@@ -21811,36 +21808,36 @@
       </c>
     </row>
     <row r="27" spans="1:10" s="214" customFormat="1" ht="30">
-      <c r="A27" s="286">
+      <c r="A27" s="243">
         <v>4</v>
       </c>
-      <c r="B27" s="287" t="s">
-        <v>437</v>
-      </c>
-      <c r="C27" s="286" t="s">
+      <c r="B27" s="248" t="s">
+        <v>436</v>
+      </c>
+      <c r="C27" s="243" t="s">
         <v>272</v>
       </c>
-      <c r="D27" s="288">
+      <c r="D27" s="245">
         <v>1</v>
       </c>
-      <c r="E27" s="289">
+      <c r="E27" s="246">
         <v>1000000</v>
       </c>
-      <c r="F27" s="290">
+      <c r="F27" s="247">
         <f t="shared" si="4"/>
         <v>804975</v>
       </c>
-      <c r="G27" s="288">
+      <c r="G27" s="245">
         <f t="shared" si="5"/>
         <v>12000</v>
       </c>
-      <c r="H27" s="288" t="s">
+      <c r="H27" s="245" t="s">
         <v>307</v>
       </c>
-      <c r="I27" s="291" t="s">
-        <v>428</v>
-      </c>
-      <c r="J27" s="292" t="s">
+      <c r="I27" s="266" t="s">
+        <v>320</v>
+      </c>
+      <c r="J27" s="271" t="s">
         <v>322</v>
       </c>
     </row>
@@ -21916,8 +21913,8 @@
       <c r="A30" s="213">
         <v>7</v>
       </c>
-      <c r="B30" s="293" t="s">
-        <v>438</v>
+      <c r="B30" s="292" t="s">
+        <v>437</v>
       </c>
       <c r="C30" s="213" t="s">
         <v>271</v>
@@ -21947,36 +21944,36 @@
       </c>
     </row>
     <row r="31" spans="1:10" s="214" customFormat="1" ht="30">
-      <c r="A31" s="286">
+      <c r="A31" s="243">
         <v>8</v>
       </c>
-      <c r="B31" s="294" t="s">
-        <v>439</v>
-      </c>
-      <c r="C31" s="286" t="s">
+      <c r="B31" s="244" t="s">
+        <v>438</v>
+      </c>
+      <c r="C31" s="243" t="s">
         <v>271</v>
       </c>
-      <c r="D31" s="288">
+      <c r="D31" s="245">
         <v>1</v>
       </c>
-      <c r="E31" s="289">
+      <c r="E31" s="246">
         <v>700000</v>
       </c>
-      <c r="F31" s="290">
+      <c r="F31" s="247">
         <f t="shared" si="4"/>
         <v>567375</v>
       </c>
-      <c r="G31" s="288">
+      <c r="G31" s="245">
         <f t="shared" si="5"/>
         <v>8400</v>
       </c>
-      <c r="H31" s="288" t="s">
+      <c r="H31" s="245" t="s">
         <v>307</v>
       </c>
-      <c r="I31" s="291" t="s">
-        <v>428</v>
-      </c>
-      <c r="J31" s="292" t="s">
+      <c r="I31" s="266" t="s">
+        <v>320</v>
+      </c>
+      <c r="J31" s="271" t="s">
         <v>322</v>
       </c>
     </row>
@@ -21985,7 +21982,7 @@
         <v>9</v>
       </c>
       <c r="B32" s="244" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C32" s="243" t="s">
         <v>271</v>
@@ -22019,7 +22016,7 @@
         <v>10</v>
       </c>
       <c r="B33" s="244" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C33" s="243" t="s">
         <v>271</v>
@@ -22165,7 +22162,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="176" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C38" s="193" t="s">
         <v>270</v>
@@ -22277,36 +22274,36 @@
       </c>
     </row>
     <row r="42" spans="1:10" s="212" customFormat="1">
-      <c r="A42" s="295">
+      <c r="A42" s="294">
         <v>5</v>
       </c>
       <c r="B42" s="210" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C42" s="213" t="s">
         <v>271</v>
       </c>
-      <c r="D42" s="296">
+      <c r="D42" s="295">
         <v>1</v>
       </c>
-      <c r="E42" s="297">
+      <c r="E42" s="296">
         <v>700000</v>
       </c>
-      <c r="F42" s="298">
+      <c r="F42" s="297">
         <f>IF(E42&gt;0,E42-MIN(E42,4250000)*10%-MIN(E42,1700000)*2%-MAX(0,E42-MIN(E42,4250000)*10%-MIN(E42,1700000)*2%-129750)*10%,0)</f>
         <v>567375</v>
       </c>
-      <c r="G42" s="296">
+      <c r="G42" s="295">
         <f>D42*E42*12/1000</f>
         <v>8400</v>
       </c>
-      <c r="H42" s="296" t="s">
+      <c r="H42" s="295" t="s">
         <v>307</v>
       </c>
-      <c r="I42" s="299" t="s">
+      <c r="I42" s="298" t="s">
         <v>311</v>
       </c>
-      <c r="J42" s="300" t="s">
+      <c r="J42" s="299" t="s">
         <v>315</v>
       </c>
     </row>
@@ -22315,7 +22312,7 @@
         <v>6</v>
       </c>
       <c r="B43" s="176" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C43" s="194" t="s">
         <v>272</v>
@@ -22349,7 +22346,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="176" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C44" s="195" t="s">
         <v>271</v>
@@ -22583,7 +22580,7 @@
     <row r="52" spans="1:10" ht="45">
       <c r="A52" s="241"/>
       <c r="B52" s="217" t="s">
-        <v>429</v>
+        <v>455</v>
       </c>
       <c r="C52" s="186"/>
       <c r="D52" s="1"/>
@@ -29692,54 +29689,54 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
-      <c r="A3" s="450" t="s">
+      <c r="A3" s="449" t="s">
         <v>334</v>
       </c>
-      <c r="B3" s="450"/>
-      <c r="C3" s="450"/>
-      <c r="D3" s="450"/>
-      <c r="E3" s="450"/>
-      <c r="F3" s="450"/>
+      <c r="B3" s="449"/>
+      <c r="C3" s="449"/>
+      <c r="D3" s="449"/>
+      <c r="E3" s="449"/>
+      <c r="F3" s="449"/>
     </row>
     <row r="4" spans="1:6" ht="44.1" customHeight="1">
-      <c r="A4" s="450" t="s">
+      <c r="A4" s="449" t="s">
         <v>335</v>
       </c>
-      <c r="B4" s="450"/>
-      <c r="C4" s="450"/>
-      <c r="D4" s="450"/>
-      <c r="E4" s="450"/>
-      <c r="F4" s="450"/>
+      <c r="B4" s="449"/>
+      <c r="C4" s="449"/>
+      <c r="D4" s="449"/>
+      <c r="E4" s="449"/>
+      <c r="F4" s="449"/>
     </row>
     <row r="5" spans="1:6" ht="44.1" customHeight="1">
-      <c r="A5" s="450" t="s">
+      <c r="A5" s="449" t="s">
         <v>336</v>
       </c>
-      <c r="B5" s="450"/>
-      <c r="C5" s="450"/>
-      <c r="D5" s="450"/>
-      <c r="E5" s="450"/>
-      <c r="F5" s="450"/>
+      <c r="B5" s="449"/>
+      <c r="C5" s="449"/>
+      <c r="D5" s="449"/>
+      <c r="E5" s="449"/>
+      <c r="F5" s="449"/>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1">
-      <c r="A6" s="450" t="s">
+      <c r="A6" s="449" t="s">
         <v>337</v>
       </c>
-      <c r="B6" s="450"/>
-      <c r="C6" s="450"/>
-      <c r="D6" s="450"/>
-      <c r="E6" s="450"/>
-      <c r="F6" s="450"/>
+      <c r="B6" s="449"/>
+      <c r="C6" s="449"/>
+      <c r="D6" s="449"/>
+      <c r="E6" s="449"/>
+      <c r="F6" s="449"/>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
-      <c r="A7" s="450" t="s">
+      <c r="A7" s="449" t="s">
         <v>338</v>
       </c>
-      <c r="B7" s="450"/>
-      <c r="C7" s="450"/>
-      <c r="D7" s="450"/>
-      <c r="E7" s="450"/>
-      <c r="F7" s="450"/>
+      <c r="B7" s="449"/>
+      <c r="C7" s="449"/>
+      <c r="D7" s="449"/>
+      <c r="E7" s="449"/>
+      <c r="F7" s="449"/>
     </row>
     <row r="9" spans="1:6" ht="25.5">
       <c r="A9" s="279" t="s">
@@ -30007,93 +30004,87 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="27" customHeight="1">
-      <c r="A24" s="449" t="s">
+      <c r="A24" s="448" t="s">
         <v>404</v>
       </c>
-      <c r="B24" s="449"/>
-      <c r="C24" s="449"/>
-      <c r="D24" s="449"/>
-      <c r="E24" s="449"/>
-      <c r="F24" s="449"/>
+      <c r="B24" s="448"/>
+      <c r="C24" s="448"/>
+      <c r="D24" s="448"/>
+      <c r="E24" s="448"/>
+      <c r="F24" s="448"/>
     </row>
     <row r="25" spans="1:6" ht="27" customHeight="1">
-      <c r="A25" s="449" t="s">
+      <c r="A25" s="448" t="s">
         <v>405</v>
       </c>
-      <c r="B25" s="449"/>
-      <c r="C25" s="449"/>
-      <c r="D25" s="449"/>
-      <c r="E25" s="449"/>
-      <c r="F25" s="449"/>
+      <c r="B25" s="448"/>
+      <c r="C25" s="448"/>
+      <c r="D25" s="448"/>
+      <c r="E25" s="448"/>
+      <c r="F25" s="448"/>
     </row>
     <row r="26" spans="1:6" ht="27" customHeight="1">
-      <c r="A26" s="449" t="s">
+      <c r="A26" s="448" t="s">
         <v>406</v>
       </c>
-      <c r="B26" s="449"/>
-      <c r="C26" s="449"/>
-      <c r="D26" s="449"/>
-      <c r="E26" s="449"/>
-      <c r="F26" s="449"/>
+      <c r="B26" s="448"/>
+      <c r="C26" s="448"/>
+      <c r="D26" s="448"/>
+      <c r="E26" s="448"/>
+      <c r="F26" s="448"/>
     </row>
     <row r="27" spans="1:6" ht="27" customHeight="1">
-      <c r="A27" s="449" t="s">
+      <c r="A27" s="448" t="s">
         <v>407</v>
       </c>
-      <c r="B27" s="449"/>
-      <c r="C27" s="449"/>
-      <c r="D27" s="449"/>
-      <c r="E27" s="449"/>
-      <c r="F27" s="449"/>
+      <c r="B27" s="448"/>
+      <c r="C27" s="448"/>
+      <c r="D27" s="448"/>
+      <c r="E27" s="448"/>
+      <c r="F27" s="448"/>
     </row>
     <row r="28" spans="1:6" ht="27" customHeight="1">
-      <c r="A28" s="449" t="s">
+      <c r="A28" s="448" t="s">
         <v>408</v>
       </c>
-      <c r="B28" s="449"/>
-      <c r="C28" s="449"/>
-      <c r="D28" s="449"/>
-      <c r="E28" s="449"/>
-      <c r="F28" s="449"/>
+      <c r="B28" s="448"/>
+      <c r="C28" s="448"/>
+      <c r="D28" s="448"/>
+      <c r="E28" s="448"/>
+      <c r="F28" s="448"/>
     </row>
     <row r="29" spans="1:6" ht="27" customHeight="1">
-      <c r="A29" s="449" t="s">
+      <c r="A29" s="448" t="s">
         <v>409</v>
       </c>
-      <c r="B29" s="449"/>
-      <c r="C29" s="449"/>
-      <c r="D29" s="449"/>
-      <c r="E29" s="449"/>
-      <c r="F29" s="449"/>
+      <c r="B29" s="448"/>
+      <c r="C29" s="448"/>
+      <c r="D29" s="448"/>
+      <c r="E29" s="448"/>
+      <c r="F29" s="448"/>
     </row>
     <row r="30" spans="1:6" ht="27" customHeight="1">
-      <c r="A30" s="449" t="s">
+      <c r="A30" s="448" t="s">
         <v>410</v>
       </c>
-      <c r="B30" s="449"/>
-      <c r="C30" s="449"/>
-      <c r="D30" s="449"/>
-      <c r="E30" s="449"/>
-      <c r="F30" s="449"/>
+      <c r="B30" s="448"/>
+      <c r="C30" s="448"/>
+      <c r="D30" s="448"/>
+      <c r="E30" s="448"/>
+      <c r="F30" s="448"/>
     </row>
     <row r="31" spans="1:6" ht="27" customHeight="1">
-      <c r="A31" s="449" t="s">
+      <c r="A31" s="448" t="s">
         <v>411</v>
       </c>
-      <c r="B31" s="449"/>
-      <c r="C31" s="449"/>
-      <c r="D31" s="449"/>
-      <c r="E31" s="449"/>
-      <c r="F31" s="449"/>
+      <c r="B31" s="448"/>
+      <c r="C31" s="448"/>
+      <c r="D31" s="448"/>
+      <c r="E31" s="448"/>
+      <c r="F31" s="448"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="A26:F26"/>
@@ -30101,6 +30092,12 @@
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>

--- a/TAZA/_документы/Штатка Фонда и проектного офиса.xlsx
+++ b/TAZA/_документы/Штатка Фонда и проектного офиса.xlsx
@@ -21527,15 +21527,15 @@
       </c>
       <c r="E18" s="221">
         <f>SUM(E19:E22)</f>
-        <v>3030000</v>
+        <v>3400000</v>
       </c>
       <c r="F18" s="222">
         <f>SUM(F19:F22)</f>
-        <v>2451660</v>
+        <v>2744700</v>
       </c>
       <c r="G18" s="181">
         <f>SUM(G19:G22)</f>
-        <v>36360</v>
+        <v>40800</v>
       </c>
       <c r="H18" s="181"/>
       <c r="I18" s="181"/>
@@ -21589,15 +21589,15 @@
         <v>1</v>
       </c>
       <c r="E20" s="282">
-        <v>615000</v>
+        <v>800000</v>
       </c>
       <c r="F20" s="283">
         <f>IF(E20&gt;0,E20-MIN(E20,4250000)*10%-MIN(E20,1700000)*2%-MAX(0,E20-MIN(E20,4250000)*10%-MIN(E20,1700000)*2%-129750)*10%,0)</f>
-        <v>500055</v>
+        <v>646575</v>
       </c>
       <c r="G20" s="281">
         <f>D20*E20*12/1000</f>
-        <v>7380</v>
+        <v>9600</v>
       </c>
       <c r="H20" s="281" t="s">
         <v>307</v>
@@ -21623,15 +21623,15 @@
         <v>1</v>
       </c>
       <c r="E21" s="282">
-        <v>615000</v>
+        <v>800000</v>
       </c>
       <c r="F21" s="283">
         <f>IF(E21&gt;0,E21-MIN(E21,4250000)*10%-MIN(E21,1700000)*2%-MAX(0,E21-MIN(E21,4250000)*10%-MIN(E21,1700000)*2%-129750)*10%,0)</f>
-        <v>500055</v>
+        <v>646575</v>
       </c>
       <c r="G21" s="281">
         <f>D21*E21*12/1000</f>
-        <v>7380</v>
+        <v>9600</v>
       </c>
       <c r="H21" s="281" t="s">
         <v>307</v>
@@ -22563,15 +22563,15 @@
       </c>
       <c r="E51" s="233">
         <f>E6+E10+E12+E18+E23+E34+E37+E46</f>
-        <v>31423100</v>
+        <v>31793100</v>
       </c>
       <c r="F51" s="235">
         <f>F6+F10+F12+F18+F23+F34+F37+F46</f>
-        <v>25302295.199999999</v>
+        <v>25595335.199999999</v>
       </c>
       <c r="G51" s="234">
         <f>G6+G10+G12+G18+G23+G34+G37+G46</f>
-        <v>361560</v>
+        <v>366000</v>
       </c>
       <c r="H51" s="234"/>
       <c r="I51" s="234"/>

--- a/TAZA/_документы/Штатка Фонда и проектного офиса.xlsx
+++ b/TAZA/_документы/Штатка Фонда и проектного офиса.xlsx
@@ -1834,9 +1834,6 @@
     <t>Вывод</t>
   </si>
   <si>
-    <t>ГИД, заместители ГИД, национальный координатор, финансовый директор</t>
-  </si>
-  <si>
     <t>1 400 000 – 1 600 000</t>
   </si>
   <si>
@@ -2431,6 +2428,9 @@
   </si>
   <si>
     <t>*приход с 12.2026 и в 2027 году выделен сиреневым (с 12.2026 – Өміртай А.; остальные – с 02.2027)</t>
+  </si>
+  <si>
+    <t>ГИД, заместители ГИД, руководитель проектного офиса «Таза Қазақстан», финансовый директор</t>
   </si>
 </sst>
 </file>
@@ -5579,60 +5579,174 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="32" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="34" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="32" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="10" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="2" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="17" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="39" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="3" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="33" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="34" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="35" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5684,119 +5798,29 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="33" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="34" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="35" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="32" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="39" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="3" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="10" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="2" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="17" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="32" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="34" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5807,47 +5831,98 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="46" fillId="2" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="46" fillId="2" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="46" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5858,15 +5933,6 @@
     <xf numFmtId="49" fontId="46" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -5879,13 +5945,67 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5896,126 +6016,6 @@
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6357,7 +6357,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6415,7 +6415,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6470,7 +6470,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000004000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10247,26 +10247,26 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="301" t="s">
+      <c r="A2" s="309" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="301"/>
+      <c r="B2" s="309"/>
       <c r="C2" s="132" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="302" t="s">
+      <c r="A3" s="314" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="303"/>
+      <c r="B3" s="315"/>
       <c r="C3" s="133"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="302" t="s">
+      <c r="A4" s="314" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="303" t="s">
+      <c r="B4" s="315" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="133"/>
@@ -10279,24 +10279,24 @@
       <c r="C5" s="133"/>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
-      <c r="A6" s="302" t="s">
+      <c r="A6" s="314" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="303"/>
+      <c r="B6" s="315"/>
       <c r="C6" s="134"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
-      <c r="A7" s="302" t="s">
+      <c r="A7" s="314" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="303"/>
+      <c r="B7" s="315"/>
       <c r="C7" s="135"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="304" t="s">
+      <c r="A8" s="305" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="305"/>
+      <c r="B8" s="306"/>
       <c r="C8" s="131">
         <f>SUM(C3:C7)</f>
         <v>0</v>
@@ -10306,17 +10306,17 @@
       <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="306" t="s">
+      <c r="A10" s="316" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="306"/>
-      <c r="C10" s="306"/>
+      <c r="B10" s="316"/>
+      <c r="C10" s="316"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="301" t="s">
+      <c r="A11" s="309" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="301"/>
+      <c r="B11" s="309"/>
       <c r="C11" s="132" t="s">
         <v>1</v>
       </c>
@@ -10343,10 +10343,10 @@
       <c r="C14" s="136"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="304" t="s">
+      <c r="A15" s="305" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="305"/>
+      <c r="B15" s="306"/>
       <c r="C15" s="130">
         <f>SUM(C12:C14)</f>
         <v>0</v>
@@ -10376,10 +10376,10 @@
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="301" t="s">
+      <c r="A20" s="309" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="301"/>
+      <c r="B20" s="309"/>
       <c r="C20" s="132" t="s">
         <v>1</v>
       </c>
@@ -10424,17 +10424,17 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="309" t="s">
+      <c r="A26" s="310" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="310"/>
-      <c r="C26" s="311"/>
+      <c r="B26" s="311"/>
+      <c r="C26" s="312"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="301" t="s">
+      <c r="A27" s="309" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="301"/>
+      <c r="B27" s="309"/>
       <c r="C27" s="138"/>
     </row>
     <row r="28" spans="1:4">
@@ -10451,17 +10451,17 @@
       <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="312" t="s">
+      <c r="A30" s="313" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="312"/>
+      <c r="B30" s="313"/>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="301" t="s">
+      <c r="A31" s="309" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="301"/>
+      <c r="B31" s="309"/>
       <c r="C31" s="132" t="s">
         <v>1</v>
       </c>
@@ -10498,8 +10498,8 @@
       <c r="D35" s="3"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="313"/>
-      <c r="B36" s="314"/>
+      <c r="A36" s="301"/>
+      <c r="B36" s="302"/>
       <c r="C36" s="144">
         <f>SUM(C32:C35)</f>
         <v>0</v>
@@ -10511,10 +10511,10 @@
       <c r="C37" s="8"/>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="315" t="s">
+      <c r="A38" s="303" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="316"/>
+      <c r="B38" s="304"/>
       <c r="C38" s="145">
         <f>C28-C36</f>
         <v>0</v>
@@ -10537,11 +10537,18 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A17:B17"/>
@@ -10554,18 +10561,11 @@
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A38:B38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10833,11 +10833,11 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1"/>
-      <c r="B19" s="301" t="s">
+      <c r="B19" s="309" t="s">
         <v>259</v>
       </c>
-      <c r="C19" s="301"/>
-      <c r="D19" s="301"/>
+      <c r="C19" s="309"/>
+      <c r="D19" s="309"/>
       <c r="E19" s="162" t="e">
         <f>E15/E18</f>
         <v>#REF!</v>
@@ -10914,17 +10914,17 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="319" t="s">
+      <c r="B1" s="357" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="319"/>
-      <c r="D1" s="319"/>
-      <c r="E1" s="319"/>
-      <c r="F1" s="319"/>
-      <c r="G1" s="319"/>
-      <c r="H1" s="319"/>
-      <c r="I1" s="319"/>
-      <c r="J1" s="319"/>
+      <c r="C1" s="357"/>
+      <c r="D1" s="357"/>
+      <c r="E1" s="357"/>
+      <c r="F1" s="357"/>
+      <c r="G1" s="357"/>
+      <c r="H1" s="357"/>
+      <c r="I1" s="357"/>
+      <c r="J1" s="357"/>
       <c r="K1" s="85"/>
       <c r="O1" s="51"/>
     </row>
@@ -10962,17 +10962,17 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="320" t="s">
+      <c r="B3" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="320"/>
-      <c r="D3" s="320"/>
-      <c r="E3" s="320"/>
-      <c r="F3" s="320"/>
-      <c r="G3" s="320"/>
-      <c r="H3" s="320"/>
-      <c r="I3" s="320"/>
-      <c r="J3" s="320"/>
+      <c r="C3" s="358"/>
+      <c r="D3" s="358"/>
+      <c r="E3" s="358"/>
+      <c r="F3" s="358"/>
+      <c r="G3" s="358"/>
+      <c r="H3" s="358"/>
+      <c r="I3" s="358"/>
+      <c r="J3" s="358"/>
       <c r="K3" s="88"/>
       <c r="O3" s="51"/>
     </row>
@@ -10980,17 +10980,17 @@
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="321" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="321"/>
-      <c r="D4" s="321"/>
-      <c r="E4" s="321"/>
-      <c r="F4" s="321"/>
-      <c r="G4" s="321"/>
-      <c r="H4" s="321"/>
-      <c r="I4" s="321"/>
-      <c r="J4" s="321"/>
+      <c r="B4" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="359"/>
+      <c r="D4" s="359"/>
+      <c r="E4" s="359"/>
+      <c r="F4" s="359"/>
+      <c r="G4" s="359"/>
+      <c r="H4" s="359"/>
+      <c r="I4" s="359"/>
+      <c r="J4" s="359"/>
       <c r="K4" s="89"/>
       <c r="O4" s="51"/>
     </row>
@@ -10998,17 +10998,17 @@
       <c r="A5" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="322" t="s">
+      <c r="B5" s="360" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="322"/>
-      <c r="D5" s="322"/>
-      <c r="E5" s="322"/>
-      <c r="F5" s="322"/>
-      <c r="G5" s="322"/>
-      <c r="H5" s="322"/>
-      <c r="I5" s="322"/>
-      <c r="J5" s="322"/>
+      <c r="C5" s="360"/>
+      <c r="D5" s="360"/>
+      <c r="E5" s="360"/>
+      <c r="F5" s="360"/>
+      <c r="G5" s="360"/>
+      <c r="H5" s="360"/>
+      <c r="I5" s="360"/>
+      <c r="J5" s="360"/>
       <c r="K5" s="90"/>
       <c r="O5" s="51"/>
     </row>
@@ -11016,17 +11016,17 @@
       <c r="A6" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="322" t="s">
+      <c r="B6" s="360" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="322"/>
-      <c r="D6" s="322"/>
-      <c r="E6" s="322"/>
-      <c r="F6" s="322"/>
-      <c r="G6" s="322"/>
-      <c r="H6" s="322"/>
-      <c r="I6" s="322"/>
-      <c r="J6" s="322"/>
+      <c r="C6" s="360"/>
+      <c r="D6" s="360"/>
+      <c r="E6" s="360"/>
+      <c r="F6" s="360"/>
+      <c r="G6" s="360"/>
+      <c r="H6" s="360"/>
+      <c r="I6" s="360"/>
+      <c r="J6" s="360"/>
       <c r="K6" s="90"/>
       <c r="O6" s="51"/>
     </row>
@@ -11034,15 +11034,15 @@
       <c r="A7" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="323" t="s">
+      <c r="B7" s="361" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="323"/>
-      <c r="D7" s="323"/>
-      <c r="E7" s="323"/>
-      <c r="F7" s="323"/>
-      <c r="G7" s="323"/>
-      <c r="H7" s="323"/>
+      <c r="C7" s="361"/>
+      <c r="D7" s="361"/>
+      <c r="E7" s="361"/>
+      <c r="F7" s="361"/>
+      <c r="G7" s="361"/>
+      <c r="H7" s="361"/>
       <c r="I7" s="91"/>
       <c r="J7" s="71" t="s">
         <v>50</v>
@@ -11068,51 +11068,51 @@
       <c r="A22" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="324" t="s">
+      <c r="B22" s="362" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="327" t="s">
+      <c r="C22" s="365" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="328"/>
-      <c r="E22" s="328"/>
-      <c r="F22" s="328"/>
-      <c r="G22" s="329"/>
+      <c r="D22" s="366"/>
+      <c r="E22" s="366"/>
+      <c r="F22" s="366"/>
+      <c r="G22" s="367"/>
       <c r="H22" s="93"/>
-      <c r="I22" s="328" t="s">
+      <c r="I22" s="366" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="329"/>
+      <c r="J22" s="367"/>
       <c r="K22" s="94"/>
     </row>
     <row r="23" spans="1:16" ht="12" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="325"/>
-      <c r="C23" s="330"/>
-      <c r="D23" s="331"/>
-      <c r="E23" s="331"/>
-      <c r="F23" s="331"/>
-      <c r="G23" s="332"/>
+      <c r="B23" s="363"/>
+      <c r="C23" s="368"/>
+      <c r="D23" s="369"/>
+      <c r="E23" s="369"/>
+      <c r="F23" s="369"/>
+      <c r="G23" s="370"/>
       <c r="H23" s="95"/>
-      <c r="I23" s="331"/>
-      <c r="J23" s="332"/>
+      <c r="I23" s="369"/>
+      <c r="J23" s="370"/>
       <c r="K23" s="94"/>
     </row>
     <row r="24" spans="1:16" ht="24" customHeight="1">
       <c r="A24" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="326"/>
-      <c r="C24" s="333"/>
-      <c r="D24" s="334"/>
-      <c r="E24" s="334"/>
-      <c r="F24" s="334"/>
-      <c r="G24" s="335"/>
+      <c r="B24" s="364"/>
+      <c r="C24" s="371"/>
+      <c r="D24" s="372"/>
+      <c r="E24" s="372"/>
+      <c r="F24" s="372"/>
+      <c r="G24" s="373"/>
       <c r="H24" s="96"/>
-      <c r="I24" s="334"/>
-      <c r="J24" s="335"/>
+      <c r="I24" s="372"/>
+      <c r="J24" s="373"/>
       <c r="K24" s="94"/>
     </row>
     <row r="25" spans="1:16" ht="15.75" hidden="1" customHeight="1"/>
@@ -11154,13 +11154,13 @@
       <c r="B29" s="58">
         <v>1</v>
       </c>
-      <c r="C29" s="336" t="s">
+      <c r="C29" s="323" t="s">
         <v>202</v>
       </c>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
-      <c r="G29" s="338"/>
+      <c r="D29" s="324"/>
+      <c r="E29" s="324"/>
+      <c r="F29" s="324"/>
+      <c r="G29" s="325"/>
       <c r="H29" s="97"/>
       <c r="I29" s="97" t="e">
         <f>I35+I44+I46+I47+I50+#REF!+I68+I71+I72+I73+I77+I89+I97+I101+I106+I108+I116+I131+I142+I146+I147+I154+I32+I34+#REF!+#REF!+I151+#REF!+I98+I113+I155</f>
@@ -11177,15 +11177,15 @@
       <c r="B30" s="58">
         <v>2</v>
       </c>
-      <c r="C30" s="339" t="s">
+      <c r="C30" s="332" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="336" t="s">
+      <c r="D30" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="337"/>
-      <c r="F30" s="337"/>
-      <c r="G30" s="338"/>
+      <c r="E30" s="324"/>
+      <c r="F30" s="324"/>
+      <c r="G30" s="325"/>
       <c r="H30" s="97"/>
       <c r="I30" s="97"/>
       <c r="J30" s="99" t="e">
@@ -11205,15 +11205,15 @@
       <c r="B31" s="58">
         <v>3</v>
       </c>
-      <c r="C31" s="340"/>
+      <c r="C31" s="333"/>
       <c r="D31" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="345" t="s">
+      <c r="E31" s="319" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="346"/>
-      <c r="G31" s="347"/>
+      <c r="F31" s="320"/>
+      <c r="G31" s="321"/>
       <c r="H31" s="72"/>
       <c r="I31" s="72"/>
       <c r="J31" s="100"/>
@@ -11230,13 +11230,13 @@
       <c r="B32" s="58">
         <v>4</v>
       </c>
-      <c r="C32" s="340"/>
+      <c r="C32" s="333"/>
       <c r="D32" s="343"/>
-      <c r="E32" s="345" t="s">
+      <c r="E32" s="319" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="346"/>
-      <c r="G32" s="347"/>
+      <c r="F32" s="320"/>
+      <c r="G32" s="321"/>
       <c r="H32" s="72"/>
       <c r="I32" s="72"/>
       <c r="J32" s="81" t="e">
@@ -11256,13 +11256,13 @@
       <c r="B33" s="58">
         <v>5</v>
       </c>
-      <c r="C33" s="340"/>
+      <c r="C33" s="333"/>
       <c r="D33" s="343"/>
-      <c r="E33" s="348" t="s">
+      <c r="E33" s="352" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="349"/>
-      <c r="G33" s="350"/>
+      <c r="F33" s="353"/>
+      <c r="G33" s="354"/>
       <c r="H33" s="72"/>
       <c r="I33" s="72"/>
       <c r="J33" s="81"/>
@@ -11275,13 +11275,13 @@
       <c r="B34" s="58">
         <v>6</v>
       </c>
-      <c r="C34" s="341"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="352" t="s">
+      <c r="C34" s="349"/>
+      <c r="D34" s="351"/>
+      <c r="E34" s="329" t="s">
         <v>170</v>
       </c>
-      <c r="F34" s="352"/>
-      <c r="G34" s="352"/>
+      <c r="F34" s="329"/>
+      <c r="G34" s="329"/>
       <c r="H34" s="72"/>
       <c r="I34" s="72"/>
       <c r="J34" s="81" t="e">
@@ -11297,15 +11297,15 @@
       <c r="B35" s="58">
         <v>7</v>
       </c>
-      <c r="C35" s="339" t="s">
+      <c r="C35" s="332" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="336" t="s">
+      <c r="D35" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E35" s="353"/>
-      <c r="F35" s="353"/>
-      <c r="G35" s="354"/>
+      <c r="E35" s="355"/>
+      <c r="F35" s="355"/>
+      <c r="G35" s="356"/>
       <c r="H35" s="97"/>
       <c r="I35" s="101">
         <f>I36+I37</f>
@@ -11321,15 +11321,15 @@
       <c r="B36" s="58">
         <v>8</v>
       </c>
-      <c r="C36" s="340"/>
+      <c r="C36" s="333"/>
       <c r="D36" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="355" t="s">
+      <c r="E36" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="356"/>
-      <c r="G36" s="357"/>
+      <c r="F36" s="337"/>
+      <c r="G36" s="338"/>
       <c r="H36" s="72"/>
       <c r="I36" s="72"/>
       <c r="J36" s="81" t="e">
@@ -11346,13 +11346,13 @@
       <c r="B37" s="58">
         <v>9</v>
       </c>
-      <c r="C37" s="341"/>
-      <c r="D37" s="351"/>
-      <c r="E37" s="355" t="s">
+      <c r="C37" s="349"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="F37" s="356"/>
-      <c r="G37" s="357"/>
+      <c r="F37" s="337"/>
+      <c r="G37" s="338"/>
       <c r="H37" s="72"/>
       <c r="I37" s="72"/>
       <c r="J37" s="81" t="e">
@@ -11369,13 +11369,13 @@
       <c r="B38" s="58">
         <v>10</v>
       </c>
-      <c r="C38" s="336" t="s">
+      <c r="C38" s="323" t="s">
         <v>203</v>
       </c>
-      <c r="D38" s="337"/>
-      <c r="E38" s="337"/>
-      <c r="F38" s="337"/>
-      <c r="G38" s="338"/>
+      <c r="D38" s="324"/>
+      <c r="E38" s="324"/>
+      <c r="F38" s="324"/>
+      <c r="G38" s="325"/>
       <c r="H38" s="97"/>
       <c r="I38" s="97"/>
       <c r="J38" s="102"/>
@@ -11388,15 +11388,15 @@
       <c r="B39" s="58">
         <v>11</v>
       </c>
-      <c r="C39" s="339" t="s">
+      <c r="C39" s="332" t="s">
         <v>186</v>
       </c>
-      <c r="D39" s="336" t="s">
+      <c r="D39" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
-      <c r="G39" s="338"/>
+      <c r="E39" s="324"/>
+      <c r="F39" s="324"/>
+      <c r="G39" s="325"/>
       <c r="H39" s="97"/>
       <c r="I39" s="97"/>
       <c r="J39" s="102"/>
@@ -11409,15 +11409,15 @@
       <c r="B40" s="58">
         <v>12</v>
       </c>
-      <c r="C40" s="340"/>
+      <c r="C40" s="333"/>
       <c r="D40" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E40" s="345" t="s">
+      <c r="E40" s="319" t="s">
         <v>128</v>
       </c>
-      <c r="F40" s="346"/>
-      <c r="G40" s="347"/>
+      <c r="F40" s="320"/>
+      <c r="G40" s="321"/>
       <c r="H40" s="72"/>
       <c r="I40" s="72"/>
       <c r="J40" s="81" t="e">
@@ -11433,13 +11433,13 @@
       <c r="B41" s="58">
         <v>13</v>
       </c>
-      <c r="C41" s="341"/>
-      <c r="D41" s="351"/>
-      <c r="E41" s="345" t="s">
+      <c r="C41" s="349"/>
+      <c r="D41" s="350"/>
+      <c r="E41" s="319" t="s">
         <v>129</v>
       </c>
-      <c r="F41" s="346"/>
-      <c r="G41" s="347"/>
+      <c r="F41" s="320"/>
+      <c r="G41" s="321"/>
       <c r="H41" s="72"/>
       <c r="I41" s="72"/>
       <c r="J41" s="81" t="e">
@@ -11455,15 +11455,15 @@
       <c r="B42" s="58">
         <v>14</v>
       </c>
-      <c r="C42" s="339" t="s">
+      <c r="C42" s="332" t="s">
         <v>204</v>
       </c>
-      <c r="D42" s="336" t="s">
+      <c r="D42" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E42" s="337"/>
-      <c r="F42" s="337"/>
-      <c r="G42" s="338"/>
+      <c r="E42" s="324"/>
+      <c r="F42" s="324"/>
+      <c r="G42" s="325"/>
       <c r="H42" s="97"/>
       <c r="I42" s="97"/>
       <c r="J42" s="102"/>
@@ -11476,15 +11476,15 @@
       <c r="B43" s="58">
         <v>15</v>
       </c>
-      <c r="C43" s="340"/>
+      <c r="C43" s="333"/>
       <c r="D43" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="345" t="s">
+      <c r="E43" s="319" t="s">
         <v>128</v>
       </c>
-      <c r="F43" s="346"/>
-      <c r="G43" s="347"/>
+      <c r="F43" s="320"/>
+      <c r="G43" s="321"/>
       <c r="H43" s="72"/>
       <c r="I43" s="72"/>
       <c r="J43" s="81" t="e">
@@ -11500,13 +11500,13 @@
       <c r="B44" s="58">
         <v>16</v>
       </c>
-      <c r="C44" s="341"/>
-      <c r="D44" s="351"/>
-      <c r="E44" s="345" t="s">
+      <c r="C44" s="349"/>
+      <c r="D44" s="350"/>
+      <c r="E44" s="319" t="s">
         <v>129</v>
       </c>
-      <c r="F44" s="346"/>
-      <c r="G44" s="347"/>
+      <c r="F44" s="320"/>
+      <c r="G44" s="321"/>
       <c r="H44" s="72"/>
       <c r="I44" s="72"/>
       <c r="J44" s="81" t="e">
@@ -11522,15 +11522,15 @@
       <c r="B45" s="58">
         <v>17</v>
       </c>
-      <c r="C45" s="339" t="s">
+      <c r="C45" s="332" t="s">
         <v>62</v>
       </c>
-      <c r="D45" s="336" t="s">
+      <c r="D45" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="337"/>
-      <c r="F45" s="337"/>
-      <c r="G45" s="338"/>
+      <c r="E45" s="324"/>
+      <c r="F45" s="324"/>
+      <c r="G45" s="325"/>
       <c r="H45" s="97"/>
       <c r="I45" s="97"/>
       <c r="J45" s="102"/>
@@ -11543,15 +11543,15 @@
       <c r="B46" s="58">
         <v>18</v>
       </c>
-      <c r="C46" s="340"/>
+      <c r="C46" s="333"/>
       <c r="D46" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E46" s="345" t="s">
+      <c r="E46" s="319" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="346"/>
-      <c r="G46" s="347"/>
+      <c r="F46" s="320"/>
+      <c r="G46" s="321"/>
       <c r="H46" s="72"/>
       <c r="I46" s="72"/>
       <c r="J46" s="81" t="e">
@@ -11567,13 +11567,13 @@
       <c r="B47" s="58">
         <v>19</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="345" t="s">
+      <c r="C47" s="349"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="319" t="s">
         <v>64</v>
       </c>
-      <c r="F47" s="346"/>
-      <c r="G47" s="347"/>
+      <c r="F47" s="320"/>
+      <c r="G47" s="321"/>
       <c r="H47" s="72"/>
       <c r="I47" s="72"/>
       <c r="J47" s="81" t="e">
@@ -11589,15 +11589,15 @@
       <c r="B48" s="58">
         <v>20</v>
       </c>
-      <c r="C48" s="339" t="s">
+      <c r="C48" s="332" t="s">
         <v>205</v>
       </c>
-      <c r="D48" s="336" t="s">
+      <c r="D48" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="337"/>
-      <c r="F48" s="337"/>
-      <c r="G48" s="338"/>
+      <c r="E48" s="324"/>
+      <c r="F48" s="324"/>
+      <c r="G48" s="325"/>
       <c r="H48" s="97"/>
       <c r="I48" s="97"/>
       <c r="J48" s="102"/>
@@ -11610,15 +11610,15 @@
       <c r="B49" s="58">
         <v>21</v>
       </c>
-      <c r="C49" s="340"/>
+      <c r="C49" s="333"/>
       <c r="D49" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="358" t="s">
-        <v>44</v>
-      </c>
-      <c r="F49" s="359"/>
-      <c r="G49" s="359"/>
+      <c r="E49" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" s="335"/>
+      <c r="G49" s="335"/>
       <c r="H49" s="104"/>
       <c r="I49" s="104"/>
       <c r="J49" s="81"/>
@@ -11637,11 +11637,11 @@
       <c r="D50" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E50" s="345" t="s">
+      <c r="E50" s="319" t="s">
         <v>206</v>
       </c>
-      <c r="F50" s="346"/>
-      <c r="G50" s="347"/>
+      <c r="F50" s="320"/>
+      <c r="G50" s="321"/>
       <c r="H50" s="72"/>
       <c r="I50" s="72"/>
       <c r="J50" s="81" t="e">
@@ -11664,11 +11664,11 @@
       <c r="D51" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E51" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="346"/>
-      <c r="G51" s="347"/>
+      <c r="E51" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="320"/>
+      <c r="G51" s="321"/>
       <c r="H51" s="72"/>
       <c r="I51" s="72"/>
       <c r="J51" s="81"/>
@@ -11682,15 +11682,15 @@
       <c r="B52" s="58">
         <v>24</v>
       </c>
-      <c r="C52" s="339" t="s">
+      <c r="C52" s="332" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="336" t="s">
+      <c r="D52" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E52" s="337"/>
-      <c r="F52" s="337"/>
-      <c r="G52" s="338"/>
+      <c r="E52" s="324"/>
+      <c r="F52" s="324"/>
+      <c r="G52" s="325"/>
       <c r="H52" s="97"/>
       <c r="I52" s="97"/>
       <c r="J52" s="102"/>
@@ -11703,15 +11703,15 @@
       <c r="B53" s="58">
         <v>25</v>
       </c>
-      <c r="C53" s="340"/>
+      <c r="C53" s="333"/>
       <c r="D53" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E53" s="345" t="s">
+      <c r="E53" s="319" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="346"/>
-      <c r="G53" s="347"/>
+      <c r="F53" s="320"/>
+      <c r="G53" s="321"/>
       <c r="H53" s="72"/>
       <c r="I53" s="72"/>
       <c r="J53" s="81"/>
@@ -11730,11 +11730,11 @@
       <c r="D54" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E54" s="345" t="s">
+      <c r="E54" s="319" t="s">
         <v>207</v>
       </c>
-      <c r="F54" s="346"/>
-      <c r="G54" s="347"/>
+      <c r="F54" s="320"/>
+      <c r="G54" s="321"/>
       <c r="H54" s="72"/>
       <c r="I54" s="72"/>
       <c r="J54" s="81" t="e">
@@ -11751,15 +11751,15 @@
       <c r="B55" s="58">
         <v>30</v>
       </c>
-      <c r="C55" s="339" t="s">
+      <c r="C55" s="332" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="336" t="s">
+      <c r="D55" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="337"/>
-      <c r="F55" s="337"/>
-      <c r="G55" s="338"/>
+      <c r="E55" s="324"/>
+      <c r="F55" s="324"/>
+      <c r="G55" s="325"/>
       <c r="H55" s="97"/>
       <c r="I55" s="97"/>
       <c r="J55" s="102"/>
@@ -11772,15 +11772,15 @@
       <c r="B56" s="58">
         <v>31</v>
       </c>
-      <c r="C56" s="340"/>
+      <c r="C56" s="333"/>
       <c r="D56" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="345" t="s">
+      <c r="E56" s="319" t="s">
         <v>146</v>
       </c>
-      <c r="F56" s="346"/>
-      <c r="G56" s="347"/>
+      <c r="F56" s="320"/>
+      <c r="G56" s="321"/>
       <c r="H56" s="72"/>
       <c r="I56" s="72"/>
       <c r="J56" s="81"/>
@@ -11793,15 +11793,15 @@
       <c r="B57" s="58">
         <v>32</v>
       </c>
-      <c r="C57" s="340"/>
+      <c r="C57" s="333"/>
       <c r="D57" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="345" t="s">
+      <c r="E57" s="319" t="s">
         <v>147</v>
       </c>
-      <c r="F57" s="346"/>
-      <c r="G57" s="347"/>
+      <c r="F57" s="320"/>
+      <c r="G57" s="321"/>
       <c r="H57" s="72"/>
       <c r="I57" s="72"/>
       <c r="J57" s="81"/>
@@ -11820,11 +11820,11 @@
       <c r="D58" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="345" t="s">
+      <c r="E58" s="319" t="s">
         <v>148</v>
       </c>
-      <c r="F58" s="346"/>
-      <c r="G58" s="347"/>
+      <c r="F58" s="320"/>
+      <c r="G58" s="321"/>
       <c r="H58" s="72"/>
       <c r="I58" s="72"/>
       <c r="J58" s="81"/>
@@ -11843,11 +11843,11 @@
       <c r="D59" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E59" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F59" s="346"/>
-      <c r="G59" s="347"/>
+      <c r="E59" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F59" s="320"/>
+      <c r="G59" s="321"/>
       <c r="H59" s="72"/>
       <c r="I59" s="72"/>
       <c r="J59" s="81"/>
@@ -11861,15 +11861,15 @@
       <c r="B60" s="58">
         <v>35</v>
       </c>
-      <c r="C60" s="339" t="s">
+      <c r="C60" s="332" t="s">
         <v>190</v>
       </c>
-      <c r="D60" s="336" t="s">
+      <c r="D60" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E60" s="337"/>
-      <c r="F60" s="337"/>
-      <c r="G60" s="338"/>
+      <c r="E60" s="324"/>
+      <c r="F60" s="324"/>
+      <c r="G60" s="325"/>
       <c r="H60" s="97"/>
       <c r="I60" s="97"/>
       <c r="J60" s="102"/>
@@ -11882,15 +11882,15 @@
       <c r="B61" s="58">
         <v>36</v>
       </c>
-      <c r="C61" s="340"/>
+      <c r="C61" s="333"/>
       <c r="D61" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E61" s="345" t="s">
+      <c r="E61" s="319" t="s">
         <v>128</v>
       </c>
-      <c r="F61" s="346"/>
-      <c r="G61" s="347"/>
+      <c r="F61" s="320"/>
+      <c r="G61" s="321"/>
       <c r="H61" s="72"/>
       <c r="I61" s="72"/>
       <c r="J61" s="81"/>
@@ -11903,15 +11903,15 @@
       <c r="B62" s="58">
         <v>37</v>
       </c>
-      <c r="C62" s="340"/>
+      <c r="C62" s="333"/>
       <c r="D62" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E62" s="345" t="s">
+      <c r="E62" s="319" t="s">
         <v>154</v>
       </c>
-      <c r="F62" s="346"/>
-      <c r="G62" s="347"/>
+      <c r="F62" s="320"/>
+      <c r="G62" s="321"/>
       <c r="H62" s="72"/>
       <c r="I62" s="72"/>
       <c r="J62" s="81"/>
@@ -11930,11 +11930,11 @@
       <c r="D63" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E63" s="345" t="s">
+      <c r="E63" s="319" t="s">
         <v>208</v>
       </c>
-      <c r="F63" s="346"/>
-      <c r="G63" s="347"/>
+      <c r="F63" s="320"/>
+      <c r="G63" s="321"/>
       <c r="H63" s="72"/>
       <c r="I63" s="72"/>
       <c r="J63" s="81"/>
@@ -11953,11 +11953,11 @@
       <c r="D64" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E64" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F64" s="346"/>
-      <c r="G64" s="347"/>
+      <c r="E64" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F64" s="320"/>
+      <c r="G64" s="321"/>
       <c r="H64" s="72"/>
       <c r="I64" s="72"/>
       <c r="J64" s="81"/>
@@ -11971,15 +11971,15 @@
       <c r="B65" s="58">
         <v>40</v>
       </c>
-      <c r="C65" s="339" t="s">
+      <c r="C65" s="332" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="336" t="s">
+      <c r="D65" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E65" s="337"/>
-      <c r="F65" s="337"/>
-      <c r="G65" s="338"/>
+      <c r="E65" s="324"/>
+      <c r="F65" s="324"/>
+      <c r="G65" s="325"/>
       <c r="H65" s="97"/>
       <c r="I65" s="97"/>
       <c r="J65" s="102"/>
@@ -11992,17 +11992,17 @@
       <c r="B66" s="58">
         <v>41</v>
       </c>
-      <c r="C66" s="340"/>
+      <c r="C66" s="333"/>
       <c r="D66" s="66" t="s">
         <v>55</v>
       </c>
       <c r="E66" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="F66" s="336" t="s">
+      <c r="F66" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G66" s="338"/>
+      <c r="G66" s="325"/>
       <c r="H66" s="97"/>
       <c r="I66" s="97"/>
       <c r="J66" s="102"/>
@@ -12015,7 +12015,7 @@
       <c r="B67" s="58">
         <v>42</v>
       </c>
-      <c r="C67" s="340"/>
+      <c r="C67" s="333"/>
       <c r="D67" s="67" t="s">
         <v>44</v>
       </c>
@@ -12108,10 +12108,10 @@
       <c r="E70" s="103" t="s">
         <v>210</v>
       </c>
-      <c r="F70" s="336" t="s">
+      <c r="F70" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G70" s="338"/>
+      <c r="G70" s="325"/>
       <c r="H70" s="97"/>
       <c r="I70" s="97"/>
       <c r="J70" s="102"/>
@@ -12280,10 +12280,10 @@
       <c r="E76" s="103" t="s">
         <v>214</v>
       </c>
-      <c r="F76" s="336" t="s">
+      <c r="F76" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G76" s="338"/>
+      <c r="G76" s="325"/>
       <c r="H76" s="97"/>
       <c r="I76" s="97"/>
       <c r="J76" s="102"/>
@@ -12385,13 +12385,13 @@
       <c r="D80" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E80" s="360" t="s">
+      <c r="E80" s="344" t="s">
         <v>216</v>
       </c>
-      <c r="F80" s="336" t="s">
+      <c r="F80" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G80" s="338"/>
+      <c r="G80" s="325"/>
       <c r="H80" s="97"/>
       <c r="I80" s="97"/>
       <c r="J80" s="102"/>
@@ -12411,15 +12411,15 @@
       <c r="D81" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E81" s="361"/>
+      <c r="E81" s="345"/>
       <c r="F81" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="G81" s="362" t="s">
+      <c r="G81" s="346" t="s">
         <v>136</v>
       </c>
-      <c r="H81" s="363"/>
-      <c r="I81" s="364"/>
+      <c r="H81" s="347"/>
+      <c r="I81" s="348"/>
       <c r="J81" s="81" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -12498,13 +12498,13 @@
       <c r="D84" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E84" s="360" t="s">
-        <v>44</v>
-      </c>
-      <c r="F84" s="336" t="s">
+      <c r="E84" s="344" t="s">
+        <v>44</v>
+      </c>
+      <c r="F84" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G84" s="338"/>
+      <c r="G84" s="325"/>
       <c r="H84" s="97"/>
       <c r="I84" s="97"/>
       <c r="J84" s="102"/>
@@ -12524,7 +12524,7 @@
       <c r="D85" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E85" s="361"/>
+      <c r="E85" s="345"/>
       <c r="F85" s="66" t="s">
         <v>55</v>
       </c>
@@ -12573,15 +12573,15 @@
       <c r="B87" s="58">
         <v>62</v>
       </c>
-      <c r="C87" s="339" t="s">
+      <c r="C87" s="332" t="s">
         <v>144</v>
       </c>
-      <c r="D87" s="336" t="s">
+      <c r="D87" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E87" s="337"/>
-      <c r="F87" s="337"/>
-      <c r="G87" s="338"/>
+      <c r="E87" s="324"/>
+      <c r="F87" s="324"/>
+      <c r="G87" s="325"/>
       <c r="H87" s="97"/>
       <c r="I87" s="110"/>
       <c r="J87" s="102"/>
@@ -12594,15 +12594,15 @@
       <c r="B88" s="58">
         <v>63</v>
       </c>
-      <c r="C88" s="340"/>
+      <c r="C88" s="333"/>
       <c r="D88" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E88" s="358" t="s">
-        <v>44</v>
-      </c>
-      <c r="F88" s="359"/>
-      <c r="G88" s="359"/>
+      <c r="E88" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F88" s="335"/>
+      <c r="G88" s="335"/>
       <c r="H88" s="104"/>
       <c r="I88" s="104"/>
       <c r="J88" s="81" t="e">
@@ -12624,11 +12624,11 @@
       <c r="D89" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F89" s="346"/>
-      <c r="G89" s="347"/>
+      <c r="E89" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F89" s="320"/>
+      <c r="G89" s="321"/>
       <c r="H89" s="72"/>
       <c r="I89" s="109"/>
       <c r="J89" s="81"/>
@@ -12648,11 +12648,11 @@
       <c r="D90" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E90" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F90" s="346"/>
-      <c r="G90" s="347"/>
+      <c r="E90" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F90" s="320"/>
+      <c r="G90" s="321"/>
       <c r="H90" s="72"/>
       <c r="I90" s="109"/>
       <c r="J90" s="81"/>
@@ -12666,15 +12666,15 @@
       <c r="B91" s="58">
         <v>66</v>
       </c>
-      <c r="C91" s="339" t="s">
+      <c r="C91" s="332" t="s">
         <v>189</v>
       </c>
-      <c r="D91" s="336" t="s">
+      <c r="D91" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="337"/>
-      <c r="F91" s="337"/>
-      <c r="G91" s="338"/>
+      <c r="E91" s="324"/>
+      <c r="F91" s="324"/>
+      <c r="G91" s="325"/>
       <c r="H91" s="97"/>
       <c r="I91" s="110"/>
       <c r="J91" s="102"/>
@@ -12687,15 +12687,15 @@
       <c r="B92" s="58">
         <v>67</v>
       </c>
-      <c r="C92" s="340"/>
+      <c r="C92" s="333"/>
       <c r="D92" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E92" s="358" t="s">
-        <v>44</v>
-      </c>
-      <c r="F92" s="359"/>
-      <c r="G92" s="359"/>
+      <c r="E92" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F92" s="335"/>
+      <c r="G92" s="335"/>
       <c r="H92" s="104"/>
       <c r="I92" s="104"/>
       <c r="J92" s="81"/>
@@ -12714,11 +12714,11 @@
       <c r="D93" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F93" s="346"/>
-      <c r="G93" s="347"/>
+      <c r="E93" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F93" s="320"/>
+      <c r="G93" s="321"/>
       <c r="H93" s="72"/>
       <c r="I93" s="109"/>
       <c r="J93" s="81"/>
@@ -12738,11 +12738,11 @@
       <c r="D94" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E94" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F94" s="346"/>
-      <c r="G94" s="347"/>
+      <c r="E94" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F94" s="320"/>
+      <c r="G94" s="321"/>
       <c r="H94" s="72"/>
       <c r="I94" s="109"/>
       <c r="J94" s="81"/>
@@ -12756,15 +12756,15 @@
       <c r="B95" s="58">
         <v>70</v>
       </c>
-      <c r="C95" s="339" t="s">
+      <c r="C95" s="332" t="s">
         <v>137</v>
       </c>
-      <c r="D95" s="336" t="s">
+      <c r="D95" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E95" s="337"/>
-      <c r="F95" s="337"/>
-      <c r="G95" s="338"/>
+      <c r="E95" s="324"/>
+      <c r="F95" s="324"/>
+      <c r="G95" s="325"/>
       <c r="H95" s="97"/>
       <c r="I95" s="110"/>
       <c r="J95" s="102"/>
@@ -12777,15 +12777,15 @@
       <c r="B96" s="58">
         <v>71</v>
       </c>
-      <c r="C96" s="340"/>
+      <c r="C96" s="333"/>
       <c r="D96" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E96" s="358" t="s">
-        <v>44</v>
-      </c>
-      <c r="F96" s="359"/>
-      <c r="G96" s="359"/>
+      <c r="E96" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F96" s="335"/>
+      <c r="G96" s="335"/>
       <c r="H96" s="104"/>
       <c r="I96" s="104"/>
       <c r="J96" s="81"/>
@@ -12804,11 +12804,11 @@
       <c r="D97" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E97" s="345" t="s">
+      <c r="E97" s="319" t="s">
         <v>217</v>
       </c>
-      <c r="F97" s="346"/>
-      <c r="G97" s="347"/>
+      <c r="F97" s="320"/>
+      <c r="G97" s="321"/>
       <c r="H97" s="72"/>
       <c r="I97" s="109"/>
       <c r="J97" s="81" t="e">
@@ -12823,11 +12823,11 @@
       <c r="B98" s="58"/>
       <c r="C98" s="77"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="345" t="s">
+      <c r="E98" s="319" t="s">
         <v>218</v>
       </c>
-      <c r="F98" s="346"/>
-      <c r="G98" s="347"/>
+      <c r="F98" s="320"/>
+      <c r="G98" s="321"/>
       <c r="H98" s="72"/>
       <c r="I98" s="109"/>
       <c r="J98" s="81"/>
@@ -12839,9 +12839,9 @@
       <c r="B99" s="58"/>
       <c r="C99" s="77"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="345"/>
-      <c r="F99" s="346"/>
-      <c r="G99" s="347"/>
+      <c r="E99" s="319"/>
+      <c r="F99" s="320"/>
+      <c r="G99" s="321"/>
       <c r="H99" s="72"/>
       <c r="I99" s="109"/>
       <c r="J99" s="81"/>
@@ -12861,11 +12861,11 @@
       <c r="D100" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E100" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F100" s="346"/>
-      <c r="G100" s="347"/>
+      <c r="E100" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F100" s="320"/>
+      <c r="G100" s="321"/>
       <c r="H100" s="72"/>
       <c r="I100" s="109"/>
       <c r="J100" s="81"/>
@@ -12879,15 +12879,15 @@
       <c r="B101" s="58">
         <v>75</v>
       </c>
-      <c r="C101" s="339" t="s">
+      <c r="C101" s="332" t="s">
         <v>17</v>
       </c>
-      <c r="D101" s="336" t="s">
+      <c r="D101" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E101" s="337"/>
-      <c r="F101" s="337"/>
-      <c r="G101" s="338"/>
+      <c r="E101" s="324"/>
+      <c r="F101" s="324"/>
+      <c r="G101" s="325"/>
       <c r="H101" s="97"/>
       <c r="I101" s="111">
         <f>I102+I103+I104</f>
@@ -12903,15 +12903,15 @@
       <c r="B102" s="58">
         <v>76</v>
       </c>
-      <c r="C102" s="340"/>
+      <c r="C102" s="333"/>
       <c r="D102" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E102" s="355" t="s">
+      <c r="E102" s="336" t="s">
         <v>219</v>
       </c>
-      <c r="F102" s="356"/>
-      <c r="G102" s="357"/>
+      <c r="F102" s="337"/>
+      <c r="G102" s="338"/>
       <c r="H102" s="72"/>
       <c r="I102" s="109"/>
       <c r="J102" s="81">
@@ -12927,15 +12927,15 @@
       <c r="B103" s="58">
         <v>77</v>
       </c>
-      <c r="C103" s="340"/>
+      <c r="C103" s="333"/>
       <c r="D103" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E103" s="355" t="s">
+      <c r="E103" s="336" t="s">
         <v>220</v>
       </c>
-      <c r="F103" s="356"/>
-      <c r="G103" s="357"/>
+      <c r="F103" s="337"/>
+      <c r="G103" s="338"/>
       <c r="H103" s="72"/>
       <c r="I103" s="72"/>
       <c r="J103" s="81">
@@ -12957,11 +12957,11 @@
       <c r="D104" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E104" s="355" t="s">
+      <c r="E104" s="336" t="s">
         <v>221</v>
       </c>
-      <c r="F104" s="356"/>
-      <c r="G104" s="357"/>
+      <c r="F104" s="337"/>
+      <c r="G104" s="338"/>
       <c r="H104" s="72"/>
       <c r="I104" s="72"/>
       <c r="J104" s="81">
@@ -12977,13 +12977,13 @@
       <c r="B105" s="58">
         <v>83</v>
       </c>
-      <c r="C105" s="336" t="s">
+      <c r="C105" s="323" t="s">
         <v>7</v>
       </c>
-      <c r="D105" s="337"/>
-      <c r="E105" s="337"/>
-      <c r="F105" s="337"/>
-      <c r="G105" s="338"/>
+      <c r="D105" s="324"/>
+      <c r="E105" s="324"/>
+      <c r="F105" s="324"/>
+      <c r="G105" s="325"/>
       <c r="H105" s="97"/>
       <c r="I105" s="97"/>
       <c r="J105" s="102" t="e">
@@ -12999,13 +12999,13 @@
       <c r="B106" s="58">
         <v>84</v>
       </c>
-      <c r="C106" s="336" t="s">
+      <c r="C106" s="323" t="s">
         <v>222</v>
       </c>
-      <c r="D106" s="337"/>
-      <c r="E106" s="337"/>
-      <c r="F106" s="337"/>
-      <c r="G106" s="338"/>
+      <c r="D106" s="324"/>
+      <c r="E106" s="324"/>
+      <c r="F106" s="324"/>
+      <c r="G106" s="325"/>
       <c r="H106" s="97"/>
       <c r="I106" s="101"/>
       <c r="J106" s="102" t="e">
@@ -13021,15 +13021,15 @@
       <c r="B107" s="58">
         <v>85</v>
       </c>
-      <c r="C107" s="339" t="s">
+      <c r="C107" s="332" t="s">
         <v>223</v>
       </c>
-      <c r="D107" s="336" t="s">
+      <c r="D107" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E107" s="337"/>
-      <c r="F107" s="337"/>
-      <c r="G107" s="338"/>
+      <c r="E107" s="324"/>
+      <c r="F107" s="324"/>
+      <c r="G107" s="325"/>
       <c r="H107" s="97"/>
       <c r="I107" s="97"/>
       <c r="J107" s="102"/>
@@ -13042,15 +13042,15 @@
       <c r="B108" s="58">
         <v>86</v>
       </c>
-      <c r="C108" s="340"/>
+      <c r="C108" s="333"/>
       <c r="D108" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E108" s="355" t="s">
+      <c r="E108" s="336" t="s">
         <v>224</v>
       </c>
-      <c r="F108" s="356"/>
-      <c r="G108" s="357"/>
+      <c r="F108" s="337"/>
+      <c r="G108" s="338"/>
       <c r="H108" s="72"/>
       <c r="I108" s="63"/>
       <c r="J108" s="81" t="e">
@@ -13072,11 +13072,11 @@
       <c r="D109" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E109" s="345" t="s">
+      <c r="E109" s="319" t="s">
         <v>225</v>
       </c>
-      <c r="F109" s="346"/>
-      <c r="G109" s="347"/>
+      <c r="F109" s="320"/>
+      <c r="G109" s="321"/>
       <c r="H109" s="72"/>
       <c r="I109" s="63"/>
       <c r="J109" s="81"/>
@@ -13096,11 +13096,11 @@
       <c r="D110" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E110" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F110" s="346"/>
-      <c r="G110" s="347"/>
+      <c r="E110" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F110" s="320"/>
+      <c r="G110" s="321"/>
       <c r="H110" s="72"/>
       <c r="I110" s="72"/>
       <c r="J110" s="81"/>
@@ -13114,15 +13114,15 @@
       <c r="B111" s="58">
         <v>89</v>
       </c>
-      <c r="C111" s="339" t="s">
+      <c r="C111" s="332" t="s">
         <v>192</v>
       </c>
-      <c r="D111" s="336" t="s">
+      <c r="D111" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E111" s="337"/>
-      <c r="F111" s="337"/>
-      <c r="G111" s="338"/>
+      <c r="E111" s="324"/>
+      <c r="F111" s="324"/>
+      <c r="G111" s="325"/>
       <c r="H111" s="97"/>
       <c r="I111" s="97"/>
       <c r="J111" s="102"/>
@@ -13135,15 +13135,15 @@
       <c r="B112" s="58">
         <v>90</v>
       </c>
-      <c r="C112" s="340"/>
+      <c r="C112" s="333"/>
       <c r="D112" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E112" s="355" t="s">
+      <c r="E112" s="336" t="s">
         <v>226</v>
       </c>
-      <c r="F112" s="356"/>
-      <c r="G112" s="357"/>
+      <c r="F112" s="337"/>
+      <c r="G112" s="338"/>
       <c r="H112" s="72"/>
       <c r="I112" s="72"/>
       <c r="J112" s="81"/>
@@ -13162,11 +13162,11 @@
       <c r="D113" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E113" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F113" s="346"/>
-      <c r="G113" s="347"/>
+      <c r="E113" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F113" s="320"/>
+      <c r="G113" s="321"/>
       <c r="H113" s="72"/>
       <c r="I113" s="72"/>
       <c r="J113" s="81"/>
@@ -13179,15 +13179,15 @@
       <c r="B114" s="58">
         <v>92</v>
       </c>
-      <c r="C114" s="339" t="s">
+      <c r="C114" s="332" t="s">
         <v>191</v>
       </c>
-      <c r="D114" s="336" t="s">
+      <c r="D114" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E114" s="337"/>
-      <c r="F114" s="337"/>
-      <c r="G114" s="338"/>
+      <c r="E114" s="324"/>
+      <c r="F114" s="324"/>
+      <c r="G114" s="325"/>
       <c r="H114" s="97"/>
       <c r="I114" s="97"/>
       <c r="J114" s="102"/>
@@ -13200,15 +13200,15 @@
       <c r="B115" s="58">
         <v>93</v>
       </c>
-      <c r="C115" s="340"/>
+      <c r="C115" s="333"/>
       <c r="D115" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E115" s="358" t="s">
-        <v>44</v>
-      </c>
-      <c r="F115" s="359"/>
-      <c r="G115" s="359"/>
+      <c r="E115" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F115" s="335"/>
+      <c r="G115" s="335"/>
       <c r="H115" s="104"/>
       <c r="I115" s="104"/>
       <c r="J115" s="112"/>
@@ -13227,11 +13227,11 @@
       <c r="D116" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E116" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F116" s="346"/>
-      <c r="G116" s="347"/>
+      <c r="E116" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F116" s="320"/>
+      <c r="G116" s="321"/>
       <c r="H116" s="72"/>
       <c r="I116" s="63"/>
       <c r="J116" s="81"/>
@@ -13251,11 +13251,11 @@
       <c r="D117" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E117" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F117" s="346"/>
-      <c r="G117" s="347"/>
+      <c r="E117" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F117" s="320"/>
+      <c r="G117" s="321"/>
       <c r="H117" s="72"/>
       <c r="I117" s="72"/>
       <c r="J117" s="81"/>
@@ -13269,15 +13269,15 @@
       <c r="B118" s="58">
         <v>96</v>
       </c>
-      <c r="C118" s="339" t="s">
+      <c r="C118" s="332" t="s">
         <v>149</v>
       </c>
-      <c r="D118" s="336" t="s">
+      <c r="D118" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E118" s="337"/>
-      <c r="F118" s="337"/>
-      <c r="G118" s="338"/>
+      <c r="E118" s="324"/>
+      <c r="F118" s="324"/>
+      <c r="G118" s="325"/>
       <c r="H118" s="97"/>
       <c r="I118" s="97"/>
       <c r="J118" s="102"/>
@@ -13290,15 +13290,15 @@
       <c r="B119" s="58">
         <v>97</v>
       </c>
-      <c r="C119" s="340"/>
+      <c r="C119" s="333"/>
       <c r="D119" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E119" s="355" t="s">
+      <c r="E119" s="336" t="s">
         <v>227</v>
       </c>
-      <c r="F119" s="356"/>
-      <c r="G119" s="357"/>
+      <c r="F119" s="337"/>
+      <c r="G119" s="338"/>
       <c r="H119" s="72"/>
       <c r="I119" s="72"/>
       <c r="J119" s="81"/>
@@ -13317,11 +13317,11 @@
       <c r="D120" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E120" s="355" t="s">
+      <c r="E120" s="336" t="s">
         <v>228</v>
       </c>
-      <c r="F120" s="356"/>
-      <c r="G120" s="357"/>
+      <c r="F120" s="337"/>
+      <c r="G120" s="338"/>
       <c r="H120" s="72"/>
       <c r="I120" s="72"/>
       <c r="J120" s="81"/>
@@ -13340,11 +13340,11 @@
       <c r="D121" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E121" s="355" t="s">
+      <c r="E121" s="336" t="s">
         <v>229</v>
       </c>
-      <c r="F121" s="356"/>
-      <c r="G121" s="357"/>
+      <c r="F121" s="337"/>
+      <c r="G121" s="338"/>
       <c r="H121" s="72"/>
       <c r="I121" s="72"/>
       <c r="J121" s="81"/>
@@ -13363,11 +13363,11 @@
       <c r="D122" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E122" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F122" s="346"/>
-      <c r="G122" s="347"/>
+      <c r="E122" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F122" s="320"/>
+      <c r="G122" s="321"/>
       <c r="H122" s="72"/>
       <c r="I122" s="72"/>
       <c r="J122" s="81"/>
@@ -13381,15 +13381,15 @@
       <c r="B123" s="58">
         <v>101</v>
       </c>
-      <c r="C123" s="339" t="s">
+      <c r="C123" s="332" t="s">
         <v>230</v>
       </c>
-      <c r="D123" s="336" t="s">
+      <c r="D123" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E123" s="337"/>
-      <c r="F123" s="337"/>
-      <c r="G123" s="338"/>
+      <c r="E123" s="324"/>
+      <c r="F123" s="324"/>
+      <c r="G123" s="325"/>
       <c r="H123" s="97"/>
       <c r="I123" s="97"/>
       <c r="J123" s="102"/>
@@ -13402,17 +13402,17 @@
       <c r="B124" s="58">
         <v>102</v>
       </c>
-      <c r="C124" s="340"/>
+      <c r="C124" s="333"/>
       <c r="D124" s="66" t="s">
         <v>55</v>
       </c>
       <c r="E124" s="342" t="s">
         <v>231</v>
       </c>
-      <c r="F124" s="336" t="s">
+      <c r="F124" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G124" s="338"/>
+      <c r="G124" s="325"/>
       <c r="H124" s="97"/>
       <c r="I124" s="97"/>
       <c r="J124" s="102"/>
@@ -13425,7 +13425,7 @@
       <c r="B125" s="58">
         <v>103</v>
       </c>
-      <c r="C125" s="340"/>
+      <c r="C125" s="333"/>
       <c r="D125" s="67" t="s">
         <v>44</v>
       </c>
@@ -13448,7 +13448,7 @@
       <c r="B126" s="58">
         <v>104</v>
       </c>
-      <c r="C126" s="340"/>
+      <c r="C126" s="333"/>
       <c r="D126" s="67" t="s">
         <v>44</v>
       </c>
@@ -13534,11 +13534,11 @@
       <c r="D129" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E129" s="355" t="s">
+      <c r="E129" s="336" t="s">
         <v>234</v>
       </c>
-      <c r="F129" s="356"/>
-      <c r="G129" s="357"/>
+      <c r="F129" s="337"/>
+      <c r="G129" s="338"/>
       <c r="H129" s="72"/>
       <c r="I129" s="72"/>
       <c r="J129" s="81"/>
@@ -13557,11 +13557,11 @@
       <c r="D130" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E130" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F130" s="346"/>
-      <c r="G130" s="347"/>
+      <c r="E130" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F130" s="320"/>
+      <c r="G130" s="321"/>
       <c r="H130" s="72"/>
       <c r="I130" s="72"/>
       <c r="J130" s="81"/>
@@ -13575,15 +13575,15 @@
       <c r="B131" s="58">
         <v>109</v>
       </c>
-      <c r="C131" s="339" t="s">
+      <c r="C131" s="332" t="s">
         <v>175</v>
       </c>
-      <c r="D131" s="336" t="s">
+      <c r="D131" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E131" s="337"/>
-      <c r="F131" s="337"/>
-      <c r="G131" s="338"/>
+      <c r="E131" s="324"/>
+      <c r="F131" s="324"/>
+      <c r="G131" s="325"/>
       <c r="H131" s="97"/>
       <c r="I131" s="101">
         <f>SUM(I132:I136)</f>
@@ -13599,15 +13599,15 @@
       <c r="B132" s="58">
         <v>110</v>
       </c>
-      <c r="C132" s="340"/>
+      <c r="C132" s="333"/>
       <c r="D132" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E132" s="355" t="s">
+      <c r="E132" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="F132" s="356"/>
-      <c r="G132" s="357"/>
+      <c r="F132" s="337"/>
+      <c r="G132" s="338"/>
       <c r="H132" s="72"/>
       <c r="I132" s="72"/>
       <c r="J132" s="81" t="e">
@@ -13623,15 +13623,15 @@
       <c r="B133" s="58">
         <v>111</v>
       </c>
-      <c r="C133" s="340"/>
+      <c r="C133" s="333"/>
       <c r="D133" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E133" s="355" t="s">
+      <c r="E133" s="336" t="s">
         <v>235</v>
       </c>
-      <c r="F133" s="356"/>
-      <c r="G133" s="357"/>
+      <c r="F133" s="337"/>
+      <c r="G133" s="338"/>
       <c r="H133" s="72"/>
       <c r="I133" s="72"/>
       <c r="J133" s="81" t="e">
@@ -13653,11 +13653,11 @@
       <c r="D134" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E134" s="355" t="s">
+      <c r="E134" s="336" t="s">
         <v>11</v>
       </c>
-      <c r="F134" s="356"/>
-      <c r="G134" s="357"/>
+      <c r="F134" s="337"/>
+      <c r="G134" s="338"/>
       <c r="H134" s="72"/>
       <c r="I134" s="72"/>
       <c r="J134" s="81" t="e">
@@ -13679,11 +13679,11 @@
       <c r="D135" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E135" s="355" t="s">
+      <c r="E135" s="336" t="s">
         <v>9</v>
       </c>
-      <c r="F135" s="356"/>
-      <c r="G135" s="357"/>
+      <c r="F135" s="337"/>
+      <c r="G135" s="338"/>
       <c r="H135" s="72"/>
       <c r="I135" s="72"/>
       <c r="J135" s="81" t="e">
@@ -13705,11 +13705,11 @@
       <c r="D136" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E136" s="352" t="s">
+      <c r="E136" s="329" t="s">
         <v>236</v>
       </c>
-      <c r="F136" s="352"/>
-      <c r="G136" s="352"/>
+      <c r="F136" s="329"/>
+      <c r="G136" s="329"/>
       <c r="H136" s="72"/>
       <c r="I136" s="72"/>
       <c r="J136" s="81" t="e">
@@ -13732,11 +13732,11 @@
       <c r="D137" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E137" s="365" t="s">
-        <v>44</v>
-      </c>
-      <c r="F137" s="366"/>
-      <c r="G137" s="367"/>
+      <c r="E137" s="339" t="s">
+        <v>44</v>
+      </c>
+      <c r="F137" s="340"/>
+      <c r="G137" s="341"/>
       <c r="H137" s="115"/>
       <c r="I137" s="115"/>
       <c r="J137" s="116"/>
@@ -13750,15 +13750,15 @@
       <c r="B138" s="58">
         <v>118</v>
       </c>
-      <c r="C138" s="339" t="s">
+      <c r="C138" s="332" t="s">
         <v>237</v>
       </c>
-      <c r="D138" s="336" t="s">
+      <c r="D138" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E138" s="337"/>
-      <c r="F138" s="337"/>
-      <c r="G138" s="338"/>
+      <c r="E138" s="324"/>
+      <c r="F138" s="324"/>
+      <c r="G138" s="325"/>
       <c r="H138" s="97"/>
       <c r="I138" s="117"/>
       <c r="J138" s="118"/>
@@ -13771,15 +13771,15 @@
       <c r="B139" s="58">
         <v>119</v>
       </c>
-      <c r="C139" s="340"/>
+      <c r="C139" s="333"/>
       <c r="D139" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E139" s="355" t="s">
+      <c r="E139" s="336" t="s">
         <v>19</v>
       </c>
-      <c r="F139" s="356"/>
-      <c r="G139" s="357"/>
+      <c r="F139" s="337"/>
+      <c r="G139" s="338"/>
       <c r="H139" s="109"/>
       <c r="I139" s="113"/>
       <c r="J139" s="81" t="e">
@@ -13804,10 +13804,10 @@
       <c r="E140" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="F140" s="336" t="s">
+      <c r="F140" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G140" s="338"/>
+      <c r="G140" s="325"/>
       <c r="H140" s="110"/>
       <c r="I140" s="97"/>
       <c r="J140" s="102"/>
@@ -13829,7 +13829,7 @@
       <c r="E141" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F141" s="372" t="s">
+      <c r="F141" s="330" t="s">
         <v>55</v>
       </c>
       <c r="G141" s="108" t="s">
@@ -13856,7 +13856,7 @@
       <c r="E142" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F142" s="373"/>
+      <c r="F142" s="331"/>
       <c r="G142" s="60" t="s">
         <v>238</v>
       </c>
@@ -13907,10 +13907,10 @@
       <c r="E144" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="F144" s="336" t="s">
+      <c r="F144" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G144" s="338"/>
+      <c r="G144" s="325"/>
       <c r="H144" s="97"/>
       <c r="I144" s="110"/>
       <c r="J144" s="102"/>
@@ -13932,7 +13932,7 @@
       <c r="E145" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F145" s="372" t="s">
+      <c r="F145" s="330" t="s">
         <v>55</v>
       </c>
       <c r="G145" s="108" t="s">
@@ -13959,7 +13959,7 @@
       <c r="E146" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F146" s="373"/>
+      <c r="F146" s="331"/>
       <c r="G146" s="60" t="s">
         <v>18</v>
       </c>
@@ -14029,15 +14029,15 @@
       <c r="B149" s="58">
         <v>129</v>
       </c>
-      <c r="C149" s="339" t="s">
+      <c r="C149" s="332" t="s">
         <v>239</v>
       </c>
-      <c r="D149" s="336" t="s">
+      <c r="D149" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E149" s="337"/>
-      <c r="F149" s="337"/>
-      <c r="G149" s="338"/>
+      <c r="E149" s="324"/>
+      <c r="F149" s="324"/>
+      <c r="G149" s="325"/>
       <c r="H149" s="97"/>
       <c r="I149" s="110"/>
       <c r="J149" s="102"/>
@@ -14050,15 +14050,15 @@
       <c r="B150" s="121">
         <v>130</v>
       </c>
-      <c r="C150" s="340"/>
+      <c r="C150" s="333"/>
       <c r="D150" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E150" s="358" t="s">
-        <v>44</v>
-      </c>
-      <c r="F150" s="359"/>
-      <c r="G150" s="359"/>
+      <c r="E150" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F150" s="335"/>
+      <c r="G150" s="335"/>
       <c r="H150" s="104"/>
       <c r="I150" s="104"/>
       <c r="J150" s="81"/>
@@ -14077,11 +14077,11 @@
       <c r="D151" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E151" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F151" s="346"/>
-      <c r="G151" s="347"/>
+      <c r="E151" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F151" s="320"/>
+      <c r="G151" s="321"/>
       <c r="H151" s="72"/>
       <c r="I151" s="109"/>
       <c r="J151" s="81"/>
@@ -14095,15 +14095,15 @@
       <c r="B152" s="58">
         <v>132</v>
       </c>
-      <c r="C152" s="368" t="s">
+      <c r="C152" s="322" t="s">
         <v>240</v>
       </c>
-      <c r="D152" s="336" t="s">
+      <c r="D152" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E152" s="337"/>
-      <c r="F152" s="337"/>
-      <c r="G152" s="338"/>
+      <c r="E152" s="324"/>
+      <c r="F152" s="324"/>
+      <c r="G152" s="325"/>
       <c r="H152" s="97"/>
       <c r="I152" s="110"/>
       <c r="J152" s="102"/>
@@ -14116,15 +14116,15 @@
       <c r="B153" s="58">
         <v>133</v>
       </c>
-      <c r="C153" s="368"/>
+      <c r="C153" s="322"/>
       <c r="D153" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E153" s="369" t="s">
+      <c r="E153" s="326" t="s">
         <v>241</v>
       </c>
-      <c r="F153" s="370"/>
-      <c r="G153" s="371"/>
+      <c r="F153" s="327"/>
+      <c r="G153" s="328"/>
       <c r="H153" s="122"/>
       <c r="I153" s="123"/>
       <c r="J153" s="81"/>
@@ -14143,11 +14143,11 @@
       <c r="D154" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E154" s="352" t="s">
+      <c r="E154" s="329" t="s">
         <v>198</v>
       </c>
-      <c r="F154" s="352"/>
-      <c r="G154" s="352"/>
+      <c r="F154" s="329"/>
+      <c r="G154" s="329"/>
       <c r="H154" s="72"/>
       <c r="I154" s="120" t="e">
         <f>SUM(#REF!)</f>
@@ -14173,120 +14173,15 @@
     </row>
   </sheetData>
   <mergeCells count="142">
-    <mergeCell ref="E151:G151"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D152:G152"/>
-    <mergeCell ref="E153:G153"/>
-    <mergeCell ref="E154:G154"/>
-    <mergeCell ref="F140:G140"/>
-    <mergeCell ref="F141:F142"/>
-    <mergeCell ref="F144:G144"/>
-    <mergeCell ref="F145:F146"/>
-    <mergeCell ref="C149:C150"/>
-    <mergeCell ref="D149:G149"/>
-    <mergeCell ref="E150:G150"/>
-    <mergeCell ref="E134:G134"/>
-    <mergeCell ref="E135:G135"/>
-    <mergeCell ref="E136:G136"/>
-    <mergeCell ref="E137:G137"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:G138"/>
-    <mergeCell ref="E139:G139"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="E130:G130"/>
-    <mergeCell ref="C131:C133"/>
-    <mergeCell ref="D131:G131"/>
-    <mergeCell ref="E132:G132"/>
-    <mergeCell ref="E133:G133"/>
-    <mergeCell ref="E121:G121"/>
-    <mergeCell ref="E122:G122"/>
-    <mergeCell ref="C123:C126"/>
-    <mergeCell ref="D123:G123"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="E116:G116"/>
-    <mergeCell ref="E117:G117"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:G118"/>
-    <mergeCell ref="E119:G119"/>
-    <mergeCell ref="E120:G120"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="D111:G111"/>
-    <mergeCell ref="E112:G112"/>
-    <mergeCell ref="E113:G113"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="D114:G114"/>
-    <mergeCell ref="E115:G115"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="D107:G107"/>
-    <mergeCell ref="E108:G108"/>
-    <mergeCell ref="E109:G109"/>
-    <mergeCell ref="E110:G110"/>
-    <mergeCell ref="E104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="E98:G98"/>
-    <mergeCell ref="E99:G99"/>
-    <mergeCell ref="E100:G100"/>
-    <mergeCell ref="C101:C103"/>
-    <mergeCell ref="D101:G101"/>
-    <mergeCell ref="E102:G102"/>
-    <mergeCell ref="E103:G103"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="E94:G94"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="D95:G95"/>
-    <mergeCell ref="E96:G96"/>
-    <mergeCell ref="E97:G97"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:G87"/>
-    <mergeCell ref="E88:G88"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="E90:G90"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="D91:G91"/>
-    <mergeCell ref="E92:G92"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="G81:I81"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="E64:G64"/>
-    <mergeCell ref="C65:C67"/>
-    <mergeCell ref="D65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="D60:G60"/>
-    <mergeCell ref="E61:G61"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D55:G55"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:G48"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:G46"/>
-    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:G24"/>
+    <mergeCell ref="I22:J24"/>
     <mergeCell ref="C29:G29"/>
     <mergeCell ref="C30:C34"/>
     <mergeCell ref="D30:G30"/>
@@ -14306,15 +14201,120 @@
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="E36:G36"/>
     <mergeCell ref="E37:G37"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:G24"/>
-    <mergeCell ref="I22:J24"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D55:G55"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="G81:I81"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="C65:C67"/>
+    <mergeCell ref="D65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="E94:G94"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:G95"/>
+    <mergeCell ref="E96:G96"/>
+    <mergeCell ref="E97:G97"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:G87"/>
+    <mergeCell ref="E88:G88"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="E90:G90"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="D91:G91"/>
+    <mergeCell ref="E92:G92"/>
+    <mergeCell ref="E104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="E98:G98"/>
+    <mergeCell ref="E99:G99"/>
+    <mergeCell ref="E100:G100"/>
+    <mergeCell ref="C101:C103"/>
+    <mergeCell ref="D101:G101"/>
+    <mergeCell ref="E102:G102"/>
+    <mergeCell ref="E103:G103"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="D111:G111"/>
+    <mergeCell ref="E112:G112"/>
+    <mergeCell ref="E113:G113"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:G114"/>
+    <mergeCell ref="E115:G115"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="D107:G107"/>
+    <mergeCell ref="E108:G108"/>
+    <mergeCell ref="E109:G109"/>
+    <mergeCell ref="E110:G110"/>
+    <mergeCell ref="E121:G121"/>
+    <mergeCell ref="E122:G122"/>
+    <mergeCell ref="C123:C126"/>
+    <mergeCell ref="D123:G123"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="E116:G116"/>
+    <mergeCell ref="E117:G117"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:G118"/>
+    <mergeCell ref="E119:G119"/>
+    <mergeCell ref="E120:G120"/>
+    <mergeCell ref="E134:G134"/>
+    <mergeCell ref="E135:G135"/>
+    <mergeCell ref="E136:G136"/>
+    <mergeCell ref="E137:G137"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:G138"/>
+    <mergeCell ref="E139:G139"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="E130:G130"/>
+    <mergeCell ref="C131:C133"/>
+    <mergeCell ref="D131:G131"/>
+    <mergeCell ref="E132:G132"/>
+    <mergeCell ref="E133:G133"/>
+    <mergeCell ref="E151:G151"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:G152"/>
+    <mergeCell ref="E153:G153"/>
+    <mergeCell ref="E154:G154"/>
+    <mergeCell ref="F140:G140"/>
+    <mergeCell ref="F141:F142"/>
+    <mergeCell ref="F144:G144"/>
+    <mergeCell ref="F145:F146"/>
+    <mergeCell ref="C149:C150"/>
+    <mergeCell ref="D149:G149"/>
+    <mergeCell ref="E150:G150"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="64" orientation="portrait" r:id="rId1"/>
@@ -14344,15 +14344,15 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="319" t="s">
+      <c r="B1" s="357" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="319"/>
-      <c r="D1" s="319"/>
-      <c r="E1" s="319"/>
-      <c r="F1" s="319"/>
-      <c r="G1" s="319"/>
-      <c r="H1" s="319"/>
+      <c r="C1" s="357"/>
+      <c r="D1" s="357"/>
+      <c r="E1" s="357"/>
+      <c r="F1" s="357"/>
+      <c r="G1" s="357"/>
+      <c r="H1" s="357"/>
       <c r="L1" s="51"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1">
@@ -14386,30 +14386,30 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="320" t="s">
+      <c r="B3" s="358" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="320"/>
-      <c r="D3" s="320"/>
-      <c r="E3" s="320"/>
-      <c r="F3" s="320"/>
-      <c r="G3" s="320"/>
-      <c r="H3" s="320"/>
+      <c r="C3" s="358"/>
+      <c r="D3" s="358"/>
+      <c r="E3" s="358"/>
+      <c r="F3" s="358"/>
+      <c r="G3" s="358"/>
+      <c r="H3" s="358"/>
       <c r="L3" s="51"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="321" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="321"/>
-      <c r="D4" s="321"/>
-      <c r="E4" s="321"/>
-      <c r="F4" s="321"/>
-      <c r="G4" s="321"/>
-      <c r="H4" s="321"/>
+      <c r="B4" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="359"/>
+      <c r="D4" s="359"/>
+      <c r="E4" s="359"/>
+      <c r="F4" s="359"/>
+      <c r="G4" s="359"/>
+      <c r="H4" s="359"/>
       <c r="L4" s="51"/>
       <c r="M4" s="53"/>
     </row>
@@ -14431,40 +14431,40 @@
       <c r="A19" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="374" t="s">
+      <c r="B19" s="382" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="327" t="s">
+      <c r="C19" s="365" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="328"/>
-      <c r="E19" s="328"/>
-      <c r="F19" s="328"/>
-      <c r="G19" s="329"/>
+      <c r="D19" s="366"/>
+      <c r="E19" s="366"/>
+      <c r="F19" s="366"/>
+      <c r="G19" s="367"/>
       <c r="H19" s="55"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1">
       <c r="A20" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="325"/>
-      <c r="C20" s="330"/>
-      <c r="D20" s="331"/>
-      <c r="E20" s="331"/>
-      <c r="F20" s="331"/>
-      <c r="G20" s="332"/>
+      <c r="B20" s="363"/>
+      <c r="C20" s="368"/>
+      <c r="D20" s="369"/>
+      <c r="E20" s="369"/>
+      <c r="F20" s="369"/>
+      <c r="G20" s="370"/>
       <c r="H20" s="55"/>
     </row>
     <row r="21" spans="1:13" ht="24" customHeight="1">
       <c r="A21" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="326"/>
-      <c r="C21" s="333"/>
-      <c r="D21" s="334"/>
-      <c r="E21" s="334"/>
-      <c r="F21" s="334"/>
-      <c r="G21" s="335"/>
+      <c r="B21" s="364"/>
+      <c r="C21" s="371"/>
+      <c r="D21" s="372"/>
+      <c r="E21" s="372"/>
+      <c r="F21" s="372"/>
+      <c r="G21" s="373"/>
       <c r="H21" s="57" t="s">
         <v>52</v>
       </c>
@@ -14480,17 +14480,17 @@
       <c r="B25" s="57">
         <v>1</v>
       </c>
-      <c r="C25" s="375">
+      <c r="C25" s="383">
         <v>2</v>
       </c>
-      <c r="D25" s="376"/>
+      <c r="D25" s="384"/>
       <c r="E25" s="57">
         <v>3</v>
       </c>
-      <c r="F25" s="375">
+      <c r="F25" s="383">
         <v>4</v>
       </c>
-      <c r="G25" s="376"/>
+      <c r="G25" s="384"/>
       <c r="H25" s="57">
         <v>8</v>
       </c>
@@ -14546,15 +14546,15 @@
       <c r="B29" s="58">
         <v>2</v>
       </c>
-      <c r="C29" s="377" t="s">
+      <c r="C29" s="374" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="378"/>
-      <c r="E29" s="336" t="s">
+      <c r="D29" s="375"/>
+      <c r="E29" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F29" s="337"/>
-      <c r="G29" s="338"/>
+      <c r="F29" s="324"/>
+      <c r="G29" s="325"/>
       <c r="H29" s="64"/>
       <c r="I29" s="49"/>
       <c r="M29" s="65"/>
@@ -14566,15 +14566,15 @@
       <c r="B30" s="58">
         <v>3</v>
       </c>
-      <c r="C30" s="379"/>
-      <c r="D30" s="380"/>
+      <c r="C30" s="376"/>
+      <c r="D30" s="377"/>
       <c r="E30" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="355" t="s">
+      <c r="F30" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="G30" s="357"/>
+      <c r="G30" s="338"/>
       <c r="H30" s="72" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14589,15 +14589,15 @@
       <c r="B31" s="58">
         <v>4</v>
       </c>
-      <c r="C31" s="379"/>
-      <c r="D31" s="380"/>
+      <c r="C31" s="376"/>
+      <c r="D31" s="377"/>
       <c r="E31" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="355" t="s">
+      <c r="F31" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="G31" s="357"/>
+      <c r="G31" s="338"/>
       <c r="H31" s="64"/>
       <c r="I31" s="49"/>
       <c r="M31" s="53"/>
@@ -14609,15 +14609,15 @@
       <c r="B32" s="58">
         <v>5</v>
       </c>
-      <c r="C32" s="379"/>
-      <c r="D32" s="380"/>
+      <c r="C32" s="376"/>
+      <c r="D32" s="377"/>
       <c r="E32" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="355" t="s">
+      <c r="F32" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="G32" s="357"/>
+      <c r="G32" s="338"/>
       <c r="H32" s="64"/>
       <c r="I32" s="49"/>
     </row>
@@ -14637,10 +14637,10 @@
       <c r="E33" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F33" s="345" t="s">
+      <c r="F33" s="319" t="s">
         <v>170</v>
       </c>
-      <c r="G33" s="347"/>
+      <c r="G33" s="321"/>
       <c r="H33" s="64"/>
       <c r="I33" s="49"/>
       <c r="J33" s="49"/>
@@ -14661,10 +14661,10 @@
       <c r="E34" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G34" s="347"/>
+      <c r="F34" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="321"/>
       <c r="H34" s="64"/>
       <c r="I34" s="49"/>
       <c r="J34" s="49"/>
@@ -14677,15 +14677,15 @@
       <c r="B35" s="58">
         <v>8</v>
       </c>
-      <c r="C35" s="377" t="s">
+      <c r="C35" s="374" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="378"/>
-      <c r="E35" s="336" t="s">
+      <c r="D35" s="375"/>
+      <c r="E35" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F35" s="337"/>
-      <c r="G35" s="338"/>
+      <c r="F35" s="324"/>
+      <c r="G35" s="325"/>
       <c r="H35" s="64"/>
       <c r="I35" s="49"/>
     </row>
@@ -14696,15 +14696,15 @@
       <c r="B36" s="58">
         <v>9</v>
       </c>
-      <c r="C36" s="379"/>
-      <c r="D36" s="380"/>
-      <c r="E36" s="372" t="s">
+      <c r="C36" s="376"/>
+      <c r="D36" s="377"/>
+      <c r="E36" s="330" t="s">
         <v>55</v>
       </c>
-      <c r="F36" s="355" t="s">
+      <c r="F36" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="G36" s="357"/>
+      <c r="G36" s="338"/>
       <c r="H36" s="72" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -14719,13 +14719,13 @@
       <c r="B37" s="58">
         <v>10</v>
       </c>
-      <c r="C37" s="381"/>
-      <c r="D37" s="382"/>
-      <c r="E37" s="373"/>
-      <c r="F37" s="355" t="s">
+      <c r="C37" s="380"/>
+      <c r="D37" s="381"/>
+      <c r="E37" s="331"/>
+      <c r="F37" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="G37" s="357"/>
+      <c r="G37" s="338"/>
       <c r="H37" s="64"/>
       <c r="I37" s="49"/>
     </row>
@@ -14736,15 +14736,15 @@
       <c r="B38" s="58">
         <v>11</v>
       </c>
-      <c r="C38" s="377" t="s">
+      <c r="C38" s="374" t="s">
         <v>174</v>
       </c>
-      <c r="D38" s="378"/>
-      <c r="E38" s="336" t="s">
+      <c r="D38" s="375"/>
+      <c r="E38" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F38" s="337"/>
-      <c r="G38" s="338"/>
+      <c r="F38" s="324"/>
+      <c r="G38" s="325"/>
       <c r="H38" s="64"/>
       <c r="I38" s="49"/>
     </row>
@@ -14755,15 +14755,15 @@
       <c r="B39" s="58">
         <v>12</v>
       </c>
-      <c r="C39" s="379"/>
-      <c r="D39" s="380"/>
+      <c r="C39" s="376"/>
+      <c r="D39" s="377"/>
       <c r="E39" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="G39" s="384"/>
+      <c r="F39" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G39" s="379"/>
       <c r="H39" s="64"/>
       <c r="I39" s="49"/>
     </row>
@@ -14783,10 +14783,10 @@
       <c r="E40" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G40" s="347"/>
+      <c r="F40" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G40" s="321"/>
       <c r="H40" s="64"/>
       <c r="I40" s="49"/>
       <c r="J40" s="49"/>
@@ -14798,15 +14798,15 @@
       <c r="B41" s="58">
         <v>14</v>
       </c>
-      <c r="C41" s="377" t="s">
+      <c r="C41" s="374" t="s">
         <v>175</v>
       </c>
-      <c r="D41" s="378"/>
-      <c r="E41" s="336" t="s">
+      <c r="D41" s="375"/>
+      <c r="E41" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F41" s="337"/>
-      <c r="G41" s="338"/>
+      <c r="F41" s="324"/>
+      <c r="G41" s="325"/>
       <c r="H41" s="64"/>
       <c r="I41" s="49"/>
     </row>
@@ -14817,15 +14817,15 @@
       <c r="B42" s="58">
         <v>15</v>
       </c>
-      <c r="C42" s="379"/>
-      <c r="D42" s="380"/>
+      <c r="C42" s="376"/>
+      <c r="D42" s="377"/>
       <c r="E42" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="355" t="s">
+      <c r="F42" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="G42" s="357"/>
+      <c r="G42" s="338"/>
       <c r="H42" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14848,10 +14848,10 @@
       <c r="E43" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F43" s="345" t="s">
+      <c r="F43" s="319" t="s">
         <v>176</v>
       </c>
-      <c r="G43" s="347"/>
+      <c r="G43" s="321"/>
       <c r="H43" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14875,10 +14875,10 @@
       <c r="E44" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F44" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G44" s="347"/>
+      <c r="F44" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" s="321"/>
       <c r="H44" s="64"/>
       <c r="I44" s="49"/>
       <c r="J44" s="49"/>
@@ -14890,15 +14890,15 @@
       <c r="B45" s="58">
         <v>18</v>
       </c>
-      <c r="C45" s="377" t="s">
+      <c r="C45" s="374" t="s">
         <v>177</v>
       </c>
-      <c r="D45" s="378"/>
-      <c r="E45" s="336" t="s">
+      <c r="D45" s="375"/>
+      <c r="E45" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="337"/>
-      <c r="G45" s="338"/>
+      <c r="F45" s="324"/>
+      <c r="G45" s="325"/>
       <c r="H45" s="64"/>
       <c r="I45" s="49"/>
     </row>
@@ -14909,15 +14909,15 @@
       <c r="B46" s="58">
         <v>19</v>
       </c>
-      <c r="C46" s="379"/>
-      <c r="D46" s="380"/>
+      <c r="C46" s="376"/>
+      <c r="D46" s="377"/>
       <c r="E46" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="G46" s="384"/>
+      <c r="F46" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" s="379"/>
       <c r="H46" s="64"/>
       <c r="I46" s="49"/>
     </row>
@@ -14937,8 +14937,8 @@
       <c r="E47" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F47" s="345"/>
-      <c r="G47" s="347"/>
+      <c r="F47" s="319"/>
+      <c r="G47" s="321"/>
       <c r="H47" s="64"/>
       <c r="I47" s="49"/>
       <c r="J47" s="49"/>
@@ -14959,10 +14959,10 @@
       <c r="E48" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F48" s="345" t="s">
+      <c r="F48" s="319" t="s">
         <v>178</v>
       </c>
-      <c r="G48" s="347"/>
+      <c r="G48" s="321"/>
       <c r="H48" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14986,10 +14986,10 @@
       <c r="E49" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F49" s="345" t="s">
+      <c r="F49" s="319" t="s">
         <v>8</v>
       </c>
-      <c r="G49" s="347"/>
+      <c r="G49" s="321"/>
       <c r="H49" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15004,13 +15004,13 @@
       <c r="B50" s="58">
         <v>24</v>
       </c>
-      <c r="C50" s="336" t="s">
+      <c r="C50" s="323" t="s">
         <v>179</v>
       </c>
-      <c r="D50" s="337"/>
-      <c r="E50" s="337"/>
-      <c r="F50" s="337"/>
-      <c r="G50" s="338"/>
+      <c r="D50" s="324"/>
+      <c r="E50" s="324"/>
+      <c r="F50" s="324"/>
+      <c r="G50" s="325"/>
       <c r="H50" s="64"/>
       <c r="I50" s="49"/>
     </row>
@@ -15021,13 +15021,13 @@
       <c r="B51" s="58">
         <v>25</v>
       </c>
-      <c r="C51" s="336" t="s">
+      <c r="C51" s="323" t="s">
         <v>180</v>
       </c>
-      <c r="D51" s="337"/>
-      <c r="E51" s="337"/>
-      <c r="F51" s="337"/>
-      <c r="G51" s="338"/>
+      <c r="D51" s="324"/>
+      <c r="E51" s="324"/>
+      <c r="F51" s="324"/>
+      <c r="G51" s="325"/>
       <c r="H51" s="64" t="e">
         <f>нак.расх.!G29-зат.осн.про.!H75-зат.осн.про.!H99</f>
         <v>#REF!</v>
@@ -15073,15 +15073,15 @@
       <c r="B53" s="58">
         <v>2</v>
       </c>
-      <c r="C53" s="377" t="s">
+      <c r="C53" s="374" t="s">
         <v>54</v>
       </c>
-      <c r="D53" s="378"/>
-      <c r="E53" s="336" t="s">
+      <c r="D53" s="375"/>
+      <c r="E53" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F53" s="337"/>
-      <c r="G53" s="338"/>
+      <c r="F53" s="324"/>
+      <c r="G53" s="325"/>
       <c r="H53" s="64"/>
       <c r="I53" s="49"/>
       <c r="M53" s="53" t="e">
@@ -15096,15 +15096,15 @@
       <c r="B54" s="58">
         <v>3</v>
       </c>
-      <c r="C54" s="379"/>
-      <c r="D54" s="380"/>
+      <c r="C54" s="376"/>
+      <c r="D54" s="377"/>
       <c r="E54" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F54" s="355" t="s">
+      <c r="F54" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="G54" s="357"/>
+      <c r="G54" s="338"/>
       <c r="H54" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15118,15 +15118,15 @@
       <c r="B55" s="58">
         <v>4</v>
       </c>
-      <c r="C55" s="379"/>
-      <c r="D55" s="380"/>
+      <c r="C55" s="376"/>
+      <c r="D55" s="377"/>
       <c r="E55" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F55" s="355" t="s">
+      <c r="F55" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="G55" s="357"/>
+      <c r="G55" s="338"/>
       <c r="H55" s="64"/>
       <c r="I55" s="49"/>
     </row>
@@ -15137,15 +15137,15 @@
       <c r="B56" s="58">
         <v>5</v>
       </c>
-      <c r="C56" s="379"/>
-      <c r="D56" s="380"/>
+      <c r="C56" s="376"/>
+      <c r="D56" s="377"/>
       <c r="E56" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="355" t="s">
+      <c r="F56" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="G56" s="357"/>
+      <c r="G56" s="338"/>
       <c r="H56" s="64"/>
       <c r="I56" s="49"/>
     </row>
@@ -15165,10 +15165,10 @@
       <c r="E57" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="345" t="s">
+      <c r="F57" s="319" t="s">
         <v>170</v>
       </c>
-      <c r="G57" s="347"/>
+      <c r="G57" s="321"/>
       <c r="H57" s="64"/>
       <c r="I57" s="49"/>
       <c r="J57" s="49"/>
@@ -15189,10 +15189,10 @@
       <c r="E58" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F58" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G58" s="347"/>
+      <c r="F58" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G58" s="321"/>
       <c r="H58" s="64"/>
       <c r="I58" s="49"/>
     </row>
@@ -15203,15 +15203,15 @@
       <c r="B59" s="58">
         <v>8</v>
       </c>
-      <c r="C59" s="377" t="s">
+      <c r="C59" s="374" t="s">
         <v>171</v>
       </c>
-      <c r="D59" s="378"/>
-      <c r="E59" s="336" t="s">
+      <c r="D59" s="375"/>
+      <c r="E59" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F59" s="337"/>
-      <c r="G59" s="338"/>
+      <c r="F59" s="324"/>
+      <c r="G59" s="325"/>
       <c r="H59" s="64"/>
       <c r="I59" s="49"/>
     </row>
@@ -15222,15 +15222,15 @@
       <c r="B60" s="58">
         <v>9</v>
       </c>
-      <c r="C60" s="379"/>
-      <c r="D60" s="380"/>
-      <c r="E60" s="372" t="s">
+      <c r="C60" s="376"/>
+      <c r="D60" s="377"/>
+      <c r="E60" s="330" t="s">
         <v>55</v>
       </c>
-      <c r="F60" s="355" t="s">
+      <c r="F60" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="G60" s="357"/>
+      <c r="G60" s="338"/>
       <c r="H60" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15244,13 +15244,13 @@
       <c r="B61" s="58">
         <v>10</v>
       </c>
-      <c r="C61" s="381"/>
-      <c r="D61" s="382"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="355" t="s">
+      <c r="C61" s="380"/>
+      <c r="D61" s="381"/>
+      <c r="E61" s="331"/>
+      <c r="F61" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="G61" s="357"/>
+      <c r="G61" s="338"/>
       <c r="H61" s="64"/>
       <c r="I61" s="49"/>
     </row>
@@ -15261,15 +15261,15 @@
       <c r="B62" s="58">
         <v>11</v>
       </c>
-      <c r="C62" s="377" t="s">
+      <c r="C62" s="374" t="s">
         <v>174</v>
       </c>
-      <c r="D62" s="378"/>
-      <c r="E62" s="336" t="s">
+      <c r="D62" s="375"/>
+      <c r="E62" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F62" s="337"/>
-      <c r="G62" s="338"/>
+      <c r="F62" s="324"/>
+      <c r="G62" s="325"/>
       <c r="H62" s="64"/>
       <c r="I62" s="49"/>
     </row>
@@ -15280,15 +15280,15 @@
       <c r="B63" s="58">
         <v>12</v>
       </c>
-      <c r="C63" s="379"/>
-      <c r="D63" s="380"/>
+      <c r="C63" s="376"/>
+      <c r="D63" s="377"/>
       <c r="E63" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F63" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="G63" s="384"/>
+      <c r="F63" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G63" s="379"/>
       <c r="H63" s="64"/>
       <c r="I63" s="49"/>
       <c r="J63" s="49"/>
@@ -15309,10 +15309,10 @@
       <c r="E64" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F64" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G64" s="347"/>
+      <c r="F64" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G64" s="321"/>
       <c r="H64" s="64"/>
       <c r="I64" s="49"/>
     </row>
@@ -15323,15 +15323,15 @@
       <c r="B65" s="58">
         <v>14</v>
       </c>
-      <c r="C65" s="377" t="s">
+      <c r="C65" s="374" t="s">
         <v>175</v>
       </c>
-      <c r="D65" s="378"/>
-      <c r="E65" s="336" t="s">
+      <c r="D65" s="375"/>
+      <c r="E65" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="337"/>
-      <c r="G65" s="338"/>
+      <c r="F65" s="324"/>
+      <c r="G65" s="325"/>
       <c r="H65" s="64"/>
       <c r="I65" s="49"/>
     </row>
@@ -15342,15 +15342,15 @@
       <c r="B66" s="58">
         <v>15</v>
       </c>
-      <c r="C66" s="379"/>
-      <c r="D66" s="380"/>
+      <c r="C66" s="376"/>
+      <c r="D66" s="377"/>
       <c r="E66" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F66" s="355" t="s">
+      <c r="F66" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="G66" s="357"/>
+      <c r="G66" s="338"/>
       <c r="H66" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15374,10 +15374,10 @@
       <c r="E67" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="345" t="s">
+      <c r="F67" s="319" t="s">
         <v>176</v>
       </c>
-      <c r="G67" s="347"/>
+      <c r="G67" s="321"/>
       <c r="H67" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15400,10 +15400,10 @@
       <c r="E68" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F68" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G68" s="347"/>
+      <c r="F68" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G68" s="321"/>
       <c r="H68" s="64"/>
       <c r="I68" s="49"/>
     </row>
@@ -15414,15 +15414,15 @@
       <c r="B69" s="58">
         <v>18</v>
       </c>
-      <c r="C69" s="377" t="s">
+      <c r="C69" s="374" t="s">
         <v>177</v>
       </c>
-      <c r="D69" s="378"/>
-      <c r="E69" s="336" t="s">
+      <c r="D69" s="375"/>
+      <c r="E69" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="337"/>
-      <c r="G69" s="338"/>
+      <c r="F69" s="324"/>
+      <c r="G69" s="325"/>
       <c r="H69" s="64"/>
       <c r="I69" s="49"/>
       <c r="J69" s="49"/>
@@ -15434,15 +15434,15 @@
       <c r="B70" s="58">
         <v>19</v>
       </c>
-      <c r="C70" s="379"/>
-      <c r="D70" s="380"/>
+      <c r="C70" s="376"/>
+      <c r="D70" s="377"/>
       <c r="E70" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F70" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="G70" s="384"/>
+      <c r="F70" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G70" s="379"/>
       <c r="H70" s="64"/>
       <c r="I70" s="49"/>
     </row>
@@ -15462,8 +15462,8 @@
       <c r="E71" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F71" s="345"/>
-      <c r="G71" s="347"/>
+      <c r="F71" s="319"/>
+      <c r="G71" s="321"/>
       <c r="H71" s="64"/>
       <c r="I71" s="49"/>
     </row>
@@ -15480,10 +15480,10 @@
       <c r="E72" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F72" s="345" t="s">
+      <c r="F72" s="319" t="s">
         <v>178</v>
       </c>
-      <c r="G72" s="347"/>
+      <c r="G72" s="321"/>
       <c r="H72" s="64"/>
       <c r="I72" s="49"/>
       <c r="J72" s="49"/>
@@ -15506,10 +15506,10 @@
       <c r="E73" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F73" s="345" t="s">
+      <c r="F73" s="319" t="s">
         <v>8</v>
       </c>
-      <c r="G73" s="347"/>
+      <c r="G73" s="321"/>
       <c r="H73" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15523,13 +15523,13 @@
       <c r="B74" s="58">
         <v>24</v>
       </c>
-      <c r="C74" s="336" t="s">
+      <c r="C74" s="323" t="s">
         <v>179</v>
       </c>
-      <c r="D74" s="337"/>
-      <c r="E74" s="337"/>
-      <c r="F74" s="337"/>
-      <c r="G74" s="338"/>
+      <c r="D74" s="324"/>
+      <c r="E74" s="324"/>
+      <c r="F74" s="324"/>
+      <c r="G74" s="325"/>
       <c r="H74" s="64"/>
       <c r="I74" s="49"/>
       <c r="J74" s="49"/>
@@ -15540,13 +15540,13 @@
       <c r="B75" s="58">
         <v>25</v>
       </c>
-      <c r="C75" s="336" t="s">
+      <c r="C75" s="323" t="s">
         <v>180</v>
       </c>
-      <c r="D75" s="337"/>
-      <c r="E75" s="337"/>
-      <c r="F75" s="337"/>
-      <c r="G75" s="338"/>
+      <c r="D75" s="324"/>
+      <c r="E75" s="324"/>
+      <c r="F75" s="324"/>
+      <c r="G75" s="325"/>
       <c r="H75" s="64" t="e">
         <f>нак.расх.!G29*4%</f>
         <v>#REF!</v>
@@ -15592,15 +15592,15 @@
       <c r="B77" s="58">
         <v>2</v>
       </c>
-      <c r="C77" s="377" t="s">
+      <c r="C77" s="374" t="s">
         <v>54</v>
       </c>
-      <c r="D77" s="378"/>
-      <c r="E77" s="336" t="s">
+      <c r="D77" s="375"/>
+      <c r="E77" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F77" s="337"/>
-      <c r="G77" s="338"/>
+      <c r="F77" s="324"/>
+      <c r="G77" s="325"/>
       <c r="H77" s="64"/>
       <c r="M77" s="53" t="e">
         <f>H76-M76</f>
@@ -15611,15 +15611,15 @@
       <c r="B78" s="58">
         <v>3</v>
       </c>
-      <c r="C78" s="379"/>
-      <c r="D78" s="380"/>
+      <c r="C78" s="376"/>
+      <c r="D78" s="377"/>
       <c r="E78" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F78" s="355" t="s">
+      <c r="F78" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="G78" s="357"/>
+      <c r="G78" s="338"/>
       <c r="H78" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15629,30 +15629,30 @@
       <c r="B79" s="58">
         <v>4</v>
       </c>
-      <c r="C79" s="379"/>
-      <c r="D79" s="380"/>
+      <c r="C79" s="376"/>
+      <c r="D79" s="377"/>
       <c r="E79" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F79" s="355" t="s">
+      <c r="F79" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="G79" s="357"/>
+      <c r="G79" s="338"/>
       <c r="H79" s="64"/>
     </row>
     <row r="80" spans="1:13" ht="15.75" customHeight="1">
       <c r="B80" s="58">
         <v>5</v>
       </c>
-      <c r="C80" s="379"/>
-      <c r="D80" s="380"/>
+      <c r="C80" s="376"/>
+      <c r="D80" s="377"/>
       <c r="E80" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F80" s="355" t="s">
+      <c r="F80" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="G80" s="357"/>
+      <c r="G80" s="338"/>
       <c r="H80" s="64"/>
     </row>
     <row r="81" spans="2:8" ht="15.75" customHeight="1">
@@ -15668,10 +15668,10 @@
       <c r="E81" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="345" t="s">
+      <c r="F81" s="319" t="s">
         <v>170</v>
       </c>
-      <c r="G81" s="347"/>
+      <c r="G81" s="321"/>
       <c r="H81" s="64"/>
     </row>
     <row r="82" spans="2:8" ht="15.75" customHeight="1">
@@ -15687,40 +15687,40 @@
       <c r="E82" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G82" s="347"/>
+      <c r="F82" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G82" s="321"/>
       <c r="H82" s="64"/>
     </row>
     <row r="83" spans="2:8" ht="15.75" customHeight="1">
       <c r="B83" s="58">
         <v>8</v>
       </c>
-      <c r="C83" s="377" t="s">
+      <c r="C83" s="374" t="s">
         <v>171</v>
       </c>
-      <c r="D83" s="378"/>
-      <c r="E83" s="336" t="s">
+      <c r="D83" s="375"/>
+      <c r="E83" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F83" s="337"/>
-      <c r="G83" s="338"/>
+      <c r="F83" s="324"/>
+      <c r="G83" s="325"/>
       <c r="H83" s="64"/>
     </row>
     <row r="84" spans="2:8" ht="15.75" customHeight="1">
       <c r="B84" s="58">
         <v>9</v>
       </c>
-      <c r="C84" s="379"/>
-      <c r="D84" s="380"/>
-      <c r="E84" s="372" t="s">
+      <c r="C84" s="376"/>
+      <c r="D84" s="377"/>
+      <c r="E84" s="330" t="s">
         <v>55</v>
       </c>
-      <c r="F84" s="355" t="s">
+      <c r="F84" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="G84" s="357"/>
+      <c r="G84" s="338"/>
       <c r="H84" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15730,43 +15730,43 @@
       <c r="B85" s="58">
         <v>10</v>
       </c>
-      <c r="C85" s="381"/>
-      <c r="D85" s="382"/>
-      <c r="E85" s="373"/>
-      <c r="F85" s="355" t="s">
+      <c r="C85" s="380"/>
+      <c r="D85" s="381"/>
+      <c r="E85" s="331"/>
+      <c r="F85" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="G85" s="357"/>
+      <c r="G85" s="338"/>
       <c r="H85" s="64"/>
     </row>
     <row r="86" spans="2:8" ht="15.75" customHeight="1">
       <c r="B86" s="58">
         <v>11</v>
       </c>
-      <c r="C86" s="377" t="s">
+      <c r="C86" s="374" t="s">
         <v>174</v>
       </c>
-      <c r="D86" s="378"/>
-      <c r="E86" s="336" t="s">
+      <c r="D86" s="375"/>
+      <c r="E86" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F86" s="337"/>
-      <c r="G86" s="338"/>
+      <c r="F86" s="324"/>
+      <c r="G86" s="325"/>
       <c r="H86" s="64"/>
     </row>
     <row r="87" spans="2:8" ht="15.75" customHeight="1">
       <c r="B87" s="58">
         <v>12</v>
       </c>
-      <c r="C87" s="379"/>
-      <c r="D87" s="380"/>
+      <c r="C87" s="376"/>
+      <c r="D87" s="377"/>
       <c r="E87" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F87" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="G87" s="384"/>
+      <c r="F87" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G87" s="379"/>
       <c r="H87" s="64"/>
     </row>
     <row r="88" spans="2:8" ht="15.75" customHeight="1">
@@ -15782,40 +15782,40 @@
       <c r="E88" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G88" s="347"/>
+      <c r="F88" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G88" s="321"/>
       <c r="H88" s="64"/>
     </row>
     <row r="89" spans="2:8" ht="15.75" customHeight="1">
       <c r="B89" s="58">
         <v>14</v>
       </c>
-      <c r="C89" s="377" t="s">
+      <c r="C89" s="374" t="s">
         <v>175</v>
       </c>
-      <c r="D89" s="378"/>
-      <c r="E89" s="336" t="s">
+      <c r="D89" s="375"/>
+      <c r="E89" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F89" s="337"/>
-      <c r="G89" s="338"/>
+      <c r="F89" s="324"/>
+      <c r="G89" s="325"/>
       <c r="H89" s="64"/>
     </row>
     <row r="90" spans="2:8" ht="15.75" customHeight="1">
       <c r="B90" s="58">
         <v>15</v>
       </c>
-      <c r="C90" s="379"/>
-      <c r="D90" s="380"/>
+      <c r="C90" s="376"/>
+      <c r="D90" s="377"/>
       <c r="E90" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F90" s="355" t="s">
+      <c r="F90" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="G90" s="357"/>
+      <c r="G90" s="338"/>
       <c r="H90" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15834,10 +15834,10 @@
       <c r="E91" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F91" s="345" t="s">
+      <c r="F91" s="319" t="s">
         <v>176</v>
       </c>
-      <c r="G91" s="347"/>
+      <c r="G91" s="321"/>
       <c r="H91" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15856,40 +15856,40 @@
       <c r="E92" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F92" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G92" s="347"/>
+      <c r="F92" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G92" s="321"/>
       <c r="H92" s="64"/>
     </row>
     <row r="93" spans="2:8" ht="15.75" customHeight="1">
       <c r="B93" s="58">
         <v>18</v>
       </c>
-      <c r="C93" s="377" t="s">
+      <c r="C93" s="374" t="s">
         <v>177</v>
       </c>
-      <c r="D93" s="378"/>
-      <c r="E93" s="336" t="s">
+      <c r="D93" s="375"/>
+      <c r="E93" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F93" s="337"/>
-      <c r="G93" s="338"/>
+      <c r="F93" s="324"/>
+      <c r="G93" s="325"/>
       <c r="H93" s="64"/>
     </row>
     <row r="94" spans="2:8" ht="15.75" customHeight="1">
       <c r="B94" s="58">
         <v>19</v>
       </c>
-      <c r="C94" s="379"/>
-      <c r="D94" s="380"/>
+      <c r="C94" s="376"/>
+      <c r="D94" s="377"/>
       <c r="E94" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F94" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="G94" s="384"/>
+      <c r="F94" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G94" s="379"/>
       <c r="H94" s="64"/>
     </row>
     <row r="95" spans="2:8" ht="15.75" customHeight="1">
@@ -15905,8 +15905,8 @@
       <c r="E95" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F95" s="345"/>
-      <c r="G95" s="347"/>
+      <c r="F95" s="319"/>
+      <c r="G95" s="321"/>
       <c r="H95" s="64"/>
     </row>
     <row r="96" spans="2:8" ht="32.25" customHeight="1">
@@ -15922,10 +15922,10 @@
       <c r="E96" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F96" s="345" t="s">
+      <c r="F96" s="319" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="347"/>
+      <c r="G96" s="321"/>
       <c r="H96" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15944,34 +15944,34 @@
       <c r="E97" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F97" s="345"/>
-      <c r="G97" s="347"/>
+      <c r="F97" s="319"/>
+      <c r="G97" s="321"/>
       <c r="H97" s="64"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1">
       <c r="B98" s="58">
         <v>24</v>
       </c>
-      <c r="C98" s="336" t="s">
+      <c r="C98" s="323" t="s">
         <v>179</v>
       </c>
-      <c r="D98" s="337"/>
-      <c r="E98" s="337"/>
-      <c r="F98" s="337"/>
-      <c r="G98" s="338"/>
+      <c r="D98" s="324"/>
+      <c r="E98" s="324"/>
+      <c r="F98" s="324"/>
+      <c r="G98" s="325"/>
       <c r="H98" s="64"/>
     </row>
     <row r="99" spans="2:8" ht="15.75" customHeight="1">
       <c r="B99" s="58">
         <v>25</v>
       </c>
-      <c r="C99" s="336" t="s">
+      <c r="C99" s="323" t="s">
         <v>180</v>
       </c>
-      <c r="D99" s="337"/>
-      <c r="E99" s="337"/>
-      <c r="F99" s="337"/>
-      <c r="G99" s="338"/>
+      <c r="D99" s="324"/>
+      <c r="E99" s="324"/>
+      <c r="F99" s="324"/>
+      <c r="G99" s="325"/>
       <c r="H99" s="64" t="e">
         <f>нак.расх.!G29*16%</f>
         <v>#REF!</v>
@@ -15979,39 +15979,54 @@
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="C93:D94"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="C86:D87"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="C89:D90"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="C83:D85"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C77:D80"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:G21"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C29:D32"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="C35:D37"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="C45:D46"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C53:D56"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="C59:D61"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F61:G61"/>
     <mergeCell ref="F71:G71"/>
     <mergeCell ref="C62:D63"/>
     <mergeCell ref="E62:G62"/>
@@ -16025,54 +16040,39 @@
     <mergeCell ref="C69:D70"/>
     <mergeCell ref="E69:G69"/>
     <mergeCell ref="F70:G70"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="C59:D61"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C53:D56"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="C41:D42"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="C45:D46"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="C35:D37"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C29:D32"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C77:D80"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="C83:D85"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="C86:D87"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="C89:D90"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="C93:D94"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="F95:G95"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="76" orientation="portrait" r:id="rId1"/>
@@ -16101,14 +16101,14 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="319" t="s">
+      <c r="B1" s="357" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="319"/>
-      <c r="D1" s="319"/>
-      <c r="E1" s="319"/>
-      <c r="F1" s="319"/>
-      <c r="G1" s="319"/>
+      <c r="C1" s="357"/>
+      <c r="D1" s="357"/>
+      <c r="E1" s="357"/>
+      <c r="F1" s="357"/>
+      <c r="G1" s="357"/>
       <c r="K1" s="51"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1">
@@ -16139,69 +16139,69 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="319" t="s">
+      <c r="B3" s="357" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="319"/>
-      <c r="D3" s="319"/>
-      <c r="E3" s="319"/>
-      <c r="F3" s="319"/>
-      <c r="G3" s="319"/>
+      <c r="C3" s="357"/>
+      <c r="D3" s="357"/>
+      <c r="E3" s="357"/>
+      <c r="F3" s="357"/>
+      <c r="G3" s="357"/>
       <c r="K3" s="51"/>
     </row>
     <row r="4" spans="1:11" ht="14.25" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="321" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="321"/>
-      <c r="D4" s="321"/>
-      <c r="E4" s="321"/>
-      <c r="F4" s="321"/>
-      <c r="G4" s="321"/>
+      <c r="B4" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="359"/>
+      <c r="D4" s="359"/>
+      <c r="E4" s="359"/>
+      <c r="F4" s="359"/>
+      <c r="G4" s="359"/>
       <c r="K4" s="51"/>
     </row>
     <row r="5" spans="1:11" ht="24.75" customHeight="1">
       <c r="A5" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="322" t="s">
+      <c r="B5" s="360" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="322"/>
-      <c r="D5" s="322"/>
-      <c r="E5" s="322"/>
-      <c r="F5" s="322"/>
-      <c r="G5" s="322"/>
+      <c r="C5" s="360"/>
+      <c r="D5" s="360"/>
+      <c r="E5" s="360"/>
+      <c r="F5" s="360"/>
+      <c r="G5" s="360"/>
       <c r="K5" s="51"/>
     </row>
     <row r="6" spans="1:11" ht="12" customHeight="1">
       <c r="A6" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="322" t="s">
+      <c r="B6" s="360" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="322"/>
-      <c r="D6" s="322"/>
-      <c r="E6" s="322"/>
-      <c r="F6" s="322"/>
-      <c r="G6" s="322"/>
+      <c r="C6" s="360"/>
+      <c r="D6" s="360"/>
+      <c r="E6" s="360"/>
+      <c r="F6" s="360"/>
+      <c r="G6" s="360"/>
       <c r="K6" s="51"/>
     </row>
     <row r="7" spans="1:11" ht="12" customHeight="1">
       <c r="A7" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="323" t="s">
+      <c r="B7" s="361" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="323"/>
-      <c r="D7" s="323"/>
-      <c r="E7" s="323"/>
-      <c r="F7" s="323"/>
+      <c r="C7" s="361"/>
+      <c r="D7" s="361"/>
+      <c r="E7" s="361"/>
+      <c r="F7" s="361"/>
       <c r="G7" s="71" t="s">
         <v>50</v>
       </c>
@@ -16225,37 +16225,37 @@
       <c r="A22" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="324" t="s">
+      <c r="B22" s="362" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="327" t="s">
+      <c r="C22" s="365" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="328"/>
-      <c r="E22" s="328"/>
-      <c r="F22" s="329"/>
+      <c r="D22" s="366"/>
+      <c r="E22" s="366"/>
+      <c r="F22" s="367"/>
       <c r="G22" s="55"/>
     </row>
     <row r="23" spans="1:12" ht="12" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="325"/>
-      <c r="C23" s="330"/>
-      <c r="D23" s="331"/>
-      <c r="E23" s="331"/>
-      <c r="F23" s="332"/>
+      <c r="B23" s="363"/>
+      <c r="C23" s="368"/>
+      <c r="D23" s="369"/>
+      <c r="E23" s="369"/>
+      <c r="F23" s="370"/>
       <c r="G23" s="55"/>
     </row>
     <row r="24" spans="1:12" ht="24" customHeight="1">
       <c r="A24" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="326"/>
-      <c r="C24" s="333"/>
-      <c r="D24" s="334"/>
-      <c r="E24" s="334"/>
-      <c r="F24" s="335"/>
+      <c r="B24" s="364"/>
+      <c r="C24" s="371"/>
+      <c r="D24" s="372"/>
+      <c r="E24" s="372"/>
+      <c r="F24" s="373"/>
       <c r="G24" s="57" t="s">
         <v>52</v>
       </c>
@@ -16276,10 +16276,10 @@
       <c r="D28" s="57">
         <v>3</v>
       </c>
-      <c r="E28" s="375">
+      <c r="E28" s="383">
         <v>4</v>
       </c>
-      <c r="F28" s="376"/>
+      <c r="F28" s="384"/>
       <c r="G28" s="57">
         <v>8</v>
       </c>
@@ -16291,12 +16291,12 @@
       <c r="B29" s="58">
         <v>1</v>
       </c>
-      <c r="C29" s="336" t="s">
+      <c r="C29" s="323" t="s">
         <v>184</v>
       </c>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="D29" s="324"/>
+      <c r="E29" s="324"/>
+      <c r="F29" s="324"/>
       <c r="G29" s="72" t="e">
         <f>SUM(G30:G77)</f>
         <v>#REF!</v>
@@ -16316,11 +16316,11 @@
       <c r="C30" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="336" t="s">
+      <c r="D30" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="337"/>
-      <c r="F30" s="337"/>
+      <c r="E30" s="324"/>
+      <c r="F30" s="324"/>
       <c r="G30" s="74"/>
       <c r="L30" s="53" t="e">
         <f>G29-L29</f>
@@ -16340,10 +16340,10 @@
       <c r="D31" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="355" t="s">
+      <c r="E31" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="356"/>
+      <c r="F31" s="337"/>
       <c r="G31" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16363,10 +16363,10 @@
       <c r="D32" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="355" t="s">
+      <c r="E32" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="356"/>
+      <c r="F32" s="337"/>
       <c r="G32" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16386,10 +16386,10 @@
       <c r="D33" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E33" s="355" t="s">
+      <c r="E33" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="356"/>
+      <c r="F33" s="337"/>
       <c r="G33" s="74"/>
     </row>
     <row r="34" spans="1:13" ht="12" customHeight="1">
@@ -16446,10 +16446,10 @@
       <c r="D36" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E36" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="346"/>
+      <c r="E36" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="320"/>
       <c r="G36" s="74"/>
       <c r="H36" s="49"/>
     </row>
@@ -16463,11 +16463,11 @@
       <c r="C37" s="73" t="s">
         <v>171</v>
       </c>
-      <c r="D37" s="336" t="s">
+      <c r="D37" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E37" s="337"/>
-      <c r="F37" s="337"/>
+      <c r="E37" s="324"/>
+      <c r="F37" s="324"/>
       <c r="G37" s="74"/>
     </row>
     <row r="38" spans="1:13" ht="12" customHeight="1">
@@ -16483,10 +16483,10 @@
       <c r="D38" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E38" s="355" t="s">
+      <c r="E38" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="F38" s="356"/>
+      <c r="F38" s="337"/>
       <c r="G38" s="74" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -16506,10 +16506,10 @@
       <c r="D39" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="355" t="s">
+      <c r="E39" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="F39" s="356"/>
+      <c r="F39" s="337"/>
       <c r="G39" s="74"/>
     </row>
     <row r="40" spans="1:13" ht="12" customHeight="1">
@@ -16519,14 +16519,14 @@
       <c r="B40" s="58">
         <v>26</v>
       </c>
-      <c r="C40" s="339" t="s">
+      <c r="C40" s="332" t="s">
         <v>174</v>
       </c>
-      <c r="D40" s="336" t="s">
+      <c r="D40" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E40" s="337"/>
-      <c r="F40" s="337"/>
+      <c r="E40" s="324"/>
+      <c r="F40" s="324"/>
       <c r="G40" s="74"/>
     </row>
     <row r="41" spans="1:13" ht="12" customHeight="1">
@@ -16536,14 +16536,14 @@
       <c r="B41" s="58">
         <v>27</v>
       </c>
-      <c r="C41" s="340"/>
+      <c r="C41" s="333"/>
       <c r="D41" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="F41" s="385"/>
+      <c r="E41" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="386"/>
       <c r="G41" s="74"/>
     </row>
     <row r="42" spans="1:13" ht="12" customHeight="1">
@@ -16559,10 +16559,10 @@
       <c r="D42" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E42" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="346"/>
+      <c r="E42" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" s="320"/>
       <c r="G42" s="74"/>
       <c r="H42" s="49"/>
     </row>
@@ -16573,14 +16573,14 @@
       <c r="B43" s="58">
         <v>29</v>
       </c>
-      <c r="C43" s="339" t="s">
+      <c r="C43" s="332" t="s">
         <v>186</v>
       </c>
-      <c r="D43" s="336" t="s">
+      <c r="D43" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="337"/>
-      <c r="F43" s="337"/>
+      <c r="E43" s="324"/>
+      <c r="F43" s="324"/>
       <c r="G43" s="74"/>
     </row>
     <row r="44" spans="1:13" ht="12" customHeight="1">
@@ -16590,14 +16590,14 @@
       <c r="B44" s="58">
         <v>30</v>
       </c>
-      <c r="C44" s="340"/>
+      <c r="C44" s="333"/>
       <c r="D44" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E44" s="345" t="s">
+      <c r="E44" s="319" t="s">
         <v>128</v>
       </c>
-      <c r="F44" s="346"/>
+      <c r="F44" s="320"/>
       <c r="G44" s="74"/>
     </row>
     <row r="45" spans="1:13" ht="18.75" customHeight="1">
@@ -16607,14 +16607,14 @@
       <c r="B45" s="58">
         <v>31</v>
       </c>
-      <c r="C45" s="341"/>
+      <c r="C45" s="349"/>
       <c r="D45" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E45" s="386" t="s">
+      <c r="E45" s="389" t="s">
         <v>129</v>
       </c>
-      <c r="F45" s="387"/>
+      <c r="F45" s="390"/>
       <c r="G45" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16629,12 +16629,12 @@
       <c r="B46" s="58">
         <v>32</v>
       </c>
-      <c r="C46" s="336" t="s">
+      <c r="C46" s="323" t="s">
         <v>20</v>
       </c>
-      <c r="D46" s="337"/>
-      <c r="E46" s="337"/>
-      <c r="F46" s="337"/>
+      <c r="D46" s="324"/>
+      <c r="E46" s="324"/>
+      <c r="F46" s="324"/>
       <c r="G46" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16651,11 +16651,11 @@
       <c r="C47" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="D47" s="336" t="s">
+      <c r="D47" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="E47" s="324"/>
+      <c r="F47" s="324"/>
       <c r="G47" s="74"/>
       <c r="L47" s="53"/>
     </row>
@@ -16672,10 +16672,10 @@
       <c r="D48" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E48" s="355" t="s">
+      <c r="E48" s="336" t="s">
         <v>63</v>
       </c>
-      <c r="F48" s="356"/>
+      <c r="F48" s="337"/>
       <c r="G48" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16694,10 +16694,10 @@
       <c r="D49" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E49" s="355" t="s">
+      <c r="E49" s="336" t="s">
         <v>64</v>
       </c>
-      <c r="F49" s="356"/>
+      <c r="F49" s="337"/>
       <c r="G49" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16710,14 +16710,14 @@
       <c r="B50" s="58">
         <v>36</v>
       </c>
-      <c r="C50" s="339" t="s">
+      <c r="C50" s="332" t="s">
         <v>187</v>
       </c>
-      <c r="D50" s="336" t="s">
+      <c r="D50" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E50" s="337"/>
-      <c r="F50" s="337"/>
+      <c r="E50" s="324"/>
+      <c r="F50" s="324"/>
       <c r="G50" s="74"/>
     </row>
     <row r="51" spans="1:8" ht="12" customHeight="1">
@@ -16727,14 +16727,14 @@
       <c r="B51" s="58">
         <v>37</v>
       </c>
-      <c r="C51" s="340"/>
+      <c r="C51" s="333"/>
       <c r="D51" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E51" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="385"/>
+      <c r="E51" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="386"/>
       <c r="G51" s="74"/>
     </row>
     <row r="52" spans="1:8" ht="24.75" customHeight="1">
@@ -16750,10 +16750,10 @@
       <c r="D52" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E52" s="345" t="s">
+      <c r="E52" s="319" t="s">
         <v>188</v>
       </c>
-      <c r="F52" s="346"/>
+      <c r="F52" s="320"/>
       <c r="G52" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16767,12 +16767,12 @@
       <c r="B53" s="58">
         <v>43</v>
       </c>
-      <c r="C53" s="336" t="s">
+      <c r="C53" s="323" t="s">
         <v>16</v>
       </c>
-      <c r="D53" s="337"/>
-      <c r="E53" s="337"/>
-      <c r="F53" s="337"/>
+      <c r="D53" s="324"/>
+      <c r="E53" s="324"/>
+      <c r="F53" s="324"/>
       <c r="G53" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16785,12 +16785,12 @@
       <c r="B54" s="58">
         <v>44</v>
       </c>
-      <c r="C54" s="336" t="s">
+      <c r="C54" s="323" t="s">
         <v>14</v>
       </c>
-      <c r="D54" s="337"/>
-      <c r="E54" s="337"/>
-      <c r="F54" s="337"/>
+      <c r="D54" s="324"/>
+      <c r="E54" s="324"/>
+      <c r="F54" s="324"/>
       <c r="G54" s="74"/>
     </row>
     <row r="55" spans="1:8" ht="12" customHeight="1">
@@ -16803,11 +16803,11 @@
       <c r="C55" s="73" t="s">
         <v>137</v>
       </c>
-      <c r="D55" s="336" t="s">
+      <c r="D55" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="337"/>
-      <c r="F55" s="337"/>
+      <c r="E55" s="324"/>
+      <c r="F55" s="324"/>
       <c r="G55" s="74"/>
     </row>
     <row r="56" spans="1:8" ht="12" customHeight="1">
@@ -16823,10 +16823,10 @@
       <c r="D56" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="F56" s="385"/>
+      <c r="E56" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" s="386"/>
       <c r="G56" s="74"/>
     </row>
     <row r="57" spans="1:8" ht="24.75" customHeight="1">
@@ -16842,10 +16842,10 @@
       <c r="D57" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="345" t="s">
+      <c r="E57" s="319" t="s">
         <v>4</v>
       </c>
-      <c r="F57" s="346"/>
+      <c r="F57" s="320"/>
       <c r="G57" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16865,10 +16865,10 @@
       <c r="D58" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F58" s="346"/>
+      <c r="E58" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F58" s="320"/>
       <c r="G58" s="74"/>
       <c r="H58" s="49"/>
     </row>
@@ -16879,12 +16879,12 @@
       <c r="B59" s="58">
         <v>51</v>
       </c>
-      <c r="C59" s="336" t="s">
+      <c r="C59" s="323" t="s">
         <v>189</v>
       </c>
-      <c r="D59" s="337"/>
-      <c r="E59" s="337"/>
-      <c r="F59" s="337"/>
+      <c r="D59" s="324"/>
+      <c r="E59" s="324"/>
+      <c r="F59" s="324"/>
       <c r="G59" s="74"/>
     </row>
     <row r="60" spans="1:8" ht="12" customHeight="1">
@@ -16894,12 +16894,12 @@
       <c r="B60" s="58">
         <v>52</v>
       </c>
-      <c r="C60" s="336" t="s">
+      <c r="C60" s="323" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="337"/>
-      <c r="E60" s="337"/>
-      <c r="F60" s="337"/>
+      <c r="D60" s="324"/>
+      <c r="E60" s="324"/>
+      <c r="F60" s="324"/>
       <c r="G60" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16912,12 +16912,12 @@
       <c r="B61" s="58">
         <v>53</v>
       </c>
-      <c r="C61" s="336" t="s">
+      <c r="C61" s="323" t="s">
         <v>190</v>
       </c>
-      <c r="D61" s="337"/>
-      <c r="E61" s="337"/>
-      <c r="F61" s="337"/>
+      <c r="D61" s="324"/>
+      <c r="E61" s="324"/>
+      <c r="F61" s="324"/>
       <c r="G61" s="74"/>
     </row>
     <row r="62" spans="1:8" ht="12" customHeight="1">
@@ -16927,12 +16927,12 @@
       <c r="B62" s="58">
         <v>54</v>
       </c>
-      <c r="C62" s="336" t="s">
+      <c r="C62" s="323" t="s">
         <v>191</v>
       </c>
-      <c r="D62" s="337"/>
-      <c r="E62" s="337"/>
-      <c r="F62" s="337"/>
+      <c r="D62" s="324"/>
+      <c r="E62" s="324"/>
+      <c r="F62" s="324"/>
       <c r="G62" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16945,12 +16945,12 @@
       <c r="B63" s="58">
         <v>55</v>
       </c>
-      <c r="C63" s="336" t="s">
+      <c r="C63" s="323" t="s">
         <v>192</v>
       </c>
-      <c r="D63" s="337"/>
-      <c r="E63" s="337"/>
-      <c r="F63" s="337"/>
+      <c r="D63" s="324"/>
+      <c r="E63" s="324"/>
+      <c r="F63" s="324"/>
       <c r="G63" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16963,14 +16963,14 @@
       <c r="B64" s="58">
         <v>56</v>
       </c>
-      <c r="C64" s="339" t="s">
+      <c r="C64" s="332" t="s">
         <v>175</v>
       </c>
-      <c r="D64" s="336" t="s">
+      <c r="D64" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E64" s="337"/>
-      <c r="F64" s="337"/>
+      <c r="E64" s="324"/>
+      <c r="F64" s="324"/>
       <c r="G64" s="74"/>
     </row>
     <row r="65" spans="1:11" ht="12" customHeight="1">
@@ -16980,14 +16980,14 @@
       <c r="B65" s="58">
         <v>57</v>
       </c>
-      <c r="C65" s="340"/>
+      <c r="C65" s="333"/>
       <c r="D65" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E65" s="355" t="s">
+      <c r="E65" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="F65" s="356"/>
+      <c r="F65" s="337"/>
       <c r="G65" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17006,10 +17006,10 @@
       <c r="D66" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E66" s="345" t="s">
+      <c r="E66" s="319" t="s">
         <v>193</v>
       </c>
-      <c r="F66" s="346"/>
+      <c r="F66" s="320"/>
       <c r="G66" s="74"/>
       <c r="H66" s="49"/>
     </row>
@@ -17020,14 +17020,14 @@
       <c r="B67" s="58">
         <v>59</v>
       </c>
-      <c r="C67" s="339" t="s">
+      <c r="C67" s="332" t="s">
         <v>102</v>
       </c>
-      <c r="D67" s="336" t="s">
+      <c r="D67" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E67" s="337"/>
-      <c r="F67" s="337"/>
+      <c r="E67" s="324"/>
+      <c r="F67" s="324"/>
       <c r="G67" s="74"/>
     </row>
     <row r="68" spans="1:11" ht="12" customHeight="1">
@@ -17037,14 +17037,14 @@
       <c r="B68" s="58">
         <v>60</v>
       </c>
-      <c r="C68" s="340"/>
+      <c r="C68" s="333"/>
       <c r="D68" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E68" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="F68" s="385"/>
+      <c r="E68" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="F68" s="386"/>
       <c r="G68" s="74"/>
     </row>
     <row r="69" spans="1:11" ht="12" customHeight="1">
@@ -17060,10 +17060,10 @@
       <c r="D69" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E69" s="345" t="s">
+      <c r="E69" s="319" t="s">
         <v>194</v>
       </c>
-      <c r="F69" s="346"/>
+      <c r="F69" s="320"/>
       <c r="G69" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17083,10 +17083,10 @@
       <c r="D70" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E70" s="345" t="s">
+      <c r="E70" s="319" t="s">
         <v>195</v>
       </c>
-      <c r="F70" s="346"/>
+      <c r="F70" s="320"/>
       <c r="G70" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17106,10 +17106,10 @@
       <c r="D71" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E71" s="388" t="s">
+      <c r="E71" s="387" t="s">
         <v>196</v>
       </c>
-      <c r="F71" s="389"/>
+      <c r="F71" s="388"/>
       <c r="G71" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17121,10 +17121,10 @@
       <c r="B72" s="58"/>
       <c r="C72" s="77"/>
       <c r="D72" s="70"/>
-      <c r="E72" s="388" t="s">
+      <c r="E72" s="387" t="s">
         <v>13</v>
       </c>
-      <c r="F72" s="389"/>
+      <c r="F72" s="388"/>
       <c r="G72" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17136,10 +17136,10 @@
       <c r="B73" s="58"/>
       <c r="C73" s="77"/>
       <c r="D73" s="70"/>
-      <c r="E73" s="388" t="s">
+      <c r="E73" s="387" t="s">
         <v>8</v>
       </c>
-      <c r="F73" s="389"/>
+      <c r="F73" s="388"/>
       <c r="G73" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17159,10 +17159,10 @@
       <c r="D74" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E74" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F74" s="346"/>
+      <c r="E74" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F74" s="320"/>
       <c r="G74" s="74"/>
       <c r="H74" s="49"/>
     </row>
@@ -17173,14 +17173,14 @@
       <c r="B75" s="58">
         <v>65</v>
       </c>
-      <c r="C75" s="339" t="s">
+      <c r="C75" s="332" t="s">
         <v>197</v>
       </c>
-      <c r="D75" s="336" t="s">
+      <c r="D75" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E75" s="337"/>
-      <c r="F75" s="337"/>
+      <c r="E75" s="324"/>
+      <c r="F75" s="324"/>
       <c r="G75" s="74"/>
     </row>
     <row r="76" spans="1:11" ht="12" customHeight="1">
@@ -17190,14 +17190,14 @@
       <c r="B76" s="58">
         <v>66</v>
       </c>
-      <c r="C76" s="340"/>
+      <c r="C76" s="333"/>
       <c r="D76" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E76" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="F76" s="385"/>
+      <c r="E76" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="F76" s="386"/>
       <c r="G76" s="74"/>
     </row>
     <row r="77" spans="1:11" ht="12" customHeight="1">
@@ -17213,10 +17213,10 @@
       <c r="D77" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E77" s="345" t="s">
+      <c r="E77" s="319" t="s">
         <v>198</v>
       </c>
-      <c r="F77" s="346"/>
+      <c r="F77" s="320"/>
       <c r="G77" s="81" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -17275,13 +17275,13 @@
       <c r="K79" s="51"/>
     </row>
     <row r="80" spans="1:11" ht="15" customHeight="1">
-      <c r="B80" s="390" t="s">
+      <c r="B80" s="385" t="s">
         <v>199</v>
       </c>
-      <c r="C80" s="390"/>
-      <c r="D80" s="390"/>
-      <c r="E80" s="390"/>
-      <c r="F80" s="390"/>
+      <c r="C80" s="385"/>
+      <c r="D80" s="385"/>
+      <c r="E80" s="385"/>
+      <c r="F80" s="385"/>
       <c r="G80" s="83"/>
       <c r="H80" s="83"/>
       <c r="I80" s="82"/>
@@ -17289,13 +17289,13 @@
       <c r="K80" s="51"/>
     </row>
     <row r="81" spans="2:11" ht="15" customHeight="1">
-      <c r="B81" s="390" t="s">
-        <v>44</v>
-      </c>
-      <c r="C81" s="390"/>
-      <c r="D81" s="390"/>
-      <c r="E81" s="390"/>
-      <c r="F81" s="390"/>
+      <c r="B81" s="385" t="s">
+        <v>44</v>
+      </c>
+      <c r="C81" s="385"/>
+      <c r="D81" s="385"/>
+      <c r="E81" s="385"/>
+      <c r="F81" s="385"/>
       <c r="G81" s="84"/>
       <c r="H81" s="84"/>
       <c r="I81" s="83"/>
@@ -17305,14 +17305,14 @@
     <row r="82" spans="2:11" ht="15.75" hidden="1" customHeight="1"/>
     <row r="83" spans="2:11" ht="15.75" hidden="1" customHeight="1"/>
     <row r="84" spans="2:11" ht="15" customHeight="1">
-      <c r="B84" s="390" t="s">
+      <c r="B84" s="385" t="s">
         <v>200</v>
       </c>
-      <c r="C84" s="390"/>
-      <c r="D84" s="390"/>
-      <c r="E84" s="390"/>
-      <c r="F84" s="390"/>
-      <c r="G84" s="390"/>
+      <c r="C84" s="385"/>
+      <c r="D84" s="385"/>
+      <c r="E84" s="385"/>
+      <c r="F84" s="385"/>
+      <c r="G84" s="385"/>
       <c r="H84" s="83"/>
       <c r="I84" s="83"/>
       <c r="J84" s="83"/>
@@ -17341,13 +17341,51 @@
     <row r="105" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B84:G84"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:F24"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C59:F59"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="C62:F62"/>
     <mergeCell ref="E74:F74"/>
     <mergeCell ref="C64:C65"/>
     <mergeCell ref="D64:F64"/>
@@ -17361,51 +17399,13 @@
     <mergeCell ref="E71:F71"/>
     <mergeCell ref="E72:F72"/>
     <mergeCell ref="E73:F73"/>
-    <mergeCell ref="C63:F63"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="C53:F53"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C59:F59"/>
-    <mergeCell ref="C60:F60"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="C62:F62"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:F24"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B84:G84"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Наименование на государственном языке заполняется автоматически в соответствии с КТРУ" sqref="B76 B49:B50 B95:B96"/>
@@ -17441,79 +17441,79 @@
       <c r="A1" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="430" t="s">
+      <c r="B1" s="399" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="430"/>
-      <c r="D1" s="430"/>
-      <c r="E1" s="430"/>
-      <c r="F1" s="430"/>
-      <c r="G1" s="430"/>
-      <c r="H1" s="430"/>
-      <c r="I1" s="430"/>
+      <c r="C1" s="399"/>
+      <c r="D1" s="399"/>
+      <c r="E1" s="399"/>
+      <c r="F1" s="399"/>
+      <c r="G1" s="399"/>
+      <c r="H1" s="399"/>
+      <c r="I1" s="399"/>
       <c r="M1" s="12"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1">
       <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="431" t="s">
+      <c r="B2" s="400" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="431"/>
-      <c r="D2" s="431"/>
-      <c r="E2" s="431"/>
-      <c r="F2" s="431"/>
-      <c r="G2" s="431"/>
-      <c r="H2" s="431"/>
-      <c r="I2" s="431"/>
+      <c r="C2" s="400"/>
+      <c r="D2" s="400"/>
+      <c r="E2" s="400"/>
+      <c r="F2" s="400"/>
+      <c r="G2" s="400"/>
+      <c r="H2" s="400"/>
+      <c r="I2" s="400"/>
       <c r="M2" s="12"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="432" t="s">
+      <c r="B3" s="401" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="432"/>
-      <c r="D3" s="432"/>
-      <c r="E3" s="432"/>
-      <c r="F3" s="432"/>
-      <c r="G3" s="432"/>
-      <c r="H3" s="432"/>
-      <c r="I3" s="432"/>
+      <c r="C3" s="401"/>
+      <c r="D3" s="401"/>
+      <c r="E3" s="401"/>
+      <c r="F3" s="401"/>
+      <c r="G3" s="401"/>
+      <c r="H3" s="401"/>
+      <c r="I3" s="401"/>
       <c r="M3" s="12"/>
     </row>
     <row r="4" spans="1:13" ht="30" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="432" t="s">
+      <c r="B4" s="401" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="432"/>
-      <c r="D4" s="432"/>
-      <c r="E4" s="432"/>
-      <c r="F4" s="432"/>
-      <c r="G4" s="432"/>
-      <c r="H4" s="432"/>
-      <c r="I4" s="432"/>
+      <c r="C4" s="401"/>
+      <c r="D4" s="401"/>
+      <c r="E4" s="401"/>
+      <c r="F4" s="401"/>
+      <c r="G4" s="401"/>
+      <c r="H4" s="401"/>
+      <c r="I4" s="401"/>
       <c r="M4" s="12"/>
     </row>
     <row r="5" spans="1:13" ht="12" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="433" t="s">
+      <c r="B5" s="402" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="433"/>
-      <c r="D5" s="433"/>
-      <c r="E5" s="433"/>
-      <c r="F5" s="433"/>
-      <c r="G5" s="433"/>
-      <c r="H5" s="433"/>
+      <c r="C5" s="402"/>
+      <c r="D5" s="402"/>
+      <c r="E5" s="402"/>
+      <c r="F5" s="402"/>
+      <c r="G5" s="402"/>
+      <c r="H5" s="402"/>
       <c r="I5" s="13" t="s">
         <v>50</v>
       </c>
@@ -17537,18 +17537,18 @@
       <c r="A20" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="434" t="s">
+      <c r="B20" s="403" t="s">
         <v>0</v>
       </c>
-      <c r="C20" s="437" t="s">
+      <c r="C20" s="406" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="438"/>
-      <c r="E20" s="438"/>
-      <c r="F20" s="438"/>
-      <c r="G20" s="438"/>
-      <c r="H20" s="439"/>
-      <c r="I20" s="446" t="s">
+      <c r="D20" s="407"/>
+      <c r="E20" s="407"/>
+      <c r="F20" s="407"/>
+      <c r="G20" s="407"/>
+      <c r="H20" s="408"/>
+      <c r="I20" s="415" t="s">
         <v>52</v>
       </c>
       <c r="J20" s="10"/>
@@ -17561,14 +17561,14 @@
       <c r="A21" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="435"/>
-      <c r="C21" s="440"/>
-      <c r="D21" s="441"/>
-      <c r="E21" s="441"/>
-      <c r="F21" s="441"/>
-      <c r="G21" s="441"/>
-      <c r="H21" s="442"/>
-      <c r="I21" s="435"/>
+      <c r="B21" s="404"/>
+      <c r="C21" s="409"/>
+      <c r="D21" s="410"/>
+      <c r="E21" s="410"/>
+      <c r="F21" s="410"/>
+      <c r="G21" s="410"/>
+      <c r="H21" s="411"/>
+      <c r="I21" s="404"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
@@ -17578,14 +17578,14 @@
       <c r="A22" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="436"/>
-      <c r="C22" s="443"/>
-      <c r="D22" s="444"/>
-      <c r="E22" s="444"/>
-      <c r="F22" s="444"/>
-      <c r="G22" s="444"/>
-      <c r="H22" s="445"/>
-      <c r="I22" s="436"/>
+      <c r="B22" s="405"/>
+      <c r="C22" s="412"/>
+      <c r="D22" s="413"/>
+      <c r="E22" s="413"/>
+      <c r="F22" s="413"/>
+      <c r="G22" s="413"/>
+      <c r="H22" s="414"/>
+      <c r="I22" s="405"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
@@ -17601,10 +17601,10 @@
       <c r="B26" s="18">
         <v>1</v>
       </c>
-      <c r="C26" s="428">
+      <c r="C26" s="391">
         <v>2</v>
       </c>
-      <c r="D26" s="429"/>
+      <c r="D26" s="392"/>
       <c r="E26" s="18">
         <v>3</v>
       </c>
@@ -17628,14 +17628,14 @@
       <c r="B27" s="19">
         <v>1</v>
       </c>
-      <c r="C27" s="394" t="s">
+      <c r="C27" s="393" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="395"/>
-      <c r="E27" s="395"/>
-      <c r="F27" s="395"/>
-      <c r="G27" s="395"/>
-      <c r="H27" s="396"/>
+      <c r="D27" s="394"/>
+      <c r="E27" s="394"/>
+      <c r="F27" s="394"/>
+      <c r="G27" s="394"/>
+      <c r="H27" s="395"/>
       <c r="I27" s="20"/>
       <c r="N27" s="16"/>
     </row>
@@ -17652,12 +17652,12 @@
       <c r="D28" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="394" t="s">
+      <c r="E28" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F28" s="395"/>
-      <c r="G28" s="395"/>
-      <c r="H28" s="396"/>
+      <c r="F28" s="394"/>
+      <c r="G28" s="394"/>
+      <c r="H28" s="395"/>
       <c r="I28" s="20" t="e">
         <f>SUM(I29:I190)</f>
         <v>#REF!</v>
@@ -17683,11 +17683,11 @@
       <c r="E29" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="401" t="s">
+      <c r="F29" s="396" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="402"/>
-      <c r="H29" s="403"/>
+      <c r="G29" s="397"/>
+      <c r="H29" s="398"/>
       <c r="I29" s="20" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17713,11 +17713,11 @@
       <c r="E30" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="401" t="s">
+      <c r="F30" s="396" t="s">
         <v>57</v>
       </c>
-      <c r="G30" s="402"/>
-      <c r="H30" s="403"/>
+      <c r="G30" s="397"/>
+      <c r="H30" s="398"/>
       <c r="I30" s="20" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17740,11 +17740,11 @@
       <c r="E31" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="401" t="s">
+      <c r="F31" s="396" t="s">
         <v>58</v>
       </c>
-      <c r="G31" s="402"/>
-      <c r="H31" s="403"/>
+      <c r="G31" s="397"/>
+      <c r="H31" s="398"/>
       <c r="I31" s="20"/>
     </row>
     <row r="32" spans="1:14" ht="12" customHeight="1">
@@ -17763,11 +17763,11 @@
       <c r="E32" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="391" t="s">
+      <c r="F32" s="416" t="s">
         <v>59</v>
       </c>
-      <c r="G32" s="392"/>
-      <c r="H32" s="393"/>
+      <c r="G32" s="417"/>
+      <c r="H32" s="418"/>
       <c r="I32" s="20" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -17793,16 +17793,16 @@
       <c r="B34" s="21">
         <v>7</v>
       </c>
-      <c r="C34" s="397" t="s">
+      <c r="C34" s="419" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="398"/>
-      <c r="E34" s="394" t="s">
+      <c r="D34" s="420"/>
+      <c r="E34" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="395"/>
-      <c r="G34" s="395"/>
-      <c r="H34" s="396"/>
+      <c r="F34" s="394"/>
+      <c r="G34" s="394"/>
+      <c r="H34" s="395"/>
       <c r="I34" s="32"/>
     </row>
     <row r="35" spans="1:15" ht="12" customHeight="1">
@@ -17812,16 +17812,16 @@
       <c r="B35" s="21">
         <v>8</v>
       </c>
-      <c r="C35" s="399"/>
-      <c r="D35" s="400"/>
+      <c r="C35" s="421"/>
+      <c r="D35" s="422"/>
       <c r="E35" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F35" s="401" t="s">
-        <v>44</v>
-      </c>
-      <c r="G35" s="402"/>
-      <c r="H35" s="403"/>
+      <c r="F35" s="396" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" s="397"/>
+      <c r="H35" s="398"/>
       <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:15" hidden="1">
@@ -17834,16 +17834,16 @@
       <c r="B37" s="21">
         <v>10</v>
       </c>
-      <c r="C37" s="407" t="s">
+      <c r="C37" s="423" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="408"/>
-      <c r="E37" s="394" t="s">
+      <c r="D37" s="424"/>
+      <c r="E37" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F37" s="395"/>
-      <c r="G37" s="395"/>
-      <c r="H37" s="396"/>
+      <c r="F37" s="394"/>
+      <c r="G37" s="394"/>
+      <c r="H37" s="395"/>
       <c r="I37" s="32"/>
     </row>
     <row r="38" spans="1:15" ht="12" customHeight="1">
@@ -17853,16 +17853,16 @@
       <c r="B38" s="21">
         <v>11</v>
       </c>
-      <c r="C38" s="409"/>
-      <c r="D38" s="410"/>
-      <c r="E38" s="413" t="s">
+      <c r="C38" s="425"/>
+      <c r="D38" s="426"/>
+      <c r="E38" s="429" t="s">
         <v>55</v>
       </c>
-      <c r="F38" s="401" t="s">
+      <c r="F38" s="396" t="s">
         <v>63</v>
       </c>
-      <c r="G38" s="402"/>
-      <c r="H38" s="403"/>
+      <c r="G38" s="397"/>
+      <c r="H38" s="398"/>
       <c r="I38" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17875,14 +17875,14 @@
       <c r="B39" s="21">
         <v>12</v>
       </c>
-      <c r="C39" s="411"/>
-      <c r="D39" s="412"/>
-      <c r="E39" s="414"/>
-      <c r="F39" s="401" t="s">
+      <c r="C39" s="427"/>
+      <c r="D39" s="428"/>
+      <c r="E39" s="430"/>
+      <c r="F39" s="396" t="s">
         <v>64</v>
       </c>
-      <c r="G39" s="402"/>
-      <c r="H39" s="403"/>
+      <c r="G39" s="397"/>
+      <c r="H39" s="398"/>
       <c r="I39" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17895,16 +17895,16 @@
       <c r="B40" s="21">
         <v>13</v>
       </c>
-      <c r="C40" s="397" t="s">
+      <c r="C40" s="419" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="398"/>
-      <c r="E40" s="394" t="s">
+      <c r="D40" s="420"/>
+      <c r="E40" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F40" s="395"/>
-      <c r="G40" s="395"/>
-      <c r="H40" s="396"/>
+      <c r="F40" s="394"/>
+      <c r="G40" s="394"/>
+      <c r="H40" s="395"/>
       <c r="I40" s="32"/>
     </row>
     <row r="41" spans="1:15" ht="17.25" customHeight="1">
@@ -17914,16 +17914,16 @@
       <c r="B41" s="21">
         <v>14</v>
       </c>
-      <c r="C41" s="399"/>
-      <c r="D41" s="400"/>
+      <c r="C41" s="421"/>
+      <c r="D41" s="422"/>
       <c r="E41" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F41" s="401" t="s">
-        <v>44</v>
-      </c>
-      <c r="G41" s="402"/>
-      <c r="H41" s="403"/>
+      <c r="F41" s="396" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" s="397"/>
+      <c r="H41" s="398"/>
       <c r="I41" s="32"/>
     </row>
     <row r="42" spans="1:15" ht="12" customHeight="1">
@@ -17942,11 +17942,11 @@
       <c r="E42" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F42" s="391" t="s">
+      <c r="F42" s="416" t="s">
         <v>66</v>
       </c>
-      <c r="G42" s="392"/>
-      <c r="H42" s="393"/>
+      <c r="G42" s="417"/>
+      <c r="H42" s="418"/>
       <c r="I42" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17963,14 +17963,14 @@
       <c r="B44" s="21">
         <v>17</v>
       </c>
-      <c r="C44" s="394" t="s">
+      <c r="C44" s="393" t="s">
         <v>67</v>
       </c>
-      <c r="D44" s="395"/>
-      <c r="E44" s="395"/>
-      <c r="F44" s="395"/>
-      <c r="G44" s="395"/>
-      <c r="H44" s="396"/>
+      <c r="D44" s="394"/>
+      <c r="E44" s="394"/>
+      <c r="F44" s="394"/>
+      <c r="G44" s="394"/>
+      <c r="H44" s="395"/>
       <c r="I44" s="32"/>
     </row>
     <row r="45" spans="1:15" ht="12" customHeight="1">
@@ -17980,16 +17980,16 @@
       <c r="B45" s="21">
         <v>18</v>
       </c>
-      <c r="C45" s="422" t="s">
+      <c r="C45" s="431" t="s">
         <v>68</v>
       </c>
-      <c r="D45" s="423"/>
-      <c r="E45" s="394" t="s">
+      <c r="D45" s="432"/>
+      <c r="E45" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="395"/>
-      <c r="G45" s="395"/>
-      <c r="H45" s="396"/>
+      <c r="F45" s="394"/>
+      <c r="G45" s="394"/>
+      <c r="H45" s="395"/>
       <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:15" ht="30" customHeight="1">
@@ -17999,16 +17999,16 @@
       <c r="B46" s="21">
         <v>19</v>
       </c>
-      <c r="C46" s="424"/>
-      <c r="D46" s="425"/>
-      <c r="E46" s="413" t="s">
+      <c r="C46" s="433"/>
+      <c r="D46" s="434"/>
+      <c r="E46" s="429" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="401" t="s">
+      <c r="F46" s="396" t="s">
         <v>69</v>
       </c>
-      <c r="G46" s="402"/>
-      <c r="H46" s="403"/>
+      <c r="G46" s="397"/>
+      <c r="H46" s="398"/>
       <c r="I46" s="127" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18023,14 +18023,14 @@
       <c r="B47" s="21">
         <v>20</v>
       </c>
-      <c r="C47" s="424"/>
-      <c r="D47" s="425"/>
-      <c r="E47" s="415"/>
-      <c r="F47" s="401" t="s">
+      <c r="C47" s="433"/>
+      <c r="D47" s="434"/>
+      <c r="E47" s="437"/>
+      <c r="F47" s="396" t="s">
         <v>70</v>
       </c>
-      <c r="G47" s="402"/>
-      <c r="H47" s="403"/>
+      <c r="G47" s="397"/>
+      <c r="H47" s="398"/>
       <c r="I47" s="127" t="e">
         <f>#REF!+#REF!-#REF!</f>
         <v>#REF!</v>
@@ -18045,14 +18045,14 @@
       <c r="B48" s="21">
         <v>21</v>
       </c>
-      <c r="C48" s="424"/>
-      <c r="D48" s="425"/>
-      <c r="E48" s="415"/>
-      <c r="F48" s="401" t="s">
+      <c r="C48" s="433"/>
+      <c r="D48" s="434"/>
+      <c r="E48" s="437"/>
+      <c r="F48" s="396" t="s">
         <v>71</v>
       </c>
-      <c r="G48" s="402"/>
-      <c r="H48" s="403"/>
+      <c r="G48" s="397"/>
+      <c r="H48" s="398"/>
       <c r="I48" s="127" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18066,14 +18066,14 @@
       <c r="B49" s="21">
         <v>22</v>
       </c>
-      <c r="C49" s="426"/>
-      <c r="D49" s="427"/>
-      <c r="E49" s="414"/>
-      <c r="F49" s="401" t="s">
+      <c r="C49" s="435"/>
+      <c r="D49" s="436"/>
+      <c r="E49" s="430"/>
+      <c r="F49" s="396" t="s">
         <v>72</v>
       </c>
-      <c r="G49" s="402"/>
-      <c r="H49" s="403"/>
+      <c r="G49" s="397"/>
+      <c r="H49" s="398"/>
       <c r="I49" s="34" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18087,16 +18087,16 @@
       <c r="B50" s="21">
         <v>23</v>
       </c>
-      <c r="C50" s="418" t="s">
+      <c r="C50" s="438" t="s">
         <v>73</v>
       </c>
-      <c r="D50" s="419"/>
-      <c r="E50" s="394" t="s">
+      <c r="D50" s="439"/>
+      <c r="E50" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F50" s="395"/>
-      <c r="G50" s="395"/>
-      <c r="H50" s="396"/>
+      <c r="F50" s="394"/>
+      <c r="G50" s="394"/>
+      <c r="H50" s="395"/>
       <c r="I50" s="32"/>
     </row>
     <row r="51" spans="1:14" ht="12" customHeight="1">
@@ -18106,16 +18106,16 @@
       <c r="B51" s="21">
         <v>24</v>
       </c>
-      <c r="C51" s="420"/>
-      <c r="D51" s="421"/>
+      <c r="C51" s="440"/>
+      <c r="D51" s="441"/>
       <c r="E51" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="401" t="s">
+      <c r="F51" s="396" t="s">
         <v>23</v>
       </c>
-      <c r="G51" s="402"/>
-      <c r="H51" s="403"/>
+      <c r="G51" s="397"/>
+      <c r="H51" s="398"/>
       <c r="I51" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18138,11 +18138,11 @@
       <c r="E52" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="401" t="s">
+      <c r="F52" s="396" t="s">
         <v>74</v>
       </c>
-      <c r="G52" s="402"/>
-      <c r="H52" s="403"/>
+      <c r="G52" s="397"/>
+      <c r="H52" s="398"/>
       <c r="I52" s="32"/>
       <c r="N52" s="35"/>
     </row>
@@ -18156,16 +18156,16 @@
       <c r="B54" s="21">
         <v>27</v>
       </c>
-      <c r="C54" s="397" t="s">
+      <c r="C54" s="419" t="s">
         <v>75</v>
       </c>
-      <c r="D54" s="398"/>
-      <c r="E54" s="394" t="s">
+      <c r="D54" s="420"/>
+      <c r="E54" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F54" s="395"/>
-      <c r="G54" s="395"/>
-      <c r="H54" s="396"/>
+      <c r="F54" s="394"/>
+      <c r="G54" s="394"/>
+      <c r="H54" s="395"/>
       <c r="I54" s="32"/>
     </row>
     <row r="55" spans="1:14" ht="12" customHeight="1">
@@ -18175,16 +18175,16 @@
       <c r="B55" s="21">
         <v>28</v>
       </c>
-      <c r="C55" s="399"/>
-      <c r="D55" s="400"/>
+      <c r="C55" s="421"/>
+      <c r="D55" s="422"/>
       <c r="E55" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F55" s="401" t="s">
+      <c r="F55" s="396" t="s">
         <v>76</v>
       </c>
-      <c r="G55" s="402"/>
-      <c r="H55" s="403"/>
+      <c r="G55" s="397"/>
+      <c r="H55" s="398"/>
       <c r="I55" s="32"/>
     </row>
     <row r="56" spans="1:14" ht="12" customHeight="1">
@@ -18194,16 +18194,16 @@
       <c r="B56" s="21">
         <v>29</v>
       </c>
-      <c r="C56" s="399"/>
-      <c r="D56" s="400"/>
+      <c r="C56" s="421"/>
+      <c r="D56" s="422"/>
       <c r="E56" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="401" t="s">
+      <c r="F56" s="396" t="s">
         <v>77</v>
       </c>
-      <c r="G56" s="402"/>
-      <c r="H56" s="403"/>
+      <c r="G56" s="397"/>
+      <c r="H56" s="398"/>
       <c r="I56" s="32"/>
     </row>
     <row r="57" spans="1:14" ht="12" customHeight="1">
@@ -18213,16 +18213,16 @@
       <c r="B57" s="21">
         <v>30</v>
       </c>
-      <c r="C57" s="399"/>
-      <c r="D57" s="400"/>
+      <c r="C57" s="421"/>
+      <c r="D57" s="422"/>
       <c r="E57" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="401" t="s">
+      <c r="F57" s="396" t="s">
         <v>78</v>
       </c>
-      <c r="G57" s="402"/>
-      <c r="H57" s="403"/>
+      <c r="G57" s="397"/>
+      <c r="H57" s="398"/>
       <c r="I57" s="32"/>
     </row>
     <row r="58" spans="1:14" ht="12" customHeight="1">
@@ -18241,11 +18241,11 @@
       <c r="E58" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F58" s="401" t="s">
+      <c r="F58" s="396" t="s">
         <v>79</v>
       </c>
-      <c r="G58" s="402"/>
-      <c r="H58" s="403"/>
+      <c r="G58" s="397"/>
+      <c r="H58" s="398"/>
       <c r="I58" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18261,14 +18261,14 @@
       <c r="B60" s="21">
         <v>33</v>
       </c>
-      <c r="C60" s="394" t="s">
+      <c r="C60" s="393" t="s">
         <v>80</v>
       </c>
-      <c r="D60" s="395"/>
-      <c r="E60" s="395"/>
-      <c r="F60" s="395"/>
-      <c r="G60" s="395"/>
-      <c r="H60" s="396"/>
+      <c r="D60" s="394"/>
+      <c r="E60" s="394"/>
+      <c r="F60" s="394"/>
+      <c r="G60" s="394"/>
+      <c r="H60" s="395"/>
       <c r="I60" s="32"/>
     </row>
     <row r="61" spans="1:14" ht="12" customHeight="1">
@@ -18278,16 +18278,16 @@
       <c r="B61" s="21">
         <v>34</v>
       </c>
-      <c r="C61" s="397" t="s">
+      <c r="C61" s="419" t="s">
         <v>81</v>
       </c>
-      <c r="D61" s="398"/>
-      <c r="E61" s="394" t="s">
+      <c r="D61" s="420"/>
+      <c r="E61" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F61" s="395"/>
-      <c r="G61" s="395"/>
-      <c r="H61" s="396"/>
+      <c r="F61" s="394"/>
+      <c r="G61" s="394"/>
+      <c r="H61" s="395"/>
       <c r="I61" s="32"/>
     </row>
     <row r="62" spans="1:14" ht="12" customHeight="1">
@@ -18297,18 +18297,18 @@
       <c r="B62" s="21">
         <v>35</v>
       </c>
-      <c r="C62" s="399"/>
-      <c r="D62" s="400"/>
+      <c r="C62" s="421"/>
+      <c r="D62" s="422"/>
       <c r="E62" s="26" t="s">
         <v>55</v>
       </c>
       <c r="F62" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G62" s="416" t="s">
+      <c r="G62" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H62" s="417"/>
+      <c r="H62" s="443"/>
       <c r="I62" s="32"/>
     </row>
     <row r="63" spans="1:14" ht="12" customHeight="1">
@@ -18318,8 +18318,8 @@
       <c r="B63" s="21">
         <v>36</v>
       </c>
-      <c r="C63" s="399"/>
-      <c r="D63" s="400"/>
+      <c r="C63" s="421"/>
+      <c r="D63" s="422"/>
       <c r="E63" s="27" t="s">
         <v>44</v>
       </c>
@@ -18383,10 +18383,10 @@
       <c r="F66" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="G66" s="416" t="s">
+      <c r="G66" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H66" s="417"/>
+      <c r="H66" s="443"/>
       <c r="I66" s="32"/>
     </row>
     <row r="67" spans="1:14" ht="12" customHeight="1">
@@ -18465,10 +18465,10 @@
       <c r="F70" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G70" s="416" t="s">
+      <c r="G70" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H70" s="417"/>
+      <c r="H70" s="443"/>
       <c r="I70" s="32"/>
     </row>
     <row r="71" spans="1:14" ht="12" customHeight="1">
@@ -18547,10 +18547,10 @@
       <c r="F74" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="G74" s="416" t="s">
+      <c r="G74" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H74" s="417"/>
+      <c r="H74" s="443"/>
       <c r="I74" s="32"/>
     </row>
     <row r="75" spans="1:14" ht="12" customHeight="1">
@@ -18617,16 +18617,16 @@
       <c r="B78" s="21">
         <v>51</v>
       </c>
-      <c r="C78" s="397" t="s">
+      <c r="C78" s="419" t="s">
         <v>88</v>
       </c>
-      <c r="D78" s="398"/>
-      <c r="E78" s="394" t="s">
+      <c r="D78" s="420"/>
+      <c r="E78" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F78" s="395"/>
-      <c r="G78" s="395"/>
-      <c r="H78" s="396"/>
+      <c r="F78" s="394"/>
+      <c r="G78" s="394"/>
+      <c r="H78" s="395"/>
       <c r="I78" s="32"/>
     </row>
     <row r="79" spans="1:14" ht="12" customHeight="1">
@@ -18636,16 +18636,16 @@
       <c r="B79" s="21">
         <v>52</v>
       </c>
-      <c r="C79" s="399"/>
-      <c r="D79" s="400"/>
+      <c r="C79" s="421"/>
+      <c r="D79" s="422"/>
       <c r="E79" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F79" s="401" t="s">
+      <c r="F79" s="396" t="s">
         <v>89</v>
       </c>
-      <c r="G79" s="402"/>
-      <c r="H79" s="403"/>
+      <c r="G79" s="397"/>
+      <c r="H79" s="398"/>
       <c r="I79" s="32"/>
     </row>
     <row r="80" spans="1:14" ht="12" customHeight="1">
@@ -18664,11 +18664,11 @@
       <c r="E80" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F80" s="401" t="s">
+      <c r="F80" s="396" t="s">
         <v>24</v>
       </c>
-      <c r="G80" s="402"/>
-      <c r="H80" s="403"/>
+      <c r="G80" s="397"/>
+      <c r="H80" s="398"/>
       <c r="I80" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18691,11 +18691,11 @@
       <c r="E81" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="401" t="s">
+      <c r="F81" s="396" t="s">
         <v>90</v>
       </c>
-      <c r="G81" s="402"/>
-      <c r="H81" s="403"/>
+      <c r="G81" s="397"/>
+      <c r="H81" s="398"/>
       <c r="I81" s="32"/>
       <c r="N81" s="35"/>
     </row>
@@ -18715,13 +18715,13 @@
       <c r="E82" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="413" t="s">
+      <c r="F82" s="429" t="s">
         <v>91</v>
       </c>
-      <c r="G82" s="416" t="s">
+      <c r="G82" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H82" s="417"/>
+      <c r="H82" s="443"/>
       <c r="I82" s="32"/>
     </row>
     <row r="83" spans="1:14" ht="24" customHeight="1">
@@ -18740,8 +18740,8 @@
       <c r="E83" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F83" s="415"/>
-      <c r="G83" s="413" t="s">
+      <c r="F83" s="437"/>
+      <c r="G83" s="429" t="s">
         <v>55</v>
       </c>
       <c r="H83" s="15" t="s">
@@ -18768,8 +18768,8 @@
       <c r="E84" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F84" s="414"/>
-      <c r="G84" s="414"/>
+      <c r="F84" s="430"/>
+      <c r="G84" s="430"/>
       <c r="H84" s="15" t="s">
         <v>92</v>
       </c>
@@ -18794,11 +18794,11 @@
       <c r="E85" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F85" s="401" t="s">
+      <c r="F85" s="396" t="s">
         <v>9</v>
       </c>
-      <c r="G85" s="402"/>
-      <c r="H85" s="403"/>
+      <c r="G85" s="397"/>
+      <c r="H85" s="398"/>
       <c r="I85" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18820,11 +18820,11 @@
       <c r="E86" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F86" s="401" t="s">
+      <c r="F86" s="396" t="s">
         <v>10</v>
       </c>
-      <c r="G86" s="402"/>
-      <c r="H86" s="403"/>
+      <c r="G86" s="397"/>
+      <c r="H86" s="398"/>
       <c r="I86" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18846,11 +18846,11 @@
       <c r="E87" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F87" s="401" t="s">
+      <c r="F87" s="396" t="s">
         <v>11</v>
       </c>
-      <c r="G87" s="402"/>
-      <c r="H87" s="403"/>
+      <c r="G87" s="397"/>
+      <c r="H87" s="398"/>
       <c r="I87" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18872,11 +18872,11 @@
       <c r="E88" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="401" t="s">
+      <c r="F88" s="396" t="s">
         <v>93</v>
       </c>
-      <c r="G88" s="402"/>
-      <c r="H88" s="403"/>
+      <c r="G88" s="397"/>
+      <c r="H88" s="398"/>
       <c r="I88" s="32"/>
     </row>
     <row r="89" spans="1:14" ht="12" customHeight="1">
@@ -18895,11 +18895,11 @@
       <c r="E89" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F89" s="391" t="s">
+      <c r="F89" s="416" t="s">
         <v>94</v>
       </c>
-      <c r="G89" s="392"/>
-      <c r="H89" s="393"/>
+      <c r="G89" s="417"/>
+      <c r="H89" s="418"/>
       <c r="I89" s="32"/>
       <c r="J89" s="10"/>
     </row>
@@ -18919,9 +18919,9 @@
       <c r="E90" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F90" s="391"/>
-      <c r="G90" s="392"/>
-      <c r="H90" s="393"/>
+      <c r="F90" s="416"/>
+      <c r="G90" s="417"/>
+      <c r="H90" s="418"/>
       <c r="I90" s="39"/>
       <c r="J90" s="10"/>
     </row>
@@ -18935,16 +18935,16 @@
       <c r="B92" s="21">
         <v>63</v>
       </c>
-      <c r="C92" s="397" t="s">
+      <c r="C92" s="419" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="398"/>
-      <c r="E92" s="394" t="s">
+      <c r="D92" s="420"/>
+      <c r="E92" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F92" s="395"/>
-      <c r="G92" s="395"/>
-      <c r="H92" s="396"/>
+      <c r="F92" s="394"/>
+      <c r="G92" s="394"/>
+      <c r="H92" s="395"/>
       <c r="I92" s="32"/>
     </row>
     <row r="93" spans="1:14" ht="12" customHeight="1">
@@ -18960,14 +18960,14 @@
       <c r="D93" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="413" t="s">
+      <c r="E93" s="429" t="s">
         <v>55</v>
       </c>
-      <c r="F93" s="401" t="s">
-        <v>44</v>
-      </c>
-      <c r="G93" s="402"/>
-      <c r="H93" s="403"/>
+      <c r="F93" s="396" t="s">
+        <v>44</v>
+      </c>
+      <c r="G93" s="397"/>
+      <c r="H93" s="398"/>
       <c r="I93" s="32"/>
     </row>
     <row r="94" spans="1:14" ht="12" customHeight="1">
@@ -18983,12 +18983,12 @@
       <c r="D94" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="E94" s="414"/>
-      <c r="F94" s="391" t="s">
+      <c r="E94" s="430"/>
+      <c r="F94" s="416" t="s">
         <v>96</v>
       </c>
-      <c r="G94" s="392"/>
-      <c r="H94" s="393"/>
+      <c r="G94" s="417"/>
+      <c r="H94" s="418"/>
       <c r="I94" s="32"/>
       <c r="J94" s="10"/>
     </row>
@@ -19002,16 +19002,16 @@
       <c r="B96" s="21">
         <v>66</v>
       </c>
-      <c r="C96" s="397" t="s">
+      <c r="C96" s="419" t="s">
         <v>97</v>
       </c>
-      <c r="D96" s="398"/>
-      <c r="E96" s="394" t="s">
+      <c r="D96" s="420"/>
+      <c r="E96" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F96" s="395"/>
-      <c r="G96" s="395"/>
-      <c r="H96" s="396"/>
+      <c r="F96" s="394"/>
+      <c r="G96" s="394"/>
+      <c r="H96" s="395"/>
       <c r="I96" s="32"/>
     </row>
     <row r="97" spans="1:10" ht="12" customHeight="1">
@@ -19030,11 +19030,11 @@
       <c r="E97" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F97" s="401" t="s">
+      <c r="F97" s="396" t="s">
         <v>98</v>
       </c>
-      <c r="G97" s="402"/>
-      <c r="H97" s="403"/>
+      <c r="G97" s="397"/>
+      <c r="H97" s="398"/>
       <c r="I97" s="32"/>
     </row>
     <row r="98" spans="1:10" ht="12" customHeight="1">
@@ -19053,11 +19053,11 @@
       <c r="E98" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F98" s="401" t="s">
+      <c r="F98" s="396" t="s">
         <v>99</v>
       </c>
-      <c r="G98" s="402"/>
-      <c r="H98" s="403"/>
+      <c r="G98" s="397"/>
+      <c r="H98" s="398"/>
       <c r="I98" s="32"/>
     </row>
     <row r="99" spans="1:10" ht="12" customHeight="1">
@@ -19076,11 +19076,11 @@
       <c r="E99" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F99" s="401" t="s">
+      <c r="F99" s="396" t="s">
         <v>12</v>
       </c>
-      <c r="G99" s="402"/>
-      <c r="H99" s="403"/>
+      <c r="G99" s="397"/>
+      <c r="H99" s="398"/>
       <c r="I99" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19102,11 +19102,11 @@
       <c r="E100" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F100" s="401" t="s">
+      <c r="F100" s="396" t="s">
         <v>100</v>
       </c>
-      <c r="G100" s="402"/>
-      <c r="H100" s="403"/>
+      <c r="G100" s="397"/>
+      <c r="H100" s="398"/>
       <c r="I100" s="32"/>
     </row>
     <row r="101" spans="1:10" ht="12" customHeight="1">
@@ -19125,11 +19125,11 @@
       <c r="E101" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F101" s="391" t="s">
-        <v>44</v>
-      </c>
-      <c r="G101" s="392"/>
-      <c r="H101" s="393"/>
+      <c r="F101" s="416" t="s">
+        <v>44</v>
+      </c>
+      <c r="G101" s="417"/>
+      <c r="H101" s="418"/>
       <c r="I101" s="32"/>
       <c r="J101" s="10"/>
     </row>
@@ -19149,11 +19149,11 @@
       <c r="E102" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F102" s="391" t="s">
-        <v>44</v>
-      </c>
-      <c r="G102" s="392"/>
-      <c r="H102" s="393"/>
+      <c r="F102" s="416" t="s">
+        <v>44</v>
+      </c>
+      <c r="G102" s="417"/>
+      <c r="H102" s="418"/>
       <c r="I102" s="32"/>
       <c r="J102" s="10"/>
     </row>
@@ -19167,14 +19167,14 @@
       <c r="B104" s="21">
         <v>72</v>
       </c>
-      <c r="C104" s="394" t="s">
+      <c r="C104" s="393" t="s">
         <v>19</v>
       </c>
-      <c r="D104" s="395"/>
-      <c r="E104" s="395"/>
-      <c r="F104" s="395"/>
-      <c r="G104" s="395"/>
-      <c r="H104" s="396"/>
+      <c r="D104" s="394"/>
+      <c r="E104" s="394"/>
+      <c r="F104" s="394"/>
+      <c r="G104" s="394"/>
+      <c r="H104" s="395"/>
       <c r="I104" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19187,14 +19187,14 @@
       <c r="B105" s="21">
         <v>73</v>
       </c>
-      <c r="C105" s="394" t="s">
+      <c r="C105" s="393" t="s">
         <v>101</v>
       </c>
-      <c r="D105" s="395"/>
-      <c r="E105" s="395"/>
-      <c r="F105" s="395"/>
-      <c r="G105" s="395"/>
-      <c r="H105" s="396"/>
+      <c r="D105" s="394"/>
+      <c r="E105" s="394"/>
+      <c r="F105" s="394"/>
+      <c r="G105" s="394"/>
+      <c r="H105" s="395"/>
       <c r="I105" s="32"/>
     </row>
     <row r="106" spans="1:10" ht="12" customHeight="1">
@@ -19204,16 +19204,16 @@
       <c r="B106" s="21">
         <v>74</v>
       </c>
-      <c r="C106" s="397" t="s">
+      <c r="C106" s="419" t="s">
         <v>102</v>
       </c>
-      <c r="D106" s="398"/>
-      <c r="E106" s="394" t="s">
+      <c r="D106" s="420"/>
+      <c r="E106" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F106" s="395"/>
-      <c r="G106" s="395"/>
-      <c r="H106" s="396"/>
+      <c r="F106" s="394"/>
+      <c r="G106" s="394"/>
+      <c r="H106" s="395"/>
       <c r="I106" s="32"/>
     </row>
     <row r="107" spans="1:10" ht="18.75" customHeight="1">
@@ -19223,16 +19223,16 @@
       <c r="B107" s="21">
         <v>75</v>
       </c>
-      <c r="C107" s="399"/>
-      <c r="D107" s="400"/>
+      <c r="C107" s="421"/>
+      <c r="D107" s="422"/>
       <c r="E107" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F107" s="401" t="s">
+      <c r="F107" s="396" t="s">
         <v>13</v>
       </c>
-      <c r="G107" s="402"/>
-      <c r="H107" s="403"/>
+      <c r="G107" s="397"/>
+      <c r="H107" s="398"/>
       <c r="I107" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19254,11 +19254,11 @@
       <c r="E108" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F108" s="391" t="s">
+      <c r="F108" s="416" t="s">
         <v>103</v>
       </c>
-      <c r="G108" s="392"/>
-      <c r="H108" s="393"/>
+      <c r="G108" s="417"/>
+      <c r="H108" s="418"/>
       <c r="I108" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19281,11 +19281,11 @@
       <c r="E109" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F109" s="391" t="s">
+      <c r="F109" s="416" t="s">
         <v>104</v>
       </c>
-      <c r="G109" s="392"/>
-      <c r="H109" s="393"/>
+      <c r="G109" s="417"/>
+      <c r="H109" s="418"/>
       <c r="I109" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19308,11 +19308,11 @@
       <c r="E110" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F110" s="391" t="s">
+      <c r="F110" s="416" t="s">
         <v>8</v>
       </c>
-      <c r="G110" s="392"/>
-      <c r="H110" s="393"/>
+      <c r="G110" s="417"/>
+      <c r="H110" s="418"/>
       <c r="I110" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19329,16 +19329,16 @@
       <c r="B112" s="21">
         <v>77</v>
       </c>
-      <c r="C112" s="397" t="s">
+      <c r="C112" s="419" t="s">
         <v>105</v>
       </c>
-      <c r="D112" s="398"/>
-      <c r="E112" s="394" t="s">
+      <c r="D112" s="420"/>
+      <c r="E112" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F112" s="395"/>
-      <c r="G112" s="395"/>
-      <c r="H112" s="396"/>
+      <c r="F112" s="394"/>
+      <c r="G112" s="394"/>
+      <c r="H112" s="395"/>
       <c r="I112" s="32"/>
     </row>
     <row r="113" spans="1:9" ht="12" customHeight="1">
@@ -19357,11 +19357,11 @@
       <c r="E113" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F113" s="401" t="s">
+      <c r="F113" s="396" t="s">
         <v>106</v>
       </c>
-      <c r="G113" s="402"/>
-      <c r="H113" s="403"/>
+      <c r="G113" s="397"/>
+      <c r="H113" s="398"/>
       <c r="I113" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19383,11 +19383,11 @@
       <c r="E114" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F114" s="401" t="s">
+      <c r="F114" s="396" t="s">
         <v>107</v>
       </c>
-      <c r="G114" s="402"/>
-      <c r="H114" s="403"/>
+      <c r="G114" s="397"/>
+      <c r="H114" s="398"/>
       <c r="I114" s="32"/>
     </row>
     <row r="115" spans="1:9" ht="12" customHeight="1">
@@ -19397,14 +19397,14 @@
       <c r="B115" s="21">
         <v>80</v>
       </c>
-      <c r="C115" s="394" t="s">
+      <c r="C115" s="393" t="s">
         <v>108</v>
       </c>
-      <c r="D115" s="395"/>
-      <c r="E115" s="395"/>
-      <c r="F115" s="395"/>
-      <c r="G115" s="395"/>
-      <c r="H115" s="396"/>
+      <c r="D115" s="394"/>
+      <c r="E115" s="394"/>
+      <c r="F115" s="394"/>
+      <c r="G115" s="394"/>
+      <c r="H115" s="395"/>
       <c r="I115" s="32"/>
     </row>
     <row r="116" spans="1:9" ht="12" customHeight="1">
@@ -19414,16 +19414,16 @@
       <c r="B116" s="21">
         <v>81</v>
       </c>
-      <c r="C116" s="397" t="s">
+      <c r="C116" s="419" t="s">
         <v>109</v>
       </c>
-      <c r="D116" s="398"/>
-      <c r="E116" s="394" t="s">
+      <c r="D116" s="420"/>
+      <c r="E116" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F116" s="395"/>
-      <c r="G116" s="395"/>
-      <c r="H116" s="396"/>
+      <c r="F116" s="394"/>
+      <c r="G116" s="394"/>
+      <c r="H116" s="395"/>
       <c r="I116" s="32"/>
     </row>
     <row r="117" spans="1:9" ht="12" customHeight="1">
@@ -19433,16 +19433,16 @@
       <c r="B117" s="21">
         <v>82</v>
       </c>
-      <c r="C117" s="399"/>
-      <c r="D117" s="400"/>
+      <c r="C117" s="421"/>
+      <c r="D117" s="422"/>
       <c r="E117" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F117" s="401" t="s">
+      <c r="F117" s="396" t="s">
         <v>110</v>
       </c>
-      <c r="G117" s="402"/>
-      <c r="H117" s="403"/>
+      <c r="G117" s="397"/>
+      <c r="H117" s="398"/>
       <c r="I117" s="32"/>
     </row>
     <row r="118" spans="1:9" ht="12" customHeight="1">
@@ -19461,11 +19461,11 @@
       <c r="E118" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F118" s="401" t="s">
+      <c r="F118" s="396" t="s">
         <v>111</v>
       </c>
-      <c r="G118" s="402"/>
-      <c r="H118" s="403"/>
+      <c r="G118" s="397"/>
+      <c r="H118" s="398"/>
       <c r="I118" s="32"/>
     </row>
     <row r="119" spans="1:9" hidden="1">
@@ -19478,16 +19478,16 @@
       <c r="B120" s="21">
         <v>85</v>
       </c>
-      <c r="C120" s="397" t="s">
+      <c r="C120" s="419" t="s">
         <v>112</v>
       </c>
-      <c r="D120" s="398"/>
-      <c r="E120" s="394" t="s">
+      <c r="D120" s="420"/>
+      <c r="E120" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F120" s="395"/>
-      <c r="G120" s="395"/>
-      <c r="H120" s="396"/>
+      <c r="F120" s="394"/>
+      <c r="G120" s="394"/>
+      <c r="H120" s="395"/>
       <c r="I120" s="32"/>
     </row>
     <row r="121" spans="1:9" ht="12" customHeight="1">
@@ -19497,16 +19497,16 @@
       <c r="B121" s="21">
         <v>86</v>
       </c>
-      <c r="C121" s="399"/>
-      <c r="D121" s="400"/>
+      <c r="C121" s="421"/>
+      <c r="D121" s="422"/>
       <c r="E121" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F121" s="401" t="s">
+      <c r="F121" s="396" t="s">
         <v>113</v>
       </c>
-      <c r="G121" s="402"/>
-      <c r="H121" s="403"/>
+      <c r="G121" s="397"/>
+      <c r="H121" s="398"/>
       <c r="I121" s="32"/>
     </row>
     <row r="122" spans="1:9" ht="12" customHeight="1">
@@ -19525,11 +19525,11 @@
       <c r="E122" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F122" s="401" t="s">
+      <c r="F122" s="396" t="s">
         <v>111</v>
       </c>
-      <c r="G122" s="402"/>
-      <c r="H122" s="403"/>
+      <c r="G122" s="397"/>
+      <c r="H122" s="398"/>
       <c r="I122" s="32"/>
     </row>
     <row r="123" spans="1:9" ht="12" customHeight="1">
@@ -19548,11 +19548,11 @@
       <c r="E123" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F123" s="401" t="s">
+      <c r="F123" s="396" t="s">
         <v>114</v>
       </c>
-      <c r="G123" s="402"/>
-      <c r="H123" s="403"/>
+      <c r="G123" s="397"/>
+      <c r="H123" s="398"/>
       <c r="I123" s="32"/>
     </row>
     <row r="124" spans="1:9" ht="12" customHeight="1">
@@ -19571,11 +19571,11 @@
       <c r="E124" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F124" s="401" t="s">
+      <c r="F124" s="396" t="s">
         <v>115</v>
       </c>
-      <c r="G124" s="402"/>
-      <c r="H124" s="403"/>
+      <c r="G124" s="397"/>
+      <c r="H124" s="398"/>
       <c r="I124" s="32"/>
     </row>
     <row r="125" spans="1:9" hidden="1">
@@ -19588,14 +19588,14 @@
       <c r="B126" s="21">
         <v>91</v>
       </c>
-      <c r="C126" s="394" t="s">
+      <c r="C126" s="393" t="s">
         <v>116</v>
       </c>
-      <c r="D126" s="395"/>
-      <c r="E126" s="395"/>
-      <c r="F126" s="395"/>
-      <c r="G126" s="395"/>
-      <c r="H126" s="396"/>
+      <c r="D126" s="394"/>
+      <c r="E126" s="394"/>
+      <c r="F126" s="394"/>
+      <c r="G126" s="394"/>
+      <c r="H126" s="395"/>
       <c r="I126" s="32"/>
     </row>
     <row r="127" spans="1:9" ht="12" customHeight="1">
@@ -19605,16 +19605,16 @@
       <c r="B127" s="21">
         <v>92</v>
       </c>
-      <c r="C127" s="397" t="s">
+      <c r="C127" s="419" t="s">
         <v>117</v>
       </c>
-      <c r="D127" s="398"/>
-      <c r="E127" s="394" t="s">
+      <c r="D127" s="420"/>
+      <c r="E127" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F127" s="395"/>
-      <c r="G127" s="395"/>
-      <c r="H127" s="396"/>
+      <c r="F127" s="394"/>
+      <c r="G127" s="394"/>
+      <c r="H127" s="395"/>
       <c r="I127" s="32"/>
     </row>
     <row r="128" spans="1:9" ht="12" customHeight="1">
@@ -19624,16 +19624,16 @@
       <c r="B128" s="21">
         <v>93</v>
       </c>
-      <c r="C128" s="399"/>
-      <c r="D128" s="400"/>
+      <c r="C128" s="421"/>
+      <c r="D128" s="422"/>
       <c r="E128" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F128" s="404" t="s">
-        <v>44</v>
-      </c>
-      <c r="G128" s="405"/>
-      <c r="H128" s="406"/>
+      <c r="F128" s="444" t="s">
+        <v>44</v>
+      </c>
+      <c r="G128" s="445"/>
+      <c r="H128" s="446"/>
       <c r="I128" s="40"/>
     </row>
     <row r="129" spans="1:14" hidden="1">
@@ -19646,14 +19646,14 @@
       <c r="B130" s="21">
         <v>95</v>
       </c>
-      <c r="C130" s="394" t="s">
+      <c r="C130" s="393" t="s">
         <v>118</v>
       </c>
-      <c r="D130" s="395"/>
-      <c r="E130" s="395"/>
-      <c r="F130" s="395"/>
-      <c r="G130" s="395"/>
-      <c r="H130" s="396"/>
+      <c r="D130" s="394"/>
+      <c r="E130" s="394"/>
+      <c r="F130" s="394"/>
+      <c r="G130" s="394"/>
+      <c r="H130" s="395"/>
       <c r="I130" s="32"/>
     </row>
     <row r="131" spans="1:14" ht="12" customHeight="1">
@@ -19663,14 +19663,14 @@
       <c r="B131" s="21">
         <v>96</v>
       </c>
-      <c r="C131" s="394" t="s">
+      <c r="C131" s="393" t="s">
         <v>119</v>
       </c>
-      <c r="D131" s="395"/>
-      <c r="E131" s="395"/>
-      <c r="F131" s="395"/>
-      <c r="G131" s="395"/>
-      <c r="H131" s="396"/>
+      <c r="D131" s="394"/>
+      <c r="E131" s="394"/>
+      <c r="F131" s="394"/>
+      <c r="G131" s="394"/>
+      <c r="H131" s="395"/>
       <c r="I131" s="32"/>
     </row>
     <row r="132" spans="1:14" ht="12" customHeight="1">
@@ -19680,16 +19680,16 @@
       <c r="B132" s="21">
         <v>97</v>
       </c>
-      <c r="C132" s="397" t="s">
+      <c r="C132" s="419" t="s">
         <v>120</v>
       </c>
-      <c r="D132" s="398"/>
-      <c r="E132" s="394" t="s">
+      <c r="D132" s="420"/>
+      <c r="E132" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F132" s="395"/>
-      <c r="G132" s="395"/>
-      <c r="H132" s="396"/>
+      <c r="F132" s="394"/>
+      <c r="G132" s="394"/>
+      <c r="H132" s="395"/>
       <c r="I132" s="32"/>
     </row>
     <row r="133" spans="1:14" ht="12" customHeight="1">
@@ -19699,16 +19699,16 @@
       <c r="B133" s="21">
         <v>98</v>
       </c>
-      <c r="C133" s="399"/>
-      <c r="D133" s="400"/>
+      <c r="C133" s="421"/>
+      <c r="D133" s="422"/>
       <c r="E133" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F133" s="401" t="s">
+      <c r="F133" s="396" t="s">
         <v>121</v>
       </c>
-      <c r="G133" s="402"/>
-      <c r="H133" s="403"/>
+      <c r="G133" s="397"/>
+      <c r="H133" s="398"/>
       <c r="I133" s="32"/>
     </row>
     <row r="134" spans="1:14" ht="12" customHeight="1">
@@ -19718,16 +19718,16 @@
       <c r="B134" s="21">
         <v>99</v>
       </c>
-      <c r="C134" s="399"/>
-      <c r="D134" s="400"/>
+      <c r="C134" s="421"/>
+      <c r="D134" s="422"/>
       <c r="E134" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F134" s="401" t="s">
+      <c r="F134" s="396" t="s">
         <v>122</v>
       </c>
-      <c r="G134" s="402"/>
-      <c r="H134" s="403"/>
+      <c r="G134" s="397"/>
+      <c r="H134" s="398"/>
       <c r="I134" s="32"/>
     </row>
     <row r="135" spans="1:14" ht="12" customHeight="1">
@@ -19737,16 +19737,16 @@
       <c r="B135" s="21">
         <v>100</v>
       </c>
-      <c r="C135" s="399"/>
-      <c r="D135" s="400"/>
+      <c r="C135" s="421"/>
+      <c r="D135" s="422"/>
       <c r="E135" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F135" s="401" t="s">
+      <c r="F135" s="396" t="s">
         <v>123</v>
       </c>
-      <c r="G135" s="402"/>
-      <c r="H135" s="403"/>
+      <c r="G135" s="397"/>
+      <c r="H135" s="398"/>
       <c r="I135" s="32"/>
     </row>
     <row r="136" spans="1:14" ht="12" customHeight="1">
@@ -19765,11 +19765,11 @@
       <c r="E136" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F136" s="401" t="s">
+      <c r="F136" s="396" t="s">
         <v>124</v>
       </c>
-      <c r="G136" s="402"/>
-      <c r="H136" s="403"/>
+      <c r="G136" s="397"/>
+      <c r="H136" s="398"/>
       <c r="I136" s="32"/>
     </row>
     <row r="137" spans="1:14" ht="12" customHeight="1">
@@ -19788,11 +19788,11 @@
       <c r="E137" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F137" s="401" t="s">
+      <c r="F137" s="396" t="s">
         <v>125</v>
       </c>
-      <c r="G137" s="402"/>
-      <c r="H137" s="403"/>
+      <c r="G137" s="397"/>
+      <c r="H137" s="398"/>
       <c r="I137" s="32"/>
     </row>
     <row r="138" spans="1:14" ht="12" customHeight="1">
@@ -19811,11 +19811,11 @@
       <c r="E138" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F138" s="401" t="s">
+      <c r="F138" s="396" t="s">
         <v>126</v>
       </c>
-      <c r="G138" s="402"/>
-      <c r="H138" s="403"/>
+      <c r="G138" s="397"/>
+      <c r="H138" s="398"/>
       <c r="I138" s="32"/>
     </row>
     <row r="139" spans="1:14" hidden="1">
@@ -19828,16 +19828,16 @@
       <c r="B140" s="21">
         <v>105</v>
       </c>
-      <c r="C140" s="407" t="s">
+      <c r="C140" s="423" t="s">
         <v>127</v>
       </c>
-      <c r="D140" s="408"/>
-      <c r="E140" s="394" t="s">
+      <c r="D140" s="424"/>
+      <c r="E140" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F140" s="395"/>
-      <c r="G140" s="395"/>
-      <c r="H140" s="396"/>
+      <c r="F140" s="394"/>
+      <c r="G140" s="394"/>
+      <c r="H140" s="395"/>
       <c r="I140" s="32"/>
     </row>
     <row r="141" spans="1:14" ht="12" customHeight="1">
@@ -19847,16 +19847,16 @@
       <c r="B141" s="21">
         <v>106</v>
       </c>
-      <c r="C141" s="409"/>
-      <c r="D141" s="410"/>
-      <c r="E141" s="413" t="s">
+      <c r="C141" s="425"/>
+      <c r="D141" s="426"/>
+      <c r="E141" s="429" t="s">
         <v>55</v>
       </c>
-      <c r="F141" s="401" t="s">
+      <c r="F141" s="396" t="s">
         <v>128</v>
       </c>
-      <c r="G141" s="402"/>
-      <c r="H141" s="403"/>
+      <c r="G141" s="397"/>
+      <c r="H141" s="398"/>
       <c r="I141" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -19869,14 +19869,14 @@
       <c r="B142" s="21">
         <v>107</v>
       </c>
-      <c r="C142" s="411"/>
-      <c r="D142" s="412"/>
-      <c r="E142" s="414"/>
-      <c r="F142" s="401" t="s">
+      <c r="C142" s="427"/>
+      <c r="D142" s="428"/>
+      <c r="E142" s="430"/>
+      <c r="F142" s="396" t="s">
         <v>129</v>
       </c>
-      <c r="G142" s="402"/>
-      <c r="H142" s="403"/>
+      <c r="G142" s="397"/>
+      <c r="H142" s="398"/>
       <c r="I142" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19890,14 +19890,14 @@
       <c r="B143" s="21">
         <v>108</v>
       </c>
-      <c r="C143" s="394" t="s">
+      <c r="C143" s="393" t="s">
         <v>22</v>
       </c>
-      <c r="D143" s="395"/>
-      <c r="E143" s="395"/>
-      <c r="F143" s="395"/>
-      <c r="G143" s="395"/>
-      <c r="H143" s="396"/>
+      <c r="D143" s="394"/>
+      <c r="E143" s="394"/>
+      <c r="F143" s="394"/>
+      <c r="G143" s="394"/>
+      <c r="H143" s="395"/>
       <c r="I143" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19917,12 +19917,12 @@
       <c r="D144" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E144" s="394" t="s">
+      <c r="E144" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F144" s="395"/>
-      <c r="G144" s="395"/>
-      <c r="H144" s="396"/>
+      <c r="F144" s="394"/>
+      <c r="G144" s="394"/>
+      <c r="H144" s="395"/>
       <c r="I144" s="32"/>
     </row>
     <row r="145" spans="1:10" ht="12" customHeight="1">
@@ -19941,11 +19941,11 @@
       <c r="E145" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F145" s="401" t="s">
+      <c r="F145" s="396" t="s">
         <v>131</v>
       </c>
-      <c r="G145" s="402"/>
-      <c r="H145" s="403"/>
+      <c r="G145" s="397"/>
+      <c r="H145" s="398"/>
       <c r="I145" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19967,11 +19967,11 @@
       <c r="E146" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F146" s="401" t="s">
+      <c r="F146" s="396" t="s">
         <v>132</v>
       </c>
-      <c r="G146" s="402"/>
-      <c r="H146" s="403"/>
+      <c r="G146" s="397"/>
+      <c r="H146" s="398"/>
       <c r="I146" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19993,11 +19993,11 @@
       <c r="E147" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F147" s="401" t="s">
+      <c r="F147" s="396" t="s">
         <v>64</v>
       </c>
-      <c r="G147" s="402"/>
-      <c r="H147" s="403"/>
+      <c r="G147" s="397"/>
+      <c r="H147" s="398"/>
       <c r="I147" s="32"/>
     </row>
     <row r="148" spans="1:10" ht="12" customHeight="1">
@@ -20016,11 +20016,11 @@
       <c r="E148" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F148" s="391" t="s">
+      <c r="F148" s="416" t="s">
         <v>133</v>
       </c>
-      <c r="G148" s="392"/>
-      <c r="H148" s="393"/>
+      <c r="G148" s="417"/>
+      <c r="H148" s="418"/>
       <c r="I148" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20043,11 +20043,11 @@
       <c r="E149" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F149" s="391" t="s">
+      <c r="F149" s="416" t="s">
         <v>134</v>
       </c>
-      <c r="G149" s="392"/>
-      <c r="H149" s="393"/>
+      <c r="G149" s="417"/>
+      <c r="H149" s="418"/>
       <c r="I149" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20070,11 +20070,11 @@
       <c r="E150" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F150" s="391" t="s">
+      <c r="F150" s="416" t="s">
         <v>135</v>
       </c>
-      <c r="G150" s="392"/>
-      <c r="H150" s="393"/>
+      <c r="G150" s="417"/>
+      <c r="H150" s="418"/>
       <c r="I150" s="32"/>
       <c r="J150" s="10"/>
     </row>
@@ -20094,11 +20094,11 @@
       <c r="E151" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F151" s="391" t="s">
+      <c r="F151" s="416" t="s">
         <v>136</v>
       </c>
-      <c r="G151" s="392"/>
-      <c r="H151" s="393"/>
+      <c r="G151" s="417"/>
+      <c r="H151" s="418"/>
       <c r="I151" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20115,16 +20115,16 @@
       <c r="B153" s="21">
         <v>114</v>
       </c>
-      <c r="C153" s="397" t="s">
+      <c r="C153" s="419" t="s">
         <v>137</v>
       </c>
-      <c r="D153" s="398"/>
-      <c r="E153" s="394" t="s">
+      <c r="D153" s="420"/>
+      <c r="E153" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F153" s="395"/>
-      <c r="G153" s="395"/>
-      <c r="H153" s="396"/>
+      <c r="F153" s="394"/>
+      <c r="G153" s="394"/>
+      <c r="H153" s="395"/>
       <c r="I153" s="32"/>
     </row>
     <row r="154" spans="1:10" ht="12" customHeight="1">
@@ -20134,16 +20134,16 @@
       <c r="B154" s="21">
         <v>115</v>
       </c>
-      <c r="C154" s="399"/>
-      <c r="D154" s="400"/>
+      <c r="C154" s="421"/>
+      <c r="D154" s="422"/>
       <c r="E154" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F154" s="404" t="s">
-        <v>44</v>
-      </c>
-      <c r="G154" s="405"/>
-      <c r="H154" s="406"/>
+      <c r="F154" s="444" t="s">
+        <v>44</v>
+      </c>
+      <c r="G154" s="445"/>
+      <c r="H154" s="446"/>
       <c r="I154" s="40"/>
     </row>
     <row r="155" spans="1:10" ht="12" customHeight="1">
@@ -20162,11 +20162,11 @@
       <c r="E155" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F155" s="391" t="s">
+      <c r="F155" s="416" t="s">
         <v>4</v>
       </c>
-      <c r="G155" s="392"/>
-      <c r="H155" s="393"/>
+      <c r="G155" s="417"/>
+      <c r="H155" s="418"/>
       <c r="I155" s="32"/>
       <c r="J155" s="10"/>
     </row>
@@ -20186,11 +20186,11 @@
       <c r="E156" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F156" s="391" t="s">
+      <c r="F156" s="416" t="s">
         <v>138</v>
       </c>
-      <c r="G156" s="392"/>
-      <c r="H156" s="393"/>
+      <c r="G156" s="417"/>
+      <c r="H156" s="418"/>
       <c r="I156" s="32"/>
       <c r="J156" s="10"/>
     </row>
@@ -20210,11 +20210,11 @@
       <c r="E157" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F157" s="391" t="s">
+      <c r="F157" s="416" t="s">
         <v>139</v>
       </c>
-      <c r="G157" s="392"/>
-      <c r="H157" s="393"/>
+      <c r="G157" s="417"/>
+      <c r="H157" s="418"/>
       <c r="I157" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20237,9 +20237,9 @@
       <c r="E158" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F158" s="391"/>
-      <c r="G158" s="392"/>
-      <c r="H158" s="393"/>
+      <c r="F158" s="416"/>
+      <c r="G158" s="417"/>
+      <c r="H158" s="418"/>
       <c r="I158" s="32"/>
       <c r="J158" s="10"/>
     </row>
@@ -20253,14 +20253,14 @@
       <c r="B160" s="21">
         <v>117</v>
       </c>
-      <c r="C160" s="394" t="s">
+      <c r="C160" s="393" t="s">
         <v>140</v>
       </c>
-      <c r="D160" s="395"/>
-      <c r="E160" s="395"/>
-      <c r="F160" s="395"/>
-      <c r="G160" s="395"/>
-      <c r="H160" s="396"/>
+      <c r="D160" s="394"/>
+      <c r="E160" s="394"/>
+      <c r="F160" s="394"/>
+      <c r="G160" s="394"/>
+      <c r="H160" s="395"/>
       <c r="I160" s="32"/>
     </row>
     <row r="161" spans="1:9" ht="12" customHeight="1">
@@ -20270,14 +20270,14 @@
       <c r="B161" s="21">
         <v>118</v>
       </c>
-      <c r="C161" s="394" t="s">
+      <c r="C161" s="393" t="s">
         <v>141</v>
       </c>
-      <c r="D161" s="395"/>
-      <c r="E161" s="395"/>
-      <c r="F161" s="395"/>
-      <c r="G161" s="395"/>
-      <c r="H161" s="396"/>
+      <c r="D161" s="394"/>
+      <c r="E161" s="394"/>
+      <c r="F161" s="394"/>
+      <c r="G161" s="394"/>
+      <c r="H161" s="395"/>
       <c r="I161" s="42" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -20290,14 +20290,14 @@
       <c r="B162" s="21">
         <v>119</v>
       </c>
-      <c r="C162" s="394" t="s">
+      <c r="C162" s="393" t="s">
         <v>142</v>
       </c>
-      <c r="D162" s="395"/>
-      <c r="E162" s="395"/>
-      <c r="F162" s="395"/>
-      <c r="G162" s="395"/>
-      <c r="H162" s="396"/>
+      <c r="D162" s="394"/>
+      <c r="E162" s="394"/>
+      <c r="F162" s="394"/>
+      <c r="G162" s="394"/>
+      <c r="H162" s="395"/>
       <c r="I162" s="32"/>
     </row>
     <row r="163" spans="1:9" ht="12" customHeight="1">
@@ -20307,14 +20307,14 @@
       <c r="B163" s="21">
         <v>120</v>
       </c>
-      <c r="C163" s="394" t="s">
+      <c r="C163" s="393" t="s">
         <v>143</v>
       </c>
-      <c r="D163" s="395"/>
-      <c r="E163" s="395"/>
-      <c r="F163" s="395"/>
-      <c r="G163" s="395"/>
-      <c r="H163" s="396"/>
+      <c r="D163" s="394"/>
+      <c r="E163" s="394"/>
+      <c r="F163" s="394"/>
+      <c r="G163" s="394"/>
+      <c r="H163" s="395"/>
       <c r="I163" s="32"/>
     </row>
     <row r="164" spans="1:9" ht="12" customHeight="1">
@@ -20324,14 +20324,14 @@
       <c r="B164" s="21">
         <v>121</v>
       </c>
-      <c r="C164" s="394" t="s">
+      <c r="C164" s="393" t="s">
         <v>144</v>
       </c>
-      <c r="D164" s="395"/>
-      <c r="E164" s="395"/>
-      <c r="F164" s="395"/>
-      <c r="G164" s="395"/>
-      <c r="H164" s="396"/>
+      <c r="D164" s="394"/>
+      <c r="E164" s="394"/>
+      <c r="F164" s="394"/>
+      <c r="G164" s="394"/>
+      <c r="H164" s="395"/>
       <c r="I164" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20344,16 +20344,16 @@
       <c r="B165" s="21">
         <v>122</v>
       </c>
-      <c r="C165" s="397" t="s">
+      <c r="C165" s="419" t="s">
         <v>145</v>
       </c>
-      <c r="D165" s="398"/>
-      <c r="E165" s="394" t="s">
+      <c r="D165" s="420"/>
+      <c r="E165" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F165" s="395"/>
-      <c r="G165" s="395"/>
-      <c r="H165" s="396"/>
+      <c r="F165" s="394"/>
+      <c r="G165" s="394"/>
+      <c r="H165" s="395"/>
       <c r="I165" s="32"/>
     </row>
     <row r="166" spans="1:9" ht="12" customHeight="1">
@@ -20363,16 +20363,16 @@
       <c r="B166" s="21">
         <v>123</v>
       </c>
-      <c r="C166" s="399"/>
-      <c r="D166" s="400"/>
+      <c r="C166" s="421"/>
+      <c r="D166" s="422"/>
       <c r="E166" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F166" s="401" t="s">
+      <c r="F166" s="396" t="s">
         <v>146</v>
       </c>
-      <c r="G166" s="402"/>
-      <c r="H166" s="403"/>
+      <c r="G166" s="397"/>
+      <c r="H166" s="398"/>
       <c r="I166" s="32"/>
     </row>
     <row r="167" spans="1:9" ht="12" customHeight="1">
@@ -20391,11 +20391,11 @@
       <c r="E167" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F167" s="401" t="s">
+      <c r="F167" s="396" t="s">
         <v>147</v>
       </c>
-      <c r="G167" s="402"/>
-      <c r="H167" s="403"/>
+      <c r="G167" s="397"/>
+      <c r="H167" s="398"/>
       <c r="I167" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20417,11 +20417,11 @@
       <c r="E168" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F168" s="401" t="s">
+      <c r="F168" s="396" t="s">
         <v>148</v>
       </c>
-      <c r="G168" s="402"/>
-      <c r="H168" s="403"/>
+      <c r="G168" s="397"/>
+      <c r="H168" s="398"/>
       <c r="I168" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20437,14 +20437,14 @@
       <c r="B170" s="21">
         <v>127</v>
       </c>
-      <c r="C170" s="394" t="s">
+      <c r="C170" s="393" t="s">
         <v>17</v>
       </c>
-      <c r="D170" s="395"/>
-      <c r="E170" s="395"/>
-      <c r="F170" s="395"/>
-      <c r="G170" s="395"/>
-      <c r="H170" s="396"/>
+      <c r="D170" s="394"/>
+      <c r="E170" s="394"/>
+      <c r="F170" s="394"/>
+      <c r="G170" s="394"/>
+      <c r="H170" s="395"/>
       <c r="I170" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20457,14 +20457,14 @@
       <c r="B171" s="21">
         <v>128</v>
       </c>
-      <c r="C171" s="394" t="s">
+      <c r="C171" s="393" t="s">
         <v>149</v>
       </c>
-      <c r="D171" s="395"/>
-      <c r="E171" s="395"/>
-      <c r="F171" s="395"/>
-      <c r="G171" s="395"/>
-      <c r="H171" s="396"/>
+      <c r="D171" s="394"/>
+      <c r="E171" s="394"/>
+      <c r="F171" s="394"/>
+      <c r="G171" s="394"/>
+      <c r="H171" s="395"/>
       <c r="I171" s="32"/>
     </row>
     <row r="172" spans="1:9" ht="12" customHeight="1">
@@ -20474,14 +20474,14 @@
       <c r="B172" s="21">
         <v>129</v>
       </c>
-      <c r="C172" s="394" t="s">
+      <c r="C172" s="393" t="s">
         <v>150</v>
       </c>
-      <c r="D172" s="395"/>
-      <c r="E172" s="395"/>
-      <c r="F172" s="395"/>
-      <c r="G172" s="395"/>
-      <c r="H172" s="396"/>
+      <c r="D172" s="394"/>
+      <c r="E172" s="394"/>
+      <c r="F172" s="394"/>
+      <c r="G172" s="394"/>
+      <c r="H172" s="395"/>
       <c r="I172" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20494,14 +20494,14 @@
       <c r="B173" s="21">
         <v>130</v>
       </c>
-      <c r="C173" s="394" t="s">
+      <c r="C173" s="393" t="s">
         <v>151</v>
       </c>
-      <c r="D173" s="395"/>
-      <c r="E173" s="395"/>
-      <c r="F173" s="395"/>
-      <c r="G173" s="395"/>
-      <c r="H173" s="396"/>
+      <c r="D173" s="394"/>
+      <c r="E173" s="394"/>
+      <c r="F173" s="394"/>
+      <c r="G173" s="394"/>
+      <c r="H173" s="395"/>
       <c r="I173" s="32"/>
     </row>
     <row r="174" spans="1:9" ht="12" customHeight="1">
@@ -20511,14 +20511,14 @@
       <c r="B174" s="21">
         <v>131</v>
       </c>
-      <c r="C174" s="394" t="s">
+      <c r="C174" s="393" t="s">
         <v>152</v>
       </c>
-      <c r="D174" s="395"/>
-      <c r="E174" s="395"/>
-      <c r="F174" s="395"/>
-      <c r="G174" s="395"/>
-      <c r="H174" s="396"/>
+      <c r="D174" s="394"/>
+      <c r="E174" s="394"/>
+      <c r="F174" s="394"/>
+      <c r="G174" s="394"/>
+      <c r="H174" s="395"/>
       <c r="I174" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20531,16 +20531,16 @@
       <c r="B175" s="21">
         <v>132</v>
       </c>
-      <c r="C175" s="397" t="s">
+      <c r="C175" s="419" t="s">
         <v>153</v>
       </c>
-      <c r="D175" s="398"/>
-      <c r="E175" s="394" t="s">
+      <c r="D175" s="420"/>
+      <c r="E175" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F175" s="395"/>
-      <c r="G175" s="395"/>
-      <c r="H175" s="396"/>
+      <c r="F175" s="394"/>
+      <c r="G175" s="394"/>
+      <c r="H175" s="395"/>
       <c r="I175" s="32"/>
     </row>
     <row r="176" spans="1:9" ht="12" customHeight="1">
@@ -20550,16 +20550,16 @@
       <c r="B176" s="21">
         <v>133</v>
       </c>
-      <c r="C176" s="399"/>
-      <c r="D176" s="400"/>
+      <c r="C176" s="421"/>
+      <c r="D176" s="422"/>
       <c r="E176" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F176" s="401" t="s">
+      <c r="F176" s="396" t="s">
         <v>128</v>
       </c>
-      <c r="G176" s="402"/>
-      <c r="H176" s="403"/>
+      <c r="G176" s="397"/>
+      <c r="H176" s="398"/>
       <c r="I176" s="32"/>
     </row>
     <row r="177" spans="1:14" ht="12" customHeight="1">
@@ -20569,16 +20569,16 @@
       <c r="B177" s="21">
         <v>134</v>
       </c>
-      <c r="C177" s="399"/>
-      <c r="D177" s="400"/>
+      <c r="C177" s="421"/>
+      <c r="D177" s="422"/>
       <c r="E177" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F177" s="401" t="s">
+      <c r="F177" s="396" t="s">
         <v>154</v>
       </c>
-      <c r="G177" s="402"/>
-      <c r="H177" s="403"/>
+      <c r="G177" s="397"/>
+      <c r="H177" s="398"/>
       <c r="I177" s="32"/>
     </row>
     <row r="178" spans="1:14" ht="12" customHeight="1">
@@ -20597,11 +20597,11 @@
       <c r="E178" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F178" s="401" t="s">
+      <c r="F178" s="396" t="s">
         <v>155</v>
       </c>
-      <c r="G178" s="402"/>
-      <c r="H178" s="403"/>
+      <c r="G178" s="397"/>
+      <c r="H178" s="398"/>
       <c r="I178" s="32"/>
     </row>
     <row r="179" spans="1:14" hidden="1">
@@ -20614,14 +20614,14 @@
       <c r="B180" s="21">
         <v>137</v>
       </c>
-      <c r="C180" s="394" t="s">
+      <c r="C180" s="393" t="s">
         <v>156</v>
       </c>
-      <c r="D180" s="395"/>
-      <c r="E180" s="395"/>
-      <c r="F180" s="395"/>
-      <c r="G180" s="395"/>
-      <c r="H180" s="396"/>
+      <c r="D180" s="394"/>
+      <c r="E180" s="394"/>
+      <c r="F180" s="394"/>
+      <c r="G180" s="394"/>
+      <c r="H180" s="395"/>
       <c r="I180" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20634,14 +20634,14 @@
       <c r="B181" s="21">
         <v>138</v>
       </c>
-      <c r="C181" s="394" t="s">
+      <c r="C181" s="393" t="s">
         <v>21</v>
       </c>
-      <c r="D181" s="395"/>
-      <c r="E181" s="395"/>
-      <c r="F181" s="395"/>
-      <c r="G181" s="395"/>
-      <c r="H181" s="396"/>
+      <c r="D181" s="394"/>
+      <c r="E181" s="394"/>
+      <c r="F181" s="394"/>
+      <c r="G181" s="394"/>
+      <c r="H181" s="395"/>
       <c r="I181" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20654,16 +20654,16 @@
       <c r="B182" s="21">
         <v>139</v>
       </c>
-      <c r="C182" s="397" t="s">
+      <c r="C182" s="419" t="s">
         <v>157</v>
       </c>
-      <c r="D182" s="398"/>
-      <c r="E182" s="394" t="s">
+      <c r="D182" s="420"/>
+      <c r="E182" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F182" s="395"/>
-      <c r="G182" s="395"/>
-      <c r="H182" s="396"/>
+      <c r="F182" s="394"/>
+      <c r="G182" s="394"/>
+      <c r="H182" s="395"/>
       <c r="I182" s="32"/>
     </row>
     <row r="183" spans="1:14" ht="12" customHeight="1">
@@ -20673,16 +20673,16 @@
       <c r="B183" s="21">
         <v>140</v>
       </c>
-      <c r="C183" s="399"/>
-      <c r="D183" s="400"/>
+      <c r="C183" s="421"/>
+      <c r="D183" s="422"/>
       <c r="E183" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F183" s="401" t="s">
-        <v>44</v>
-      </c>
-      <c r="G183" s="402"/>
-      <c r="H183" s="403"/>
+      <c r="F183" s="396" t="s">
+        <v>44</v>
+      </c>
+      <c r="G183" s="397"/>
+      <c r="H183" s="398"/>
       <c r="I183" s="32"/>
     </row>
     <row r="184" spans="1:14" hidden="1">
@@ -20695,16 +20695,16 @@
       <c r="B185" s="21">
         <v>142</v>
       </c>
-      <c r="C185" s="397" t="s">
+      <c r="C185" s="419" t="s">
         <v>158</v>
       </c>
-      <c r="D185" s="398"/>
-      <c r="E185" s="394" t="s">
+      <c r="D185" s="420"/>
+      <c r="E185" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F185" s="395"/>
-      <c r="G185" s="395"/>
-      <c r="H185" s="396"/>
+      <c r="F185" s="394"/>
+      <c r="G185" s="394"/>
+      <c r="H185" s="395"/>
       <c r="I185" s="32"/>
     </row>
     <row r="186" spans="1:14" ht="12" customHeight="1">
@@ -20714,16 +20714,16 @@
       <c r="B186" s="21">
         <v>143</v>
       </c>
-      <c r="C186" s="399"/>
-      <c r="D186" s="400"/>
+      <c r="C186" s="421"/>
+      <c r="D186" s="422"/>
       <c r="E186" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F186" s="401" t="s">
+      <c r="F186" s="396" t="s">
         <v>159</v>
       </c>
-      <c r="G186" s="402"/>
-      <c r="H186" s="403"/>
+      <c r="G186" s="397"/>
+      <c r="H186" s="398"/>
       <c r="I186" s="32"/>
     </row>
     <row r="187" spans="1:14" ht="12" customHeight="1">
@@ -20733,16 +20733,16 @@
       <c r="B187" s="21">
         <v>144</v>
       </c>
-      <c r="C187" s="399"/>
-      <c r="D187" s="400"/>
+      <c r="C187" s="421"/>
+      <c r="D187" s="422"/>
       <c r="E187" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F187" s="401" t="s">
+      <c r="F187" s="396" t="s">
         <v>160</v>
       </c>
-      <c r="G187" s="402"/>
-      <c r="H187" s="403"/>
+      <c r="G187" s="397"/>
+      <c r="H187" s="398"/>
       <c r="I187" s="32"/>
     </row>
     <row r="188" spans="1:14" ht="12" customHeight="1">
@@ -20761,11 +20761,11 @@
       <c r="E188" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F188" s="391" t="s">
+      <c r="F188" s="416" t="s">
         <v>161</v>
       </c>
-      <c r="G188" s="392"/>
-      <c r="H188" s="393"/>
+      <c r="G188" s="417"/>
+      <c r="H188" s="418"/>
       <c r="I188" s="32"/>
       <c r="J188" s="10"/>
     </row>
@@ -20785,11 +20785,11 @@
       <c r="E189" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F189" s="391" t="s">
+      <c r="F189" s="416" t="s">
         <v>162</v>
       </c>
-      <c r="G189" s="392"/>
-      <c r="H189" s="393"/>
+      <c r="G189" s="417"/>
+      <c r="H189" s="418"/>
       <c r="I189" s="32"/>
       <c r="J189" s="10"/>
     </row>
@@ -20809,11 +20809,11 @@
       <c r="E190" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="F190" s="391" t="s">
+      <c r="F190" s="416" t="s">
         <v>163</v>
       </c>
-      <c r="G190" s="392"/>
-      <c r="H190" s="393"/>
+      <c r="G190" s="417"/>
+      <c r="H190" s="418"/>
       <c r="I190" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -20876,6 +20876,161 @@
     </row>
   </sheetData>
   <mergeCells count="169">
+    <mergeCell ref="F188:H188"/>
+    <mergeCell ref="F189:H189"/>
+    <mergeCell ref="F190:H190"/>
+    <mergeCell ref="C180:H180"/>
+    <mergeCell ref="C181:H181"/>
+    <mergeCell ref="C182:D183"/>
+    <mergeCell ref="E182:H182"/>
+    <mergeCell ref="F183:H183"/>
+    <mergeCell ref="C185:D187"/>
+    <mergeCell ref="E185:H185"/>
+    <mergeCell ref="F186:H186"/>
+    <mergeCell ref="F187:H187"/>
+    <mergeCell ref="C174:H174"/>
+    <mergeCell ref="C175:D177"/>
+    <mergeCell ref="E175:H175"/>
+    <mergeCell ref="F176:H176"/>
+    <mergeCell ref="F177:H177"/>
+    <mergeCell ref="F178:H178"/>
+    <mergeCell ref="F167:H167"/>
+    <mergeCell ref="F168:H168"/>
+    <mergeCell ref="C170:H170"/>
+    <mergeCell ref="C171:H171"/>
+    <mergeCell ref="C172:H172"/>
+    <mergeCell ref="C173:H173"/>
+    <mergeCell ref="C162:H162"/>
+    <mergeCell ref="C163:H163"/>
+    <mergeCell ref="C164:H164"/>
+    <mergeCell ref="C165:D166"/>
+    <mergeCell ref="E165:H165"/>
+    <mergeCell ref="F166:H166"/>
+    <mergeCell ref="F155:H155"/>
+    <mergeCell ref="F156:H156"/>
+    <mergeCell ref="F157:H157"/>
+    <mergeCell ref="F158:H158"/>
+    <mergeCell ref="C160:H160"/>
+    <mergeCell ref="C161:H161"/>
+    <mergeCell ref="F149:H149"/>
+    <mergeCell ref="F150:H150"/>
+    <mergeCell ref="F151:H151"/>
+    <mergeCell ref="C153:D154"/>
+    <mergeCell ref="E153:H153"/>
+    <mergeCell ref="F154:H154"/>
+    <mergeCell ref="C143:H143"/>
+    <mergeCell ref="E144:H144"/>
+    <mergeCell ref="F145:H145"/>
+    <mergeCell ref="F146:H146"/>
+    <mergeCell ref="F147:H147"/>
+    <mergeCell ref="F148:H148"/>
+    <mergeCell ref="F137:H137"/>
+    <mergeCell ref="F138:H138"/>
+    <mergeCell ref="C140:D142"/>
+    <mergeCell ref="E140:H140"/>
+    <mergeCell ref="E141:E142"/>
+    <mergeCell ref="F141:H141"/>
+    <mergeCell ref="F142:H142"/>
+    <mergeCell ref="C132:D135"/>
+    <mergeCell ref="E132:H132"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="F134:H134"/>
+    <mergeCell ref="F135:H135"/>
+    <mergeCell ref="F136:H136"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="C127:D128"/>
+    <mergeCell ref="E127:H127"/>
+    <mergeCell ref="F128:H128"/>
+    <mergeCell ref="C130:H130"/>
+    <mergeCell ref="C131:H131"/>
+    <mergeCell ref="C120:D121"/>
+    <mergeCell ref="E120:H120"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="F122:H122"/>
+    <mergeCell ref="F123:H123"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="C115:H115"/>
+    <mergeCell ref="C116:D117"/>
+    <mergeCell ref="E116:H116"/>
+    <mergeCell ref="F117:H117"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="F110:H110"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="E112:H112"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="C104:H104"/>
+    <mergeCell ref="C105:H105"/>
+    <mergeCell ref="C106:D107"/>
+    <mergeCell ref="E106:H106"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="F97:H97"/>
+    <mergeCell ref="F98:H98"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="F88:H88"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="F90:H90"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:E94"/>
+    <mergeCell ref="F93:H93"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="F82:F84"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="G83:G84"/>
+    <mergeCell ref="F85:H85"/>
+    <mergeCell ref="F86:H86"/>
+    <mergeCell ref="F87:H87"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="C78:D79"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="F80:H80"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="C60:H60"/>
+    <mergeCell ref="C61:D63"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="C54:D57"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="F58:H58"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="C50:D51"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="C44:H44"/>
+    <mergeCell ref="C45:D49"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:D35"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:D39"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:H27"/>
     <mergeCell ref="E28:H28"/>
@@ -20890,161 +21045,6 @@
     <mergeCell ref="B20:B22"/>
     <mergeCell ref="C20:H22"/>
     <mergeCell ref="I20:I22"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:D35"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C37:D39"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="C44:H44"/>
-    <mergeCell ref="C45:D49"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="C54:D57"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="F58:H58"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="C50:D51"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="G74:H74"/>
-    <mergeCell ref="C78:D79"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="F80:H80"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="C60:H60"/>
-    <mergeCell ref="C61:D63"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="F88:H88"/>
-    <mergeCell ref="F89:H89"/>
-    <mergeCell ref="F90:H90"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:E94"/>
-    <mergeCell ref="F93:H93"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="F82:F84"/>
-    <mergeCell ref="G82:H82"/>
-    <mergeCell ref="G83:G84"/>
-    <mergeCell ref="F85:H85"/>
-    <mergeCell ref="F86:H86"/>
-    <mergeCell ref="F87:H87"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="C104:H104"/>
-    <mergeCell ref="C105:H105"/>
-    <mergeCell ref="C106:D107"/>
-    <mergeCell ref="E106:H106"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="F97:H97"/>
-    <mergeCell ref="F98:H98"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="F100:H100"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="C115:H115"/>
-    <mergeCell ref="C116:D117"/>
-    <mergeCell ref="E116:H116"/>
-    <mergeCell ref="F117:H117"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="F110:H110"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="E112:H112"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="C126:H126"/>
-    <mergeCell ref="C127:D128"/>
-    <mergeCell ref="E127:H127"/>
-    <mergeCell ref="F128:H128"/>
-    <mergeCell ref="C130:H130"/>
-    <mergeCell ref="C131:H131"/>
-    <mergeCell ref="C120:D121"/>
-    <mergeCell ref="E120:H120"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="F122:H122"/>
-    <mergeCell ref="F123:H123"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="F137:H137"/>
-    <mergeCell ref="F138:H138"/>
-    <mergeCell ref="C140:D142"/>
-    <mergeCell ref="E140:H140"/>
-    <mergeCell ref="E141:E142"/>
-    <mergeCell ref="F141:H141"/>
-    <mergeCell ref="F142:H142"/>
-    <mergeCell ref="C132:D135"/>
-    <mergeCell ref="E132:H132"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="F134:H134"/>
-    <mergeCell ref="F135:H135"/>
-    <mergeCell ref="F136:H136"/>
-    <mergeCell ref="F149:H149"/>
-    <mergeCell ref="F150:H150"/>
-    <mergeCell ref="F151:H151"/>
-    <mergeCell ref="C153:D154"/>
-    <mergeCell ref="E153:H153"/>
-    <mergeCell ref="F154:H154"/>
-    <mergeCell ref="C143:H143"/>
-    <mergeCell ref="E144:H144"/>
-    <mergeCell ref="F145:H145"/>
-    <mergeCell ref="F146:H146"/>
-    <mergeCell ref="F147:H147"/>
-    <mergeCell ref="F148:H148"/>
-    <mergeCell ref="C162:H162"/>
-    <mergeCell ref="C163:H163"/>
-    <mergeCell ref="C164:H164"/>
-    <mergeCell ref="C165:D166"/>
-    <mergeCell ref="E165:H165"/>
-    <mergeCell ref="F166:H166"/>
-    <mergeCell ref="F155:H155"/>
-    <mergeCell ref="F156:H156"/>
-    <mergeCell ref="F157:H157"/>
-    <mergeCell ref="F158:H158"/>
-    <mergeCell ref="C160:H160"/>
-    <mergeCell ref="C161:H161"/>
-    <mergeCell ref="C174:H174"/>
-    <mergeCell ref="C175:D177"/>
-    <mergeCell ref="E175:H175"/>
-    <mergeCell ref="F176:H176"/>
-    <mergeCell ref="F177:H177"/>
-    <mergeCell ref="F178:H178"/>
-    <mergeCell ref="F167:H167"/>
-    <mergeCell ref="F168:H168"/>
-    <mergeCell ref="C170:H170"/>
-    <mergeCell ref="C171:H171"/>
-    <mergeCell ref="C172:H172"/>
-    <mergeCell ref="C173:H173"/>
-    <mergeCell ref="F188:H188"/>
-    <mergeCell ref="F189:H189"/>
-    <mergeCell ref="F190:H190"/>
-    <mergeCell ref="C180:H180"/>
-    <mergeCell ref="C181:H181"/>
-    <mergeCell ref="C182:D183"/>
-    <mergeCell ref="E182:H182"/>
-    <mergeCell ref="F183:H183"/>
-    <mergeCell ref="C185:D187"/>
-    <mergeCell ref="E185:H185"/>
-    <mergeCell ref="F186:H186"/>
-    <mergeCell ref="F187:H187"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
@@ -21170,7 +21170,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="206" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C7" s="207" t="s">
         <v>269</v>
@@ -21196,7 +21196,7 @@
         <v>309</v>
       </c>
       <c r="J7" s="270" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30">
@@ -21204,7 +21204,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="206" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C8" s="207" t="s">
         <v>274</v>
@@ -21238,7 +21238,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="206" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C9" s="207" t="s">
         <v>274</v>
@@ -21264,7 +21264,7 @@
         <v>309</v>
       </c>
       <c r="J9" s="270" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -21300,7 +21300,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="206" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C11" s="207" t="s">
         <v>274</v>
@@ -21362,7 +21362,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="293" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C13" s="286" t="s">
         <v>270</v>
@@ -21385,7 +21385,7 @@
         <v>307</v>
       </c>
       <c r="I13" s="290" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="J13" s="291" t="s">
         <v>330</v>
@@ -21396,7 +21396,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="210" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C14" s="194" t="s">
         <v>272</v>
@@ -21430,7 +21430,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="210" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C15" s="213" t="s">
         <v>272</v>
@@ -21464,7 +21464,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="255" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C16" s="249"/>
       <c r="D16" s="251"/>
@@ -21478,7 +21478,7 @@
         <v>311</v>
       </c>
       <c r="J16" s="272" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="214" customFormat="1" ht="30">
@@ -21486,7 +21486,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="244" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C17" s="243" t="s">
         <v>271</v>
@@ -21518,7 +21518,7 @@
     <row r="18" spans="1:10" ht="42.75">
       <c r="A18" s="202"/>
       <c r="B18" s="203" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C18" s="204"/>
       <c r="D18" s="181">
@@ -21546,7 +21546,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="211" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C19" s="194" t="s">
         <v>272</v>
@@ -21572,7 +21572,7 @@
         <v>311</v>
       </c>
       <c r="J19" s="270" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="214" customFormat="1" ht="30">
@@ -21580,7 +21580,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="210" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C20" s="213" t="s">
         <v>272</v>
@@ -21614,7 +21614,7 @@
         <v>3</v>
       </c>
       <c r="B21" s="210" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C21" s="213" t="s">
         <v>272</v>
@@ -21640,7 +21640,7 @@
         <v>311</v>
       </c>
       <c r="J21" s="285" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="214" customFormat="1" ht="30">
@@ -21648,7 +21648,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="244" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C22" s="243" t="s">
         <v>272</v>
@@ -21710,7 +21710,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="248" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C24" s="243" t="s">
         <v>270</v>
@@ -21744,7 +21744,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="183" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C25" s="194" t="s">
         <v>272</v>
@@ -21778,7 +21778,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="183" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C26" s="194" t="s">
         <v>272</v>
@@ -21804,7 +21804,7 @@
         <v>311</v>
       </c>
       <c r="J26" s="270" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="214" customFormat="1" ht="30">
@@ -21812,7 +21812,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="248" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C27" s="243" t="s">
         <v>272</v>
@@ -21846,7 +21846,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="183" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C28" s="194" t="s">
         <v>272</v>
@@ -21872,7 +21872,7 @@
         <v>311</v>
       </c>
       <c r="J28" s="270" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="30">
@@ -21880,7 +21880,7 @@
         <v>6</v>
       </c>
       <c r="B29" s="183" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C29" s="194" t="s">
         <v>272</v>
@@ -21906,7 +21906,7 @@
         <v>311</v>
       </c>
       <c r="J29" s="270" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="30">
@@ -21914,7 +21914,7 @@
         <v>7</v>
       </c>
       <c r="B30" s="292" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C30" s="213" t="s">
         <v>271</v>
@@ -21948,7 +21948,7 @@
         <v>8</v>
       </c>
       <c r="B31" s="244" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C31" s="243" t="s">
         <v>271</v>
@@ -21982,7 +21982,7 @@
         <v>9</v>
       </c>
       <c r="B32" s="244" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C32" s="243" t="s">
         <v>271</v>
@@ -22016,7 +22016,7 @@
         <v>10</v>
       </c>
       <c r="B33" s="244" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C33" s="243" t="s">
         <v>271</v>
@@ -22078,7 +22078,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="183" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C35" s="192" t="s">
         <v>270</v>
@@ -22104,7 +22104,7 @@
         <v>311</v>
       </c>
       <c r="J35" s="270" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="30">
@@ -22162,7 +22162,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="176" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C38" s="193" t="s">
         <v>270</v>
@@ -22196,7 +22196,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="210" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C39" s="194" t="s">
         <v>272</v>
@@ -22222,7 +22222,7 @@
         <v>311</v>
       </c>
       <c r="J39" s="273" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="212" customFormat="1" ht="30">
@@ -22278,7 +22278,7 @@
         <v>5</v>
       </c>
       <c r="B42" s="210" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C42" s="213" t="s">
         <v>271</v>
@@ -22312,7 +22312,7 @@
         <v>6</v>
       </c>
       <c r="B43" s="176" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C43" s="194" t="s">
         <v>272</v>
@@ -22346,7 +22346,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="176" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C44" s="195" t="s">
         <v>271</v>
@@ -22580,7 +22580,7 @@
     <row r="52" spans="1:10" ht="45">
       <c r="A52" s="241"/>
       <c r="B52" s="217" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C52" s="186"/>
       <c r="D52" s="1"/>
@@ -29760,252 +29760,252 @@
     </row>
     <row r="10" spans="1:6" ht="51">
       <c r="A10" s="278" t="s">
+        <v>455</v>
+      </c>
+      <c r="B10" s="280" t="s">
         <v>345</v>
       </c>
-      <c r="B10" s="280" t="s">
+      <c r="C10" s="280" t="s">
         <v>346</v>
       </c>
-      <c r="C10" s="280" t="s">
+      <c r="D10" s="278" t="s">
         <v>347</v>
       </c>
-      <c r="D10" s="278" t="s">
+      <c r="E10" s="278" t="s">
         <v>348</v>
       </c>
-      <c r="E10" s="278" t="s">
+      <c r="F10" s="278" t="s">
         <v>349</v>
-      </c>
-      <c r="F10" s="278" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="76.5">
       <c r="A11" s="278" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B11" s="280" t="s">
+        <v>350</v>
+      </c>
+      <c r="C11" s="280" t="s">
         <v>351</v>
       </c>
-      <c r="C11" s="280" t="s">
+      <c r="D11" s="278" t="s">
         <v>352</v>
       </c>
-      <c r="D11" s="278" t="s">
+      <c r="E11" s="278" t="s">
         <v>353</v>
       </c>
-      <c r="E11" s="278" t="s">
+      <c r="F11" s="278" t="s">
         <v>354</v>
-      </c>
-      <c r="F11" s="278" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="51">
       <c r="A12" s="278" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B12" s="280" t="s">
+        <v>355</v>
+      </c>
+      <c r="C12" s="280" t="s">
         <v>356</v>
       </c>
-      <c r="C12" s="280" t="s">
+      <c r="D12" s="278" t="s">
         <v>357</v>
       </c>
-      <c r="D12" s="278" t="s">
+      <c r="E12" s="278" t="s">
         <v>358</v>
       </c>
-      <c r="E12" s="278" t="s">
+      <c r="F12" s="278" t="s">
         <v>359</v>
-      </c>
-      <c r="F12" s="278" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="63.75">
       <c r="A13" s="278" t="s">
+        <v>360</v>
+      </c>
+      <c r="B13" s="280" t="s">
         <v>361</v>
       </c>
-      <c r="B13" s="280" t="s">
+      <c r="C13" s="280" t="s">
         <v>362</v>
       </c>
-      <c r="C13" s="280" t="s">
+      <c r="D13" s="278" t="s">
         <v>363</v>
       </c>
-      <c r="D13" s="278" t="s">
+      <c r="E13" s="278" t="s">
         <v>364</v>
       </c>
-      <c r="E13" s="278" t="s">
+      <c r="F13" s="278" t="s">
         <v>365</v>
-      </c>
-      <c r="F13" s="278" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="51">
       <c r="A14" s="278" t="s">
+        <v>366</v>
+      </c>
+      <c r="B14" s="280" t="s">
         <v>367</v>
       </c>
-      <c r="B14" s="280" t="s">
+      <c r="C14" s="280" t="s">
         <v>368</v>
       </c>
-      <c r="C14" s="280" t="s">
+      <c r="D14" s="278" t="s">
         <v>369</v>
       </c>
-      <c r="D14" s="278" t="s">
+      <c r="E14" s="278" t="s">
         <v>370</v>
       </c>
-      <c r="E14" s="278" t="s">
+      <c r="F14" s="278" t="s">
         <v>371</v>
-      </c>
-      <c r="F14" s="278" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="51">
       <c r="A15" s="278" t="s">
+        <v>372</v>
+      </c>
+      <c r="B15" s="280" t="s">
         <v>373</v>
       </c>
-      <c r="B15" s="280" t="s">
+      <c r="C15" s="280" t="s">
         <v>374</v>
       </c>
-      <c r="C15" s="280" t="s">
+      <c r="D15" s="278" t="s">
         <v>375</v>
       </c>
-      <c r="D15" s="278" t="s">
+      <c r="E15" s="278" t="s">
         <v>376</v>
       </c>
-      <c r="E15" s="278" t="s">
+      <c r="F15" s="278" t="s">
         <v>377</v>
-      </c>
-      <c r="F15" s="278" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="51">
       <c r="A16" s="278" t="s">
+        <v>378</v>
+      </c>
+      <c r="B16" s="280" t="s">
+        <v>361</v>
+      </c>
+      <c r="C16" s="280" t="s">
         <v>379</v>
       </c>
-      <c r="B16" s="280" t="s">
-        <v>362</v>
-      </c>
-      <c r="C16" s="280" t="s">
+      <c r="D16" s="278" t="s">
         <v>380</v>
       </c>
-      <c r="D16" s="278" t="s">
+      <c r="E16" s="278" t="s">
         <v>381</v>
       </c>
-      <c r="E16" s="278" t="s">
+      <c r="F16" s="278" t="s">
         <v>382</v>
-      </c>
-      <c r="F16" s="278" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="25.5">
       <c r="A17" s="278" t="s">
+        <v>383</v>
+      </c>
+      <c r="B17" s="280" t="s">
+        <v>361</v>
+      </c>
+      <c r="C17" s="280" t="s">
+        <v>379</v>
+      </c>
+      <c r="D17" s="278" t="s">
         <v>384</v>
       </c>
-      <c r="B17" s="280" t="s">
-        <v>362</v>
-      </c>
-      <c r="C17" s="280" t="s">
-        <v>380</v>
-      </c>
-      <c r="D17" s="278" t="s">
+      <c r="E17" s="278" t="s">
+        <v>358</v>
+      </c>
+      <c r="F17" s="278" t="s">
         <v>385</v>
-      </c>
-      <c r="E17" s="278" t="s">
-        <v>359</v>
-      </c>
-      <c r="F17" s="278" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="38.25">
       <c r="A18" s="278" t="s">
+        <v>386</v>
+      </c>
+      <c r="B18" s="280" t="s">
+        <v>361</v>
+      </c>
+      <c r="C18" s="280" t="s">
+        <v>379</v>
+      </c>
+      <c r="D18" s="278" t="s">
         <v>387</v>
       </c>
-      <c r="B18" s="280" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" s="280" t="s">
-        <v>380</v>
-      </c>
-      <c r="D18" s="278" t="s">
+      <c r="E18" s="278" t="s">
         <v>388</v>
       </c>
-      <c r="E18" s="278" t="s">
+      <c r="F18" s="278" t="s">
         <v>389</v>
-      </c>
-      <c r="F18" s="278" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="38.25">
       <c r="A19" s="278" t="s">
+        <v>390</v>
+      </c>
+      <c r="B19" s="280" t="s">
+        <v>373</v>
+      </c>
+      <c r="C19" s="280" t="s">
+        <v>379</v>
+      </c>
+      <c r="D19" s="278" t="s">
         <v>391</v>
       </c>
-      <c r="B19" s="280" t="s">
-        <v>374</v>
-      </c>
-      <c r="C19" s="280" t="s">
-        <v>380</v>
-      </c>
-      <c r="D19" s="278" t="s">
+      <c r="E19" s="278" t="s">
         <v>392</v>
       </c>
-      <c r="E19" s="278" t="s">
+      <c r="F19" s="278" t="s">
         <v>393</v>
-      </c>
-      <c r="F19" s="278" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="51">
       <c r="A20" s="278" t="s">
+        <v>394</v>
+      </c>
+      <c r="B20" s="280" t="s">
+        <v>373</v>
+      </c>
+      <c r="C20" s="280" t="s">
+        <v>379</v>
+      </c>
+      <c r="D20" s="278" t="s">
         <v>395</v>
       </c>
-      <c r="B20" s="280" t="s">
-        <v>374</v>
-      </c>
-      <c r="C20" s="280" t="s">
-        <v>380</v>
-      </c>
-      <c r="D20" s="278" t="s">
+      <c r="E20" s="278" t="s">
         <v>396</v>
       </c>
-      <c r="E20" s="278" t="s">
+      <c r="F20" s="278" t="s">
         <v>397</v>
-      </c>
-      <c r="F20" s="278" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="25.5">
       <c r="A21" s="278" t="s">
+        <v>398</v>
+      </c>
+      <c r="B21" s="280" t="s">
+        <v>373</v>
+      </c>
+      <c r="C21" s="280" t="s">
+        <v>379</v>
+      </c>
+      <c r="D21" s="278" t="s">
         <v>399</v>
       </c>
-      <c r="B21" s="280" t="s">
-        <v>374</v>
-      </c>
-      <c r="C21" s="280" t="s">
-        <v>380</v>
-      </c>
-      <c r="D21" s="278" t="s">
+      <c r="E21" s="278" t="s">
         <v>400</v>
       </c>
-      <c r="E21" s="278" t="s">
+      <c r="F21" s="278" t="s">
         <v>401</v>
-      </c>
-      <c r="F21" s="278" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="276" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="27" customHeight="1">
       <c r="A24" s="448" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B24" s="448"/>
       <c r="C24" s="448"/>
@@ -30015,7 +30015,7 @@
     </row>
     <row r="25" spans="1:6" ht="27" customHeight="1">
       <c r="A25" s="448" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B25" s="448"/>
       <c r="C25" s="448"/>
@@ -30025,7 +30025,7 @@
     </row>
     <row r="26" spans="1:6" ht="27" customHeight="1">
       <c r="A26" s="448" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B26" s="448"/>
       <c r="C26" s="448"/>
@@ -30035,7 +30035,7 @@
     </row>
     <row r="27" spans="1:6" ht="27" customHeight="1">
       <c r="A27" s="448" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B27" s="448"/>
       <c r="C27" s="448"/>
@@ -30045,7 +30045,7 @@
     </row>
     <row r="28" spans="1:6" ht="27" customHeight="1">
       <c r="A28" s="448" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B28" s="448"/>
       <c r="C28" s="448"/>
@@ -30055,7 +30055,7 @@
     </row>
     <row r="29" spans="1:6" ht="27" customHeight="1">
       <c r="A29" s="448" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B29" s="448"/>
       <c r="C29" s="448"/>
@@ -30065,7 +30065,7 @@
     </row>
     <row r="30" spans="1:6" ht="27" customHeight="1">
       <c r="A30" s="448" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B30" s="448"/>
       <c r="C30" s="448"/>
@@ -30075,7 +30075,7 @@
     </row>
     <row r="31" spans="1:6" ht="27" customHeight="1">
       <c r="A31" s="448" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B31" s="448"/>
       <c r="C31" s="448"/>
@@ -30085,6 +30085,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="A26:F26"/>
@@ -30092,12 +30098,6 @@
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>

--- a/TAZA/_документы/Штатка Фонда и проектного офиса.xlsx
+++ b/TAZA/_документы/Штатка Фонда и проектного офиса.xlsx
@@ -301,7 +301,7 @@
     <definedName name="nfn">#REF!</definedName>
     <definedName name="Print_Area" localSheetId="5">'выбытие денег '!$A$1:$N$195</definedName>
     <definedName name="Print_Area" localSheetId="4">нак.расх.!$A$1:$L$95</definedName>
-    <definedName name="Print_Area" localSheetId="6">ФОТ!$A$1:$J$55</definedName>
+    <definedName name="Print_Area" localSheetId="6">ФОТ!$A$1:$J$56</definedName>
     <definedName name="Profit_Loss" localSheetId="2">#REF!</definedName>
     <definedName name="Profit_Loss" localSheetId="5">#REF!</definedName>
     <definedName name="Profit_Loss" localSheetId="3">#REF!</definedName>
@@ -590,8 +590,8 @@
     <definedName name="пппп">#REF!</definedName>
     <definedName name="прейс">#REF!</definedName>
     <definedName name="прейск">#REF!</definedName>
-    <definedName name="принтареа2" localSheetId="6">ФОТ!$A$1:$G$54</definedName>
-    <definedName name="принтареа3" localSheetId="6">ФОТ!$A$1:$G$55</definedName>
+    <definedName name="принтареа2" localSheetId="6">ФОТ!$A$1:$G$55</definedName>
+    <definedName name="принтареа3" localSheetId="6">ФОТ!$A$1:$G$56</definedName>
     <definedName name="про" localSheetId="2">#REF!</definedName>
     <definedName name="про" localSheetId="5">#REF!</definedName>
     <definedName name="про" localSheetId="3">#REF!</definedName>
@@ -772,7 +772,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="459">
   <si>
     <t>№ п/п</t>
   </si>
@@ -2406,12 +2406,6 @@
     <t>Стратегия и научное направление Фонда, аналитические и экспертные материалы, международные партнёры; поручения ГИД</t>
   </si>
   <si>
-    <t>Главный исполнительный директор Фонда, Руководитель Проектного офиса для Центральной Азии / Қаражан</t>
-  </si>
-  <si>
-    <t>Общее руководство Фондом и проектом, представительство, утверждение планов, бюджета и отчётов; руководство Проектным офисом для Центральной Азии</t>
-  </si>
-  <si>
     <t>Молодёжь, волонтёры, НПО, школы и вузы; экспертиза молодёжных и общественных проектов</t>
   </si>
   <si>
@@ -2431,6 +2425,21 @@
   </si>
   <si>
     <t>ГИД, заместители ГИД, руководитель проектного офиса «Таза Қазақстан», финансовый директор</t>
+  </si>
+  <si>
+    <t>Главный исполнительный директор Фонда / Қаражан</t>
+  </si>
+  <si>
+    <t>Общее руководство Фондом и проектом, представительство, утверждение планов, бюджета и отчётов; до назначения Руководителя Проектного офиса для Центральной Азии исполняет его обязанности без оклада и доплаты</t>
+  </si>
+  <si>
+    <t>Руководитель Проектного офиса для Центральной Азии / вакансия (обязанности исполняет ГИД)</t>
+  </si>
+  <si>
+    <t>вакансия</t>
+  </si>
+  <si>
+    <t>Руководство Проектным офисом для Центральной Азии; до назначения Руководителя обязанности исполняет ГИД без оклада и доплаты</t>
   </si>
 </sst>
 </file>
@@ -21056,7 +21065,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J935"/>
+  <dimension ref="A1:J936"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -21165,12 +21174,12 @@
       <c r="I6" s="181"/>
       <c r="J6" s="181"/>
     </row>
-    <row r="7" spans="1:10" ht="45">
+    <row r="7" spans="1:10" ht="60">
       <c r="A7" s="205">
         <v>1</v>
       </c>
       <c r="B7" s="206" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C7" s="207" t="s">
         <v>269</v>
@@ -21196,7 +21205,7 @@
         <v>309</v>
       </c>
       <c r="J7" s="270" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30">
@@ -21522,20 +21531,20 @@
       </c>
       <c r="C18" s="204"/>
       <c r="D18" s="181">
-        <f>SUM(D19:D22)</f>
-        <v>4</v>
+        <f>SUM(D19:D23)</f>
+        <v>5</v>
       </c>
       <c r="E18" s="221">
-        <f>SUM(E19:E22)</f>
-        <v>3400000</v>
+        <f>SUM(E19:E23)</f>
+        <v>4800000</v>
       </c>
       <c r="F18" s="222">
-        <f>SUM(F19:F22)</f>
-        <v>2744700</v>
+        <f>SUM(F19:F23)</f>
+        <v>3866475</v>
       </c>
       <c r="G18" s="181">
-        <f>SUM(G19:G22)</f>
-        <v>40800</v>
+        <f>SUM(G19:G23)</f>
+        <v>57600</v>
       </c>
       <c r="H18" s="181"/>
       <c r="I18" s="181"/>
@@ -21546,67 +21555,67 @@
         <v>1</v>
       </c>
       <c r="B19" s="211" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C19" s="194" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D19" s="177">
         <v>1</v>
       </c>
       <c r="E19" s="223">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="F19" s="224">
         <f>IF(E19&gt;0,E19-MIN(E19,4250000)*10%-MIN(E19,1700000)*2%-MAX(0,E19-MIN(E19,4250000)*10%-MIN(E19,1700000)*2%-129750)*10%,0)</f>
-        <v>804975</v>
+        <v>1121775</v>
       </c>
       <c r="G19" s="177">
         <f>D19*E19*12/1000</f>
-        <v>12000</v>
+        <v>16800</v>
       </c>
       <c r="H19" s="177" t="s">
         <v>307</v>
       </c>
       <c r="I19" s="264" t="s">
+        <v>457</v>
+      </c>
+      <c r="J19" s="270" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="45">
+      <c r="A20" s="196">
+        <v>2</v>
+      </c>
+      <c r="B20" s="211" t="s">
+        <v>448</v>
+      </c>
+      <c r="C20" s="194" t="s">
+        <v>272</v>
+      </c>
+      <c r="D20" s="177">
+        <v>1</v>
+      </c>
+      <c r="E20" s="223">
+        <v>1000000</v>
+      </c>
+      <c r="F20" s="224">
+        <f>IF(E20&gt;0,E20-MIN(E20,4250000)*10%-MIN(E20,1700000)*2%-MAX(0,E20-MIN(E20,4250000)*10%-MIN(E20,1700000)*2%-129750)*10%,0)</f>
+        <v>804975</v>
+      </c>
+      <c r="G20" s="177">
+        <f>D20*E20*12/1000</f>
+        <v>12000</v>
+      </c>
+      <c r="H20" s="177" t="s">
+        <v>307</v>
+      </c>
+      <c r="I20" s="264" t="s">
         <v>311</v>
       </c>
-      <c r="J19" s="270" t="s">
+      <c r="J20" s="270" t="s">
         <v>411</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" s="214" customFormat="1" ht="30">
-      <c r="A20" s="213">
-        <v>2</v>
-      </c>
-      <c r="B20" s="210" t="s">
-        <v>451</v>
-      </c>
-      <c r="C20" s="213" t="s">
-        <v>272</v>
-      </c>
-      <c r="D20" s="281">
-        <v>1</v>
-      </c>
-      <c r="E20" s="282">
-        <v>800000</v>
-      </c>
-      <c r="F20" s="283">
-        <f>IF(E20&gt;0,E20-MIN(E20,4250000)*10%-MIN(E20,1700000)*2%-MAX(0,E20-MIN(E20,4250000)*10%-MIN(E20,1700000)*2%-129750)*10%,0)</f>
-        <v>646575</v>
-      </c>
-      <c r="G20" s="281">
-        <f>D20*E20*12/1000</f>
-        <v>9600</v>
-      </c>
-      <c r="H20" s="281" t="s">
-        <v>307</v>
-      </c>
-      <c r="I20" s="284" t="s">
-        <v>311</v>
-      </c>
-      <c r="J20" s="285" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="214" customFormat="1" ht="30">
@@ -21614,7 +21623,7 @@
         <v>3</v>
       </c>
       <c r="B21" s="210" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C21" s="213" t="s">
         <v>272</v>
@@ -21640,247 +21649,247 @@
         <v>311</v>
       </c>
       <c r="J21" s="285" t="s">
-        <v>449</v>
+        <v>326</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="214" customFormat="1" ht="30">
-      <c r="A22" s="243">
+      <c r="A22" s="213">
         <v>4</v>
       </c>
-      <c r="B22" s="244" t="s">
-        <v>453</v>
-      </c>
-      <c r="C22" s="243" t="s">
+      <c r="B22" s="210" t="s">
+        <v>450</v>
+      </c>
+      <c r="C22" s="213" t="s">
         <v>272</v>
       </c>
-      <c r="D22" s="245">
+      <c r="D22" s="281">
         <v>1</v>
       </c>
-      <c r="E22" s="246">
+      <c r="E22" s="282">
         <v>800000</v>
       </c>
-      <c r="F22" s="247">
+      <c r="F22" s="283">
         <f>IF(E22&gt;0,E22-MIN(E22,4250000)*10%-MIN(E22,1700000)*2%-MAX(0,E22-MIN(E22,4250000)*10%-MIN(E22,1700000)*2%-129750)*10%,0)</f>
         <v>646575</v>
       </c>
-      <c r="G22" s="245">
+      <c r="G22" s="281">
         <f>D22*E22*12/1000</f>
         <v>9600</v>
       </c>
-      <c r="H22" s="245" t="s">
+      <c r="H22" s="281" t="s">
         <v>307</v>
       </c>
-      <c r="I22" s="266" t="s">
+      <c r="I22" s="284" t="s">
+        <v>311</v>
+      </c>
+      <c r="J22" s="285" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" s="214" customFormat="1" ht="30">
+      <c r="A23" s="243">
+        <v>5</v>
+      </c>
+      <c r="B23" s="244" t="s">
+        <v>451</v>
+      </c>
+      <c r="C23" s="243" t="s">
+        <v>272</v>
+      </c>
+      <c r="D23" s="245">
+        <v>1</v>
+      </c>
+      <c r="E23" s="246">
+        <v>800000</v>
+      </c>
+      <c r="F23" s="247">
+        <f>IF(E23&gt;0,E23-MIN(E23,4250000)*10%-MIN(E23,1700000)*2%-MAX(0,E23-MIN(E23,4250000)*10%-MIN(E23,1700000)*2%-129750)*10%,0)</f>
+        <v>646575</v>
+      </c>
+      <c r="G23" s="245">
+        <f>D23*E23*12/1000</f>
+        <v>9600</v>
+      </c>
+      <c r="H23" s="245" t="s">
+        <v>307</v>
+      </c>
+      <c r="I23" s="266" t="s">
         <v>320</v>
       </c>
-      <c r="J22" s="271" t="s">
+      <c r="J23" s="271" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="28.5">
-      <c r="A23" s="171" t="s">
+    <row r="24" spans="1:10" ht="28.5">
+      <c r="A24" s="171" t="s">
         <v>280</v>
       </c>
-      <c r="B23" s="180" t="s">
+      <c r="B24" s="180" t="s">
         <v>277</v>
       </c>
-      <c r="C23" s="179"/>
-      <c r="D23" s="181">
-        <f>SUM(D24:D33)</f>
+      <c r="C24" s="179"/>
+      <c r="D24" s="181">
+        <f>SUM(D25:D34)</f>
         <v>10</v>
       </c>
-      <c r="E23" s="221">
-        <f t="shared" ref="E23:G23" si="3">SUM(E24:E33)</f>
+      <c r="E24" s="221">
+        <f t="shared" ref="E24:G24" si="3">SUM(E25:E34)</f>
         <v>9200000</v>
       </c>
-      <c r="F23" s="222">
-        <f>SUM(F24:F33)</f>
+      <c r="F24" s="222">
+        <f>SUM(F25:F34)</f>
         <v>7416150</v>
       </c>
-      <c r="G23" s="181">
+      <c r="G24" s="181">
         <f t="shared" si="3"/>
         <v>110400</v>
       </c>
-      <c r="H23" s="181"/>
-      <c r="I23" s="181"/>
-      <c r="J23" s="267"/>
-    </row>
-    <row r="24" spans="1:10" s="214" customFormat="1" ht="30">
-      <c r="A24" s="243">
+      <c r="H24" s="181"/>
+      <c r="I24" s="181"/>
+      <c r="J24" s="267"/>
+    </row>
+    <row r="25" spans="1:10" s="214" customFormat="1" ht="30">
+      <c r="A25" s="243">
         <v>1</v>
       </c>
-      <c r="B24" s="248" t="s">
+      <c r="B25" s="248" t="s">
         <v>434</v>
       </c>
-      <c r="C24" s="243" t="s">
+      <c r="C25" s="243" t="s">
         <v>270</v>
       </c>
-      <c r="D24" s="245">
+      <c r="D25" s="245">
         <v>1</v>
       </c>
-      <c r="E24" s="246">
+      <c r="E25" s="246">
         <v>1300000</v>
       </c>
-      <c r="F24" s="247">
-        <f t="shared" ref="F24:F33" si="4">IF(E24&gt;0,E24-MIN(E24,4250000)*10%-MIN(E24,1700000)*2%-MAX(0,E24-MIN(E24,4250000)*10%-MIN(E24,1700000)*2%-129750)*10%,0)</f>
+      <c r="F25" s="247">
+        <f t="shared" ref="F25:F34" si="4">IF(E25&gt;0,E25-MIN(E25,4250000)*10%-MIN(E25,1700000)*2%-MAX(0,E25-MIN(E25,4250000)*10%-MIN(E25,1700000)*2%-129750)*10%,0)</f>
         <v>1042575</v>
       </c>
-      <c r="G24" s="245">
-        <f t="shared" ref="G24:G33" si="5">D24*E24*12/1000</f>
+      <c r="G25" s="245">
+        <f t="shared" ref="G25:G34" si="5">D25*E25*12/1000</f>
         <v>15600</v>
       </c>
-      <c r="H24" s="245" t="s">
+      <c r="H25" s="245" t="s">
         <v>307</v>
       </c>
-      <c r="I24" s="266" t="s">
+      <c r="I25" s="266" t="s">
         <v>320</v>
       </c>
-      <c r="J24" s="271" t="s">
+      <c r="J25" s="271" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="30">
-      <c r="A25" s="182">
+    <row r="26" spans="1:10" ht="30">
+      <c r="A26" s="182">
         <v>2</v>
       </c>
-      <c r="B25" s="183" t="s">
+      <c r="B26" s="183" t="s">
         <v>444</v>
       </c>
-      <c r="C25" s="194" t="s">
+      <c r="C26" s="194" t="s">
         <v>272</v>
       </c>
-      <c r="D25" s="177">
+      <c r="D26" s="177">
         <v>1</v>
       </c>
-      <c r="E25" s="223">
+      <c r="E26" s="223">
         <v>1100000</v>
       </c>
-      <c r="F25" s="224">
+      <c r="F26" s="224">
         <f t="shared" si="4"/>
         <v>884175</v>
       </c>
-      <c r="G25" s="177">
+      <c r="G26" s="177">
         <f t="shared" si="5"/>
         <v>13200</v>
       </c>
-      <c r="H25" s="177" t="s">
+      <c r="H26" s="177" t="s">
         <v>307</v>
       </c>
-      <c r="I25" s="264" t="s">
+      <c r="I26" s="264" t="s">
         <v>311</v>
       </c>
-      <c r="J25" s="270" t="s">
+      <c r="J26" s="270" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="30">
-      <c r="A26" s="213">
+    <row r="27" spans="1:10" ht="30">
+      <c r="A27" s="213">
         <v>3</v>
       </c>
-      <c r="B26" s="183" t="s">
+      <c r="B27" s="183" t="s">
         <v>424</v>
       </c>
-      <c r="C26" s="194" t="s">
+      <c r="C27" s="194" t="s">
         <v>272</v>
       </c>
-      <c r="D26" s="177">
+      <c r="D27" s="177">
         <v>1</v>
       </c>
-      <c r="E26" s="223">
+      <c r="E27" s="223">
         <v>1000000</v>
       </c>
-      <c r="F26" s="224">
+      <c r="F27" s="224">
         <f t="shared" si="4"/>
         <v>804975</v>
       </c>
-      <c r="G26" s="177">
+      <c r="G27" s="177">
         <f t="shared" si="5"/>
         <v>12000</v>
       </c>
-      <c r="H26" s="177" t="s">
+      <c r="H27" s="177" t="s">
         <v>307</v>
       </c>
-      <c r="I26" s="264" t="s">
+      <c r="I27" s="264" t="s">
         <v>311</v>
       </c>
-      <c r="J26" s="270" t="s">
+      <c r="J27" s="270" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="214" customFormat="1" ht="30">
-      <c r="A27" s="243">
+    <row r="28" spans="1:10" s="214" customFormat="1" ht="30">
+      <c r="A28" s="243">
         <v>4</v>
       </c>
-      <c r="B27" s="248" t="s">
+      <c r="B28" s="248" t="s">
         <v>435</v>
       </c>
-      <c r="C27" s="243" t="s">
+      <c r="C28" s="243" t="s">
         <v>272</v>
       </c>
-      <c r="D27" s="245">
+      <c r="D28" s="245">
         <v>1</v>
       </c>
-      <c r="E27" s="246">
+      <c r="E28" s="246">
         <v>1000000</v>
       </c>
-      <c r="F27" s="247">
+      <c r="F28" s="247">
         <f t="shared" si="4"/>
         <v>804975</v>
       </c>
-      <c r="G27" s="245">
+      <c r="G28" s="245">
         <f t="shared" si="5"/>
         <v>12000</v>
       </c>
-      <c r="H27" s="245" t="s">
+      <c r="H28" s="245" t="s">
         <v>307</v>
       </c>
-      <c r="I27" s="266" t="s">
+      <c r="I28" s="266" t="s">
         <v>320</v>
       </c>
-      <c r="J27" s="271" t="s">
+      <c r="J28" s="271" t="s">
         <v>322</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="30">
-      <c r="A28" s="182">
-        <v>5</v>
-      </c>
-      <c r="B28" s="183" t="s">
-        <v>422</v>
-      </c>
-      <c r="C28" s="194" t="s">
-        <v>272</v>
-      </c>
-      <c r="D28" s="177">
-        <v>1</v>
-      </c>
-      <c r="E28" s="223">
-        <v>1000000</v>
-      </c>
-      <c r="F28" s="224">
-        <f t="shared" si="4"/>
-        <v>804975</v>
-      </c>
-      <c r="G28" s="177">
-        <f t="shared" si="5"/>
-        <v>12000</v>
-      </c>
-      <c r="H28" s="177" t="s">
-        <v>307</v>
-      </c>
-      <c r="I28" s="264" t="s">
-        <v>311</v>
-      </c>
-      <c r="J28" s="270" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="30">
       <c r="A29" s="182">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B29" s="183" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C29" s="194" t="s">
         <v>272</v>
@@ -21906,83 +21915,83 @@
         <v>311</v>
       </c>
       <c r="J29" s="270" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="30">
+      <c r="A30" s="182">
+        <v>6</v>
+      </c>
+      <c r="B30" s="183" t="s">
+        <v>423</v>
+      </c>
+      <c r="C30" s="194" t="s">
+        <v>272</v>
+      </c>
+      <c r="D30" s="177">
+        <v>1</v>
+      </c>
+      <c r="E30" s="223">
+        <v>1000000</v>
+      </c>
+      <c r="F30" s="224">
+        <f t="shared" si="4"/>
+        <v>804975</v>
+      </c>
+      <c r="G30" s="177">
+        <f t="shared" si="5"/>
+        <v>12000</v>
+      </c>
+      <c r="H30" s="177" t="s">
+        <v>307</v>
+      </c>
+      <c r="I30" s="264" t="s">
+        <v>311</v>
+      </c>
+      <c r="J30" s="270" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="30">
-      <c r="A30" s="213">
+    <row r="31" spans="1:10" ht="30">
+      <c r="A31" s="213">
         <v>7</v>
       </c>
-      <c r="B30" s="292" t="s">
+      <c r="B31" s="292" t="s">
         <v>436</v>
       </c>
-      <c r="C30" s="213" t="s">
+      <c r="C31" s="213" t="s">
         <v>271</v>
       </c>
-      <c r="D30" s="281">
+      <c r="D31" s="281">
         <v>1</v>
       </c>
-      <c r="E30" s="282">
+      <c r="E31" s="282">
         <v>700000</v>
       </c>
-      <c r="F30" s="283">
+      <c r="F31" s="283">
         <f t="shared" si="4"/>
         <v>567375</v>
       </c>
-      <c r="G30" s="281">
+      <c r="G31" s="281">
         <f t="shared" si="5"/>
         <v>8400</v>
       </c>
-      <c r="H30" s="281" t="s">
+      <c r="H31" s="281" t="s">
         <v>307</v>
       </c>
-      <c r="I30" s="284" t="s">
+      <c r="I31" s="284" t="s">
         <v>311</v>
       </c>
-      <c r="J30" s="285" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" s="214" customFormat="1" ht="30">
-      <c r="A31" s="243">
-        <v>8</v>
-      </c>
-      <c r="B31" s="244" t="s">
-        <v>437</v>
-      </c>
-      <c r="C31" s="243" t="s">
-        <v>271</v>
-      </c>
-      <c r="D31" s="245">
-        <v>1</v>
-      </c>
-      <c r="E31" s="246">
-        <v>700000</v>
-      </c>
-      <c r="F31" s="247">
-        <f t="shared" si="4"/>
-        <v>567375</v>
-      </c>
-      <c r="G31" s="245">
-        <f t="shared" si="5"/>
-        <v>8400</v>
-      </c>
-      <c r="H31" s="245" t="s">
-        <v>307</v>
-      </c>
-      <c r="I31" s="266" t="s">
-        <v>320</v>
-      </c>
-      <c r="J31" s="271" t="s">
+      <c r="J31" s="285" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="214" customFormat="1" ht="30">
       <c r="A32" s="243">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B32" s="244" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C32" s="243" t="s">
         <v>271</v>
@@ -22008,15 +22017,15 @@
         <v>320</v>
       </c>
       <c r="J32" s="271" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="214" customFormat="1" ht="30">
       <c r="A33" s="243">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B33" s="244" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C33" s="243" t="s">
         <v>271</v>
@@ -22042,178 +22051,178 @@
         <v>320</v>
       </c>
       <c r="J33" s="271" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" s="214" customFormat="1" ht="30">
+      <c r="A34" s="243">
+        <v>10</v>
+      </c>
+      <c r="B34" s="244" t="s">
+        <v>439</v>
+      </c>
+      <c r="C34" s="243" t="s">
+        <v>271</v>
+      </c>
+      <c r="D34" s="245">
+        <v>1</v>
+      </c>
+      <c r="E34" s="246">
+        <v>700000</v>
+      </c>
+      <c r="F34" s="247">
+        <f t="shared" si="4"/>
+        <v>567375</v>
+      </c>
+      <c r="G34" s="245">
+        <f t="shared" si="5"/>
+        <v>8400</v>
+      </c>
+      <c r="H34" s="245" t="s">
+        <v>307</v>
+      </c>
+      <c r="I34" s="266" t="s">
+        <v>320</v>
+      </c>
+      <c r="J34" s="271" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="166" customFormat="1">
-      <c r="A34" s="171" t="s">
+    <row r="35" spans="1:10" s="166" customFormat="1">
+      <c r="A35" s="171" t="s">
         <v>281</v>
       </c>
-      <c r="B34" s="184" t="s">
+      <c r="B35" s="184" t="s">
         <v>278</v>
       </c>
-      <c r="C34" s="187"/>
-      <c r="D34" s="185">
-        <f t="shared" ref="D34:G34" si="6">SUM(D35:D36)</f>
+      <c r="C35" s="187"/>
+      <c r="D35" s="185">
+        <f t="shared" ref="D35:G35" si="6">SUM(D36:D37)</f>
         <v>1</v>
       </c>
-      <c r="E34" s="225">
+      <c r="E35" s="225">
         <f t="shared" si="6"/>
         <v>1300000</v>
       </c>
-      <c r="F34" s="226">
+      <c r="F35" s="226">
         <f t="shared" si="6"/>
         <v>1042575</v>
       </c>
-      <c r="G34" s="185">
+      <c r="G35" s="185">
         <f t="shared" si="6"/>
         <v>15600</v>
       </c>
-      <c r="H34" s="185"/>
-      <c r="I34" s="185"/>
-      <c r="J34" s="268"/>
-    </row>
-    <row r="35" spans="1:10" ht="30">
-      <c r="A35" s="182">
+      <c r="H35" s="185"/>
+      <c r="I35" s="185"/>
+      <c r="J35" s="268"/>
+    </row>
+    <row r="36" spans="1:10" ht="30">
+      <c r="A36" s="182">
         <v>1</v>
       </c>
-      <c r="B35" s="183" t="s">
+      <c r="B36" s="183" t="s">
         <v>421</v>
       </c>
-      <c r="C35" s="192" t="s">
+      <c r="C36" s="192" t="s">
         <v>270</v>
       </c>
-      <c r="D35" s="177">
+      <c r="D36" s="177">
         <v>1</v>
       </c>
-      <c r="E35" s="223">
+      <c r="E36" s="223">
         <v>1300000</v>
       </c>
-      <c r="F35" s="224">
-        <f>IF(E35&gt;0,E35-MIN(E35,4250000)*10%-MIN(E35,1700000)*2%-MAX(0,E35-MIN(E35,4250000)*10%-MIN(E35,1700000)*2%-129750)*10%,0)</f>
+      <c r="F36" s="224">
+        <f>IF(E36&gt;0,E36-MIN(E36,4250000)*10%-MIN(E36,1700000)*2%-MAX(0,E36-MIN(E36,4250000)*10%-MIN(E36,1700000)*2%-129750)*10%,0)</f>
         <v>1042575</v>
       </c>
-      <c r="G35" s="177">
-        <f>D35*E35*12/1000</f>
+      <c r="G36" s="177">
+        <f>D36*E36*12/1000</f>
         <v>15600</v>
       </c>
-      <c r="H35" s="177" t="s">
+      <c r="H36" s="177" t="s">
         <v>307</v>
       </c>
-      <c r="I35" s="264" t="s">
+      <c r="I36" s="264" t="s">
         <v>311</v>
       </c>
-      <c r="J35" s="270" t="s">
+      <c r="J36" s="270" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="30">
-      <c r="A36" s="249">
+    <row r="37" spans="1:10" ht="30">
+      <c r="A37" s="249">
         <v>2</v>
       </c>
-      <c r="B36" s="250" t="s">
+      <c r="B37" s="250" t="s">
         <v>297</v>
       </c>
-      <c r="C36" s="249"/>
-      <c r="D36" s="251"/>
-      <c r="E36" s="252"/>
-      <c r="F36" s="253"/>
-      <c r="G36" s="251"/>
-      <c r="H36" s="251" t="s">
+      <c r="C37" s="249"/>
+      <c r="D37" s="251"/>
+      <c r="E37" s="252"/>
+      <c r="F37" s="253"/>
+      <c r="G37" s="251"/>
+      <c r="H37" s="251" t="s">
         <v>304</v>
       </c>
-      <c r="I36" s="263" t="s">
+      <c r="I37" s="263" t="s">
         <v>311</v>
       </c>
-      <c r="J36" s="272" t="s">
+      <c r="J37" s="272" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="171" t="s">
+    <row r="38" spans="1:10">
+      <c r="A38" s="171" t="s">
         <v>266</v>
       </c>
-      <c r="B37" s="172" t="s">
+      <c r="B38" s="172" t="s">
         <v>275</v>
       </c>
-      <c r="C37" s="188"/>
-      <c r="D37" s="173">
-        <f t="shared" ref="D37:G37" si="7">SUM(D38:D45)</f>
+      <c r="C38" s="188"/>
+      <c r="D38" s="173">
+        <f t="shared" ref="D38:G38" si="7">SUM(D39:D46)</f>
         <v>5</v>
       </c>
-      <c r="E37" s="227">
+      <c r="E38" s="227">
         <f t="shared" si="7"/>
         <v>4700000</v>
       </c>
-      <c r="F37" s="228">
-        <f>SUM(F38:F45)</f>
+      <c r="F38" s="228">
+        <f>SUM(F39:F46)</f>
         <v>3787275</v>
       </c>
-      <c r="G37" s="173">
+      <c r="G38" s="173">
         <f t="shared" si="7"/>
         <v>56400</v>
       </c>
-      <c r="H37" s="173"/>
-      <c r="I37" s="173"/>
-      <c r="J37" s="269"/>
-    </row>
-    <row r="38" spans="1:10" ht="30">
-      <c r="A38" s="168">
-        <v>1</v>
-      </c>
-      <c r="B38" s="176" t="s">
-        <v>440</v>
-      </c>
-      <c r="C38" s="193" t="s">
-        <v>270</v>
-      </c>
-      <c r="D38" s="170">
-        <v>1</v>
-      </c>
-      <c r="E38" s="229">
-        <v>1300000</v>
-      </c>
-      <c r="F38" s="230">
-        <f>IF(E38&gt;0,E38-MIN(E38,4250000)*10%-MIN(E38,1700000)*2%-MAX(0,E38-MIN(E38,4250000)*10%-MIN(E38,1700000)*2%-129750)*10%,0)</f>
-        <v>1042575</v>
-      </c>
-      <c r="G38" s="170">
-        <f>D38*E38*12/1000</f>
-        <v>15600</v>
-      </c>
-      <c r="H38" s="170" t="s">
-        <v>307</v>
-      </c>
-      <c r="I38" s="265" t="s">
-        <v>311</v>
-      </c>
-      <c r="J38" s="273" t="s">
-        <v>318</v>
-      </c>
+      <c r="H38" s="173"/>
+      <c r="I38" s="173"/>
+      <c r="J38" s="269"/>
     </row>
     <row r="39" spans="1:10" ht="30">
       <c r="A39" s="168">
-        <v>2</v>
-      </c>
-      <c r="B39" s="210" t="s">
-        <v>420</v>
-      </c>
-      <c r="C39" s="194" t="s">
-        <v>272</v>
+        <v>1</v>
+      </c>
+      <c r="B39" s="176" t="s">
+        <v>440</v>
+      </c>
+      <c r="C39" s="193" t="s">
+        <v>270</v>
       </c>
       <c r="D39" s="170">
         <v>1</v>
       </c>
       <c r="E39" s="229">
-        <v>1000000</v>
+        <v>1300000</v>
       </c>
       <c r="F39" s="230">
         <f>IF(E39&gt;0,E39-MIN(E39,4250000)*10%-MIN(E39,1700000)*2%-MAX(0,E39-MIN(E39,4250000)*10%-MIN(E39,1700000)*2%-129750)*10%,0)</f>
-        <v>804975</v>
+        <v>1042575</v>
       </c>
       <c r="G39" s="170">
         <f>D39*E39*12/1000</f>
-        <v>12000</v>
+        <v>15600</v>
       </c>
       <c r="H39" s="170" t="s">
         <v>307</v>
@@ -22222,42 +22231,52 @@
         <v>311</v>
       </c>
       <c r="J39" s="273" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="30">
+      <c r="A40" s="168">
+        <v>2</v>
+      </c>
+      <c r="B40" s="210" t="s">
+        <v>420</v>
+      </c>
+      <c r="C40" s="194" t="s">
+        <v>272</v>
+      </c>
+      <c r="D40" s="170">
+        <v>1</v>
+      </c>
+      <c r="E40" s="229">
+        <v>1000000</v>
+      </c>
+      <c r="F40" s="230">
+        <f>IF(E40&gt;0,E40-MIN(E40,4250000)*10%-MIN(E40,1700000)*2%-MAX(0,E40-MIN(E40,4250000)*10%-MIN(E40,1700000)*2%-129750)*10%,0)</f>
+        <v>804975</v>
+      </c>
+      <c r="G40" s="170">
+        <f>D40*E40*12/1000</f>
+        <v>12000</v>
+      </c>
+      <c r="H40" s="170" t="s">
+        <v>307</v>
+      </c>
+      <c r="I40" s="265" t="s">
+        <v>311</v>
+      </c>
+      <c r="J40" s="273" t="s">
         <v>418</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" s="212" customFormat="1" ht="30">
-      <c r="A40" s="254">
-        <v>3</v>
-      </c>
-      <c r="B40" s="255" t="s">
-        <v>294</v>
-      </c>
-      <c r="C40" s="249" t="s">
-        <v>272</v>
-      </c>
-      <c r="D40" s="256"/>
-      <c r="E40" s="257"/>
-      <c r="F40" s="258"/>
-      <c r="G40" s="256"/>
-      <c r="H40" s="256" t="s">
-        <v>304</v>
-      </c>
-      <c r="I40" s="262" t="s">
-        <v>311</v>
-      </c>
-      <c r="J40" s="274" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="212" customFormat="1" ht="30">
       <c r="A41" s="254">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B41" s="255" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C41" s="249" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D41" s="256"/>
       <c r="E41" s="257"/>
@@ -22270,358 +22289,374 @@
         <v>311</v>
       </c>
       <c r="J41" s="274" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" s="212" customFormat="1" ht="30">
+      <c r="A42" s="254">
+        <v>4</v>
+      </c>
+      <c r="B42" s="255" t="s">
+        <v>295</v>
+      </c>
+      <c r="C42" s="249" t="s">
+        <v>271</v>
+      </c>
+      <c r="D42" s="256"/>
+      <c r="E42" s="257"/>
+      <c r="F42" s="258"/>
+      <c r="G42" s="256"/>
+      <c r="H42" s="256" t="s">
+        <v>304</v>
+      </c>
+      <c r="I42" s="262" t="s">
+        <v>311</v>
+      </c>
+      <c r="J42" s="274" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="42" spans="1:10" s="212" customFormat="1">
-      <c r="A42" s="294">
+    <row r="43" spans="1:10" s="212" customFormat="1">
+      <c r="A43" s="294">
         <v>5</v>
       </c>
-      <c r="B42" s="210" t="s">
+      <c r="B43" s="210" t="s">
         <v>441</v>
       </c>
-      <c r="C42" s="213" t="s">
+      <c r="C43" s="213" t="s">
         <v>271</v>
       </c>
-      <c r="D42" s="295">
+      <c r="D43" s="295">
         <v>1</v>
       </c>
-      <c r="E42" s="296">
+      <c r="E43" s="296">
         <v>700000</v>
       </c>
-      <c r="F42" s="297">
-        <f>IF(E42&gt;0,E42-MIN(E42,4250000)*10%-MIN(E42,1700000)*2%-MAX(0,E42-MIN(E42,4250000)*10%-MIN(E42,1700000)*2%-129750)*10%,0)</f>
+      <c r="F43" s="297">
+        <f>IF(E43&gt;0,E43-MIN(E43,4250000)*10%-MIN(E43,1700000)*2%-MAX(0,E43-MIN(E43,4250000)*10%-MIN(E43,1700000)*2%-129750)*10%,0)</f>
         <v>567375</v>
       </c>
-      <c r="G42" s="295">
-        <f>D42*E42*12/1000</f>
+      <c r="G43" s="295">
+        <f>D43*E43*12/1000</f>
         <v>8400</v>
       </c>
-      <c r="H42" s="295" t="s">
+      <c r="H43" s="295" t="s">
         <v>307</v>
       </c>
-      <c r="I42" s="298" t="s">
+      <c r="I43" s="298" t="s">
         <v>311</v>
       </c>
-      <c r="J42" s="299" t="s">
+      <c r="J43" s="299" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="30">
-      <c r="A43" s="168">
+    <row r="44" spans="1:10" ht="30">
+      <c r="A44" s="168">
         <v>6</v>
       </c>
-      <c r="B43" s="176" t="s">
+      <c r="B44" s="176" t="s">
         <v>442</v>
       </c>
-      <c r="C43" s="194" t="s">
+      <c r="C44" s="194" t="s">
         <v>272</v>
-      </c>
-      <c r="D43" s="177">
-        <v>1</v>
-      </c>
-      <c r="E43" s="229">
-        <v>1000000</v>
-      </c>
-      <c r="F43" s="230">
-        <f>IF(E43&gt;0,E43-MIN(E43,4250000)*10%-MIN(E43,1700000)*2%-MAX(0,E43-MIN(E43,4250000)*10%-MIN(E43,1700000)*2%-129750)*10%,0)</f>
-        <v>804975</v>
-      </c>
-      <c r="G43" s="170">
-        <f>D43*E43*12/1000</f>
-        <v>12000</v>
-      </c>
-      <c r="H43" s="170" t="s">
-        <v>307</v>
-      </c>
-      <c r="I43" s="265" t="s">
-        <v>311</v>
-      </c>
-      <c r="J43" s="273" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="30">
-      <c r="A44" s="182">
-        <v>7</v>
-      </c>
-      <c r="B44" s="176" t="s">
-        <v>443</v>
-      </c>
-      <c r="C44" s="195" t="s">
-        <v>271</v>
       </c>
       <c r="D44" s="177">
         <v>1</v>
       </c>
-      <c r="E44" s="223">
+      <c r="E44" s="229">
+        <v>1000000</v>
+      </c>
+      <c r="F44" s="230">
+        <f>IF(E44&gt;0,E44-MIN(E44,4250000)*10%-MIN(E44,1700000)*2%-MAX(0,E44-MIN(E44,4250000)*10%-MIN(E44,1700000)*2%-129750)*10%,0)</f>
+        <v>804975</v>
+      </c>
+      <c r="G44" s="170">
+        <f>D44*E44*12/1000</f>
+        <v>12000</v>
+      </c>
+      <c r="H44" s="170" t="s">
+        <v>307</v>
+      </c>
+      <c r="I44" s="265" t="s">
+        <v>311</v>
+      </c>
+      <c r="J44" s="273" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="30">
+      <c r="A45" s="182">
+        <v>7</v>
+      </c>
+      <c r="B45" s="176" t="s">
+        <v>443</v>
+      </c>
+      <c r="C45" s="195" t="s">
+        <v>271</v>
+      </c>
+      <c r="D45" s="177">
+        <v>1</v>
+      </c>
+      <c r="E45" s="223">
         <v>700000</v>
       </c>
-      <c r="F44" s="224">
-        <f>IF(E44&gt;0,E44-MIN(E44,4250000)*10%-MIN(E44,1700000)*2%-MAX(0,E44-MIN(E44,4250000)*10%-MIN(E44,1700000)*2%-129750)*10%,0)</f>
+      <c r="F45" s="224">
+        <f>IF(E45&gt;0,E45-MIN(E45,4250000)*10%-MIN(E45,1700000)*2%-MAX(0,E45-MIN(E45,4250000)*10%-MIN(E45,1700000)*2%-129750)*10%,0)</f>
         <v>567375</v>
       </c>
-      <c r="G44" s="177">
-        <f>D44*E44*12/1000</f>
+      <c r="G45" s="177">
+        <f>D45*E45*12/1000</f>
         <v>8400</v>
       </c>
-      <c r="H44" s="177" t="s">
+      <c r="H45" s="177" t="s">
         <v>307</v>
       </c>
-      <c r="I44" s="264" t="s">
+      <c r="I45" s="264" t="s">
         <v>311</v>
       </c>
-      <c r="J44" s="270" t="s">
+      <c r="J45" s="270" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="45" spans="1:10" s="212" customFormat="1" ht="30">
-      <c r="A45" s="254">
+    <row r="46" spans="1:10" s="212" customFormat="1" ht="30">
+      <c r="A46" s="254">
         <v>8</v>
       </c>
-      <c r="B45" s="255" t="s">
+      <c r="B46" s="255" t="s">
         <v>296</v>
       </c>
-      <c r="C45" s="249" t="s">
+      <c r="C46" s="249" t="s">
         <v>271</v>
       </c>
-      <c r="D45" s="256">
+      <c r="D46" s="256">
         <v>0</v>
       </c>
-      <c r="E45" s="257"/>
-      <c r="F45" s="258"/>
-      <c r="G45" s="256"/>
-      <c r="H45" s="256" t="s">
+      <c r="E46" s="257"/>
+      <c r="F46" s="258"/>
+      <c r="G46" s="256"/>
+      <c r="H46" s="256" t="s">
         <v>304</v>
       </c>
-      <c r="I45" s="262" t="s">
+      <c r="I46" s="262" t="s">
         <v>311</v>
       </c>
-      <c r="J45" s="274" t="s">
+      <c r="J46" s="274" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="167" t="s">
+    <row r="47" spans="1:10">
+      <c r="A47" s="167" t="s">
         <v>267</v>
       </c>
-      <c r="B46" s="167" t="s">
+      <c r="B47" s="167" t="s">
         <v>293</v>
       </c>
-      <c r="C46" s="167"/>
-      <c r="D46" s="167">
-        <f t="shared" ref="D46:G46" si="8">SUM(D47:D50)</f>
+      <c r="C47" s="167"/>
+      <c r="D47" s="167">
+        <f t="shared" ref="D47:G47" si="8">SUM(D48:D51)</f>
         <v>2</v>
       </c>
-      <c r="E46" s="231">
+      <c r="E47" s="231">
         <f t="shared" si="8"/>
         <v>3393100</v>
       </c>
-      <c r="F46" s="232">
+      <c r="F47" s="232">
         <f t="shared" si="8"/>
         <v>2739235.2</v>
       </c>
-      <c r="G46" s="167">
+      <c r="G47" s="167">
         <f t="shared" si="8"/>
         <v>25200</v>
       </c>
-      <c r="H46" s="167"/>
-      <c r="I46" s="167"/>
-      <c r="J46" s="269"/>
-    </row>
-    <row r="47" spans="1:10" ht="30">
-      <c r="A47" s="168">
+      <c r="H47" s="167"/>
+      <c r="I47" s="167"/>
+      <c r="J47" s="269"/>
+    </row>
+    <row r="48" spans="1:10" ht="30">
+      <c r="A48" s="168">
         <v>1</v>
       </c>
-      <c r="B47" s="169" t="s">
+      <c r="B48" s="169" t="s">
         <v>283</v>
       </c>
-      <c r="C47" s="193" t="s">
+      <c r="C48" s="193" t="s">
         <v>270</v>
-      </c>
-      <c r="D47" s="170">
-        <v>1</v>
-      </c>
-      <c r="E47" s="229">
-        <v>1400000</v>
-      </c>
-      <c r="F47" s="230">
-        <f>IF(E47&gt;0,E47-MIN(E47,4250000)*10%-MIN(E47,1700000)*2%-MAX(0,E47-MIN(E47,4250000)*10%-MIN(E47,1700000)*2%-129750)*10%,0)</f>
-        <v>1121775</v>
-      </c>
-      <c r="G47" s="170">
-        <f>D47*E47*12/1000</f>
-        <v>16800</v>
-      </c>
-      <c r="H47" s="170" t="s">
-        <v>307</v>
-      </c>
-      <c r="I47" s="265" t="s">
-        <v>309</v>
-      </c>
-      <c r="J47" s="273" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="196">
-        <v>2</v>
-      </c>
-      <c r="B48" s="215" t="s">
-        <v>284</v>
-      </c>
-      <c r="C48" s="194" t="s">
-        <v>272</v>
       </c>
       <c r="D48" s="170">
         <v>1</v>
       </c>
-      <c r="E48" s="223">
+      <c r="E48" s="229">
+        <v>1400000</v>
+      </c>
+      <c r="F48" s="230">
+        <f>IF(E48&gt;0,E48-MIN(E48,4250000)*10%-MIN(E48,1700000)*2%-MAX(0,E48-MIN(E48,4250000)*10%-MIN(E48,1700000)*2%-129750)*10%,0)</f>
+        <v>1121775</v>
+      </c>
+      <c r="G48" s="170">
+        <f>D48*E48*12/1000</f>
+        <v>16800</v>
+      </c>
+      <c r="H48" s="170" t="s">
+        <v>307</v>
+      </c>
+      <c r="I48" s="265" t="s">
+        <v>309</v>
+      </c>
+      <c r="J48" s="273" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="196">
+        <v>2</v>
+      </c>
+      <c r="B49" s="215" t="s">
+        <v>284</v>
+      </c>
+      <c r="C49" s="194" t="s">
+        <v>272</v>
+      </c>
+      <c r="D49" s="170">
+        <v>1</v>
+      </c>
+      <c r="E49" s="223">
         <v>700000</v>
       </c>
-      <c r="F48" s="224">
-        <f>IF(E48&gt;0,E48-MIN(E48,4250000)*10%-MIN(E48,1700000)*2%-MAX(0,E48-MIN(E48,4250000)*10%-MIN(E48,1700000)*2%-129750)*10%,0)</f>
+      <c r="F49" s="224">
+        <f>IF(E49&gt;0,E49-MIN(E49,4250000)*10%-MIN(E49,1700000)*2%-MAX(0,E49-MIN(E49,4250000)*10%-MIN(E49,1700000)*2%-129750)*10%,0)</f>
         <v>567375</v>
       </c>
-      <c r="G48" s="177">
-        <f>D48*E48*12/1000</f>
+      <c r="G49" s="177">
+        <f>D49*E49*12/1000</f>
         <v>8400</v>
       </c>
-      <c r="H48" s="177" t="s">
+      <c r="H49" s="177" t="s">
         <v>307</v>
       </c>
-      <c r="I48" s="264" t="s">
+      <c r="I49" s="264" t="s">
         <v>311</v>
       </c>
-      <c r="J48" s="270" t="s">
+      <c r="J49" s="270" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
-      <c r="A49" s="259">
+    <row r="50" spans="1:10">
+      <c r="A50" s="259">
         <v>3</v>
       </c>
-      <c r="B49" s="260" t="s">
+      <c r="B50" s="260" t="s">
         <v>285</v>
       </c>
-      <c r="C49" s="249"/>
-      <c r="D49" s="256"/>
-      <c r="E49" s="252">
+      <c r="C50" s="249"/>
+      <c r="D50" s="256"/>
+      <c r="E50" s="252">
         <v>867500</v>
       </c>
-      <c r="F49" s="253">
-        <f>IF(E49&gt;0,E49-MIN(E49,4250000)*10%-MIN(E49,1700000)*2%-MAX(0,E49-MIN(E49,4250000)*10%-MIN(E49,1700000)*2%-129750)*10%,0)</f>
+      <c r="F50" s="253">
+        <f>IF(E50&gt;0,E50-MIN(E50,4250000)*10%-MIN(E50,1700000)*2%-MAX(0,E50-MIN(E50,4250000)*10%-MIN(E50,1700000)*2%-129750)*10%,0)</f>
         <v>700035</v>
       </c>
-      <c r="G49" s="251"/>
-      <c r="H49" s="251" t="s">
+      <c r="G50" s="251"/>
+      <c r="H50" s="251" t="s">
         <v>304</v>
       </c>
-      <c r="I49" s="263" t="s">
+      <c r="I50" s="263" t="s">
         <v>311</v>
       </c>
-      <c r="J49" s="272" t="s">
+      <c r="J50" s="272" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="30">
-      <c r="A50" s="259">
+    <row r="51" spans="1:10" ht="30">
+      <c r="A51" s="259">
         <v>4</v>
       </c>
-      <c r="B50" s="260" t="s">
+      <c r="B51" s="260" t="s">
         <v>286</v>
       </c>
-      <c r="C50" s="249"/>
-      <c r="D50" s="251"/>
-      <c r="E50" s="257">
+      <c r="C51" s="249"/>
+      <c r="D51" s="251"/>
+      <c r="E51" s="257">
         <v>425600</v>
       </c>
-      <c r="F50" s="258">
-        <f>IF(E50&gt;0,E50-MIN(E50,4250000)*10%-MIN(E50,1700000)*2%-MAX(0,E50-MIN(E50,4250000)*10%-MIN(E50,1700000)*2%-129750)*10%,0)</f>
+      <c r="F51" s="258">
+        <f>IF(E51&gt;0,E51-MIN(E51,4250000)*10%-MIN(E51,1700000)*2%-MAX(0,E51-MIN(E51,4250000)*10%-MIN(E51,1700000)*2%-129750)*10%,0)</f>
         <v>350050.2</v>
       </c>
-      <c r="G50" s="256"/>
-      <c r="H50" s="256" t="s">
+      <c r="G51" s="256"/>
+      <c r="H51" s="256" t="s">
         <v>304</v>
       </c>
-      <c r="I50" s="262" t="s">
+      <c r="I51" s="262" t="s">
         <v>311</v>
       </c>
-      <c r="J50" s="274" t="s">
+      <c r="J51" s="274" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A51" s="197"/>
-      <c r="B51" s="198" t="s">
+    <row r="52" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A52" s="197"/>
+      <c r="B52" s="198" t="s">
         <v>292</v>
       </c>
-      <c r="C51" s="189"/>
-      <c r="D51" s="174">
-        <f>D6+D10+D12+D18+D23+D34+D37+D46</f>
-        <v>30</v>
-      </c>
-      <c r="E51" s="233">
-        <f>E6+E10+E12+E18+E23+E34+E37+E46</f>
-        <v>31793100</v>
-      </c>
-      <c r="F51" s="235">
-        <f>F6+F10+F12+F18+F23+F34+F37+F46</f>
-        <v>25595335.199999999</v>
-      </c>
-      <c r="G51" s="234">
-        <f>G6+G10+G12+G18+G23+G34+G37+G46</f>
-        <v>366000</v>
-      </c>
-      <c r="H51" s="234"/>
-      <c r="I51" s="234"/>
-      <c r="J51" s="234"/>
-    </row>
-    <row r="52" spans="1:10" ht="45">
-      <c r="A52" s="241"/>
-      <c r="B52" s="217" t="s">
-        <v>454</v>
-      </c>
-      <c r="C52" s="186"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="175"/>
-      <c r="G52" s="165"/>
-    </row>
-    <row r="53" spans="1:10">
+      <c r="C52" s="189"/>
+      <c r="D52" s="174">
+        <f>D6+D10+D12+D18+D24+D35+D38+D47</f>
+        <v>31</v>
+      </c>
+      <c r="E52" s="233">
+        <f>E6+E10+E12+E18+E24+E35+E38+E47</f>
+        <v>33193100</v>
+      </c>
+      <c r="F52" s="235">
+        <f>F6+F10+F12+F18+F24+F35+F38+F47</f>
+        <v>26717110.199999999</v>
+      </c>
+      <c r="G52" s="234">
+        <f>G6+G10+G12+G18+G24+G35+G38+G47</f>
+        <v>382800</v>
+      </c>
+      <c r="H52" s="234"/>
+      <c r="I52" s="234"/>
+      <c r="J52" s="234"/>
+    </row>
+    <row r="53" spans="1:10" ht="45">
       <c r="A53" s="241"/>
-      <c r="B53" s="261" t="s">
-        <v>298</v>
-      </c>
-      <c r="C53" s="190"/>
-      <c r="D53" s="129"/>
-      <c r="E53" s="129"/>
-      <c r="G53" s="1"/>
+      <c r="B53" s="217" t="s">
+        <v>452</v>
+      </c>
+      <c r="C53" s="186"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="175"/>
+      <c r="G53" s="165"/>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="241"/>
-      <c r="B54" s="216" t="str">
-        <f>"Всего в штате по таблице (столбец D) — "&amp;D51&amp;" чел."</f>
-        <v>Всего в штате по таблице (столбец D) — 30 чел.</v>
+      <c r="B54" s="261" t="s">
+        <v>298</v>
       </c>
       <c r="C54" s="190"/>
       <c r="D54" s="129"/>
       <c r="E54" s="129"/>
       <c r="G54" s="1"/>
     </row>
-    <row r="55" spans="1:10" ht="43.5">
+    <row r="55" spans="1:10">
       <c r="A55" s="241"/>
-      <c r="B55" s="240" t="str">
-        <f>"Состав: проектный офис — "&amp;(D10+D12+D23+D34+D37)&amp;" чел.; Фонд с Проектным офисом для Центральной Азии — "&amp;(D6+D18+D46)&amp;" чел."</f>
-        <v>Состав: проектный офис — 21 чел.; Фонд с Проектным офисом для Центральной Азии — 9 чел.</v>
-      </c>
-      <c r="C55" s="186"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
+      <c r="B55" s="216" t="str">
+        <f>"Всего в штате по таблице (столбец D) — "&amp;D52&amp;" чел."</f>
+        <v>Всего в штате по таблице (столбец D) — 31 чел.</v>
+      </c>
+      <c r="C55" s="190"/>
+      <c r="D55" s="129"/>
+      <c r="E55" s="129"/>
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="1:10">
-      <c r="A56" s="1"/>
-      <c r="B56" s="217"/>
+    <row r="56" spans="1:10" ht="43.5">
+      <c r="A56" s="241"/>
+      <c r="B56" s="240" t="str">
+        <f>"Состав: проектный офис — "&amp;(D10+D12+D24+D35+D38)&amp;" чел.; Фонд с Проектным офисом для Центральной Азии — "&amp;(D6+D18+D47)&amp;" чел."</f>
+        <v>Состав: проектный офис — 21 чел.; Фонд с Проектным офисом для Центральной Азии — 10 чел.</v>
+      </c>
       <c r="C56" s="186"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -22629,7 +22664,7 @@
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="1"/>
-      <c r="B57" s="209"/>
+      <c r="B57" s="217"/>
       <c r="C57" s="186"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -29658,6 +29693,14 @@
       <c r="D935" s="1"/>
       <c r="E935" s="1"/>
       <c r="G935" s="1"/>
+    </row>
+    <row r="936" spans="1:7">
+      <c r="A936" s="1"/>
+      <c r="B936" s="209"/>
+      <c r="C936" s="186"/>
+      <c r="D936" s="1"/>
+      <c r="E936" s="1"/>
+      <c r="G936" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -29760,7 +29803,7 @@
     </row>
     <row r="10" spans="1:6" ht="51">
       <c r="A10" s="278" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B10" s="280" t="s">
         <v>345</v>

--- a/TAZA/_документы/Штатка Фонда и проектного офиса.xlsx
+++ b/TAZA/_документы/Штатка Фонда и проектного офиса.xlsx
@@ -2412,15 +2412,6 @@
     <t>Заместитель руководителя Проектного офиса для Центральной Азии</t>
   </si>
   <si>
-    <t>Менеджер проектов – эколог / Загирова Анастасия</t>
-  </si>
-  <si>
-    <t>Менеджер проектов – эколог / Абулхан А.</t>
-  </si>
-  <si>
-    <t>Менеджер проектов – эколог (отходы, вода, воздух) / вакансия</t>
-  </si>
-  <si>
     <t>*приход с 12.2026 и в 2027 году выделен сиреневым (с 12.2026 – Өміртай А.; остальные – с 02.2027)</t>
   </si>
   <si>
@@ -2440,6 +2431,15 @@
   </si>
   <si>
     <t>Руководство Проектным офисом для Центральной Азии; до назначения Руководителя обязанности исполняет ГИД без оклада и доплаты</t>
+  </si>
+  <si>
+    <t>Менеджер проектов / Загирова Анастасия</t>
+  </si>
+  <si>
+    <t>Менеджер проектов / Абулхан А.</t>
+  </si>
+  <si>
+    <t>Менеджер проектов / вакансия</t>
   </si>
 </sst>
 </file>
@@ -5588,6 +5588,42 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5600,48 +5636,90 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="34" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5651,18 +5729,69 @@
     <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="33" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="34" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="35" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="32" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="39" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="3" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="10" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="2" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="17" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="32" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5672,139 +5801,19 @@
     <xf numFmtId="0" fontId="46" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="32" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="10" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="2" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="17" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="39" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="3" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="33" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="34" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="35" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="34" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5819,43 +5828,145 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="2" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="2" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="2" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="2" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5864,24 +5975,6 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5932,99 +6025,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6366,7 +6366,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6424,7 +6424,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6479,7 +6479,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10256,26 +10256,26 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="309" t="s">
+      <c r="A2" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="309"/>
+      <c r="B2" s="301"/>
       <c r="C2" s="132" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="314" t="s">
+      <c r="A3" s="302" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="315"/>
+      <c r="B3" s="303"/>
       <c r="C3" s="133"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="314" t="s">
+      <c r="A4" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="315" t="s">
+      <c r="B4" s="303" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="133"/>
@@ -10288,24 +10288,24 @@
       <c r="C5" s="133"/>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
-      <c r="A6" s="314" t="s">
+      <c r="A6" s="302" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="315"/>
+      <c r="B6" s="303"/>
       <c r="C6" s="134"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
-      <c r="A7" s="314" t="s">
+      <c r="A7" s="302" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="315"/>
+      <c r="B7" s="303"/>
       <c r="C7" s="135"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="305" t="s">
+      <c r="A8" s="304" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="306"/>
+      <c r="B8" s="305"/>
       <c r="C8" s="131">
         <f>SUM(C3:C7)</f>
         <v>0</v>
@@ -10315,17 +10315,17 @@
       <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="316" t="s">
+      <c r="A10" s="306" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="316"/>
-      <c r="C10" s="316"/>
+      <c r="B10" s="306"/>
+      <c r="C10" s="306"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="309" t="s">
+      <c r="A11" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="309"/>
+      <c r="B11" s="301"/>
       <c r="C11" s="132" t="s">
         <v>1</v>
       </c>
@@ -10352,10 +10352,10 @@
       <c r="C14" s="136"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="305" t="s">
+      <c r="A15" s="304" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="306"/>
+      <c r="B15" s="305"/>
       <c r="C15" s="130">
         <f>SUM(C12:C14)</f>
         <v>0</v>
@@ -10385,10 +10385,10 @@
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="309" t="s">
+      <c r="A20" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="309"/>
+      <c r="B20" s="301"/>
       <c r="C20" s="132" t="s">
         <v>1</v>
       </c>
@@ -10433,17 +10433,17 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="310" t="s">
+      <c r="A26" s="309" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="311"/>
-      <c r="C26" s="312"/>
+      <c r="B26" s="310"/>
+      <c r="C26" s="311"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="309" t="s">
+      <c r="A27" s="301" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="309"/>
+      <c r="B27" s="301"/>
       <c r="C27" s="138"/>
     </row>
     <row r="28" spans="1:4">
@@ -10460,17 +10460,17 @@
       <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="313" t="s">
+      <c r="A30" s="312" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="313"/>
+      <c r="B30" s="312"/>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="309" t="s">
+      <c r="A31" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="309"/>
+      <c r="B31" s="301"/>
       <c r="C31" s="132" t="s">
         <v>1</v>
       </c>
@@ -10507,8 +10507,8 @@
       <c r="D35" s="3"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="301"/>
-      <c r="B36" s="302"/>
+      <c r="A36" s="313"/>
+      <c r="B36" s="314"/>
       <c r="C36" s="144">
         <f>SUM(C32:C35)</f>
         <v>0</v>
@@ -10520,10 +10520,10 @@
       <c r="C37" s="8"/>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="303" t="s">
+      <c r="A38" s="315" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="304"/>
+      <c r="B38" s="316"/>
       <c r="C38" s="145">
         <f>C28-C36</f>
         <v>0</v>
@@ -10546,6 +10546,23 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
@@ -10558,23 +10575,6 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10842,11 +10842,11 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1"/>
-      <c r="B19" s="309" t="s">
+      <c r="B19" s="301" t="s">
         <v>259</v>
       </c>
-      <c r="C19" s="309"/>
-      <c r="D19" s="309"/>
+      <c r="C19" s="301"/>
+      <c r="D19" s="301"/>
       <c r="E19" s="162" t="e">
         <f>E15/E18</f>
         <v>#REF!</v>
@@ -10923,17 +10923,17 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="357" t="s">
+      <c r="B1" s="319" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="357"/>
-      <c r="D1" s="357"/>
-      <c r="E1" s="357"/>
-      <c r="F1" s="357"/>
-      <c r="G1" s="357"/>
-      <c r="H1" s="357"/>
-      <c r="I1" s="357"/>
-      <c r="J1" s="357"/>
+      <c r="C1" s="319"/>
+      <c r="D1" s="319"/>
+      <c r="E1" s="319"/>
+      <c r="F1" s="319"/>
+      <c r="G1" s="319"/>
+      <c r="H1" s="319"/>
+      <c r="I1" s="319"/>
+      <c r="J1" s="319"/>
       <c r="K1" s="85"/>
       <c r="O1" s="51"/>
     </row>
@@ -10971,17 +10971,17 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="358" t="s">
+      <c r="B3" s="320" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="358"/>
-      <c r="D3" s="358"/>
-      <c r="E3" s="358"/>
-      <c r="F3" s="358"/>
-      <c r="G3" s="358"/>
-      <c r="H3" s="358"/>
-      <c r="I3" s="358"/>
-      <c r="J3" s="358"/>
+      <c r="C3" s="320"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="320"/>
+      <c r="G3" s="320"/>
+      <c r="H3" s="320"/>
+      <c r="I3" s="320"/>
+      <c r="J3" s="320"/>
       <c r="K3" s="88"/>
       <c r="O3" s="51"/>
     </row>
@@ -10989,17 +10989,17 @@
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="359" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="359"/>
-      <c r="D4" s="359"/>
-      <c r="E4" s="359"/>
-      <c r="F4" s="359"/>
-      <c r="G4" s="359"/>
-      <c r="H4" s="359"/>
-      <c r="I4" s="359"/>
-      <c r="J4" s="359"/>
+      <c r="B4" s="321" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="321"/>
+      <c r="D4" s="321"/>
+      <c r="E4" s="321"/>
+      <c r="F4" s="321"/>
+      <c r="G4" s="321"/>
+      <c r="H4" s="321"/>
+      <c r="I4" s="321"/>
+      <c r="J4" s="321"/>
       <c r="K4" s="89"/>
       <c r="O4" s="51"/>
     </row>
@@ -11007,17 +11007,17 @@
       <c r="A5" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="360" t="s">
+      <c r="B5" s="322" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="360"/>
-      <c r="D5" s="360"/>
-      <c r="E5" s="360"/>
-      <c r="F5" s="360"/>
-      <c r="G5" s="360"/>
-      <c r="H5" s="360"/>
-      <c r="I5" s="360"/>
-      <c r="J5" s="360"/>
+      <c r="C5" s="322"/>
+      <c r="D5" s="322"/>
+      <c r="E5" s="322"/>
+      <c r="F5" s="322"/>
+      <c r="G5" s="322"/>
+      <c r="H5" s="322"/>
+      <c r="I5" s="322"/>
+      <c r="J5" s="322"/>
       <c r="K5" s="90"/>
       <c r="O5" s="51"/>
     </row>
@@ -11025,17 +11025,17 @@
       <c r="A6" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="360" t="s">
+      <c r="B6" s="322" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="360"/>
-      <c r="D6" s="360"/>
-      <c r="E6" s="360"/>
-      <c r="F6" s="360"/>
-      <c r="G6" s="360"/>
-      <c r="H6" s="360"/>
-      <c r="I6" s="360"/>
-      <c r="J6" s="360"/>
+      <c r="C6" s="322"/>
+      <c r="D6" s="322"/>
+      <c r="E6" s="322"/>
+      <c r="F6" s="322"/>
+      <c r="G6" s="322"/>
+      <c r="H6" s="322"/>
+      <c r="I6" s="322"/>
+      <c r="J6" s="322"/>
       <c r="K6" s="90"/>
       <c r="O6" s="51"/>
     </row>
@@ -11043,15 +11043,15 @@
       <c r="A7" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="361" t="s">
+      <c r="B7" s="323" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="361"/>
-      <c r="D7" s="361"/>
-      <c r="E7" s="361"/>
-      <c r="F7" s="361"/>
-      <c r="G7" s="361"/>
-      <c r="H7" s="361"/>
+      <c r="C7" s="323"/>
+      <c r="D7" s="323"/>
+      <c r="E7" s="323"/>
+      <c r="F7" s="323"/>
+      <c r="G7" s="323"/>
+      <c r="H7" s="323"/>
       <c r="I7" s="91"/>
       <c r="J7" s="71" t="s">
         <v>50</v>
@@ -11077,51 +11077,51 @@
       <c r="A22" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="362" t="s">
+      <c r="B22" s="324" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="365" t="s">
+      <c r="C22" s="327" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="366"/>
-      <c r="E22" s="366"/>
-      <c r="F22" s="366"/>
-      <c r="G22" s="367"/>
+      <c r="D22" s="328"/>
+      <c r="E22" s="328"/>
+      <c r="F22" s="328"/>
+      <c r="G22" s="329"/>
       <c r="H22" s="93"/>
-      <c r="I22" s="366" t="s">
+      <c r="I22" s="328" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="367"/>
+      <c r="J22" s="329"/>
       <c r="K22" s="94"/>
     </row>
     <row r="23" spans="1:16" ht="12" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="363"/>
-      <c r="C23" s="368"/>
-      <c r="D23" s="369"/>
-      <c r="E23" s="369"/>
-      <c r="F23" s="369"/>
-      <c r="G23" s="370"/>
+      <c r="B23" s="325"/>
+      <c r="C23" s="330"/>
+      <c r="D23" s="331"/>
+      <c r="E23" s="331"/>
+      <c r="F23" s="331"/>
+      <c r="G23" s="332"/>
       <c r="H23" s="95"/>
-      <c r="I23" s="369"/>
-      <c r="J23" s="370"/>
+      <c r="I23" s="331"/>
+      <c r="J23" s="332"/>
       <c r="K23" s="94"/>
     </row>
     <row r="24" spans="1:16" ht="24" customHeight="1">
       <c r="A24" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="364"/>
-      <c r="C24" s="371"/>
-      <c r="D24" s="372"/>
-      <c r="E24" s="372"/>
-      <c r="F24" s="372"/>
-      <c r="G24" s="373"/>
+      <c r="B24" s="326"/>
+      <c r="C24" s="333"/>
+      <c r="D24" s="334"/>
+      <c r="E24" s="334"/>
+      <c r="F24" s="334"/>
+      <c r="G24" s="335"/>
       <c r="H24" s="96"/>
-      <c r="I24" s="372"/>
-      <c r="J24" s="373"/>
+      <c r="I24" s="334"/>
+      <c r="J24" s="335"/>
       <c r="K24" s="94"/>
     </row>
     <row r="25" spans="1:16" ht="15.75" hidden="1" customHeight="1"/>
@@ -11163,13 +11163,13 @@
       <c r="B29" s="58">
         <v>1</v>
       </c>
-      <c r="C29" s="323" t="s">
+      <c r="C29" s="336" t="s">
         <v>202</v>
       </c>
-      <c r="D29" s="324"/>
-      <c r="E29" s="324"/>
-      <c r="F29" s="324"/>
-      <c r="G29" s="325"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
+      <c r="G29" s="338"/>
       <c r="H29" s="97"/>
       <c r="I29" s="97" t="e">
         <f>I35+I44+I46+I47+I50+#REF!+I68+I71+I72+I73+I77+I89+I97+I101+I106+I108+I116+I131+I142+I146+I147+I154+I32+I34+#REF!+#REF!+I151+#REF!+I98+I113+I155</f>
@@ -11186,15 +11186,15 @@
       <c r="B30" s="58">
         <v>2</v>
       </c>
-      <c r="C30" s="332" t="s">
+      <c r="C30" s="339" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="323" t="s">
+      <c r="D30" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="324"/>
-      <c r="F30" s="324"/>
-      <c r="G30" s="325"/>
+      <c r="E30" s="337"/>
+      <c r="F30" s="337"/>
+      <c r="G30" s="338"/>
       <c r="H30" s="97"/>
       <c r="I30" s="97"/>
       <c r="J30" s="99" t="e">
@@ -11214,15 +11214,15 @@
       <c r="B31" s="58">
         <v>3</v>
       </c>
-      <c r="C31" s="333"/>
+      <c r="C31" s="340"/>
       <c r="D31" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="319" t="s">
+      <c r="E31" s="345" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="320"/>
-      <c r="G31" s="321"/>
+      <c r="F31" s="346"/>
+      <c r="G31" s="347"/>
       <c r="H31" s="72"/>
       <c r="I31" s="72"/>
       <c r="J31" s="100"/>
@@ -11239,13 +11239,13 @@
       <c r="B32" s="58">
         <v>4</v>
       </c>
-      <c r="C32" s="333"/>
+      <c r="C32" s="340"/>
       <c r="D32" s="343"/>
-      <c r="E32" s="319" t="s">
+      <c r="E32" s="345" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="320"/>
-      <c r="G32" s="321"/>
+      <c r="F32" s="346"/>
+      <c r="G32" s="347"/>
       <c r="H32" s="72"/>
       <c r="I32" s="72"/>
       <c r="J32" s="81" t="e">
@@ -11265,13 +11265,13 @@
       <c r="B33" s="58">
         <v>5</v>
       </c>
-      <c r="C33" s="333"/>
+      <c r="C33" s="340"/>
       <c r="D33" s="343"/>
-      <c r="E33" s="352" t="s">
+      <c r="E33" s="348" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="353"/>
-      <c r="G33" s="354"/>
+      <c r="F33" s="349"/>
+      <c r="G33" s="350"/>
       <c r="H33" s="72"/>
       <c r="I33" s="72"/>
       <c r="J33" s="81"/>
@@ -11284,13 +11284,13 @@
       <c r="B34" s="58">
         <v>6</v>
       </c>
-      <c r="C34" s="349"/>
-      <c r="D34" s="351"/>
-      <c r="E34" s="329" t="s">
+      <c r="C34" s="341"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="352" t="s">
         <v>170</v>
       </c>
-      <c r="F34" s="329"/>
-      <c r="G34" s="329"/>
+      <c r="F34" s="352"/>
+      <c r="G34" s="352"/>
       <c r="H34" s="72"/>
       <c r="I34" s="72"/>
       <c r="J34" s="81" t="e">
@@ -11306,15 +11306,15 @@
       <c r="B35" s="58">
         <v>7</v>
       </c>
-      <c r="C35" s="332" t="s">
+      <c r="C35" s="339" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="323" t="s">
+      <c r="D35" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E35" s="355"/>
-      <c r="F35" s="355"/>
-      <c r="G35" s="356"/>
+      <c r="E35" s="353"/>
+      <c r="F35" s="353"/>
+      <c r="G35" s="354"/>
       <c r="H35" s="97"/>
       <c r="I35" s="101">
         <f>I36+I37</f>
@@ -11330,15 +11330,15 @@
       <c r="B36" s="58">
         <v>8</v>
       </c>
-      <c r="C36" s="333"/>
+      <c r="C36" s="340"/>
       <c r="D36" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="336" t="s">
+      <c r="E36" s="355" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="337"/>
-      <c r="G36" s="338"/>
+      <c r="F36" s="356"/>
+      <c r="G36" s="357"/>
       <c r="H36" s="72"/>
       <c r="I36" s="72"/>
       <c r="J36" s="81" t="e">
@@ -11355,13 +11355,13 @@
       <c r="B37" s="58">
         <v>9</v>
       </c>
-      <c r="C37" s="349"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="336" t="s">
+      <c r="C37" s="341"/>
+      <c r="D37" s="351"/>
+      <c r="E37" s="355" t="s">
         <v>173</v>
       </c>
-      <c r="F37" s="337"/>
-      <c r="G37" s="338"/>
+      <c r="F37" s="356"/>
+      <c r="G37" s="357"/>
       <c r="H37" s="72"/>
       <c r="I37" s="72"/>
       <c r="J37" s="81" t="e">
@@ -11378,13 +11378,13 @@
       <c r="B38" s="58">
         <v>10</v>
       </c>
-      <c r="C38" s="323" t="s">
+      <c r="C38" s="336" t="s">
         <v>203</v>
       </c>
-      <c r="D38" s="324"/>
-      <c r="E38" s="324"/>
-      <c r="F38" s="324"/>
-      <c r="G38" s="325"/>
+      <c r="D38" s="337"/>
+      <c r="E38" s="337"/>
+      <c r="F38" s="337"/>
+      <c r="G38" s="338"/>
       <c r="H38" s="97"/>
       <c r="I38" s="97"/>
       <c r="J38" s="102"/>
@@ -11397,15 +11397,15 @@
       <c r="B39" s="58">
         <v>11</v>
       </c>
-      <c r="C39" s="332" t="s">
+      <c r="C39" s="339" t="s">
         <v>186</v>
       </c>
-      <c r="D39" s="323" t="s">
+      <c r="D39" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E39" s="324"/>
-      <c r="F39" s="324"/>
-      <c r="G39" s="325"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
+      <c r="G39" s="338"/>
       <c r="H39" s="97"/>
       <c r="I39" s="97"/>
       <c r="J39" s="102"/>
@@ -11418,15 +11418,15 @@
       <c r="B40" s="58">
         <v>12</v>
       </c>
-      <c r="C40" s="333"/>
+      <c r="C40" s="340"/>
       <c r="D40" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E40" s="319" t="s">
+      <c r="E40" s="345" t="s">
         <v>128</v>
       </c>
-      <c r="F40" s="320"/>
-      <c r="G40" s="321"/>
+      <c r="F40" s="346"/>
+      <c r="G40" s="347"/>
       <c r="H40" s="72"/>
       <c r="I40" s="72"/>
       <c r="J40" s="81" t="e">
@@ -11442,13 +11442,13 @@
       <c r="B41" s="58">
         <v>13</v>
       </c>
-      <c r="C41" s="349"/>
-      <c r="D41" s="350"/>
-      <c r="E41" s="319" t="s">
+      <c r="C41" s="341"/>
+      <c r="D41" s="351"/>
+      <c r="E41" s="345" t="s">
         <v>129</v>
       </c>
-      <c r="F41" s="320"/>
-      <c r="G41" s="321"/>
+      <c r="F41" s="346"/>
+      <c r="G41" s="347"/>
       <c r="H41" s="72"/>
       <c r="I41" s="72"/>
       <c r="J41" s="81" t="e">
@@ -11464,15 +11464,15 @@
       <c r="B42" s="58">
         <v>14</v>
       </c>
-      <c r="C42" s="332" t="s">
+      <c r="C42" s="339" t="s">
         <v>204</v>
       </c>
-      <c r="D42" s="323" t="s">
+      <c r="D42" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E42" s="324"/>
-      <c r="F42" s="324"/>
-      <c r="G42" s="325"/>
+      <c r="E42" s="337"/>
+      <c r="F42" s="337"/>
+      <c r="G42" s="338"/>
       <c r="H42" s="97"/>
       <c r="I42" s="97"/>
       <c r="J42" s="102"/>
@@ -11485,15 +11485,15 @@
       <c r="B43" s="58">
         <v>15</v>
       </c>
-      <c r="C43" s="333"/>
+      <c r="C43" s="340"/>
       <c r="D43" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="319" t="s">
+      <c r="E43" s="345" t="s">
         <v>128</v>
       </c>
-      <c r="F43" s="320"/>
-      <c r="G43" s="321"/>
+      <c r="F43" s="346"/>
+      <c r="G43" s="347"/>
       <c r="H43" s="72"/>
       <c r="I43" s="72"/>
       <c r="J43" s="81" t="e">
@@ -11509,13 +11509,13 @@
       <c r="B44" s="58">
         <v>16</v>
       </c>
-      <c r="C44" s="349"/>
-      <c r="D44" s="350"/>
-      <c r="E44" s="319" t="s">
+      <c r="C44" s="341"/>
+      <c r="D44" s="351"/>
+      <c r="E44" s="345" t="s">
         <v>129</v>
       </c>
-      <c r="F44" s="320"/>
-      <c r="G44" s="321"/>
+      <c r="F44" s="346"/>
+      <c r="G44" s="347"/>
       <c r="H44" s="72"/>
       <c r="I44" s="72"/>
       <c r="J44" s="81" t="e">
@@ -11531,15 +11531,15 @@
       <c r="B45" s="58">
         <v>17</v>
       </c>
-      <c r="C45" s="332" t="s">
+      <c r="C45" s="339" t="s">
         <v>62</v>
       </c>
-      <c r="D45" s="323" t="s">
+      <c r="D45" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="324"/>
-      <c r="F45" s="324"/>
-      <c r="G45" s="325"/>
+      <c r="E45" s="337"/>
+      <c r="F45" s="337"/>
+      <c r="G45" s="338"/>
       <c r="H45" s="97"/>
       <c r="I45" s="97"/>
       <c r="J45" s="102"/>
@@ -11552,15 +11552,15 @@
       <c r="B46" s="58">
         <v>18</v>
       </c>
-      <c r="C46" s="333"/>
+      <c r="C46" s="340"/>
       <c r="D46" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E46" s="319" t="s">
+      <c r="E46" s="345" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="320"/>
-      <c r="G46" s="321"/>
+      <c r="F46" s="346"/>
+      <c r="G46" s="347"/>
       <c r="H46" s="72"/>
       <c r="I46" s="72"/>
       <c r="J46" s="81" t="e">
@@ -11576,13 +11576,13 @@
       <c r="B47" s="58">
         <v>19</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="319" t="s">
+      <c r="C47" s="341"/>
+      <c r="D47" s="351"/>
+      <c r="E47" s="345" t="s">
         <v>64</v>
       </c>
-      <c r="F47" s="320"/>
-      <c r="G47" s="321"/>
+      <c r="F47" s="346"/>
+      <c r="G47" s="347"/>
       <c r="H47" s="72"/>
       <c r="I47" s="72"/>
       <c r="J47" s="81" t="e">
@@ -11598,15 +11598,15 @@
       <c r="B48" s="58">
         <v>20</v>
       </c>
-      <c r="C48" s="332" t="s">
+      <c r="C48" s="339" t="s">
         <v>205</v>
       </c>
-      <c r="D48" s="323" t="s">
+      <c r="D48" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="324"/>
-      <c r="F48" s="324"/>
-      <c r="G48" s="325"/>
+      <c r="E48" s="337"/>
+      <c r="F48" s="337"/>
+      <c r="G48" s="338"/>
       <c r="H48" s="97"/>
       <c r="I48" s="97"/>
       <c r="J48" s="102"/>
@@ -11619,15 +11619,15 @@
       <c r="B49" s="58">
         <v>21</v>
       </c>
-      <c r="C49" s="333"/>
+      <c r="C49" s="340"/>
       <c r="D49" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="334" t="s">
-        <v>44</v>
-      </c>
-      <c r="F49" s="335"/>
-      <c r="G49" s="335"/>
+      <c r="E49" s="358" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" s="359"/>
+      <c r="G49" s="359"/>
       <c r="H49" s="104"/>
       <c r="I49" s="104"/>
       <c r="J49" s="81"/>
@@ -11646,11 +11646,11 @@
       <c r="D50" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E50" s="319" t="s">
+      <c r="E50" s="345" t="s">
         <v>206</v>
       </c>
-      <c r="F50" s="320"/>
-      <c r="G50" s="321"/>
+      <c r="F50" s="346"/>
+      <c r="G50" s="347"/>
       <c r="H50" s="72"/>
       <c r="I50" s="72"/>
       <c r="J50" s="81" t="e">
@@ -11673,11 +11673,11 @@
       <c r="D51" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E51" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="320"/>
-      <c r="G51" s="321"/>
+      <c r="E51" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="346"/>
+      <c r="G51" s="347"/>
       <c r="H51" s="72"/>
       <c r="I51" s="72"/>
       <c r="J51" s="81"/>
@@ -11691,15 +11691,15 @@
       <c r="B52" s="58">
         <v>24</v>
       </c>
-      <c r="C52" s="332" t="s">
+      <c r="C52" s="339" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="323" t="s">
+      <c r="D52" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E52" s="324"/>
-      <c r="F52" s="324"/>
-      <c r="G52" s="325"/>
+      <c r="E52" s="337"/>
+      <c r="F52" s="337"/>
+      <c r="G52" s="338"/>
       <c r="H52" s="97"/>
       <c r="I52" s="97"/>
       <c r="J52" s="102"/>
@@ -11712,15 +11712,15 @@
       <c r="B53" s="58">
         <v>25</v>
       </c>
-      <c r="C53" s="333"/>
+      <c r="C53" s="340"/>
       <c r="D53" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E53" s="319" t="s">
+      <c r="E53" s="345" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="320"/>
-      <c r="G53" s="321"/>
+      <c r="F53" s="346"/>
+      <c r="G53" s="347"/>
       <c r="H53" s="72"/>
       <c r="I53" s="72"/>
       <c r="J53" s="81"/>
@@ -11739,11 +11739,11 @@
       <c r="D54" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E54" s="319" t="s">
+      <c r="E54" s="345" t="s">
         <v>207</v>
       </c>
-      <c r="F54" s="320"/>
-      <c r="G54" s="321"/>
+      <c r="F54" s="346"/>
+      <c r="G54" s="347"/>
       <c r="H54" s="72"/>
       <c r="I54" s="72"/>
       <c r="J54" s="81" t="e">
@@ -11760,15 +11760,15 @@
       <c r="B55" s="58">
         <v>30</v>
       </c>
-      <c r="C55" s="332" t="s">
+      <c r="C55" s="339" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="323" t="s">
+      <c r="D55" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="324"/>
-      <c r="F55" s="324"/>
-      <c r="G55" s="325"/>
+      <c r="E55" s="337"/>
+      <c r="F55" s="337"/>
+      <c r="G55" s="338"/>
       <c r="H55" s="97"/>
       <c r="I55" s="97"/>
       <c r="J55" s="102"/>
@@ -11781,15 +11781,15 @@
       <c r="B56" s="58">
         <v>31</v>
       </c>
-      <c r="C56" s="333"/>
+      <c r="C56" s="340"/>
       <c r="D56" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="319" t="s">
+      <c r="E56" s="345" t="s">
         <v>146</v>
       </c>
-      <c r="F56" s="320"/>
-      <c r="G56" s="321"/>
+      <c r="F56" s="346"/>
+      <c r="G56" s="347"/>
       <c r="H56" s="72"/>
       <c r="I56" s="72"/>
       <c r="J56" s="81"/>
@@ -11802,15 +11802,15 @@
       <c r="B57" s="58">
         <v>32</v>
       </c>
-      <c r="C57" s="333"/>
+      <c r="C57" s="340"/>
       <c r="D57" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="319" t="s">
+      <c r="E57" s="345" t="s">
         <v>147</v>
       </c>
-      <c r="F57" s="320"/>
-      <c r="G57" s="321"/>
+      <c r="F57" s="346"/>
+      <c r="G57" s="347"/>
       <c r="H57" s="72"/>
       <c r="I57" s="72"/>
       <c r="J57" s="81"/>
@@ -11829,11 +11829,11 @@
       <c r="D58" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="319" t="s">
+      <c r="E58" s="345" t="s">
         <v>148</v>
       </c>
-      <c r="F58" s="320"/>
-      <c r="G58" s="321"/>
+      <c r="F58" s="346"/>
+      <c r="G58" s="347"/>
       <c r="H58" s="72"/>
       <c r="I58" s="72"/>
       <c r="J58" s="81"/>
@@ -11852,11 +11852,11 @@
       <c r="D59" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E59" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F59" s="320"/>
-      <c r="G59" s="321"/>
+      <c r="E59" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F59" s="346"/>
+      <c r="G59" s="347"/>
       <c r="H59" s="72"/>
       <c r="I59" s="72"/>
       <c r="J59" s="81"/>
@@ -11870,15 +11870,15 @@
       <c r="B60" s="58">
         <v>35</v>
       </c>
-      <c r="C60" s="332" t="s">
+      <c r="C60" s="339" t="s">
         <v>190</v>
       </c>
-      <c r="D60" s="323" t="s">
+      <c r="D60" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E60" s="324"/>
-      <c r="F60" s="324"/>
-      <c r="G60" s="325"/>
+      <c r="E60" s="337"/>
+      <c r="F60" s="337"/>
+      <c r="G60" s="338"/>
       <c r="H60" s="97"/>
       <c r="I60" s="97"/>
       <c r="J60" s="102"/>
@@ -11891,15 +11891,15 @@
       <c r="B61" s="58">
         <v>36</v>
       </c>
-      <c r="C61" s="333"/>
+      <c r="C61" s="340"/>
       <c r="D61" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E61" s="319" t="s">
+      <c r="E61" s="345" t="s">
         <v>128</v>
       </c>
-      <c r="F61" s="320"/>
-      <c r="G61" s="321"/>
+      <c r="F61" s="346"/>
+      <c r="G61" s="347"/>
       <c r="H61" s="72"/>
       <c r="I61" s="72"/>
       <c r="J61" s="81"/>
@@ -11912,15 +11912,15 @@
       <c r="B62" s="58">
         <v>37</v>
       </c>
-      <c r="C62" s="333"/>
+      <c r="C62" s="340"/>
       <c r="D62" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E62" s="319" t="s">
+      <c r="E62" s="345" t="s">
         <v>154</v>
       </c>
-      <c r="F62" s="320"/>
-      <c r="G62" s="321"/>
+      <c r="F62" s="346"/>
+      <c r="G62" s="347"/>
       <c r="H62" s="72"/>
       <c r="I62" s="72"/>
       <c r="J62" s="81"/>
@@ -11939,11 +11939,11 @@
       <c r="D63" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E63" s="319" t="s">
+      <c r="E63" s="345" t="s">
         <v>208</v>
       </c>
-      <c r="F63" s="320"/>
-      <c r="G63" s="321"/>
+      <c r="F63" s="346"/>
+      <c r="G63" s="347"/>
       <c r="H63" s="72"/>
       <c r="I63" s="72"/>
       <c r="J63" s="81"/>
@@ -11962,11 +11962,11 @@
       <c r="D64" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E64" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F64" s="320"/>
-      <c r="G64" s="321"/>
+      <c r="E64" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F64" s="346"/>
+      <c r="G64" s="347"/>
       <c r="H64" s="72"/>
       <c r="I64" s="72"/>
       <c r="J64" s="81"/>
@@ -11980,15 +11980,15 @@
       <c r="B65" s="58">
         <v>40</v>
       </c>
-      <c r="C65" s="332" t="s">
+      <c r="C65" s="339" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="323" t="s">
+      <c r="D65" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E65" s="324"/>
-      <c r="F65" s="324"/>
-      <c r="G65" s="325"/>
+      <c r="E65" s="337"/>
+      <c r="F65" s="337"/>
+      <c r="G65" s="338"/>
       <c r="H65" s="97"/>
       <c r="I65" s="97"/>
       <c r="J65" s="102"/>
@@ -12001,17 +12001,17 @@
       <c r="B66" s="58">
         <v>41</v>
       </c>
-      <c r="C66" s="333"/>
+      <c r="C66" s="340"/>
       <c r="D66" s="66" t="s">
         <v>55</v>
       </c>
       <c r="E66" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="F66" s="323" t="s">
+      <c r="F66" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G66" s="325"/>
+      <c r="G66" s="338"/>
       <c r="H66" s="97"/>
       <c r="I66" s="97"/>
       <c r="J66" s="102"/>
@@ -12024,7 +12024,7 @@
       <c r="B67" s="58">
         <v>42</v>
       </c>
-      <c r="C67" s="333"/>
+      <c r="C67" s="340"/>
       <c r="D67" s="67" t="s">
         <v>44</v>
       </c>
@@ -12117,10 +12117,10 @@
       <c r="E70" s="103" t="s">
         <v>210</v>
       </c>
-      <c r="F70" s="323" t="s">
+      <c r="F70" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G70" s="325"/>
+      <c r="G70" s="338"/>
       <c r="H70" s="97"/>
       <c r="I70" s="97"/>
       <c r="J70" s="102"/>
@@ -12289,10 +12289,10 @@
       <c r="E76" s="103" t="s">
         <v>214</v>
       </c>
-      <c r="F76" s="323" t="s">
+      <c r="F76" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G76" s="325"/>
+      <c r="G76" s="338"/>
       <c r="H76" s="97"/>
       <c r="I76" s="97"/>
       <c r="J76" s="102"/>
@@ -12394,13 +12394,13 @@
       <c r="D80" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E80" s="344" t="s">
+      <c r="E80" s="360" t="s">
         <v>216</v>
       </c>
-      <c r="F80" s="323" t="s">
+      <c r="F80" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G80" s="325"/>
+      <c r="G80" s="338"/>
       <c r="H80" s="97"/>
       <c r="I80" s="97"/>
       <c r="J80" s="102"/>
@@ -12420,15 +12420,15 @@
       <c r="D81" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E81" s="345"/>
+      <c r="E81" s="361"/>
       <c r="F81" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="G81" s="346" t="s">
+      <c r="G81" s="362" t="s">
         <v>136</v>
       </c>
-      <c r="H81" s="347"/>
-      <c r="I81" s="348"/>
+      <c r="H81" s="363"/>
+      <c r="I81" s="364"/>
       <c r="J81" s="81" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -12507,13 +12507,13 @@
       <c r="D84" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E84" s="344" t="s">
-        <v>44</v>
-      </c>
-      <c r="F84" s="323" t="s">
+      <c r="E84" s="360" t="s">
+        <v>44</v>
+      </c>
+      <c r="F84" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G84" s="325"/>
+      <c r="G84" s="338"/>
       <c r="H84" s="97"/>
       <c r="I84" s="97"/>
       <c r="J84" s="102"/>
@@ -12533,7 +12533,7 @@
       <c r="D85" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E85" s="345"/>
+      <c r="E85" s="361"/>
       <c r="F85" s="66" t="s">
         <v>55</v>
       </c>
@@ -12582,15 +12582,15 @@
       <c r="B87" s="58">
         <v>62</v>
       </c>
-      <c r="C87" s="332" t="s">
+      <c r="C87" s="339" t="s">
         <v>144</v>
       </c>
-      <c r="D87" s="323" t="s">
+      <c r="D87" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E87" s="324"/>
-      <c r="F87" s="324"/>
-      <c r="G87" s="325"/>
+      <c r="E87" s="337"/>
+      <c r="F87" s="337"/>
+      <c r="G87" s="338"/>
       <c r="H87" s="97"/>
       <c r="I87" s="110"/>
       <c r="J87" s="102"/>
@@ -12603,15 +12603,15 @@
       <c r="B88" s="58">
         <v>63</v>
       </c>
-      <c r="C88" s="333"/>
+      <c r="C88" s="340"/>
       <c r="D88" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E88" s="334" t="s">
-        <v>44</v>
-      </c>
-      <c r="F88" s="335"/>
-      <c r="G88" s="335"/>
+      <c r="E88" s="358" t="s">
+        <v>44</v>
+      </c>
+      <c r="F88" s="359"/>
+      <c r="G88" s="359"/>
       <c r="H88" s="104"/>
       <c r="I88" s="104"/>
       <c r="J88" s="81" t="e">
@@ -12633,11 +12633,11 @@
       <c r="D89" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F89" s="320"/>
-      <c r="G89" s="321"/>
+      <c r="E89" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F89" s="346"/>
+      <c r="G89" s="347"/>
       <c r="H89" s="72"/>
       <c r="I89" s="109"/>
       <c r="J89" s="81"/>
@@ -12657,11 +12657,11 @@
       <c r="D90" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E90" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F90" s="320"/>
-      <c r="G90" s="321"/>
+      <c r="E90" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F90" s="346"/>
+      <c r="G90" s="347"/>
       <c r="H90" s="72"/>
       <c r="I90" s="109"/>
       <c r="J90" s="81"/>
@@ -12675,15 +12675,15 @@
       <c r="B91" s="58">
         <v>66</v>
       </c>
-      <c r="C91" s="332" t="s">
+      <c r="C91" s="339" t="s">
         <v>189</v>
       </c>
-      <c r="D91" s="323" t="s">
+      <c r="D91" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="324"/>
-      <c r="F91" s="324"/>
-      <c r="G91" s="325"/>
+      <c r="E91" s="337"/>
+      <c r="F91" s="337"/>
+      <c r="G91" s="338"/>
       <c r="H91" s="97"/>
       <c r="I91" s="110"/>
       <c r="J91" s="102"/>
@@ -12696,15 +12696,15 @@
       <c r="B92" s="58">
         <v>67</v>
       </c>
-      <c r="C92" s="333"/>
+      <c r="C92" s="340"/>
       <c r="D92" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E92" s="334" t="s">
-        <v>44</v>
-      </c>
-      <c r="F92" s="335"/>
-      <c r="G92" s="335"/>
+      <c r="E92" s="358" t="s">
+        <v>44</v>
+      </c>
+      <c r="F92" s="359"/>
+      <c r="G92" s="359"/>
       <c r="H92" s="104"/>
       <c r="I92" s="104"/>
       <c r="J92" s="81"/>
@@ -12723,11 +12723,11 @@
       <c r="D93" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F93" s="320"/>
-      <c r="G93" s="321"/>
+      <c r="E93" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F93" s="346"/>
+      <c r="G93" s="347"/>
       <c r="H93" s="72"/>
       <c r="I93" s="109"/>
       <c r="J93" s="81"/>
@@ -12747,11 +12747,11 @@
       <c r="D94" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E94" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F94" s="320"/>
-      <c r="G94" s="321"/>
+      <c r="E94" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F94" s="346"/>
+      <c r="G94" s="347"/>
       <c r="H94" s="72"/>
       <c r="I94" s="109"/>
       <c r="J94" s="81"/>
@@ -12765,15 +12765,15 @@
       <c r="B95" s="58">
         <v>70</v>
       </c>
-      <c r="C95" s="332" t="s">
+      <c r="C95" s="339" t="s">
         <v>137</v>
       </c>
-      <c r="D95" s="323" t="s">
+      <c r="D95" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E95" s="324"/>
-      <c r="F95" s="324"/>
-      <c r="G95" s="325"/>
+      <c r="E95" s="337"/>
+      <c r="F95" s="337"/>
+      <c r="G95" s="338"/>
       <c r="H95" s="97"/>
       <c r="I95" s="110"/>
       <c r="J95" s="102"/>
@@ -12786,15 +12786,15 @@
       <c r="B96" s="58">
         <v>71</v>
       </c>
-      <c r="C96" s="333"/>
+      <c r="C96" s="340"/>
       <c r="D96" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E96" s="334" t="s">
-        <v>44</v>
-      </c>
-      <c r="F96" s="335"/>
-      <c r="G96" s="335"/>
+      <c r="E96" s="358" t="s">
+        <v>44</v>
+      </c>
+      <c r="F96" s="359"/>
+      <c r="G96" s="359"/>
       <c r="H96" s="104"/>
       <c r="I96" s="104"/>
       <c r="J96" s="81"/>
@@ -12813,11 +12813,11 @@
       <c r="D97" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E97" s="319" t="s">
+      <c r="E97" s="345" t="s">
         <v>217</v>
       </c>
-      <c r="F97" s="320"/>
-      <c r="G97" s="321"/>
+      <c r="F97" s="346"/>
+      <c r="G97" s="347"/>
       <c r="H97" s="72"/>
       <c r="I97" s="109"/>
       <c r="J97" s="81" t="e">
@@ -12832,11 +12832,11 @@
       <c r="B98" s="58"/>
       <c r="C98" s="77"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="319" t="s">
+      <c r="E98" s="345" t="s">
         <v>218</v>
       </c>
-      <c r="F98" s="320"/>
-      <c r="G98" s="321"/>
+      <c r="F98" s="346"/>
+      <c r="G98" s="347"/>
       <c r="H98" s="72"/>
       <c r="I98" s="109"/>
       <c r="J98" s="81"/>
@@ -12848,9 +12848,9 @@
       <c r="B99" s="58"/>
       <c r="C99" s="77"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="319"/>
-      <c r="F99" s="320"/>
-      <c r="G99" s="321"/>
+      <c r="E99" s="345"/>
+      <c r="F99" s="346"/>
+      <c r="G99" s="347"/>
       <c r="H99" s="72"/>
       <c r="I99" s="109"/>
       <c r="J99" s="81"/>
@@ -12870,11 +12870,11 @@
       <c r="D100" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E100" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F100" s="320"/>
-      <c r="G100" s="321"/>
+      <c r="E100" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F100" s="346"/>
+      <c r="G100" s="347"/>
       <c r="H100" s="72"/>
       <c r="I100" s="109"/>
       <c r="J100" s="81"/>
@@ -12888,15 +12888,15 @@
       <c r="B101" s="58">
         <v>75</v>
       </c>
-      <c r="C101" s="332" t="s">
+      <c r="C101" s="339" t="s">
         <v>17</v>
       </c>
-      <c r="D101" s="323" t="s">
+      <c r="D101" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E101" s="324"/>
-      <c r="F101" s="324"/>
-      <c r="G101" s="325"/>
+      <c r="E101" s="337"/>
+      <c r="F101" s="337"/>
+      <c r="G101" s="338"/>
       <c r="H101" s="97"/>
       <c r="I101" s="111">
         <f>I102+I103+I104</f>
@@ -12912,15 +12912,15 @@
       <c r="B102" s="58">
         <v>76</v>
       </c>
-      <c r="C102" s="333"/>
+      <c r="C102" s="340"/>
       <c r="D102" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E102" s="336" t="s">
+      <c r="E102" s="355" t="s">
         <v>219</v>
       </c>
-      <c r="F102" s="337"/>
-      <c r="G102" s="338"/>
+      <c r="F102" s="356"/>
+      <c r="G102" s="357"/>
       <c r="H102" s="72"/>
       <c r="I102" s="109"/>
       <c r="J102" s="81">
@@ -12936,15 +12936,15 @@
       <c r="B103" s="58">
         <v>77</v>
       </c>
-      <c r="C103" s="333"/>
+      <c r="C103" s="340"/>
       <c r="D103" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E103" s="336" t="s">
+      <c r="E103" s="355" t="s">
         <v>220</v>
       </c>
-      <c r="F103" s="337"/>
-      <c r="G103" s="338"/>
+      <c r="F103" s="356"/>
+      <c r="G103" s="357"/>
       <c r="H103" s="72"/>
       <c r="I103" s="72"/>
       <c r="J103" s="81">
@@ -12966,11 +12966,11 @@
       <c r="D104" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E104" s="336" t="s">
+      <c r="E104" s="355" t="s">
         <v>221</v>
       </c>
-      <c r="F104" s="337"/>
-      <c r="G104" s="338"/>
+      <c r="F104" s="356"/>
+      <c r="G104" s="357"/>
       <c r="H104" s="72"/>
       <c r="I104" s="72"/>
       <c r="J104" s="81">
@@ -12986,13 +12986,13 @@
       <c r="B105" s="58">
         <v>83</v>
       </c>
-      <c r="C105" s="323" t="s">
+      <c r="C105" s="336" t="s">
         <v>7</v>
       </c>
-      <c r="D105" s="324"/>
-      <c r="E105" s="324"/>
-      <c r="F105" s="324"/>
-      <c r="G105" s="325"/>
+      <c r="D105" s="337"/>
+      <c r="E105" s="337"/>
+      <c r="F105" s="337"/>
+      <c r="G105" s="338"/>
       <c r="H105" s="97"/>
       <c r="I105" s="97"/>
       <c r="J105" s="102" t="e">
@@ -13008,13 +13008,13 @@
       <c r="B106" s="58">
         <v>84</v>
       </c>
-      <c r="C106" s="323" t="s">
+      <c r="C106" s="336" t="s">
         <v>222</v>
       </c>
-      <c r="D106" s="324"/>
-      <c r="E106" s="324"/>
-      <c r="F106" s="324"/>
-      <c r="G106" s="325"/>
+      <c r="D106" s="337"/>
+      <c r="E106" s="337"/>
+      <c r="F106" s="337"/>
+      <c r="G106" s="338"/>
       <c r="H106" s="97"/>
       <c r="I106" s="101"/>
       <c r="J106" s="102" t="e">
@@ -13030,15 +13030,15 @@
       <c r="B107" s="58">
         <v>85</v>
       </c>
-      <c r="C107" s="332" t="s">
+      <c r="C107" s="339" t="s">
         <v>223</v>
       </c>
-      <c r="D107" s="323" t="s">
+      <c r="D107" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E107" s="324"/>
-      <c r="F107" s="324"/>
-      <c r="G107" s="325"/>
+      <c r="E107" s="337"/>
+      <c r="F107" s="337"/>
+      <c r="G107" s="338"/>
       <c r="H107" s="97"/>
       <c r="I107" s="97"/>
       <c r="J107" s="102"/>
@@ -13051,15 +13051,15 @@
       <c r="B108" s="58">
         <v>86</v>
       </c>
-      <c r="C108" s="333"/>
+      <c r="C108" s="340"/>
       <c r="D108" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E108" s="336" t="s">
+      <c r="E108" s="355" t="s">
         <v>224</v>
       </c>
-      <c r="F108" s="337"/>
-      <c r="G108" s="338"/>
+      <c r="F108" s="356"/>
+      <c r="G108" s="357"/>
       <c r="H108" s="72"/>
       <c r="I108" s="63"/>
       <c r="J108" s="81" t="e">
@@ -13081,11 +13081,11 @@
       <c r="D109" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E109" s="319" t="s">
+      <c r="E109" s="345" t="s">
         <v>225</v>
       </c>
-      <c r="F109" s="320"/>
-      <c r="G109" s="321"/>
+      <c r="F109" s="346"/>
+      <c r="G109" s="347"/>
       <c r="H109" s="72"/>
       <c r="I109" s="63"/>
       <c r="J109" s="81"/>
@@ -13105,11 +13105,11 @@
       <c r="D110" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E110" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F110" s="320"/>
-      <c r="G110" s="321"/>
+      <c r="E110" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F110" s="346"/>
+      <c r="G110" s="347"/>
       <c r="H110" s="72"/>
       <c r="I110" s="72"/>
       <c r="J110" s="81"/>
@@ -13123,15 +13123,15 @@
       <c r="B111" s="58">
         <v>89</v>
       </c>
-      <c r="C111" s="332" t="s">
+      <c r="C111" s="339" t="s">
         <v>192</v>
       </c>
-      <c r="D111" s="323" t="s">
+      <c r="D111" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E111" s="324"/>
-      <c r="F111" s="324"/>
-      <c r="G111" s="325"/>
+      <c r="E111" s="337"/>
+      <c r="F111" s="337"/>
+      <c r="G111" s="338"/>
       <c r="H111" s="97"/>
       <c r="I111" s="97"/>
       <c r="J111" s="102"/>
@@ -13144,15 +13144,15 @@
       <c r="B112" s="58">
         <v>90</v>
       </c>
-      <c r="C112" s="333"/>
+      <c r="C112" s="340"/>
       <c r="D112" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E112" s="336" t="s">
+      <c r="E112" s="355" t="s">
         <v>226</v>
       </c>
-      <c r="F112" s="337"/>
-      <c r="G112" s="338"/>
+      <c r="F112" s="356"/>
+      <c r="G112" s="357"/>
       <c r="H112" s="72"/>
       <c r="I112" s="72"/>
       <c r="J112" s="81"/>
@@ -13171,11 +13171,11 @@
       <c r="D113" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E113" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F113" s="320"/>
-      <c r="G113" s="321"/>
+      <c r="E113" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F113" s="346"/>
+      <c r="G113" s="347"/>
       <c r="H113" s="72"/>
       <c r="I113" s="72"/>
       <c r="J113" s="81"/>
@@ -13188,15 +13188,15 @@
       <c r="B114" s="58">
         <v>92</v>
       </c>
-      <c r="C114" s="332" t="s">
+      <c r="C114" s="339" t="s">
         <v>191</v>
       </c>
-      <c r="D114" s="323" t="s">
+      <c r="D114" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E114" s="324"/>
-      <c r="F114" s="324"/>
-      <c r="G114" s="325"/>
+      <c r="E114" s="337"/>
+      <c r="F114" s="337"/>
+      <c r="G114" s="338"/>
       <c r="H114" s="97"/>
       <c r="I114" s="97"/>
       <c r="J114" s="102"/>
@@ -13209,15 +13209,15 @@
       <c r="B115" s="58">
         <v>93</v>
       </c>
-      <c r="C115" s="333"/>
+      <c r="C115" s="340"/>
       <c r="D115" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E115" s="334" t="s">
-        <v>44</v>
-      </c>
-      <c r="F115" s="335"/>
-      <c r="G115" s="335"/>
+      <c r="E115" s="358" t="s">
+        <v>44</v>
+      </c>
+      <c r="F115" s="359"/>
+      <c r="G115" s="359"/>
       <c r="H115" s="104"/>
       <c r="I115" s="104"/>
       <c r="J115" s="112"/>
@@ -13236,11 +13236,11 @@
       <c r="D116" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E116" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F116" s="320"/>
-      <c r="G116" s="321"/>
+      <c r="E116" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F116" s="346"/>
+      <c r="G116" s="347"/>
       <c r="H116" s="72"/>
       <c r="I116" s="63"/>
       <c r="J116" s="81"/>
@@ -13260,11 +13260,11 @@
       <c r="D117" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E117" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F117" s="320"/>
-      <c r="G117" s="321"/>
+      <c r="E117" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F117" s="346"/>
+      <c r="G117" s="347"/>
       <c r="H117" s="72"/>
       <c r="I117" s="72"/>
       <c r="J117" s="81"/>
@@ -13278,15 +13278,15 @@
       <c r="B118" s="58">
         <v>96</v>
       </c>
-      <c r="C118" s="332" t="s">
+      <c r="C118" s="339" t="s">
         <v>149</v>
       </c>
-      <c r="D118" s="323" t="s">
+      <c r="D118" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E118" s="324"/>
-      <c r="F118" s="324"/>
-      <c r="G118" s="325"/>
+      <c r="E118" s="337"/>
+      <c r="F118" s="337"/>
+      <c r="G118" s="338"/>
       <c r="H118" s="97"/>
       <c r="I118" s="97"/>
       <c r="J118" s="102"/>
@@ -13299,15 +13299,15 @@
       <c r="B119" s="58">
         <v>97</v>
       </c>
-      <c r="C119" s="333"/>
+      <c r="C119" s="340"/>
       <c r="D119" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E119" s="336" t="s">
+      <c r="E119" s="355" t="s">
         <v>227</v>
       </c>
-      <c r="F119" s="337"/>
-      <c r="G119" s="338"/>
+      <c r="F119" s="356"/>
+      <c r="G119" s="357"/>
       <c r="H119" s="72"/>
       <c r="I119" s="72"/>
       <c r="J119" s="81"/>
@@ -13326,11 +13326,11 @@
       <c r="D120" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E120" s="336" t="s">
+      <c r="E120" s="355" t="s">
         <v>228</v>
       </c>
-      <c r="F120" s="337"/>
-      <c r="G120" s="338"/>
+      <c r="F120" s="356"/>
+      <c r="G120" s="357"/>
       <c r="H120" s="72"/>
       <c r="I120" s="72"/>
       <c r="J120" s="81"/>
@@ -13349,11 +13349,11 @@
       <c r="D121" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E121" s="336" t="s">
+      <c r="E121" s="355" t="s">
         <v>229</v>
       </c>
-      <c r="F121" s="337"/>
-      <c r="G121" s="338"/>
+      <c r="F121" s="356"/>
+      <c r="G121" s="357"/>
       <c r="H121" s="72"/>
       <c r="I121" s="72"/>
       <c r="J121" s="81"/>
@@ -13372,11 +13372,11 @@
       <c r="D122" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E122" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F122" s="320"/>
-      <c r="G122" s="321"/>
+      <c r="E122" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F122" s="346"/>
+      <c r="G122" s="347"/>
       <c r="H122" s="72"/>
       <c r="I122" s="72"/>
       <c r="J122" s="81"/>
@@ -13390,15 +13390,15 @@
       <c r="B123" s="58">
         <v>101</v>
       </c>
-      <c r="C123" s="332" t="s">
+      <c r="C123" s="339" t="s">
         <v>230</v>
       </c>
-      <c r="D123" s="323" t="s">
+      <c r="D123" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E123" s="324"/>
-      <c r="F123" s="324"/>
-      <c r="G123" s="325"/>
+      <c r="E123" s="337"/>
+      <c r="F123" s="337"/>
+      <c r="G123" s="338"/>
       <c r="H123" s="97"/>
       <c r="I123" s="97"/>
       <c r="J123" s="102"/>
@@ -13411,17 +13411,17 @@
       <c r="B124" s="58">
         <v>102</v>
       </c>
-      <c r="C124" s="333"/>
+      <c r="C124" s="340"/>
       <c r="D124" s="66" t="s">
         <v>55</v>
       </c>
       <c r="E124" s="342" t="s">
         <v>231</v>
       </c>
-      <c r="F124" s="323" t="s">
+      <c r="F124" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G124" s="325"/>
+      <c r="G124" s="338"/>
       <c r="H124" s="97"/>
       <c r="I124" s="97"/>
       <c r="J124" s="102"/>
@@ -13434,7 +13434,7 @@
       <c r="B125" s="58">
         <v>103</v>
       </c>
-      <c r="C125" s="333"/>
+      <c r="C125" s="340"/>
       <c r="D125" s="67" t="s">
         <v>44</v>
       </c>
@@ -13457,7 +13457,7 @@
       <c r="B126" s="58">
         <v>104</v>
       </c>
-      <c r="C126" s="333"/>
+      <c r="C126" s="340"/>
       <c r="D126" s="67" t="s">
         <v>44</v>
       </c>
@@ -13543,11 +13543,11 @@
       <c r="D129" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E129" s="336" t="s">
+      <c r="E129" s="355" t="s">
         <v>234</v>
       </c>
-      <c r="F129" s="337"/>
-      <c r="G129" s="338"/>
+      <c r="F129" s="356"/>
+      <c r="G129" s="357"/>
       <c r="H129" s="72"/>
       <c r="I129" s="72"/>
       <c r="J129" s="81"/>
@@ -13566,11 +13566,11 @@
       <c r="D130" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E130" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F130" s="320"/>
-      <c r="G130" s="321"/>
+      <c r="E130" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F130" s="346"/>
+      <c r="G130" s="347"/>
       <c r="H130" s="72"/>
       <c r="I130" s="72"/>
       <c r="J130" s="81"/>
@@ -13584,15 +13584,15 @@
       <c r="B131" s="58">
         <v>109</v>
       </c>
-      <c r="C131" s="332" t="s">
+      <c r="C131" s="339" t="s">
         <v>175</v>
       </c>
-      <c r="D131" s="323" t="s">
+      <c r="D131" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E131" s="324"/>
-      <c r="F131" s="324"/>
-      <c r="G131" s="325"/>
+      <c r="E131" s="337"/>
+      <c r="F131" s="337"/>
+      <c r="G131" s="338"/>
       <c r="H131" s="97"/>
       <c r="I131" s="101">
         <f>SUM(I132:I136)</f>
@@ -13608,15 +13608,15 @@
       <c r="B132" s="58">
         <v>110</v>
       </c>
-      <c r="C132" s="333"/>
+      <c r="C132" s="340"/>
       <c r="D132" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E132" s="336" t="s">
+      <c r="E132" s="355" t="s">
         <v>91</v>
       </c>
-      <c r="F132" s="337"/>
-      <c r="G132" s="338"/>
+      <c r="F132" s="356"/>
+      <c r="G132" s="357"/>
       <c r="H132" s="72"/>
       <c r="I132" s="72"/>
       <c r="J132" s="81" t="e">
@@ -13632,15 +13632,15 @@
       <c r="B133" s="58">
         <v>111</v>
       </c>
-      <c r="C133" s="333"/>
+      <c r="C133" s="340"/>
       <c r="D133" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E133" s="336" t="s">
+      <c r="E133" s="355" t="s">
         <v>235</v>
       </c>
-      <c r="F133" s="337"/>
-      <c r="G133" s="338"/>
+      <c r="F133" s="356"/>
+      <c r="G133" s="357"/>
       <c r="H133" s="72"/>
       <c r="I133" s="72"/>
       <c r="J133" s="81" t="e">
@@ -13662,11 +13662,11 @@
       <c r="D134" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E134" s="336" t="s">
+      <c r="E134" s="355" t="s">
         <v>11</v>
       </c>
-      <c r="F134" s="337"/>
-      <c r="G134" s="338"/>
+      <c r="F134" s="356"/>
+      <c r="G134" s="357"/>
       <c r="H134" s="72"/>
       <c r="I134" s="72"/>
       <c r="J134" s="81" t="e">
@@ -13688,11 +13688,11 @@
       <c r="D135" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E135" s="336" t="s">
+      <c r="E135" s="355" t="s">
         <v>9</v>
       </c>
-      <c r="F135" s="337"/>
-      <c r="G135" s="338"/>
+      <c r="F135" s="356"/>
+      <c r="G135" s="357"/>
       <c r="H135" s="72"/>
       <c r="I135" s="72"/>
       <c r="J135" s="81" t="e">
@@ -13714,11 +13714,11 @@
       <c r="D136" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E136" s="329" t="s">
+      <c r="E136" s="352" t="s">
         <v>236</v>
       </c>
-      <c r="F136" s="329"/>
-      <c r="G136" s="329"/>
+      <c r="F136" s="352"/>
+      <c r="G136" s="352"/>
       <c r="H136" s="72"/>
       <c r="I136" s="72"/>
       <c r="J136" s="81" t="e">
@@ -13741,11 +13741,11 @@
       <c r="D137" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E137" s="339" t="s">
-        <v>44</v>
-      </c>
-      <c r="F137" s="340"/>
-      <c r="G137" s="341"/>
+      <c r="E137" s="365" t="s">
+        <v>44</v>
+      </c>
+      <c r="F137" s="366"/>
+      <c r="G137" s="367"/>
       <c r="H137" s="115"/>
       <c r="I137" s="115"/>
       <c r="J137" s="116"/>
@@ -13759,15 +13759,15 @@
       <c r="B138" s="58">
         <v>118</v>
       </c>
-      <c r="C138" s="332" t="s">
+      <c r="C138" s="339" t="s">
         <v>237</v>
       </c>
-      <c r="D138" s="323" t="s">
+      <c r="D138" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E138" s="324"/>
-      <c r="F138" s="324"/>
-      <c r="G138" s="325"/>
+      <c r="E138" s="337"/>
+      <c r="F138" s="337"/>
+      <c r="G138" s="338"/>
       <c r="H138" s="97"/>
       <c r="I138" s="117"/>
       <c r="J138" s="118"/>
@@ -13780,15 +13780,15 @@
       <c r="B139" s="58">
         <v>119</v>
       </c>
-      <c r="C139" s="333"/>
+      <c r="C139" s="340"/>
       <c r="D139" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E139" s="336" t="s">
+      <c r="E139" s="355" t="s">
         <v>19</v>
       </c>
-      <c r="F139" s="337"/>
-      <c r="G139" s="338"/>
+      <c r="F139" s="356"/>
+      <c r="G139" s="357"/>
       <c r="H139" s="109"/>
       <c r="I139" s="113"/>
       <c r="J139" s="81" t="e">
@@ -13813,10 +13813,10 @@
       <c r="E140" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="F140" s="323" t="s">
+      <c r="F140" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G140" s="325"/>
+      <c r="G140" s="338"/>
       <c r="H140" s="110"/>
       <c r="I140" s="97"/>
       <c r="J140" s="102"/>
@@ -13838,7 +13838,7 @@
       <c r="E141" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F141" s="330" t="s">
+      <c r="F141" s="372" t="s">
         <v>55</v>
       </c>
       <c r="G141" s="108" t="s">
@@ -13865,7 +13865,7 @@
       <c r="E142" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F142" s="331"/>
+      <c r="F142" s="373"/>
       <c r="G142" s="60" t="s">
         <v>238</v>
       </c>
@@ -13916,10 +13916,10 @@
       <c r="E144" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="F144" s="323" t="s">
+      <c r="F144" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G144" s="325"/>
+      <c r="G144" s="338"/>
       <c r="H144" s="97"/>
       <c r="I144" s="110"/>
       <c r="J144" s="102"/>
@@ -13941,7 +13941,7 @@
       <c r="E145" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F145" s="330" t="s">
+      <c r="F145" s="372" t="s">
         <v>55</v>
       </c>
       <c r="G145" s="108" t="s">
@@ -13968,7 +13968,7 @@
       <c r="E146" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F146" s="331"/>
+      <c r="F146" s="373"/>
       <c r="G146" s="60" t="s">
         <v>18</v>
       </c>
@@ -14038,15 +14038,15 @@
       <c r="B149" s="58">
         <v>129</v>
       </c>
-      <c r="C149" s="332" t="s">
+      <c r="C149" s="339" t="s">
         <v>239</v>
       </c>
-      <c r="D149" s="323" t="s">
+      <c r="D149" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E149" s="324"/>
-      <c r="F149" s="324"/>
-      <c r="G149" s="325"/>
+      <c r="E149" s="337"/>
+      <c r="F149" s="337"/>
+      <c r="G149" s="338"/>
       <c r="H149" s="97"/>
       <c r="I149" s="110"/>
       <c r="J149" s="102"/>
@@ -14059,15 +14059,15 @@
       <c r="B150" s="121">
         <v>130</v>
       </c>
-      <c r="C150" s="333"/>
+      <c r="C150" s="340"/>
       <c r="D150" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E150" s="334" t="s">
-        <v>44</v>
-      </c>
-      <c r="F150" s="335"/>
-      <c r="G150" s="335"/>
+      <c r="E150" s="358" t="s">
+        <v>44</v>
+      </c>
+      <c r="F150" s="359"/>
+      <c r="G150" s="359"/>
       <c r="H150" s="104"/>
       <c r="I150" s="104"/>
       <c r="J150" s="81"/>
@@ -14086,11 +14086,11 @@
       <c r="D151" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E151" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F151" s="320"/>
-      <c r="G151" s="321"/>
+      <c r="E151" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F151" s="346"/>
+      <c r="G151" s="347"/>
       <c r="H151" s="72"/>
       <c r="I151" s="109"/>
       <c r="J151" s="81"/>
@@ -14104,15 +14104,15 @@
       <c r="B152" s="58">
         <v>132</v>
       </c>
-      <c r="C152" s="322" t="s">
+      <c r="C152" s="368" t="s">
         <v>240</v>
       </c>
-      <c r="D152" s="323" t="s">
+      <c r="D152" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E152" s="324"/>
-      <c r="F152" s="324"/>
-      <c r="G152" s="325"/>
+      <c r="E152" s="337"/>
+      <c r="F152" s="337"/>
+      <c r="G152" s="338"/>
       <c r="H152" s="97"/>
       <c r="I152" s="110"/>
       <c r="J152" s="102"/>
@@ -14125,15 +14125,15 @@
       <c r="B153" s="58">
         <v>133</v>
       </c>
-      <c r="C153" s="322"/>
+      <c r="C153" s="368"/>
       <c r="D153" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E153" s="326" t="s">
+      <c r="E153" s="369" t="s">
         <v>241</v>
       </c>
-      <c r="F153" s="327"/>
-      <c r="G153" s="328"/>
+      <c r="F153" s="370"/>
+      <c r="G153" s="371"/>
       <c r="H153" s="122"/>
       <c r="I153" s="123"/>
       <c r="J153" s="81"/>
@@ -14152,11 +14152,11 @@
       <c r="D154" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E154" s="329" t="s">
+      <c r="E154" s="352" t="s">
         <v>198</v>
       </c>
-      <c r="F154" s="329"/>
-      <c r="G154" s="329"/>
+      <c r="F154" s="352"/>
+      <c r="G154" s="352"/>
       <c r="H154" s="72"/>
       <c r="I154" s="120" t="e">
         <f>SUM(#REF!)</f>
@@ -14182,15 +14182,120 @@
     </row>
   </sheetData>
   <mergeCells count="142">
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:G24"/>
-    <mergeCell ref="I22:J24"/>
+    <mergeCell ref="E151:G151"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:G152"/>
+    <mergeCell ref="E153:G153"/>
+    <mergeCell ref="E154:G154"/>
+    <mergeCell ref="F140:G140"/>
+    <mergeCell ref="F141:F142"/>
+    <mergeCell ref="F144:G144"/>
+    <mergeCell ref="F145:F146"/>
+    <mergeCell ref="C149:C150"/>
+    <mergeCell ref="D149:G149"/>
+    <mergeCell ref="E150:G150"/>
+    <mergeCell ref="E134:G134"/>
+    <mergeCell ref="E135:G135"/>
+    <mergeCell ref="E136:G136"/>
+    <mergeCell ref="E137:G137"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:G138"/>
+    <mergeCell ref="E139:G139"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="E130:G130"/>
+    <mergeCell ref="C131:C133"/>
+    <mergeCell ref="D131:G131"/>
+    <mergeCell ref="E132:G132"/>
+    <mergeCell ref="E133:G133"/>
+    <mergeCell ref="E121:G121"/>
+    <mergeCell ref="E122:G122"/>
+    <mergeCell ref="C123:C126"/>
+    <mergeCell ref="D123:G123"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="E116:G116"/>
+    <mergeCell ref="E117:G117"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:G118"/>
+    <mergeCell ref="E119:G119"/>
+    <mergeCell ref="E120:G120"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="D111:G111"/>
+    <mergeCell ref="E112:G112"/>
+    <mergeCell ref="E113:G113"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:G114"/>
+    <mergeCell ref="E115:G115"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="D107:G107"/>
+    <mergeCell ref="E108:G108"/>
+    <mergeCell ref="E109:G109"/>
+    <mergeCell ref="E110:G110"/>
+    <mergeCell ref="E104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="E98:G98"/>
+    <mergeCell ref="E99:G99"/>
+    <mergeCell ref="E100:G100"/>
+    <mergeCell ref="C101:C103"/>
+    <mergeCell ref="D101:G101"/>
+    <mergeCell ref="E102:G102"/>
+    <mergeCell ref="E103:G103"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="E94:G94"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:G95"/>
+    <mergeCell ref="E96:G96"/>
+    <mergeCell ref="E97:G97"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:G87"/>
+    <mergeCell ref="E88:G88"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="E90:G90"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="D91:G91"/>
+    <mergeCell ref="E92:G92"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="G81:I81"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="C65:C67"/>
+    <mergeCell ref="D65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D55:G55"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="E47:G47"/>
     <mergeCell ref="C29:G29"/>
     <mergeCell ref="C30:C34"/>
     <mergeCell ref="D30:G30"/>
@@ -14210,120 +14315,15 @@
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="E36:G36"/>
     <mergeCell ref="E37:G37"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:G48"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:G46"/>
-    <mergeCell ref="E47:G47"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="D60:G60"/>
-    <mergeCell ref="E61:G61"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D55:G55"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="G81:I81"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="E64:G64"/>
-    <mergeCell ref="C65:C67"/>
-    <mergeCell ref="D65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="E94:G94"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="D95:G95"/>
-    <mergeCell ref="E96:G96"/>
-    <mergeCell ref="E97:G97"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:G87"/>
-    <mergeCell ref="E88:G88"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="E90:G90"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="D91:G91"/>
-    <mergeCell ref="E92:G92"/>
-    <mergeCell ref="E104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="E98:G98"/>
-    <mergeCell ref="E99:G99"/>
-    <mergeCell ref="E100:G100"/>
-    <mergeCell ref="C101:C103"/>
-    <mergeCell ref="D101:G101"/>
-    <mergeCell ref="E102:G102"/>
-    <mergeCell ref="E103:G103"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="D111:G111"/>
-    <mergeCell ref="E112:G112"/>
-    <mergeCell ref="E113:G113"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="D114:G114"/>
-    <mergeCell ref="E115:G115"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="D107:G107"/>
-    <mergeCell ref="E108:G108"/>
-    <mergeCell ref="E109:G109"/>
-    <mergeCell ref="E110:G110"/>
-    <mergeCell ref="E121:G121"/>
-    <mergeCell ref="E122:G122"/>
-    <mergeCell ref="C123:C126"/>
-    <mergeCell ref="D123:G123"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="E116:G116"/>
-    <mergeCell ref="E117:G117"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:G118"/>
-    <mergeCell ref="E119:G119"/>
-    <mergeCell ref="E120:G120"/>
-    <mergeCell ref="E134:G134"/>
-    <mergeCell ref="E135:G135"/>
-    <mergeCell ref="E136:G136"/>
-    <mergeCell ref="E137:G137"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:G138"/>
-    <mergeCell ref="E139:G139"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="E130:G130"/>
-    <mergeCell ref="C131:C133"/>
-    <mergeCell ref="D131:G131"/>
-    <mergeCell ref="E132:G132"/>
-    <mergeCell ref="E133:G133"/>
-    <mergeCell ref="E151:G151"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D152:G152"/>
-    <mergeCell ref="E153:G153"/>
-    <mergeCell ref="E154:G154"/>
-    <mergeCell ref="F140:G140"/>
-    <mergeCell ref="F141:F142"/>
-    <mergeCell ref="F144:G144"/>
-    <mergeCell ref="F145:F146"/>
-    <mergeCell ref="C149:C150"/>
-    <mergeCell ref="D149:G149"/>
-    <mergeCell ref="E150:G150"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:G24"/>
+    <mergeCell ref="I22:J24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="64" orientation="portrait" r:id="rId1"/>
@@ -14353,15 +14353,15 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="357" t="s">
+      <c r="B1" s="319" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="357"/>
-      <c r="D1" s="357"/>
-      <c r="E1" s="357"/>
-      <c r="F1" s="357"/>
-      <c r="G1" s="357"/>
-      <c r="H1" s="357"/>
+      <c r="C1" s="319"/>
+      <c r="D1" s="319"/>
+      <c r="E1" s="319"/>
+      <c r="F1" s="319"/>
+      <c r="G1" s="319"/>
+      <c r="H1" s="319"/>
       <c r="L1" s="51"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1">
@@ -14395,30 +14395,30 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="358" t="s">
+      <c r="B3" s="320" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="358"/>
-      <c r="D3" s="358"/>
-      <c r="E3" s="358"/>
-      <c r="F3" s="358"/>
-      <c r="G3" s="358"/>
-      <c r="H3" s="358"/>
+      <c r="C3" s="320"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="320"/>
+      <c r="G3" s="320"/>
+      <c r="H3" s="320"/>
       <c r="L3" s="51"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="359" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="359"/>
-      <c r="D4" s="359"/>
-      <c r="E4" s="359"/>
-      <c r="F4" s="359"/>
-      <c r="G4" s="359"/>
-      <c r="H4" s="359"/>
+      <c r="B4" s="321" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="321"/>
+      <c r="D4" s="321"/>
+      <c r="E4" s="321"/>
+      <c r="F4" s="321"/>
+      <c r="G4" s="321"/>
+      <c r="H4" s="321"/>
       <c r="L4" s="51"/>
       <c r="M4" s="53"/>
     </row>
@@ -14440,40 +14440,40 @@
       <c r="A19" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="382" t="s">
+      <c r="B19" s="374" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="365" t="s">
+      <c r="C19" s="327" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="366"/>
-      <c r="E19" s="366"/>
-      <c r="F19" s="366"/>
-      <c r="G19" s="367"/>
+      <c r="D19" s="328"/>
+      <c r="E19" s="328"/>
+      <c r="F19" s="328"/>
+      <c r="G19" s="329"/>
       <c r="H19" s="55"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1">
       <c r="A20" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="363"/>
-      <c r="C20" s="368"/>
-      <c r="D20" s="369"/>
-      <c r="E20" s="369"/>
-      <c r="F20" s="369"/>
-      <c r="G20" s="370"/>
+      <c r="B20" s="325"/>
+      <c r="C20" s="330"/>
+      <c r="D20" s="331"/>
+      <c r="E20" s="331"/>
+      <c r="F20" s="331"/>
+      <c r="G20" s="332"/>
       <c r="H20" s="55"/>
     </row>
     <row r="21" spans="1:13" ht="24" customHeight="1">
       <c r="A21" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="364"/>
-      <c r="C21" s="371"/>
-      <c r="D21" s="372"/>
-      <c r="E21" s="372"/>
-      <c r="F21" s="372"/>
-      <c r="G21" s="373"/>
+      <c r="B21" s="326"/>
+      <c r="C21" s="333"/>
+      <c r="D21" s="334"/>
+      <c r="E21" s="334"/>
+      <c r="F21" s="334"/>
+      <c r="G21" s="335"/>
       <c r="H21" s="57" t="s">
         <v>52</v>
       </c>
@@ -14489,17 +14489,17 @@
       <c r="B25" s="57">
         <v>1</v>
       </c>
-      <c r="C25" s="383">
+      <c r="C25" s="375">
         <v>2</v>
       </c>
-      <c r="D25" s="384"/>
+      <c r="D25" s="376"/>
       <c r="E25" s="57">
         <v>3</v>
       </c>
-      <c r="F25" s="383">
+      <c r="F25" s="375">
         <v>4</v>
       </c>
-      <c r="G25" s="384"/>
+      <c r="G25" s="376"/>
       <c r="H25" s="57">
         <v>8</v>
       </c>
@@ -14555,15 +14555,15 @@
       <c r="B29" s="58">
         <v>2</v>
       </c>
-      <c r="C29" s="374" t="s">
+      <c r="C29" s="377" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="375"/>
-      <c r="E29" s="323" t="s">
+      <c r="D29" s="378"/>
+      <c r="E29" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F29" s="324"/>
-      <c r="G29" s="325"/>
+      <c r="F29" s="337"/>
+      <c r="G29" s="338"/>
       <c r="H29" s="64"/>
       <c r="I29" s="49"/>
       <c r="M29" s="65"/>
@@ -14575,15 +14575,15 @@
       <c r="B30" s="58">
         <v>3</v>
       </c>
-      <c r="C30" s="376"/>
-      <c r="D30" s="377"/>
+      <c r="C30" s="379"/>
+      <c r="D30" s="380"/>
       <c r="E30" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="336" t="s">
+      <c r="F30" s="355" t="s">
         <v>56</v>
       </c>
-      <c r="G30" s="338"/>
+      <c r="G30" s="357"/>
       <c r="H30" s="72" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14598,15 +14598,15 @@
       <c r="B31" s="58">
         <v>4</v>
       </c>
-      <c r="C31" s="376"/>
-      <c r="D31" s="377"/>
+      <c r="C31" s="379"/>
+      <c r="D31" s="380"/>
       <c r="E31" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="336" t="s">
+      <c r="F31" s="355" t="s">
         <v>57</v>
       </c>
-      <c r="G31" s="338"/>
+      <c r="G31" s="357"/>
       <c r="H31" s="64"/>
       <c r="I31" s="49"/>
       <c r="M31" s="53"/>
@@ -14618,15 +14618,15 @@
       <c r="B32" s="58">
         <v>5</v>
       </c>
-      <c r="C32" s="376"/>
-      <c r="D32" s="377"/>
+      <c r="C32" s="379"/>
+      <c r="D32" s="380"/>
       <c r="E32" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="336" t="s">
+      <c r="F32" s="355" t="s">
         <v>58</v>
       </c>
-      <c r="G32" s="338"/>
+      <c r="G32" s="357"/>
       <c r="H32" s="64"/>
       <c r="I32" s="49"/>
     </row>
@@ -14646,10 +14646,10 @@
       <c r="E33" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F33" s="319" t="s">
+      <c r="F33" s="345" t="s">
         <v>170</v>
       </c>
-      <c r="G33" s="321"/>
+      <c r="G33" s="347"/>
       <c r="H33" s="64"/>
       <c r="I33" s="49"/>
       <c r="J33" s="49"/>
@@ -14670,10 +14670,10 @@
       <c r="E34" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="G34" s="321"/>
+      <c r="F34" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="347"/>
       <c r="H34" s="64"/>
       <c r="I34" s="49"/>
       <c r="J34" s="49"/>
@@ -14686,15 +14686,15 @@
       <c r="B35" s="58">
         <v>8</v>
       </c>
-      <c r="C35" s="374" t="s">
+      <c r="C35" s="377" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="375"/>
-      <c r="E35" s="323" t="s">
+      <c r="D35" s="378"/>
+      <c r="E35" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F35" s="324"/>
-      <c r="G35" s="325"/>
+      <c r="F35" s="337"/>
+      <c r="G35" s="338"/>
       <c r="H35" s="64"/>
       <c r="I35" s="49"/>
     </row>
@@ -14705,15 +14705,15 @@
       <c r="B36" s="58">
         <v>9</v>
       </c>
-      <c r="C36" s="376"/>
-      <c r="D36" s="377"/>
-      <c r="E36" s="330" t="s">
+      <c r="C36" s="379"/>
+      <c r="D36" s="380"/>
+      <c r="E36" s="372" t="s">
         <v>55</v>
       </c>
-      <c r="F36" s="336" t="s">
+      <c r="F36" s="355" t="s">
         <v>172</v>
       </c>
-      <c r="G36" s="338"/>
+      <c r="G36" s="357"/>
       <c r="H36" s="72" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -14728,13 +14728,13 @@
       <c r="B37" s="58">
         <v>10</v>
       </c>
-      <c r="C37" s="380"/>
-      <c r="D37" s="381"/>
-      <c r="E37" s="331"/>
-      <c r="F37" s="336" t="s">
+      <c r="C37" s="381"/>
+      <c r="D37" s="382"/>
+      <c r="E37" s="373"/>
+      <c r="F37" s="355" t="s">
         <v>173</v>
       </c>
-      <c r="G37" s="338"/>
+      <c r="G37" s="357"/>
       <c r="H37" s="64"/>
       <c r="I37" s="49"/>
     </row>
@@ -14745,15 +14745,15 @@
       <c r="B38" s="58">
         <v>11</v>
       </c>
-      <c r="C38" s="374" t="s">
+      <c r="C38" s="377" t="s">
         <v>174</v>
       </c>
-      <c r="D38" s="375"/>
-      <c r="E38" s="323" t="s">
+      <c r="D38" s="378"/>
+      <c r="E38" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F38" s="324"/>
-      <c r="G38" s="325"/>
+      <c r="F38" s="337"/>
+      <c r="G38" s="338"/>
       <c r="H38" s="64"/>
       <c r="I38" s="49"/>
     </row>
@@ -14764,15 +14764,15 @@
       <c r="B39" s="58">
         <v>12</v>
       </c>
-      <c r="C39" s="376"/>
-      <c r="D39" s="377"/>
+      <c r="C39" s="379"/>
+      <c r="D39" s="380"/>
       <c r="E39" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="G39" s="379"/>
+      <c r="F39" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="G39" s="384"/>
       <c r="H39" s="64"/>
       <c r="I39" s="49"/>
     </row>
@@ -14792,10 +14792,10 @@
       <c r="E40" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="G40" s="321"/>
+      <c r="F40" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G40" s="347"/>
       <c r="H40" s="64"/>
       <c r="I40" s="49"/>
       <c r="J40" s="49"/>
@@ -14807,15 +14807,15 @@
       <c r="B41" s="58">
         <v>14</v>
       </c>
-      <c r="C41" s="374" t="s">
+      <c r="C41" s="377" t="s">
         <v>175</v>
       </c>
-      <c r="D41" s="375"/>
-      <c r="E41" s="323" t="s">
+      <c r="D41" s="378"/>
+      <c r="E41" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F41" s="324"/>
-      <c r="G41" s="325"/>
+      <c r="F41" s="337"/>
+      <c r="G41" s="338"/>
       <c r="H41" s="64"/>
       <c r="I41" s="49"/>
     </row>
@@ -14826,15 +14826,15 @@
       <c r="B42" s="58">
         <v>15</v>
       </c>
-      <c r="C42" s="376"/>
-      <c r="D42" s="377"/>
+      <c r="C42" s="379"/>
+      <c r="D42" s="380"/>
       <c r="E42" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="336" t="s">
+      <c r="F42" s="355" t="s">
         <v>91</v>
       </c>
-      <c r="G42" s="338"/>
+      <c r="G42" s="357"/>
       <c r="H42" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14857,10 +14857,10 @@
       <c r="E43" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F43" s="319" t="s">
+      <c r="F43" s="345" t="s">
         <v>176</v>
       </c>
-      <c r="G43" s="321"/>
+      <c r="G43" s="347"/>
       <c r="H43" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14884,10 +14884,10 @@
       <c r="E44" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F44" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="G44" s="321"/>
+      <c r="F44" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" s="347"/>
       <c r="H44" s="64"/>
       <c r="I44" s="49"/>
       <c r="J44" s="49"/>
@@ -14899,15 +14899,15 @@
       <c r="B45" s="58">
         <v>18</v>
       </c>
-      <c r="C45" s="374" t="s">
+      <c r="C45" s="377" t="s">
         <v>177</v>
       </c>
-      <c r="D45" s="375"/>
-      <c r="E45" s="323" t="s">
+      <c r="D45" s="378"/>
+      <c r="E45" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="324"/>
-      <c r="G45" s="325"/>
+      <c r="F45" s="337"/>
+      <c r="G45" s="338"/>
       <c r="H45" s="64"/>
       <c r="I45" s="49"/>
     </row>
@@ -14918,15 +14918,15 @@
       <c r="B46" s="58">
         <v>19</v>
       </c>
-      <c r="C46" s="376"/>
-      <c r="D46" s="377"/>
+      <c r="C46" s="379"/>
+      <c r="D46" s="380"/>
       <c r="E46" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="G46" s="379"/>
+      <c r="F46" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" s="384"/>
       <c r="H46" s="64"/>
       <c r="I46" s="49"/>
     </row>
@@ -14946,8 +14946,8 @@
       <c r="E47" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F47" s="319"/>
-      <c r="G47" s="321"/>
+      <c r="F47" s="345"/>
+      <c r="G47" s="347"/>
       <c r="H47" s="64"/>
       <c r="I47" s="49"/>
       <c r="J47" s="49"/>
@@ -14968,10 +14968,10 @@
       <c r="E48" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F48" s="319" t="s">
+      <c r="F48" s="345" t="s">
         <v>178</v>
       </c>
-      <c r="G48" s="321"/>
+      <c r="G48" s="347"/>
       <c r="H48" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14995,10 +14995,10 @@
       <c r="E49" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F49" s="319" t="s">
+      <c r="F49" s="345" t="s">
         <v>8</v>
       </c>
-      <c r="G49" s="321"/>
+      <c r="G49" s="347"/>
       <c r="H49" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15013,13 +15013,13 @@
       <c r="B50" s="58">
         <v>24</v>
       </c>
-      <c r="C50" s="323" t="s">
+      <c r="C50" s="336" t="s">
         <v>179</v>
       </c>
-      <c r="D50" s="324"/>
-      <c r="E50" s="324"/>
-      <c r="F50" s="324"/>
-      <c r="G50" s="325"/>
+      <c r="D50" s="337"/>
+      <c r="E50" s="337"/>
+      <c r="F50" s="337"/>
+      <c r="G50" s="338"/>
       <c r="H50" s="64"/>
       <c r="I50" s="49"/>
     </row>
@@ -15030,13 +15030,13 @@
       <c r="B51" s="58">
         <v>25</v>
       </c>
-      <c r="C51" s="323" t="s">
+      <c r="C51" s="336" t="s">
         <v>180</v>
       </c>
-      <c r="D51" s="324"/>
-      <c r="E51" s="324"/>
-      <c r="F51" s="324"/>
-      <c r="G51" s="325"/>
+      <c r="D51" s="337"/>
+      <c r="E51" s="337"/>
+      <c r="F51" s="337"/>
+      <c r="G51" s="338"/>
       <c r="H51" s="64" t="e">
         <f>нак.расх.!G29-зат.осн.про.!H75-зат.осн.про.!H99</f>
         <v>#REF!</v>
@@ -15082,15 +15082,15 @@
       <c r="B53" s="58">
         <v>2</v>
       </c>
-      <c r="C53" s="374" t="s">
+      <c r="C53" s="377" t="s">
         <v>54</v>
       </c>
-      <c r="D53" s="375"/>
-      <c r="E53" s="323" t="s">
+      <c r="D53" s="378"/>
+      <c r="E53" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F53" s="324"/>
-      <c r="G53" s="325"/>
+      <c r="F53" s="337"/>
+      <c r="G53" s="338"/>
       <c r="H53" s="64"/>
       <c r="I53" s="49"/>
       <c r="M53" s="53" t="e">
@@ -15105,15 +15105,15 @@
       <c r="B54" s="58">
         <v>3</v>
       </c>
-      <c r="C54" s="376"/>
-      <c r="D54" s="377"/>
+      <c r="C54" s="379"/>
+      <c r="D54" s="380"/>
       <c r="E54" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F54" s="336" t="s">
+      <c r="F54" s="355" t="s">
         <v>56</v>
       </c>
-      <c r="G54" s="338"/>
+      <c r="G54" s="357"/>
       <c r="H54" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15127,15 +15127,15 @@
       <c r="B55" s="58">
         <v>4</v>
       </c>
-      <c r="C55" s="376"/>
-      <c r="D55" s="377"/>
+      <c r="C55" s="379"/>
+      <c r="D55" s="380"/>
       <c r="E55" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F55" s="336" t="s">
+      <c r="F55" s="355" t="s">
         <v>57</v>
       </c>
-      <c r="G55" s="338"/>
+      <c r="G55" s="357"/>
       <c r="H55" s="64"/>
       <c r="I55" s="49"/>
     </row>
@@ -15146,15 +15146,15 @@
       <c r="B56" s="58">
         <v>5</v>
       </c>
-      <c r="C56" s="376"/>
-      <c r="D56" s="377"/>
+      <c r="C56" s="379"/>
+      <c r="D56" s="380"/>
       <c r="E56" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="336" t="s">
+      <c r="F56" s="355" t="s">
         <v>58</v>
       </c>
-      <c r="G56" s="338"/>
+      <c r="G56" s="357"/>
       <c r="H56" s="64"/>
       <c r="I56" s="49"/>
     </row>
@@ -15174,10 +15174,10 @@
       <c r="E57" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="319" t="s">
+      <c r="F57" s="345" t="s">
         <v>170</v>
       </c>
-      <c r="G57" s="321"/>
+      <c r="G57" s="347"/>
       <c r="H57" s="64"/>
       <c r="I57" s="49"/>
       <c r="J57" s="49"/>
@@ -15198,10 +15198,10 @@
       <c r="E58" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F58" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="G58" s="321"/>
+      <c r="F58" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G58" s="347"/>
       <c r="H58" s="64"/>
       <c r="I58" s="49"/>
     </row>
@@ -15212,15 +15212,15 @@
       <c r="B59" s="58">
         <v>8</v>
       </c>
-      <c r="C59" s="374" t="s">
+      <c r="C59" s="377" t="s">
         <v>171</v>
       </c>
-      <c r="D59" s="375"/>
-      <c r="E59" s="323" t="s">
+      <c r="D59" s="378"/>
+      <c r="E59" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F59" s="324"/>
-      <c r="G59" s="325"/>
+      <c r="F59" s="337"/>
+      <c r="G59" s="338"/>
       <c r="H59" s="64"/>
       <c r="I59" s="49"/>
     </row>
@@ -15231,15 +15231,15 @@
       <c r="B60" s="58">
         <v>9</v>
       </c>
-      <c r="C60" s="376"/>
-      <c r="D60" s="377"/>
-      <c r="E60" s="330" t="s">
+      <c r="C60" s="379"/>
+      <c r="D60" s="380"/>
+      <c r="E60" s="372" t="s">
         <v>55</v>
       </c>
-      <c r="F60" s="336" t="s">
+      <c r="F60" s="355" t="s">
         <v>172</v>
       </c>
-      <c r="G60" s="338"/>
+      <c r="G60" s="357"/>
       <c r="H60" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15253,13 +15253,13 @@
       <c r="B61" s="58">
         <v>10</v>
       </c>
-      <c r="C61" s="380"/>
-      <c r="D61" s="381"/>
-      <c r="E61" s="331"/>
-      <c r="F61" s="336" t="s">
+      <c r="C61" s="381"/>
+      <c r="D61" s="382"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="355" t="s">
         <v>173</v>
       </c>
-      <c r="G61" s="338"/>
+      <c r="G61" s="357"/>
       <c r="H61" s="64"/>
       <c r="I61" s="49"/>
     </row>
@@ -15270,15 +15270,15 @@
       <c r="B62" s="58">
         <v>11</v>
       </c>
-      <c r="C62" s="374" t="s">
+      <c r="C62" s="377" t="s">
         <v>174</v>
       </c>
-      <c r="D62" s="375"/>
-      <c r="E62" s="323" t="s">
+      <c r="D62" s="378"/>
+      <c r="E62" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F62" s="324"/>
-      <c r="G62" s="325"/>
+      <c r="F62" s="337"/>
+      <c r="G62" s="338"/>
       <c r="H62" s="64"/>
       <c r="I62" s="49"/>
     </row>
@@ -15289,15 +15289,15 @@
       <c r="B63" s="58">
         <v>12</v>
       </c>
-      <c r="C63" s="376"/>
-      <c r="D63" s="377"/>
+      <c r="C63" s="379"/>
+      <c r="D63" s="380"/>
       <c r="E63" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F63" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="G63" s="379"/>
+      <c r="F63" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="G63" s="384"/>
       <c r="H63" s="64"/>
       <c r="I63" s="49"/>
       <c r="J63" s="49"/>
@@ -15318,10 +15318,10 @@
       <c r="E64" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F64" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="G64" s="321"/>
+      <c r="F64" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G64" s="347"/>
       <c r="H64" s="64"/>
       <c r="I64" s="49"/>
     </row>
@@ -15332,15 +15332,15 @@
       <c r="B65" s="58">
         <v>14</v>
       </c>
-      <c r="C65" s="374" t="s">
+      <c r="C65" s="377" t="s">
         <v>175</v>
       </c>
-      <c r="D65" s="375"/>
-      <c r="E65" s="323" t="s">
+      <c r="D65" s="378"/>
+      <c r="E65" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="324"/>
-      <c r="G65" s="325"/>
+      <c r="F65" s="337"/>
+      <c r="G65" s="338"/>
       <c r="H65" s="64"/>
       <c r="I65" s="49"/>
     </row>
@@ -15351,15 +15351,15 @@
       <c r="B66" s="58">
         <v>15</v>
       </c>
-      <c r="C66" s="376"/>
-      <c r="D66" s="377"/>
+      <c r="C66" s="379"/>
+      <c r="D66" s="380"/>
       <c r="E66" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F66" s="336" t="s">
+      <c r="F66" s="355" t="s">
         <v>91</v>
       </c>
-      <c r="G66" s="338"/>
+      <c r="G66" s="357"/>
       <c r="H66" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15383,10 +15383,10 @@
       <c r="E67" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="319" t="s">
+      <c r="F67" s="345" t="s">
         <v>176</v>
       </c>
-      <c r="G67" s="321"/>
+      <c r="G67" s="347"/>
       <c r="H67" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15409,10 +15409,10 @@
       <c r="E68" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F68" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="G68" s="321"/>
+      <c r="F68" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G68" s="347"/>
       <c r="H68" s="64"/>
       <c r="I68" s="49"/>
     </row>
@@ -15423,15 +15423,15 @@
       <c r="B69" s="58">
         <v>18</v>
       </c>
-      <c r="C69" s="374" t="s">
+      <c r="C69" s="377" t="s">
         <v>177</v>
       </c>
-      <c r="D69" s="375"/>
-      <c r="E69" s="323" t="s">
+      <c r="D69" s="378"/>
+      <c r="E69" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="324"/>
-      <c r="G69" s="325"/>
+      <c r="F69" s="337"/>
+      <c r="G69" s="338"/>
       <c r="H69" s="64"/>
       <c r="I69" s="49"/>
       <c r="J69" s="49"/>
@@ -15443,15 +15443,15 @@
       <c r="B70" s="58">
         <v>19</v>
       </c>
-      <c r="C70" s="376"/>
-      <c r="D70" s="377"/>
+      <c r="C70" s="379"/>
+      <c r="D70" s="380"/>
       <c r="E70" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F70" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="G70" s="379"/>
+      <c r="F70" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="G70" s="384"/>
       <c r="H70" s="64"/>
       <c r="I70" s="49"/>
     </row>
@@ -15471,8 +15471,8 @@
       <c r="E71" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F71" s="319"/>
-      <c r="G71" s="321"/>
+      <c r="F71" s="345"/>
+      <c r="G71" s="347"/>
       <c r="H71" s="64"/>
       <c r="I71" s="49"/>
     </row>
@@ -15489,10 +15489,10 @@
       <c r="E72" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F72" s="319" t="s">
+      <c r="F72" s="345" t="s">
         <v>178</v>
       </c>
-      <c r="G72" s="321"/>
+      <c r="G72" s="347"/>
       <c r="H72" s="64"/>
       <c r="I72" s="49"/>
       <c r="J72" s="49"/>
@@ -15515,10 +15515,10 @@
       <c r="E73" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F73" s="319" t="s">
+      <c r="F73" s="345" t="s">
         <v>8</v>
       </c>
-      <c r="G73" s="321"/>
+      <c r="G73" s="347"/>
       <c r="H73" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15532,13 +15532,13 @@
       <c r="B74" s="58">
         <v>24</v>
       </c>
-      <c r="C74" s="323" t="s">
+      <c r="C74" s="336" t="s">
         <v>179</v>
       </c>
-      <c r="D74" s="324"/>
-      <c r="E74" s="324"/>
-      <c r="F74" s="324"/>
-      <c r="G74" s="325"/>
+      <c r="D74" s="337"/>
+      <c r="E74" s="337"/>
+      <c r="F74" s="337"/>
+      <c r="G74" s="338"/>
       <c r="H74" s="64"/>
       <c r="I74" s="49"/>
       <c r="J74" s="49"/>
@@ -15549,13 +15549,13 @@
       <c r="B75" s="58">
         <v>25</v>
       </c>
-      <c r="C75" s="323" t="s">
+      <c r="C75" s="336" t="s">
         <v>180</v>
       </c>
-      <c r="D75" s="324"/>
-      <c r="E75" s="324"/>
-      <c r="F75" s="324"/>
-      <c r="G75" s="325"/>
+      <c r="D75" s="337"/>
+      <c r="E75" s="337"/>
+      <c r="F75" s="337"/>
+      <c r="G75" s="338"/>
       <c r="H75" s="64" t="e">
         <f>нак.расх.!G29*4%</f>
         <v>#REF!</v>
@@ -15601,15 +15601,15 @@
       <c r="B77" s="58">
         <v>2</v>
       </c>
-      <c r="C77" s="374" t="s">
+      <c r="C77" s="377" t="s">
         <v>54</v>
       </c>
-      <c r="D77" s="375"/>
-      <c r="E77" s="323" t="s">
+      <c r="D77" s="378"/>
+      <c r="E77" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F77" s="324"/>
-      <c r="G77" s="325"/>
+      <c r="F77" s="337"/>
+      <c r="G77" s="338"/>
       <c r="H77" s="64"/>
       <c r="M77" s="53" t="e">
         <f>H76-M76</f>
@@ -15620,15 +15620,15 @@
       <c r="B78" s="58">
         <v>3</v>
       </c>
-      <c r="C78" s="376"/>
-      <c r="D78" s="377"/>
+      <c r="C78" s="379"/>
+      <c r="D78" s="380"/>
       <c r="E78" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F78" s="336" t="s">
+      <c r="F78" s="355" t="s">
         <v>56</v>
       </c>
-      <c r="G78" s="338"/>
+      <c r="G78" s="357"/>
       <c r="H78" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15638,30 +15638,30 @@
       <c r="B79" s="58">
         <v>4</v>
       </c>
-      <c r="C79" s="376"/>
-      <c r="D79" s="377"/>
+      <c r="C79" s="379"/>
+      <c r="D79" s="380"/>
       <c r="E79" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F79" s="336" t="s">
+      <c r="F79" s="355" t="s">
         <v>57</v>
       </c>
-      <c r="G79" s="338"/>
+      <c r="G79" s="357"/>
       <c r="H79" s="64"/>
     </row>
     <row r="80" spans="1:13" ht="15.75" customHeight="1">
       <c r="B80" s="58">
         <v>5</v>
       </c>
-      <c r="C80" s="376"/>
-      <c r="D80" s="377"/>
+      <c r="C80" s="379"/>
+      <c r="D80" s="380"/>
       <c r="E80" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F80" s="336" t="s">
+      <c r="F80" s="355" t="s">
         <v>58</v>
       </c>
-      <c r="G80" s="338"/>
+      <c r="G80" s="357"/>
       <c r="H80" s="64"/>
     </row>
     <row r="81" spans="2:8" ht="15.75" customHeight="1">
@@ -15677,10 +15677,10 @@
       <c r="E81" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="319" t="s">
+      <c r="F81" s="345" t="s">
         <v>170</v>
       </c>
-      <c r="G81" s="321"/>
+      <c r="G81" s="347"/>
       <c r="H81" s="64"/>
     </row>
     <row r="82" spans="2:8" ht="15.75" customHeight="1">
@@ -15696,40 +15696,40 @@
       <c r="E82" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="G82" s="321"/>
+      <c r="F82" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G82" s="347"/>
       <c r="H82" s="64"/>
     </row>
     <row r="83" spans="2:8" ht="15.75" customHeight="1">
       <c r="B83" s="58">
         <v>8</v>
       </c>
-      <c r="C83" s="374" t="s">
+      <c r="C83" s="377" t="s">
         <v>171</v>
       </c>
-      <c r="D83" s="375"/>
-      <c r="E83" s="323" t="s">
+      <c r="D83" s="378"/>
+      <c r="E83" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F83" s="324"/>
-      <c r="G83" s="325"/>
+      <c r="F83" s="337"/>
+      <c r="G83" s="338"/>
       <c r="H83" s="64"/>
     </row>
     <row r="84" spans="2:8" ht="15.75" customHeight="1">
       <c r="B84" s="58">
         <v>9</v>
       </c>
-      <c r="C84" s="376"/>
-      <c r="D84" s="377"/>
-      <c r="E84" s="330" t="s">
+      <c r="C84" s="379"/>
+      <c r="D84" s="380"/>
+      <c r="E84" s="372" t="s">
         <v>55</v>
       </c>
-      <c r="F84" s="336" t="s">
+      <c r="F84" s="355" t="s">
         <v>172</v>
       </c>
-      <c r="G84" s="338"/>
+      <c r="G84" s="357"/>
       <c r="H84" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15739,43 +15739,43 @@
       <c r="B85" s="58">
         <v>10</v>
       </c>
-      <c r="C85" s="380"/>
-      <c r="D85" s="381"/>
-      <c r="E85" s="331"/>
-      <c r="F85" s="336" t="s">
+      <c r="C85" s="381"/>
+      <c r="D85" s="382"/>
+      <c r="E85" s="373"/>
+      <c r="F85" s="355" t="s">
         <v>173</v>
       </c>
-      <c r="G85" s="338"/>
+      <c r="G85" s="357"/>
       <c r="H85" s="64"/>
     </row>
     <row r="86" spans="2:8" ht="15.75" customHeight="1">
       <c r="B86" s="58">
         <v>11</v>
       </c>
-      <c r="C86" s="374" t="s">
+      <c r="C86" s="377" t="s">
         <v>174</v>
       </c>
-      <c r="D86" s="375"/>
-      <c r="E86" s="323" t="s">
+      <c r="D86" s="378"/>
+      <c r="E86" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F86" s="324"/>
-      <c r="G86" s="325"/>
+      <c r="F86" s="337"/>
+      <c r="G86" s="338"/>
       <c r="H86" s="64"/>
     </row>
     <row r="87" spans="2:8" ht="15.75" customHeight="1">
       <c r="B87" s="58">
         <v>12</v>
       </c>
-      <c r="C87" s="376"/>
-      <c r="D87" s="377"/>
+      <c r="C87" s="379"/>
+      <c r="D87" s="380"/>
       <c r="E87" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F87" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="G87" s="379"/>
+      <c r="F87" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="G87" s="384"/>
       <c r="H87" s="64"/>
     </row>
     <row r="88" spans="2:8" ht="15.75" customHeight="1">
@@ -15791,40 +15791,40 @@
       <c r="E88" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="G88" s="321"/>
+      <c r="F88" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G88" s="347"/>
       <c r="H88" s="64"/>
     </row>
     <row r="89" spans="2:8" ht="15.75" customHeight="1">
       <c r="B89" s="58">
         <v>14</v>
       </c>
-      <c r="C89" s="374" t="s">
+      <c r="C89" s="377" t="s">
         <v>175</v>
       </c>
-      <c r="D89" s="375"/>
-      <c r="E89" s="323" t="s">
+      <c r="D89" s="378"/>
+      <c r="E89" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F89" s="324"/>
-      <c r="G89" s="325"/>
+      <c r="F89" s="337"/>
+      <c r="G89" s="338"/>
       <c r="H89" s="64"/>
     </row>
     <row r="90" spans="2:8" ht="15.75" customHeight="1">
       <c r="B90" s="58">
         <v>15</v>
       </c>
-      <c r="C90" s="376"/>
-      <c r="D90" s="377"/>
+      <c r="C90" s="379"/>
+      <c r="D90" s="380"/>
       <c r="E90" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F90" s="336" t="s">
+      <c r="F90" s="355" t="s">
         <v>91</v>
       </c>
-      <c r="G90" s="338"/>
+      <c r="G90" s="357"/>
       <c r="H90" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15843,10 +15843,10 @@
       <c r="E91" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F91" s="319" t="s">
+      <c r="F91" s="345" t="s">
         <v>176</v>
       </c>
-      <c r="G91" s="321"/>
+      <c r="G91" s="347"/>
       <c r="H91" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15865,40 +15865,40 @@
       <c r="E92" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F92" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="G92" s="321"/>
+      <c r="F92" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G92" s="347"/>
       <c r="H92" s="64"/>
     </row>
     <row r="93" spans="2:8" ht="15.75" customHeight="1">
       <c r="B93" s="58">
         <v>18</v>
       </c>
-      <c r="C93" s="374" t="s">
+      <c r="C93" s="377" t="s">
         <v>177</v>
       </c>
-      <c r="D93" s="375"/>
-      <c r="E93" s="323" t="s">
+      <c r="D93" s="378"/>
+      <c r="E93" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F93" s="324"/>
-      <c r="G93" s="325"/>
+      <c r="F93" s="337"/>
+      <c r="G93" s="338"/>
       <c r="H93" s="64"/>
     </row>
     <row r="94" spans="2:8" ht="15.75" customHeight="1">
       <c r="B94" s="58">
         <v>19</v>
       </c>
-      <c r="C94" s="376"/>
-      <c r="D94" s="377"/>
+      <c r="C94" s="379"/>
+      <c r="D94" s="380"/>
       <c r="E94" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F94" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="G94" s="379"/>
+      <c r="F94" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="G94" s="384"/>
       <c r="H94" s="64"/>
     </row>
     <row r="95" spans="2:8" ht="15.75" customHeight="1">
@@ -15914,8 +15914,8 @@
       <c r="E95" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F95" s="319"/>
-      <c r="G95" s="321"/>
+      <c r="F95" s="345"/>
+      <c r="G95" s="347"/>
       <c r="H95" s="64"/>
     </row>
     <row r="96" spans="2:8" ht="32.25" customHeight="1">
@@ -15931,10 +15931,10 @@
       <c r="E96" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F96" s="319" t="s">
+      <c r="F96" s="345" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="321"/>
+      <c r="G96" s="347"/>
       <c r="H96" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15953,34 +15953,34 @@
       <c r="E97" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F97" s="319"/>
-      <c r="G97" s="321"/>
+      <c r="F97" s="345"/>
+      <c r="G97" s="347"/>
       <c r="H97" s="64"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1">
       <c r="B98" s="58">
         <v>24</v>
       </c>
-      <c r="C98" s="323" t="s">
+      <c r="C98" s="336" t="s">
         <v>179</v>
       </c>
-      <c r="D98" s="324"/>
-      <c r="E98" s="324"/>
-      <c r="F98" s="324"/>
-      <c r="G98" s="325"/>
+      <c r="D98" s="337"/>
+      <c r="E98" s="337"/>
+      <c r="F98" s="337"/>
+      <c r="G98" s="338"/>
       <c r="H98" s="64"/>
     </row>
     <row r="99" spans="2:8" ht="15.75" customHeight="1">
       <c r="B99" s="58">
         <v>25</v>
       </c>
-      <c r="C99" s="323" t="s">
+      <c r="C99" s="336" t="s">
         <v>180</v>
       </c>
-      <c r="D99" s="324"/>
-      <c r="E99" s="324"/>
-      <c r="F99" s="324"/>
-      <c r="G99" s="325"/>
+      <c r="D99" s="337"/>
+      <c r="E99" s="337"/>
+      <c r="F99" s="337"/>
+      <c r="G99" s="338"/>
       <c r="H99" s="64" t="e">
         <f>нак.расх.!G29*16%</f>
         <v>#REF!</v>
@@ -15988,6 +15988,87 @@
     </row>
   </sheetData>
   <mergeCells count="94">
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="C93:D94"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="C86:D87"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="C89:D90"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="C83:D85"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C77:D80"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="C62:D63"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="C65:D66"/>
+    <mergeCell ref="E65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="C69:D70"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="C59:D61"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C53:D56"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="C45:D46"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="C35:D37"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B3:H3"/>
@@ -16001,87 +16082,6 @@
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="C35:D37"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="C41:D42"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="C45:D46"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C53:D56"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="C59:D61"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="C62:D63"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="C65:D66"/>
-    <mergeCell ref="E65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="C69:D70"/>
-    <mergeCell ref="E69:G69"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C77:D80"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="C83:D85"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="C86:D87"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="C89:D90"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="C93:D94"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="F95:G95"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="76" orientation="portrait" r:id="rId1"/>
@@ -16110,14 +16110,14 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="357" t="s">
+      <c r="B1" s="319" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="357"/>
-      <c r="D1" s="357"/>
-      <c r="E1" s="357"/>
-      <c r="F1" s="357"/>
-      <c r="G1" s="357"/>
+      <c r="C1" s="319"/>
+      <c r="D1" s="319"/>
+      <c r="E1" s="319"/>
+      <c r="F1" s="319"/>
+      <c r="G1" s="319"/>
       <c r="K1" s="51"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1">
@@ -16148,69 +16148,69 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="357" t="s">
+      <c r="B3" s="319" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="357"/>
-      <c r="D3" s="357"/>
-      <c r="E3" s="357"/>
-      <c r="F3" s="357"/>
-      <c r="G3" s="357"/>
+      <c r="C3" s="319"/>
+      <c r="D3" s="319"/>
+      <c r="E3" s="319"/>
+      <c r="F3" s="319"/>
+      <c r="G3" s="319"/>
       <c r="K3" s="51"/>
     </row>
     <row r="4" spans="1:11" ht="14.25" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="359" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="359"/>
-      <c r="D4" s="359"/>
-      <c r="E4" s="359"/>
-      <c r="F4" s="359"/>
-      <c r="G4" s="359"/>
+      <c r="B4" s="321" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="321"/>
+      <c r="D4" s="321"/>
+      <c r="E4" s="321"/>
+      <c r="F4" s="321"/>
+      <c r="G4" s="321"/>
       <c r="K4" s="51"/>
     </row>
     <row r="5" spans="1:11" ht="24.75" customHeight="1">
       <c r="A5" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="360" t="s">
+      <c r="B5" s="322" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="360"/>
-      <c r="D5" s="360"/>
-      <c r="E5" s="360"/>
-      <c r="F5" s="360"/>
-      <c r="G5" s="360"/>
+      <c r="C5" s="322"/>
+      <c r="D5" s="322"/>
+      <c r="E5" s="322"/>
+      <c r="F5" s="322"/>
+      <c r="G5" s="322"/>
       <c r="K5" s="51"/>
     </row>
     <row r="6" spans="1:11" ht="12" customHeight="1">
       <c r="A6" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="360" t="s">
+      <c r="B6" s="322" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="360"/>
-      <c r="D6" s="360"/>
-      <c r="E6" s="360"/>
-      <c r="F6" s="360"/>
-      <c r="G6" s="360"/>
+      <c r="C6" s="322"/>
+      <c r="D6" s="322"/>
+      <c r="E6" s="322"/>
+      <c r="F6" s="322"/>
+      <c r="G6" s="322"/>
       <c r="K6" s="51"/>
     </row>
     <row r="7" spans="1:11" ht="12" customHeight="1">
       <c r="A7" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="361" t="s">
+      <c r="B7" s="323" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="361"/>
-      <c r="D7" s="361"/>
-      <c r="E7" s="361"/>
-      <c r="F7" s="361"/>
+      <c r="C7" s="323"/>
+      <c r="D7" s="323"/>
+      <c r="E7" s="323"/>
+      <c r="F7" s="323"/>
       <c r="G7" s="71" t="s">
         <v>50</v>
       </c>
@@ -16234,37 +16234,37 @@
       <c r="A22" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="362" t="s">
+      <c r="B22" s="324" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="365" t="s">
+      <c r="C22" s="327" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="366"/>
-      <c r="E22" s="366"/>
-      <c r="F22" s="367"/>
+      <c r="D22" s="328"/>
+      <c r="E22" s="328"/>
+      <c r="F22" s="329"/>
       <c r="G22" s="55"/>
     </row>
     <row r="23" spans="1:12" ht="12" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="363"/>
-      <c r="C23" s="368"/>
-      <c r="D23" s="369"/>
-      <c r="E23" s="369"/>
-      <c r="F23" s="370"/>
+      <c r="B23" s="325"/>
+      <c r="C23" s="330"/>
+      <c r="D23" s="331"/>
+      <c r="E23" s="331"/>
+      <c r="F23" s="332"/>
       <c r="G23" s="55"/>
     </row>
     <row r="24" spans="1:12" ht="24" customHeight="1">
       <c r="A24" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="364"/>
-      <c r="C24" s="371"/>
-      <c r="D24" s="372"/>
-      <c r="E24" s="372"/>
-      <c r="F24" s="373"/>
+      <c r="B24" s="326"/>
+      <c r="C24" s="333"/>
+      <c r="D24" s="334"/>
+      <c r="E24" s="334"/>
+      <c r="F24" s="335"/>
       <c r="G24" s="57" t="s">
         <v>52</v>
       </c>
@@ -16285,10 +16285,10 @@
       <c r="D28" s="57">
         <v>3</v>
       </c>
-      <c r="E28" s="383">
+      <c r="E28" s="375">
         <v>4</v>
       </c>
-      <c r="F28" s="384"/>
+      <c r="F28" s="376"/>
       <c r="G28" s="57">
         <v>8</v>
       </c>
@@ -16300,12 +16300,12 @@
       <c r="B29" s="58">
         <v>1</v>
       </c>
-      <c r="C29" s="323" t="s">
+      <c r="C29" s="336" t="s">
         <v>184</v>
       </c>
-      <c r="D29" s="324"/>
-      <c r="E29" s="324"/>
-      <c r="F29" s="324"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
       <c r="G29" s="72" t="e">
         <f>SUM(G30:G77)</f>
         <v>#REF!</v>
@@ -16325,11 +16325,11 @@
       <c r="C30" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="323" t="s">
+      <c r="D30" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="324"/>
-      <c r="F30" s="324"/>
+      <c r="E30" s="337"/>
+      <c r="F30" s="337"/>
       <c r="G30" s="74"/>
       <c r="L30" s="53" t="e">
         <f>G29-L29</f>
@@ -16349,10 +16349,10 @@
       <c r="D31" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="336" t="s">
+      <c r="E31" s="355" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="337"/>
+      <c r="F31" s="356"/>
       <c r="G31" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16372,10 +16372,10 @@
       <c r="D32" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="336" t="s">
+      <c r="E32" s="355" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="337"/>
+      <c r="F32" s="356"/>
       <c r="G32" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16395,10 +16395,10 @@
       <c r="D33" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E33" s="336" t="s">
+      <c r="E33" s="355" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="337"/>
+      <c r="F33" s="356"/>
       <c r="G33" s="74"/>
     </row>
     <row r="34" spans="1:13" ht="12" customHeight="1">
@@ -16455,10 +16455,10 @@
       <c r="D36" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E36" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="320"/>
+      <c r="E36" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="346"/>
       <c r="G36" s="74"/>
       <c r="H36" s="49"/>
     </row>
@@ -16472,11 +16472,11 @@
       <c r="C37" s="73" t="s">
         <v>171</v>
       </c>
-      <c r="D37" s="323" t="s">
+      <c r="D37" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E37" s="324"/>
-      <c r="F37" s="324"/>
+      <c r="E37" s="337"/>
+      <c r="F37" s="337"/>
       <c r="G37" s="74"/>
     </row>
     <row r="38" spans="1:13" ht="12" customHeight="1">
@@ -16492,10 +16492,10 @@
       <c r="D38" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E38" s="336" t="s">
+      <c r="E38" s="355" t="s">
         <v>172</v>
       </c>
-      <c r="F38" s="337"/>
+      <c r="F38" s="356"/>
       <c r="G38" s="74" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -16515,10 +16515,10 @@
       <c r="D39" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="336" t="s">
+      <c r="E39" s="355" t="s">
         <v>173</v>
       </c>
-      <c r="F39" s="337"/>
+      <c r="F39" s="356"/>
       <c r="G39" s="74"/>
     </row>
     <row r="40" spans="1:13" ht="12" customHeight="1">
@@ -16528,14 +16528,14 @@
       <c r="B40" s="58">
         <v>26</v>
       </c>
-      <c r="C40" s="332" t="s">
+      <c r="C40" s="339" t="s">
         <v>174</v>
       </c>
-      <c r="D40" s="323" t="s">
+      <c r="D40" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E40" s="324"/>
-      <c r="F40" s="324"/>
+      <c r="E40" s="337"/>
+      <c r="F40" s="337"/>
       <c r="G40" s="74"/>
     </row>
     <row r="41" spans="1:13" ht="12" customHeight="1">
@@ -16545,14 +16545,14 @@
       <c r="B41" s="58">
         <v>27</v>
       </c>
-      <c r="C41" s="333"/>
+      <c r="C41" s="340"/>
       <c r="D41" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="F41" s="386"/>
+      <c r="E41" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="385"/>
       <c r="G41" s="74"/>
     </row>
     <row r="42" spans="1:13" ht="12" customHeight="1">
@@ -16568,10 +16568,10 @@
       <c r="D42" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E42" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="320"/>
+      <c r="E42" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" s="346"/>
       <c r="G42" s="74"/>
       <c r="H42" s="49"/>
     </row>
@@ -16582,14 +16582,14 @@
       <c r="B43" s="58">
         <v>29</v>
       </c>
-      <c r="C43" s="332" t="s">
+      <c r="C43" s="339" t="s">
         <v>186</v>
       </c>
-      <c r="D43" s="323" t="s">
+      <c r="D43" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="324"/>
-      <c r="F43" s="324"/>
+      <c r="E43" s="337"/>
+      <c r="F43" s="337"/>
       <c r="G43" s="74"/>
     </row>
     <row r="44" spans="1:13" ht="12" customHeight="1">
@@ -16599,14 +16599,14 @@
       <c r="B44" s="58">
         <v>30</v>
       </c>
-      <c r="C44" s="333"/>
+      <c r="C44" s="340"/>
       <c r="D44" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E44" s="319" t="s">
+      <c r="E44" s="345" t="s">
         <v>128</v>
       </c>
-      <c r="F44" s="320"/>
+      <c r="F44" s="346"/>
       <c r="G44" s="74"/>
     </row>
     <row r="45" spans="1:13" ht="18.75" customHeight="1">
@@ -16616,14 +16616,14 @@
       <c r="B45" s="58">
         <v>31</v>
       </c>
-      <c r="C45" s="349"/>
+      <c r="C45" s="341"/>
       <c r="D45" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E45" s="389" t="s">
+      <c r="E45" s="386" t="s">
         <v>129</v>
       </c>
-      <c r="F45" s="390"/>
+      <c r="F45" s="387"/>
       <c r="G45" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16638,12 +16638,12 @@
       <c r="B46" s="58">
         <v>32</v>
       </c>
-      <c r="C46" s="323" t="s">
+      <c r="C46" s="336" t="s">
         <v>20</v>
       </c>
-      <c r="D46" s="324"/>
-      <c r="E46" s="324"/>
-      <c r="F46" s="324"/>
+      <c r="D46" s="337"/>
+      <c r="E46" s="337"/>
+      <c r="F46" s="337"/>
       <c r="G46" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16660,11 +16660,11 @@
       <c r="C47" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="D47" s="323" t="s">
+      <c r="D47" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E47" s="324"/>
-      <c r="F47" s="324"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
       <c r="G47" s="74"/>
       <c r="L47" s="53"/>
     </row>
@@ -16681,10 +16681,10 @@
       <c r="D48" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E48" s="336" t="s">
+      <c r="E48" s="355" t="s">
         <v>63</v>
       </c>
-      <c r="F48" s="337"/>
+      <c r="F48" s="356"/>
       <c r="G48" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16703,10 +16703,10 @@
       <c r="D49" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E49" s="336" t="s">
+      <c r="E49" s="355" t="s">
         <v>64</v>
       </c>
-      <c r="F49" s="337"/>
+      <c r="F49" s="356"/>
       <c r="G49" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16719,14 +16719,14 @@
       <c r="B50" s="58">
         <v>36</v>
       </c>
-      <c r="C50" s="332" t="s">
+      <c r="C50" s="339" t="s">
         <v>187</v>
       </c>
-      <c r="D50" s="323" t="s">
+      <c r="D50" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E50" s="324"/>
-      <c r="F50" s="324"/>
+      <c r="E50" s="337"/>
+      <c r="F50" s="337"/>
       <c r="G50" s="74"/>
     </row>
     <row r="51" spans="1:8" ht="12" customHeight="1">
@@ -16736,14 +16736,14 @@
       <c r="B51" s="58">
         <v>37</v>
       </c>
-      <c r="C51" s="333"/>
+      <c r="C51" s="340"/>
       <c r="D51" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E51" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="386"/>
+      <c r="E51" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="385"/>
       <c r="G51" s="74"/>
     </row>
     <row r="52" spans="1:8" ht="24.75" customHeight="1">
@@ -16759,10 +16759,10 @@
       <c r="D52" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E52" s="319" t="s">
+      <c r="E52" s="345" t="s">
         <v>188</v>
       </c>
-      <c r="F52" s="320"/>
+      <c r="F52" s="346"/>
       <c r="G52" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16776,12 +16776,12 @@
       <c r="B53" s="58">
         <v>43</v>
       </c>
-      <c r="C53" s="323" t="s">
+      <c r="C53" s="336" t="s">
         <v>16</v>
       </c>
-      <c r="D53" s="324"/>
-      <c r="E53" s="324"/>
-      <c r="F53" s="324"/>
+      <c r="D53" s="337"/>
+      <c r="E53" s="337"/>
+      <c r="F53" s="337"/>
       <c r="G53" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16794,12 +16794,12 @@
       <c r="B54" s="58">
         <v>44</v>
       </c>
-      <c r="C54" s="323" t="s">
+      <c r="C54" s="336" t="s">
         <v>14</v>
       </c>
-      <c r="D54" s="324"/>
-      <c r="E54" s="324"/>
-      <c r="F54" s="324"/>
+      <c r="D54" s="337"/>
+      <c r="E54" s="337"/>
+      <c r="F54" s="337"/>
       <c r="G54" s="74"/>
     </row>
     <row r="55" spans="1:8" ht="12" customHeight="1">
@@ -16812,11 +16812,11 @@
       <c r="C55" s="73" t="s">
         <v>137</v>
       </c>
-      <c r="D55" s="323" t="s">
+      <c r="D55" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="324"/>
-      <c r="F55" s="324"/>
+      <c r="E55" s="337"/>
+      <c r="F55" s="337"/>
       <c r="G55" s="74"/>
     </row>
     <row r="56" spans="1:8" ht="12" customHeight="1">
@@ -16832,10 +16832,10 @@
       <c r="D56" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="F56" s="386"/>
+      <c r="E56" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" s="385"/>
       <c r="G56" s="74"/>
     </row>
     <row r="57" spans="1:8" ht="24.75" customHeight="1">
@@ -16851,10 +16851,10 @@
       <c r="D57" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="319" t="s">
+      <c r="E57" s="345" t="s">
         <v>4</v>
       </c>
-      <c r="F57" s="320"/>
+      <c r="F57" s="346"/>
       <c r="G57" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16874,10 +16874,10 @@
       <c r="D58" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F58" s="320"/>
+      <c r="E58" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F58" s="346"/>
       <c r="G58" s="74"/>
       <c r="H58" s="49"/>
     </row>
@@ -16888,12 +16888,12 @@
       <c r="B59" s="58">
         <v>51</v>
       </c>
-      <c r="C59" s="323" t="s">
+      <c r="C59" s="336" t="s">
         <v>189</v>
       </c>
-      <c r="D59" s="324"/>
-      <c r="E59" s="324"/>
-      <c r="F59" s="324"/>
+      <c r="D59" s="337"/>
+      <c r="E59" s="337"/>
+      <c r="F59" s="337"/>
       <c r="G59" s="74"/>
     </row>
     <row r="60" spans="1:8" ht="12" customHeight="1">
@@ -16903,12 +16903,12 @@
       <c r="B60" s="58">
         <v>52</v>
       </c>
-      <c r="C60" s="323" t="s">
+      <c r="C60" s="336" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="324"/>
-      <c r="E60" s="324"/>
-      <c r="F60" s="324"/>
+      <c r="D60" s="337"/>
+      <c r="E60" s="337"/>
+      <c r="F60" s="337"/>
       <c r="G60" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16921,12 +16921,12 @@
       <c r="B61" s="58">
         <v>53</v>
       </c>
-      <c r="C61" s="323" t="s">
+      <c r="C61" s="336" t="s">
         <v>190</v>
       </c>
-      <c r="D61" s="324"/>
-      <c r="E61" s="324"/>
-      <c r="F61" s="324"/>
+      <c r="D61" s="337"/>
+      <c r="E61" s="337"/>
+      <c r="F61" s="337"/>
       <c r="G61" s="74"/>
     </row>
     <row r="62" spans="1:8" ht="12" customHeight="1">
@@ -16936,12 +16936,12 @@
       <c r="B62" s="58">
         <v>54</v>
       </c>
-      <c r="C62" s="323" t="s">
+      <c r="C62" s="336" t="s">
         <v>191</v>
       </c>
-      <c r="D62" s="324"/>
-      <c r="E62" s="324"/>
-      <c r="F62" s="324"/>
+      <c r="D62" s="337"/>
+      <c r="E62" s="337"/>
+      <c r="F62" s="337"/>
       <c r="G62" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16954,12 +16954,12 @@
       <c r="B63" s="58">
         <v>55</v>
       </c>
-      <c r="C63" s="323" t="s">
+      <c r="C63" s="336" t="s">
         <v>192</v>
       </c>
-      <c r="D63" s="324"/>
-      <c r="E63" s="324"/>
-      <c r="F63" s="324"/>
+      <c r="D63" s="337"/>
+      <c r="E63" s="337"/>
+      <c r="F63" s="337"/>
       <c r="G63" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16972,14 +16972,14 @@
       <c r="B64" s="58">
         <v>56</v>
       </c>
-      <c r="C64" s="332" t="s">
+      <c r="C64" s="339" t="s">
         <v>175</v>
       </c>
-      <c r="D64" s="323" t="s">
+      <c r="D64" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E64" s="324"/>
-      <c r="F64" s="324"/>
+      <c r="E64" s="337"/>
+      <c r="F64" s="337"/>
       <c r="G64" s="74"/>
     </row>
     <row r="65" spans="1:11" ht="12" customHeight="1">
@@ -16989,14 +16989,14 @@
       <c r="B65" s="58">
         <v>57</v>
       </c>
-      <c r="C65" s="333"/>
+      <c r="C65" s="340"/>
       <c r="D65" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E65" s="336" t="s">
+      <c r="E65" s="355" t="s">
         <v>91</v>
       </c>
-      <c r="F65" s="337"/>
+      <c r="F65" s="356"/>
       <c r="G65" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17015,10 +17015,10 @@
       <c r="D66" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E66" s="319" t="s">
+      <c r="E66" s="345" t="s">
         <v>193</v>
       </c>
-      <c r="F66" s="320"/>
+      <c r="F66" s="346"/>
       <c r="G66" s="74"/>
       <c r="H66" s="49"/>
     </row>
@@ -17029,14 +17029,14 @@
       <c r="B67" s="58">
         <v>59</v>
       </c>
-      <c r="C67" s="332" t="s">
+      <c r="C67" s="339" t="s">
         <v>102</v>
       </c>
-      <c r="D67" s="323" t="s">
+      <c r="D67" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E67" s="324"/>
-      <c r="F67" s="324"/>
+      <c r="E67" s="337"/>
+      <c r="F67" s="337"/>
       <c r="G67" s="74"/>
     </row>
     <row r="68" spans="1:11" ht="12" customHeight="1">
@@ -17046,14 +17046,14 @@
       <c r="B68" s="58">
         <v>60</v>
       </c>
-      <c r="C68" s="333"/>
+      <c r="C68" s="340"/>
       <c r="D68" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E68" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="F68" s="386"/>
+      <c r="E68" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="F68" s="385"/>
       <c r="G68" s="74"/>
     </row>
     <row r="69" spans="1:11" ht="12" customHeight="1">
@@ -17069,10 +17069,10 @@
       <c r="D69" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E69" s="319" t="s">
+      <c r="E69" s="345" t="s">
         <v>194</v>
       </c>
-      <c r="F69" s="320"/>
+      <c r="F69" s="346"/>
       <c r="G69" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17092,10 +17092,10 @@
       <c r="D70" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E70" s="319" t="s">
+      <c r="E70" s="345" t="s">
         <v>195</v>
       </c>
-      <c r="F70" s="320"/>
+      <c r="F70" s="346"/>
       <c r="G70" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17115,10 +17115,10 @@
       <c r="D71" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E71" s="387" t="s">
+      <c r="E71" s="388" t="s">
         <v>196</v>
       </c>
-      <c r="F71" s="388"/>
+      <c r="F71" s="389"/>
       <c r="G71" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17130,10 +17130,10 @@
       <c r="B72" s="58"/>
       <c r="C72" s="77"/>
       <c r="D72" s="70"/>
-      <c r="E72" s="387" t="s">
+      <c r="E72" s="388" t="s">
         <v>13</v>
       </c>
-      <c r="F72" s="388"/>
+      <c r="F72" s="389"/>
       <c r="G72" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17145,10 +17145,10 @@
       <c r="B73" s="58"/>
       <c r="C73" s="77"/>
       <c r="D73" s="70"/>
-      <c r="E73" s="387" t="s">
+      <c r="E73" s="388" t="s">
         <v>8</v>
       </c>
-      <c r="F73" s="388"/>
+      <c r="F73" s="389"/>
       <c r="G73" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17168,10 +17168,10 @@
       <c r="D74" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E74" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F74" s="320"/>
+      <c r="E74" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F74" s="346"/>
       <c r="G74" s="74"/>
       <c r="H74" s="49"/>
     </row>
@@ -17182,14 +17182,14 @@
       <c r="B75" s="58">
         <v>65</v>
       </c>
-      <c r="C75" s="332" t="s">
+      <c r="C75" s="339" t="s">
         <v>197</v>
       </c>
-      <c r="D75" s="323" t="s">
+      <c r="D75" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E75" s="324"/>
-      <c r="F75" s="324"/>
+      <c r="E75" s="337"/>
+      <c r="F75" s="337"/>
       <c r="G75" s="74"/>
     </row>
     <row r="76" spans="1:11" ht="12" customHeight="1">
@@ -17199,14 +17199,14 @@
       <c r="B76" s="58">
         <v>66</v>
       </c>
-      <c r="C76" s="333"/>
+      <c r="C76" s="340"/>
       <c r="D76" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E76" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="F76" s="386"/>
+      <c r="E76" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="F76" s="385"/>
       <c r="G76" s="74"/>
     </row>
     <row r="77" spans="1:11" ht="12" customHeight="1">
@@ -17222,10 +17222,10 @@
       <c r="D77" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E77" s="319" t="s">
+      <c r="E77" s="345" t="s">
         <v>198</v>
       </c>
-      <c r="F77" s="320"/>
+      <c r="F77" s="346"/>
       <c r="G77" s="81" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -17284,13 +17284,13 @@
       <c r="K79" s="51"/>
     </row>
     <row r="80" spans="1:11" ht="15" customHeight="1">
-      <c r="B80" s="385" t="s">
+      <c r="B80" s="390" t="s">
         <v>199</v>
       </c>
-      <c r="C80" s="385"/>
-      <c r="D80" s="385"/>
-      <c r="E80" s="385"/>
-      <c r="F80" s="385"/>
+      <c r="C80" s="390"/>
+      <c r="D80" s="390"/>
+      <c r="E80" s="390"/>
+      <c r="F80" s="390"/>
       <c r="G80" s="83"/>
       <c r="H80" s="83"/>
       <c r="I80" s="82"/>
@@ -17298,13 +17298,13 @@
       <c r="K80" s="51"/>
     </row>
     <row r="81" spans="2:11" ht="15" customHeight="1">
-      <c r="B81" s="385" t="s">
-        <v>44</v>
-      </c>
-      <c r="C81" s="385"/>
-      <c r="D81" s="385"/>
-      <c r="E81" s="385"/>
-      <c r="F81" s="385"/>
+      <c r="B81" s="390" t="s">
+        <v>44</v>
+      </c>
+      <c r="C81" s="390"/>
+      <c r="D81" s="390"/>
+      <c r="E81" s="390"/>
+      <c r="F81" s="390"/>
       <c r="G81" s="84"/>
       <c r="H81" s="84"/>
       <c r="I81" s="83"/>
@@ -17314,14 +17314,14 @@
     <row r="82" spans="2:11" ht="15.75" hidden="1" customHeight="1"/>
     <row r="83" spans="2:11" ht="15.75" hidden="1" customHeight="1"/>
     <row r="84" spans="2:11" ht="15" customHeight="1">
-      <c r="B84" s="385" t="s">
+      <c r="B84" s="390" t="s">
         <v>200</v>
       </c>
-      <c r="C84" s="385"/>
-      <c r="D84" s="385"/>
-      <c r="E84" s="385"/>
-      <c r="F84" s="385"/>
-      <c r="G84" s="385"/>
+      <c r="C84" s="390"/>
+      <c r="D84" s="390"/>
+      <c r="E84" s="390"/>
+      <c r="F84" s="390"/>
+      <c r="G84" s="390"/>
       <c r="H84" s="83"/>
       <c r="I84" s="83"/>
       <c r="J84" s="83"/>
@@ -17350,51 +17350,13 @@
     <row r="105" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:F24"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="C63:F63"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="C53:F53"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C59:F59"/>
-    <mergeCell ref="C60:F60"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="B84:G84"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
     <mergeCell ref="E74:F74"/>
     <mergeCell ref="C64:C65"/>
     <mergeCell ref="D64:F64"/>
@@ -17408,13 +17370,51 @@
     <mergeCell ref="E71:F71"/>
     <mergeCell ref="E72:F72"/>
     <mergeCell ref="E73:F73"/>
-    <mergeCell ref="B84:G84"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C59:F59"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:F24"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Наименование на государственном языке заполняется автоматически в соответствии с КТРУ" sqref="B76 B49:B50 B95:B96"/>
@@ -17450,79 +17450,79 @@
       <c r="A1" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="399" t="s">
+      <c r="B1" s="430" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="399"/>
-      <c r="D1" s="399"/>
-      <c r="E1" s="399"/>
-      <c r="F1" s="399"/>
-      <c r="G1" s="399"/>
-      <c r="H1" s="399"/>
-      <c r="I1" s="399"/>
+      <c r="C1" s="430"/>
+      <c r="D1" s="430"/>
+      <c r="E1" s="430"/>
+      <c r="F1" s="430"/>
+      <c r="G1" s="430"/>
+      <c r="H1" s="430"/>
+      <c r="I1" s="430"/>
       <c r="M1" s="12"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1">
       <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="400" t="s">
+      <c r="B2" s="431" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="400"/>
-      <c r="D2" s="400"/>
-      <c r="E2" s="400"/>
-      <c r="F2" s="400"/>
-      <c r="G2" s="400"/>
-      <c r="H2" s="400"/>
-      <c r="I2" s="400"/>
+      <c r="C2" s="431"/>
+      <c r="D2" s="431"/>
+      <c r="E2" s="431"/>
+      <c r="F2" s="431"/>
+      <c r="G2" s="431"/>
+      <c r="H2" s="431"/>
+      <c r="I2" s="431"/>
       <c r="M2" s="12"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="401" t="s">
+      <c r="B3" s="432" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="401"/>
-      <c r="D3" s="401"/>
-      <c r="E3" s="401"/>
-      <c r="F3" s="401"/>
-      <c r="G3" s="401"/>
-      <c r="H3" s="401"/>
-      <c r="I3" s="401"/>
+      <c r="C3" s="432"/>
+      <c r="D3" s="432"/>
+      <c r="E3" s="432"/>
+      <c r="F3" s="432"/>
+      <c r="G3" s="432"/>
+      <c r="H3" s="432"/>
+      <c r="I3" s="432"/>
       <c r="M3" s="12"/>
     </row>
     <row r="4" spans="1:13" ht="30" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="401" t="s">
+      <c r="B4" s="432" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="401"/>
-      <c r="D4" s="401"/>
-      <c r="E4" s="401"/>
-      <c r="F4" s="401"/>
-      <c r="G4" s="401"/>
-      <c r="H4" s="401"/>
-      <c r="I4" s="401"/>
+      <c r="C4" s="432"/>
+      <c r="D4" s="432"/>
+      <c r="E4" s="432"/>
+      <c r="F4" s="432"/>
+      <c r="G4" s="432"/>
+      <c r="H4" s="432"/>
+      <c r="I4" s="432"/>
       <c r="M4" s="12"/>
     </row>
     <row r="5" spans="1:13" ht="12" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="402" t="s">
+      <c r="B5" s="433" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="402"/>
-      <c r="D5" s="402"/>
-      <c r="E5" s="402"/>
-      <c r="F5" s="402"/>
-      <c r="G5" s="402"/>
-      <c r="H5" s="402"/>
+      <c r="C5" s="433"/>
+      <c r="D5" s="433"/>
+      <c r="E5" s="433"/>
+      <c r="F5" s="433"/>
+      <c r="G5" s="433"/>
+      <c r="H5" s="433"/>
       <c r="I5" s="13" t="s">
         <v>50</v>
       </c>
@@ -17546,18 +17546,18 @@
       <c r="A20" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="403" t="s">
+      <c r="B20" s="434" t="s">
         <v>0</v>
       </c>
-      <c r="C20" s="406" t="s">
+      <c r="C20" s="437" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="407"/>
-      <c r="E20" s="407"/>
-      <c r="F20" s="407"/>
-      <c r="G20" s="407"/>
-      <c r="H20" s="408"/>
-      <c r="I20" s="415" t="s">
+      <c r="D20" s="438"/>
+      <c r="E20" s="438"/>
+      <c r="F20" s="438"/>
+      <c r="G20" s="438"/>
+      <c r="H20" s="439"/>
+      <c r="I20" s="446" t="s">
         <v>52</v>
       </c>
       <c r="J20" s="10"/>
@@ -17570,14 +17570,14 @@
       <c r="A21" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="404"/>
-      <c r="C21" s="409"/>
-      <c r="D21" s="410"/>
-      <c r="E21" s="410"/>
-      <c r="F21" s="410"/>
-      <c r="G21" s="410"/>
-      <c r="H21" s="411"/>
-      <c r="I21" s="404"/>
+      <c r="B21" s="435"/>
+      <c r="C21" s="440"/>
+      <c r="D21" s="441"/>
+      <c r="E21" s="441"/>
+      <c r="F21" s="441"/>
+      <c r="G21" s="441"/>
+      <c r="H21" s="442"/>
+      <c r="I21" s="435"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
@@ -17587,14 +17587,14 @@
       <c r="A22" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="405"/>
-      <c r="C22" s="412"/>
-      <c r="D22" s="413"/>
-      <c r="E22" s="413"/>
-      <c r="F22" s="413"/>
-      <c r="G22" s="413"/>
-      <c r="H22" s="414"/>
-      <c r="I22" s="405"/>
+      <c r="B22" s="436"/>
+      <c r="C22" s="443"/>
+      <c r="D22" s="444"/>
+      <c r="E22" s="444"/>
+      <c r="F22" s="444"/>
+      <c r="G22" s="444"/>
+      <c r="H22" s="445"/>
+      <c r="I22" s="436"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
@@ -17610,10 +17610,10 @@
       <c r="B26" s="18">
         <v>1</v>
       </c>
-      <c r="C26" s="391">
+      <c r="C26" s="428">
         <v>2</v>
       </c>
-      <c r="D26" s="392"/>
+      <c r="D26" s="429"/>
       <c r="E26" s="18">
         <v>3</v>
       </c>
@@ -17637,14 +17637,14 @@
       <c r="B27" s="19">
         <v>1</v>
       </c>
-      <c r="C27" s="393" t="s">
+      <c r="C27" s="394" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="394"/>
-      <c r="E27" s="394"/>
-      <c r="F27" s="394"/>
-      <c r="G27" s="394"/>
-      <c r="H27" s="395"/>
+      <c r="D27" s="395"/>
+      <c r="E27" s="395"/>
+      <c r="F27" s="395"/>
+      <c r="G27" s="395"/>
+      <c r="H27" s="396"/>
       <c r="I27" s="20"/>
       <c r="N27" s="16"/>
     </row>
@@ -17661,12 +17661,12 @@
       <c r="D28" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="393" t="s">
+      <c r="E28" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F28" s="394"/>
-      <c r="G28" s="394"/>
-      <c r="H28" s="395"/>
+      <c r="F28" s="395"/>
+      <c r="G28" s="395"/>
+      <c r="H28" s="396"/>
       <c r="I28" s="20" t="e">
         <f>SUM(I29:I190)</f>
         <v>#REF!</v>
@@ -17692,11 +17692,11 @@
       <c r="E29" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="396" t="s">
+      <c r="F29" s="401" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="397"/>
-      <c r="H29" s="398"/>
+      <c r="G29" s="402"/>
+      <c r="H29" s="403"/>
       <c r="I29" s="20" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17722,11 +17722,11 @@
       <c r="E30" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="396" t="s">
+      <c r="F30" s="401" t="s">
         <v>57</v>
       </c>
-      <c r="G30" s="397"/>
-      <c r="H30" s="398"/>
+      <c r="G30" s="402"/>
+      <c r="H30" s="403"/>
       <c r="I30" s="20" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17749,11 +17749,11 @@
       <c r="E31" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="396" t="s">
+      <c r="F31" s="401" t="s">
         <v>58</v>
       </c>
-      <c r="G31" s="397"/>
-      <c r="H31" s="398"/>
+      <c r="G31" s="402"/>
+      <c r="H31" s="403"/>
       <c r="I31" s="20"/>
     </row>
     <row r="32" spans="1:14" ht="12" customHeight="1">
@@ -17772,11 +17772,11 @@
       <c r="E32" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="416" t="s">
+      <c r="F32" s="391" t="s">
         <v>59</v>
       </c>
-      <c r="G32" s="417"/>
-      <c r="H32" s="418"/>
+      <c r="G32" s="392"/>
+      <c r="H32" s="393"/>
       <c r="I32" s="20" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -17802,16 +17802,16 @@
       <c r="B34" s="21">
         <v>7</v>
       </c>
-      <c r="C34" s="419" t="s">
+      <c r="C34" s="397" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="420"/>
-      <c r="E34" s="393" t="s">
+      <c r="D34" s="398"/>
+      <c r="E34" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="394"/>
-      <c r="G34" s="394"/>
-      <c r="H34" s="395"/>
+      <c r="F34" s="395"/>
+      <c r="G34" s="395"/>
+      <c r="H34" s="396"/>
       <c r="I34" s="32"/>
     </row>
     <row r="35" spans="1:15" ht="12" customHeight="1">
@@ -17821,16 +17821,16 @@
       <c r="B35" s="21">
         <v>8</v>
       </c>
-      <c r="C35" s="421"/>
-      <c r="D35" s="422"/>
+      <c r="C35" s="399"/>
+      <c r="D35" s="400"/>
       <c r="E35" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F35" s="396" t="s">
-        <v>44</v>
-      </c>
-      <c r="G35" s="397"/>
-      <c r="H35" s="398"/>
+      <c r="F35" s="401" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" s="402"/>
+      <c r="H35" s="403"/>
       <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:15" hidden="1">
@@ -17843,16 +17843,16 @@
       <c r="B37" s="21">
         <v>10</v>
       </c>
-      <c r="C37" s="423" t="s">
+      <c r="C37" s="407" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="424"/>
-      <c r="E37" s="393" t="s">
+      <c r="D37" s="408"/>
+      <c r="E37" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F37" s="394"/>
-      <c r="G37" s="394"/>
-      <c r="H37" s="395"/>
+      <c r="F37" s="395"/>
+      <c r="G37" s="395"/>
+      <c r="H37" s="396"/>
       <c r="I37" s="32"/>
     </row>
     <row r="38" spans="1:15" ht="12" customHeight="1">
@@ -17862,16 +17862,16 @@
       <c r="B38" s="21">
         <v>11</v>
       </c>
-      <c r="C38" s="425"/>
-      <c r="D38" s="426"/>
-      <c r="E38" s="429" t="s">
+      <c r="C38" s="409"/>
+      <c r="D38" s="410"/>
+      <c r="E38" s="413" t="s">
         <v>55</v>
       </c>
-      <c r="F38" s="396" t="s">
+      <c r="F38" s="401" t="s">
         <v>63</v>
       </c>
-      <c r="G38" s="397"/>
-      <c r="H38" s="398"/>
+      <c r="G38" s="402"/>
+      <c r="H38" s="403"/>
       <c r="I38" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17884,14 +17884,14 @@
       <c r="B39" s="21">
         <v>12</v>
       </c>
-      <c r="C39" s="427"/>
-      <c r="D39" s="428"/>
-      <c r="E39" s="430"/>
-      <c r="F39" s="396" t="s">
+      <c r="C39" s="411"/>
+      <c r="D39" s="412"/>
+      <c r="E39" s="414"/>
+      <c r="F39" s="401" t="s">
         <v>64</v>
       </c>
-      <c r="G39" s="397"/>
-      <c r="H39" s="398"/>
+      <c r="G39" s="402"/>
+      <c r="H39" s="403"/>
       <c r="I39" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17904,16 +17904,16 @@
       <c r="B40" s="21">
         <v>13</v>
       </c>
-      <c r="C40" s="419" t="s">
+      <c r="C40" s="397" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="420"/>
-      <c r="E40" s="393" t="s">
+      <c r="D40" s="398"/>
+      <c r="E40" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F40" s="394"/>
-      <c r="G40" s="394"/>
-      <c r="H40" s="395"/>
+      <c r="F40" s="395"/>
+      <c r="G40" s="395"/>
+      <c r="H40" s="396"/>
       <c r="I40" s="32"/>
     </row>
     <row r="41" spans="1:15" ht="17.25" customHeight="1">
@@ -17923,16 +17923,16 @@
       <c r="B41" s="21">
         <v>14</v>
       </c>
-      <c r="C41" s="421"/>
-      <c r="D41" s="422"/>
+      <c r="C41" s="399"/>
+      <c r="D41" s="400"/>
       <c r="E41" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F41" s="396" t="s">
-        <v>44</v>
-      </c>
-      <c r="G41" s="397"/>
-      <c r="H41" s="398"/>
+      <c r="F41" s="401" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" s="402"/>
+      <c r="H41" s="403"/>
       <c r="I41" s="32"/>
     </row>
     <row r="42" spans="1:15" ht="12" customHeight="1">
@@ -17951,11 +17951,11 @@
       <c r="E42" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F42" s="416" t="s">
+      <c r="F42" s="391" t="s">
         <v>66</v>
       </c>
-      <c r="G42" s="417"/>
-      <c r="H42" s="418"/>
+      <c r="G42" s="392"/>
+      <c r="H42" s="393"/>
       <c r="I42" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17972,14 +17972,14 @@
       <c r="B44" s="21">
         <v>17</v>
       </c>
-      <c r="C44" s="393" t="s">
+      <c r="C44" s="394" t="s">
         <v>67</v>
       </c>
-      <c r="D44" s="394"/>
-      <c r="E44" s="394"/>
-      <c r="F44" s="394"/>
-      <c r="G44" s="394"/>
-      <c r="H44" s="395"/>
+      <c r="D44" s="395"/>
+      <c r="E44" s="395"/>
+      <c r="F44" s="395"/>
+      <c r="G44" s="395"/>
+      <c r="H44" s="396"/>
       <c r="I44" s="32"/>
     </row>
     <row r="45" spans="1:15" ht="12" customHeight="1">
@@ -17989,16 +17989,16 @@
       <c r="B45" s="21">
         <v>18</v>
       </c>
-      <c r="C45" s="431" t="s">
+      <c r="C45" s="422" t="s">
         <v>68</v>
       </c>
-      <c r="D45" s="432"/>
-      <c r="E45" s="393" t="s">
+      <c r="D45" s="423"/>
+      <c r="E45" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="394"/>
-      <c r="G45" s="394"/>
-      <c r="H45" s="395"/>
+      <c r="F45" s="395"/>
+      <c r="G45" s="395"/>
+      <c r="H45" s="396"/>
       <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:15" ht="30" customHeight="1">
@@ -18008,16 +18008,16 @@
       <c r="B46" s="21">
         <v>19</v>
       </c>
-      <c r="C46" s="433"/>
-      <c r="D46" s="434"/>
-      <c r="E46" s="429" t="s">
+      <c r="C46" s="424"/>
+      <c r="D46" s="425"/>
+      <c r="E46" s="413" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="396" t="s">
+      <c r="F46" s="401" t="s">
         <v>69</v>
       </c>
-      <c r="G46" s="397"/>
-      <c r="H46" s="398"/>
+      <c r="G46" s="402"/>
+      <c r="H46" s="403"/>
       <c r="I46" s="127" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18032,14 +18032,14 @@
       <c r="B47" s="21">
         <v>20</v>
       </c>
-      <c r="C47" s="433"/>
-      <c r="D47" s="434"/>
-      <c r="E47" s="437"/>
-      <c r="F47" s="396" t="s">
+      <c r="C47" s="424"/>
+      <c r="D47" s="425"/>
+      <c r="E47" s="415"/>
+      <c r="F47" s="401" t="s">
         <v>70</v>
       </c>
-      <c r="G47" s="397"/>
-      <c r="H47" s="398"/>
+      <c r="G47" s="402"/>
+      <c r="H47" s="403"/>
       <c r="I47" s="127" t="e">
         <f>#REF!+#REF!-#REF!</f>
         <v>#REF!</v>
@@ -18054,14 +18054,14 @@
       <c r="B48" s="21">
         <v>21</v>
       </c>
-      <c r="C48" s="433"/>
-      <c r="D48" s="434"/>
-      <c r="E48" s="437"/>
-      <c r="F48" s="396" t="s">
+      <c r="C48" s="424"/>
+      <c r="D48" s="425"/>
+      <c r="E48" s="415"/>
+      <c r="F48" s="401" t="s">
         <v>71</v>
       </c>
-      <c r="G48" s="397"/>
-      <c r="H48" s="398"/>
+      <c r="G48" s="402"/>
+      <c r="H48" s="403"/>
       <c r="I48" s="127" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18075,14 +18075,14 @@
       <c r="B49" s="21">
         <v>22</v>
       </c>
-      <c r="C49" s="435"/>
-      <c r="D49" s="436"/>
-      <c r="E49" s="430"/>
-      <c r="F49" s="396" t="s">
+      <c r="C49" s="426"/>
+      <c r="D49" s="427"/>
+      <c r="E49" s="414"/>
+      <c r="F49" s="401" t="s">
         <v>72</v>
       </c>
-      <c r="G49" s="397"/>
-      <c r="H49" s="398"/>
+      <c r="G49" s="402"/>
+      <c r="H49" s="403"/>
       <c r="I49" s="34" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18096,16 +18096,16 @@
       <c r="B50" s="21">
         <v>23</v>
       </c>
-      <c r="C50" s="438" t="s">
+      <c r="C50" s="418" t="s">
         <v>73</v>
       </c>
-      <c r="D50" s="439"/>
-      <c r="E50" s="393" t="s">
+      <c r="D50" s="419"/>
+      <c r="E50" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F50" s="394"/>
-      <c r="G50" s="394"/>
-      <c r="H50" s="395"/>
+      <c r="F50" s="395"/>
+      <c r="G50" s="395"/>
+      <c r="H50" s="396"/>
       <c r="I50" s="32"/>
     </row>
     <row r="51" spans="1:14" ht="12" customHeight="1">
@@ -18115,16 +18115,16 @@
       <c r="B51" s="21">
         <v>24</v>
       </c>
-      <c r="C51" s="440"/>
-      <c r="D51" s="441"/>
+      <c r="C51" s="420"/>
+      <c r="D51" s="421"/>
       <c r="E51" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="396" t="s">
+      <c r="F51" s="401" t="s">
         <v>23</v>
       </c>
-      <c r="G51" s="397"/>
-      <c r="H51" s="398"/>
+      <c r="G51" s="402"/>
+      <c r="H51" s="403"/>
       <c r="I51" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18147,11 +18147,11 @@
       <c r="E52" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="396" t="s">
+      <c r="F52" s="401" t="s">
         <v>74</v>
       </c>
-      <c r="G52" s="397"/>
-      <c r="H52" s="398"/>
+      <c r="G52" s="402"/>
+      <c r="H52" s="403"/>
       <c r="I52" s="32"/>
       <c r="N52" s="35"/>
     </row>
@@ -18165,16 +18165,16 @@
       <c r="B54" s="21">
         <v>27</v>
       </c>
-      <c r="C54" s="419" t="s">
+      <c r="C54" s="397" t="s">
         <v>75</v>
       </c>
-      <c r="D54" s="420"/>
-      <c r="E54" s="393" t="s">
+      <c r="D54" s="398"/>
+      <c r="E54" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F54" s="394"/>
-      <c r="G54" s="394"/>
-      <c r="H54" s="395"/>
+      <c r="F54" s="395"/>
+      <c r="G54" s="395"/>
+      <c r="H54" s="396"/>
       <c r="I54" s="32"/>
     </row>
     <row r="55" spans="1:14" ht="12" customHeight="1">
@@ -18184,16 +18184,16 @@
       <c r="B55" s="21">
         <v>28</v>
       </c>
-      <c r="C55" s="421"/>
-      <c r="D55" s="422"/>
+      <c r="C55" s="399"/>
+      <c r="D55" s="400"/>
       <c r="E55" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F55" s="396" t="s">
+      <c r="F55" s="401" t="s">
         <v>76</v>
       </c>
-      <c r="G55" s="397"/>
-      <c r="H55" s="398"/>
+      <c r="G55" s="402"/>
+      <c r="H55" s="403"/>
       <c r="I55" s="32"/>
     </row>
     <row r="56" spans="1:14" ht="12" customHeight="1">
@@ -18203,16 +18203,16 @@
       <c r="B56" s="21">
         <v>29</v>
       </c>
-      <c r="C56" s="421"/>
-      <c r="D56" s="422"/>
+      <c r="C56" s="399"/>
+      <c r="D56" s="400"/>
       <c r="E56" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="396" t="s">
+      <c r="F56" s="401" t="s">
         <v>77</v>
       </c>
-      <c r="G56" s="397"/>
-      <c r="H56" s="398"/>
+      <c r="G56" s="402"/>
+      <c r="H56" s="403"/>
       <c r="I56" s="32"/>
     </row>
     <row r="57" spans="1:14" ht="12" customHeight="1">
@@ -18222,16 +18222,16 @@
       <c r="B57" s="21">
         <v>30</v>
       </c>
-      <c r="C57" s="421"/>
-      <c r="D57" s="422"/>
+      <c r="C57" s="399"/>
+      <c r="D57" s="400"/>
       <c r="E57" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="396" t="s">
+      <c r="F57" s="401" t="s">
         <v>78</v>
       </c>
-      <c r="G57" s="397"/>
-      <c r="H57" s="398"/>
+      <c r="G57" s="402"/>
+      <c r="H57" s="403"/>
       <c r="I57" s="32"/>
     </row>
     <row r="58" spans="1:14" ht="12" customHeight="1">
@@ -18250,11 +18250,11 @@
       <c r="E58" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F58" s="396" t="s">
+      <c r="F58" s="401" t="s">
         <v>79</v>
       </c>
-      <c r="G58" s="397"/>
-      <c r="H58" s="398"/>
+      <c r="G58" s="402"/>
+      <c r="H58" s="403"/>
       <c r="I58" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18270,14 +18270,14 @@
       <c r="B60" s="21">
         <v>33</v>
       </c>
-      <c r="C60" s="393" t="s">
+      <c r="C60" s="394" t="s">
         <v>80</v>
       </c>
-      <c r="D60" s="394"/>
-      <c r="E60" s="394"/>
-      <c r="F60" s="394"/>
-      <c r="G60" s="394"/>
-      <c r="H60" s="395"/>
+      <c r="D60" s="395"/>
+      <c r="E60" s="395"/>
+      <c r="F60" s="395"/>
+      <c r="G60" s="395"/>
+      <c r="H60" s="396"/>
       <c r="I60" s="32"/>
     </row>
     <row r="61" spans="1:14" ht="12" customHeight="1">
@@ -18287,16 +18287,16 @@
       <c r="B61" s="21">
         <v>34</v>
       </c>
-      <c r="C61" s="419" t="s">
+      <c r="C61" s="397" t="s">
         <v>81</v>
       </c>
-      <c r="D61" s="420"/>
-      <c r="E61" s="393" t="s">
+      <c r="D61" s="398"/>
+      <c r="E61" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F61" s="394"/>
-      <c r="G61" s="394"/>
-      <c r="H61" s="395"/>
+      <c r="F61" s="395"/>
+      <c r="G61" s="395"/>
+      <c r="H61" s="396"/>
       <c r="I61" s="32"/>
     </row>
     <row r="62" spans="1:14" ht="12" customHeight="1">
@@ -18306,18 +18306,18 @@
       <c r="B62" s="21">
         <v>35</v>
       </c>
-      <c r="C62" s="421"/>
-      <c r="D62" s="422"/>
+      <c r="C62" s="399"/>
+      <c r="D62" s="400"/>
       <c r="E62" s="26" t="s">
         <v>55</v>
       </c>
       <c r="F62" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G62" s="442" t="s">
+      <c r="G62" s="416" t="s">
         <v>5</v>
       </c>
-      <c r="H62" s="443"/>
+      <c r="H62" s="417"/>
       <c r="I62" s="32"/>
     </row>
     <row r="63" spans="1:14" ht="12" customHeight="1">
@@ -18327,8 +18327,8 @@
       <c r="B63" s="21">
         <v>36</v>
       </c>
-      <c r="C63" s="421"/>
-      <c r="D63" s="422"/>
+      <c r="C63" s="399"/>
+      <c r="D63" s="400"/>
       <c r="E63" s="27" t="s">
         <v>44</v>
       </c>
@@ -18392,10 +18392,10 @@
       <c r="F66" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="G66" s="442" t="s">
+      <c r="G66" s="416" t="s">
         <v>5</v>
       </c>
-      <c r="H66" s="443"/>
+      <c r="H66" s="417"/>
       <c r="I66" s="32"/>
     </row>
     <row r="67" spans="1:14" ht="12" customHeight="1">
@@ -18474,10 +18474,10 @@
       <c r="F70" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G70" s="442" t="s">
+      <c r="G70" s="416" t="s">
         <v>5</v>
       </c>
-      <c r="H70" s="443"/>
+      <c r="H70" s="417"/>
       <c r="I70" s="32"/>
     </row>
     <row r="71" spans="1:14" ht="12" customHeight="1">
@@ -18556,10 +18556,10 @@
       <c r="F74" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="G74" s="442" t="s">
+      <c r="G74" s="416" t="s">
         <v>5</v>
       </c>
-      <c r="H74" s="443"/>
+      <c r="H74" s="417"/>
       <c r="I74" s="32"/>
     </row>
     <row r="75" spans="1:14" ht="12" customHeight="1">
@@ -18626,16 +18626,16 @@
       <c r="B78" s="21">
         <v>51</v>
       </c>
-      <c r="C78" s="419" t="s">
+      <c r="C78" s="397" t="s">
         <v>88</v>
       </c>
-      <c r="D78" s="420"/>
-      <c r="E78" s="393" t="s">
+      <c r="D78" s="398"/>
+      <c r="E78" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F78" s="394"/>
-      <c r="G78" s="394"/>
-      <c r="H78" s="395"/>
+      <c r="F78" s="395"/>
+      <c r="G78" s="395"/>
+      <c r="H78" s="396"/>
       <c r="I78" s="32"/>
     </row>
     <row r="79" spans="1:14" ht="12" customHeight="1">
@@ -18645,16 +18645,16 @@
       <c r="B79" s="21">
         <v>52</v>
       </c>
-      <c r="C79" s="421"/>
-      <c r="D79" s="422"/>
+      <c r="C79" s="399"/>
+      <c r="D79" s="400"/>
       <c r="E79" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F79" s="396" t="s">
+      <c r="F79" s="401" t="s">
         <v>89</v>
       </c>
-      <c r="G79" s="397"/>
-      <c r="H79" s="398"/>
+      <c r="G79" s="402"/>
+      <c r="H79" s="403"/>
       <c r="I79" s="32"/>
     </row>
     <row r="80" spans="1:14" ht="12" customHeight="1">
@@ -18673,11 +18673,11 @@
       <c r="E80" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F80" s="396" t="s">
+      <c r="F80" s="401" t="s">
         <v>24</v>
       </c>
-      <c r="G80" s="397"/>
-      <c r="H80" s="398"/>
+      <c r="G80" s="402"/>
+      <c r="H80" s="403"/>
       <c r="I80" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18700,11 +18700,11 @@
       <c r="E81" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="396" t="s">
+      <c r="F81" s="401" t="s">
         <v>90</v>
       </c>
-      <c r="G81" s="397"/>
-      <c r="H81" s="398"/>
+      <c r="G81" s="402"/>
+      <c r="H81" s="403"/>
       <c r="I81" s="32"/>
       <c r="N81" s="35"/>
     </row>
@@ -18724,13 +18724,13 @@
       <c r="E82" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="429" t="s">
+      <c r="F82" s="413" t="s">
         <v>91</v>
       </c>
-      <c r="G82" s="442" t="s">
+      <c r="G82" s="416" t="s">
         <v>5</v>
       </c>
-      <c r="H82" s="443"/>
+      <c r="H82" s="417"/>
       <c r="I82" s="32"/>
     </row>
     <row r="83" spans="1:14" ht="24" customHeight="1">
@@ -18749,8 +18749,8 @@
       <c r="E83" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F83" s="437"/>
-      <c r="G83" s="429" t="s">
+      <c r="F83" s="415"/>
+      <c r="G83" s="413" t="s">
         <v>55</v>
       </c>
       <c r="H83" s="15" t="s">
@@ -18777,8 +18777,8 @@
       <c r="E84" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F84" s="430"/>
-      <c r="G84" s="430"/>
+      <c r="F84" s="414"/>
+      <c r="G84" s="414"/>
       <c r="H84" s="15" t="s">
         <v>92</v>
       </c>
@@ -18803,11 +18803,11 @@
       <c r="E85" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F85" s="396" t="s">
+      <c r="F85" s="401" t="s">
         <v>9</v>
       </c>
-      <c r="G85" s="397"/>
-      <c r="H85" s="398"/>
+      <c r="G85" s="402"/>
+      <c r="H85" s="403"/>
       <c r="I85" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18829,11 +18829,11 @@
       <c r="E86" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F86" s="396" t="s">
+      <c r="F86" s="401" t="s">
         <v>10</v>
       </c>
-      <c r="G86" s="397"/>
-      <c r="H86" s="398"/>
+      <c r="G86" s="402"/>
+      <c r="H86" s="403"/>
       <c r="I86" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18855,11 +18855,11 @@
       <c r="E87" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F87" s="396" t="s">
+      <c r="F87" s="401" t="s">
         <v>11</v>
       </c>
-      <c r="G87" s="397"/>
-      <c r="H87" s="398"/>
+      <c r="G87" s="402"/>
+      <c r="H87" s="403"/>
       <c r="I87" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18881,11 +18881,11 @@
       <c r="E88" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="396" t="s">
+      <c r="F88" s="401" t="s">
         <v>93</v>
       </c>
-      <c r="G88" s="397"/>
-      <c r="H88" s="398"/>
+      <c r="G88" s="402"/>
+      <c r="H88" s="403"/>
       <c r="I88" s="32"/>
     </row>
     <row r="89" spans="1:14" ht="12" customHeight="1">
@@ -18904,11 +18904,11 @@
       <c r="E89" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F89" s="416" t="s">
+      <c r="F89" s="391" t="s">
         <v>94</v>
       </c>
-      <c r="G89" s="417"/>
-      <c r="H89" s="418"/>
+      <c r="G89" s="392"/>
+      <c r="H89" s="393"/>
       <c r="I89" s="32"/>
       <c r="J89" s="10"/>
     </row>
@@ -18928,9 +18928,9 @@
       <c r="E90" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F90" s="416"/>
-      <c r="G90" s="417"/>
-      <c r="H90" s="418"/>
+      <c r="F90" s="391"/>
+      <c r="G90" s="392"/>
+      <c r="H90" s="393"/>
       <c r="I90" s="39"/>
       <c r="J90" s="10"/>
     </row>
@@ -18944,16 +18944,16 @@
       <c r="B92" s="21">
         <v>63</v>
       </c>
-      <c r="C92" s="419" t="s">
+      <c r="C92" s="397" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="420"/>
-      <c r="E92" s="393" t="s">
+      <c r="D92" s="398"/>
+      <c r="E92" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F92" s="394"/>
-      <c r="G92" s="394"/>
-      <c r="H92" s="395"/>
+      <c r="F92" s="395"/>
+      <c r="G92" s="395"/>
+      <c r="H92" s="396"/>
       <c r="I92" s="32"/>
     </row>
     <row r="93" spans="1:14" ht="12" customHeight="1">
@@ -18969,14 +18969,14 @@
       <c r="D93" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="429" t="s">
+      <c r="E93" s="413" t="s">
         <v>55</v>
       </c>
-      <c r="F93" s="396" t="s">
-        <v>44</v>
-      </c>
-      <c r="G93" s="397"/>
-      <c r="H93" s="398"/>
+      <c r="F93" s="401" t="s">
+        <v>44</v>
+      </c>
+      <c r="G93" s="402"/>
+      <c r="H93" s="403"/>
       <c r="I93" s="32"/>
     </row>
     <row r="94" spans="1:14" ht="12" customHeight="1">
@@ -18992,12 +18992,12 @@
       <c r="D94" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="E94" s="430"/>
-      <c r="F94" s="416" t="s">
+      <c r="E94" s="414"/>
+      <c r="F94" s="391" t="s">
         <v>96</v>
       </c>
-      <c r="G94" s="417"/>
-      <c r="H94" s="418"/>
+      <c r="G94" s="392"/>
+      <c r="H94" s="393"/>
       <c r="I94" s="32"/>
       <c r="J94" s="10"/>
     </row>
@@ -19011,16 +19011,16 @@
       <c r="B96" s="21">
         <v>66</v>
       </c>
-      <c r="C96" s="419" t="s">
+      <c r="C96" s="397" t="s">
         <v>97</v>
       </c>
-      <c r="D96" s="420"/>
-      <c r="E96" s="393" t="s">
+      <c r="D96" s="398"/>
+      <c r="E96" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F96" s="394"/>
-      <c r="G96" s="394"/>
-      <c r="H96" s="395"/>
+      <c r="F96" s="395"/>
+      <c r="G96" s="395"/>
+      <c r="H96" s="396"/>
       <c r="I96" s="32"/>
     </row>
     <row r="97" spans="1:10" ht="12" customHeight="1">
@@ -19039,11 +19039,11 @@
       <c r="E97" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F97" s="396" t="s">
+      <c r="F97" s="401" t="s">
         <v>98</v>
       </c>
-      <c r="G97" s="397"/>
-      <c r="H97" s="398"/>
+      <c r="G97" s="402"/>
+      <c r="H97" s="403"/>
       <c r="I97" s="32"/>
     </row>
     <row r="98" spans="1:10" ht="12" customHeight="1">
@@ -19062,11 +19062,11 @@
       <c r="E98" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F98" s="396" t="s">
+      <c r="F98" s="401" t="s">
         <v>99</v>
       </c>
-      <c r="G98" s="397"/>
-      <c r="H98" s="398"/>
+      <c r="G98" s="402"/>
+      <c r="H98" s="403"/>
       <c r="I98" s="32"/>
     </row>
     <row r="99" spans="1:10" ht="12" customHeight="1">
@@ -19085,11 +19085,11 @@
       <c r="E99" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F99" s="396" t="s">
+      <c r="F99" s="401" t="s">
         <v>12</v>
       </c>
-      <c r="G99" s="397"/>
-      <c r="H99" s="398"/>
+      <c r="G99" s="402"/>
+      <c r="H99" s="403"/>
       <c r="I99" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19111,11 +19111,11 @@
       <c r="E100" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F100" s="396" t="s">
+      <c r="F100" s="401" t="s">
         <v>100</v>
       </c>
-      <c r="G100" s="397"/>
-      <c r="H100" s="398"/>
+      <c r="G100" s="402"/>
+      <c r="H100" s="403"/>
       <c r="I100" s="32"/>
     </row>
     <row r="101" spans="1:10" ht="12" customHeight="1">
@@ -19134,11 +19134,11 @@
       <c r="E101" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F101" s="416" t="s">
-        <v>44</v>
-      </c>
-      <c r="G101" s="417"/>
-      <c r="H101" s="418"/>
+      <c r="F101" s="391" t="s">
+        <v>44</v>
+      </c>
+      <c r="G101" s="392"/>
+      <c r="H101" s="393"/>
       <c r="I101" s="32"/>
       <c r="J101" s="10"/>
     </row>
@@ -19158,11 +19158,11 @@
       <c r="E102" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F102" s="416" t="s">
-        <v>44</v>
-      </c>
-      <c r="G102" s="417"/>
-      <c r="H102" s="418"/>
+      <c r="F102" s="391" t="s">
+        <v>44</v>
+      </c>
+      <c r="G102" s="392"/>
+      <c r="H102" s="393"/>
       <c r="I102" s="32"/>
       <c r="J102" s="10"/>
     </row>
@@ -19176,14 +19176,14 @@
       <c r="B104" s="21">
         <v>72</v>
       </c>
-      <c r="C104" s="393" t="s">
+      <c r="C104" s="394" t="s">
         <v>19</v>
       </c>
-      <c r="D104" s="394"/>
-      <c r="E104" s="394"/>
-      <c r="F104" s="394"/>
-      <c r="G104" s="394"/>
-      <c r="H104" s="395"/>
+      <c r="D104" s="395"/>
+      <c r="E104" s="395"/>
+      <c r="F104" s="395"/>
+      <c r="G104" s="395"/>
+      <c r="H104" s="396"/>
       <c r="I104" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19196,14 +19196,14 @@
       <c r="B105" s="21">
         <v>73</v>
       </c>
-      <c r="C105" s="393" t="s">
+      <c r="C105" s="394" t="s">
         <v>101</v>
       </c>
-      <c r="D105" s="394"/>
-      <c r="E105" s="394"/>
-      <c r="F105" s="394"/>
-      <c r="G105" s="394"/>
-      <c r="H105" s="395"/>
+      <c r="D105" s="395"/>
+      <c r="E105" s="395"/>
+      <c r="F105" s="395"/>
+      <c r="G105" s="395"/>
+      <c r="H105" s="396"/>
       <c r="I105" s="32"/>
     </row>
     <row r="106" spans="1:10" ht="12" customHeight="1">
@@ -19213,16 +19213,16 @@
       <c r="B106" s="21">
         <v>74</v>
       </c>
-      <c r="C106" s="419" t="s">
+      <c r="C106" s="397" t="s">
         <v>102</v>
       </c>
-      <c r="D106" s="420"/>
-      <c r="E106" s="393" t="s">
+      <c r="D106" s="398"/>
+      <c r="E106" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F106" s="394"/>
-      <c r="G106" s="394"/>
-      <c r="H106" s="395"/>
+      <c r="F106" s="395"/>
+      <c r="G106" s="395"/>
+      <c r="H106" s="396"/>
       <c r="I106" s="32"/>
     </row>
     <row r="107" spans="1:10" ht="18.75" customHeight="1">
@@ -19232,16 +19232,16 @@
       <c r="B107" s="21">
         <v>75</v>
       </c>
-      <c r="C107" s="421"/>
-      <c r="D107" s="422"/>
+      <c r="C107" s="399"/>
+      <c r="D107" s="400"/>
       <c r="E107" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F107" s="396" t="s">
+      <c r="F107" s="401" t="s">
         <v>13</v>
       </c>
-      <c r="G107" s="397"/>
-      <c r="H107" s="398"/>
+      <c r="G107" s="402"/>
+      <c r="H107" s="403"/>
       <c r="I107" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19263,11 +19263,11 @@
       <c r="E108" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F108" s="416" t="s">
+      <c r="F108" s="391" t="s">
         <v>103</v>
       </c>
-      <c r="G108" s="417"/>
-      <c r="H108" s="418"/>
+      <c r="G108" s="392"/>
+      <c r="H108" s="393"/>
       <c r="I108" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19290,11 +19290,11 @@
       <c r="E109" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F109" s="416" t="s">
+      <c r="F109" s="391" t="s">
         <v>104</v>
       </c>
-      <c r="G109" s="417"/>
-      <c r="H109" s="418"/>
+      <c r="G109" s="392"/>
+      <c r="H109" s="393"/>
       <c r="I109" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19317,11 +19317,11 @@
       <c r="E110" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F110" s="416" t="s">
+      <c r="F110" s="391" t="s">
         <v>8</v>
       </c>
-      <c r="G110" s="417"/>
-      <c r="H110" s="418"/>
+      <c r="G110" s="392"/>
+      <c r="H110" s="393"/>
       <c r="I110" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19338,16 +19338,16 @@
       <c r="B112" s="21">
         <v>77</v>
       </c>
-      <c r="C112" s="419" t="s">
+      <c r="C112" s="397" t="s">
         <v>105</v>
       </c>
-      <c r="D112" s="420"/>
-      <c r="E112" s="393" t="s">
+      <c r="D112" s="398"/>
+      <c r="E112" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F112" s="394"/>
-      <c r="G112" s="394"/>
-      <c r="H112" s="395"/>
+      <c r="F112" s="395"/>
+      <c r="G112" s="395"/>
+      <c r="H112" s="396"/>
       <c r="I112" s="32"/>
     </row>
     <row r="113" spans="1:9" ht="12" customHeight="1">
@@ -19366,11 +19366,11 @@
       <c r="E113" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F113" s="396" t="s">
+      <c r="F113" s="401" t="s">
         <v>106</v>
       </c>
-      <c r="G113" s="397"/>
-      <c r="H113" s="398"/>
+      <c r="G113" s="402"/>
+      <c r="H113" s="403"/>
       <c r="I113" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19392,11 +19392,11 @@
       <c r="E114" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F114" s="396" t="s">
+      <c r="F114" s="401" t="s">
         <v>107</v>
       </c>
-      <c r="G114" s="397"/>
-      <c r="H114" s="398"/>
+      <c r="G114" s="402"/>
+      <c r="H114" s="403"/>
       <c r="I114" s="32"/>
     </row>
     <row r="115" spans="1:9" ht="12" customHeight="1">
@@ -19406,14 +19406,14 @@
       <c r="B115" s="21">
         <v>80</v>
       </c>
-      <c r="C115" s="393" t="s">
+      <c r="C115" s="394" t="s">
         <v>108</v>
       </c>
-      <c r="D115" s="394"/>
-      <c r="E115" s="394"/>
-      <c r="F115" s="394"/>
-      <c r="G115" s="394"/>
-      <c r="H115" s="395"/>
+      <c r="D115" s="395"/>
+      <c r="E115" s="395"/>
+      <c r="F115" s="395"/>
+      <c r="G115" s="395"/>
+      <c r="H115" s="396"/>
       <c r="I115" s="32"/>
     </row>
     <row r="116" spans="1:9" ht="12" customHeight="1">
@@ -19423,16 +19423,16 @@
       <c r="B116" s="21">
         <v>81</v>
       </c>
-      <c r="C116" s="419" t="s">
+      <c r="C116" s="397" t="s">
         <v>109</v>
       </c>
-      <c r="D116" s="420"/>
-      <c r="E116" s="393" t="s">
+      <c r="D116" s="398"/>
+      <c r="E116" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F116" s="394"/>
-      <c r="G116" s="394"/>
-      <c r="H116" s="395"/>
+      <c r="F116" s="395"/>
+      <c r="G116" s="395"/>
+      <c r="H116" s="396"/>
       <c r="I116" s="32"/>
     </row>
     <row r="117" spans="1:9" ht="12" customHeight="1">
@@ -19442,16 +19442,16 @@
       <c r="B117" s="21">
         <v>82</v>
       </c>
-      <c r="C117" s="421"/>
-      <c r="D117" s="422"/>
+      <c r="C117" s="399"/>
+      <c r="D117" s="400"/>
       <c r="E117" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F117" s="396" t="s">
+      <c r="F117" s="401" t="s">
         <v>110</v>
       </c>
-      <c r="G117" s="397"/>
-      <c r="H117" s="398"/>
+      <c r="G117" s="402"/>
+      <c r="H117" s="403"/>
       <c r="I117" s="32"/>
     </row>
     <row r="118" spans="1:9" ht="12" customHeight="1">
@@ -19470,11 +19470,11 @@
       <c r="E118" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F118" s="396" t="s">
+      <c r="F118" s="401" t="s">
         <v>111</v>
       </c>
-      <c r="G118" s="397"/>
-      <c r="H118" s="398"/>
+      <c r="G118" s="402"/>
+      <c r="H118" s="403"/>
       <c r="I118" s="32"/>
     </row>
     <row r="119" spans="1:9" hidden="1">
@@ -19487,16 +19487,16 @@
       <c r="B120" s="21">
         <v>85</v>
       </c>
-      <c r="C120" s="419" t="s">
+      <c r="C120" s="397" t="s">
         <v>112</v>
       </c>
-      <c r="D120" s="420"/>
-      <c r="E120" s="393" t="s">
+      <c r="D120" s="398"/>
+      <c r="E120" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F120" s="394"/>
-      <c r="G120" s="394"/>
-      <c r="H120" s="395"/>
+      <c r="F120" s="395"/>
+      <c r="G120" s="395"/>
+      <c r="H120" s="396"/>
       <c r="I120" s="32"/>
     </row>
     <row r="121" spans="1:9" ht="12" customHeight="1">
@@ -19506,16 +19506,16 @@
       <c r="B121" s="21">
         <v>86</v>
       </c>
-      <c r="C121" s="421"/>
-      <c r="D121" s="422"/>
+      <c r="C121" s="399"/>
+      <c r="D121" s="400"/>
       <c r="E121" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F121" s="396" t="s">
+      <c r="F121" s="401" t="s">
         <v>113</v>
       </c>
-      <c r="G121" s="397"/>
-      <c r="H121" s="398"/>
+      <c r="G121" s="402"/>
+      <c r="H121" s="403"/>
       <c r="I121" s="32"/>
     </row>
     <row r="122" spans="1:9" ht="12" customHeight="1">
@@ -19534,11 +19534,11 @@
       <c r="E122" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F122" s="396" t="s">
+      <c r="F122" s="401" t="s">
         <v>111</v>
       </c>
-      <c r="G122" s="397"/>
-      <c r="H122" s="398"/>
+      <c r="G122" s="402"/>
+      <c r="H122" s="403"/>
       <c r="I122" s="32"/>
     </row>
     <row r="123" spans="1:9" ht="12" customHeight="1">
@@ -19557,11 +19557,11 @@
       <c r="E123" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F123" s="396" t="s">
+      <c r="F123" s="401" t="s">
         <v>114</v>
       </c>
-      <c r="G123" s="397"/>
-      <c r="H123" s="398"/>
+      <c r="G123" s="402"/>
+      <c r="H123" s="403"/>
       <c r="I123" s="32"/>
     </row>
     <row r="124" spans="1:9" ht="12" customHeight="1">
@@ -19580,11 +19580,11 @@
       <c r="E124" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F124" s="396" t="s">
+      <c r="F124" s="401" t="s">
         <v>115</v>
       </c>
-      <c r="G124" s="397"/>
-      <c r="H124" s="398"/>
+      <c r="G124" s="402"/>
+      <c r="H124" s="403"/>
       <c r="I124" s="32"/>
     </row>
     <row r="125" spans="1:9" hidden="1">
@@ -19597,14 +19597,14 @@
       <c r="B126" s="21">
         <v>91</v>
       </c>
-      <c r="C126" s="393" t="s">
+      <c r="C126" s="394" t="s">
         <v>116</v>
       </c>
-      <c r="D126" s="394"/>
-      <c r="E126" s="394"/>
-      <c r="F126" s="394"/>
-      <c r="G126" s="394"/>
-      <c r="H126" s="395"/>
+      <c r="D126" s="395"/>
+      <c r="E126" s="395"/>
+      <c r="F126" s="395"/>
+      <c r="G126" s="395"/>
+      <c r="H126" s="396"/>
       <c r="I126" s="32"/>
     </row>
     <row r="127" spans="1:9" ht="12" customHeight="1">
@@ -19614,16 +19614,16 @@
       <c r="B127" s="21">
         <v>92</v>
       </c>
-      <c r="C127" s="419" t="s">
+      <c r="C127" s="397" t="s">
         <v>117</v>
       </c>
-      <c r="D127" s="420"/>
-      <c r="E127" s="393" t="s">
+      <c r="D127" s="398"/>
+      <c r="E127" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F127" s="394"/>
-      <c r="G127" s="394"/>
-      <c r="H127" s="395"/>
+      <c r="F127" s="395"/>
+      <c r="G127" s="395"/>
+      <c r="H127" s="396"/>
       <c r="I127" s="32"/>
     </row>
     <row r="128" spans="1:9" ht="12" customHeight="1">
@@ -19633,16 +19633,16 @@
       <c r="B128" s="21">
         <v>93</v>
       </c>
-      <c r="C128" s="421"/>
-      <c r="D128" s="422"/>
+      <c r="C128" s="399"/>
+      <c r="D128" s="400"/>
       <c r="E128" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F128" s="444" t="s">
-        <v>44</v>
-      </c>
-      <c r="G128" s="445"/>
-      <c r="H128" s="446"/>
+      <c r="F128" s="404" t="s">
+        <v>44</v>
+      </c>
+      <c r="G128" s="405"/>
+      <c r="H128" s="406"/>
       <c r="I128" s="40"/>
     </row>
     <row r="129" spans="1:14" hidden="1">
@@ -19655,14 +19655,14 @@
       <c r="B130" s="21">
         <v>95</v>
       </c>
-      <c r="C130" s="393" t="s">
+      <c r="C130" s="394" t="s">
         <v>118</v>
       </c>
-      <c r="D130" s="394"/>
-      <c r="E130" s="394"/>
-      <c r="F130" s="394"/>
-      <c r="G130" s="394"/>
-      <c r="H130" s="395"/>
+      <c r="D130" s="395"/>
+      <c r="E130" s="395"/>
+      <c r="F130" s="395"/>
+      <c r="G130" s="395"/>
+      <c r="H130" s="396"/>
       <c r="I130" s="32"/>
     </row>
     <row r="131" spans="1:14" ht="12" customHeight="1">
@@ -19672,14 +19672,14 @@
       <c r="B131" s="21">
         <v>96</v>
       </c>
-      <c r="C131" s="393" t="s">
+      <c r="C131" s="394" t="s">
         <v>119</v>
       </c>
-      <c r="D131" s="394"/>
-      <c r="E131" s="394"/>
-      <c r="F131" s="394"/>
-      <c r="G131" s="394"/>
-      <c r="H131" s="395"/>
+      <c r="D131" s="395"/>
+      <c r="E131" s="395"/>
+      <c r="F131" s="395"/>
+      <c r="G131" s="395"/>
+      <c r="H131" s="396"/>
       <c r="I131" s="32"/>
     </row>
     <row r="132" spans="1:14" ht="12" customHeight="1">
@@ -19689,16 +19689,16 @@
       <c r="B132" s="21">
         <v>97</v>
       </c>
-      <c r="C132" s="419" t="s">
+      <c r="C132" s="397" t="s">
         <v>120</v>
       </c>
-      <c r="D132" s="420"/>
-      <c r="E132" s="393" t="s">
+      <c r="D132" s="398"/>
+      <c r="E132" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F132" s="394"/>
-      <c r="G132" s="394"/>
-      <c r="H132" s="395"/>
+      <c r="F132" s="395"/>
+      <c r="G132" s="395"/>
+      <c r="H132" s="396"/>
       <c r="I132" s="32"/>
     </row>
     <row r="133" spans="1:14" ht="12" customHeight="1">
@@ -19708,16 +19708,16 @@
       <c r="B133" s="21">
         <v>98</v>
       </c>
-      <c r="C133" s="421"/>
-      <c r="D133" s="422"/>
+      <c r="C133" s="399"/>
+      <c r="D133" s="400"/>
       <c r="E133" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F133" s="396" t="s">
+      <c r="F133" s="401" t="s">
         <v>121</v>
       </c>
-      <c r="G133" s="397"/>
-      <c r="H133" s="398"/>
+      <c r="G133" s="402"/>
+      <c r="H133" s="403"/>
       <c r="I133" s="32"/>
     </row>
     <row r="134" spans="1:14" ht="12" customHeight="1">
@@ -19727,16 +19727,16 @@
       <c r="B134" s="21">
         <v>99</v>
       </c>
-      <c r="C134" s="421"/>
-      <c r="D134" s="422"/>
+      <c r="C134" s="399"/>
+      <c r="D134" s="400"/>
       <c r="E134" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F134" s="396" t="s">
+      <c r="F134" s="401" t="s">
         <v>122</v>
       </c>
-      <c r="G134" s="397"/>
-      <c r="H134" s="398"/>
+      <c r="G134" s="402"/>
+      <c r="H134" s="403"/>
       <c r="I134" s="32"/>
     </row>
     <row r="135" spans="1:14" ht="12" customHeight="1">
@@ -19746,16 +19746,16 @@
       <c r="B135" s="21">
         <v>100</v>
       </c>
-      <c r="C135" s="421"/>
-      <c r="D135" s="422"/>
+      <c r="C135" s="399"/>
+      <c r="D135" s="400"/>
       <c r="E135" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F135" s="396" t="s">
+      <c r="F135" s="401" t="s">
         <v>123</v>
       </c>
-      <c r="G135" s="397"/>
-      <c r="H135" s="398"/>
+      <c r="G135" s="402"/>
+      <c r="H135" s="403"/>
       <c r="I135" s="32"/>
     </row>
     <row r="136" spans="1:14" ht="12" customHeight="1">
@@ -19774,11 +19774,11 @@
       <c r="E136" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F136" s="396" t="s">
+      <c r="F136" s="401" t="s">
         <v>124</v>
       </c>
-      <c r="G136" s="397"/>
-      <c r="H136" s="398"/>
+      <c r="G136" s="402"/>
+      <c r="H136" s="403"/>
       <c r="I136" s="32"/>
     </row>
     <row r="137" spans="1:14" ht="12" customHeight="1">
@@ -19797,11 +19797,11 @@
       <c r="E137" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F137" s="396" t="s">
+      <c r="F137" s="401" t="s">
         <v>125</v>
       </c>
-      <c r="G137" s="397"/>
-      <c r="H137" s="398"/>
+      <c r="G137" s="402"/>
+      <c r="H137" s="403"/>
       <c r="I137" s="32"/>
     </row>
     <row r="138" spans="1:14" ht="12" customHeight="1">
@@ -19820,11 +19820,11 @@
       <c r="E138" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F138" s="396" t="s">
+      <c r="F138" s="401" t="s">
         <v>126</v>
       </c>
-      <c r="G138" s="397"/>
-      <c r="H138" s="398"/>
+      <c r="G138" s="402"/>
+      <c r="H138" s="403"/>
       <c r="I138" s="32"/>
     </row>
     <row r="139" spans="1:14" hidden="1">
@@ -19837,16 +19837,16 @@
       <c r="B140" s="21">
         <v>105</v>
       </c>
-      <c r="C140" s="423" t="s">
+      <c r="C140" s="407" t="s">
         <v>127</v>
       </c>
-      <c r="D140" s="424"/>
-      <c r="E140" s="393" t="s">
+      <c r="D140" s="408"/>
+      <c r="E140" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F140" s="394"/>
-      <c r="G140" s="394"/>
-      <c r="H140" s="395"/>
+      <c r="F140" s="395"/>
+      <c r="G140" s="395"/>
+      <c r="H140" s="396"/>
       <c r="I140" s="32"/>
     </row>
     <row r="141" spans="1:14" ht="12" customHeight="1">
@@ -19856,16 +19856,16 @@
       <c r="B141" s="21">
         <v>106</v>
       </c>
-      <c r="C141" s="425"/>
-      <c r="D141" s="426"/>
-      <c r="E141" s="429" t="s">
+      <c r="C141" s="409"/>
+      <c r="D141" s="410"/>
+      <c r="E141" s="413" t="s">
         <v>55</v>
       </c>
-      <c r="F141" s="396" t="s">
+      <c r="F141" s="401" t="s">
         <v>128</v>
       </c>
-      <c r="G141" s="397"/>
-      <c r="H141" s="398"/>
+      <c r="G141" s="402"/>
+      <c r="H141" s="403"/>
       <c r="I141" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -19878,14 +19878,14 @@
       <c r="B142" s="21">
         <v>107</v>
       </c>
-      <c r="C142" s="427"/>
-      <c r="D142" s="428"/>
-      <c r="E142" s="430"/>
-      <c r="F142" s="396" t="s">
+      <c r="C142" s="411"/>
+      <c r="D142" s="412"/>
+      <c r="E142" s="414"/>
+      <c r="F142" s="401" t="s">
         <v>129</v>
       </c>
-      <c r="G142" s="397"/>
-      <c r="H142" s="398"/>
+      <c r="G142" s="402"/>
+      <c r="H142" s="403"/>
       <c r="I142" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19899,14 +19899,14 @@
       <c r="B143" s="21">
         <v>108</v>
       </c>
-      <c r="C143" s="393" t="s">
+      <c r="C143" s="394" t="s">
         <v>22</v>
       </c>
-      <c r="D143" s="394"/>
-      <c r="E143" s="394"/>
-      <c r="F143" s="394"/>
-      <c r="G143" s="394"/>
-      <c r="H143" s="395"/>
+      <c r="D143" s="395"/>
+      <c r="E143" s="395"/>
+      <c r="F143" s="395"/>
+      <c r="G143" s="395"/>
+      <c r="H143" s="396"/>
       <c r="I143" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19926,12 +19926,12 @@
       <c r="D144" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E144" s="393" t="s">
+      <c r="E144" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F144" s="394"/>
-      <c r="G144" s="394"/>
-      <c r="H144" s="395"/>
+      <c r="F144" s="395"/>
+      <c r="G144" s="395"/>
+      <c r="H144" s="396"/>
       <c r="I144" s="32"/>
     </row>
     <row r="145" spans="1:10" ht="12" customHeight="1">
@@ -19950,11 +19950,11 @@
       <c r="E145" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F145" s="396" t="s">
+      <c r="F145" s="401" t="s">
         <v>131</v>
       </c>
-      <c r="G145" s="397"/>
-      <c r="H145" s="398"/>
+      <c r="G145" s="402"/>
+      <c r="H145" s="403"/>
       <c r="I145" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19976,11 +19976,11 @@
       <c r="E146" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F146" s="396" t="s">
+      <c r="F146" s="401" t="s">
         <v>132</v>
       </c>
-      <c r="G146" s="397"/>
-      <c r="H146" s="398"/>
+      <c r="G146" s="402"/>
+      <c r="H146" s="403"/>
       <c r="I146" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20002,11 +20002,11 @@
       <c r="E147" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F147" s="396" t="s">
+      <c r="F147" s="401" t="s">
         <v>64</v>
       </c>
-      <c r="G147" s="397"/>
-      <c r="H147" s="398"/>
+      <c r="G147" s="402"/>
+      <c r="H147" s="403"/>
       <c r="I147" s="32"/>
     </row>
     <row r="148" spans="1:10" ht="12" customHeight="1">
@@ -20025,11 +20025,11 @@
       <c r="E148" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F148" s="416" t="s">
+      <c r="F148" s="391" t="s">
         <v>133</v>
       </c>
-      <c r="G148" s="417"/>
-      <c r="H148" s="418"/>
+      <c r="G148" s="392"/>
+      <c r="H148" s="393"/>
       <c r="I148" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20052,11 +20052,11 @@
       <c r="E149" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F149" s="416" t="s">
+      <c r="F149" s="391" t="s">
         <v>134</v>
       </c>
-      <c r="G149" s="417"/>
-      <c r="H149" s="418"/>
+      <c r="G149" s="392"/>
+      <c r="H149" s="393"/>
       <c r="I149" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20079,11 +20079,11 @@
       <c r="E150" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F150" s="416" t="s">
+      <c r="F150" s="391" t="s">
         <v>135</v>
       </c>
-      <c r="G150" s="417"/>
-      <c r="H150" s="418"/>
+      <c r="G150" s="392"/>
+      <c r="H150" s="393"/>
       <c r="I150" s="32"/>
       <c r="J150" s="10"/>
     </row>
@@ -20103,11 +20103,11 @@
       <c r="E151" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F151" s="416" t="s">
+      <c r="F151" s="391" t="s">
         <v>136</v>
       </c>
-      <c r="G151" s="417"/>
-      <c r="H151" s="418"/>
+      <c r="G151" s="392"/>
+      <c r="H151" s="393"/>
       <c r="I151" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20124,16 +20124,16 @@
       <c r="B153" s="21">
         <v>114</v>
       </c>
-      <c r="C153" s="419" t="s">
+      <c r="C153" s="397" t="s">
         <v>137</v>
       </c>
-      <c r="D153" s="420"/>
-      <c r="E153" s="393" t="s">
+      <c r="D153" s="398"/>
+      <c r="E153" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F153" s="394"/>
-      <c r="G153" s="394"/>
-      <c r="H153" s="395"/>
+      <c r="F153" s="395"/>
+      <c r="G153" s="395"/>
+      <c r="H153" s="396"/>
       <c r="I153" s="32"/>
     </row>
     <row r="154" spans="1:10" ht="12" customHeight="1">
@@ -20143,16 +20143,16 @@
       <c r="B154" s="21">
         <v>115</v>
       </c>
-      <c r="C154" s="421"/>
-      <c r="D154" s="422"/>
+      <c r="C154" s="399"/>
+      <c r="D154" s="400"/>
       <c r="E154" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F154" s="444" t="s">
-        <v>44</v>
-      </c>
-      <c r="G154" s="445"/>
-      <c r="H154" s="446"/>
+      <c r="F154" s="404" t="s">
+        <v>44</v>
+      </c>
+      <c r="G154" s="405"/>
+      <c r="H154" s="406"/>
       <c r="I154" s="40"/>
     </row>
     <row r="155" spans="1:10" ht="12" customHeight="1">
@@ -20171,11 +20171,11 @@
       <c r="E155" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F155" s="416" t="s">
+      <c r="F155" s="391" t="s">
         <v>4</v>
       </c>
-      <c r="G155" s="417"/>
-      <c r="H155" s="418"/>
+      <c r="G155" s="392"/>
+      <c r="H155" s="393"/>
       <c r="I155" s="32"/>
       <c r="J155" s="10"/>
     </row>
@@ -20195,11 +20195,11 @@
       <c r="E156" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F156" s="416" t="s">
+      <c r="F156" s="391" t="s">
         <v>138</v>
       </c>
-      <c r="G156" s="417"/>
-      <c r="H156" s="418"/>
+      <c r="G156" s="392"/>
+      <c r="H156" s="393"/>
       <c r="I156" s="32"/>
       <c r="J156" s="10"/>
     </row>
@@ -20219,11 +20219,11 @@
       <c r="E157" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F157" s="416" t="s">
+      <c r="F157" s="391" t="s">
         <v>139</v>
       </c>
-      <c r="G157" s="417"/>
-      <c r="H157" s="418"/>
+      <c r="G157" s="392"/>
+      <c r="H157" s="393"/>
       <c r="I157" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20246,9 +20246,9 @@
       <c r="E158" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F158" s="416"/>
-      <c r="G158" s="417"/>
-      <c r="H158" s="418"/>
+      <c r="F158" s="391"/>
+      <c r="G158" s="392"/>
+      <c r="H158" s="393"/>
       <c r="I158" s="32"/>
       <c r="J158" s="10"/>
     </row>
@@ -20262,14 +20262,14 @@
       <c r="B160" s="21">
         <v>117</v>
       </c>
-      <c r="C160" s="393" t="s">
+      <c r="C160" s="394" t="s">
         <v>140</v>
       </c>
-      <c r="D160" s="394"/>
-      <c r="E160" s="394"/>
-      <c r="F160" s="394"/>
-      <c r="G160" s="394"/>
-      <c r="H160" s="395"/>
+      <c r="D160" s="395"/>
+      <c r="E160" s="395"/>
+      <c r="F160" s="395"/>
+      <c r="G160" s="395"/>
+      <c r="H160" s="396"/>
       <c r="I160" s="32"/>
     </row>
     <row r="161" spans="1:9" ht="12" customHeight="1">
@@ -20279,14 +20279,14 @@
       <c r="B161" s="21">
         <v>118</v>
       </c>
-      <c r="C161" s="393" t="s">
+      <c r="C161" s="394" t="s">
         <v>141</v>
       </c>
-      <c r="D161" s="394"/>
-      <c r="E161" s="394"/>
-      <c r="F161" s="394"/>
-      <c r="G161" s="394"/>
-      <c r="H161" s="395"/>
+      <c r="D161" s="395"/>
+      <c r="E161" s="395"/>
+      <c r="F161" s="395"/>
+      <c r="G161" s="395"/>
+      <c r="H161" s="396"/>
       <c r="I161" s="42" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -20299,14 +20299,14 @@
       <c r="B162" s="21">
         <v>119</v>
       </c>
-      <c r="C162" s="393" t="s">
+      <c r="C162" s="394" t="s">
         <v>142</v>
       </c>
-      <c r="D162" s="394"/>
-      <c r="E162" s="394"/>
-      <c r="F162" s="394"/>
-      <c r="G162" s="394"/>
-      <c r="H162" s="395"/>
+      <c r="D162" s="395"/>
+      <c r="E162" s="395"/>
+      <c r="F162" s="395"/>
+      <c r="G162" s="395"/>
+      <c r="H162" s="396"/>
       <c r="I162" s="32"/>
     </row>
     <row r="163" spans="1:9" ht="12" customHeight="1">
@@ -20316,14 +20316,14 @@
       <c r="B163" s="21">
         <v>120</v>
       </c>
-      <c r="C163" s="393" t="s">
+      <c r="C163" s="394" t="s">
         <v>143</v>
       </c>
-      <c r="D163" s="394"/>
-      <c r="E163" s="394"/>
-      <c r="F163" s="394"/>
-      <c r="G163" s="394"/>
-      <c r="H163" s="395"/>
+      <c r="D163" s="395"/>
+      <c r="E163" s="395"/>
+      <c r="F163" s="395"/>
+      <c r="G163" s="395"/>
+      <c r="H163" s="396"/>
       <c r="I163" s="32"/>
     </row>
     <row r="164" spans="1:9" ht="12" customHeight="1">
@@ -20333,14 +20333,14 @@
       <c r="B164" s="21">
         <v>121</v>
       </c>
-      <c r="C164" s="393" t="s">
+      <c r="C164" s="394" t="s">
         <v>144</v>
       </c>
-      <c r="D164" s="394"/>
-      <c r="E164" s="394"/>
-      <c r="F164" s="394"/>
-      <c r="G164" s="394"/>
-      <c r="H164" s="395"/>
+      <c r="D164" s="395"/>
+      <c r="E164" s="395"/>
+      <c r="F164" s="395"/>
+      <c r="G164" s="395"/>
+      <c r="H164" s="396"/>
       <c r="I164" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20353,16 +20353,16 @@
       <c r="B165" s="21">
         <v>122</v>
       </c>
-      <c r="C165" s="419" t="s">
+      <c r="C165" s="397" t="s">
         <v>145</v>
       </c>
-      <c r="D165" s="420"/>
-      <c r="E165" s="393" t="s">
+      <c r="D165" s="398"/>
+      <c r="E165" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F165" s="394"/>
-      <c r="G165" s="394"/>
-      <c r="H165" s="395"/>
+      <c r="F165" s="395"/>
+      <c r="G165" s="395"/>
+      <c r="H165" s="396"/>
       <c r="I165" s="32"/>
     </row>
     <row r="166" spans="1:9" ht="12" customHeight="1">
@@ -20372,16 +20372,16 @@
       <c r="B166" s="21">
         <v>123</v>
       </c>
-      <c r="C166" s="421"/>
-      <c r="D166" s="422"/>
+      <c r="C166" s="399"/>
+      <c r="D166" s="400"/>
       <c r="E166" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F166" s="396" t="s">
+      <c r="F166" s="401" t="s">
         <v>146</v>
       </c>
-      <c r="G166" s="397"/>
-      <c r="H166" s="398"/>
+      <c r="G166" s="402"/>
+      <c r="H166" s="403"/>
       <c r="I166" s="32"/>
     </row>
     <row r="167" spans="1:9" ht="12" customHeight="1">
@@ -20400,11 +20400,11 @@
       <c r="E167" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F167" s="396" t="s">
+      <c r="F167" s="401" t="s">
         <v>147</v>
       </c>
-      <c r="G167" s="397"/>
-      <c r="H167" s="398"/>
+      <c r="G167" s="402"/>
+      <c r="H167" s="403"/>
       <c r="I167" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20426,11 +20426,11 @@
       <c r="E168" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F168" s="396" t="s">
+      <c r="F168" s="401" t="s">
         <v>148</v>
       </c>
-      <c r="G168" s="397"/>
-      <c r="H168" s="398"/>
+      <c r="G168" s="402"/>
+      <c r="H168" s="403"/>
       <c r="I168" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20446,14 +20446,14 @@
       <c r="B170" s="21">
         <v>127</v>
       </c>
-      <c r="C170" s="393" t="s">
+      <c r="C170" s="394" t="s">
         <v>17</v>
       </c>
-      <c r="D170" s="394"/>
-      <c r="E170" s="394"/>
-      <c r="F170" s="394"/>
-      <c r="G170" s="394"/>
-      <c r="H170" s="395"/>
+      <c r="D170" s="395"/>
+      <c r="E170" s="395"/>
+      <c r="F170" s="395"/>
+      <c r="G170" s="395"/>
+      <c r="H170" s="396"/>
       <c r="I170" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20466,14 +20466,14 @@
       <c r="B171" s="21">
         <v>128</v>
       </c>
-      <c r="C171" s="393" t="s">
+      <c r="C171" s="394" t="s">
         <v>149</v>
       </c>
-      <c r="D171" s="394"/>
-      <c r="E171" s="394"/>
-      <c r="F171" s="394"/>
-      <c r="G171" s="394"/>
-      <c r="H171" s="395"/>
+      <c r="D171" s="395"/>
+      <c r="E171" s="395"/>
+      <c r="F171" s="395"/>
+      <c r="G171" s="395"/>
+      <c r="H171" s="396"/>
       <c r="I171" s="32"/>
     </row>
     <row r="172" spans="1:9" ht="12" customHeight="1">
@@ -20483,14 +20483,14 @@
       <c r="B172" s="21">
         <v>129</v>
       </c>
-      <c r="C172" s="393" t="s">
+      <c r="C172" s="394" t="s">
         <v>150</v>
       </c>
-      <c r="D172" s="394"/>
-      <c r="E172" s="394"/>
-      <c r="F172" s="394"/>
-      <c r="G172" s="394"/>
-      <c r="H172" s="395"/>
+      <c r="D172" s="395"/>
+      <c r="E172" s="395"/>
+      <c r="F172" s="395"/>
+      <c r="G172" s="395"/>
+      <c r="H172" s="396"/>
       <c r="I172" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20503,14 +20503,14 @@
       <c r="B173" s="21">
         <v>130</v>
       </c>
-      <c r="C173" s="393" t="s">
+      <c r="C173" s="394" t="s">
         <v>151</v>
       </c>
-      <c r="D173" s="394"/>
-      <c r="E173" s="394"/>
-      <c r="F173" s="394"/>
-      <c r="G173" s="394"/>
-      <c r="H173" s="395"/>
+      <c r="D173" s="395"/>
+      <c r="E173" s="395"/>
+      <c r="F173" s="395"/>
+      <c r="G173" s="395"/>
+      <c r="H173" s="396"/>
       <c r="I173" s="32"/>
     </row>
     <row r="174" spans="1:9" ht="12" customHeight="1">
@@ -20520,14 +20520,14 @@
       <c r="B174" s="21">
         <v>131</v>
       </c>
-      <c r="C174" s="393" t="s">
+      <c r="C174" s="394" t="s">
         <v>152</v>
       </c>
-      <c r="D174" s="394"/>
-      <c r="E174" s="394"/>
-      <c r="F174" s="394"/>
-      <c r="G174" s="394"/>
-      <c r="H174" s="395"/>
+      <c r="D174" s="395"/>
+      <c r="E174" s="395"/>
+      <c r="F174" s="395"/>
+      <c r="G174" s="395"/>
+      <c r="H174" s="396"/>
       <c r="I174" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20540,16 +20540,16 @@
       <c r="B175" s="21">
         <v>132</v>
       </c>
-      <c r="C175" s="419" t="s">
+      <c r="C175" s="397" t="s">
         <v>153</v>
       </c>
-      <c r="D175" s="420"/>
-      <c r="E175" s="393" t="s">
+      <c r="D175" s="398"/>
+      <c r="E175" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F175" s="394"/>
-      <c r="G175" s="394"/>
-      <c r="H175" s="395"/>
+      <c r="F175" s="395"/>
+      <c r="G175" s="395"/>
+      <c r="H175" s="396"/>
       <c r="I175" s="32"/>
     </row>
     <row r="176" spans="1:9" ht="12" customHeight="1">
@@ -20559,16 +20559,16 @@
       <c r="B176" s="21">
         <v>133</v>
       </c>
-      <c r="C176" s="421"/>
-      <c r="D176" s="422"/>
+      <c r="C176" s="399"/>
+      <c r="D176" s="400"/>
       <c r="E176" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F176" s="396" t="s">
+      <c r="F176" s="401" t="s">
         <v>128</v>
       </c>
-      <c r="G176" s="397"/>
-      <c r="H176" s="398"/>
+      <c r="G176" s="402"/>
+      <c r="H176" s="403"/>
       <c r="I176" s="32"/>
     </row>
     <row r="177" spans="1:14" ht="12" customHeight="1">
@@ -20578,16 +20578,16 @@
       <c r="B177" s="21">
         <v>134</v>
       </c>
-      <c r="C177" s="421"/>
-      <c r="D177" s="422"/>
+      <c r="C177" s="399"/>
+      <c r="D177" s="400"/>
       <c r="E177" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F177" s="396" t="s">
+      <c r="F177" s="401" t="s">
         <v>154</v>
       </c>
-      <c r="G177" s="397"/>
-      <c r="H177" s="398"/>
+      <c r="G177" s="402"/>
+      <c r="H177" s="403"/>
       <c r="I177" s="32"/>
     </row>
     <row r="178" spans="1:14" ht="12" customHeight="1">
@@ -20606,11 +20606,11 @@
       <c r="E178" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F178" s="396" t="s">
+      <c r="F178" s="401" t="s">
         <v>155</v>
       </c>
-      <c r="G178" s="397"/>
-      <c r="H178" s="398"/>
+      <c r="G178" s="402"/>
+      <c r="H178" s="403"/>
       <c r="I178" s="32"/>
     </row>
     <row r="179" spans="1:14" hidden="1">
@@ -20623,14 +20623,14 @@
       <c r="B180" s="21">
         <v>137</v>
       </c>
-      <c r="C180" s="393" t="s">
+      <c r="C180" s="394" t="s">
         <v>156</v>
       </c>
-      <c r="D180" s="394"/>
-      <c r="E180" s="394"/>
-      <c r="F180" s="394"/>
-      <c r="G180" s="394"/>
-      <c r="H180" s="395"/>
+      <c r="D180" s="395"/>
+      <c r="E180" s="395"/>
+      <c r="F180" s="395"/>
+      <c r="G180" s="395"/>
+      <c r="H180" s="396"/>
       <c r="I180" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20643,14 +20643,14 @@
       <c r="B181" s="21">
         <v>138</v>
       </c>
-      <c r="C181" s="393" t="s">
+      <c r="C181" s="394" t="s">
         <v>21</v>
       </c>
-      <c r="D181" s="394"/>
-      <c r="E181" s="394"/>
-      <c r="F181" s="394"/>
-      <c r="G181" s="394"/>
-      <c r="H181" s="395"/>
+      <c r="D181" s="395"/>
+      <c r="E181" s="395"/>
+      <c r="F181" s="395"/>
+      <c r="G181" s="395"/>
+      <c r="H181" s="396"/>
       <c r="I181" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20663,16 +20663,16 @@
       <c r="B182" s="21">
         <v>139</v>
       </c>
-      <c r="C182" s="419" t="s">
+      <c r="C182" s="397" t="s">
         <v>157</v>
       </c>
-      <c r="D182" s="420"/>
-      <c r="E182" s="393" t="s">
+      <c r="D182" s="398"/>
+      <c r="E182" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F182" s="394"/>
-      <c r="G182" s="394"/>
-      <c r="H182" s="395"/>
+      <c r="F182" s="395"/>
+      <c r="G182" s="395"/>
+      <c r="H182" s="396"/>
       <c r="I182" s="32"/>
     </row>
     <row r="183" spans="1:14" ht="12" customHeight="1">
@@ -20682,16 +20682,16 @@
       <c r="B183" s="21">
         <v>140</v>
       </c>
-      <c r="C183" s="421"/>
-      <c r="D183" s="422"/>
+      <c r="C183" s="399"/>
+      <c r="D183" s="400"/>
       <c r="E183" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F183" s="396" t="s">
-        <v>44</v>
-      </c>
-      <c r="G183" s="397"/>
-      <c r="H183" s="398"/>
+      <c r="F183" s="401" t="s">
+        <v>44</v>
+      </c>
+      <c r="G183" s="402"/>
+      <c r="H183" s="403"/>
       <c r="I183" s="32"/>
     </row>
     <row r="184" spans="1:14" hidden="1">
@@ -20704,16 +20704,16 @@
       <c r="B185" s="21">
         <v>142</v>
       </c>
-      <c r="C185" s="419" t="s">
+      <c r="C185" s="397" t="s">
         <v>158</v>
       </c>
-      <c r="D185" s="420"/>
-      <c r="E185" s="393" t="s">
+      <c r="D185" s="398"/>
+      <c r="E185" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F185" s="394"/>
-      <c r="G185" s="394"/>
-      <c r="H185" s="395"/>
+      <c r="F185" s="395"/>
+      <c r="G185" s="395"/>
+      <c r="H185" s="396"/>
       <c r="I185" s="32"/>
     </row>
     <row r="186" spans="1:14" ht="12" customHeight="1">
@@ -20723,16 +20723,16 @@
       <c r="B186" s="21">
         <v>143</v>
       </c>
-      <c r="C186" s="421"/>
-      <c r="D186" s="422"/>
+      <c r="C186" s="399"/>
+      <c r="D186" s="400"/>
       <c r="E186" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F186" s="396" t="s">
+      <c r="F186" s="401" t="s">
         <v>159</v>
       </c>
-      <c r="G186" s="397"/>
-      <c r="H186" s="398"/>
+      <c r="G186" s="402"/>
+      <c r="H186" s="403"/>
       <c r="I186" s="32"/>
     </row>
     <row r="187" spans="1:14" ht="12" customHeight="1">
@@ -20742,16 +20742,16 @@
       <c r="B187" s="21">
         <v>144</v>
       </c>
-      <c r="C187" s="421"/>
-      <c r="D187" s="422"/>
+      <c r="C187" s="399"/>
+      <c r="D187" s="400"/>
       <c r="E187" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F187" s="396" t="s">
+      <c r="F187" s="401" t="s">
         <v>160</v>
       </c>
-      <c r="G187" s="397"/>
-      <c r="H187" s="398"/>
+      <c r="G187" s="402"/>
+      <c r="H187" s="403"/>
       <c r="I187" s="32"/>
     </row>
     <row r="188" spans="1:14" ht="12" customHeight="1">
@@ -20770,11 +20770,11 @@
       <c r="E188" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F188" s="416" t="s">
+      <c r="F188" s="391" t="s">
         <v>161</v>
       </c>
-      <c r="G188" s="417"/>
-      <c r="H188" s="418"/>
+      <c r="G188" s="392"/>
+      <c r="H188" s="393"/>
       <c r="I188" s="32"/>
       <c r="J188" s="10"/>
     </row>
@@ -20794,11 +20794,11 @@
       <c r="E189" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F189" s="416" t="s">
+      <c r="F189" s="391" t="s">
         <v>162</v>
       </c>
-      <c r="G189" s="417"/>
-      <c r="H189" s="418"/>
+      <c r="G189" s="392"/>
+      <c r="H189" s="393"/>
       <c r="I189" s="32"/>
       <c r="J189" s="10"/>
     </row>
@@ -20818,11 +20818,11 @@
       <c r="E190" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="F190" s="416" t="s">
+      <c r="F190" s="391" t="s">
         <v>163</v>
       </c>
-      <c r="G190" s="417"/>
-      <c r="H190" s="418"/>
+      <c r="G190" s="392"/>
+      <c r="H190" s="393"/>
       <c r="I190" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -20885,104 +20885,63 @@
     </row>
   </sheetData>
   <mergeCells count="169">
-    <mergeCell ref="F188:H188"/>
-    <mergeCell ref="F189:H189"/>
-    <mergeCell ref="F190:H190"/>
-    <mergeCell ref="C180:H180"/>
-    <mergeCell ref="C181:H181"/>
-    <mergeCell ref="C182:D183"/>
-    <mergeCell ref="E182:H182"/>
-    <mergeCell ref="F183:H183"/>
-    <mergeCell ref="C185:D187"/>
-    <mergeCell ref="E185:H185"/>
-    <mergeCell ref="F186:H186"/>
-    <mergeCell ref="F187:H187"/>
-    <mergeCell ref="C174:H174"/>
-    <mergeCell ref="C175:D177"/>
-    <mergeCell ref="E175:H175"/>
-    <mergeCell ref="F176:H176"/>
-    <mergeCell ref="F177:H177"/>
-    <mergeCell ref="F178:H178"/>
-    <mergeCell ref="F167:H167"/>
-    <mergeCell ref="F168:H168"/>
-    <mergeCell ref="C170:H170"/>
-    <mergeCell ref="C171:H171"/>
-    <mergeCell ref="C172:H172"/>
-    <mergeCell ref="C173:H173"/>
-    <mergeCell ref="C162:H162"/>
-    <mergeCell ref="C163:H163"/>
-    <mergeCell ref="C164:H164"/>
-    <mergeCell ref="C165:D166"/>
-    <mergeCell ref="E165:H165"/>
-    <mergeCell ref="F166:H166"/>
-    <mergeCell ref="F155:H155"/>
-    <mergeCell ref="F156:H156"/>
-    <mergeCell ref="F157:H157"/>
-    <mergeCell ref="F158:H158"/>
-    <mergeCell ref="C160:H160"/>
-    <mergeCell ref="C161:H161"/>
-    <mergeCell ref="F149:H149"/>
-    <mergeCell ref="F150:H150"/>
-    <mergeCell ref="F151:H151"/>
-    <mergeCell ref="C153:D154"/>
-    <mergeCell ref="E153:H153"/>
-    <mergeCell ref="F154:H154"/>
-    <mergeCell ref="C143:H143"/>
-    <mergeCell ref="E144:H144"/>
-    <mergeCell ref="F145:H145"/>
-    <mergeCell ref="F146:H146"/>
-    <mergeCell ref="F147:H147"/>
-    <mergeCell ref="F148:H148"/>
-    <mergeCell ref="F137:H137"/>
-    <mergeCell ref="F138:H138"/>
-    <mergeCell ref="C140:D142"/>
-    <mergeCell ref="E140:H140"/>
-    <mergeCell ref="E141:E142"/>
-    <mergeCell ref="F141:H141"/>
-    <mergeCell ref="F142:H142"/>
-    <mergeCell ref="C132:D135"/>
-    <mergeCell ref="E132:H132"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="F134:H134"/>
-    <mergeCell ref="F135:H135"/>
-    <mergeCell ref="F136:H136"/>
-    <mergeCell ref="C126:H126"/>
-    <mergeCell ref="C127:D128"/>
-    <mergeCell ref="E127:H127"/>
-    <mergeCell ref="F128:H128"/>
-    <mergeCell ref="C130:H130"/>
-    <mergeCell ref="C131:H131"/>
-    <mergeCell ref="C120:D121"/>
-    <mergeCell ref="E120:H120"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="F122:H122"/>
-    <mergeCell ref="F123:H123"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="C115:H115"/>
-    <mergeCell ref="C116:D117"/>
-    <mergeCell ref="E116:H116"/>
-    <mergeCell ref="F117:H117"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="F110:H110"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="E112:H112"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="C104:H104"/>
-    <mergeCell ref="C105:H105"/>
-    <mergeCell ref="C106:D107"/>
-    <mergeCell ref="E106:H106"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="F97:H97"/>
-    <mergeCell ref="F98:H98"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:H22"/>
+    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:D35"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:D39"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="C44:H44"/>
+    <mergeCell ref="C45:D49"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="C54:D57"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="F58:H58"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="C50:D51"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="C78:D79"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="F80:H80"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="C60:H60"/>
+    <mergeCell ref="C61:D63"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="G70:H70"/>
     <mergeCell ref="F88:H88"/>
     <mergeCell ref="F89:H89"/>
     <mergeCell ref="F90:H90"/>
@@ -20997,63 +20956,104 @@
     <mergeCell ref="F85:H85"/>
     <mergeCell ref="F86:H86"/>
     <mergeCell ref="F87:H87"/>
-    <mergeCell ref="G74:H74"/>
-    <mergeCell ref="C78:D79"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="F80:H80"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="C60:H60"/>
-    <mergeCell ref="C61:D63"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="C54:D57"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="F58:H58"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="C50:D51"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="C44:H44"/>
-    <mergeCell ref="C45:D49"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:D35"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C37:D39"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C20:H22"/>
-    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="C104:H104"/>
+    <mergeCell ref="C105:H105"/>
+    <mergeCell ref="C106:D107"/>
+    <mergeCell ref="E106:H106"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="F97:H97"/>
+    <mergeCell ref="F98:H98"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="C115:H115"/>
+    <mergeCell ref="C116:D117"/>
+    <mergeCell ref="E116:H116"/>
+    <mergeCell ref="F117:H117"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="F110:H110"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="E112:H112"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="C127:D128"/>
+    <mergeCell ref="E127:H127"/>
+    <mergeCell ref="F128:H128"/>
+    <mergeCell ref="C130:H130"/>
+    <mergeCell ref="C131:H131"/>
+    <mergeCell ref="C120:D121"/>
+    <mergeCell ref="E120:H120"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="F122:H122"/>
+    <mergeCell ref="F123:H123"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="F137:H137"/>
+    <mergeCell ref="F138:H138"/>
+    <mergeCell ref="C140:D142"/>
+    <mergeCell ref="E140:H140"/>
+    <mergeCell ref="E141:E142"/>
+    <mergeCell ref="F141:H141"/>
+    <mergeCell ref="F142:H142"/>
+    <mergeCell ref="C132:D135"/>
+    <mergeCell ref="E132:H132"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="F134:H134"/>
+    <mergeCell ref="F135:H135"/>
+    <mergeCell ref="F136:H136"/>
+    <mergeCell ref="F149:H149"/>
+    <mergeCell ref="F150:H150"/>
+    <mergeCell ref="F151:H151"/>
+    <mergeCell ref="C153:D154"/>
+    <mergeCell ref="E153:H153"/>
+    <mergeCell ref="F154:H154"/>
+    <mergeCell ref="C143:H143"/>
+    <mergeCell ref="E144:H144"/>
+    <mergeCell ref="F145:H145"/>
+    <mergeCell ref="F146:H146"/>
+    <mergeCell ref="F147:H147"/>
+    <mergeCell ref="F148:H148"/>
+    <mergeCell ref="C162:H162"/>
+    <mergeCell ref="C163:H163"/>
+    <mergeCell ref="C164:H164"/>
+    <mergeCell ref="C165:D166"/>
+    <mergeCell ref="E165:H165"/>
+    <mergeCell ref="F166:H166"/>
+    <mergeCell ref="F155:H155"/>
+    <mergeCell ref="F156:H156"/>
+    <mergeCell ref="F157:H157"/>
+    <mergeCell ref="F158:H158"/>
+    <mergeCell ref="C160:H160"/>
+    <mergeCell ref="C161:H161"/>
+    <mergeCell ref="C174:H174"/>
+    <mergeCell ref="C175:D177"/>
+    <mergeCell ref="E175:H175"/>
+    <mergeCell ref="F176:H176"/>
+    <mergeCell ref="F177:H177"/>
+    <mergeCell ref="F178:H178"/>
+    <mergeCell ref="F167:H167"/>
+    <mergeCell ref="F168:H168"/>
+    <mergeCell ref="C170:H170"/>
+    <mergeCell ref="C171:H171"/>
+    <mergeCell ref="C172:H172"/>
+    <mergeCell ref="C173:H173"/>
+    <mergeCell ref="F188:H188"/>
+    <mergeCell ref="F189:H189"/>
+    <mergeCell ref="F190:H190"/>
+    <mergeCell ref="C180:H180"/>
+    <mergeCell ref="C181:H181"/>
+    <mergeCell ref="C182:D183"/>
+    <mergeCell ref="E182:H182"/>
+    <mergeCell ref="F183:H183"/>
+    <mergeCell ref="C185:D187"/>
+    <mergeCell ref="E185:H185"/>
+    <mergeCell ref="F186:H186"/>
+    <mergeCell ref="F187:H187"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
@@ -21179,7 +21179,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="206" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C7" s="207" t="s">
         <v>269</v>
@@ -21205,7 +21205,7 @@
         <v>309</v>
       </c>
       <c r="J7" s="270" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30">
@@ -21555,7 +21555,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="211" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C19" s="194" t="s">
         <v>274</v>
@@ -21578,10 +21578,10 @@
         <v>307</v>
       </c>
       <c r="I19" s="264" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="J19" s="270" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="45">
@@ -21623,7 +21623,7 @@
         <v>3</v>
       </c>
       <c r="B21" s="210" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C21" s="213" t="s">
         <v>272</v>
@@ -21657,7 +21657,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="210" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="C22" s="213" t="s">
         <v>272</v>
@@ -21691,7 +21691,7 @@
         <v>5</v>
       </c>
       <c r="B23" s="244" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="C23" s="243" t="s">
         <v>272</v>
@@ -22623,7 +22623,7 @@
     <row r="53" spans="1:10" ht="45">
       <c r="A53" s="241"/>
       <c r="B53" s="217" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C53" s="186"/>
       <c r="D53" s="1"/>
@@ -29803,7 +29803,7 @@
     </row>
     <row r="10" spans="1:6" ht="51">
       <c r="A10" s="278" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B10" s="280" t="s">
         <v>345</v>
@@ -30128,12 +30128,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="A26:F26"/>
@@ -30141,6 +30135,12 @@
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>
